--- a/Group_milestones.xlsx
+++ b/Group_milestones.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="154" documentId="8_{E3DD19CA-42A4-4FC4-9F7E-AFC078DE9187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{17F94C1E-8CBB-4B29-9E0B-4EDAFDE96E87}"/>
+  <xr:revisionPtr revIDLastSave="170" documentId="8_{E3DD19CA-42A4-4FC4-9F7E-AFC078DE9187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDFB911E-7937-4E21-ADD4-F23BA8FBE6F8}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="824" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView minimized="1" xWindow="2898" yWindow="2898" windowWidth="17280" windowHeight="10254" tabRatio="824" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="52" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="36">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
   <si>
     <t>Notes</t>
   </si>
@@ -185,9 +185,6 @@
     <t>MCTR1: Enclosure v1 test, ICD complete with- MCTR2?</t>
   </si>
   <si>
-    <t>MCTR1: Enclosure v1 design</t>
-  </si>
-  <si>
     <t>Shared milestone calendar sodat ons kan sien wanneer wie wat gedoen wil he, en sodat ons n volle prentjie het</t>
   </si>
   <si>
@@ -211,6 +208,12 @@
   <si>
     <t>MCTR1: Gearbox design</t>
   </si>
+  <si>
+    <t>MCTR1: Carraige v2 design</t>
+  </si>
+  <si>
+    <t>MCTR1: Carriage v2 build</t>
+  </si>
 </sst>
 </file>
 
@@ -223,7 +226,7 @@
     <numFmt numFmtId="167" formatCode="mmmm\ yyyy"/>
     <numFmt numFmtId="168" formatCode="dddd"/>
   </numFmts>
-  <fonts count="37" x14ac:knownFonts="1">
+  <fonts count="38" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -461,6 +464,13 @@
       <name val="Seaford"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <strike/>
+      <sz val="10"/>
+      <color theme="2" tint="-0.89996032593768116"/>
+      <name val="Seaford"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -689,7 +699,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="151">
+  <cellXfs count="158">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -902,62 +912,185 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" indent="1"/>
     </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -968,156 +1101,56 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="4">
@@ -1281,6 +1314,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1490,7 +1527,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R15"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.6" x14ac:dyDescent="0.6"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.3" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="4" width="5.5546875" style="3" customWidth="1"/>
     <col min="5" max="9" width="10.5546875" style="3" customWidth="1"/>
@@ -1502,7 +1539,7 @@
     <col min="19" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="1" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1544,7 +1581,7 @@
       <c r="Q2" s="6"/>
       <c r="R2" s="4"/>
     </row>
-    <row r="3" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="2.2000000000000002">
+    <row r="3" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="2.15">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="8"/>
@@ -1564,7 +1601,7 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -1578,15 +1615,15 @@
       <c r="K4" s="12"/>
       <c r="L4" s="11"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="78" t="s">
+      <c r="N4" s="134" t="s">
         <v>10</v>
       </c>
-      <c r="O4" s="78"/>
-      <c r="P4" s="78"/>
-      <c r="Q4" s="78"/>
+      <c r="O4" s="134"/>
+      <c r="P4" s="134"/>
+      <c r="Q4" s="134"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1"/>
       <c r="B5" s="11"/>
       <c r="C5" s="13" t="s">
@@ -1604,13 +1641,13 @@
       <c r="K5" s="15"/>
       <c r="L5" s="16"/>
       <c r="M5" s="4"/>
-      <c r="N5" s="78"/>
-      <c r="O5" s="78"/>
-      <c r="P5" s="78"/>
-      <c r="Q5" s="78"/>
+      <c r="N5" s="134"/>
+      <c r="O5" s="134"/>
+      <c r="P5" s="134"/>
+      <c r="Q5" s="134"/>
       <c r="R5" s="1"/>
     </row>
-    <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1"/>
       <c r="B6" s="11"/>
       <c r="C6" s="17"/>
@@ -1624,13 +1661,13 @@
       <c r="K6" s="20"/>
       <c r="L6" s="19"/>
       <c r="M6" s="4"/>
-      <c r="N6" s="78"/>
-      <c r="O6" s="78"/>
-      <c r="P6" s="78"/>
-      <c r="Q6" s="78"/>
+      <c r="N6" s="134"/>
+      <c r="O6" s="134"/>
+      <c r="P6" s="134"/>
+      <c r="Q6" s="134"/>
       <c r="R6" s="1"/>
     </row>
-    <row r="7" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1"/>
       <c r="B7" s="11"/>
       <c r="C7" s="13" t="s">
@@ -1654,7 +1691,7 @@
       <c r="Q7" s="11"/>
       <c r="R7" s="1"/>
     </row>
-    <row r="8" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="8" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="1"/>
       <c r="B8" s="11"/>
       <c r="C8" s="17"/>
@@ -1678,7 +1715,7 @@
       </c>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="9" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="1"/>
       <c r="B9" s="11"/>
       <c r="C9" s="13" t="s">
@@ -1702,7 +1739,7 @@
       <c r="Q9" s="11"/>
       <c r="R9" s="1"/>
     </row>
-    <row r="10" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="10" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="1"/>
       <c r="B10" s="11"/>
       <c r="C10" s="24"/>
@@ -1728,7 +1765,7 @@
       <c r="Q10" s="18"/>
       <c r="R10" s="1"/>
     </row>
-    <row r="11" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1"/>
       <c r="B11" s="11"/>
       <c r="C11" s="24"/>
@@ -1748,7 +1785,7 @@
       <c r="Q11" s="18"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="12" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="1"/>
       <c r="B12" s="11"/>
       <c r="C12" s="13" t="s">
@@ -1772,7 +1809,7 @@
       <c r="Q12" s="18"/>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="13" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="1"/>
       <c r="B13" s="11"/>
       <c r="C13" s="25"/>
@@ -1794,7 +1831,7 @@
       <c r="Q13" s="18"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="14" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1"/>
       <c r="B14" s="11"/>
       <c r="C14" s="18"/>
@@ -1814,7 +1851,7 @@
       <c r="Q14" s="18"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="15" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1848,8 +1885,8 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AP41"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="12.9" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:AP40"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="12.6" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="3" width="5.5546875" style="3" customWidth="1"/>
     <col min="4" max="4" width="15.5546875" style="3" customWidth="1"/>
@@ -1867,7 +1904,7 @@
     <col min="35" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1901,42 +1938,42 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="2.2000000000000002">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="2.15">
       <c r="A2" s="29"/>
-      <c r="C2" s="91">
+      <c r="C2" s="114">
         <f ca="1">DATE(About!P8,9,1)</f>
         <v>46266</v>
       </c>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
-      <c r="H2" s="91"/>
-      <c r="I2" s="91"/>
-      <c r="J2" s="91"/>
-      <c r="K2" s="91"/>
-      <c r="L2" s="91"/>
-      <c r="M2" s="91"/>
-      <c r="N2" s="91"/>
-      <c r="O2" s="91"/>
-      <c r="P2" s="91"/>
-      <c r="Q2" s="91"/>
-      <c r="R2" s="91"/>
-      <c r="S2" s="91"/>
-      <c r="T2" s="91"/>
-      <c r="U2" s="91"/>
-      <c r="V2" s="91"/>
-      <c r="W2" s="91"/>
-      <c r="X2" s="91"/>
-      <c r="Y2" s="91"/>
-      <c r="Z2" s="91"/>
-      <c r="AA2" s="91"/>
-      <c r="AB2" s="91"/>
-      <c r="AC2" s="91"/>
-      <c r="AD2" s="91"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="114"/>
+      <c r="O2" s="114"/>
+      <c r="P2" s="114"/>
+      <c r="Q2" s="114"/>
+      <c r="R2" s="114"/>
+      <c r="S2" s="114"/>
+      <c r="T2" s="114"/>
+      <c r="U2" s="114"/>
+      <c r="V2" s="114"/>
+      <c r="W2" s="114"/>
+      <c r="X2" s="114"/>
+      <c r="Y2" s="114"/>
+      <c r="Z2" s="114"/>
+      <c r="AA2" s="114"/>
+      <c r="AB2" s="114"/>
+      <c r="AC2" s="114"/>
+      <c r="AD2" s="114"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="2.2000000000000002">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="2.15">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -1956,114 +1993,114 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A4" s="35"/>
-      <c r="C4" s="82">
+      <c r="C4" s="115">
         <f ca="1">C5</f>
         <v>46264</v>
       </c>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82">
+      <c r="D4" s="115"/>
+      <c r="E4" s="115">
         <f ca="1">E5</f>
         <v>46265</v>
       </c>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82">
+      <c r="F4" s="115"/>
+      <c r="G4" s="115">
         <f ca="1">G5</f>
         <v>46266</v>
       </c>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82">
+      <c r="H4" s="115"/>
+      <c r="I4" s="115">
         <f ca="1">I5</f>
         <v>46267</v>
       </c>
-      <c r="J4" s="82"/>
-      <c r="K4" s="82">
+      <c r="J4" s="115"/>
+      <c r="K4" s="115">
         <f ca="1">K5</f>
         <v>46268</v>
       </c>
-      <c r="L4" s="82"/>
-      <c r="M4" s="82"/>
+      <c r="L4" s="115"/>
+      <c r="M4" s="115"/>
       <c r="N4" s="37"/>
-      <c r="O4" s="82">
+      <c r="O4" s="115">
         <f ca="1">O5</f>
         <v>46269</v>
       </c>
-      <c r="P4" s="82"/>
-      <c r="Q4" s="82"/>
-      <c r="R4" s="82"/>
-      <c r="S4" s="82"/>
-      <c r="T4" s="82"/>
-      <c r="U4" s="82"/>
-      <c r="V4" s="82"/>
-      <c r="W4" s="82">
+      <c r="P4" s="115"/>
+      <c r="Q4" s="115"/>
+      <c r="R4" s="115"/>
+      <c r="S4" s="115"/>
+      <c r="T4" s="115"/>
+      <c r="U4" s="115"/>
+      <c r="V4" s="115"/>
+      <c r="W4" s="115">
         <f ca="1">W5</f>
         <v>46270</v>
       </c>
-      <c r="X4" s="82"/>
-      <c r="Y4" s="82"/>
-      <c r="Z4" s="82"/>
-      <c r="AA4" s="82"/>
-      <c r="AB4" s="82"/>
-      <c r="AC4" s="82"/>
-      <c r="AD4" s="82"/>
+      <c r="X4" s="115"/>
+      <c r="Y4" s="115"/>
+      <c r="Z4" s="115"/>
+      <c r="AA4" s="115"/>
+      <c r="AB4" s="115"/>
+      <c r="AC4" s="115"/>
+      <c r="AD4" s="115"/>
       <c r="AF4" s="38"/>
       <c r="AG4" s="39"/>
       <c r="AH4" s="39"/>
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1"/>
-      <c r="C5" s="89">
+      <c r="C5" s="116">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46264</v>
       </c>
-      <c r="D5" s="90"/>
-      <c r="E5" s="89">
+      <c r="D5" s="118"/>
+      <c r="E5" s="116">
         <f ca="1">C5+1</f>
         <v>46265</v>
       </c>
-      <c r="F5" s="90"/>
-      <c r="G5" s="89">
+      <c r="F5" s="118"/>
+      <c r="G5" s="116">
         <f ca="1">E5+1</f>
         <v>46266</v>
       </c>
-      <c r="H5" s="90"/>
-      <c r="I5" s="89">
+      <c r="H5" s="118"/>
+      <c r="I5" s="116">
         <f ca="1">G5+1</f>
         <v>46267</v>
       </c>
-      <c r="J5" s="90"/>
-      <c r="K5" s="89">
+      <c r="J5" s="118"/>
+      <c r="K5" s="116">
         <f ca="1">I5+1</f>
         <v>46268</v>
       </c>
-      <c r="L5" s="92"/>
-      <c r="M5" s="92"/>
+      <c r="L5" s="117"/>
+      <c r="M5" s="117"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="89">
+      <c r="O5" s="116">
         <f ca="1">K5+1</f>
         <v>46269</v>
       </c>
-      <c r="P5" s="92"/>
-      <c r="Q5" s="92"/>
-      <c r="R5" s="92"/>
-      <c r="S5" s="92"/>
-      <c r="T5" s="92"/>
-      <c r="U5" s="92"/>
-      <c r="V5" s="90"/>
-      <c r="W5" s="89">
+      <c r="P5" s="117"/>
+      <c r="Q5" s="117"/>
+      <c r="R5" s="117"/>
+      <c r="S5" s="117"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="117"/>
+      <c r="V5" s="118"/>
+      <c r="W5" s="116">
         <f ca="1">O5+1</f>
         <v>46270</v>
       </c>
-      <c r="X5" s="92"/>
-      <c r="Y5" s="92"/>
-      <c r="Z5" s="92"/>
-      <c r="AA5" s="92"/>
-      <c r="AB5" s="92"/>
-      <c r="AC5" s="92"/>
-      <c r="AD5" s="90"/>
+      <c r="X5" s="117"/>
+      <c r="Y5" s="117"/>
+      <c r="Z5" s="117"/>
+      <c r="AA5" s="117"/>
+      <c r="AB5" s="117"/>
+      <c r="AC5" s="117"/>
+      <c r="AD5" s="118"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
@@ -2072,162 +2109,162 @@
     </row>
     <row r="6" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="42"/>
-      <c r="C6" s="79"/>
-      <c r="D6" s="81"/>
-      <c r="E6" s="79"/>
-      <c r="F6" s="81"/>
-      <c r="G6" s="148"/>
-      <c r="H6" s="149"/>
-      <c r="I6" s="148"/>
-      <c r="J6" s="149"/>
-      <c r="K6" s="148"/>
-      <c r="L6" s="150"/>
-      <c r="M6" s="150"/>
-      <c r="N6" s="149"/>
-      <c r="O6" s="148"/>
-      <c r="P6" s="150"/>
-      <c r="Q6" s="150"/>
-      <c r="R6" s="150"/>
-      <c r="S6" s="150"/>
-      <c r="T6" s="150"/>
-      <c r="U6" s="150"/>
-      <c r="V6" s="149"/>
-      <c r="W6" s="148"/>
-      <c r="X6" s="150"/>
-      <c r="Y6" s="150"/>
-      <c r="Z6" s="150"/>
-      <c r="AA6" s="150"/>
-      <c r="AB6" s="150"/>
-      <c r="AC6" s="150"/>
-      <c r="AD6" s="149"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="111"/>
+      <c r="F6" s="113"/>
+      <c r="G6" s="135"/>
+      <c r="H6" s="136"/>
+      <c r="I6" s="135"/>
+      <c r="J6" s="136"/>
+      <c r="K6" s="135"/>
+      <c r="L6" s="137"/>
+      <c r="M6" s="137"/>
+      <c r="N6" s="136"/>
+      <c r="O6" s="135"/>
+      <c r="P6" s="137"/>
+      <c r="Q6" s="137"/>
+      <c r="R6" s="137"/>
+      <c r="S6" s="137"/>
+      <c r="T6" s="137"/>
+      <c r="U6" s="137"/>
+      <c r="V6" s="136"/>
+      <c r="W6" s="135"/>
+      <c r="X6" s="137"/>
+      <c r="Y6" s="137"/>
+      <c r="Z6" s="137"/>
+      <c r="AA6" s="137"/>
+      <c r="AB6" s="137"/>
+      <c r="AC6" s="137"/>
+      <c r="AD6" s="136"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
-    <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1"/>
-      <c r="C7" s="89">
+      <c r="C7" s="116">
         <f ca="1">W5+1</f>
         <v>46271</v>
       </c>
-      <c r="D7" s="90"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="85"/>
-      <c r="K7" s="83"/>
-      <c r="L7" s="84"/>
-      <c r="M7" s="84"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="124"/>
+      <c r="F7" s="125"/>
+      <c r="G7" s="124"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="124"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="124"/>
+      <c r="L7" s="126"/>
+      <c r="M7" s="126"/>
       <c r="N7" s="75"/>
-      <c r="O7" s="83"/>
-      <c r="P7" s="84"/>
-      <c r="Q7" s="84"/>
-      <c r="R7" s="84"/>
-      <c r="S7" s="84"/>
-      <c r="T7" s="84"/>
-      <c r="U7" s="84"/>
-      <c r="V7" s="85"/>
-      <c r="W7" s="83"/>
-      <c r="X7" s="84"/>
-      <c r="Y7" s="84"/>
-      <c r="Z7" s="84"/>
-      <c r="AA7" s="84"/>
-      <c r="AB7" s="84"/>
-      <c r="AC7" s="84"/>
-      <c r="AD7" s="85"/>
+      <c r="O7" s="124"/>
+      <c r="P7" s="126"/>
+      <c r="Q7" s="126"/>
+      <c r="R7" s="126"/>
+      <c r="S7" s="126"/>
+      <c r="T7" s="126"/>
+      <c r="U7" s="126"/>
+      <c r="V7" s="125"/>
+      <c r="W7" s="124"/>
+      <c r="X7" s="126"/>
+      <c r="Y7" s="126"/>
+      <c r="Z7" s="126"/>
+      <c r="AA7" s="126"/>
+      <c r="AB7" s="126"/>
+      <c r="AC7" s="126"/>
+      <c r="AD7" s="125"/>
       <c r="AF7" s="1"/>
     </row>
     <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="4"/>
-      <c r="C8" s="89"/>
-      <c r="D8" s="90"/>
-      <c r="E8" s="86">
+      <c r="C8" s="116"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="127">
         <f ca="1">C7+1</f>
         <v>46272</v>
       </c>
-      <c r="F8" s="88"/>
-      <c r="G8" s="86">
+      <c r="F8" s="128"/>
+      <c r="G8" s="127">
         <f ca="1">E8+1</f>
         <v>46273</v>
       </c>
-      <c r="H8" s="88"/>
-      <c r="I8" s="86">
+      <c r="H8" s="128"/>
+      <c r="I8" s="127">
         <f ca="1">G8+1</f>
         <v>46274</v>
       </c>
-      <c r="J8" s="88"/>
-      <c r="K8" s="86">
+      <c r="J8" s="128"/>
+      <c r="K8" s="127">
         <f ca="1">I8+1</f>
         <v>46275</v>
       </c>
-      <c r="L8" s="87"/>
-      <c r="M8" s="87"/>
+      <c r="L8" s="129"/>
+      <c r="M8" s="129"/>
       <c r="N8" s="50"/>
-      <c r="O8" s="86">
+      <c r="O8" s="127">
         <f ca="1">K8+1</f>
         <v>46276</v>
       </c>
-      <c r="P8" s="87"/>
-      <c r="Q8" s="87"/>
-      <c r="R8" s="87"/>
-      <c r="S8" s="87"/>
-      <c r="T8" s="87"/>
-      <c r="U8" s="87"/>
-      <c r="V8" s="88"/>
-      <c r="W8" s="86">
+      <c r="P8" s="129"/>
+      <c r="Q8" s="129"/>
+      <c r="R8" s="129"/>
+      <c r="S8" s="129"/>
+      <c r="T8" s="129"/>
+      <c r="U8" s="129"/>
+      <c r="V8" s="128"/>
+      <c r="W8" s="127">
         <f ca="1">O8+1</f>
         <v>46277</v>
       </c>
-      <c r="X8" s="87"/>
-      <c r="Y8" s="87"/>
-      <c r="Z8" s="87"/>
-      <c r="AA8" s="87"/>
-      <c r="AB8" s="87"/>
-      <c r="AC8" s="87"/>
-      <c r="AD8" s="88"/>
+      <c r="X8" s="129"/>
+      <c r="Y8" s="129"/>
+      <c r="Z8" s="129"/>
+      <c r="AA8" s="129"/>
+      <c r="AB8" s="129"/>
+      <c r="AC8" s="129"/>
+      <c r="AD8" s="128"/>
       <c r="AF8" s="4"/>
     </row>
     <row r="9" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="42"/>
-      <c r="C9" s="148"/>
-      <c r="D9" s="149"/>
-      <c r="E9" s="148"/>
-      <c r="F9" s="149"/>
-      <c r="G9" s="148"/>
-      <c r="H9" s="149"/>
-      <c r="I9" s="148"/>
-      <c r="J9" s="149"/>
-      <c r="K9" s="148"/>
-      <c r="L9" s="150"/>
-      <c r="M9" s="150"/>
-      <c r="N9" s="149"/>
-      <c r="O9" s="148"/>
-      <c r="P9" s="150"/>
-      <c r="Q9" s="150"/>
-      <c r="R9" s="150"/>
-      <c r="S9" s="150"/>
-      <c r="T9" s="150"/>
-      <c r="U9" s="150"/>
-      <c r="V9" s="149"/>
-      <c r="W9" s="148"/>
-      <c r="X9" s="150"/>
-      <c r="Y9" s="150"/>
-      <c r="Z9" s="150"/>
-      <c r="AA9" s="150"/>
-      <c r="AB9" s="150"/>
-      <c r="AC9" s="150"/>
-      <c r="AD9" s="149"/>
+      <c r="C9" s="135"/>
+      <c r="D9" s="136"/>
+      <c r="E9" s="135"/>
+      <c r="F9" s="136"/>
+      <c r="G9" s="135"/>
+      <c r="H9" s="136"/>
+      <c r="I9" s="135"/>
+      <c r="J9" s="136"/>
+      <c r="K9" s="135"/>
+      <c r="L9" s="137"/>
+      <c r="M9" s="137"/>
+      <c r="N9" s="136"/>
+      <c r="O9" s="135"/>
+      <c r="P9" s="137"/>
+      <c r="Q9" s="137"/>
+      <c r="R9" s="137"/>
+      <c r="S9" s="137"/>
+      <c r="T9" s="137"/>
+      <c r="U9" s="137"/>
+      <c r="V9" s="136"/>
+      <c r="W9" s="135"/>
+      <c r="X9" s="137"/>
+      <c r="Y9" s="137"/>
+      <c r="Z9" s="137"/>
+      <c r="AA9" s="137"/>
+      <c r="AB9" s="137"/>
+      <c r="AC9" s="137"/>
+      <c r="AD9" s="136"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
     <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="42"/>
-      <c r="C10" s="89">
+      <c r="C10" s="116">
         <f ca="1">W8+1</f>
         <v>46278</v>
       </c>
-      <c r="D10" s="90"/>
+      <c r="D10" s="118"/>
       <c r="E10" s="45"/>
       <c r="F10" s="75"/>
       <c r="G10" s="45"/>
@@ -2257,97 +2294,97 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="42"/>
     </row>
-    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="4"/>
-      <c r="C11" s="89"/>
-      <c r="D11" s="90"/>
-      <c r="E11" s="86">
+      <c r="C11" s="116"/>
+      <c r="D11" s="118"/>
+      <c r="E11" s="127">
         <f ca="1">C10+1</f>
         <v>46279</v>
       </c>
-      <c r="F11" s="88"/>
-      <c r="G11" s="86">
+      <c r="F11" s="128"/>
+      <c r="G11" s="127">
         <f ca="1">E11+1</f>
         <v>46280</v>
       </c>
-      <c r="H11" s="88"/>
-      <c r="I11" s="86">
+      <c r="H11" s="128"/>
+      <c r="I11" s="127">
         <f ca="1">G11+1</f>
         <v>46281</v>
       </c>
-      <c r="J11" s="88"/>
-      <c r="K11" s="86">
+      <c r="J11" s="128"/>
+      <c r="K11" s="127">
         <f ca="1">I11+1</f>
         <v>46282</v>
       </c>
-      <c r="L11" s="87"/>
-      <c r="M11" s="87"/>
+      <c r="L11" s="129"/>
+      <c r="M11" s="129"/>
       <c r="N11" s="50"/>
-      <c r="O11" s="86">
+      <c r="O11" s="127">
         <f ca="1">K11+1</f>
         <v>46283</v>
       </c>
-      <c r="P11" s="87"/>
-      <c r="Q11" s="87"/>
-      <c r="R11" s="87"/>
-      <c r="S11" s="87"/>
-      <c r="T11" s="87"/>
-      <c r="U11" s="87"/>
-      <c r="V11" s="88"/>
-      <c r="W11" s="86">
+      <c r="P11" s="129"/>
+      <c r="Q11" s="129"/>
+      <c r="R11" s="129"/>
+      <c r="S11" s="129"/>
+      <c r="T11" s="129"/>
+      <c r="U11" s="129"/>
+      <c r="V11" s="128"/>
+      <c r="W11" s="127">
         <f ca="1">O11+1</f>
         <v>46284</v>
       </c>
-      <c r="X11" s="87"/>
-      <c r="Y11" s="87"/>
-      <c r="Z11" s="87"/>
-      <c r="AA11" s="87"/>
-      <c r="AB11" s="87"/>
-      <c r="AC11" s="87"/>
-      <c r="AD11" s="88"/>
+      <c r="X11" s="129"/>
+      <c r="Y11" s="129"/>
+      <c r="Z11" s="129"/>
+      <c r="AA11" s="129"/>
+      <c r="AB11" s="129"/>
+      <c r="AC11" s="129"/>
+      <c r="AD11" s="128"/>
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
     <row r="12" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="42"/>
-      <c r="C12" s="148"/>
-      <c r="D12" s="149"/>
-      <c r="E12" s="148"/>
-      <c r="F12" s="149"/>
-      <c r="G12" s="148"/>
-      <c r="H12" s="149"/>
-      <c r="I12" s="148"/>
-      <c r="J12" s="149"/>
-      <c r="K12" s="148"/>
-      <c r="L12" s="150"/>
-      <c r="M12" s="150"/>
-      <c r="N12" s="149"/>
-      <c r="O12" s="148"/>
-      <c r="P12" s="150"/>
-      <c r="Q12" s="150"/>
-      <c r="R12" s="150"/>
-      <c r="S12" s="150"/>
-      <c r="T12" s="150"/>
-      <c r="U12" s="150"/>
-      <c r="V12" s="149"/>
-      <c r="W12" s="148"/>
-      <c r="X12" s="150"/>
-      <c r="Y12" s="150"/>
-      <c r="Z12" s="150"/>
-      <c r="AA12" s="150"/>
-      <c r="AB12" s="150"/>
-      <c r="AC12" s="150"/>
-      <c r="AD12" s="149"/>
+      <c r="C12" s="135"/>
+      <c r="D12" s="136"/>
+      <c r="E12" s="135"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="135"/>
+      <c r="H12" s="136"/>
+      <c r="I12" s="135"/>
+      <c r="J12" s="136"/>
+      <c r="K12" s="135"/>
+      <c r="L12" s="137"/>
+      <c r="M12" s="137"/>
+      <c r="N12" s="136"/>
+      <c r="O12" s="135"/>
+      <c r="P12" s="137"/>
+      <c r="Q12" s="137"/>
+      <c r="R12" s="137"/>
+      <c r="S12" s="137"/>
+      <c r="T12" s="137"/>
+      <c r="U12" s="137"/>
+      <c r="V12" s="136"/>
+      <c r="W12" s="135"/>
+      <c r="X12" s="137"/>
+      <c r="Y12" s="137"/>
+      <c r="Z12" s="137"/>
+      <c r="AA12" s="137"/>
+      <c r="AB12" s="137"/>
+      <c r="AC12" s="137"/>
+      <c r="AD12" s="136"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
     <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="42"/>
-      <c r="C13" s="89">
+      <c r="C13" s="116">
         <f ca="1">W11+1</f>
         <v>46285</v>
       </c>
-      <c r="D13" s="90"/>
+      <c r="D13" s="118"/>
       <c r="E13" s="45"/>
       <c r="F13" s="75"/>
       <c r="G13" s="45"/>
@@ -2379,112 +2416,112 @@
     </row>
     <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="4"/>
-      <c r="C14" s="89"/>
-      <c r="D14" s="90"/>
-      <c r="E14" s="86">
+      <c r="C14" s="116"/>
+      <c r="D14" s="118"/>
+      <c r="E14" s="127">
         <f ca="1">C13+1</f>
         <v>46286</v>
       </c>
-      <c r="F14" s="88"/>
-      <c r="G14" s="86">
+      <c r="F14" s="128"/>
+      <c r="G14" s="127">
         <f ca="1">E14+1</f>
         <v>46287</v>
       </c>
-      <c r="H14" s="88"/>
-      <c r="I14" s="86">
+      <c r="H14" s="128"/>
+      <c r="I14" s="127">
         <f ca="1">G14+1</f>
         <v>46288</v>
       </c>
-      <c r="J14" s="88"/>
-      <c r="K14" s="86">
+      <c r="J14" s="128"/>
+      <c r="K14" s="127">
         <f ca="1">I14+1</f>
         <v>46289</v>
       </c>
-      <c r="L14" s="87"/>
-      <c r="M14" s="87"/>
+      <c r="L14" s="129"/>
+      <c r="M14" s="129"/>
       <c r="N14" s="50"/>
-      <c r="O14" s="86">
+      <c r="O14" s="127">
         <f ca="1">K14+1</f>
         <v>46290</v>
       </c>
-      <c r="P14" s="87"/>
-      <c r="Q14" s="87"/>
-      <c r="R14" s="87"/>
-      <c r="S14" s="87"/>
-      <c r="T14" s="87"/>
-      <c r="U14" s="87"/>
-      <c r="V14" s="88"/>
-      <c r="W14" s="86">
+      <c r="P14" s="129"/>
+      <c r="Q14" s="129"/>
+      <c r="R14" s="129"/>
+      <c r="S14" s="129"/>
+      <c r="T14" s="129"/>
+      <c r="U14" s="129"/>
+      <c r="V14" s="128"/>
+      <c r="W14" s="127">
         <f ca="1">O14+1</f>
         <v>46291</v>
       </c>
-      <c r="X14" s="87"/>
-      <c r="Y14" s="87"/>
-      <c r="Z14" s="87"/>
-      <c r="AA14" s="87"/>
-      <c r="AB14" s="87"/>
-      <c r="AC14" s="87"/>
-      <c r="AD14" s="88"/>
+      <c r="X14" s="129"/>
+      <c r="Y14" s="129"/>
+      <c r="Z14" s="129"/>
+      <c r="AA14" s="129"/>
+      <c r="AB14" s="129"/>
+      <c r="AC14" s="129"/>
+      <c r="AD14" s="128"/>
       <c r="AF14" s="4"/>
     </row>
     <row r="15" spans="1:36" s="43" customFormat="1" ht="162.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="42"/>
-      <c r="C15" s="148"/>
-      <c r="D15" s="149"/>
-      <c r="E15" s="148"/>
-      <c r="F15" s="149"/>
-      <c r="G15" s="148"/>
-      <c r="H15" s="149"/>
-      <c r="I15" s="114"/>
-      <c r="J15" s="115"/>
-      <c r="K15" s="114"/>
-      <c r="L15" s="116"/>
-      <c r="M15" s="116"/>
-      <c r="N15" s="115"/>
-      <c r="O15" s="114"/>
-      <c r="P15" s="116"/>
-      <c r="Q15" s="116"/>
-      <c r="R15" s="116"/>
-      <c r="S15" s="116"/>
-      <c r="T15" s="116"/>
-      <c r="U15" s="116"/>
-      <c r="V15" s="115"/>
-      <c r="W15" s="114"/>
-      <c r="X15" s="116"/>
-      <c r="Y15" s="116"/>
-      <c r="Z15" s="116"/>
-      <c r="AA15" s="116"/>
-      <c r="AB15" s="116"/>
-      <c r="AC15" s="116"/>
-      <c r="AD15" s="115"/>
+      <c r="C15" s="135"/>
+      <c r="D15" s="136"/>
+      <c r="E15" s="135"/>
+      <c r="F15" s="136"/>
+      <c r="G15" s="135"/>
+      <c r="H15" s="136"/>
+      <c r="I15" s="150"/>
+      <c r="J15" s="151"/>
+      <c r="K15" s="150"/>
+      <c r="L15" s="152"/>
+      <c r="M15" s="152"/>
+      <c r="N15" s="151"/>
+      <c r="O15" s="150"/>
+      <c r="P15" s="152"/>
+      <c r="Q15" s="152"/>
+      <c r="R15" s="152"/>
+      <c r="S15" s="152"/>
+      <c r="T15" s="152"/>
+      <c r="U15" s="152"/>
+      <c r="V15" s="151"/>
+      <c r="W15" s="150"/>
+      <c r="X15" s="152"/>
+      <c r="Y15" s="152"/>
+      <c r="Z15" s="152"/>
+      <c r="AA15" s="152"/>
+      <c r="AB15" s="152"/>
+      <c r="AC15" s="152"/>
+      <c r="AD15" s="151"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
     <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="42"/>
-      <c r="C16" s="89">
+      <c r="C16" s="116">
         <f ca="1">W14+1</f>
         <v>46292</v>
       </c>
-      <c r="D16" s="90"/>
+      <c r="D16" s="118"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
       <c r="H16" s="75"/>
-      <c r="I16" s="97"/>
-      <c r="J16" s="98"/>
+      <c r="I16" s="138"/>
+      <c r="J16" s="139"/>
       <c r="K16" s="66"/>
       <c r="L16" s="68"/>
       <c r="M16" s="68"/>
       <c r="N16" s="67"/>
-      <c r="O16" s="97"/>
-      <c r="P16" s="99"/>
-      <c r="Q16" s="99"/>
-      <c r="R16" s="99"/>
-      <c r="S16" s="99"/>
-      <c r="T16" s="99"/>
-      <c r="U16" s="99"/>
-      <c r="V16" s="98"/>
+      <c r="O16" s="138"/>
+      <c r="P16" s="140"/>
+      <c r="Q16" s="140"/>
+      <c r="R16" s="140"/>
+      <c r="S16" s="140"/>
+      <c r="T16" s="140"/>
+      <c r="U16" s="140"/>
+      <c r="V16" s="139"/>
       <c r="W16" s="45"/>
       <c r="X16" s="76"/>
       <c r="Y16" s="76"/>
@@ -2498,23 +2535,23 @@
     </row>
     <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4"/>
-      <c r="C17" s="89"/>
-      <c r="D17" s="90"/>
-      <c r="E17" s="86">
+      <c r="C17" s="116"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="127">
         <f ca="1">C16+1</f>
         <v>46293</v>
       </c>
-      <c r="F17" s="88"/>
-      <c r="G17" s="86">
+      <c r="F17" s="128"/>
+      <c r="G17" s="127">
         <f ca="1">E17+1</f>
         <v>46294</v>
       </c>
-      <c r="H17" s="88"/>
-      <c r="I17" s="86">
+      <c r="H17" s="128"/>
+      <c r="I17" s="127">
         <f ca="1">G17+1</f>
         <v>46295</v>
       </c>
-      <c r="J17" s="88"/>
+      <c r="J17" s="128"/>
       <c r="K17" s="46">
         <f ca="1">I17+1</f>
         <v>46296</v>
@@ -2522,93 +2559,93 @@
       <c r="L17" s="51"/>
       <c r="M17" s="51"/>
       <c r="N17" s="69"/>
-      <c r="O17" s="86">
+      <c r="O17" s="127">
         <f ca="1">K17+1</f>
         <v>46297</v>
       </c>
-      <c r="P17" s="87"/>
-      <c r="Q17" s="87"/>
-      <c r="R17" s="87"/>
-      <c r="S17" s="87"/>
-      <c r="T17" s="87"/>
-      <c r="U17" s="87"/>
-      <c r="V17" s="88"/>
-      <c r="W17" s="86">
+      <c r="P17" s="129"/>
+      <c r="Q17" s="129"/>
+      <c r="R17" s="129"/>
+      <c r="S17" s="129"/>
+      <c r="T17" s="129"/>
+      <c r="U17" s="129"/>
+      <c r="V17" s="128"/>
+      <c r="W17" s="127">
         <f ca="1">O17+1</f>
         <v>46298</v>
       </c>
-      <c r="X17" s="87"/>
-      <c r="Y17" s="87"/>
-      <c r="Z17" s="87"/>
-      <c r="AA17" s="87"/>
-      <c r="AB17" s="87"/>
-      <c r="AC17" s="87"/>
-      <c r="AD17" s="88"/>
+      <c r="X17" s="129"/>
+      <c r="Y17" s="129"/>
+      <c r="Z17" s="129"/>
+      <c r="AA17" s="129"/>
+      <c r="AB17" s="129"/>
+      <c r="AC17" s="129"/>
+      <c r="AD17" s="128"/>
       <c r="AF17" s="4"/>
     </row>
     <row r="18" spans="1:42" s="43" customFormat="1" ht="147.30000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="42"/>
-      <c r="C18" s="114" t="s">
+      <c r="C18" s="153" t="s">
         <v>23</v>
       </c>
-      <c r="D18" s="115"/>
-      <c r="E18" s="114"/>
-      <c r="F18" s="115"/>
-      <c r="G18" s="114"/>
-      <c r="H18" s="115"/>
-      <c r="I18" s="114" t="s">
+      <c r="D18" s="154"/>
+      <c r="E18" s="150"/>
+      <c r="F18" s="151"/>
+      <c r="G18" s="150"/>
+      <c r="H18" s="151"/>
+      <c r="I18" s="153" t="s">
         <v>17</v>
       </c>
-      <c r="J18" s="115"/>
+      <c r="J18" s="154"/>
       <c r="K18" s="70"/>
       <c r="L18" s="71"/>
       <c r="M18" s="71"/>
       <c r="N18" s="72"/>
-      <c r="O18" s="79"/>
-      <c r="P18" s="80"/>
-      <c r="Q18" s="80"/>
-      <c r="R18" s="80"/>
-      <c r="S18" s="80"/>
-      <c r="T18" s="80"/>
-      <c r="U18" s="80"/>
-      <c r="V18" s="81"/>
-      <c r="W18" s="79"/>
-      <c r="X18" s="80"/>
-      <c r="Y18" s="80"/>
-      <c r="Z18" s="80"/>
-      <c r="AA18" s="80"/>
-      <c r="AB18" s="80"/>
-      <c r="AC18" s="80"/>
-      <c r="AD18" s="81"/>
+      <c r="O18" s="111"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="112"/>
+      <c r="R18" s="112"/>
+      <c r="S18" s="112"/>
+      <c r="T18" s="112"/>
+      <c r="U18" s="112"/>
+      <c r="V18" s="113"/>
+      <c r="W18" s="111"/>
+      <c r="X18" s="112"/>
+      <c r="Y18" s="112"/>
+      <c r="Z18" s="112"/>
+      <c r="AA18" s="112"/>
+      <c r="AB18" s="112"/>
+      <c r="AC18" s="112"/>
+      <c r="AD18" s="113"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
     <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="42"/>
-      <c r="C19" s="89">
+      <c r="C19" s="116">
         <f ca="1">W17+1</f>
         <v>46299</v>
       </c>
-      <c r="D19" s="90"/>
+      <c r="D19" s="118"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
       <c r="H19" s="75"/>
-      <c r="I19" s="97"/>
-      <c r="J19" s="98"/>
+      <c r="I19" s="138"/>
+      <c r="J19" s="139"/>
       <c r="K19" s="66"/>
       <c r="L19" s="68"/>
       <c r="M19" s="68"/>
       <c r="N19" s="67"/>
-      <c r="O19" s="97"/>
-      <c r="P19" s="99"/>
-      <c r="Q19" s="99"/>
-      <c r="R19" s="99"/>
-      <c r="S19" s="99"/>
-      <c r="T19" s="99"/>
-      <c r="U19" s="99"/>
-      <c r="V19" s="98"/>
+      <c r="O19" s="138"/>
+      <c r="P19" s="140"/>
+      <c r="Q19" s="140"/>
+      <c r="R19" s="140"/>
+      <c r="S19" s="140"/>
+      <c r="T19" s="140"/>
+      <c r="U19" s="140"/>
+      <c r="V19" s="139"/>
       <c r="W19" s="45"/>
       <c r="X19" s="76"/>
       <c r="Y19" s="76"/>
@@ -2622,23 +2659,23 @@
     </row>
     <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4"/>
-      <c r="C20" s="89"/>
-      <c r="D20" s="90"/>
-      <c r="E20" s="86">
+      <c r="C20" s="116"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="127">
         <f ca="1">C19+1</f>
         <v>46300</v>
       </c>
-      <c r="F20" s="88"/>
-      <c r="G20" s="86">
+      <c r="F20" s="128"/>
+      <c r="G20" s="127">
         <f ca="1">E20+1</f>
         <v>46301</v>
       </c>
-      <c r="H20" s="88"/>
-      <c r="I20" s="86">
+      <c r="H20" s="128"/>
+      <c r="I20" s="127">
         <f ca="1">G20+1</f>
         <v>46302</v>
       </c>
-      <c r="J20" s="88"/>
+      <c r="J20" s="128"/>
       <c r="K20" s="46">
         <f ca="1">I20+1</f>
         <v>46303</v>
@@ -2646,60 +2683,60 @@
       <c r="L20" s="51"/>
       <c r="M20" s="51"/>
       <c r="N20" s="69"/>
-      <c r="O20" s="86">
+      <c r="O20" s="127">
         <f ca="1">K20+1</f>
         <v>46304</v>
       </c>
-      <c r="P20" s="87"/>
-      <c r="Q20" s="87"/>
-      <c r="R20" s="87"/>
-      <c r="S20" s="87"/>
-      <c r="T20" s="87"/>
-      <c r="U20" s="87"/>
-      <c r="V20" s="88"/>
-      <c r="W20" s="86">
+      <c r="P20" s="129"/>
+      <c r="Q20" s="129"/>
+      <c r="R20" s="129"/>
+      <c r="S20" s="129"/>
+      <c r="T20" s="129"/>
+      <c r="U20" s="129"/>
+      <c r="V20" s="128"/>
+      <c r="W20" s="127">
         <f ca="1">O20+1</f>
         <v>46305</v>
       </c>
-      <c r="X20" s="87"/>
-      <c r="Y20" s="87"/>
-      <c r="Z20" s="87"/>
-      <c r="AA20" s="87"/>
-      <c r="AB20" s="87"/>
-      <c r="AC20" s="87"/>
-      <c r="AD20" s="88"/>
+      <c r="X20" s="129"/>
+      <c r="Y20" s="129"/>
+      <c r="Z20" s="129"/>
+      <c r="AA20" s="129"/>
+      <c r="AB20" s="129"/>
+      <c r="AC20" s="129"/>
+      <c r="AD20" s="128"/>
       <c r="AF20" s="4"/>
     </row>
     <row r="21" spans="1:42" s="43" customFormat="1" ht="166.8" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="42"/>
-      <c r="C21" s="79"/>
-      <c r="D21" s="81"/>
-      <c r="E21" s="79"/>
-      <c r="F21" s="81"/>
-      <c r="G21" s="79"/>
-      <c r="H21" s="81"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="81"/>
+      <c r="C21" s="111"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="113"/>
       <c r="K21" s="70"/>
       <c r="L21" s="71"/>
       <c r="M21" s="71"/>
       <c r="N21" s="72"/>
-      <c r="O21" s="79"/>
-      <c r="P21" s="80"/>
-      <c r="Q21" s="80"/>
-      <c r="R21" s="80"/>
-      <c r="S21" s="80"/>
-      <c r="T21" s="80"/>
-      <c r="U21" s="80"/>
-      <c r="V21" s="81"/>
-      <c r="W21" s="79"/>
-      <c r="X21" s="80"/>
-      <c r="Y21" s="80"/>
-      <c r="Z21" s="80"/>
-      <c r="AA21" s="80"/>
-      <c r="AB21" s="80"/>
-      <c r="AC21" s="80"/>
-      <c r="AD21" s="81"/>
+      <c r="O21" s="111"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="112"/>
+      <c r="R21" s="112"/>
+      <c r="S21" s="112"/>
+      <c r="T21" s="112"/>
+      <c r="U21" s="112"/>
+      <c r="V21" s="113"/>
+      <c r="W21" s="111"/>
+      <c r="X21" s="112"/>
+      <c r="Y21" s="112"/>
+      <c r="Z21" s="112"/>
+      <c r="AA21" s="112"/>
+      <c r="AB21" s="112"/>
+      <c r="AC21" s="112"/>
+      <c r="AD21" s="113"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
@@ -2777,54 +2814,54 @@
     </row>
     <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="1"/>
-      <c r="C25" s="95" t="s">
+      <c r="C25" s="132" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="95"/>
-      <c r="E25" s="95"/>
-      <c r="F25" s="95"/>
-      <c r="G25" s="95"/>
-      <c r="H25" s="95"/>
-      <c r="I25" s="95"/>
-      <c r="J25" s="95"/>
-      <c r="K25" s="95"/>
+      <c r="D25" s="132"/>
+      <c r="E25" s="132"/>
+      <c r="F25" s="132"/>
+      <c r="G25" s="132"/>
+      <c r="H25" s="132"/>
+      <c r="I25" s="132"/>
+      <c r="J25" s="132"/>
+      <c r="K25" s="132"/>
       <c r="L25" s="60"/>
       <c r="M25" s="1"/>
-      <c r="O25" s="96">
+      <c r="O25" s="133">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)-1,1)</f>
         <v>46235</v>
       </c>
-      <c r="P25" s="96"/>
-      <c r="Q25" s="96"/>
-      <c r="R25" s="96"/>
-      <c r="S25" s="96"/>
-      <c r="T25" s="96"/>
-      <c r="U25" s="96"/>
+      <c r="P25" s="133"/>
+      <c r="Q25" s="133"/>
+      <c r="R25" s="133"/>
+      <c r="S25" s="133"/>
+      <c r="T25" s="133"/>
+      <c r="U25" s="133"/>
       <c r="V25" s="61"/>
       <c r="W25" s="61"/>
-      <c r="X25" s="96">
+      <c r="X25" s="133">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)+1,1)</f>
         <v>46296</v>
       </c>
-      <c r="Y25" s="96"/>
-      <c r="Z25" s="96"/>
-      <c r="AA25" s="96"/>
-      <c r="AB25" s="96"/>
-      <c r="AC25" s="96"/>
-      <c r="AD25" s="96"/>
+      <c r="Y25" s="133"/>
+      <c r="Z25" s="133"/>
+      <c r="AA25" s="133"/>
+      <c r="AB25" s="133"/>
+      <c r="AC25" s="133"/>
+      <c r="AD25" s="133"/>
       <c r="AF25" s="1"/>
     </row>
     <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="1"/>
-      <c r="C26" s="95"/>
-      <c r="D26" s="95"/>
-      <c r="E26" s="95"/>
-      <c r="F26" s="95"/>
-      <c r="G26" s="95"/>
-      <c r="H26" s="95"/>
-      <c r="I26" s="95"/>
-      <c r="J26" s="95"/>
-      <c r="K26" s="95"/>
+      <c r="C26" s="132"/>
+      <c r="D26" s="132"/>
+      <c r="E26" s="132"/>
+      <c r="F26" s="132"/>
+      <c r="G26" s="132"/>
+      <c r="H26" s="132"/>
+      <c r="I26" s="132"/>
+      <c r="J26" s="132"/>
+      <c r="K26" s="132"/>
       <c r="L26" s="60"/>
       <c r="M26" s="1"/>
       <c r="O26" s="62" t="str">
@@ -2889,17 +2926,17 @@
     </row>
     <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="1"/>
-      <c r="C27" s="93" t="s">
-        <v>28</v>
-      </c>
-      <c r="D27" s="93"/>
-      <c r="E27" s="93"/>
-      <c r="F27" s="93"/>
-      <c r="G27" s="93"/>
-      <c r="H27" s="93"/>
-      <c r="I27" s="93"/>
-      <c r="J27" s="93"/>
-      <c r="K27" s="93"/>
+      <c r="C27" s="131" t="s">
+        <v>27</v>
+      </c>
+      <c r="D27" s="131"/>
+      <c r="E27" s="131"/>
+      <c r="F27" s="131"/>
+      <c r="G27" s="131"/>
+      <c r="H27" s="131"/>
+      <c r="I27" s="131"/>
+      <c r="J27" s="131"/>
+      <c r="K27" s="131"/>
       <c r="M27" s="1"/>
       <c r="O27" s="64" t="str">
         <f t="shared" ref="O27:U32" ca="1" si="0">IF(MONTH($O$25)&lt;&gt;MONTH($O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1)),"",$O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1))</f>
@@ -2963,17 +3000,17 @@
     </row>
     <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="1"/>
-      <c r="C28" s="94" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="94"/>
-      <c r="E28" s="94"/>
-      <c r="F28" s="94"/>
-      <c r="G28" s="94"/>
-      <c r="H28" s="94"/>
-      <c r="I28" s="94"/>
-      <c r="J28" s="94"/>
-      <c r="K28" s="94"/>
+      <c r="C28" s="130" t="s">
+        <v>28</v>
+      </c>
+      <c r="D28" s="130"/>
+      <c r="E28" s="130"/>
+      <c r="F28" s="130"/>
+      <c r="G28" s="130"/>
+      <c r="H28" s="130"/>
+      <c r="I28" s="130"/>
+      <c r="J28" s="130"/>
+      <c r="K28" s="130"/>
       <c r="M28" s="1"/>
       <c r="O28" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3037,15 +3074,15 @@
     </row>
     <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="1"/>
-      <c r="C29" s="93"/>
-      <c r="D29" s="93"/>
-      <c r="E29" s="93"/>
-      <c r="F29" s="93"/>
-      <c r="G29" s="93"/>
-      <c r="H29" s="93"/>
-      <c r="I29" s="93"/>
-      <c r="J29" s="93"/>
-      <c r="K29" s="93"/>
+      <c r="C29" s="131"/>
+      <c r="D29" s="131"/>
+      <c r="E29" s="131"/>
+      <c r="F29" s="131"/>
+      <c r="G29" s="131"/>
+      <c r="H29" s="131"/>
+      <c r="I29" s="131"/>
+      <c r="J29" s="131"/>
+      <c r="K29" s="131"/>
       <c r="M29" s="1"/>
       <c r="O29" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3109,17 +3146,17 @@
     </row>
     <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="1"/>
-      <c r="C30" s="94" t="s">
-        <v>30</v>
-      </c>
-      <c r="D30" s="94"/>
-      <c r="E30" s="94"/>
-      <c r="F30" s="94"/>
-      <c r="G30" s="94"/>
-      <c r="H30" s="94"/>
-      <c r="I30" s="94"/>
-      <c r="J30" s="94"/>
-      <c r="K30" s="94"/>
+      <c r="C30" s="130" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="130"/>
+      <c r="E30" s="130"/>
+      <c r="F30" s="130"/>
+      <c r="G30" s="130"/>
+      <c r="H30" s="130"/>
+      <c r="I30" s="130"/>
+      <c r="J30" s="130"/>
+      <c r="K30" s="130"/>
       <c r="M30" s="1"/>
       <c r="O30" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3183,15 +3220,15 @@
     </row>
     <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="1"/>
-      <c r="C31" s="93"/>
-      <c r="D31" s="93"/>
-      <c r="E31" s="93"/>
-      <c r="F31" s="93"/>
-      <c r="G31" s="93"/>
-      <c r="H31" s="93"/>
-      <c r="I31" s="93"/>
-      <c r="J31" s="93"/>
-      <c r="K31" s="93"/>
+      <c r="C31" s="131"/>
+      <c r="D31" s="131"/>
+      <c r="E31" s="131"/>
+      <c r="F31" s="131"/>
+      <c r="G31" s="131"/>
+      <c r="H31" s="131"/>
+      <c r="I31" s="131"/>
+      <c r="J31" s="131"/>
+      <c r="K31" s="131"/>
       <c r="M31" s="1"/>
       <c r="O31" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3253,7 +3290,7 @@
       </c>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" ht="12.6" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.45">
       <c r="A32" s="1"/>
       <c r="M32" s="1"/>
       <c r="O32" s="64">
@@ -3316,7 +3353,7 @@
       </c>
       <c r="AF32" s="1"/>
     </row>
-    <row r="33" spans="1:32" ht="12.6" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A33" s="1"/>
       <c r="M33" s="1"/>
       <c r="O33" s="64"/>
@@ -3371,167 +3408,69 @@
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
     </row>
-    <row r="36" spans="1:32" ht="12.6" x14ac:dyDescent="0.45"/>
-    <row r="37" spans="1:32" ht="12.6" x14ac:dyDescent="0.45">
-      <c r="I37" s="118"/>
-      <c r="J37" s="118"/>
-    </row>
-    <row r="38" spans="1:32" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="I38" s="118"/>
-      <c r="J38" s="118"/>
-    </row>
+    <row r="38" spans="1:32" ht="12.9" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D39" s="119" t="s">
+      <c r="D39" s="83" t="s">
+        <v>30</v>
+      </c>
+      <c r="E39" s="84"/>
+      <c r="F39" s="85"/>
+      <c r="G39" s="89">
+        <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
+        <v>5</v>
+      </c>
+      <c r="H39" s="90"/>
+      <c r="I39" s="83" t="s">
+        <v>33</v>
+      </c>
+      <c r="J39" s="93"/>
+      <c r="K39" s="95" t="s">
         <v>31</v>
       </c>
-      <c r="E39" s="120"/>
-      <c r="F39" s="145"/>
-      <c r="G39" s="121">
-        <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
-        <v>7</v>
-      </c>
-      <c r="H39" s="122"/>
-      <c r="I39" s="119" t="s">
-        <v>34</v>
-      </c>
-      <c r="J39" s="133"/>
-      <c r="K39" s="134" t="s">
+      <c r="L39" s="96"/>
+      <c r="M39" s="99">
+        <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
+        <v>5.9999999999999973</v>
+      </c>
+      <c r="N39" s="100"/>
+      <c r="O39" s="100"/>
+      <c r="P39" s="100"/>
+      <c r="Q39" s="100"/>
+      <c r="R39" s="101"/>
+      <c r="S39" s="105" t="s">
         <v>32</v>
       </c>
-      <c r="L39" s="135"/>
-      <c r="M39" s="136">
-        <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
-        <v>1.9999999999999991</v>
-      </c>
-      <c r="N39" s="137"/>
-      <c r="O39" s="137"/>
-      <c r="P39" s="137"/>
-      <c r="Q39" s="137"/>
-      <c r="R39" s="138"/>
-      <c r="S39" s="131" t="s">
-        <v>33</v>
-      </c>
-      <c r="T39" s="127"/>
-      <c r="U39" s="127"/>
-      <c r="V39" s="127"/>
-      <c r="W39" s="127"/>
-      <c r="X39" s="128"/>
+      <c r="T39" s="106"/>
+      <c r="U39" s="106"/>
+      <c r="V39" s="106"/>
+      <c r="W39" s="106"/>
+      <c r="X39" s="107"/>
     </row>
     <row r="40" spans="1:32" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D40" s="123"/>
-      <c r="E40" s="124"/>
-      <c r="F40" s="146"/>
-      <c r="G40" s="125"/>
-      <c r="H40" s="126"/>
-      <c r="I40" s="123"/>
-      <c r="J40" s="139"/>
-      <c r="K40" s="140"/>
-      <c r="L40" s="141"/>
-      <c r="M40" s="142"/>
-      <c r="N40" s="143"/>
-      <c r="O40" s="143"/>
-      <c r="P40" s="143"/>
-      <c r="Q40" s="143"/>
-      <c r="R40" s="144"/>
-      <c r="S40" s="132"/>
-      <c r="T40" s="129"/>
-      <c r="U40" s="129"/>
-      <c r="V40" s="129"/>
-      <c r="W40" s="129"/>
-      <c r="X40" s="130"/>
-    </row>
-    <row r="41" spans="1:32" ht="12.6" x14ac:dyDescent="0.45"/>
+      <c r="D40" s="86"/>
+      <c r="E40" s="87"/>
+      <c r="F40" s="88"/>
+      <c r="G40" s="91"/>
+      <c r="H40" s="92"/>
+      <c r="I40" s="86"/>
+      <c r="J40" s="94"/>
+      <c r="K40" s="97"/>
+      <c r="L40" s="98"/>
+      <c r="M40" s="102"/>
+      <c r="N40" s="103"/>
+      <c r="O40" s="103"/>
+      <c r="P40" s="103"/>
+      <c r="Q40" s="103"/>
+      <c r="R40" s="104"/>
+      <c r="S40" s="108"/>
+      <c r="T40" s="109"/>
+      <c r="U40" s="109"/>
+      <c r="V40" s="109"/>
+      <c r="W40" s="109"/>
+      <c r="X40" s="110"/>
+    </row>
   </sheetData>
   <mergeCells count="110">
-    <mergeCell ref="D39:F40"/>
-    <mergeCell ref="G39:H40"/>
-    <mergeCell ref="K39:L40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="S39:X40"/>
-    <mergeCell ref="M39:R40"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="O20:V20"/>
-    <mergeCell ref="C2:AD2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="W5:AD5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:V6"/>
-    <mergeCell ref="W6:AD6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="O5:V5"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="W7:AD7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="O8:V8"/>
-    <mergeCell ref="W8:AD8"/>
-    <mergeCell ref="O7:V7"/>
-    <mergeCell ref="W9:AD9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="O11:V11"/>
-    <mergeCell ref="W11:AD11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:V9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="W12:AD12"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="O14:V14"/>
-    <mergeCell ref="W14:AD14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="O12:V12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="W15:AD15"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="O17:V17"/>
-    <mergeCell ref="W17:AD17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="O15:V15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="C30:K31"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="O16:V16"/>
     <mergeCell ref="W18:AD18"/>
     <mergeCell ref="C25:K26"/>
     <mergeCell ref="O25:U25"/>
@@ -3553,6 +3492,95 @@
     <mergeCell ref="O21:V21"/>
     <mergeCell ref="W21:AD21"/>
     <mergeCell ref="O19:V19"/>
+    <mergeCell ref="W15:AD15"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="O17:V17"/>
+    <mergeCell ref="W17:AD17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="O15:V15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="O16:V16"/>
+    <mergeCell ref="W12:AD12"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O14:V14"/>
+    <mergeCell ref="W14:AD14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="O12:V12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="W9:AD9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="O11:V11"/>
+    <mergeCell ref="W11:AD11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:V9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="W7:AD7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="O8:V8"/>
+    <mergeCell ref="W8:AD8"/>
+    <mergeCell ref="O7:V7"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:V6"/>
+    <mergeCell ref="W6:AD6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="O5:V5"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="C2:AD2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="W5:AD5"/>
+    <mergeCell ref="D39:F40"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="K39:L40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="S39:X40"/>
+    <mergeCell ref="M39:R40"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="O20:V20"/>
+    <mergeCell ref="C30:K31"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 E5 G5 I5 K5:L5 O5 W5 C7 E8 G8 I8 K8:L8 O8 W8 C10 E11 G11 I11 K11:L11 O11 W11 C13 E14 G14 I14 K14:L14 O14 W14 C16 E17 G17 I17 K17:L17 O17 W17">
     <cfRule type="expression" dxfId="11" priority="3">
@@ -3590,8 +3618,8 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AP41"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="12.9" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:AP40"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="12.6" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="3" width="5.5546875" style="3" customWidth="1"/>
     <col min="4" max="4" width="15.5546875" style="3" customWidth="1"/>
@@ -3609,7 +3637,7 @@
     <col min="35" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3643,42 +3671,42 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="2.2000000000000002">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="2.15">
       <c r="A2" s="29"/>
-      <c r="C2" s="91">
+      <c r="C2" s="114">
         <f ca="1">DATE(About!P8,10,1)</f>
         <v>46296</v>
       </c>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
-      <c r="H2" s="91"/>
-      <c r="I2" s="91"/>
-      <c r="J2" s="91"/>
-      <c r="K2" s="91"/>
-      <c r="L2" s="91"/>
-      <c r="M2" s="91"/>
-      <c r="N2" s="91"/>
-      <c r="O2" s="91"/>
-      <c r="P2" s="91"/>
-      <c r="Q2" s="91"/>
-      <c r="R2" s="91"/>
-      <c r="S2" s="91"/>
-      <c r="T2" s="91"/>
-      <c r="U2" s="91"/>
-      <c r="V2" s="91"/>
-      <c r="W2" s="91"/>
-      <c r="X2" s="91"/>
-      <c r="Y2" s="91"/>
-      <c r="Z2" s="91"/>
-      <c r="AA2" s="91"/>
-      <c r="AB2" s="91"/>
-      <c r="AC2" s="91"/>
-      <c r="AD2" s="91"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="114"/>
+      <c r="O2" s="114"/>
+      <c r="P2" s="114"/>
+      <c r="Q2" s="114"/>
+      <c r="R2" s="114"/>
+      <c r="S2" s="114"/>
+      <c r="T2" s="114"/>
+      <c r="U2" s="114"/>
+      <c r="V2" s="114"/>
+      <c r="W2" s="114"/>
+      <c r="X2" s="114"/>
+      <c r="Y2" s="114"/>
+      <c r="Z2" s="114"/>
+      <c r="AA2" s="114"/>
+      <c r="AB2" s="114"/>
+      <c r="AC2" s="114"/>
+      <c r="AD2" s="114"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="2.2000000000000002">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="2.15">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -3698,114 +3726,114 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A4" s="35"/>
-      <c r="C4" s="82">
+      <c r="C4" s="115">
         <f ca="1">C5</f>
         <v>46292</v>
       </c>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82">
+      <c r="D4" s="115"/>
+      <c r="E4" s="115">
         <f ca="1">E5</f>
         <v>46293</v>
       </c>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82">
+      <c r="F4" s="115"/>
+      <c r="G4" s="115">
         <f ca="1">G5</f>
         <v>46294</v>
       </c>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82">
+      <c r="H4" s="115"/>
+      <c r="I4" s="115">
         <f ca="1">I5</f>
         <v>46295</v>
       </c>
-      <c r="J4" s="82"/>
-      <c r="K4" s="82">
+      <c r="J4" s="115"/>
+      <c r="K4" s="115">
         <f ca="1">K5</f>
         <v>46296</v>
       </c>
-      <c r="L4" s="82"/>
-      <c r="M4" s="82"/>
+      <c r="L4" s="115"/>
+      <c r="M4" s="115"/>
       <c r="N4" s="37"/>
-      <c r="O4" s="82">
+      <c r="O4" s="115">
         <f ca="1">O5</f>
         <v>46297</v>
       </c>
-      <c r="P4" s="82"/>
-      <c r="Q4" s="82"/>
-      <c r="R4" s="82"/>
-      <c r="S4" s="82"/>
-      <c r="T4" s="82"/>
-      <c r="U4" s="82"/>
-      <c r="V4" s="82"/>
-      <c r="W4" s="82">
+      <c r="P4" s="115"/>
+      <c r="Q4" s="115"/>
+      <c r="R4" s="115"/>
+      <c r="S4" s="115"/>
+      <c r="T4" s="115"/>
+      <c r="U4" s="115"/>
+      <c r="V4" s="115"/>
+      <c r="W4" s="115">
         <f ca="1">W5</f>
         <v>46298</v>
       </c>
-      <c r="X4" s="82"/>
-      <c r="Y4" s="82"/>
-      <c r="Z4" s="82"/>
-      <c r="AA4" s="82"/>
-      <c r="AB4" s="82"/>
-      <c r="AC4" s="82"/>
-      <c r="AD4" s="82"/>
+      <c r="X4" s="115"/>
+      <c r="Y4" s="115"/>
+      <c r="Z4" s="115"/>
+      <c r="AA4" s="115"/>
+      <c r="AB4" s="115"/>
+      <c r="AC4" s="115"/>
+      <c r="AD4" s="115"/>
       <c r="AF4" s="38"/>
       <c r="AG4" s="39"/>
       <c r="AH4" s="39"/>
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1"/>
-      <c r="C5" s="89">
+      <c r="C5" s="116">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46292</v>
       </c>
-      <c r="D5" s="90"/>
-      <c r="E5" s="89">
+      <c r="D5" s="118"/>
+      <c r="E5" s="116">
         <f ca="1">C5+1</f>
         <v>46293</v>
       </c>
-      <c r="F5" s="90"/>
-      <c r="G5" s="89">
+      <c r="F5" s="118"/>
+      <c r="G5" s="116">
         <f ca="1">E5+1</f>
         <v>46294</v>
       </c>
-      <c r="H5" s="90"/>
-      <c r="I5" s="89">
+      <c r="H5" s="118"/>
+      <c r="I5" s="116">
         <f ca="1">G5+1</f>
         <v>46295</v>
       </c>
-      <c r="J5" s="90"/>
-      <c r="K5" s="89">
+      <c r="J5" s="118"/>
+      <c r="K5" s="116">
         <f ca="1">I5+1</f>
         <v>46296</v>
       </c>
-      <c r="L5" s="92"/>
-      <c r="M5" s="92"/>
+      <c r="L5" s="117"/>
+      <c r="M5" s="117"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="89">
+      <c r="O5" s="116">
         <f ca="1">K5+1</f>
         <v>46297</v>
       </c>
-      <c r="P5" s="92"/>
-      <c r="Q5" s="92"/>
-      <c r="R5" s="92"/>
-      <c r="S5" s="92"/>
-      <c r="T5" s="92"/>
-      <c r="U5" s="92"/>
-      <c r="V5" s="90"/>
-      <c r="W5" s="89">
+      <c r="P5" s="117"/>
+      <c r="Q5" s="117"/>
+      <c r="R5" s="117"/>
+      <c r="S5" s="117"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="117"/>
+      <c r="V5" s="118"/>
+      <c r="W5" s="116">
         <f ca="1">O5+1</f>
         <v>46298</v>
       </c>
-      <c r="X5" s="92"/>
-      <c r="Y5" s="92"/>
-      <c r="Z5" s="92"/>
-      <c r="AA5" s="92"/>
-      <c r="AB5" s="92"/>
-      <c r="AC5" s="92"/>
-      <c r="AD5" s="90"/>
+      <c r="X5" s="117"/>
+      <c r="Y5" s="117"/>
+      <c r="Z5" s="117"/>
+      <c r="AA5" s="117"/>
+      <c r="AB5" s="117"/>
+      <c r="AC5" s="117"/>
+      <c r="AD5" s="118"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
@@ -3814,172 +3842,174 @@
     </row>
     <row r="6" spans="1:36" s="43" customFormat="1" ht="131.69999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="42"/>
-      <c r="C6" s="100"/>
-      <c r="D6" s="101"/>
-      <c r="E6" s="100"/>
-      <c r="F6" s="101"/>
-      <c r="G6" s="100"/>
-      <c r="H6" s="101"/>
-      <c r="I6" s="100"/>
-      <c r="J6" s="101"/>
-      <c r="K6" s="114"/>
-      <c r="L6" s="116"/>
-      <c r="M6" s="116"/>
-      <c r="N6" s="115"/>
-      <c r="O6" s="114"/>
-      <c r="P6" s="116"/>
-      <c r="Q6" s="116"/>
-      <c r="R6" s="116"/>
-      <c r="S6" s="116"/>
-      <c r="T6" s="116"/>
-      <c r="U6" s="116"/>
-      <c r="V6" s="115"/>
-      <c r="W6" s="114" t="s">
+      <c r="C6" s="119"/>
+      <c r="D6" s="120"/>
+      <c r="E6" s="119"/>
+      <c r="F6" s="120"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="120"/>
+      <c r="I6" s="119"/>
+      <c r="J6" s="120"/>
+      <c r="K6" s="150"/>
+      <c r="L6" s="152"/>
+      <c r="M6" s="152"/>
+      <c r="N6" s="151"/>
+      <c r="O6" s="150"/>
+      <c r="P6" s="152"/>
+      <c r="Q6" s="152"/>
+      <c r="R6" s="152"/>
+      <c r="S6" s="152"/>
+      <c r="T6" s="152"/>
+      <c r="U6" s="152"/>
+      <c r="V6" s="151"/>
+      <c r="W6" s="155" t="s">
         <v>24</v>
       </c>
-      <c r="X6" s="116"/>
-      <c r="Y6" s="116"/>
-      <c r="Z6" s="116"/>
-      <c r="AA6" s="116"/>
-      <c r="AB6" s="116"/>
-      <c r="AC6" s="116"/>
-      <c r="AD6" s="115"/>
+      <c r="X6" s="156"/>
+      <c r="Y6" s="156"/>
+      <c r="Z6" s="156"/>
+      <c r="AA6" s="156"/>
+      <c r="AB6" s="156"/>
+      <c r="AC6" s="156"/>
+      <c r="AD6" s="157"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
-    <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1"/>
-      <c r="C7" s="89">
+      <c r="C7" s="116">
         <f ca="1">W5+1</f>
         <v>46299</v>
       </c>
-      <c r="D7" s="90"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="85"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="85"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="85"/>
-      <c r="K7" s="83"/>
-      <c r="L7" s="84"/>
-      <c r="M7" s="84"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="124"/>
+      <c r="F7" s="125"/>
+      <c r="G7" s="124"/>
+      <c r="H7" s="125"/>
+      <c r="I7" s="124"/>
+      <c r="J7" s="125"/>
+      <c r="K7" s="124"/>
+      <c r="L7" s="126"/>
+      <c r="M7" s="126"/>
       <c r="N7" s="75"/>
-      <c r="O7" s="83"/>
-      <c r="P7" s="84"/>
-      <c r="Q7" s="84"/>
-      <c r="R7" s="84"/>
-      <c r="S7" s="84"/>
-      <c r="T7" s="84"/>
-      <c r="U7" s="84"/>
-      <c r="V7" s="85"/>
-      <c r="W7" s="83"/>
-      <c r="X7" s="84"/>
-      <c r="Y7" s="84"/>
-      <c r="Z7" s="84"/>
-      <c r="AA7" s="84"/>
-      <c r="AB7" s="84"/>
-      <c r="AC7" s="84"/>
-      <c r="AD7" s="85"/>
+      <c r="O7" s="124"/>
+      <c r="P7" s="126"/>
+      <c r="Q7" s="126"/>
+      <c r="R7" s="126"/>
+      <c r="S7" s="126"/>
+      <c r="T7" s="126"/>
+      <c r="U7" s="126"/>
+      <c r="V7" s="125"/>
+      <c r="W7" s="124"/>
+      <c r="X7" s="126"/>
+      <c r="Y7" s="126"/>
+      <c r="Z7" s="126"/>
+      <c r="AA7" s="126"/>
+      <c r="AB7" s="126"/>
+      <c r="AC7" s="126"/>
+      <c r="AD7" s="125"/>
       <c r="AF7" s="1"/>
     </row>
     <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="4"/>
-      <c r="C8" s="89"/>
-      <c r="D8" s="90"/>
-      <c r="E8" s="86">
+      <c r="C8" s="116"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="127">
         <f ca="1">C7+1</f>
         <v>46300</v>
       </c>
-      <c r="F8" s="88"/>
-      <c r="G8" s="86">
+      <c r="F8" s="128"/>
+      <c r="G8" s="127">
         <f ca="1">E8+1</f>
         <v>46301</v>
       </c>
-      <c r="H8" s="88"/>
-      <c r="I8" s="86">
+      <c r="H8" s="128"/>
+      <c r="I8" s="127">
         <f ca="1">G8+1</f>
         <v>46302</v>
       </c>
-      <c r="J8" s="88"/>
-      <c r="K8" s="86">
+      <c r="J8" s="128"/>
+      <c r="K8" s="127">
         <f ca="1">I8+1</f>
         <v>46303</v>
       </c>
-      <c r="L8" s="87"/>
-      <c r="M8" s="87"/>
+      <c r="L8" s="129"/>
+      <c r="M8" s="129"/>
       <c r="N8" s="50"/>
-      <c r="O8" s="86">
+      <c r="O8" s="127">
         <f ca="1">K8+1</f>
         <v>46304</v>
       </c>
-      <c r="P8" s="87"/>
-      <c r="Q8" s="87"/>
-      <c r="R8" s="87"/>
-      <c r="S8" s="87"/>
-      <c r="T8" s="87"/>
-      <c r="U8" s="87"/>
-      <c r="V8" s="88"/>
-      <c r="W8" s="86">
+      <c r="P8" s="129"/>
+      <c r="Q8" s="129"/>
+      <c r="R8" s="129"/>
+      <c r="S8" s="129"/>
+      <c r="T8" s="129"/>
+      <c r="U8" s="129"/>
+      <c r="V8" s="128"/>
+      <c r="W8" s="127">
         <f ca="1">O8+1</f>
         <v>46305</v>
       </c>
-      <c r="X8" s="87"/>
-      <c r="Y8" s="87"/>
-      <c r="Z8" s="87"/>
-      <c r="AA8" s="87"/>
-      <c r="AB8" s="87"/>
-      <c r="AC8" s="87"/>
-      <c r="AD8" s="88"/>
+      <c r="X8" s="129"/>
+      <c r="Y8" s="129"/>
+      <c r="Z8" s="129"/>
+      <c r="AA8" s="129"/>
+      <c r="AB8" s="129"/>
+      <c r="AC8" s="129"/>
+      <c r="AD8" s="128"/>
       <c r="AF8" s="4"/>
     </row>
     <row r="9" spans="1:36" s="43" customFormat="1" ht="149.69999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="42"/>
-      <c r="C9" s="114"/>
-      <c r="D9" s="115"/>
-      <c r="E9" s="114"/>
-      <c r="F9" s="115"/>
-      <c r="G9" s="114" t="s">
+      <c r="C9" s="121"/>
+      <c r="D9" s="123"/>
+      <c r="E9" s="121" t="s">
         <v>35</v>
       </c>
-      <c r="H9" s="115"/>
-      <c r="I9" s="114"/>
-      <c r="J9" s="115"/>
-      <c r="K9" s="114" t="s">
-        <v>27</v>
-      </c>
-      <c r="L9" s="116"/>
-      <c r="M9" s="116"/>
-      <c r="N9" s="115"/>
-      <c r="O9" s="114" t="s">
+      <c r="F9" s="123"/>
+      <c r="G9" s="121" t="s">
+        <v>34</v>
+      </c>
+      <c r="H9" s="123"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="123"/>
+      <c r="K9" s="121" t="s">
+        <v>36</v>
+      </c>
+      <c r="L9" s="122"/>
+      <c r="M9" s="122"/>
+      <c r="N9" s="123"/>
+      <c r="O9" s="121" t="s">
         <v>25</v>
       </c>
-      <c r="P9" s="116"/>
-      <c r="Q9" s="116"/>
-      <c r="R9" s="116"/>
-      <c r="S9" s="116"/>
-      <c r="T9" s="116"/>
-      <c r="U9" s="116"/>
-      <c r="V9" s="115"/>
-      <c r="W9" s="114" t="s">
+      <c r="P9" s="122"/>
+      <c r="Q9" s="122"/>
+      <c r="R9" s="122"/>
+      <c r="S9" s="122"/>
+      <c r="T9" s="122"/>
+      <c r="U9" s="122"/>
+      <c r="V9" s="123"/>
+      <c r="W9" s="121" t="s">
         <v>18</v>
       </c>
-      <c r="X9" s="116"/>
-      <c r="Y9" s="116"/>
-      <c r="Z9" s="116"/>
-      <c r="AA9" s="116"/>
-      <c r="AB9" s="116"/>
-      <c r="AC9" s="116"/>
-      <c r="AD9" s="115"/>
+      <c r="X9" s="122"/>
+      <c r="Y9" s="122"/>
+      <c r="Z9" s="122"/>
+      <c r="AA9" s="122"/>
+      <c r="AB9" s="122"/>
+      <c r="AC9" s="122"/>
+      <c r="AD9" s="123"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
     <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="42"/>
-      <c r="C10" s="89">
+      <c r="C10" s="116">
         <f ca="1">W8+1</f>
         <v>46306</v>
       </c>
-      <c r="D10" s="90"/>
+      <c r="D10" s="118"/>
       <c r="E10" s="45"/>
       <c r="F10" s="75"/>
       <c r="G10" s="45"/>
@@ -4009,99 +4039,99 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="42"/>
     </row>
-    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="4"/>
-      <c r="C11" s="89"/>
-      <c r="D11" s="90"/>
-      <c r="E11" s="86">
+      <c r="C11" s="116"/>
+      <c r="D11" s="118"/>
+      <c r="E11" s="127">
         <f ca="1">C10+1</f>
         <v>46307</v>
       </c>
-      <c r="F11" s="88"/>
-      <c r="G11" s="86">
+      <c r="F11" s="128"/>
+      <c r="G11" s="127">
         <f ca="1">E11+1</f>
         <v>46308</v>
       </c>
-      <c r="H11" s="88"/>
-      <c r="I11" s="86">
+      <c r="H11" s="128"/>
+      <c r="I11" s="127">
         <f ca="1">G11+1</f>
         <v>46309</v>
       </c>
-      <c r="J11" s="88"/>
-      <c r="K11" s="86">
+      <c r="J11" s="128"/>
+      <c r="K11" s="127">
         <f ca="1">I11+1</f>
         <v>46310</v>
       </c>
-      <c r="L11" s="87"/>
-      <c r="M11" s="87"/>
+      <c r="L11" s="129"/>
+      <c r="M11" s="129"/>
       <c r="N11" s="50"/>
-      <c r="O11" s="86">
+      <c r="O11" s="127">
         <f ca="1">K11+1</f>
         <v>46311</v>
       </c>
-      <c r="P11" s="87"/>
-      <c r="Q11" s="87"/>
-      <c r="R11" s="87"/>
-      <c r="S11" s="87"/>
-      <c r="T11" s="87"/>
-      <c r="U11" s="87"/>
-      <c r="V11" s="88"/>
-      <c r="W11" s="86">
+      <c r="P11" s="129"/>
+      <c r="Q11" s="129"/>
+      <c r="R11" s="129"/>
+      <c r="S11" s="129"/>
+      <c r="T11" s="129"/>
+      <c r="U11" s="129"/>
+      <c r="V11" s="128"/>
+      <c r="W11" s="127">
         <f ca="1">O11+1</f>
         <v>46312</v>
       </c>
-      <c r="X11" s="87"/>
-      <c r="Y11" s="87"/>
-      <c r="Z11" s="87"/>
-      <c r="AA11" s="87"/>
-      <c r="AB11" s="87"/>
-      <c r="AC11" s="87"/>
-      <c r="AD11" s="88"/>
+      <c r="X11" s="129"/>
+      <c r="Y11" s="129"/>
+      <c r="Z11" s="129"/>
+      <c r="AA11" s="129"/>
+      <c r="AB11" s="129"/>
+      <c r="AC11" s="129"/>
+      <c r="AD11" s="128"/>
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
     <row r="12" spans="1:36" s="43" customFormat="1" ht="134.69999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="42"/>
-      <c r="C12" s="114"/>
-      <c r="D12" s="115"/>
-      <c r="E12" s="114"/>
-      <c r="F12" s="115"/>
-      <c r="G12" s="114"/>
-      <c r="H12" s="115"/>
-      <c r="I12" s="114"/>
-      <c r="J12" s="115"/>
-      <c r="K12" s="114"/>
-      <c r="L12" s="116"/>
-      <c r="M12" s="116"/>
-      <c r="N12" s="115"/>
-      <c r="O12" s="114" t="s">
+      <c r="C12" s="121"/>
+      <c r="D12" s="123"/>
+      <c r="E12" s="121"/>
+      <c r="F12" s="123"/>
+      <c r="G12" s="121"/>
+      <c r="H12" s="123"/>
+      <c r="I12" s="121"/>
+      <c r="J12" s="123"/>
+      <c r="K12" s="121"/>
+      <c r="L12" s="122"/>
+      <c r="M12" s="122"/>
+      <c r="N12" s="123"/>
+      <c r="O12" s="121" t="s">
         <v>26</v>
       </c>
-      <c r="P12" s="116"/>
-      <c r="Q12" s="116"/>
-      <c r="R12" s="116"/>
-      <c r="S12" s="116"/>
-      <c r="T12" s="116"/>
-      <c r="U12" s="116"/>
-      <c r="V12" s="115"/>
-      <c r="W12" s="114"/>
-      <c r="X12" s="116"/>
-      <c r="Y12" s="116"/>
-      <c r="Z12" s="116"/>
-      <c r="AA12" s="116"/>
-      <c r="AB12" s="116"/>
-      <c r="AC12" s="116"/>
-      <c r="AD12" s="115"/>
+      <c r="P12" s="122"/>
+      <c r="Q12" s="122"/>
+      <c r="R12" s="122"/>
+      <c r="S12" s="122"/>
+      <c r="T12" s="122"/>
+      <c r="U12" s="122"/>
+      <c r="V12" s="123"/>
+      <c r="W12" s="121"/>
+      <c r="X12" s="122"/>
+      <c r="Y12" s="122"/>
+      <c r="Z12" s="122"/>
+      <c r="AA12" s="122"/>
+      <c r="AB12" s="122"/>
+      <c r="AC12" s="122"/>
+      <c r="AD12" s="123"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
     <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="42"/>
-      <c r="C13" s="89">
+      <c r="C13" s="116">
         <f ca="1">W11+1</f>
         <v>46313</v>
       </c>
-      <c r="D13" s="90"/>
+      <c r="D13" s="118"/>
       <c r="E13" s="45"/>
       <c r="F13" s="75"/>
       <c r="G13" s="45"/>
@@ -4133,96 +4163,96 @@
     </row>
     <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="4"/>
-      <c r="C14" s="89"/>
-      <c r="D14" s="90"/>
-      <c r="E14" s="86">
+      <c r="C14" s="116"/>
+      <c r="D14" s="118"/>
+      <c r="E14" s="127">
         <f ca="1">C13+1</f>
         <v>46314</v>
       </c>
-      <c r="F14" s="88"/>
-      <c r="G14" s="86">
+      <c r="F14" s="128"/>
+      <c r="G14" s="127">
         <f ca="1">E14+1</f>
         <v>46315</v>
       </c>
-      <c r="H14" s="88"/>
-      <c r="I14" s="86">
+      <c r="H14" s="128"/>
+      <c r="I14" s="127">
         <f ca="1">G14+1</f>
         <v>46316</v>
       </c>
-      <c r="J14" s="88"/>
-      <c r="K14" s="86">
+      <c r="J14" s="128"/>
+      <c r="K14" s="127">
         <f ca="1">I14+1</f>
         <v>46317</v>
       </c>
-      <c r="L14" s="87"/>
-      <c r="M14" s="87"/>
+      <c r="L14" s="129"/>
+      <c r="M14" s="129"/>
       <c r="N14" s="50"/>
-      <c r="O14" s="86">
+      <c r="O14" s="127">
         <f ca="1">K14+1</f>
         <v>46318</v>
       </c>
-      <c r="P14" s="87"/>
-      <c r="Q14" s="87"/>
-      <c r="R14" s="87"/>
-      <c r="S14" s="87"/>
-      <c r="T14" s="87"/>
-      <c r="U14" s="87"/>
-      <c r="V14" s="88"/>
-      <c r="W14" s="86">
+      <c r="P14" s="129"/>
+      <c r="Q14" s="129"/>
+      <c r="R14" s="129"/>
+      <c r="S14" s="129"/>
+      <c r="T14" s="129"/>
+      <c r="U14" s="129"/>
+      <c r="V14" s="128"/>
+      <c r="W14" s="127">
         <f ca="1">O14+1</f>
         <v>46319</v>
       </c>
-      <c r="X14" s="87"/>
-      <c r="Y14" s="87"/>
-      <c r="Z14" s="87"/>
-      <c r="AA14" s="87"/>
-      <c r="AB14" s="87"/>
-      <c r="AC14" s="87"/>
-      <c r="AD14" s="88"/>
+      <c r="X14" s="129"/>
+      <c r="Y14" s="129"/>
+      <c r="Z14" s="129"/>
+      <c r="AA14" s="129"/>
+      <c r="AB14" s="129"/>
+      <c r="AC14" s="129"/>
+      <c r="AD14" s="128"/>
       <c r="AF14" s="4"/>
     </row>
     <row r="15" spans="1:36" s="43" customFormat="1" ht="140.69999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="42"/>
-      <c r="C15" s="114"/>
-      <c r="D15" s="115"/>
-      <c r="E15" s="114"/>
-      <c r="F15" s="115"/>
-      <c r="G15" s="114"/>
-      <c r="H15" s="115"/>
-      <c r="I15" s="114"/>
-      <c r="J15" s="115"/>
-      <c r="K15" s="114"/>
-      <c r="L15" s="116"/>
-      <c r="M15" s="116"/>
-      <c r="N15" s="115"/>
-      <c r="O15" s="114" t="s">
+      <c r="C15" s="121"/>
+      <c r="D15" s="123"/>
+      <c r="E15" s="121"/>
+      <c r="F15" s="123"/>
+      <c r="G15" s="121"/>
+      <c r="H15" s="123"/>
+      <c r="I15" s="121"/>
+      <c r="J15" s="123"/>
+      <c r="K15" s="121"/>
+      <c r="L15" s="122"/>
+      <c r="M15" s="122"/>
+      <c r="N15" s="123"/>
+      <c r="O15" s="121" t="s">
         <v>19</v>
       </c>
-      <c r="P15" s="116"/>
-      <c r="Q15" s="116"/>
-      <c r="R15" s="116"/>
-      <c r="S15" s="116"/>
-      <c r="T15" s="116"/>
-      <c r="U15" s="116"/>
-      <c r="V15" s="115"/>
-      <c r="W15" s="114"/>
-      <c r="X15" s="116"/>
-      <c r="Y15" s="116"/>
-      <c r="Z15" s="116"/>
-      <c r="AA15" s="116"/>
-      <c r="AB15" s="116"/>
-      <c r="AC15" s="116"/>
-      <c r="AD15" s="115"/>
+      <c r="P15" s="122"/>
+      <c r="Q15" s="122"/>
+      <c r="R15" s="122"/>
+      <c r="S15" s="122"/>
+      <c r="T15" s="122"/>
+      <c r="U15" s="122"/>
+      <c r="V15" s="123"/>
+      <c r="W15" s="121"/>
+      <c r="X15" s="122"/>
+      <c r="Y15" s="122"/>
+      <c r="Z15" s="122"/>
+      <c r="AA15" s="122"/>
+      <c r="AB15" s="122"/>
+      <c r="AC15" s="122"/>
+      <c r="AD15" s="123"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
     <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="42"/>
-      <c r="C16" s="89">
+      <c r="C16" s="116">
         <f ca="1">W14+1</f>
         <v>46320</v>
       </c>
-      <c r="D16" s="90"/>
+      <c r="D16" s="118"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
@@ -4254,97 +4284,97 @@
     </row>
     <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4"/>
-      <c r="C17" s="89"/>
-      <c r="D17" s="90"/>
-      <c r="E17" s="86">
+      <c r="C17" s="116"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="127">
         <f ca="1">C16+1</f>
         <v>46321</v>
       </c>
-      <c r="F17" s="88"/>
-      <c r="G17" s="86">
+      <c r="F17" s="128"/>
+      <c r="G17" s="127">
         <f ca="1">E17+1</f>
         <v>46322</v>
       </c>
-      <c r="H17" s="88"/>
-      <c r="I17" s="86">
+      <c r="H17" s="128"/>
+      <c r="I17" s="127">
         <f ca="1">G17+1</f>
         <v>46323</v>
       </c>
-      <c r="J17" s="88"/>
-      <c r="K17" s="86">
+      <c r="J17" s="128"/>
+      <c r="K17" s="127">
         <f ca="1">I17+1</f>
         <v>46324</v>
       </c>
-      <c r="L17" s="87"/>
-      <c r="M17" s="87"/>
+      <c r="L17" s="129"/>
+      <c r="M17" s="129"/>
       <c r="N17" s="50"/>
-      <c r="O17" s="86">
+      <c r="O17" s="127">
         <f ca="1">K17+1</f>
         <v>46325</v>
       </c>
-      <c r="P17" s="87"/>
-      <c r="Q17" s="87"/>
-      <c r="R17" s="87"/>
-      <c r="S17" s="87"/>
-      <c r="T17" s="87"/>
-      <c r="U17" s="87"/>
-      <c r="V17" s="88"/>
-      <c r="W17" s="86">
+      <c r="P17" s="129"/>
+      <c r="Q17" s="129"/>
+      <c r="R17" s="129"/>
+      <c r="S17" s="129"/>
+      <c r="T17" s="129"/>
+      <c r="U17" s="129"/>
+      <c r="V17" s="128"/>
+      <c r="W17" s="127">
         <f ca="1">O17+1</f>
         <v>46326</v>
       </c>
-      <c r="X17" s="87"/>
-      <c r="Y17" s="87"/>
-      <c r="Z17" s="87"/>
-      <c r="AA17" s="87"/>
-      <c r="AB17" s="87"/>
-      <c r="AC17" s="87"/>
-      <c r="AD17" s="88"/>
+      <c r="X17" s="129"/>
+      <c r="Y17" s="129"/>
+      <c r="Z17" s="129"/>
+      <c r="AA17" s="129"/>
+      <c r="AB17" s="129"/>
+      <c r="AC17" s="129"/>
+      <c r="AD17" s="128"/>
       <c r="AF17" s="4"/>
     </row>
     <row r="18" spans="1:42" s="43" customFormat="1" ht="149.69999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="42"/>
-      <c r="C18" s="114"/>
-      <c r="D18" s="115"/>
-      <c r="E18" s="114" t="s">
+      <c r="C18" s="121"/>
+      <c r="D18" s="123"/>
+      <c r="E18" s="121" t="s">
         <v>20</v>
       </c>
-      <c r="F18" s="115"/>
-      <c r="G18" s="114"/>
-      <c r="H18" s="115"/>
-      <c r="I18" s="114"/>
-      <c r="J18" s="115"/>
-      <c r="K18" s="114"/>
-      <c r="L18" s="116"/>
-      <c r="M18" s="116"/>
-      <c r="N18" s="117"/>
-      <c r="O18" s="114"/>
-      <c r="P18" s="116"/>
-      <c r="Q18" s="116"/>
-      <c r="R18" s="116"/>
-      <c r="S18" s="116"/>
-      <c r="T18" s="116"/>
-      <c r="U18" s="116"/>
-      <c r="V18" s="115"/>
-      <c r="W18" s="114"/>
-      <c r="X18" s="116"/>
-      <c r="Y18" s="116"/>
-      <c r="Z18" s="116"/>
-      <c r="AA18" s="116"/>
-      <c r="AB18" s="116"/>
-      <c r="AC18" s="116"/>
-      <c r="AD18" s="115"/>
+      <c r="F18" s="123"/>
+      <c r="G18" s="121"/>
+      <c r="H18" s="123"/>
+      <c r="I18" s="121"/>
+      <c r="J18" s="123"/>
+      <c r="K18" s="121"/>
+      <c r="L18" s="122"/>
+      <c r="M18" s="122"/>
+      <c r="N18" s="82"/>
+      <c r="O18" s="121"/>
+      <c r="P18" s="122"/>
+      <c r="Q18" s="122"/>
+      <c r="R18" s="122"/>
+      <c r="S18" s="122"/>
+      <c r="T18" s="122"/>
+      <c r="U18" s="122"/>
+      <c r="V18" s="123"/>
+      <c r="W18" s="121"/>
+      <c r="X18" s="122"/>
+      <c r="Y18" s="122"/>
+      <c r="Z18" s="122"/>
+      <c r="AA18" s="122"/>
+      <c r="AB18" s="122"/>
+      <c r="AC18" s="122"/>
+      <c r="AD18" s="123"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
     <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="42"/>
-      <c r="C19" s="89">
+      <c r="C19" s="116">
         <f ca="1">W17+1</f>
         <v>46327</v>
       </c>
-      <c r="D19" s="90"/>
+      <c r="D19" s="118"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
@@ -4376,84 +4406,84 @@
     </row>
     <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4"/>
-      <c r="C20" s="89"/>
-      <c r="D20" s="90"/>
-      <c r="E20" s="86">
+      <c r="C20" s="116"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="127">
         <f ca="1">C19+1</f>
         <v>46328</v>
       </c>
-      <c r="F20" s="88"/>
-      <c r="G20" s="86">
+      <c r="F20" s="128"/>
+      <c r="G20" s="127">
         <f ca="1">E20+1</f>
         <v>46329</v>
       </c>
-      <c r="H20" s="88"/>
-      <c r="I20" s="86">
+      <c r="H20" s="128"/>
+      <c r="I20" s="127">
         <f ca="1">G20+1</f>
         <v>46330</v>
       </c>
-      <c r="J20" s="88"/>
-      <c r="K20" s="86">
+      <c r="J20" s="128"/>
+      <c r="K20" s="127">
         <f ca="1">I20+1</f>
         <v>46331</v>
       </c>
-      <c r="L20" s="87"/>
-      <c r="M20" s="87"/>
+      <c r="L20" s="129"/>
+      <c r="M20" s="129"/>
       <c r="N20" s="50"/>
-      <c r="O20" s="86">
+      <c r="O20" s="127">
         <f ca="1">K20+1</f>
         <v>46332</v>
       </c>
-      <c r="P20" s="87"/>
-      <c r="Q20" s="87"/>
-      <c r="R20" s="87"/>
-      <c r="S20" s="87"/>
-      <c r="T20" s="87"/>
-      <c r="U20" s="87"/>
-      <c r="V20" s="88"/>
-      <c r="W20" s="86">
+      <c r="P20" s="129"/>
+      <c r="Q20" s="129"/>
+      <c r="R20" s="129"/>
+      <c r="S20" s="129"/>
+      <c r="T20" s="129"/>
+      <c r="U20" s="129"/>
+      <c r="V20" s="128"/>
+      <c r="W20" s="127">
         <f ca="1">O20+1</f>
         <v>46333</v>
       </c>
-      <c r="X20" s="87"/>
-      <c r="Y20" s="87"/>
-      <c r="Z20" s="87"/>
-      <c r="AA20" s="87"/>
-      <c r="AB20" s="87"/>
-      <c r="AC20" s="87"/>
-      <c r="AD20" s="88"/>
+      <c r="X20" s="129"/>
+      <c r="Y20" s="129"/>
+      <c r="Z20" s="129"/>
+      <c r="AA20" s="129"/>
+      <c r="AB20" s="129"/>
+      <c r="AC20" s="129"/>
+      <c r="AD20" s="128"/>
       <c r="AF20" s="4"/>
     </row>
     <row r="21" spans="1:42" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="42"/>
-      <c r="C21" s="79"/>
-      <c r="D21" s="81"/>
-      <c r="E21" s="79"/>
-      <c r="F21" s="81"/>
-      <c r="G21" s="79"/>
-      <c r="H21" s="81"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="81"/>
-      <c r="K21" s="79"/>
-      <c r="L21" s="80"/>
-      <c r="M21" s="80"/>
+      <c r="C21" s="111"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="113"/>
+      <c r="K21" s="111"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
       <c r="N21" s="44"/>
-      <c r="O21" s="79"/>
-      <c r="P21" s="80"/>
-      <c r="Q21" s="80"/>
-      <c r="R21" s="80"/>
-      <c r="S21" s="80"/>
-      <c r="T21" s="80"/>
-      <c r="U21" s="80"/>
-      <c r="V21" s="81"/>
-      <c r="W21" s="79"/>
-      <c r="X21" s="80"/>
-      <c r="Y21" s="80"/>
-      <c r="Z21" s="80"/>
-      <c r="AA21" s="80"/>
-      <c r="AB21" s="80"/>
-      <c r="AC21" s="80"/>
-      <c r="AD21" s="81"/>
+      <c r="O21" s="111"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="112"/>
+      <c r="R21" s="112"/>
+      <c r="S21" s="112"/>
+      <c r="T21" s="112"/>
+      <c r="U21" s="112"/>
+      <c r="V21" s="113"/>
+      <c r="W21" s="111"/>
+      <c r="X21" s="112"/>
+      <c r="Y21" s="112"/>
+      <c r="Z21" s="112"/>
+      <c r="AA21" s="112"/>
+      <c r="AB21" s="112"/>
+      <c r="AC21" s="112"/>
+      <c r="AD21" s="113"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
@@ -4531,54 +4561,54 @@
     </row>
     <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="1"/>
-      <c r="C25" s="95" t="s">
+      <c r="C25" s="132" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="95"/>
-      <c r="E25" s="95"/>
-      <c r="F25" s="95"/>
-      <c r="G25" s="95"/>
-      <c r="H25" s="95"/>
-      <c r="I25" s="95"/>
-      <c r="J25" s="95"/>
-      <c r="K25" s="95"/>
+      <c r="D25" s="132"/>
+      <c r="E25" s="132"/>
+      <c r="F25" s="132"/>
+      <c r="G25" s="132"/>
+      <c r="H25" s="132"/>
+      <c r="I25" s="132"/>
+      <c r="J25" s="132"/>
+      <c r="K25" s="132"/>
       <c r="L25" s="60"/>
       <c r="M25" s="1"/>
-      <c r="O25" s="96">
+      <c r="O25" s="133">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)-1,1)</f>
         <v>46266</v>
       </c>
-      <c r="P25" s="96"/>
-      <c r="Q25" s="96"/>
-      <c r="R25" s="96"/>
-      <c r="S25" s="96"/>
-      <c r="T25" s="96"/>
-      <c r="U25" s="96"/>
+      <c r="P25" s="133"/>
+      <c r="Q25" s="133"/>
+      <c r="R25" s="133"/>
+      <c r="S25" s="133"/>
+      <c r="T25" s="133"/>
+      <c r="U25" s="133"/>
       <c r="V25" s="61"/>
       <c r="W25" s="61"/>
-      <c r="X25" s="96">
+      <c r="X25" s="133">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)+1,1)</f>
         <v>46327</v>
       </c>
-      <c r="Y25" s="96"/>
-      <c r="Z25" s="96"/>
-      <c r="AA25" s="96"/>
-      <c r="AB25" s="96"/>
-      <c r="AC25" s="96"/>
-      <c r="AD25" s="96"/>
+      <c r="Y25" s="133"/>
+      <c r="Z25" s="133"/>
+      <c r="AA25" s="133"/>
+      <c r="AB25" s="133"/>
+      <c r="AC25" s="133"/>
+      <c r="AD25" s="133"/>
       <c r="AF25" s="1"/>
     </row>
     <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="1"/>
-      <c r="C26" s="95"/>
-      <c r="D26" s="95"/>
-      <c r="E26" s="95"/>
-      <c r="F26" s="95"/>
-      <c r="G26" s="95"/>
-      <c r="H26" s="95"/>
-      <c r="I26" s="95"/>
-      <c r="J26" s="95"/>
-      <c r="K26" s="95"/>
+      <c r="C26" s="132"/>
+      <c r="D26" s="132"/>
+      <c r="E26" s="132"/>
+      <c r="F26" s="132"/>
+      <c r="G26" s="132"/>
+      <c r="H26" s="132"/>
+      <c r="I26" s="132"/>
+      <c r="J26" s="132"/>
+      <c r="K26" s="132"/>
       <c r="L26" s="60"/>
       <c r="M26" s="1"/>
       <c r="O26" s="62" t="str">
@@ -4643,15 +4673,15 @@
     </row>
     <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="1"/>
-      <c r="C27" s="93"/>
-      <c r="D27" s="93"/>
-      <c r="E27" s="93"/>
-      <c r="F27" s="93"/>
-      <c r="G27" s="93"/>
-      <c r="H27" s="93"/>
-      <c r="I27" s="93"/>
-      <c r="J27" s="93"/>
-      <c r="K27" s="93"/>
+      <c r="C27" s="131"/>
+      <c r="D27" s="131"/>
+      <c r="E27" s="131"/>
+      <c r="F27" s="131"/>
+      <c r="G27" s="131"/>
+      <c r="H27" s="131"/>
+      <c r="I27" s="131"/>
+      <c r="J27" s="131"/>
+      <c r="K27" s="131"/>
       <c r="M27" s="1"/>
       <c r="O27" s="64" t="str">
         <f t="shared" ref="O27:U32" ca="1" si="0">IF(MONTH($O$25)&lt;&gt;MONTH($O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1)),"",$O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1))</f>
@@ -4715,15 +4745,15 @@
     </row>
     <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="1"/>
-      <c r="C28" s="94"/>
-      <c r="D28" s="94"/>
-      <c r="E28" s="94"/>
-      <c r="F28" s="94"/>
-      <c r="G28" s="94"/>
-      <c r="H28" s="94"/>
-      <c r="I28" s="94"/>
-      <c r="J28" s="94"/>
-      <c r="K28" s="94"/>
+      <c r="C28" s="130"/>
+      <c r="D28" s="130"/>
+      <c r="E28" s="130"/>
+      <c r="F28" s="130"/>
+      <c r="G28" s="130"/>
+      <c r="H28" s="130"/>
+      <c r="I28" s="130"/>
+      <c r="J28" s="130"/>
+      <c r="K28" s="130"/>
       <c r="M28" s="1"/>
       <c r="O28" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -4787,15 +4817,15 @@
     </row>
     <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="1"/>
-      <c r="C29" s="93"/>
-      <c r="D29" s="93"/>
-      <c r="E29" s="93"/>
-      <c r="F29" s="93"/>
-      <c r="G29" s="93"/>
-      <c r="H29" s="93"/>
-      <c r="I29" s="93"/>
-      <c r="J29" s="93"/>
-      <c r="K29" s="93"/>
+      <c r="C29" s="131"/>
+      <c r="D29" s="131"/>
+      <c r="E29" s="131"/>
+      <c r="F29" s="131"/>
+      <c r="G29" s="131"/>
+      <c r="H29" s="131"/>
+      <c r="I29" s="131"/>
+      <c r="J29" s="131"/>
+      <c r="K29" s="131"/>
       <c r="M29" s="1"/>
       <c r="O29" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -4859,15 +4889,15 @@
     </row>
     <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="1"/>
-      <c r="C30" s="94"/>
-      <c r="D30" s="94"/>
-      <c r="E30" s="94"/>
-      <c r="F30" s="94"/>
-      <c r="G30" s="94"/>
-      <c r="H30" s="94"/>
-      <c r="I30" s="94"/>
-      <c r="J30" s="94"/>
-      <c r="K30" s="94"/>
+      <c r="C30" s="130"/>
+      <c r="D30" s="130"/>
+      <c r="E30" s="130"/>
+      <c r="F30" s="130"/>
+      <c r="G30" s="130"/>
+      <c r="H30" s="130"/>
+      <c r="I30" s="130"/>
+      <c r="J30" s="130"/>
+      <c r="K30" s="130"/>
       <c r="M30" s="1"/>
       <c r="O30" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -4931,15 +4961,15 @@
     </row>
     <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="1"/>
-      <c r="C31" s="93"/>
-      <c r="D31" s="93"/>
-      <c r="E31" s="93"/>
-      <c r="F31" s="93"/>
-      <c r="G31" s="93"/>
-      <c r="H31" s="93"/>
-      <c r="I31" s="93"/>
-      <c r="J31" s="93"/>
-      <c r="K31" s="93"/>
+      <c r="C31" s="131"/>
+      <c r="D31" s="131"/>
+      <c r="E31" s="131"/>
+      <c r="F31" s="131"/>
+      <c r="G31" s="131"/>
+      <c r="H31" s="131"/>
+      <c r="I31" s="131"/>
+      <c r="J31" s="131"/>
+      <c r="K31" s="131"/>
       <c r="M31" s="1"/>
       <c r="O31" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -5001,7 +5031,7 @@
       </c>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" ht="12.6" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.45">
       <c r="A32" s="1"/>
       <c r="M32" s="1"/>
       <c r="O32" s="64" t="str">
@@ -5064,7 +5094,7 @@
       </c>
       <c r="AF32" s="1"/>
     </row>
-    <row r="33" spans="1:32" ht="12.6" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A33" s="1"/>
       <c r="M33" s="1"/>
       <c r="O33" s="64"/>
@@ -5119,157 +5149,69 @@
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
     </row>
-    <row r="38" spans="1:32" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="38" spans="1:32" ht="12.9" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D39" s="119" t="s">
+      <c r="D39" s="83" t="s">
+        <v>30</v>
+      </c>
+      <c r="E39" s="84"/>
+      <c r="F39" s="85"/>
+      <c r="G39" s="89">
+        <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
+        <v>5</v>
+      </c>
+      <c r="H39" s="90"/>
+      <c r="I39" s="83" t="s">
+        <v>33</v>
+      </c>
+      <c r="J39" s="93"/>
+      <c r="K39" s="95" t="s">
         <v>31</v>
       </c>
-      <c r="E39" s="120"/>
-      <c r="F39" s="145"/>
-      <c r="G39" s="121">
-        <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
-        <v>7</v>
-      </c>
-      <c r="H39" s="122"/>
-      <c r="I39" s="119" t="s">
-        <v>34</v>
-      </c>
-      <c r="J39" s="133"/>
-      <c r="K39" s="134" t="s">
+      <c r="L39" s="96"/>
+      <c r="M39" s="99">
+        <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
+        <v>5.9999999999999973</v>
+      </c>
+      <c r="N39" s="100"/>
+      <c r="O39" s="100"/>
+      <c r="P39" s="100"/>
+      <c r="Q39" s="100"/>
+      <c r="R39" s="101"/>
+      <c r="S39" s="105" t="s">
         <v>32</v>
       </c>
-      <c r="L39" s="135"/>
-      <c r="M39" s="136">
-        <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
-        <v>1.9999999999999991</v>
-      </c>
-      <c r="N39" s="137"/>
-      <c r="O39" s="137"/>
-      <c r="P39" s="137"/>
-      <c r="Q39" s="137"/>
-      <c r="R39" s="138"/>
-      <c r="S39" s="131" t="s">
-        <v>33</v>
-      </c>
-      <c r="T39" s="127"/>
-      <c r="U39" s="127"/>
-      <c r="V39" s="127"/>
-      <c r="W39" s="127"/>
-      <c r="X39" s="128"/>
+      <c r="T39" s="106"/>
+      <c r="U39" s="106"/>
+      <c r="V39" s="106"/>
+      <c r="W39" s="106"/>
+      <c r="X39" s="107"/>
     </row>
     <row r="40" spans="1:32" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D40" s="123"/>
-      <c r="E40" s="124"/>
-      <c r="F40" s="146"/>
-      <c r="G40" s="125"/>
-      <c r="H40" s="126"/>
-      <c r="I40" s="123"/>
-      <c r="J40" s="139"/>
-      <c r="K40" s="140"/>
-      <c r="L40" s="141"/>
-      <c r="M40" s="142"/>
-      <c r="N40" s="143"/>
-      <c r="O40" s="143"/>
-      <c r="P40" s="143"/>
-      <c r="Q40" s="143"/>
-      <c r="R40" s="144"/>
-      <c r="S40" s="132"/>
-      <c r="T40" s="129"/>
-      <c r="U40" s="129"/>
-      <c r="V40" s="129"/>
-      <c r="W40" s="129"/>
-      <c r="X40" s="130"/>
-    </row>
-    <row r="41" spans="1:32" ht="12.6" x14ac:dyDescent="0.45"/>
+      <c r="D40" s="86"/>
+      <c r="E40" s="87"/>
+      <c r="F40" s="88"/>
+      <c r="G40" s="91"/>
+      <c r="H40" s="92"/>
+      <c r="I40" s="86"/>
+      <c r="J40" s="94"/>
+      <c r="K40" s="97"/>
+      <c r="L40" s="98"/>
+      <c r="M40" s="102"/>
+      <c r="N40" s="103"/>
+      <c r="O40" s="103"/>
+      <c r="P40" s="103"/>
+      <c r="Q40" s="103"/>
+      <c r="R40" s="104"/>
+      <c r="S40" s="108"/>
+      <c r="T40" s="109"/>
+      <c r="U40" s="109"/>
+      <c r="V40" s="109"/>
+      <c r="W40" s="109"/>
+      <c r="X40" s="110"/>
+    </row>
   </sheetData>
   <mergeCells count="110">
-    <mergeCell ref="D39:F40"/>
-    <mergeCell ref="G39:H40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="K39:L40"/>
-    <mergeCell ref="M39:R40"/>
-    <mergeCell ref="S39:X40"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="O21:V21"/>
-    <mergeCell ref="W21:AD21"/>
-    <mergeCell ref="C2:AD2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="W5:AD5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:V6"/>
-    <mergeCell ref="W6:AD6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="O5:V5"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="W7:AD7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="O8:V8"/>
-    <mergeCell ref="W8:AD8"/>
-    <mergeCell ref="O7:V7"/>
-    <mergeCell ref="W9:AD9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="O11:V11"/>
-    <mergeCell ref="W11:AD11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:V9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="W12:AD12"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="O14:V14"/>
-    <mergeCell ref="W14:AD14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="O12:V12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="W15:AD15"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="O17:V17"/>
-    <mergeCell ref="W17:AD17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="O15:V15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="C30:K31"/>
     <mergeCell ref="W18:AD18"/>
     <mergeCell ref="C25:K26"/>
     <mergeCell ref="O25:U25"/>
@@ -5293,6 +5235,93 @@
     <mergeCell ref="E21:F21"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="I21:J21"/>
+    <mergeCell ref="W15:AD15"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="O17:V17"/>
+    <mergeCell ref="W17:AD17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="O15:V15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="W12:AD12"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O14:V14"/>
+    <mergeCell ref="W14:AD14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="O12:V12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="W9:AD9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="O11:V11"/>
+    <mergeCell ref="W11:AD11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:V9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="W7:AD7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="O8:V8"/>
+    <mergeCell ref="W8:AD8"/>
+    <mergeCell ref="O7:V7"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:V6"/>
+    <mergeCell ref="W6:AD6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="O5:V5"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="C2:AD2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="W5:AD5"/>
+    <mergeCell ref="D39:F40"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="K39:L40"/>
+    <mergeCell ref="M39:R40"/>
+    <mergeCell ref="S39:X40"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="O21:V21"/>
+    <mergeCell ref="W21:AD21"/>
+    <mergeCell ref="C30:K31"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 E5 G5 I5 K5:L5 O5 W5 C7 E8 G8 I8 K8:L8 O8 W8 C10 E11 G11 I11 K11:L11 O11 W11 C13 E14 G14 I14 K14:L14 O14 W14 C16 E17 G17 I17 K17:L17 O17 W17">
     <cfRule type="expression" dxfId="7" priority="3">
@@ -5330,8 +5359,8 @@
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AP40"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="12.9" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:AP39"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="12.6" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="3" width="5.5546875" style="3" customWidth="1"/>
     <col min="4" max="4" width="15.5546875" style="3" customWidth="1"/>
@@ -5349,7 +5378,7 @@
     <col min="35" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5383,42 +5412,42 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="2.2000000000000002">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="2.15">
       <c r="A2" s="29"/>
-      <c r="C2" s="91">
+      <c r="C2" s="114">
         <f ca="1">DATE(About!P8,11,1)</f>
         <v>46327</v>
       </c>
-      <c r="D2" s="91"/>
-      <c r="E2" s="91"/>
-      <c r="F2" s="91"/>
-      <c r="G2" s="91"/>
-      <c r="H2" s="91"/>
-      <c r="I2" s="91"/>
-      <c r="J2" s="91"/>
-      <c r="K2" s="91"/>
-      <c r="L2" s="91"/>
-      <c r="M2" s="91"/>
-      <c r="N2" s="91"/>
-      <c r="O2" s="91"/>
-      <c r="P2" s="91"/>
-      <c r="Q2" s="91"/>
-      <c r="R2" s="91"/>
-      <c r="S2" s="91"/>
-      <c r="T2" s="91"/>
-      <c r="U2" s="91"/>
-      <c r="V2" s="91"/>
-      <c r="W2" s="91"/>
-      <c r="X2" s="91"/>
-      <c r="Y2" s="91"/>
-      <c r="Z2" s="91"/>
-      <c r="AA2" s="91"/>
-      <c r="AB2" s="91"/>
-      <c r="AC2" s="91"/>
-      <c r="AD2" s="91"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="114"/>
+      <c r="O2" s="114"/>
+      <c r="P2" s="114"/>
+      <c r="Q2" s="114"/>
+      <c r="R2" s="114"/>
+      <c r="S2" s="114"/>
+      <c r="T2" s="114"/>
+      <c r="U2" s="114"/>
+      <c r="V2" s="114"/>
+      <c r="W2" s="114"/>
+      <c r="X2" s="114"/>
+      <c r="Y2" s="114"/>
+      <c r="Z2" s="114"/>
+      <c r="AA2" s="114"/>
+      <c r="AB2" s="114"/>
+      <c r="AC2" s="114"/>
+      <c r="AD2" s="114"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="2.2000000000000002">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="2.15">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -5438,114 +5467,114 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.7">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A4" s="35"/>
-      <c r="C4" s="82">
+      <c r="C4" s="115">
         <f ca="1">C5</f>
         <v>46327</v>
       </c>
-      <c r="D4" s="82"/>
-      <c r="E4" s="82">
+      <c r="D4" s="115"/>
+      <c r="E4" s="115">
         <f ca="1">E5</f>
         <v>46328</v>
       </c>
-      <c r="F4" s="82"/>
-      <c r="G4" s="82">
+      <c r="F4" s="115"/>
+      <c r="G4" s="115">
         <f ca="1">G5</f>
         <v>46329</v>
       </c>
-      <c r="H4" s="82"/>
-      <c r="I4" s="82">
+      <c r="H4" s="115"/>
+      <c r="I4" s="115">
         <f ca="1">I5</f>
         <v>46330</v>
       </c>
-      <c r="J4" s="82"/>
-      <c r="K4" s="82">
+      <c r="J4" s="115"/>
+      <c r="K4" s="115">
         <f ca="1">K5</f>
         <v>46331</v>
       </c>
-      <c r="L4" s="82"/>
-      <c r="M4" s="82"/>
+      <c r="L4" s="115"/>
+      <c r="M4" s="115"/>
       <c r="N4" s="37"/>
-      <c r="O4" s="82">
+      <c r="O4" s="115">
         <f ca="1">O5</f>
         <v>46332</v>
       </c>
-      <c r="P4" s="82"/>
-      <c r="Q4" s="82"/>
-      <c r="R4" s="82"/>
-      <c r="S4" s="82"/>
-      <c r="T4" s="82"/>
-      <c r="U4" s="82"/>
-      <c r="V4" s="82"/>
-      <c r="W4" s="82">
+      <c r="P4" s="115"/>
+      <c r="Q4" s="115"/>
+      <c r="R4" s="115"/>
+      <c r="S4" s="115"/>
+      <c r="T4" s="115"/>
+      <c r="U4" s="115"/>
+      <c r="V4" s="115"/>
+      <c r="W4" s="115">
         <f ca="1">W5</f>
         <v>46333</v>
       </c>
-      <c r="X4" s="82"/>
-      <c r="Y4" s="82"/>
-      <c r="Z4" s="82"/>
-      <c r="AA4" s="82"/>
-      <c r="AB4" s="82"/>
-      <c r="AC4" s="82"/>
-      <c r="AD4" s="82"/>
+      <c r="X4" s="115"/>
+      <c r="Y4" s="115"/>
+      <c r="Z4" s="115"/>
+      <c r="AA4" s="115"/>
+      <c r="AB4" s="115"/>
+      <c r="AC4" s="115"/>
+      <c r="AD4" s="115"/>
       <c r="AF4" s="38"/>
       <c r="AG4" s="39"/>
       <c r="AH4" s="39"/>
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.6">
+    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1"/>
-      <c r="C5" s="89">
+      <c r="C5" s="116">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46327</v>
       </c>
-      <c r="D5" s="90"/>
-      <c r="E5" s="89">
+      <c r="D5" s="118"/>
+      <c r="E5" s="116">
         <f ca="1">C5+1</f>
         <v>46328</v>
       </c>
-      <c r="F5" s="90"/>
-      <c r="G5" s="89">
+      <c r="F5" s="118"/>
+      <c r="G5" s="116">
         <f ca="1">E5+1</f>
         <v>46329</v>
       </c>
-      <c r="H5" s="90"/>
-      <c r="I5" s="89">
+      <c r="H5" s="118"/>
+      <c r="I5" s="116">
         <f ca="1">G5+1</f>
         <v>46330</v>
       </c>
-      <c r="J5" s="90"/>
-      <c r="K5" s="89">
+      <c r="J5" s="118"/>
+      <c r="K5" s="116">
         <f ca="1">I5+1</f>
         <v>46331</v>
       </c>
-      <c r="L5" s="92"/>
-      <c r="M5" s="92"/>
+      <c r="L5" s="117"/>
+      <c r="M5" s="117"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="89">
+      <c r="O5" s="116">
         <f ca="1">K5+1</f>
         <v>46332</v>
       </c>
-      <c r="P5" s="92"/>
-      <c r="Q5" s="92"/>
-      <c r="R5" s="92"/>
-      <c r="S5" s="92"/>
-      <c r="T5" s="92"/>
-      <c r="U5" s="92"/>
-      <c r="V5" s="90"/>
-      <c r="W5" s="89">
+      <c r="P5" s="117"/>
+      <c r="Q5" s="117"/>
+      <c r="R5" s="117"/>
+      <c r="S5" s="117"/>
+      <c r="T5" s="117"/>
+      <c r="U5" s="117"/>
+      <c r="V5" s="118"/>
+      <c r="W5" s="116">
         <f ca="1">O5+1</f>
         <v>46333</v>
       </c>
-      <c r="X5" s="92"/>
-      <c r="Y5" s="92"/>
-      <c r="Z5" s="92"/>
-      <c r="AA5" s="92"/>
-      <c r="AB5" s="92"/>
-      <c r="AC5" s="92"/>
-      <c r="AD5" s="90"/>
+      <c r="X5" s="117"/>
+      <c r="Y5" s="117"/>
+      <c r="Z5" s="117"/>
+      <c r="AA5" s="117"/>
+      <c r="AB5" s="117"/>
+      <c r="AC5" s="117"/>
+      <c r="AD5" s="118"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
@@ -5554,415 +5583,415 @@
     </row>
     <row r="6" spans="1:36" s="43" customFormat="1" ht="133.80000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="42"/>
-      <c r="C6" s="114"/>
-      <c r="D6" s="115"/>
-      <c r="E6" s="114"/>
-      <c r="F6" s="115"/>
-      <c r="G6" s="114"/>
-      <c r="H6" s="115"/>
-      <c r="I6" s="114"/>
-      <c r="J6" s="115"/>
-      <c r="K6" s="114"/>
-      <c r="L6" s="116"/>
-      <c r="M6" s="116"/>
-      <c r="N6" s="115"/>
-      <c r="O6" s="114" t="s">
+      <c r="C6" s="121"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="121"/>
+      <c r="F6" s="123"/>
+      <c r="G6" s="121"/>
+      <c r="H6" s="123"/>
+      <c r="I6" s="121"/>
+      <c r="J6" s="123"/>
+      <c r="K6" s="121"/>
+      <c r="L6" s="122"/>
+      <c r="M6" s="122"/>
+      <c r="N6" s="123"/>
+      <c r="O6" s="121" t="s">
         <v>21</v>
       </c>
-      <c r="P6" s="116"/>
-      <c r="Q6" s="116"/>
-      <c r="R6" s="116"/>
-      <c r="S6" s="116"/>
-      <c r="T6" s="116"/>
-      <c r="U6" s="116"/>
-      <c r="V6" s="115"/>
-      <c r="W6" s="114"/>
-      <c r="X6" s="116"/>
-      <c r="Y6" s="116"/>
-      <c r="Z6" s="116"/>
-      <c r="AA6" s="116"/>
-      <c r="AB6" s="116"/>
-      <c r="AC6" s="116"/>
-      <c r="AD6" s="115"/>
+      <c r="P6" s="122"/>
+      <c r="Q6" s="122"/>
+      <c r="R6" s="122"/>
+      <c r="S6" s="122"/>
+      <c r="T6" s="122"/>
+      <c r="U6" s="122"/>
+      <c r="V6" s="123"/>
+      <c r="W6" s="121"/>
+      <c r="X6" s="122"/>
+      <c r="Y6" s="122"/>
+      <c r="Z6" s="122"/>
+      <c r="AA6" s="122"/>
+      <c r="AB6" s="122"/>
+      <c r="AC6" s="122"/>
+      <c r="AD6" s="123"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
     <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1"/>
-      <c r="C7" s="104">
+      <c r="C7" s="141">
         <f ca="1">W5+1</f>
         <v>46334</v>
       </c>
-      <c r="D7" s="105"/>
-      <c r="E7" s="106"/>
-      <c r="F7" s="107"/>
-      <c r="G7" s="106"/>
-      <c r="H7" s="107"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="107"/>
-      <c r="K7" s="106"/>
-      <c r="L7" s="108"/>
-      <c r="M7" s="108"/>
-      <c r="N7" s="109"/>
-      <c r="O7" s="106"/>
-      <c r="P7" s="108"/>
-      <c r="Q7" s="108"/>
-      <c r="R7" s="108"/>
-      <c r="S7" s="108"/>
-      <c r="T7" s="108"/>
-      <c r="U7" s="108"/>
-      <c r="V7" s="107"/>
-      <c r="W7" s="106"/>
-      <c r="X7" s="108"/>
-      <c r="Y7" s="108"/>
-      <c r="Z7" s="108"/>
-      <c r="AA7" s="108"/>
-      <c r="AB7" s="108"/>
-      <c r="AC7" s="108"/>
-      <c r="AD7" s="107"/>
+      <c r="D7" s="142"/>
+      <c r="E7" s="143"/>
+      <c r="F7" s="144"/>
+      <c r="G7" s="143"/>
+      <c r="H7" s="144"/>
+      <c r="I7" s="143"/>
+      <c r="J7" s="144"/>
+      <c r="K7" s="143"/>
+      <c r="L7" s="145"/>
+      <c r="M7" s="145"/>
+      <c r="N7" s="80"/>
+      <c r="O7" s="143"/>
+      <c r="P7" s="145"/>
+      <c r="Q7" s="145"/>
+      <c r="R7" s="145"/>
+      <c r="S7" s="145"/>
+      <c r="T7" s="145"/>
+      <c r="U7" s="145"/>
+      <c r="V7" s="144"/>
+      <c r="W7" s="143"/>
+      <c r="X7" s="145"/>
+      <c r="Y7" s="145"/>
+      <c r="Z7" s="145"/>
+      <c r="AA7" s="145"/>
+      <c r="AB7" s="145"/>
+      <c r="AC7" s="145"/>
+      <c r="AD7" s="144"/>
       <c r="AF7" s="1"/>
     </row>
     <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="4"/>
-      <c r="C8" s="104"/>
-      <c r="D8" s="105"/>
-      <c r="E8" s="104">
+      <c r="C8" s="141"/>
+      <c r="D8" s="142"/>
+      <c r="E8" s="141">
         <f ca="1">C7+1</f>
         <v>46335</v>
       </c>
-      <c r="F8" s="105"/>
-      <c r="G8" s="104">
+      <c r="F8" s="142"/>
+      <c r="G8" s="141">
         <f ca="1">E8+1</f>
         <v>46336</v>
       </c>
-      <c r="H8" s="105"/>
-      <c r="I8" s="104">
+      <c r="H8" s="142"/>
+      <c r="I8" s="141">
         <f ca="1">G8+1</f>
         <v>46337</v>
       </c>
-      <c r="J8" s="105"/>
-      <c r="K8" s="104">
+      <c r="J8" s="142"/>
+      <c r="K8" s="141">
         <f ca="1">I8+1</f>
         <v>46338</v>
       </c>
-      <c r="L8" s="110"/>
-      <c r="M8" s="110"/>
-      <c r="N8" s="111"/>
-      <c r="O8" s="104">
+      <c r="L8" s="146"/>
+      <c r="M8" s="146"/>
+      <c r="N8" s="78"/>
+      <c r="O8" s="141">
         <f ca="1">K8+1</f>
         <v>46339</v>
       </c>
-      <c r="P8" s="110"/>
-      <c r="Q8" s="110"/>
-      <c r="R8" s="110"/>
-      <c r="S8" s="110"/>
-      <c r="T8" s="110"/>
-      <c r="U8" s="110"/>
-      <c r="V8" s="105"/>
-      <c r="W8" s="104">
+      <c r="P8" s="146"/>
+      <c r="Q8" s="146"/>
+      <c r="R8" s="146"/>
+      <c r="S8" s="146"/>
+      <c r="T8" s="146"/>
+      <c r="U8" s="146"/>
+      <c r="V8" s="142"/>
+      <c r="W8" s="141">
         <f ca="1">O8+1</f>
         <v>46340</v>
       </c>
-      <c r="X8" s="110"/>
-      <c r="Y8" s="110"/>
-      <c r="Z8" s="110"/>
-      <c r="AA8" s="110"/>
-      <c r="AB8" s="110"/>
-      <c r="AC8" s="110"/>
-      <c r="AD8" s="105"/>
+      <c r="X8" s="146"/>
+      <c r="Y8" s="146"/>
+      <c r="Z8" s="146"/>
+      <c r="AA8" s="146"/>
+      <c r="AB8" s="146"/>
+      <c r="AC8" s="146"/>
+      <c r="AD8" s="142"/>
       <c r="AF8" s="4"/>
     </row>
     <row r="9" spans="1:36" s="43" customFormat="1" ht="146.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="42"/>
-      <c r="C9" s="114"/>
-      <c r="D9" s="115"/>
-      <c r="E9" s="114"/>
-      <c r="F9" s="115"/>
-      <c r="G9" s="114"/>
-      <c r="H9" s="115"/>
-      <c r="I9" s="114"/>
-      <c r="J9" s="115"/>
-      <c r="K9" s="114" t="s">
+      <c r="C9" s="121"/>
+      <c r="D9" s="123"/>
+      <c r="E9" s="121"/>
+      <c r="F9" s="123"/>
+      <c r="G9" s="121"/>
+      <c r="H9" s="123"/>
+      <c r="I9" s="121"/>
+      <c r="J9" s="123"/>
+      <c r="K9" s="121" t="s">
         <v>22</v>
       </c>
-      <c r="L9" s="116"/>
-      <c r="M9" s="116"/>
-      <c r="N9" s="115"/>
-      <c r="O9" s="147" t="s">
+      <c r="L9" s="122"/>
+      <c r="M9" s="122"/>
+      <c r="N9" s="123"/>
+      <c r="O9" s="148" t="s">
         <v>15</v>
       </c>
-      <c r="P9" s="103"/>
-      <c r="Q9" s="103"/>
-      <c r="R9" s="103"/>
-      <c r="S9" s="103"/>
-      <c r="T9" s="103"/>
-      <c r="U9" s="103"/>
-      <c r="V9" s="101"/>
-      <c r="W9" s="100"/>
-      <c r="X9" s="103"/>
-      <c r="Y9" s="103"/>
-      <c r="Z9" s="103"/>
-      <c r="AA9" s="103"/>
-      <c r="AB9" s="103"/>
-      <c r="AC9" s="103"/>
-      <c r="AD9" s="101"/>
+      <c r="P9" s="147"/>
+      <c r="Q9" s="147"/>
+      <c r="R9" s="147"/>
+      <c r="S9" s="147"/>
+      <c r="T9" s="147"/>
+      <c r="U9" s="147"/>
+      <c r="V9" s="120"/>
+      <c r="W9" s="119"/>
+      <c r="X9" s="147"/>
+      <c r="Y9" s="147"/>
+      <c r="Z9" s="147"/>
+      <c r="AA9" s="147"/>
+      <c r="AB9" s="147"/>
+      <c r="AC9" s="147"/>
+      <c r="AD9" s="120"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
     <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="42"/>
-      <c r="C10" s="104">
+      <c r="C10" s="141">
         <f ca="1">W8+1</f>
         <v>46341</v>
       </c>
-      <c r="D10" s="105"/>
-      <c r="E10" s="112"/>
-      <c r="F10" s="109"/>
-      <c r="G10" s="112"/>
-      <c r="H10" s="109"/>
-      <c r="I10" s="112"/>
-      <c r="J10" s="109"/>
-      <c r="K10" s="112"/>
-      <c r="L10" s="113"/>
-      <c r="M10" s="113"/>
-      <c r="N10" s="109"/>
-      <c r="O10" s="112"/>
-      <c r="P10" s="113"/>
-      <c r="Q10" s="113"/>
-      <c r="R10" s="113"/>
-      <c r="S10" s="113"/>
-      <c r="T10" s="113"/>
-      <c r="U10" s="113"/>
-      <c r="V10" s="109"/>
-      <c r="W10" s="112"/>
-      <c r="X10" s="113"/>
-      <c r="Y10" s="113"/>
-      <c r="Z10" s="113"/>
-      <c r="AA10" s="113"/>
-      <c r="AB10" s="113"/>
-      <c r="AC10" s="113"/>
-      <c r="AD10" s="109"/>
+      <c r="D10" s="142"/>
+      <c r="E10" s="79"/>
+      <c r="F10" s="80"/>
+      <c r="G10" s="79"/>
+      <c r="H10" s="80"/>
+      <c r="I10" s="79"/>
+      <c r="J10" s="80"/>
+      <c r="K10" s="79"/>
+      <c r="L10" s="81"/>
+      <c r="M10" s="81"/>
+      <c r="N10" s="80"/>
+      <c r="O10" s="79"/>
+      <c r="P10" s="81"/>
+      <c r="Q10" s="81"/>
+      <c r="R10" s="81"/>
+      <c r="S10" s="81"/>
+      <c r="T10" s="81"/>
+      <c r="U10" s="81"/>
+      <c r="V10" s="80"/>
+      <c r="W10" s="79"/>
+      <c r="X10" s="81"/>
+      <c r="Y10" s="81"/>
+      <c r="Z10" s="81"/>
+      <c r="AA10" s="81"/>
+      <c r="AB10" s="81"/>
+      <c r="AC10" s="81"/>
+      <c r="AD10" s="80"/>
       <c r="AE10" s="7"/>
       <c r="AF10" s="42"/>
     </row>
     <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="4"/>
-      <c r="C11" s="104"/>
-      <c r="D11" s="105"/>
-      <c r="E11" s="104">
+      <c r="C11" s="141"/>
+      <c r="D11" s="142"/>
+      <c r="E11" s="141">
         <f ca="1">C10+1</f>
         <v>46342</v>
       </c>
-      <c r="F11" s="105"/>
-      <c r="G11" s="104">
+      <c r="F11" s="142"/>
+      <c r="G11" s="141">
         <f ca="1">E11+1</f>
         <v>46343</v>
       </c>
-      <c r="H11" s="105"/>
-      <c r="I11" s="104">
+      <c r="H11" s="142"/>
+      <c r="I11" s="141">
         <f ca="1">G11+1</f>
         <v>46344</v>
       </c>
-      <c r="J11" s="105"/>
-      <c r="K11" s="104">
+      <c r="J11" s="142"/>
+      <c r="K11" s="141">
         <f ca="1">I11+1</f>
         <v>46345</v>
       </c>
-      <c r="L11" s="110"/>
-      <c r="M11" s="110"/>
-      <c r="N11" s="111"/>
-      <c r="O11" s="104">
+      <c r="L11" s="146"/>
+      <c r="M11" s="146"/>
+      <c r="N11" s="78"/>
+      <c r="O11" s="141">
         <f ca="1">K11+1</f>
         <v>46346</v>
       </c>
-      <c r="P11" s="110"/>
-      <c r="Q11" s="110"/>
-      <c r="R11" s="110"/>
-      <c r="S11" s="110"/>
-      <c r="T11" s="110"/>
-      <c r="U11" s="110"/>
-      <c r="V11" s="105"/>
-      <c r="W11" s="104">
+      <c r="P11" s="146"/>
+      <c r="Q11" s="146"/>
+      <c r="R11" s="146"/>
+      <c r="S11" s="146"/>
+      <c r="T11" s="146"/>
+      <c r="U11" s="146"/>
+      <c r="V11" s="142"/>
+      <c r="W11" s="141">
         <f ca="1">O11+1</f>
         <v>46347</v>
       </c>
-      <c r="X11" s="110"/>
-      <c r="Y11" s="110"/>
-      <c r="Z11" s="110"/>
-      <c r="AA11" s="110"/>
-      <c r="AB11" s="110"/>
-      <c r="AC11" s="110"/>
-      <c r="AD11" s="105"/>
+      <c r="X11" s="146"/>
+      <c r="Y11" s="146"/>
+      <c r="Z11" s="146"/>
+      <c r="AA11" s="146"/>
+      <c r="AB11" s="146"/>
+      <c r="AC11" s="146"/>
+      <c r="AD11" s="142"/>
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
     <row r="12" spans="1:36" s="43" customFormat="1" ht="134.69999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="42"/>
-      <c r="C12" s="100"/>
-      <c r="D12" s="101"/>
-      <c r="E12" s="147" t="s">
+      <c r="C12" s="119"/>
+      <c r="D12" s="120"/>
+      <c r="E12" s="148" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="102"/>
-      <c r="G12" s="100"/>
-      <c r="H12" s="101"/>
-      <c r="I12" s="100"/>
-      <c r="J12" s="101"/>
-      <c r="K12" s="100"/>
-      <c r="L12" s="103"/>
-      <c r="M12" s="103"/>
-      <c r="N12" s="101"/>
-      <c r="O12" s="100"/>
-      <c r="P12" s="103"/>
-      <c r="Q12" s="103"/>
-      <c r="R12" s="103"/>
-      <c r="S12" s="103"/>
-      <c r="T12" s="103"/>
-      <c r="U12" s="103"/>
-      <c r="V12" s="101"/>
-      <c r="W12" s="100"/>
-      <c r="X12" s="103"/>
-      <c r="Y12" s="103"/>
-      <c r="Z12" s="103"/>
-      <c r="AA12" s="103"/>
-      <c r="AB12" s="103"/>
-      <c r="AC12" s="103"/>
-      <c r="AD12" s="101"/>
+      <c r="F12" s="149"/>
+      <c r="G12" s="119"/>
+      <c r="H12" s="120"/>
+      <c r="I12" s="119"/>
+      <c r="J12" s="120"/>
+      <c r="K12" s="119"/>
+      <c r="L12" s="147"/>
+      <c r="M12" s="147"/>
+      <c r="N12" s="120"/>
+      <c r="O12" s="119"/>
+      <c r="P12" s="147"/>
+      <c r="Q12" s="147"/>
+      <c r="R12" s="147"/>
+      <c r="S12" s="147"/>
+      <c r="T12" s="147"/>
+      <c r="U12" s="147"/>
+      <c r="V12" s="120"/>
+      <c r="W12" s="119"/>
+      <c r="X12" s="147"/>
+      <c r="Y12" s="147"/>
+      <c r="Z12" s="147"/>
+      <c r="AA12" s="147"/>
+      <c r="AB12" s="147"/>
+      <c r="AC12" s="147"/>
+      <c r="AD12" s="120"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
     <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="42"/>
-      <c r="C13" s="104">
+      <c r="C13" s="141">
         <f ca="1">W11+1</f>
         <v>46348</v>
       </c>
-      <c r="D13" s="105"/>
-      <c r="E13" s="112"/>
-      <c r="F13" s="109"/>
-      <c r="G13" s="112"/>
-      <c r="H13" s="109"/>
-      <c r="I13" s="112"/>
-      <c r="J13" s="109"/>
-      <c r="K13" s="112"/>
-      <c r="L13" s="113"/>
-      <c r="M13" s="113"/>
-      <c r="N13" s="109"/>
-      <c r="O13" s="112"/>
-      <c r="P13" s="113"/>
-      <c r="Q13" s="113"/>
-      <c r="R13" s="113"/>
-      <c r="S13" s="113"/>
-      <c r="T13" s="113"/>
-      <c r="U13" s="113"/>
-      <c r="V13" s="109"/>
-      <c r="W13" s="112"/>
-      <c r="X13" s="113"/>
-      <c r="Y13" s="113"/>
-      <c r="Z13" s="113"/>
-      <c r="AA13" s="113"/>
-      <c r="AB13" s="113"/>
-      <c r="AC13" s="113"/>
-      <c r="AD13" s="109"/>
+      <c r="D13" s="142"/>
+      <c r="E13" s="79"/>
+      <c r="F13" s="80"/>
+      <c r="G13" s="79"/>
+      <c r="H13" s="80"/>
+      <c r="I13" s="79"/>
+      <c r="J13" s="80"/>
+      <c r="K13" s="79"/>
+      <c r="L13" s="81"/>
+      <c r="M13" s="81"/>
+      <c r="N13" s="80"/>
+      <c r="O13" s="79"/>
+      <c r="P13" s="81"/>
+      <c r="Q13" s="81"/>
+      <c r="R13" s="81"/>
+      <c r="S13" s="81"/>
+      <c r="T13" s="81"/>
+      <c r="U13" s="81"/>
+      <c r="V13" s="80"/>
+      <c r="W13" s="79"/>
+      <c r="X13" s="81"/>
+      <c r="Y13" s="81"/>
+      <c r="Z13" s="81"/>
+      <c r="AA13" s="81"/>
+      <c r="AB13" s="81"/>
+      <c r="AC13" s="81"/>
+      <c r="AD13" s="80"/>
       <c r="AE13" s="7"/>
       <c r="AF13" s="42"/>
     </row>
     <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="4"/>
-      <c r="C14" s="104"/>
-      <c r="D14" s="105"/>
-      <c r="E14" s="104">
+      <c r="C14" s="141"/>
+      <c r="D14" s="142"/>
+      <c r="E14" s="141">
         <f ca="1">C13+1</f>
         <v>46349</v>
       </c>
-      <c r="F14" s="105"/>
-      <c r="G14" s="104">
+      <c r="F14" s="142"/>
+      <c r="G14" s="141">
         <f ca="1">E14+1</f>
         <v>46350</v>
       </c>
-      <c r="H14" s="105"/>
-      <c r="I14" s="104">
+      <c r="H14" s="142"/>
+      <c r="I14" s="141">
         <f ca="1">G14+1</f>
         <v>46351</v>
       </c>
-      <c r="J14" s="105"/>
-      <c r="K14" s="104">
+      <c r="J14" s="142"/>
+      <c r="K14" s="141">
         <f ca="1">I14+1</f>
         <v>46352</v>
       </c>
-      <c r="L14" s="110"/>
-      <c r="M14" s="110"/>
-      <c r="N14" s="111"/>
-      <c r="O14" s="104">
+      <c r="L14" s="146"/>
+      <c r="M14" s="146"/>
+      <c r="N14" s="78"/>
+      <c r="O14" s="141">
         <f ca="1">K14+1</f>
         <v>46353</v>
       </c>
-      <c r="P14" s="110"/>
-      <c r="Q14" s="110"/>
-      <c r="R14" s="110"/>
-      <c r="S14" s="110"/>
-      <c r="T14" s="110"/>
-      <c r="U14" s="110"/>
-      <c r="V14" s="105"/>
-      <c r="W14" s="104">
+      <c r="P14" s="146"/>
+      <c r="Q14" s="146"/>
+      <c r="R14" s="146"/>
+      <c r="S14" s="146"/>
+      <c r="T14" s="146"/>
+      <c r="U14" s="146"/>
+      <c r="V14" s="142"/>
+      <c r="W14" s="141">
         <f ca="1">O14+1</f>
         <v>46354</v>
       </c>
-      <c r="X14" s="110"/>
-      <c r="Y14" s="110"/>
-      <c r="Z14" s="110"/>
-      <c r="AA14" s="110"/>
-      <c r="AB14" s="110"/>
-      <c r="AC14" s="110"/>
-      <c r="AD14" s="105"/>
+      <c r="X14" s="146"/>
+      <c r="Y14" s="146"/>
+      <c r="Z14" s="146"/>
+      <c r="AA14" s="146"/>
+      <c r="AB14" s="146"/>
+      <c r="AC14" s="146"/>
+      <c r="AD14" s="142"/>
       <c r="AF14" s="4"/>
     </row>
     <row r="15" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="42"/>
-      <c r="C15" s="100"/>
-      <c r="D15" s="101"/>
-      <c r="E15" s="100"/>
-      <c r="F15" s="101"/>
-      <c r="G15" s="100"/>
-      <c r="H15" s="101"/>
-      <c r="I15" s="100"/>
-      <c r="J15" s="101"/>
-      <c r="K15" s="100"/>
-      <c r="L15" s="103"/>
-      <c r="M15" s="103"/>
-      <c r="N15" s="101"/>
-      <c r="O15" s="100"/>
-      <c r="P15" s="103"/>
-      <c r="Q15" s="103"/>
-      <c r="R15" s="103"/>
-      <c r="S15" s="103"/>
-      <c r="T15" s="103"/>
-      <c r="U15" s="103"/>
-      <c r="V15" s="101"/>
-      <c r="W15" s="100"/>
-      <c r="X15" s="103"/>
-      <c r="Y15" s="103"/>
-      <c r="Z15" s="103"/>
-      <c r="AA15" s="103"/>
-      <c r="AB15" s="103"/>
-      <c r="AC15" s="103"/>
-      <c r="AD15" s="101"/>
+      <c r="C15" s="119"/>
+      <c r="D15" s="120"/>
+      <c r="E15" s="119"/>
+      <c r="F15" s="120"/>
+      <c r="G15" s="119"/>
+      <c r="H15" s="120"/>
+      <c r="I15" s="119"/>
+      <c r="J15" s="120"/>
+      <c r="K15" s="119"/>
+      <c r="L15" s="147"/>
+      <c r="M15" s="147"/>
+      <c r="N15" s="120"/>
+      <c r="O15" s="119"/>
+      <c r="P15" s="147"/>
+      <c r="Q15" s="147"/>
+      <c r="R15" s="147"/>
+      <c r="S15" s="147"/>
+      <c r="T15" s="147"/>
+      <c r="U15" s="147"/>
+      <c r="V15" s="120"/>
+      <c r="W15" s="119"/>
+      <c r="X15" s="147"/>
+      <c r="Y15" s="147"/>
+      <c r="Z15" s="147"/>
+      <c r="AA15" s="147"/>
+      <c r="AB15" s="147"/>
+      <c r="AC15" s="147"/>
+      <c r="AD15" s="120"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
     <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="42"/>
-      <c r="C16" s="89">
+      <c r="C16" s="116">
         <f ca="1">W14+1</f>
         <v>46355</v>
       </c>
-      <c r="D16" s="90"/>
+      <c r="D16" s="118"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
       <c r="H16" s="75"/>
-      <c r="I16" s="97"/>
-      <c r="J16" s="98"/>
+      <c r="I16" s="138"/>
+      <c r="J16" s="139"/>
       <c r="K16" s="66"/>
       <c r="L16" s="68"/>
       <c r="M16" s="68"/>
@@ -5988,101 +6017,101 @@
     </row>
     <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4"/>
-      <c r="C17" s="89"/>
-      <c r="D17" s="90"/>
-      <c r="E17" s="86">
+      <c r="C17" s="116"/>
+      <c r="D17" s="118"/>
+      <c r="E17" s="127">
         <f ca="1">C16+1</f>
         <v>46356</v>
       </c>
-      <c r="F17" s="88"/>
-      <c r="G17" s="86">
+      <c r="F17" s="128"/>
+      <c r="G17" s="127">
         <f ca="1">E17+1</f>
         <v>46357</v>
       </c>
-      <c r="H17" s="88"/>
-      <c r="I17" s="86">
+      <c r="H17" s="128"/>
+      <c r="I17" s="127">
         <f ca="1">G17+1</f>
         <v>46358</v>
       </c>
-      <c r="J17" s="88"/>
-      <c r="K17" s="86">
+      <c r="J17" s="128"/>
+      <c r="K17" s="127">
         <f ca="1">I17+1</f>
         <v>46359</v>
       </c>
-      <c r="L17" s="87"/>
-      <c r="M17" s="87"/>
-      <c r="N17" s="88"/>
-      <c r="O17" s="86">
+      <c r="L17" s="129"/>
+      <c r="M17" s="129"/>
+      <c r="N17" s="128"/>
+      <c r="O17" s="127">
         <f ca="1">K17+1</f>
         <v>46360</v>
       </c>
-      <c r="P17" s="87"/>
-      <c r="Q17" s="87"/>
-      <c r="R17" s="87"/>
-      <c r="S17" s="87"/>
-      <c r="T17" s="87"/>
-      <c r="U17" s="87"/>
-      <c r="V17" s="88"/>
-      <c r="W17" s="86">
+      <c r="P17" s="129"/>
+      <c r="Q17" s="129"/>
+      <c r="R17" s="129"/>
+      <c r="S17" s="129"/>
+      <c r="T17" s="129"/>
+      <c r="U17" s="129"/>
+      <c r="V17" s="128"/>
+      <c r="W17" s="127">
         <f ca="1">O17+1</f>
         <v>46361</v>
       </c>
-      <c r="X17" s="87"/>
-      <c r="Y17" s="87"/>
-      <c r="Z17" s="87"/>
-      <c r="AA17" s="87"/>
-      <c r="AB17" s="87"/>
-      <c r="AC17" s="87"/>
-      <c r="AD17" s="88"/>
+      <c r="X17" s="129"/>
+      <c r="Y17" s="129"/>
+      <c r="Z17" s="129"/>
+      <c r="AA17" s="129"/>
+      <c r="AB17" s="129"/>
+      <c r="AC17" s="129"/>
+      <c r="AD17" s="128"/>
       <c r="AF17" s="4"/>
     </row>
     <row r="18" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="42"/>
-      <c r="C18" s="79"/>
-      <c r="D18" s="81"/>
-      <c r="E18" s="79"/>
-      <c r="F18" s="81"/>
-      <c r="G18" s="79"/>
-      <c r="H18" s="81"/>
-      <c r="I18" s="79"/>
-      <c r="J18" s="81"/>
-      <c r="K18" s="79"/>
-      <c r="L18" s="80"/>
-      <c r="M18" s="80"/>
-      <c r="N18" s="81"/>
-      <c r="O18" s="79"/>
-      <c r="P18" s="80"/>
-      <c r="Q18" s="80"/>
-      <c r="R18" s="80"/>
-      <c r="S18" s="80"/>
-      <c r="T18" s="80"/>
-      <c r="U18" s="80"/>
-      <c r="V18" s="81"/>
-      <c r="W18" s="79"/>
-      <c r="X18" s="80"/>
-      <c r="Y18" s="80"/>
-      <c r="Z18" s="80"/>
-      <c r="AA18" s="80"/>
-      <c r="AB18" s="80"/>
-      <c r="AC18" s="80"/>
-      <c r="AD18" s="81"/>
+      <c r="C18" s="111"/>
+      <c r="D18" s="113"/>
+      <c r="E18" s="111"/>
+      <c r="F18" s="113"/>
+      <c r="G18" s="111"/>
+      <c r="H18" s="113"/>
+      <c r="I18" s="111"/>
+      <c r="J18" s="113"/>
+      <c r="K18" s="111"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="113"/>
+      <c r="O18" s="111"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="112"/>
+      <c r="R18" s="112"/>
+      <c r="S18" s="112"/>
+      <c r="T18" s="112"/>
+      <c r="U18" s="112"/>
+      <c r="V18" s="113"/>
+      <c r="W18" s="111"/>
+      <c r="X18" s="112"/>
+      <c r="Y18" s="112"/>
+      <c r="Z18" s="112"/>
+      <c r="AA18" s="112"/>
+      <c r="AB18" s="112"/>
+      <c r="AC18" s="112"/>
+      <c r="AD18" s="113"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
     <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="42"/>
-      <c r="C19" s="89">
+      <c r="C19" s="116">
         <f ca="1">W17+1</f>
         <v>46362</v>
       </c>
-      <c r="D19" s="90"/>
+      <c r="D19" s="118"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
       <c r="H19" s="75"/>
-      <c r="I19" s="97"/>
-      <c r="J19" s="98"/>
+      <c r="I19" s="138"/>
+      <c r="J19" s="139"/>
       <c r="K19" s="66"/>
       <c r="L19" s="68"/>
       <c r="M19" s="68"/>
@@ -6108,84 +6137,84 @@
     </row>
     <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4"/>
-      <c r="C20" s="89"/>
-      <c r="D20" s="90"/>
-      <c r="E20" s="86">
+      <c r="C20" s="116"/>
+      <c r="D20" s="118"/>
+      <c r="E20" s="127">
         <f ca="1">C19+1</f>
         <v>46363</v>
       </c>
-      <c r="F20" s="88"/>
-      <c r="G20" s="86">
+      <c r="F20" s="128"/>
+      <c r="G20" s="127">
         <f ca="1">E20+1</f>
         <v>46364</v>
       </c>
-      <c r="H20" s="88"/>
-      <c r="I20" s="86">
+      <c r="H20" s="128"/>
+      <c r="I20" s="127">
         <f ca="1">G20+1</f>
         <v>46365</v>
       </c>
-      <c r="J20" s="88"/>
-      <c r="K20" s="86">
+      <c r="J20" s="128"/>
+      <c r="K20" s="127">
         <f ca="1">I20+1</f>
         <v>46366</v>
       </c>
-      <c r="L20" s="87"/>
-      <c r="M20" s="87"/>
-      <c r="N20" s="88"/>
-      <c r="O20" s="86">
+      <c r="L20" s="129"/>
+      <c r="M20" s="129"/>
+      <c r="N20" s="128"/>
+      <c r="O20" s="127">
         <f ca="1">K20+1</f>
         <v>46367</v>
       </c>
-      <c r="P20" s="87"/>
-      <c r="Q20" s="87"/>
-      <c r="R20" s="87"/>
-      <c r="S20" s="87"/>
-      <c r="T20" s="87"/>
-      <c r="U20" s="87"/>
-      <c r="V20" s="88"/>
-      <c r="W20" s="86">
+      <c r="P20" s="129"/>
+      <c r="Q20" s="129"/>
+      <c r="R20" s="129"/>
+      <c r="S20" s="129"/>
+      <c r="T20" s="129"/>
+      <c r="U20" s="129"/>
+      <c r="V20" s="128"/>
+      <c r="W20" s="127">
         <f ca="1">O20+1</f>
         <v>46368</v>
       </c>
-      <c r="X20" s="87"/>
-      <c r="Y20" s="87"/>
-      <c r="Z20" s="87"/>
-      <c r="AA20" s="87"/>
-      <c r="AB20" s="87"/>
-      <c r="AC20" s="87"/>
-      <c r="AD20" s="88"/>
+      <c r="X20" s="129"/>
+      <c r="Y20" s="129"/>
+      <c r="Z20" s="129"/>
+      <c r="AA20" s="129"/>
+      <c r="AB20" s="129"/>
+      <c r="AC20" s="129"/>
+      <c r="AD20" s="128"/>
       <c r="AF20" s="4"/>
     </row>
     <row r="21" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="42"/>
-      <c r="C21" s="79"/>
-      <c r="D21" s="81"/>
-      <c r="E21" s="79"/>
-      <c r="F21" s="81"/>
-      <c r="G21" s="79"/>
-      <c r="H21" s="81"/>
-      <c r="I21" s="79"/>
-      <c r="J21" s="81"/>
-      <c r="K21" s="79"/>
-      <c r="L21" s="80"/>
-      <c r="M21" s="80"/>
-      <c r="N21" s="81"/>
-      <c r="O21" s="79"/>
-      <c r="P21" s="80"/>
-      <c r="Q21" s="80"/>
-      <c r="R21" s="80"/>
-      <c r="S21" s="80"/>
-      <c r="T21" s="80"/>
-      <c r="U21" s="80"/>
-      <c r="V21" s="81"/>
-      <c r="W21" s="79"/>
-      <c r="X21" s="80"/>
-      <c r="Y21" s="80"/>
-      <c r="Z21" s="80"/>
-      <c r="AA21" s="80"/>
-      <c r="AB21" s="80"/>
-      <c r="AC21" s="80"/>
-      <c r="AD21" s="81"/>
+      <c r="C21" s="111"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="113"/>
+      <c r="K21" s="111"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="113"/>
+      <c r="O21" s="111"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="112"/>
+      <c r="R21" s="112"/>
+      <c r="S21" s="112"/>
+      <c r="T21" s="112"/>
+      <c r="U21" s="112"/>
+      <c r="V21" s="113"/>
+      <c r="W21" s="111"/>
+      <c r="X21" s="112"/>
+      <c r="Y21" s="112"/>
+      <c r="Z21" s="112"/>
+      <c r="AA21" s="112"/>
+      <c r="AB21" s="112"/>
+      <c r="AC21" s="112"/>
+      <c r="AD21" s="113"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
@@ -6263,54 +6292,54 @@
     </row>
     <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="1"/>
-      <c r="C25" s="95" t="s">
+      <c r="C25" s="132" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="95"/>
-      <c r="E25" s="95"/>
-      <c r="F25" s="95"/>
-      <c r="G25" s="95"/>
-      <c r="H25" s="95"/>
-      <c r="I25" s="95"/>
-      <c r="J25" s="95"/>
-      <c r="K25" s="95"/>
+      <c r="D25" s="132"/>
+      <c r="E25" s="132"/>
+      <c r="F25" s="132"/>
+      <c r="G25" s="132"/>
+      <c r="H25" s="132"/>
+      <c r="I25" s="132"/>
+      <c r="J25" s="132"/>
+      <c r="K25" s="132"/>
       <c r="L25" s="60"/>
       <c r="M25" s="1"/>
-      <c r="O25" s="96">
+      <c r="O25" s="133">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)-1,1)</f>
         <v>46296</v>
       </c>
-      <c r="P25" s="96"/>
-      <c r="Q25" s="96"/>
-      <c r="R25" s="96"/>
-      <c r="S25" s="96"/>
-      <c r="T25" s="96"/>
-      <c r="U25" s="96"/>
+      <c r="P25" s="133"/>
+      <c r="Q25" s="133"/>
+      <c r="R25" s="133"/>
+      <c r="S25" s="133"/>
+      <c r="T25" s="133"/>
+      <c r="U25" s="133"/>
       <c r="V25" s="61"/>
       <c r="W25" s="61"/>
-      <c r="X25" s="96">
+      <c r="X25" s="133">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)+1,1)</f>
         <v>46357</v>
       </c>
-      <c r="Y25" s="96"/>
-      <c r="Z25" s="96"/>
-      <c r="AA25" s="96"/>
-      <c r="AB25" s="96"/>
-      <c r="AC25" s="96"/>
-      <c r="AD25" s="96"/>
+      <c r="Y25" s="133"/>
+      <c r="Z25" s="133"/>
+      <c r="AA25" s="133"/>
+      <c r="AB25" s="133"/>
+      <c r="AC25" s="133"/>
+      <c r="AD25" s="133"/>
       <c r="AF25" s="1"/>
     </row>
     <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="1"/>
-      <c r="C26" s="95"/>
-      <c r="D26" s="95"/>
-      <c r="E26" s="95"/>
-      <c r="F26" s="95"/>
-      <c r="G26" s="95"/>
-      <c r="H26" s="95"/>
-      <c r="I26" s="95"/>
-      <c r="J26" s="95"/>
-      <c r="K26" s="95"/>
+      <c r="C26" s="132"/>
+      <c r="D26" s="132"/>
+      <c r="E26" s="132"/>
+      <c r="F26" s="132"/>
+      <c r="G26" s="132"/>
+      <c r="H26" s="132"/>
+      <c r="I26" s="132"/>
+      <c r="J26" s="132"/>
+      <c r="K26" s="132"/>
       <c r="L26" s="60"/>
       <c r="M26" s="1"/>
       <c r="O26" s="62" t="str">
@@ -6375,15 +6404,15 @@
     </row>
     <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="1"/>
-      <c r="C27" s="93"/>
-      <c r="D27" s="93"/>
-      <c r="E27" s="93"/>
-      <c r="F27" s="93"/>
-      <c r="G27" s="93"/>
-      <c r="H27" s="93"/>
-      <c r="I27" s="93"/>
-      <c r="J27" s="93"/>
-      <c r="K27" s="93"/>
+      <c r="C27" s="131"/>
+      <c r="D27" s="131"/>
+      <c r="E27" s="131"/>
+      <c r="F27" s="131"/>
+      <c r="G27" s="131"/>
+      <c r="H27" s="131"/>
+      <c r="I27" s="131"/>
+      <c r="J27" s="131"/>
+      <c r="K27" s="131"/>
       <c r="M27" s="1"/>
       <c r="O27" s="64" t="str">
         <f t="shared" ref="O27:U32" ca="1" si="0">IF(MONTH($O$25)&lt;&gt;MONTH($O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1)),"",$O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1))</f>
@@ -6447,15 +6476,15 @@
     </row>
     <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="1"/>
-      <c r="C28" s="94"/>
-      <c r="D28" s="94"/>
-      <c r="E28" s="94"/>
-      <c r="F28" s="94"/>
-      <c r="G28" s="94"/>
-      <c r="H28" s="94"/>
-      <c r="I28" s="94"/>
-      <c r="J28" s="94"/>
-      <c r="K28" s="94"/>
+      <c r="C28" s="130"/>
+      <c r="D28" s="130"/>
+      <c r="E28" s="130"/>
+      <c r="F28" s="130"/>
+      <c r="G28" s="130"/>
+      <c r="H28" s="130"/>
+      <c r="I28" s="130"/>
+      <c r="J28" s="130"/>
+      <c r="K28" s="130"/>
       <c r="M28" s="1"/>
       <c r="O28" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6519,15 +6548,15 @@
     </row>
     <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="1"/>
-      <c r="C29" s="93"/>
-      <c r="D29" s="93"/>
-      <c r="E29" s="93"/>
-      <c r="F29" s="93"/>
-      <c r="G29" s="93"/>
-      <c r="H29" s="93"/>
-      <c r="I29" s="93"/>
-      <c r="J29" s="93"/>
-      <c r="K29" s="93"/>
+      <c r="C29" s="131"/>
+      <c r="D29" s="131"/>
+      <c r="E29" s="131"/>
+      <c r="F29" s="131"/>
+      <c r="G29" s="131"/>
+      <c r="H29" s="131"/>
+      <c r="I29" s="131"/>
+      <c r="J29" s="131"/>
+      <c r="K29" s="131"/>
       <c r="M29" s="1"/>
       <c r="O29" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6591,15 +6620,15 @@
     </row>
     <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="1"/>
-      <c r="C30" s="94"/>
-      <c r="D30" s="94"/>
-      <c r="E30" s="94"/>
-      <c r="F30" s="94"/>
-      <c r="G30" s="94"/>
-      <c r="H30" s="94"/>
-      <c r="I30" s="94"/>
-      <c r="J30" s="94"/>
-      <c r="K30" s="94"/>
+      <c r="C30" s="130"/>
+      <c r="D30" s="130"/>
+      <c r="E30" s="130"/>
+      <c r="F30" s="130"/>
+      <c r="G30" s="130"/>
+      <c r="H30" s="130"/>
+      <c r="I30" s="130"/>
+      <c r="J30" s="130"/>
+      <c r="K30" s="130"/>
       <c r="M30" s="1"/>
       <c r="O30" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6663,15 +6692,15 @@
     </row>
     <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="1"/>
-      <c r="C31" s="93"/>
-      <c r="D31" s="93"/>
-      <c r="E31" s="93"/>
-      <c r="F31" s="93"/>
-      <c r="G31" s="93"/>
-      <c r="H31" s="93"/>
-      <c r="I31" s="93"/>
-      <c r="J31" s="93"/>
-      <c r="K31" s="93"/>
+      <c r="C31" s="131"/>
+      <c r="D31" s="131"/>
+      <c r="E31" s="131"/>
+      <c r="F31" s="131"/>
+      <c r="G31" s="131"/>
+      <c r="H31" s="131"/>
+      <c r="I31" s="131"/>
+      <c r="J31" s="131"/>
+      <c r="K31" s="131"/>
       <c r="M31" s="1"/>
       <c r="O31" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6805,7 +6834,7 @@
       </c>
       <c r="AF32" s="1"/>
     </row>
-    <row r="33" spans="1:32" ht="12.6" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A33" s="1"/>
       <c r="M33" s="1"/>
       <c r="AF33" s="1"/>
@@ -6844,101 +6873,130 @@
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
     </row>
-    <row r="37" spans="1:32" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="37" spans="1:32" ht="12.9" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="38" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D38" s="119" t="s">
+      <c r="D38" s="83" t="s">
+        <v>30</v>
+      </c>
+      <c r="E38" s="84"/>
+      <c r="F38" s="85"/>
+      <c r="G38" s="89">
+        <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
+        <v>5</v>
+      </c>
+      <c r="H38" s="90"/>
+      <c r="I38" s="83" t="s">
+        <v>33</v>
+      </c>
+      <c r="J38" s="93"/>
+      <c r="K38" s="95" t="s">
         <v>31</v>
       </c>
-      <c r="E38" s="120"/>
-      <c r="F38" s="145"/>
-      <c r="G38" s="121">
-        <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
-        <v>7</v>
-      </c>
-      <c r="H38" s="122"/>
-      <c r="I38" s="119" t="s">
-        <v>34</v>
-      </c>
-      <c r="J38" s="133"/>
-      <c r="K38" s="134" t="s">
+      <c r="L38" s="96"/>
+      <c r="M38" s="99">
+        <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
+        <v>5.9999999999999973</v>
+      </c>
+      <c r="N38" s="100"/>
+      <c r="O38" s="100"/>
+      <c r="P38" s="100"/>
+      <c r="Q38" s="100"/>
+      <c r="R38" s="101"/>
+      <c r="S38" s="105" t="s">
         <v>32</v>
       </c>
-      <c r="L38" s="135"/>
-      <c r="M38" s="136">
-        <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
-        <v>1.9999999999999991</v>
-      </c>
-      <c r="N38" s="137"/>
-      <c r="O38" s="137"/>
-      <c r="P38" s="137"/>
-      <c r="Q38" s="137"/>
-      <c r="R38" s="138"/>
-      <c r="S38" s="131" t="s">
-        <v>33</v>
-      </c>
-      <c r="T38" s="127"/>
-      <c r="U38" s="127"/>
-      <c r="V38" s="127"/>
-      <c r="W38" s="127"/>
-      <c r="X38" s="128"/>
+      <c r="T38" s="106"/>
+      <c r="U38" s="106"/>
+      <c r="V38" s="106"/>
+      <c r="W38" s="106"/>
+      <c r="X38" s="107"/>
     </row>
     <row r="39" spans="1:32" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D39" s="123"/>
-      <c r="E39" s="124"/>
-      <c r="F39" s="146"/>
-      <c r="G39" s="125"/>
-      <c r="H39" s="126"/>
-      <c r="I39" s="123"/>
-      <c r="J39" s="139"/>
-      <c r="K39" s="140"/>
-      <c r="L39" s="141"/>
-      <c r="M39" s="142"/>
-      <c r="N39" s="143"/>
-      <c r="O39" s="143"/>
-      <c r="P39" s="143"/>
-      <c r="Q39" s="143"/>
-      <c r="R39" s="144"/>
-      <c r="S39" s="132"/>
-      <c r="T39" s="129"/>
-      <c r="U39" s="129"/>
-      <c r="V39" s="129"/>
-      <c r="W39" s="129"/>
-      <c r="X39" s="130"/>
-    </row>
-    <row r="40" spans="1:32" ht="12.6" x14ac:dyDescent="0.45"/>
+      <c r="D39" s="86"/>
+      <c r="E39" s="87"/>
+      <c r="F39" s="88"/>
+      <c r="G39" s="91"/>
+      <c r="H39" s="92"/>
+      <c r="I39" s="86"/>
+      <c r="J39" s="94"/>
+      <c r="K39" s="97"/>
+      <c r="L39" s="98"/>
+      <c r="M39" s="102"/>
+      <c r="N39" s="103"/>
+      <c r="O39" s="103"/>
+      <c r="P39" s="103"/>
+      <c r="Q39" s="103"/>
+      <c r="R39" s="104"/>
+      <c r="S39" s="108"/>
+      <c r="T39" s="109"/>
+      <c r="U39" s="109"/>
+      <c r="V39" s="109"/>
+      <c r="W39" s="109"/>
+      <c r="X39" s="110"/>
+    </row>
   </sheetData>
   <mergeCells count="112">
-    <mergeCell ref="D38:F39"/>
-    <mergeCell ref="G38:H39"/>
-    <mergeCell ref="I38:J39"/>
-    <mergeCell ref="K38:L39"/>
-    <mergeCell ref="M38:R39"/>
-    <mergeCell ref="S38:X39"/>
-    <mergeCell ref="C30:K31"/>
-    <mergeCell ref="O20:V20"/>
-    <mergeCell ref="W20:AD20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:N21"/>
-    <mergeCell ref="O21:V21"/>
-    <mergeCell ref="W21:AD21"/>
-    <mergeCell ref="C2:AD2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="W5:AD5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="O5:V5"/>
+    <mergeCell ref="K18:N18"/>
+    <mergeCell ref="W18:AD18"/>
+    <mergeCell ref="C25:K26"/>
+    <mergeCell ref="O25:U25"/>
+    <mergeCell ref="X25:AD25"/>
+    <mergeCell ref="C27:K27"/>
+    <mergeCell ref="C28:K29"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="O18:V18"/>
+    <mergeCell ref="C19:D20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:N20"/>
+    <mergeCell ref="W15:AD15"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="O17:V17"/>
+    <mergeCell ref="W17:AD17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="O15:V15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="W12:AD12"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O14:V14"/>
+    <mergeCell ref="W14:AD14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="O12:V12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="W9:AD9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="O11:V11"/>
+    <mergeCell ref="W11:AD11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:V9"/>
+    <mergeCell ref="K9:N9"/>
     <mergeCell ref="K6:N6"/>
     <mergeCell ref="C7:D8"/>
     <mergeCell ref="E7:F7"/>
@@ -6959,67 +7017,37 @@
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="O6:V6"/>
     <mergeCell ref="W6:AD6"/>
-    <mergeCell ref="W9:AD9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="O11:V11"/>
-    <mergeCell ref="W11:AD11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:V9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="W12:AD12"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="O14:V14"/>
-    <mergeCell ref="W14:AD14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="O12:V12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="W15:AD15"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="O17:V17"/>
-    <mergeCell ref="W17:AD17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="O15:V15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="K18:N18"/>
-    <mergeCell ref="W18:AD18"/>
-    <mergeCell ref="C25:K26"/>
-    <mergeCell ref="O25:U25"/>
-    <mergeCell ref="X25:AD25"/>
-    <mergeCell ref="C27:K27"/>
-    <mergeCell ref="C28:K29"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="O18:V18"/>
-    <mergeCell ref="C19:D20"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:N20"/>
+    <mergeCell ref="C2:AD2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="W5:AD5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="O5:V5"/>
+    <mergeCell ref="D38:F39"/>
+    <mergeCell ref="G38:H39"/>
+    <mergeCell ref="I38:J39"/>
+    <mergeCell ref="K38:L39"/>
+    <mergeCell ref="M38:R39"/>
+    <mergeCell ref="S38:X39"/>
+    <mergeCell ref="C30:K31"/>
+    <mergeCell ref="O20:V20"/>
+    <mergeCell ref="W20:AD20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:N21"/>
+    <mergeCell ref="O21:V21"/>
+    <mergeCell ref="W21:AD21"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 E5 G5 I5 K5:L5 O5 W5 C7 E8 G8 I8 K8:L8 O8 W8 C10 E11 G11 I11 K11:L11 O11 W11 C13 E14 G14 I14 K14:L14 O14 W14 C16 E17 G17 I17 K17 O17 W17">
     <cfRule type="expression" dxfId="3" priority="3">
@@ -7053,35 +7081,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="30" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cec0622158e8f13124e9e8fd4de31bd1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3b52f30ab005d15df08657af532e6e38" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -7399,27 +7398,36 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F0D3479-5903-425F-9669-62B4E7216DE9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B201CC6-7A0A-429C-B445-7EDA1CF4A1D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{652EDDE9-C911-407A-9906-647D87C81E69}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7440,6 +7448,26 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B201CC6-7A0A-429C-B445-7EDA1CF4A1D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F0D3479-5903-425F-9669-62B4E7216DE9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata"/>
 </file>
--- a/Group_milestones.xlsx
+++ b/Group_milestones.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="170" documentId="8_{E3DD19CA-42A4-4FC4-9F7E-AFC078DE9187}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DDFB911E-7937-4E21-ADD4-F23BA8FBE6F8}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{916827F6-E579-45A9-A0BF-AC19F3C06EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="2898" yWindow="2898" windowWidth="17280" windowHeight="10254" tabRatio="824" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="824" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="52" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="47" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
   <si>
     <t>Notes</t>
   </si>
@@ -158,18 +158,6 @@
     <t>MCTR1: ICD templates, carriage build</t>
   </si>
   <si>
-    <t>MCTR1: ICD complete with- REII,EEII1?</t>
-  </si>
-  <si>
-    <t>MCTR1: Enclosure final + fit test</t>
-  </si>
-  <si>
-    <t>Group: First integration test</t>
-  </si>
-  <si>
-    <t>Group: Integration successful</t>
-  </si>
-  <si>
     <t>Group: Final touches</t>
   </si>
   <si>
@@ -177,9 +165,6 @@
   </si>
   <si>
     <t>MCTR1: carriage v2 test</t>
-  </si>
-  <si>
-    <t>MCTR1: Carriage motor drive test, carriage v3 test</t>
   </si>
   <si>
     <t>MCTR1: Enclosure v1 test, ICD complete with- MCTR2?</t>
@@ -214,6 +199,86 @@
   <si>
     <t>MCTR1: Carriage v2 build</t>
   </si>
+  <si>
+    <t>MCTR1: ICD complete with- REII</t>
+  </si>
+  <si>
+    <t>EEII1: ICD complete with REII and MCTR2</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">MCTR1: Carriage motor drive test, carriage v3 test </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EEII1:Order heat sinks and power supply(at the latest)</t>
+    </r>
+  </si>
+  <si>
+    <t>EEII1:Working low voltage switching circuit in thevinin lab(one IGBT +driver +opto)</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Group: First integration test                               </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EEII1: Testing with PWM of REII in Heavy current lab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">MCTR1: Enclosure final + fit test                    </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve"> EEII1: Final Drive circuit complete+DB box wired</t>
+  </si>
+  <si>
+    <t>EEII1: PCB manufactured by MR van Huysteen</t>
+  </si>
+  <si>
+    <t>EERI 324</t>
+  </si>
+  <si>
+    <t>EERI 321</t>
+  </si>
+  <si>
+    <t>EEII 321</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">EERI 325             </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Group: Integration successful</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -226,7 +291,7 @@
     <numFmt numFmtId="167" formatCode="mmmm\ yyyy"/>
     <numFmt numFmtId="168" formatCode="dddd"/>
   </numFmts>
-  <fonts count="38" x14ac:knownFonts="1">
+  <fonts count="41" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -471,6 +536,24 @@
       <name val="Seaford"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF00B0F0"/>
+      <name val="Seaford"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF7030A0"/>
+      <name val="Seaford"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Seaford"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -699,7 +782,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="160">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -927,6 +1010,96 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1011,78 +1184,27 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1092,14 +1214,8 @@
     <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
@@ -1107,6 +1223,15 @@
     <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -1114,42 +1239,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -1314,10 +1403,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1527,7 +1612,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R15"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.3" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="5.5546875" style="3" customWidth="1"/>
     <col min="5" max="9" width="10.5546875" style="3" customWidth="1"/>
@@ -1539,7 +1624,7 @@
     <col min="19" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1559,7 +1644,7 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
     </row>
-    <row r="2" spans="1:18" s="7" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:18" s="7" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="5"/>
       <c r="C2" s="73" t="s">
@@ -1581,7 +1666,7 @@
       <c r="Q2" s="6"/>
       <c r="R2" s="4"/>
     </row>
-    <row r="3" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="2.15">
+    <row r="3" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="8"/>
@@ -1601,7 +1686,7 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -1615,15 +1700,15 @@
       <c r="K4" s="12"/>
       <c r="L4" s="11"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="134" t="s">
+      <c r="N4" s="142" t="s">
         <v>10</v>
       </c>
-      <c r="O4" s="134"/>
-      <c r="P4" s="134"/>
-      <c r="Q4" s="134"/>
+      <c r="O4" s="142"/>
+      <c r="P4" s="142"/>
+      <c r="Q4" s="142"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="11"/>
       <c r="C5" s="13" t="s">
@@ -1641,13 +1726,13 @@
       <c r="K5" s="15"/>
       <c r="L5" s="16"/>
       <c r="M5" s="4"/>
-      <c r="N5" s="134"/>
-      <c r="O5" s="134"/>
-      <c r="P5" s="134"/>
-      <c r="Q5" s="134"/>
+      <c r="N5" s="142"/>
+      <c r="O5" s="142"/>
+      <c r="P5" s="142"/>
+      <c r="Q5" s="142"/>
       <c r="R5" s="1"/>
     </row>
-    <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="11"/>
       <c r="C6" s="17"/>
@@ -1661,13 +1746,13 @@
       <c r="K6" s="20"/>
       <c r="L6" s="19"/>
       <c r="M6" s="4"/>
-      <c r="N6" s="134"/>
-      <c r="O6" s="134"/>
-      <c r="P6" s="134"/>
-      <c r="Q6" s="134"/>
+      <c r="N6" s="142"/>
+      <c r="O6" s="142"/>
+      <c r="P6" s="142"/>
+      <c r="Q6" s="142"/>
       <c r="R6" s="1"/>
     </row>
-    <row r="7" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="11"/>
       <c r="C7" s="13" t="s">
@@ -1691,7 +1776,7 @@
       <c r="Q7" s="11"/>
       <c r="R7" s="1"/>
     </row>
-    <row r="8" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1"/>
       <c r="B8" s="11"/>
       <c r="C8" s="17"/>
@@ -1715,7 +1800,7 @@
       </c>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1"/>
       <c r="B9" s="11"/>
       <c r="C9" s="13" t="s">
@@ -1739,7 +1824,7 @@
       <c r="Q9" s="11"/>
       <c r="R9" s="1"/>
     </row>
-    <row r="10" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="11"/>
       <c r="C10" s="24"/>
@@ -1765,7 +1850,7 @@
       <c r="Q10" s="18"/>
       <c r="R10" s="1"/>
     </row>
-    <row r="11" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="11"/>
       <c r="C11" s="24"/>
@@ -1785,7 +1870,7 @@
       <c r="Q11" s="18"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="11"/>
       <c r="C12" s="13" t="s">
@@ -1809,7 +1894,7 @@
       <c r="Q12" s="18"/>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="11"/>
       <c r="C13" s="25"/>
@@ -1831,7 +1916,7 @@
       <c r="Q13" s="18"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="11"/>
       <c r="C14" s="18"/>
@@ -1851,7 +1936,7 @@
       <c r="Q14" s="18"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1886,7 +1971,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AP40"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="12.6" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="5.5546875" style="3" customWidth="1"/>
     <col min="4" max="4" width="15.5546875" style="3" customWidth="1"/>
@@ -1904,7 +1989,7 @@
     <col min="35" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1938,42 +2023,42 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="2.15">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A2" s="29"/>
-      <c r="C2" s="114">
+      <c r="C2" s="111">
         <f ca="1">DATE(About!P8,9,1)</f>
         <v>46266</v>
       </c>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
-      <c r="I2" s="114"/>
-      <c r="J2" s="114"/>
-      <c r="K2" s="114"/>
-      <c r="L2" s="114"/>
-      <c r="M2" s="114"/>
-      <c r="N2" s="114"/>
-      <c r="O2" s="114"/>
-      <c r="P2" s="114"/>
-      <c r="Q2" s="114"/>
-      <c r="R2" s="114"/>
-      <c r="S2" s="114"/>
-      <c r="T2" s="114"/>
-      <c r="U2" s="114"/>
-      <c r="V2" s="114"/>
-      <c r="W2" s="114"/>
-      <c r="X2" s="114"/>
-      <c r="Y2" s="114"/>
-      <c r="Z2" s="114"/>
-      <c r="AA2" s="114"/>
-      <c r="AB2" s="114"/>
-      <c r="AC2" s="114"/>
-      <c r="AD2" s="114"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="111"/>
+      <c r="G2" s="111"/>
+      <c r="H2" s="111"/>
+      <c r="I2" s="111"/>
+      <c r="J2" s="111"/>
+      <c r="K2" s="111"/>
+      <c r="L2" s="111"/>
+      <c r="M2" s="111"/>
+      <c r="N2" s="111"/>
+      <c r="O2" s="111"/>
+      <c r="P2" s="111"/>
+      <c r="Q2" s="111"/>
+      <c r="R2" s="111"/>
+      <c r="S2" s="111"/>
+      <c r="T2" s="111"/>
+      <c r="U2" s="111"/>
+      <c r="V2" s="111"/>
+      <c r="W2" s="111"/>
+      <c r="X2" s="111"/>
+      <c r="Y2" s="111"/>
+      <c r="Z2" s="111"/>
+      <c r="AA2" s="111"/>
+      <c r="AB2" s="111"/>
+      <c r="AC2" s="111"/>
+      <c r="AD2" s="111"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="2.15">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -1993,278 +2078,278 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="35"/>
-      <c r="C4" s="115">
+      <c r="C4" s="112">
         <f ca="1">C5</f>
         <v>46264</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115">
+      <c r="D4" s="112"/>
+      <c r="E4" s="112">
         <f ca="1">E5</f>
         <v>46265</v>
       </c>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115">
+      <c r="F4" s="112"/>
+      <c r="G4" s="112">
         <f ca="1">G5</f>
         <v>46266</v>
       </c>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115">
+      <c r="H4" s="112"/>
+      <c r="I4" s="112">
         <f ca="1">I5</f>
         <v>46267</v>
       </c>
-      <c r="J4" s="115"/>
-      <c r="K4" s="115">
+      <c r="J4" s="112"/>
+      <c r="K4" s="112">
         <f ca="1">K5</f>
         <v>46268</v>
       </c>
-      <c r="L4" s="115"/>
-      <c r="M4" s="115"/>
+      <c r="L4" s="112"/>
+      <c r="M4" s="112"/>
       <c r="N4" s="37"/>
-      <c r="O4" s="115">
+      <c r="O4" s="112">
         <f ca="1">O5</f>
         <v>46269</v>
       </c>
-      <c r="P4" s="115"/>
-      <c r="Q4" s="115"/>
-      <c r="R4" s="115"/>
-      <c r="S4" s="115"/>
-      <c r="T4" s="115"/>
-      <c r="U4" s="115"/>
-      <c r="V4" s="115"/>
-      <c r="W4" s="115">
+      <c r="P4" s="112"/>
+      <c r="Q4" s="112"/>
+      <c r="R4" s="112"/>
+      <c r="S4" s="112"/>
+      <c r="T4" s="112"/>
+      <c r="U4" s="112"/>
+      <c r="V4" s="112"/>
+      <c r="W4" s="112">
         <f ca="1">W5</f>
         <v>46270</v>
       </c>
-      <c r="X4" s="115"/>
-      <c r="Y4" s="115"/>
-      <c r="Z4" s="115"/>
-      <c r="AA4" s="115"/>
-      <c r="AB4" s="115"/>
-      <c r="AC4" s="115"/>
-      <c r="AD4" s="115"/>
+      <c r="X4" s="112"/>
+      <c r="Y4" s="112"/>
+      <c r="Z4" s="112"/>
+      <c r="AA4" s="112"/>
+      <c r="AB4" s="112"/>
+      <c r="AC4" s="112"/>
+      <c r="AD4" s="112"/>
       <c r="AF4" s="38"/>
       <c r="AG4" s="39"/>
       <c r="AH4" s="39"/>
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="C5" s="116">
+      <c r="C5" s="91">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46264</v>
       </c>
-      <c r="D5" s="118"/>
-      <c r="E5" s="116">
+      <c r="D5" s="92"/>
+      <c r="E5" s="91">
         <f ca="1">C5+1</f>
         <v>46265</v>
       </c>
-      <c r="F5" s="118"/>
-      <c r="G5" s="116">
+      <c r="F5" s="92"/>
+      <c r="G5" s="91">
         <f ca="1">E5+1</f>
         <v>46266</v>
       </c>
-      <c r="H5" s="118"/>
-      <c r="I5" s="116">
+      <c r="H5" s="92"/>
+      <c r="I5" s="91">
         <f ca="1">G5+1</f>
         <v>46267</v>
       </c>
-      <c r="J5" s="118"/>
-      <c r="K5" s="116">
+      <c r="J5" s="92"/>
+      <c r="K5" s="91">
         <f ca="1">I5+1</f>
         <v>46268</v>
       </c>
-      <c r="L5" s="117"/>
-      <c r="M5" s="117"/>
+      <c r="L5" s="110"/>
+      <c r="M5" s="110"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="116">
+      <c r="O5" s="91">
         <f ca="1">K5+1</f>
         <v>46269</v>
       </c>
-      <c r="P5" s="117"/>
-      <c r="Q5" s="117"/>
-      <c r="R5" s="117"/>
-      <c r="S5" s="117"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="117"/>
-      <c r="V5" s="118"/>
-      <c r="W5" s="116">
+      <c r="P5" s="110"/>
+      <c r="Q5" s="110"/>
+      <c r="R5" s="110"/>
+      <c r="S5" s="110"/>
+      <c r="T5" s="110"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="92"/>
+      <c r="W5" s="91">
         <f ca="1">O5+1</f>
         <v>46270</v>
       </c>
-      <c r="X5" s="117"/>
-      <c r="Y5" s="117"/>
-      <c r="Z5" s="117"/>
-      <c r="AA5" s="117"/>
-      <c r="AB5" s="117"/>
-      <c r="AC5" s="117"/>
-      <c r="AD5" s="118"/>
+      <c r="X5" s="110"/>
+      <c r="Y5" s="110"/>
+      <c r="Z5" s="110"/>
+      <c r="AA5" s="110"/>
+      <c r="AB5" s="110"/>
+      <c r="AC5" s="110"/>
+      <c r="AD5" s="92"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
       <c r="AI5" s="41"/>
       <c r="AJ5" s="41"/>
     </row>
-    <row r="6" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="42"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="113"/>
-      <c r="E6" s="111"/>
-      <c r="F6" s="113"/>
-      <c r="G6" s="135"/>
-      <c r="H6" s="136"/>
-      <c r="I6" s="135"/>
-      <c r="J6" s="136"/>
-      <c r="K6" s="135"/>
-      <c r="L6" s="137"/>
-      <c r="M6" s="137"/>
-      <c r="N6" s="136"/>
-      <c r="O6" s="135"/>
-      <c r="P6" s="137"/>
-      <c r="Q6" s="137"/>
-      <c r="R6" s="137"/>
-      <c r="S6" s="137"/>
-      <c r="T6" s="137"/>
-      <c r="U6" s="137"/>
-      <c r="V6" s="136"/>
-      <c r="W6" s="135"/>
-      <c r="X6" s="137"/>
-      <c r="Y6" s="137"/>
-      <c r="Z6" s="137"/>
-      <c r="AA6" s="137"/>
-      <c r="AB6" s="137"/>
-      <c r="AC6" s="137"/>
-      <c r="AD6" s="136"/>
+      <c r="C6" s="96"/>
+      <c r="D6" s="97"/>
+      <c r="E6" s="96"/>
+      <c r="F6" s="97"/>
+      <c r="G6" s="148"/>
+      <c r="H6" s="149"/>
+      <c r="I6" s="148"/>
+      <c r="J6" s="149"/>
+      <c r="K6" s="148"/>
+      <c r="L6" s="150"/>
+      <c r="M6" s="150"/>
+      <c r="N6" s="149"/>
+      <c r="O6" s="148"/>
+      <c r="P6" s="150"/>
+      <c r="Q6" s="150"/>
+      <c r="R6" s="150"/>
+      <c r="S6" s="150"/>
+      <c r="T6" s="150"/>
+      <c r="U6" s="150"/>
+      <c r="V6" s="149"/>
+      <c r="W6" s="148"/>
+      <c r="X6" s="150"/>
+      <c r="Y6" s="150"/>
+      <c r="Z6" s="150"/>
+      <c r="AA6" s="150"/>
+      <c r="AB6" s="150"/>
+      <c r="AC6" s="150"/>
+      <c r="AD6" s="149"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
-    <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
-      <c r="C7" s="116">
+      <c r="C7" s="91">
         <f ca="1">W5+1</f>
         <v>46271</v>
       </c>
-      <c r="D7" s="118"/>
-      <c r="E7" s="124"/>
-      <c r="F7" s="125"/>
-      <c r="G7" s="124"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="124"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="124"/>
-      <c r="L7" s="126"/>
-      <c r="M7" s="126"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="99"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="100"/>
+      <c r="I7" s="99"/>
+      <c r="J7" s="100"/>
+      <c r="K7" s="99"/>
+      <c r="L7" s="101"/>
+      <c r="M7" s="101"/>
       <c r="N7" s="75"/>
-      <c r="O7" s="124"/>
-      <c r="P7" s="126"/>
-      <c r="Q7" s="126"/>
-      <c r="R7" s="126"/>
-      <c r="S7" s="126"/>
-      <c r="T7" s="126"/>
-      <c r="U7" s="126"/>
-      <c r="V7" s="125"/>
-      <c r="W7" s="124"/>
-      <c r="X7" s="126"/>
-      <c r="Y7" s="126"/>
-      <c r="Z7" s="126"/>
-      <c r="AA7" s="126"/>
-      <c r="AB7" s="126"/>
-      <c r="AC7" s="126"/>
-      <c r="AD7" s="125"/>
+      <c r="O7" s="99"/>
+      <c r="P7" s="101"/>
+      <c r="Q7" s="101"/>
+      <c r="R7" s="101"/>
+      <c r="S7" s="101"/>
+      <c r="T7" s="101"/>
+      <c r="U7" s="101"/>
+      <c r="V7" s="100"/>
+      <c r="W7" s="99"/>
+      <c r="X7" s="101"/>
+      <c r="Y7" s="101"/>
+      <c r="Z7" s="101"/>
+      <c r="AA7" s="101"/>
+      <c r="AB7" s="101"/>
+      <c r="AC7" s="101"/>
+      <c r="AD7" s="100"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
-      <c r="C8" s="116"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="127">
+      <c r="C8" s="91"/>
+      <c r="D8" s="92"/>
+      <c r="E8" s="93">
         <f ca="1">C7+1</f>
         <v>46272</v>
       </c>
-      <c r="F8" s="128"/>
-      <c r="G8" s="127">
+      <c r="F8" s="94"/>
+      <c r="G8" s="93">
         <f ca="1">E8+1</f>
         <v>46273</v>
       </c>
-      <c r="H8" s="128"/>
-      <c r="I8" s="127">
+      <c r="H8" s="94"/>
+      <c r="I8" s="93">
         <f ca="1">G8+1</f>
         <v>46274</v>
       </c>
-      <c r="J8" s="128"/>
-      <c r="K8" s="127">
+      <c r="J8" s="94"/>
+      <c r="K8" s="93">
         <f ca="1">I8+1</f>
         <v>46275</v>
       </c>
-      <c r="L8" s="129"/>
-      <c r="M8" s="129"/>
+      <c r="L8" s="95"/>
+      <c r="M8" s="95"/>
       <c r="N8" s="50"/>
-      <c r="O8" s="127">
+      <c r="O8" s="93">
         <f ca="1">K8+1</f>
         <v>46276</v>
       </c>
-      <c r="P8" s="129"/>
-      <c r="Q8" s="129"/>
-      <c r="R8" s="129"/>
-      <c r="S8" s="129"/>
-      <c r="T8" s="129"/>
-      <c r="U8" s="129"/>
-      <c r="V8" s="128"/>
-      <c r="W8" s="127">
+      <c r="P8" s="95"/>
+      <c r="Q8" s="95"/>
+      <c r="R8" s="95"/>
+      <c r="S8" s="95"/>
+      <c r="T8" s="95"/>
+      <c r="U8" s="95"/>
+      <c r="V8" s="94"/>
+      <c r="W8" s="93">
         <f ca="1">O8+1</f>
         <v>46277</v>
       </c>
-      <c r="X8" s="129"/>
-      <c r="Y8" s="129"/>
-      <c r="Z8" s="129"/>
-      <c r="AA8" s="129"/>
-      <c r="AB8" s="129"/>
-      <c r="AC8" s="129"/>
-      <c r="AD8" s="128"/>
+      <c r="X8" s="95"/>
+      <c r="Y8" s="95"/>
+      <c r="Z8" s="95"/>
+      <c r="AA8" s="95"/>
+      <c r="AB8" s="95"/>
+      <c r="AC8" s="95"/>
+      <c r="AD8" s="94"/>
       <c r="AF8" s="4"/>
     </row>
-    <row r="9" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="42"/>
-      <c r="C9" s="135"/>
-      <c r="D9" s="136"/>
-      <c r="E9" s="135"/>
-      <c r="F9" s="136"/>
-      <c r="G9" s="135"/>
-      <c r="H9" s="136"/>
-      <c r="I9" s="135"/>
-      <c r="J9" s="136"/>
-      <c r="K9" s="135"/>
-      <c r="L9" s="137"/>
-      <c r="M9" s="137"/>
-      <c r="N9" s="136"/>
-      <c r="O9" s="135"/>
-      <c r="P9" s="137"/>
-      <c r="Q9" s="137"/>
-      <c r="R9" s="137"/>
-      <c r="S9" s="137"/>
-      <c r="T9" s="137"/>
-      <c r="U9" s="137"/>
-      <c r="V9" s="136"/>
-      <c r="W9" s="135"/>
-      <c r="X9" s="137"/>
-      <c r="Y9" s="137"/>
-      <c r="Z9" s="137"/>
-      <c r="AA9" s="137"/>
-      <c r="AB9" s="137"/>
-      <c r="AC9" s="137"/>
-      <c r="AD9" s="136"/>
+      <c r="C9" s="148"/>
+      <c r="D9" s="149"/>
+      <c r="E9" s="148"/>
+      <c r="F9" s="149"/>
+      <c r="G9" s="148"/>
+      <c r="H9" s="149"/>
+      <c r="I9" s="148"/>
+      <c r="J9" s="149"/>
+      <c r="K9" s="148"/>
+      <c r="L9" s="150"/>
+      <c r="M9" s="150"/>
+      <c r="N9" s="149"/>
+      <c r="O9" s="148"/>
+      <c r="P9" s="150"/>
+      <c r="Q9" s="150"/>
+      <c r="R9" s="150"/>
+      <c r="S9" s="150"/>
+      <c r="T9" s="150"/>
+      <c r="U9" s="150"/>
+      <c r="V9" s="149"/>
+      <c r="W9" s="148"/>
+      <c r="X9" s="150"/>
+      <c r="Y9" s="150"/>
+      <c r="Z9" s="150"/>
+      <c r="AA9" s="150"/>
+      <c r="AB9" s="150"/>
+      <c r="AC9" s="150"/>
+      <c r="AD9" s="149"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
-    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="42"/>
-      <c r="C10" s="116">
+      <c r="C10" s="91">
         <f ca="1">W8+1</f>
         <v>46278</v>
       </c>
-      <c r="D10" s="118"/>
+      <c r="D10" s="92"/>
       <c r="E10" s="45"/>
       <c r="F10" s="75"/>
       <c r="G10" s="45"/>
@@ -2294,97 +2379,97 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="42"/>
     </row>
-    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
-      <c r="C11" s="116"/>
-      <c r="D11" s="118"/>
-      <c r="E11" s="127">
+      <c r="C11" s="91"/>
+      <c r="D11" s="92"/>
+      <c r="E11" s="93">
         <f ca="1">C10+1</f>
         <v>46279</v>
       </c>
-      <c r="F11" s="128"/>
-      <c r="G11" s="127">
+      <c r="F11" s="94"/>
+      <c r="G11" s="93">
         <f ca="1">E11+1</f>
         <v>46280</v>
       </c>
-      <c r="H11" s="128"/>
-      <c r="I11" s="127">
+      <c r="H11" s="94"/>
+      <c r="I11" s="93">
         <f ca="1">G11+1</f>
         <v>46281</v>
       </c>
-      <c r="J11" s="128"/>
-      <c r="K11" s="127">
+      <c r="J11" s="94"/>
+      <c r="K11" s="93">
         <f ca="1">I11+1</f>
         <v>46282</v>
       </c>
-      <c r="L11" s="129"/>
-      <c r="M11" s="129"/>
+      <c r="L11" s="95"/>
+      <c r="M11" s="95"/>
       <c r="N11" s="50"/>
-      <c r="O11" s="127">
+      <c r="O11" s="93">
         <f ca="1">K11+1</f>
         <v>46283</v>
       </c>
-      <c r="P11" s="129"/>
-      <c r="Q11" s="129"/>
-      <c r="R11" s="129"/>
-      <c r="S11" s="129"/>
-      <c r="T11" s="129"/>
-      <c r="U11" s="129"/>
-      <c r="V11" s="128"/>
-      <c r="W11" s="127">
+      <c r="P11" s="95"/>
+      <c r="Q11" s="95"/>
+      <c r="R11" s="95"/>
+      <c r="S11" s="95"/>
+      <c r="T11" s="95"/>
+      <c r="U11" s="95"/>
+      <c r="V11" s="94"/>
+      <c r="W11" s="93">
         <f ca="1">O11+1</f>
         <v>46284</v>
       </c>
-      <c r="X11" s="129"/>
-      <c r="Y11" s="129"/>
-      <c r="Z11" s="129"/>
-      <c r="AA11" s="129"/>
-      <c r="AB11" s="129"/>
-      <c r="AC11" s="129"/>
-      <c r="AD11" s="128"/>
+      <c r="X11" s="95"/>
+      <c r="Y11" s="95"/>
+      <c r="Z11" s="95"/>
+      <c r="AA11" s="95"/>
+      <c r="AB11" s="95"/>
+      <c r="AC11" s="95"/>
+      <c r="AD11" s="94"/>
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="42"/>
-      <c r="C12" s="135"/>
-      <c r="D12" s="136"/>
-      <c r="E12" s="135"/>
-      <c r="F12" s="136"/>
-      <c r="G12" s="135"/>
-      <c r="H12" s="136"/>
-      <c r="I12" s="135"/>
-      <c r="J12" s="136"/>
-      <c r="K12" s="135"/>
-      <c r="L12" s="137"/>
-      <c r="M12" s="137"/>
-      <c r="N12" s="136"/>
-      <c r="O12" s="135"/>
-      <c r="P12" s="137"/>
-      <c r="Q12" s="137"/>
-      <c r="R12" s="137"/>
-      <c r="S12" s="137"/>
-      <c r="T12" s="137"/>
-      <c r="U12" s="137"/>
-      <c r="V12" s="136"/>
-      <c r="W12" s="135"/>
-      <c r="X12" s="137"/>
-      <c r="Y12" s="137"/>
-      <c r="Z12" s="137"/>
-      <c r="AA12" s="137"/>
-      <c r="AB12" s="137"/>
-      <c r="AC12" s="137"/>
-      <c r="AD12" s="136"/>
+      <c r="C12" s="148"/>
+      <c r="D12" s="149"/>
+      <c r="E12" s="148"/>
+      <c r="F12" s="149"/>
+      <c r="G12" s="148"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="148"/>
+      <c r="J12" s="149"/>
+      <c r="K12" s="148"/>
+      <c r="L12" s="150"/>
+      <c r="M12" s="150"/>
+      <c r="N12" s="149"/>
+      <c r="O12" s="148"/>
+      <c r="P12" s="150"/>
+      <c r="Q12" s="150"/>
+      <c r="R12" s="150"/>
+      <c r="S12" s="150"/>
+      <c r="T12" s="150"/>
+      <c r="U12" s="150"/>
+      <c r="V12" s="149"/>
+      <c r="W12" s="148"/>
+      <c r="X12" s="150"/>
+      <c r="Y12" s="150"/>
+      <c r="Z12" s="150"/>
+      <c r="AA12" s="150"/>
+      <c r="AB12" s="150"/>
+      <c r="AC12" s="150"/>
+      <c r="AD12" s="149"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
-    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="42"/>
-      <c r="C13" s="116">
+      <c r="C13" s="91">
         <f ca="1">W11+1</f>
         <v>46285</v>
       </c>
-      <c r="D13" s="118"/>
+      <c r="D13" s="92"/>
       <c r="E13" s="45"/>
       <c r="F13" s="75"/>
       <c r="G13" s="45"/>
@@ -2414,114 +2499,114 @@
       <c r="AE13" s="7"/>
       <c r="AF13" s="42"/>
     </row>
-    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
-      <c r="C14" s="116"/>
-      <c r="D14" s="118"/>
-      <c r="E14" s="127">
+      <c r="C14" s="91"/>
+      <c r="D14" s="92"/>
+      <c r="E14" s="93">
         <f ca="1">C13+1</f>
         <v>46286</v>
       </c>
-      <c r="F14" s="128"/>
-      <c r="G14" s="127">
+      <c r="F14" s="94"/>
+      <c r="G14" s="93">
         <f ca="1">E14+1</f>
         <v>46287</v>
       </c>
-      <c r="H14" s="128"/>
-      <c r="I14" s="127">
+      <c r="H14" s="94"/>
+      <c r="I14" s="93">
         <f ca="1">G14+1</f>
         <v>46288</v>
       </c>
-      <c r="J14" s="128"/>
-      <c r="K14" s="127">
+      <c r="J14" s="94"/>
+      <c r="K14" s="93">
         <f ca="1">I14+1</f>
         <v>46289</v>
       </c>
-      <c r="L14" s="129"/>
-      <c r="M14" s="129"/>
+      <c r="L14" s="95"/>
+      <c r="M14" s="95"/>
       <c r="N14" s="50"/>
-      <c r="O14" s="127">
+      <c r="O14" s="93">
         <f ca="1">K14+1</f>
         <v>46290</v>
       </c>
-      <c r="P14" s="129"/>
-      <c r="Q14" s="129"/>
-      <c r="R14" s="129"/>
-      <c r="S14" s="129"/>
-      <c r="T14" s="129"/>
-      <c r="U14" s="129"/>
-      <c r="V14" s="128"/>
-      <c r="W14" s="127">
+      <c r="P14" s="95"/>
+      <c r="Q14" s="95"/>
+      <c r="R14" s="95"/>
+      <c r="S14" s="95"/>
+      <c r="T14" s="95"/>
+      <c r="U14" s="95"/>
+      <c r="V14" s="94"/>
+      <c r="W14" s="93">
         <f ca="1">O14+1</f>
         <v>46291</v>
       </c>
-      <c r="X14" s="129"/>
-      <c r="Y14" s="129"/>
-      <c r="Z14" s="129"/>
-      <c r="AA14" s="129"/>
-      <c r="AB14" s="129"/>
-      <c r="AC14" s="129"/>
-      <c r="AD14" s="128"/>
+      <c r="X14" s="95"/>
+      <c r="Y14" s="95"/>
+      <c r="Z14" s="95"/>
+      <c r="AA14" s="95"/>
+      <c r="AB14" s="95"/>
+      <c r="AC14" s="95"/>
+      <c r="AD14" s="94"/>
       <c r="AF14" s="4"/>
     </row>
-    <row r="15" spans="1:36" s="43" customFormat="1" ht="162.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:36" s="43" customFormat="1" ht="162.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="42"/>
-      <c r="C15" s="135"/>
-      <c r="D15" s="136"/>
-      <c r="E15" s="135"/>
-      <c r="F15" s="136"/>
-      <c r="G15" s="135"/>
-      <c r="H15" s="136"/>
-      <c r="I15" s="150"/>
-      <c r="J15" s="151"/>
-      <c r="K15" s="150"/>
-      <c r="L15" s="152"/>
-      <c r="M15" s="152"/>
-      <c r="N15" s="151"/>
-      <c r="O15" s="150"/>
-      <c r="P15" s="152"/>
-      <c r="Q15" s="152"/>
-      <c r="R15" s="152"/>
-      <c r="S15" s="152"/>
-      <c r="T15" s="152"/>
-      <c r="U15" s="152"/>
-      <c r="V15" s="151"/>
-      <c r="W15" s="150"/>
-      <c r="X15" s="152"/>
-      <c r="Y15" s="152"/>
-      <c r="Z15" s="152"/>
-      <c r="AA15" s="152"/>
-      <c r="AB15" s="152"/>
-      <c r="AC15" s="152"/>
-      <c r="AD15" s="151"/>
+      <c r="C15" s="148"/>
+      <c r="D15" s="149"/>
+      <c r="E15" s="148"/>
+      <c r="F15" s="149"/>
+      <c r="G15" s="148"/>
+      <c r="H15" s="149"/>
+      <c r="I15" s="104"/>
+      <c r="J15" s="106"/>
+      <c r="K15" s="104"/>
+      <c r="L15" s="105"/>
+      <c r="M15" s="105"/>
+      <c r="N15" s="106"/>
+      <c r="O15" s="104"/>
+      <c r="P15" s="105"/>
+      <c r="Q15" s="105"/>
+      <c r="R15" s="105"/>
+      <c r="S15" s="105"/>
+      <c r="T15" s="105"/>
+      <c r="U15" s="105"/>
+      <c r="V15" s="106"/>
+      <c r="W15" s="104"/>
+      <c r="X15" s="105"/>
+      <c r="Y15" s="105"/>
+      <c r="Z15" s="105"/>
+      <c r="AA15" s="105"/>
+      <c r="AB15" s="105"/>
+      <c r="AC15" s="105"/>
+      <c r="AD15" s="106"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
-    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="42"/>
-      <c r="C16" s="116">
+      <c r="C16" s="91">
         <f ca="1">W14+1</f>
         <v>46292</v>
       </c>
-      <c r="D16" s="118"/>
+      <c r="D16" s="92"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
       <c r="H16" s="75"/>
-      <c r="I16" s="138"/>
-      <c r="J16" s="139"/>
+      <c r="I16" s="145"/>
+      <c r="J16" s="146"/>
       <c r="K16" s="66"/>
       <c r="L16" s="68"/>
       <c r="M16" s="68"/>
       <c r="N16" s="67"/>
-      <c r="O16" s="138"/>
-      <c r="P16" s="140"/>
-      <c r="Q16" s="140"/>
-      <c r="R16" s="140"/>
-      <c r="S16" s="140"/>
-      <c r="T16" s="140"/>
-      <c r="U16" s="140"/>
-      <c r="V16" s="139"/>
+      <c r="O16" s="145"/>
+      <c r="P16" s="147"/>
+      <c r="Q16" s="147"/>
+      <c r="R16" s="147"/>
+      <c r="S16" s="147"/>
+      <c r="T16" s="147"/>
+      <c r="U16" s="147"/>
+      <c r="V16" s="146"/>
       <c r="W16" s="45"/>
       <c r="X16" s="76"/>
       <c r="Y16" s="76"/>
@@ -2533,25 +2618,25 @@
       <c r="AE16" s="7"/>
       <c r="AF16" s="42"/>
     </row>
-    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
-      <c r="C17" s="116"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="127">
+      <c r="C17" s="91"/>
+      <c r="D17" s="92"/>
+      <c r="E17" s="93">
         <f ca="1">C16+1</f>
         <v>46293</v>
       </c>
-      <c r="F17" s="128"/>
-      <c r="G17" s="127">
+      <c r="F17" s="94"/>
+      <c r="G17" s="93">
         <f ca="1">E17+1</f>
         <v>46294</v>
       </c>
-      <c r="H17" s="128"/>
-      <c r="I17" s="127">
+      <c r="H17" s="94"/>
+      <c r="I17" s="93">
         <f ca="1">G17+1</f>
         <v>46295</v>
       </c>
-      <c r="J17" s="128"/>
+      <c r="J17" s="94"/>
       <c r="K17" s="46">
         <f ca="1">I17+1</f>
         <v>46296</v>
@@ -2559,93 +2644,93 @@
       <c r="L17" s="51"/>
       <c r="M17" s="51"/>
       <c r="N17" s="69"/>
-      <c r="O17" s="127">
+      <c r="O17" s="93">
         <f ca="1">K17+1</f>
         <v>46297</v>
       </c>
-      <c r="P17" s="129"/>
-      <c r="Q17" s="129"/>
-      <c r="R17" s="129"/>
-      <c r="S17" s="129"/>
-      <c r="T17" s="129"/>
-      <c r="U17" s="129"/>
-      <c r="V17" s="128"/>
-      <c r="W17" s="127">
+      <c r="P17" s="95"/>
+      <c r="Q17" s="95"/>
+      <c r="R17" s="95"/>
+      <c r="S17" s="95"/>
+      <c r="T17" s="95"/>
+      <c r="U17" s="95"/>
+      <c r="V17" s="94"/>
+      <c r="W17" s="93">
         <f ca="1">O17+1</f>
         <v>46298</v>
       </c>
-      <c r="X17" s="129"/>
-      <c r="Y17" s="129"/>
-      <c r="Z17" s="129"/>
-      <c r="AA17" s="129"/>
-      <c r="AB17" s="129"/>
-      <c r="AC17" s="129"/>
-      <c r="AD17" s="128"/>
+      <c r="X17" s="95"/>
+      <c r="Y17" s="95"/>
+      <c r="Z17" s="95"/>
+      <c r="AA17" s="95"/>
+      <c r="AB17" s="95"/>
+      <c r="AC17" s="95"/>
+      <c r="AD17" s="94"/>
       <c r="AF17" s="4"/>
     </row>
-    <row r="18" spans="1:42" s="43" customFormat="1" ht="147.30000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:42" s="43" customFormat="1" ht="147.30000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="42"/>
-      <c r="C18" s="153" t="s">
-        <v>23</v>
-      </c>
-      <c r="D18" s="154"/>
-      <c r="E18" s="150"/>
-      <c r="F18" s="151"/>
-      <c r="G18" s="150"/>
-      <c r="H18" s="151"/>
-      <c r="I18" s="153" t="s">
+      <c r="C18" s="143" t="s">
+        <v>19</v>
+      </c>
+      <c r="D18" s="144"/>
+      <c r="E18" s="104"/>
+      <c r="F18" s="106"/>
+      <c r="G18" s="104"/>
+      <c r="H18" s="106"/>
+      <c r="I18" s="143" t="s">
         <v>17</v>
       </c>
-      <c r="J18" s="154"/>
+      <c r="J18" s="144"/>
       <c r="K18" s="70"/>
       <c r="L18" s="71"/>
       <c r="M18" s="71"/>
       <c r="N18" s="72"/>
-      <c r="O18" s="111"/>
-      <c r="P18" s="112"/>
-      <c r="Q18" s="112"/>
-      <c r="R18" s="112"/>
-      <c r="S18" s="112"/>
-      <c r="T18" s="112"/>
-      <c r="U18" s="112"/>
-      <c r="V18" s="113"/>
-      <c r="W18" s="111"/>
-      <c r="X18" s="112"/>
-      <c r="Y18" s="112"/>
-      <c r="Z18" s="112"/>
-      <c r="AA18" s="112"/>
-      <c r="AB18" s="112"/>
-      <c r="AC18" s="112"/>
-      <c r="AD18" s="113"/>
+      <c r="O18" s="96"/>
+      <c r="P18" s="141"/>
+      <c r="Q18" s="141"/>
+      <c r="R18" s="141"/>
+      <c r="S18" s="141"/>
+      <c r="T18" s="141"/>
+      <c r="U18" s="141"/>
+      <c r="V18" s="97"/>
+      <c r="W18" s="96"/>
+      <c r="X18" s="141"/>
+      <c r="Y18" s="141"/>
+      <c r="Z18" s="141"/>
+      <c r="AA18" s="141"/>
+      <c r="AB18" s="141"/>
+      <c r="AC18" s="141"/>
+      <c r="AD18" s="97"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
-    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="42"/>
-      <c r="C19" s="116">
+      <c r="C19" s="91">
         <f ca="1">W17+1</f>
         <v>46299</v>
       </c>
-      <c r="D19" s="118"/>
+      <c r="D19" s="92"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
       <c r="H19" s="75"/>
-      <c r="I19" s="138"/>
-      <c r="J19" s="139"/>
+      <c r="I19" s="145"/>
+      <c r="J19" s="146"/>
       <c r="K19" s="66"/>
       <c r="L19" s="68"/>
       <c r="M19" s="68"/>
       <c r="N19" s="67"/>
-      <c r="O19" s="138"/>
-      <c r="P19" s="140"/>
-      <c r="Q19" s="140"/>
-      <c r="R19" s="140"/>
-      <c r="S19" s="140"/>
-      <c r="T19" s="140"/>
-      <c r="U19" s="140"/>
-      <c r="V19" s="139"/>
+      <c r="O19" s="145"/>
+      <c r="P19" s="147"/>
+      <c r="Q19" s="147"/>
+      <c r="R19" s="147"/>
+      <c r="S19" s="147"/>
+      <c r="T19" s="147"/>
+      <c r="U19" s="147"/>
+      <c r="V19" s="146"/>
       <c r="W19" s="45"/>
       <c r="X19" s="76"/>
       <c r="Y19" s="76"/>
@@ -2657,25 +2742,25 @@
       <c r="AE19" s="7"/>
       <c r="AF19" s="42"/>
     </row>
-    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
-      <c r="C20" s="116"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="127">
+      <c r="C20" s="91"/>
+      <c r="D20" s="92"/>
+      <c r="E20" s="93">
         <f ca="1">C19+1</f>
         <v>46300</v>
       </c>
-      <c r="F20" s="128"/>
-      <c r="G20" s="127">
+      <c r="F20" s="94"/>
+      <c r="G20" s="93">
         <f ca="1">E20+1</f>
         <v>46301</v>
       </c>
-      <c r="H20" s="128"/>
-      <c r="I20" s="127">
+      <c r="H20" s="94"/>
+      <c r="I20" s="93">
         <f ca="1">G20+1</f>
         <v>46302</v>
       </c>
-      <c r="J20" s="128"/>
+      <c r="J20" s="94"/>
       <c r="K20" s="46">
         <f ca="1">I20+1</f>
         <v>46303</v>
@@ -2683,65 +2768,65 @@
       <c r="L20" s="51"/>
       <c r="M20" s="51"/>
       <c r="N20" s="69"/>
-      <c r="O20" s="127">
+      <c r="O20" s="93">
         <f ca="1">K20+1</f>
         <v>46304</v>
       </c>
-      <c r="P20" s="129"/>
-      <c r="Q20" s="129"/>
-      <c r="R20" s="129"/>
-      <c r="S20" s="129"/>
-      <c r="T20" s="129"/>
-      <c r="U20" s="129"/>
-      <c r="V20" s="128"/>
-      <c r="W20" s="127">
+      <c r="P20" s="95"/>
+      <c r="Q20" s="95"/>
+      <c r="R20" s="95"/>
+      <c r="S20" s="95"/>
+      <c r="T20" s="95"/>
+      <c r="U20" s="95"/>
+      <c r="V20" s="94"/>
+      <c r="W20" s="93">
         <f ca="1">O20+1</f>
         <v>46305</v>
       </c>
-      <c r="X20" s="129"/>
-      <c r="Y20" s="129"/>
-      <c r="Z20" s="129"/>
-      <c r="AA20" s="129"/>
-      <c r="AB20" s="129"/>
-      <c r="AC20" s="129"/>
-      <c r="AD20" s="128"/>
+      <c r="X20" s="95"/>
+      <c r="Y20" s="95"/>
+      <c r="Z20" s="95"/>
+      <c r="AA20" s="95"/>
+      <c r="AB20" s="95"/>
+      <c r="AC20" s="95"/>
+      <c r="AD20" s="94"/>
       <c r="AF20" s="4"/>
     </row>
-    <row r="21" spans="1:42" s="43" customFormat="1" ht="166.8" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:42" s="43" customFormat="1" ht="166.8" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="42"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="111"/>
-      <c r="H21" s="113"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="113"/>
+      <c r="C21" s="96"/>
+      <c r="D21" s="97"/>
+      <c r="E21" s="96"/>
+      <c r="F21" s="97"/>
+      <c r="G21" s="96"/>
+      <c r="H21" s="97"/>
+      <c r="I21" s="96"/>
+      <c r="J21" s="97"/>
       <c r="K21" s="70"/>
       <c r="L21" s="71"/>
       <c r="M21" s="71"/>
       <c r="N21" s="72"/>
-      <c r="O21" s="111"/>
-      <c r="P21" s="112"/>
-      <c r="Q21" s="112"/>
-      <c r="R21" s="112"/>
-      <c r="S21" s="112"/>
-      <c r="T21" s="112"/>
-      <c r="U21" s="112"/>
-      <c r="V21" s="113"/>
-      <c r="W21" s="111"/>
-      <c r="X21" s="112"/>
-      <c r="Y21" s="112"/>
-      <c r="Z21" s="112"/>
-      <c r="AA21" s="112"/>
-      <c r="AB21" s="112"/>
-      <c r="AC21" s="112"/>
-      <c r="AD21" s="113"/>
+      <c r="O21" s="96"/>
+      <c r="P21" s="141"/>
+      <c r="Q21" s="141"/>
+      <c r="R21" s="141"/>
+      <c r="S21" s="141"/>
+      <c r="T21" s="141"/>
+      <c r="U21" s="141"/>
+      <c r="V21" s="97"/>
+      <c r="W21" s="96"/>
+      <c r="X21" s="141"/>
+      <c r="Y21" s="141"/>
+      <c r="Z21" s="141"/>
+      <c r="AA21" s="141"/>
+      <c r="AB21" s="141"/>
+      <c r="AC21" s="141"/>
+      <c r="AD21" s="97"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
     </row>
-    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52"/>
@@ -2773,7 +2858,7 @@
       <c r="AD22" s="55"/>
       <c r="AF22" s="4"/>
     </row>
-    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="56"/>
@@ -2807,61 +2892,61 @@
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
     </row>
-    <row r="24" spans="1:42" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:42" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="M24" s="1"/>
       <c r="AF24" s="1"/>
     </row>
-    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="C25" s="132" t="s">
+      <c r="C25" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="132"/>
-      <c r="E25" s="132"/>
-      <c r="F25" s="132"/>
-      <c r="G25" s="132"/>
-      <c r="H25" s="132"/>
-      <c r="I25" s="132"/>
-      <c r="J25" s="132"/>
-      <c r="K25" s="132"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="86"/>
+      <c r="H25" s="86"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="86"/>
+      <c r="K25" s="86"/>
       <c r="L25" s="60"/>
       <c r="M25" s="1"/>
-      <c r="O25" s="133">
+      <c r="O25" s="87">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)-1,1)</f>
         <v>46235</v>
       </c>
-      <c r="P25" s="133"/>
-      <c r="Q25" s="133"/>
-      <c r="R25" s="133"/>
-      <c r="S25" s="133"/>
-      <c r="T25" s="133"/>
-      <c r="U25" s="133"/>
+      <c r="P25" s="87"/>
+      <c r="Q25" s="87"/>
+      <c r="R25" s="87"/>
+      <c r="S25" s="87"/>
+      <c r="T25" s="87"/>
+      <c r="U25" s="87"/>
       <c r="V25" s="61"/>
       <c r="W25" s="61"/>
-      <c r="X25" s="133">
+      <c r="X25" s="87">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)+1,1)</f>
         <v>46296</v>
       </c>
-      <c r="Y25" s="133"/>
-      <c r="Z25" s="133"/>
-      <c r="AA25" s="133"/>
-      <c r="AB25" s="133"/>
-      <c r="AC25" s="133"/>
-      <c r="AD25" s="133"/>
+      <c r="Y25" s="87"/>
+      <c r="Z25" s="87"/>
+      <c r="AA25" s="87"/>
+      <c r="AB25" s="87"/>
+      <c r="AC25" s="87"/>
+      <c r="AD25" s="87"/>
       <c r="AF25" s="1"/>
     </row>
-    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="C26" s="132"/>
-      <c r="D26" s="132"/>
-      <c r="E26" s="132"/>
-      <c r="F26" s="132"/>
-      <c r="G26" s="132"/>
-      <c r="H26" s="132"/>
-      <c r="I26" s="132"/>
-      <c r="J26" s="132"/>
-      <c r="K26" s="132"/>
+      <c r="C26" s="86"/>
+      <c r="D26" s="86"/>
+      <c r="E26" s="86"/>
+      <c r="F26" s="86"/>
+      <c r="G26" s="86"/>
+      <c r="H26" s="86"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="K26" s="86"/>
       <c r="L26" s="60"/>
       <c r="M26" s="1"/>
       <c r="O26" s="62" t="str">
@@ -2924,19 +3009,19 @@
       </c>
       <c r="AF26" s="1"/>
     </row>
-    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="C27" s="131" t="s">
-        <v>27</v>
-      </c>
-      <c r="D27" s="131"/>
-      <c r="E27" s="131"/>
-      <c r="F27" s="131"/>
-      <c r="G27" s="131"/>
-      <c r="H27" s="131"/>
-      <c r="I27" s="131"/>
-      <c r="J27" s="131"/>
-      <c r="K27" s="131"/>
+      <c r="C27" s="88" t="s">
+        <v>22</v>
+      </c>
+      <c r="D27" s="88"/>
+      <c r="E27" s="88"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="88"/>
+      <c r="H27" s="88"/>
+      <c r="I27" s="88"/>
+      <c r="J27" s="88"/>
+      <c r="K27" s="88"/>
       <c r="M27" s="1"/>
       <c r="O27" s="64" t="str">
         <f t="shared" ref="O27:U32" ca="1" si="0">IF(MONTH($O$25)&lt;&gt;MONTH($O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1)),"",$O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1))</f>
@@ -2998,19 +3083,19 @@
       </c>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="C28" s="130" t="s">
-        <v>28</v>
-      </c>
-      <c r="D28" s="130"/>
-      <c r="E28" s="130"/>
-      <c r="F28" s="130"/>
-      <c r="G28" s="130"/>
-      <c r="H28" s="130"/>
-      <c r="I28" s="130"/>
-      <c r="J28" s="130"/>
-      <c r="K28" s="130"/>
+      <c r="C28" s="89" t="s">
+        <v>23</v>
+      </c>
+      <c r="D28" s="89"/>
+      <c r="E28" s="89"/>
+      <c r="F28" s="89"/>
+      <c r="G28" s="89"/>
+      <c r="H28" s="89"/>
+      <c r="I28" s="89"/>
+      <c r="J28" s="89"/>
+      <c r="K28" s="89"/>
       <c r="M28" s="1"/>
       <c r="O28" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3072,17 +3157,17 @@
       </c>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="C29" s="131"/>
-      <c r="D29" s="131"/>
-      <c r="E29" s="131"/>
-      <c r="F29" s="131"/>
-      <c r="G29" s="131"/>
-      <c r="H29" s="131"/>
-      <c r="I29" s="131"/>
-      <c r="J29" s="131"/>
-      <c r="K29" s="131"/>
+      <c r="C29" s="88"/>
+      <c r="D29" s="88"/>
+      <c r="E29" s="88"/>
+      <c r="F29" s="88"/>
+      <c r="G29" s="88"/>
+      <c r="H29" s="88"/>
+      <c r="I29" s="88"/>
+      <c r="J29" s="88"/>
+      <c r="K29" s="88"/>
       <c r="M29" s="1"/>
       <c r="O29" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3144,19 +3229,19 @@
       </c>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="C30" s="130" t="s">
-        <v>29</v>
-      </c>
-      <c r="D30" s="130"/>
-      <c r="E30" s="130"/>
-      <c r="F30" s="130"/>
-      <c r="G30" s="130"/>
-      <c r="H30" s="130"/>
-      <c r="I30" s="130"/>
-      <c r="J30" s="130"/>
-      <c r="K30" s="130"/>
+      <c r="C30" s="89" t="s">
+        <v>24</v>
+      </c>
+      <c r="D30" s="89"/>
+      <c r="E30" s="89"/>
+      <c r="F30" s="89"/>
+      <c r="G30" s="89"/>
+      <c r="H30" s="89"/>
+      <c r="I30" s="89"/>
+      <c r="J30" s="89"/>
+      <c r="K30" s="89"/>
       <c r="M30" s="1"/>
       <c r="O30" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3218,17 +3303,17 @@
       </c>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="C31" s="131"/>
-      <c r="D31" s="131"/>
-      <c r="E31" s="131"/>
-      <c r="F31" s="131"/>
-      <c r="G31" s="131"/>
-      <c r="H31" s="131"/>
-      <c r="I31" s="131"/>
-      <c r="J31" s="131"/>
-      <c r="K31" s="131"/>
+      <c r="C31" s="88"/>
+      <c r="D31" s="88"/>
+      <c r="E31" s="88"/>
+      <c r="F31" s="88"/>
+      <c r="G31" s="88"/>
+      <c r="H31" s="88"/>
+      <c r="I31" s="88"/>
+      <c r="J31" s="88"/>
+      <c r="K31" s="88"/>
       <c r="M31" s="1"/>
       <c r="O31" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3290,7 +3375,7 @@
       </c>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="M32" s="1"/>
       <c r="O32" s="64">
@@ -3353,7 +3438,7 @@
       </c>
       <c r="AF32" s="1"/>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="M33" s="1"/>
       <c r="O33" s="64"/>
@@ -3374,7 +3459,7 @@
       <c r="AD33" s="65"/>
       <c r="AF33" s="1"/>
     </row>
-    <row r="34" spans="1:32" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:32" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -3408,69 +3493,158 @@
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
     </row>
-    <row r="38" spans="1:32" ht="12.9" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D39" s="83" t="s">
-        <v>30</v>
-      </c>
-      <c r="E39" s="84"/>
-      <c r="F39" s="85"/>
-      <c r="G39" s="89">
+    <row r="38" spans="1:32" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D39" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="114"/>
+      <c r="F39" s="115"/>
+      <c r="G39" s="119">
         <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
         <v>5</v>
       </c>
-      <c r="H39" s="90"/>
-      <c r="I39" s="83" t="s">
-        <v>33</v>
-      </c>
-      <c r="J39" s="93"/>
-      <c r="K39" s="95" t="s">
-        <v>31</v>
-      </c>
-      <c r="L39" s="96"/>
-      <c r="M39" s="99">
+      <c r="H39" s="120"/>
+      <c r="I39" s="113" t="s">
+        <v>28</v>
+      </c>
+      <c r="J39" s="123"/>
+      <c r="K39" s="125" t="s">
+        <v>26</v>
+      </c>
+      <c r="L39" s="126"/>
+      <c r="M39" s="129">
         <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
         <v>5.9999999999999973</v>
       </c>
-      <c r="N39" s="100"/>
-      <c r="O39" s="100"/>
-      <c r="P39" s="100"/>
-      <c r="Q39" s="100"/>
-      <c r="R39" s="101"/>
-      <c r="S39" s="105" t="s">
-        <v>32</v>
-      </c>
-      <c r="T39" s="106"/>
-      <c r="U39" s="106"/>
-      <c r="V39" s="106"/>
-      <c r="W39" s="106"/>
-      <c r="X39" s="107"/>
-    </row>
-    <row r="40" spans="1:32" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D40" s="86"/>
-      <c r="E40" s="87"/>
-      <c r="F40" s="88"/>
-      <c r="G40" s="91"/>
-      <c r="H40" s="92"/>
-      <c r="I40" s="86"/>
-      <c r="J40" s="94"/>
-      <c r="K40" s="97"/>
-      <c r="L40" s="98"/>
-      <c r="M40" s="102"/>
-      <c r="N40" s="103"/>
-      <c r="O40" s="103"/>
-      <c r="P40" s="103"/>
-      <c r="Q40" s="103"/>
-      <c r="R40" s="104"/>
-      <c r="S40" s="108"/>
-      <c r="T40" s="109"/>
-      <c r="U40" s="109"/>
-      <c r="V40" s="109"/>
-      <c r="W40" s="109"/>
-      <c r="X40" s="110"/>
+      <c r="N39" s="130"/>
+      <c r="O39" s="130"/>
+      <c r="P39" s="130"/>
+      <c r="Q39" s="130"/>
+      <c r="R39" s="131"/>
+      <c r="S39" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="T39" s="136"/>
+      <c r="U39" s="136"/>
+      <c r="V39" s="136"/>
+      <c r="W39" s="136"/>
+      <c r="X39" s="137"/>
+    </row>
+    <row r="40" spans="1:32" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D40" s="116"/>
+      <c r="E40" s="117"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="121"/>
+      <c r="H40" s="122"/>
+      <c r="I40" s="116"/>
+      <c r="J40" s="124"/>
+      <c r="K40" s="127"/>
+      <c r="L40" s="128"/>
+      <c r="M40" s="132"/>
+      <c r="N40" s="133"/>
+      <c r="O40" s="133"/>
+      <c r="P40" s="133"/>
+      <c r="Q40" s="133"/>
+      <c r="R40" s="134"/>
+      <c r="S40" s="138"/>
+      <c r="T40" s="139"/>
+      <c r="U40" s="139"/>
+      <c r="V40" s="139"/>
+      <c r="W40" s="139"/>
+      <c r="X40" s="140"/>
     </row>
   </sheetData>
   <mergeCells count="110">
+    <mergeCell ref="D39:F40"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="K39:L40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="S39:X40"/>
+    <mergeCell ref="M39:R40"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="O20:V20"/>
+    <mergeCell ref="C30:K31"/>
+    <mergeCell ref="C2:AD2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="W5:AD5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:V6"/>
+    <mergeCell ref="W6:AD6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="O5:V5"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="W7:AD7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="O8:V8"/>
+    <mergeCell ref="W8:AD8"/>
+    <mergeCell ref="O7:V7"/>
+    <mergeCell ref="W9:AD9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="O11:V11"/>
+    <mergeCell ref="W11:AD11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:V9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="W12:AD12"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O14:V14"/>
+    <mergeCell ref="W14:AD14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="O12:V12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="W15:AD15"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="O17:V17"/>
+    <mergeCell ref="W17:AD17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="O15:V15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="O16:V16"/>
     <mergeCell ref="W18:AD18"/>
     <mergeCell ref="C25:K26"/>
     <mergeCell ref="O25:U25"/>
@@ -3492,95 +3666,6 @@
     <mergeCell ref="O21:V21"/>
     <mergeCell ref="W21:AD21"/>
     <mergeCell ref="O19:V19"/>
-    <mergeCell ref="W15:AD15"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="O17:V17"/>
-    <mergeCell ref="W17:AD17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="O15:V15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="O16:V16"/>
-    <mergeCell ref="W12:AD12"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="O14:V14"/>
-    <mergeCell ref="W14:AD14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="O12:V12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="W9:AD9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="O11:V11"/>
-    <mergeCell ref="W11:AD11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:V9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="W7:AD7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="O8:V8"/>
-    <mergeCell ref="W8:AD8"/>
-    <mergeCell ref="O7:V7"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:V6"/>
-    <mergeCell ref="W6:AD6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="O5:V5"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="C2:AD2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="W5:AD5"/>
-    <mergeCell ref="D39:F40"/>
-    <mergeCell ref="G39:H40"/>
-    <mergeCell ref="K39:L40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="S39:X40"/>
-    <mergeCell ref="M39:R40"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="O20:V20"/>
-    <mergeCell ref="C30:K31"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 E5 G5 I5 K5:L5 O5 W5 C7 E8 G8 I8 K8:L8 O8 W8 C10 E11 G11 I11 K11:L11 O11 W11 C13 E14 G14 I14 K14:L14 O14 W14 C16 E17 G17 I17 K17:L17 O17 W17">
     <cfRule type="expression" dxfId="11" priority="3">
@@ -3619,7 +3704,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AP40"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="12.6" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="5.5546875" style="3" customWidth="1"/>
     <col min="4" max="4" width="15.5546875" style="3" customWidth="1"/>
@@ -3637,7 +3722,7 @@
     <col min="35" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3671,42 +3756,42 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="2.15">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A2" s="29"/>
-      <c r="C2" s="114">
+      <c r="C2" s="111">
         <f ca="1">DATE(About!P8,10,1)</f>
         <v>46296</v>
       </c>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
-      <c r="I2" s="114"/>
-      <c r="J2" s="114"/>
-      <c r="K2" s="114"/>
-      <c r="L2" s="114"/>
-      <c r="M2" s="114"/>
-      <c r="N2" s="114"/>
-      <c r="O2" s="114"/>
-      <c r="P2" s="114"/>
-      <c r="Q2" s="114"/>
-      <c r="R2" s="114"/>
-      <c r="S2" s="114"/>
-      <c r="T2" s="114"/>
-      <c r="U2" s="114"/>
-      <c r="V2" s="114"/>
-      <c r="W2" s="114"/>
-      <c r="X2" s="114"/>
-      <c r="Y2" s="114"/>
-      <c r="Z2" s="114"/>
-      <c r="AA2" s="114"/>
-      <c r="AB2" s="114"/>
-      <c r="AC2" s="114"/>
-      <c r="AD2" s="114"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="111"/>
+      <c r="G2" s="111"/>
+      <c r="H2" s="111"/>
+      <c r="I2" s="111"/>
+      <c r="J2" s="111"/>
+      <c r="K2" s="111"/>
+      <c r="L2" s="111"/>
+      <c r="M2" s="111"/>
+      <c r="N2" s="111"/>
+      <c r="O2" s="111"/>
+      <c r="P2" s="111"/>
+      <c r="Q2" s="111"/>
+      <c r="R2" s="111"/>
+      <c r="S2" s="111"/>
+      <c r="T2" s="111"/>
+      <c r="U2" s="111"/>
+      <c r="V2" s="111"/>
+      <c r="W2" s="111"/>
+      <c r="X2" s="111"/>
+      <c r="Y2" s="111"/>
+      <c r="Z2" s="111"/>
+      <c r="AA2" s="111"/>
+      <c r="AB2" s="111"/>
+      <c r="AC2" s="111"/>
+      <c r="AD2" s="111"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="2.15">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -3726,290 +3811,290 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="35"/>
-      <c r="C4" s="115">
+      <c r="C4" s="112">
         <f ca="1">C5</f>
         <v>46292</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115">
+      <c r="D4" s="112"/>
+      <c r="E4" s="112">
         <f ca="1">E5</f>
         <v>46293</v>
       </c>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115">
+      <c r="F4" s="112"/>
+      <c r="G4" s="112">
         <f ca="1">G5</f>
         <v>46294</v>
       </c>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115">
+      <c r="H4" s="112"/>
+      <c r="I4" s="112">
         <f ca="1">I5</f>
         <v>46295</v>
       </c>
-      <c r="J4" s="115"/>
-      <c r="K4" s="115">
+      <c r="J4" s="112"/>
+      <c r="K4" s="112">
         <f ca="1">K5</f>
         <v>46296</v>
       </c>
-      <c r="L4" s="115"/>
-      <c r="M4" s="115"/>
+      <c r="L4" s="112"/>
+      <c r="M4" s="112"/>
       <c r="N4" s="37"/>
-      <c r="O4" s="115">
+      <c r="O4" s="112">
         <f ca="1">O5</f>
         <v>46297</v>
       </c>
-      <c r="P4" s="115"/>
-      <c r="Q4" s="115"/>
-      <c r="R4" s="115"/>
-      <c r="S4" s="115"/>
-      <c r="T4" s="115"/>
-      <c r="U4" s="115"/>
-      <c r="V4" s="115"/>
-      <c r="W4" s="115">
+      <c r="P4" s="112"/>
+      <c r="Q4" s="112"/>
+      <c r="R4" s="112"/>
+      <c r="S4" s="112"/>
+      <c r="T4" s="112"/>
+      <c r="U4" s="112"/>
+      <c r="V4" s="112"/>
+      <c r="W4" s="112">
         <f ca="1">W5</f>
         <v>46298</v>
       </c>
-      <c r="X4" s="115"/>
-      <c r="Y4" s="115"/>
-      <c r="Z4" s="115"/>
-      <c r="AA4" s="115"/>
-      <c r="AB4" s="115"/>
-      <c r="AC4" s="115"/>
-      <c r="AD4" s="115"/>
+      <c r="X4" s="112"/>
+      <c r="Y4" s="112"/>
+      <c r="Z4" s="112"/>
+      <c r="AA4" s="112"/>
+      <c r="AB4" s="112"/>
+      <c r="AC4" s="112"/>
+      <c r="AD4" s="112"/>
       <c r="AF4" s="38"/>
       <c r="AG4" s="39"/>
       <c r="AH4" s="39"/>
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="C5" s="116">
+      <c r="C5" s="91">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46292</v>
       </c>
-      <c r="D5" s="118"/>
-      <c r="E5" s="116">
+      <c r="D5" s="92"/>
+      <c r="E5" s="91">
         <f ca="1">C5+1</f>
         <v>46293</v>
       </c>
-      <c r="F5" s="118"/>
-      <c r="G5" s="116">
+      <c r="F5" s="92"/>
+      <c r="G5" s="91">
         <f ca="1">E5+1</f>
         <v>46294</v>
       </c>
-      <c r="H5" s="118"/>
-      <c r="I5" s="116">
+      <c r="H5" s="92"/>
+      <c r="I5" s="91">
         <f ca="1">G5+1</f>
         <v>46295</v>
       </c>
-      <c r="J5" s="118"/>
-      <c r="K5" s="116">
+      <c r="J5" s="92"/>
+      <c r="K5" s="91">
         <f ca="1">I5+1</f>
         <v>46296</v>
       </c>
-      <c r="L5" s="117"/>
-      <c r="M5" s="117"/>
+      <c r="L5" s="110"/>
+      <c r="M5" s="110"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="116">
+      <c r="O5" s="91">
         <f ca="1">K5+1</f>
         <v>46297</v>
       </c>
-      <c r="P5" s="117"/>
-      <c r="Q5" s="117"/>
-      <c r="R5" s="117"/>
-      <c r="S5" s="117"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="117"/>
-      <c r="V5" s="118"/>
-      <c r="W5" s="116">
+      <c r="P5" s="110"/>
+      <c r="Q5" s="110"/>
+      <c r="R5" s="110"/>
+      <c r="S5" s="110"/>
+      <c r="T5" s="110"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="92"/>
+      <c r="W5" s="91">
         <f ca="1">O5+1</f>
         <v>46298</v>
       </c>
-      <c r="X5" s="117"/>
-      <c r="Y5" s="117"/>
-      <c r="Z5" s="117"/>
-      <c r="AA5" s="117"/>
-      <c r="AB5" s="117"/>
-      <c r="AC5" s="117"/>
-      <c r="AD5" s="118"/>
+      <c r="X5" s="110"/>
+      <c r="Y5" s="110"/>
+      <c r="Z5" s="110"/>
+      <c r="AA5" s="110"/>
+      <c r="AB5" s="110"/>
+      <c r="AC5" s="110"/>
+      <c r="AD5" s="92"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
       <c r="AI5" s="41"/>
       <c r="AJ5" s="41"/>
     </row>
-    <row r="6" spans="1:36" s="43" customFormat="1" ht="131.69999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:36" s="43" customFormat="1" ht="131.69999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="42"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="120"/>
-      <c r="E6" s="119"/>
-      <c r="F6" s="120"/>
-      <c r="G6" s="119"/>
-      <c r="H6" s="120"/>
-      <c r="I6" s="119"/>
-      <c r="J6" s="120"/>
-      <c r="K6" s="150"/>
-      <c r="L6" s="152"/>
-      <c r="M6" s="152"/>
-      <c r="N6" s="151"/>
-      <c r="O6" s="150"/>
-      <c r="P6" s="152"/>
-      <c r="Q6" s="152"/>
-      <c r="R6" s="152"/>
-      <c r="S6" s="152"/>
-      <c r="T6" s="152"/>
-      <c r="U6" s="152"/>
-      <c r="V6" s="151"/>
-      <c r="W6" s="155" t="s">
-        <v>24</v>
-      </c>
-      <c r="X6" s="156"/>
-      <c r="Y6" s="156"/>
-      <c r="Z6" s="156"/>
-      <c r="AA6" s="156"/>
-      <c r="AB6" s="156"/>
-      <c r="AC6" s="156"/>
-      <c r="AD6" s="157"/>
+      <c r="C6" s="102"/>
+      <c r="D6" s="103"/>
+      <c r="E6" s="102"/>
+      <c r="F6" s="103"/>
+      <c r="G6" s="102"/>
+      <c r="H6" s="103"/>
+      <c r="I6" s="102"/>
+      <c r="J6" s="103"/>
+      <c r="K6" s="104"/>
+      <c r="L6" s="105"/>
+      <c r="M6" s="105"/>
+      <c r="N6" s="106"/>
+      <c r="O6" s="104"/>
+      <c r="P6" s="105"/>
+      <c r="Q6" s="105"/>
+      <c r="R6" s="105"/>
+      <c r="S6" s="105"/>
+      <c r="T6" s="105"/>
+      <c r="U6" s="105"/>
+      <c r="V6" s="106"/>
+      <c r="W6" s="107" t="s">
+        <v>20</v>
+      </c>
+      <c r="X6" s="108"/>
+      <c r="Y6" s="108"/>
+      <c r="Z6" s="108"/>
+      <c r="AA6" s="108"/>
+      <c r="AB6" s="108"/>
+      <c r="AC6" s="108"/>
+      <c r="AD6" s="109"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
-    <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
-      <c r="C7" s="116">
+      <c r="C7" s="91">
         <f ca="1">W5+1</f>
         <v>46299</v>
       </c>
-      <c r="D7" s="118"/>
-      <c r="E7" s="124"/>
-      <c r="F7" s="125"/>
-      <c r="G7" s="124"/>
-      <c r="H7" s="125"/>
-      <c r="I7" s="124"/>
-      <c r="J7" s="125"/>
-      <c r="K7" s="124"/>
-      <c r="L7" s="126"/>
-      <c r="M7" s="126"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="99"/>
+      <c r="F7" s="100"/>
+      <c r="G7" s="99"/>
+      <c r="H7" s="100"/>
+      <c r="I7" s="99"/>
+      <c r="J7" s="100"/>
+      <c r="K7" s="99"/>
+      <c r="L7" s="101"/>
+      <c r="M7" s="101"/>
       <c r="N7" s="75"/>
-      <c r="O7" s="124"/>
-      <c r="P7" s="126"/>
-      <c r="Q7" s="126"/>
-      <c r="R7" s="126"/>
-      <c r="S7" s="126"/>
-      <c r="T7" s="126"/>
-      <c r="U7" s="126"/>
-      <c r="V7" s="125"/>
-      <c r="W7" s="124"/>
-      <c r="X7" s="126"/>
-      <c r="Y7" s="126"/>
-      <c r="Z7" s="126"/>
-      <c r="AA7" s="126"/>
-      <c r="AB7" s="126"/>
-      <c r="AC7" s="126"/>
-      <c r="AD7" s="125"/>
+      <c r="O7" s="99"/>
+      <c r="P7" s="101"/>
+      <c r="Q7" s="101"/>
+      <c r="R7" s="101"/>
+      <c r="S7" s="101"/>
+      <c r="T7" s="101"/>
+      <c r="U7" s="101"/>
+      <c r="V7" s="100"/>
+      <c r="W7" s="99"/>
+      <c r="X7" s="101"/>
+      <c r="Y7" s="101"/>
+      <c r="Z7" s="101"/>
+      <c r="AA7" s="101"/>
+      <c r="AB7" s="101"/>
+      <c r="AC7" s="101"/>
+      <c r="AD7" s="100"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
-      <c r="C8" s="116"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="127">
+      <c r="C8" s="91"/>
+      <c r="D8" s="92"/>
+      <c r="E8" s="93">
         <f ca="1">C7+1</f>
         <v>46300</v>
       </c>
-      <c r="F8" s="128"/>
-      <c r="G8" s="127">
+      <c r="F8" s="94"/>
+      <c r="G8" s="93">
         <f ca="1">E8+1</f>
         <v>46301</v>
       </c>
-      <c r="H8" s="128"/>
-      <c r="I8" s="127">
+      <c r="H8" s="94"/>
+      <c r="I8" s="93">
         <f ca="1">G8+1</f>
         <v>46302</v>
       </c>
-      <c r="J8" s="128"/>
-      <c r="K8" s="127">
+      <c r="J8" s="94"/>
+      <c r="K8" s="93">
         <f ca="1">I8+1</f>
         <v>46303</v>
       </c>
-      <c r="L8" s="129"/>
-      <c r="M8" s="129"/>
+      <c r="L8" s="95"/>
+      <c r="M8" s="95"/>
       <c r="N8" s="50"/>
-      <c r="O8" s="127">
+      <c r="O8" s="93">
         <f ca="1">K8+1</f>
         <v>46304</v>
       </c>
-      <c r="P8" s="129"/>
-      <c r="Q8" s="129"/>
-      <c r="R8" s="129"/>
-      <c r="S8" s="129"/>
-      <c r="T8" s="129"/>
-      <c r="U8" s="129"/>
-      <c r="V8" s="128"/>
-      <c r="W8" s="127">
+      <c r="P8" s="95"/>
+      <c r="Q8" s="95"/>
+      <c r="R8" s="95"/>
+      <c r="S8" s="95"/>
+      <c r="T8" s="95"/>
+      <c r="U8" s="95"/>
+      <c r="V8" s="94"/>
+      <c r="W8" s="93">
         <f ca="1">O8+1</f>
         <v>46305</v>
       </c>
-      <c r="X8" s="129"/>
-      <c r="Y8" s="129"/>
-      <c r="Z8" s="129"/>
-      <c r="AA8" s="129"/>
-      <c r="AB8" s="129"/>
-      <c r="AC8" s="129"/>
-      <c r="AD8" s="128"/>
+      <c r="X8" s="95"/>
+      <c r="Y8" s="95"/>
+      <c r="Z8" s="95"/>
+      <c r="AA8" s="95"/>
+      <c r="AB8" s="95"/>
+      <c r="AC8" s="95"/>
+      <c r="AD8" s="94"/>
       <c r="AF8" s="4"/>
     </row>
-    <row r="9" spans="1:36" s="43" customFormat="1" ht="149.69999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:36" s="43" customFormat="1" ht="149.69999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="42"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="123"/>
-      <c r="E9" s="121" t="s">
-        <v>35</v>
-      </c>
-      <c r="F9" s="123"/>
-      <c r="G9" s="121" t="s">
+      <c r="C9" s="83"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="83" t="s">
+        <v>30</v>
+      </c>
+      <c r="F9" s="85"/>
+      <c r="G9" s="83" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="85"/>
+      <c r="I9" s="83"/>
+      <c r="J9" s="85"/>
+      <c r="K9" s="83" t="s">
+        <v>31</v>
+      </c>
+      <c r="L9" s="84"/>
+      <c r="M9" s="84"/>
+      <c r="N9" s="85"/>
+      <c r="O9" s="83" t="s">
         <v>34</v>
       </c>
-      <c r="H9" s="123"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="123"/>
-      <c r="K9" s="121" t="s">
-        <v>36</v>
-      </c>
-      <c r="L9" s="122"/>
-      <c r="M9" s="122"/>
-      <c r="N9" s="123"/>
-      <c r="O9" s="121" t="s">
-        <v>25</v>
-      </c>
-      <c r="P9" s="122"/>
-      <c r="Q9" s="122"/>
-      <c r="R9" s="122"/>
-      <c r="S9" s="122"/>
-      <c r="T9" s="122"/>
-      <c r="U9" s="122"/>
-      <c r="V9" s="123"/>
-      <c r="W9" s="121" t="s">
-        <v>18</v>
-      </c>
-      <c r="X9" s="122"/>
-      <c r="Y9" s="122"/>
-      <c r="Z9" s="122"/>
-      <c r="AA9" s="122"/>
-      <c r="AB9" s="122"/>
-      <c r="AC9" s="122"/>
-      <c r="AD9" s="123"/>
+      <c r="P9" s="84"/>
+      <c r="Q9" s="84"/>
+      <c r="R9" s="84"/>
+      <c r="S9" s="84"/>
+      <c r="T9" s="84"/>
+      <c r="U9" s="84"/>
+      <c r="V9" s="85"/>
+      <c r="W9" s="83" t="s">
+        <v>32</v>
+      </c>
+      <c r="X9" s="84"/>
+      <c r="Y9" s="84"/>
+      <c r="Z9" s="84"/>
+      <c r="AA9" s="84"/>
+      <c r="AB9" s="84"/>
+      <c r="AC9" s="84"/>
+      <c r="AD9" s="85"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
-    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="42"/>
-      <c r="C10" s="116">
+      <c r="C10" s="91">
         <f ca="1">W8+1</f>
         <v>46306</v>
       </c>
-      <c r="D10" s="118"/>
+      <c r="D10" s="92"/>
       <c r="E10" s="45"/>
       <c r="F10" s="75"/>
       <c r="G10" s="45"/>
@@ -4039,99 +4124,101 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="42"/>
     </row>
-    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
-      <c r="C11" s="116"/>
-      <c r="D11" s="118"/>
-      <c r="E11" s="127">
+      <c r="C11" s="91"/>
+      <c r="D11" s="92"/>
+      <c r="E11" s="93">
         <f ca="1">C10+1</f>
         <v>46307</v>
       </c>
-      <c r="F11" s="128"/>
-      <c r="G11" s="127">
+      <c r="F11" s="94"/>
+      <c r="G11" s="93">
         <f ca="1">E11+1</f>
         <v>46308</v>
       </c>
-      <c r="H11" s="128"/>
-      <c r="I11" s="127">
+      <c r="H11" s="94"/>
+      <c r="I11" s="93">
         <f ca="1">G11+1</f>
         <v>46309</v>
       </c>
-      <c r="J11" s="128"/>
-      <c r="K11" s="127">
+      <c r="J11" s="94"/>
+      <c r="K11" s="93">
         <f ca="1">I11+1</f>
         <v>46310</v>
       </c>
-      <c r="L11" s="129"/>
-      <c r="M11" s="129"/>
+      <c r="L11" s="95"/>
+      <c r="M11" s="95"/>
       <c r="N11" s="50"/>
-      <c r="O11" s="127">
+      <c r="O11" s="93">
         <f ca="1">K11+1</f>
         <v>46311</v>
       </c>
-      <c r="P11" s="129"/>
-      <c r="Q11" s="129"/>
-      <c r="R11" s="129"/>
-      <c r="S11" s="129"/>
-      <c r="T11" s="129"/>
-      <c r="U11" s="129"/>
-      <c r="V11" s="128"/>
-      <c r="W11" s="127">
+      <c r="P11" s="95"/>
+      <c r="Q11" s="95"/>
+      <c r="R11" s="95"/>
+      <c r="S11" s="95"/>
+      <c r="T11" s="95"/>
+      <c r="U11" s="95"/>
+      <c r="V11" s="94"/>
+      <c r="W11" s="93">
         <f ca="1">O11+1</f>
         <v>46312</v>
       </c>
-      <c r="X11" s="129"/>
-      <c r="Y11" s="129"/>
-      <c r="Z11" s="129"/>
-      <c r="AA11" s="129"/>
-      <c r="AB11" s="129"/>
-      <c r="AC11" s="129"/>
-      <c r="AD11" s="128"/>
+      <c r="X11" s="95"/>
+      <c r="Y11" s="95"/>
+      <c r="Z11" s="95"/>
+      <c r="AA11" s="95"/>
+      <c r="AB11" s="95"/>
+      <c r="AC11" s="95"/>
+      <c r="AD11" s="94"/>
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:36" s="43" customFormat="1" ht="134.69999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:36" s="43" customFormat="1" ht="134.69999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="42"/>
-      <c r="C12" s="121"/>
-      <c r="D12" s="123"/>
-      <c r="E12" s="121"/>
-      <c r="F12" s="123"/>
-      <c r="G12" s="121"/>
-      <c r="H12" s="123"/>
-      <c r="I12" s="121"/>
-      <c r="J12" s="123"/>
-      <c r="K12" s="121"/>
-      <c r="L12" s="122"/>
-      <c r="M12" s="122"/>
-      <c r="N12" s="123"/>
-      <c r="O12" s="121" t="s">
-        <v>26</v>
-      </c>
-      <c r="P12" s="122"/>
-      <c r="Q12" s="122"/>
-      <c r="R12" s="122"/>
-      <c r="S12" s="122"/>
-      <c r="T12" s="122"/>
-      <c r="U12" s="122"/>
-      <c r="V12" s="123"/>
-      <c r="W12" s="121"/>
-      <c r="X12" s="122"/>
-      <c r="Y12" s="122"/>
-      <c r="Z12" s="122"/>
-      <c r="AA12" s="122"/>
-      <c r="AB12" s="122"/>
-      <c r="AC12" s="122"/>
-      <c r="AD12" s="123"/>
+      <c r="C12" s="83"/>
+      <c r="D12" s="85"/>
+      <c r="E12" s="83"/>
+      <c r="F12" s="85"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="85"/>
+      <c r="I12" s="83"/>
+      <c r="J12" s="85"/>
+      <c r="K12" s="83"/>
+      <c r="L12" s="84"/>
+      <c r="M12" s="84"/>
+      <c r="N12" s="85"/>
+      <c r="O12" s="83" t="s">
+        <v>21</v>
+      </c>
+      <c r="P12" s="84"/>
+      <c r="Q12" s="84"/>
+      <c r="R12" s="84"/>
+      <c r="S12" s="84"/>
+      <c r="T12" s="84"/>
+      <c r="U12" s="84"/>
+      <c r="V12" s="85"/>
+      <c r="W12" s="98" t="s">
+        <v>33</v>
+      </c>
+      <c r="X12" s="84"/>
+      <c r="Y12" s="84"/>
+      <c r="Z12" s="84"/>
+      <c r="AA12" s="84"/>
+      <c r="AB12" s="84"/>
+      <c r="AC12" s="84"/>
+      <c r="AD12" s="85"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
-    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="42"/>
-      <c r="C13" s="116">
+      <c r="C13" s="91">
         <f ca="1">W11+1</f>
         <v>46313</v>
       </c>
-      <c r="D13" s="118"/>
+      <c r="D13" s="92"/>
       <c r="E13" s="45"/>
       <c r="F13" s="75"/>
       <c r="G13" s="45"/>
@@ -4161,98 +4248,104 @@
       <c r="AE13" s="7"/>
       <c r="AF13" s="42"/>
     </row>
-    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
-      <c r="C14" s="116"/>
-      <c r="D14" s="118"/>
-      <c r="E14" s="127">
+      <c r="C14" s="91"/>
+      <c r="D14" s="92"/>
+      <c r="E14" s="93">
         <f ca="1">C13+1</f>
         <v>46314</v>
       </c>
-      <c r="F14" s="128"/>
-      <c r="G14" s="127">
+      <c r="F14" s="94"/>
+      <c r="G14" s="93">
         <f ca="1">E14+1</f>
         <v>46315</v>
       </c>
-      <c r="H14" s="128"/>
-      <c r="I14" s="127">
+      <c r="H14" s="94"/>
+      <c r="I14" s="93">
         <f ca="1">G14+1</f>
         <v>46316</v>
       </c>
-      <c r="J14" s="128"/>
-      <c r="K14" s="127">
+      <c r="J14" s="94"/>
+      <c r="K14" s="93">
         <f ca="1">I14+1</f>
         <v>46317</v>
       </c>
-      <c r="L14" s="129"/>
-      <c r="M14" s="129"/>
+      <c r="L14" s="95"/>
+      <c r="M14" s="95"/>
       <c r="N14" s="50"/>
-      <c r="O14" s="127">
+      <c r="O14" s="93">
         <f ca="1">K14+1</f>
         <v>46318</v>
       </c>
-      <c r="P14" s="129"/>
-      <c r="Q14" s="129"/>
-      <c r="R14" s="129"/>
-      <c r="S14" s="129"/>
-      <c r="T14" s="129"/>
-      <c r="U14" s="129"/>
-      <c r="V14" s="128"/>
-      <c r="W14" s="127">
+      <c r="P14" s="95"/>
+      <c r="Q14" s="95"/>
+      <c r="R14" s="95"/>
+      <c r="S14" s="95"/>
+      <c r="T14" s="95"/>
+      <c r="U14" s="95"/>
+      <c r="V14" s="94"/>
+      <c r="W14" s="93">
         <f ca="1">O14+1</f>
         <v>46319</v>
       </c>
-      <c r="X14" s="129"/>
-      <c r="Y14" s="129"/>
-      <c r="Z14" s="129"/>
-      <c r="AA14" s="129"/>
-      <c r="AB14" s="129"/>
-      <c r="AC14" s="129"/>
-      <c r="AD14" s="128"/>
+      <c r="X14" s="95"/>
+      <c r="Y14" s="95"/>
+      <c r="Z14" s="95"/>
+      <c r="AA14" s="95"/>
+      <c r="AB14" s="95"/>
+      <c r="AC14" s="95"/>
+      <c r="AD14" s="94"/>
       <c r="AF14" s="4"/>
     </row>
-    <row r="15" spans="1:36" s="43" customFormat="1" ht="140.69999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:36" s="43" customFormat="1" ht="140.69999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="42"/>
-      <c r="C15" s="121"/>
-      <c r="D15" s="123"/>
-      <c r="E15" s="121"/>
-      <c r="F15" s="123"/>
-      <c r="G15" s="121"/>
-      <c r="H15" s="123"/>
-      <c r="I15" s="121"/>
-      <c r="J15" s="123"/>
-      <c r="K15" s="121"/>
-      <c r="L15" s="122"/>
-      <c r="M15" s="122"/>
-      <c r="N15" s="123"/>
-      <c r="O15" s="121" t="s">
-        <v>19</v>
-      </c>
-      <c r="P15" s="122"/>
-      <c r="Q15" s="122"/>
-      <c r="R15" s="122"/>
-      <c r="S15" s="122"/>
-      <c r="T15" s="122"/>
-      <c r="U15" s="122"/>
-      <c r="V15" s="123"/>
-      <c r="W15" s="121"/>
-      <c r="X15" s="122"/>
-      <c r="Y15" s="122"/>
-      <c r="Z15" s="122"/>
-      <c r="AA15" s="122"/>
-      <c r="AB15" s="122"/>
-      <c r="AC15" s="122"/>
-      <c r="AD15" s="123"/>
+      <c r="C15" s="98" t="s">
+        <v>35</v>
+      </c>
+      <c r="D15" s="85"/>
+      <c r="E15" s="83"/>
+      <c r="F15" s="85"/>
+      <c r="G15" s="83"/>
+      <c r="H15" s="85"/>
+      <c r="I15" s="98" t="s">
+        <v>39</v>
+      </c>
+      <c r="J15" s="85"/>
+      <c r="K15" s="83"/>
+      <c r="L15" s="84"/>
+      <c r="M15" s="84"/>
+      <c r="N15" s="85"/>
+      <c r="O15" s="83" t="s">
+        <v>37</v>
+      </c>
+      <c r="P15" s="84"/>
+      <c r="Q15" s="84"/>
+      <c r="R15" s="84"/>
+      <c r="S15" s="84"/>
+      <c r="T15" s="84"/>
+      <c r="U15" s="84"/>
+      <c r="V15" s="85"/>
+      <c r="W15" s="98" t="s">
+        <v>38</v>
+      </c>
+      <c r="X15" s="84"/>
+      <c r="Y15" s="84"/>
+      <c r="Z15" s="84"/>
+      <c r="AA15" s="84"/>
+      <c r="AB15" s="84"/>
+      <c r="AC15" s="84"/>
+      <c r="AD15" s="85"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
-    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="42"/>
-      <c r="C16" s="116">
+      <c r="C16" s="91">
         <f ca="1">W14+1</f>
         <v>46320</v>
       </c>
-      <c r="D16" s="118"/>
+      <c r="D16" s="92"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
@@ -4282,99 +4375,101 @@
       <c r="AE16" s="7"/>
       <c r="AF16" s="42"/>
     </row>
-    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
-      <c r="C17" s="116"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="127">
+      <c r="C17" s="91"/>
+      <c r="D17" s="92"/>
+      <c r="E17" s="93">
         <f ca="1">C16+1</f>
         <v>46321</v>
       </c>
-      <c r="F17" s="128"/>
-      <c r="G17" s="127">
+      <c r="F17" s="94"/>
+      <c r="G17" s="93">
         <f ca="1">E17+1</f>
         <v>46322</v>
       </c>
-      <c r="H17" s="128"/>
-      <c r="I17" s="127">
+      <c r="H17" s="94"/>
+      <c r="I17" s="93">
         <f ca="1">G17+1</f>
         <v>46323</v>
       </c>
-      <c r="J17" s="128"/>
-      <c r="K17" s="127">
+      <c r="J17" s="94"/>
+      <c r="K17" s="93">
         <f ca="1">I17+1</f>
         <v>46324</v>
       </c>
-      <c r="L17" s="129"/>
-      <c r="M17" s="129"/>
+      <c r="L17" s="95"/>
+      <c r="M17" s="95"/>
       <c r="N17" s="50"/>
-      <c r="O17" s="127">
+      <c r="O17" s="93">
         <f ca="1">K17+1</f>
         <v>46325</v>
       </c>
-      <c r="P17" s="129"/>
-      <c r="Q17" s="129"/>
-      <c r="R17" s="129"/>
-      <c r="S17" s="129"/>
-      <c r="T17" s="129"/>
-      <c r="U17" s="129"/>
-      <c r="V17" s="128"/>
-      <c r="W17" s="127">
+      <c r="P17" s="95"/>
+      <c r="Q17" s="95"/>
+      <c r="R17" s="95"/>
+      <c r="S17" s="95"/>
+      <c r="T17" s="95"/>
+      <c r="U17" s="95"/>
+      <c r="V17" s="94"/>
+      <c r="W17" s="93">
         <f ca="1">O17+1</f>
         <v>46326</v>
       </c>
-      <c r="X17" s="129"/>
-      <c r="Y17" s="129"/>
-      <c r="Z17" s="129"/>
-      <c r="AA17" s="129"/>
-      <c r="AB17" s="129"/>
-      <c r="AC17" s="129"/>
-      <c r="AD17" s="128"/>
+      <c r="X17" s="95"/>
+      <c r="Y17" s="95"/>
+      <c r="Z17" s="95"/>
+      <c r="AA17" s="95"/>
+      <c r="AB17" s="95"/>
+      <c r="AC17" s="95"/>
+      <c r="AD17" s="94"/>
       <c r="AF17" s="4"/>
     </row>
-    <row r="18" spans="1:42" s="43" customFormat="1" ht="149.69999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:42" s="43" customFormat="1" ht="149.69999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="42"/>
-      <c r="C18" s="121"/>
-      <c r="D18" s="123"/>
-      <c r="E18" s="121" t="s">
-        <v>20</v>
-      </c>
-      <c r="F18" s="123"/>
-      <c r="G18" s="121"/>
-      <c r="H18" s="123"/>
-      <c r="I18" s="121"/>
-      <c r="J18" s="123"/>
-      <c r="K18" s="121"/>
-      <c r="L18" s="122"/>
-      <c r="M18" s="122"/>
+      <c r="C18" s="83"/>
+      <c r="D18" s="85"/>
+      <c r="E18" s="83" t="s">
+        <v>36</v>
+      </c>
+      <c r="F18" s="85"/>
+      <c r="G18" s="83"/>
+      <c r="H18" s="85"/>
+      <c r="I18" s="83"/>
+      <c r="J18" s="85"/>
+      <c r="K18" s="90" t="s">
+        <v>40</v>
+      </c>
+      <c r="L18" s="84"/>
+      <c r="M18" s="84"/>
       <c r="N18" s="82"/>
-      <c r="O18" s="121"/>
-      <c r="P18" s="122"/>
-      <c r="Q18" s="122"/>
-      <c r="R18" s="122"/>
-      <c r="S18" s="122"/>
-      <c r="T18" s="122"/>
-      <c r="U18" s="122"/>
-      <c r="V18" s="123"/>
-      <c r="W18" s="121"/>
-      <c r="X18" s="122"/>
-      <c r="Y18" s="122"/>
-      <c r="Z18" s="122"/>
-      <c r="AA18" s="122"/>
-      <c r="AB18" s="122"/>
-      <c r="AC18" s="122"/>
-      <c r="AD18" s="123"/>
+      <c r="O18" s="83"/>
+      <c r="P18" s="84"/>
+      <c r="Q18" s="84"/>
+      <c r="R18" s="84"/>
+      <c r="S18" s="84"/>
+      <c r="T18" s="84"/>
+      <c r="U18" s="84"/>
+      <c r="V18" s="85"/>
+      <c r="W18" s="83"/>
+      <c r="X18" s="84"/>
+      <c r="Y18" s="84"/>
+      <c r="Z18" s="84"/>
+      <c r="AA18" s="84"/>
+      <c r="AB18" s="84"/>
+      <c r="AC18" s="84"/>
+      <c r="AD18" s="85"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
-    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="42"/>
-      <c r="C19" s="116">
+      <c r="C19" s="91">
         <f ca="1">W17+1</f>
         <v>46327</v>
       </c>
-      <c r="D19" s="118"/>
+      <c r="D19" s="92"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
@@ -4404,91 +4499,91 @@
       <c r="AE19" s="7"/>
       <c r="AF19" s="42"/>
     </row>
-    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
-      <c r="C20" s="116"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="127">
+      <c r="C20" s="91"/>
+      <c r="D20" s="92"/>
+      <c r="E20" s="93">
         <f ca="1">C19+1</f>
         <v>46328</v>
       </c>
-      <c r="F20" s="128"/>
-      <c r="G20" s="127">
+      <c r="F20" s="94"/>
+      <c r="G20" s="93">
         <f ca="1">E20+1</f>
         <v>46329</v>
       </c>
-      <c r="H20" s="128"/>
-      <c r="I20" s="127">
+      <c r="H20" s="94"/>
+      <c r="I20" s="93">
         <f ca="1">G20+1</f>
         <v>46330</v>
       </c>
-      <c r="J20" s="128"/>
-      <c r="K20" s="127">
+      <c r="J20" s="94"/>
+      <c r="K20" s="93">
         <f ca="1">I20+1</f>
         <v>46331</v>
       </c>
-      <c r="L20" s="129"/>
-      <c r="M20" s="129"/>
+      <c r="L20" s="95"/>
+      <c r="M20" s="95"/>
       <c r="N20" s="50"/>
-      <c r="O20" s="127">
+      <c r="O20" s="93">
         <f ca="1">K20+1</f>
         <v>46332</v>
       </c>
-      <c r="P20" s="129"/>
-      <c r="Q20" s="129"/>
-      <c r="R20" s="129"/>
-      <c r="S20" s="129"/>
-      <c r="T20" s="129"/>
-      <c r="U20" s="129"/>
-      <c r="V20" s="128"/>
-      <c r="W20" s="127">
+      <c r="P20" s="95"/>
+      <c r="Q20" s="95"/>
+      <c r="R20" s="95"/>
+      <c r="S20" s="95"/>
+      <c r="T20" s="95"/>
+      <c r="U20" s="95"/>
+      <c r="V20" s="94"/>
+      <c r="W20" s="93">
         <f ca="1">O20+1</f>
         <v>46333</v>
       </c>
-      <c r="X20" s="129"/>
-      <c r="Y20" s="129"/>
-      <c r="Z20" s="129"/>
-      <c r="AA20" s="129"/>
-      <c r="AB20" s="129"/>
-      <c r="AC20" s="129"/>
-      <c r="AD20" s="128"/>
+      <c r="X20" s="95"/>
+      <c r="Y20" s="95"/>
+      <c r="Z20" s="95"/>
+      <c r="AA20" s="95"/>
+      <c r="AB20" s="95"/>
+      <c r="AC20" s="95"/>
+      <c r="AD20" s="94"/>
       <c r="AF20" s="4"/>
     </row>
-    <row r="21" spans="1:42" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:42" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="42"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="111"/>
-      <c r="H21" s="113"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="113"/>
-      <c r="K21" s="111"/>
-      <c r="L21" s="112"/>
-      <c r="M21" s="112"/>
+      <c r="C21" s="96"/>
+      <c r="D21" s="97"/>
+      <c r="E21" s="96"/>
+      <c r="F21" s="97"/>
+      <c r="G21" s="96"/>
+      <c r="H21" s="97"/>
+      <c r="I21" s="96"/>
+      <c r="J21" s="97"/>
+      <c r="K21" s="96"/>
+      <c r="L21" s="141"/>
+      <c r="M21" s="141"/>
       <c r="N21" s="44"/>
-      <c r="O21" s="111"/>
-      <c r="P21" s="112"/>
-      <c r="Q21" s="112"/>
-      <c r="R21" s="112"/>
-      <c r="S21" s="112"/>
-      <c r="T21" s="112"/>
-      <c r="U21" s="112"/>
-      <c r="V21" s="113"/>
-      <c r="W21" s="111"/>
-      <c r="X21" s="112"/>
-      <c r="Y21" s="112"/>
-      <c r="Z21" s="112"/>
-      <c r="AA21" s="112"/>
-      <c r="AB21" s="112"/>
-      <c r="AC21" s="112"/>
-      <c r="AD21" s="113"/>
+      <c r="O21" s="96"/>
+      <c r="P21" s="141"/>
+      <c r="Q21" s="141"/>
+      <c r="R21" s="141"/>
+      <c r="S21" s="141"/>
+      <c r="T21" s="141"/>
+      <c r="U21" s="141"/>
+      <c r="V21" s="97"/>
+      <c r="W21" s="96"/>
+      <c r="X21" s="141"/>
+      <c r="Y21" s="141"/>
+      <c r="Z21" s="141"/>
+      <c r="AA21" s="141"/>
+      <c r="AB21" s="141"/>
+      <c r="AC21" s="141"/>
+      <c r="AD21" s="97"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
     </row>
-    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52"/>
@@ -4520,7 +4615,7 @@
       <c r="AD22" s="55"/>
       <c r="AF22" s="4"/>
     </row>
-    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="56"/>
@@ -4554,61 +4649,61 @@
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
     </row>
-    <row r="24" spans="1:42" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:42" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="M24" s="1"/>
       <c r="AF24" s="1"/>
     </row>
-    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="C25" s="132" t="s">
+      <c r="C25" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="132"/>
-      <c r="E25" s="132"/>
-      <c r="F25" s="132"/>
-      <c r="G25" s="132"/>
-      <c r="H25" s="132"/>
-      <c r="I25" s="132"/>
-      <c r="J25" s="132"/>
-      <c r="K25" s="132"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="86"/>
+      <c r="H25" s="86"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="86"/>
+      <c r="K25" s="86"/>
       <c r="L25" s="60"/>
       <c r="M25" s="1"/>
-      <c r="O25" s="133">
+      <c r="O25" s="87">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)-1,1)</f>
         <v>46266</v>
       </c>
-      <c r="P25" s="133"/>
-      <c r="Q25" s="133"/>
-      <c r="R25" s="133"/>
-      <c r="S25" s="133"/>
-      <c r="T25" s="133"/>
-      <c r="U25" s="133"/>
+      <c r="P25" s="87"/>
+      <c r="Q25" s="87"/>
+      <c r="R25" s="87"/>
+      <c r="S25" s="87"/>
+      <c r="T25" s="87"/>
+      <c r="U25" s="87"/>
       <c r="V25" s="61"/>
       <c r="W25" s="61"/>
-      <c r="X25" s="133">
+      <c r="X25" s="87">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)+1,1)</f>
         <v>46327</v>
       </c>
-      <c r="Y25" s="133"/>
-      <c r="Z25" s="133"/>
-      <c r="AA25" s="133"/>
-      <c r="AB25" s="133"/>
-      <c r="AC25" s="133"/>
-      <c r="AD25" s="133"/>
+      <c r="Y25" s="87"/>
+      <c r="Z25" s="87"/>
+      <c r="AA25" s="87"/>
+      <c r="AB25" s="87"/>
+      <c r="AC25" s="87"/>
+      <c r="AD25" s="87"/>
       <c r="AF25" s="1"/>
     </row>
-    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="C26" s="132"/>
-      <c r="D26" s="132"/>
-      <c r="E26" s="132"/>
-      <c r="F26" s="132"/>
-      <c r="G26" s="132"/>
-      <c r="H26" s="132"/>
-      <c r="I26" s="132"/>
-      <c r="J26" s="132"/>
-      <c r="K26" s="132"/>
+      <c r="C26" s="86"/>
+      <c r="D26" s="86"/>
+      <c r="E26" s="86"/>
+      <c r="F26" s="86"/>
+      <c r="G26" s="86"/>
+      <c r="H26" s="86"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="K26" s="86"/>
       <c r="L26" s="60"/>
       <c r="M26" s="1"/>
       <c r="O26" s="62" t="str">
@@ -4671,17 +4766,17 @@
       </c>
       <c r="AF26" s="1"/>
     </row>
-    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="C27" s="131"/>
-      <c r="D27" s="131"/>
-      <c r="E27" s="131"/>
-      <c r="F27" s="131"/>
-      <c r="G27" s="131"/>
-      <c r="H27" s="131"/>
-      <c r="I27" s="131"/>
-      <c r="J27" s="131"/>
-      <c r="K27" s="131"/>
+      <c r="C27" s="88"/>
+      <c r="D27" s="88"/>
+      <c r="E27" s="88"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="88"/>
+      <c r="H27" s="88"/>
+      <c r="I27" s="88"/>
+      <c r="J27" s="88"/>
+      <c r="K27" s="88"/>
       <c r="M27" s="1"/>
       <c r="O27" s="64" t="str">
         <f t="shared" ref="O27:U32" ca="1" si="0">IF(MONTH($O$25)&lt;&gt;MONTH($O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1)),"",$O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1))</f>
@@ -4743,17 +4838,17 @@
       </c>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="C28" s="130"/>
-      <c r="D28" s="130"/>
-      <c r="E28" s="130"/>
-      <c r="F28" s="130"/>
-      <c r="G28" s="130"/>
-      <c r="H28" s="130"/>
-      <c r="I28" s="130"/>
-      <c r="J28" s="130"/>
-      <c r="K28" s="130"/>
+      <c r="C28" s="89"/>
+      <c r="D28" s="89"/>
+      <c r="E28" s="89"/>
+      <c r="F28" s="89"/>
+      <c r="G28" s="89"/>
+      <c r="H28" s="89"/>
+      <c r="I28" s="89"/>
+      <c r="J28" s="89"/>
+      <c r="K28" s="89"/>
       <c r="M28" s="1"/>
       <c r="O28" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -4815,17 +4910,17 @@
       </c>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="C29" s="131"/>
-      <c r="D29" s="131"/>
-      <c r="E29" s="131"/>
-      <c r="F29" s="131"/>
-      <c r="G29" s="131"/>
-      <c r="H29" s="131"/>
-      <c r="I29" s="131"/>
-      <c r="J29" s="131"/>
-      <c r="K29" s="131"/>
+      <c r="C29" s="88"/>
+      <c r="D29" s="88"/>
+      <c r="E29" s="88"/>
+      <c r="F29" s="88"/>
+      <c r="G29" s="88"/>
+      <c r="H29" s="88"/>
+      <c r="I29" s="88"/>
+      <c r="J29" s="88"/>
+      <c r="K29" s="88"/>
       <c r="M29" s="1"/>
       <c r="O29" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -4887,17 +4982,17 @@
       </c>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="C30" s="130"/>
-      <c r="D30" s="130"/>
-      <c r="E30" s="130"/>
-      <c r="F30" s="130"/>
-      <c r="G30" s="130"/>
-      <c r="H30" s="130"/>
-      <c r="I30" s="130"/>
-      <c r="J30" s="130"/>
-      <c r="K30" s="130"/>
+      <c r="C30" s="89"/>
+      <c r="D30" s="89"/>
+      <c r="E30" s="89"/>
+      <c r="F30" s="89"/>
+      <c r="G30" s="89"/>
+      <c r="H30" s="89"/>
+      <c r="I30" s="89"/>
+      <c r="J30" s="89"/>
+      <c r="K30" s="89"/>
       <c r="M30" s="1"/>
       <c r="O30" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -4959,17 +5054,17 @@
       </c>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="C31" s="131"/>
-      <c r="D31" s="131"/>
-      <c r="E31" s="131"/>
-      <c r="F31" s="131"/>
-      <c r="G31" s="131"/>
-      <c r="H31" s="131"/>
-      <c r="I31" s="131"/>
-      <c r="J31" s="131"/>
-      <c r="K31" s="131"/>
+      <c r="C31" s="88"/>
+      <c r="D31" s="88"/>
+      <c r="E31" s="88"/>
+      <c r="F31" s="88"/>
+      <c r="G31" s="88"/>
+      <c r="H31" s="88"/>
+      <c r="I31" s="88"/>
+      <c r="J31" s="88"/>
+      <c r="K31" s="88"/>
       <c r="M31" s="1"/>
       <c r="O31" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -5031,7 +5126,7 @@
       </c>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="M32" s="1"/>
       <c r="O32" s="64" t="str">
@@ -5094,7 +5189,7 @@
       </c>
       <c r="AF32" s="1"/>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="M33" s="1"/>
       <c r="O33" s="64"/>
@@ -5115,7 +5210,7 @@
       <c r="AD33" s="65"/>
       <c r="AF33" s="1"/>
     </row>
-    <row r="34" spans="1:32" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:32" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -5149,69 +5244,156 @@
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
     </row>
-    <row r="38" spans="1:32" ht="12.9" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D39" s="83" t="s">
-        <v>30</v>
-      </c>
-      <c r="E39" s="84"/>
-      <c r="F39" s="85"/>
-      <c r="G39" s="89">
+    <row r="38" spans="1:32" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D39" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="E39" s="114"/>
+      <c r="F39" s="115"/>
+      <c r="G39" s="119">
         <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
         <v>5</v>
       </c>
-      <c r="H39" s="90"/>
-      <c r="I39" s="83" t="s">
-        <v>33</v>
-      </c>
-      <c r="J39" s="93"/>
-      <c r="K39" s="95" t="s">
-        <v>31</v>
-      </c>
-      <c r="L39" s="96"/>
-      <c r="M39" s="99">
+      <c r="H39" s="120"/>
+      <c r="I39" s="113" t="s">
+        <v>28</v>
+      </c>
+      <c r="J39" s="123"/>
+      <c r="K39" s="125" t="s">
+        <v>26</v>
+      </c>
+      <c r="L39" s="126"/>
+      <c r="M39" s="129">
         <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
         <v>5.9999999999999973</v>
       </c>
-      <c r="N39" s="100"/>
-      <c r="O39" s="100"/>
-      <c r="P39" s="100"/>
-      <c r="Q39" s="100"/>
-      <c r="R39" s="101"/>
-      <c r="S39" s="105" t="s">
-        <v>32</v>
-      </c>
-      <c r="T39" s="106"/>
-      <c r="U39" s="106"/>
-      <c r="V39" s="106"/>
-      <c r="W39" s="106"/>
-      <c r="X39" s="107"/>
-    </row>
-    <row r="40" spans="1:32" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D40" s="86"/>
-      <c r="E40" s="87"/>
-      <c r="F40" s="88"/>
-      <c r="G40" s="91"/>
-      <c r="H40" s="92"/>
-      <c r="I40" s="86"/>
-      <c r="J40" s="94"/>
-      <c r="K40" s="97"/>
-      <c r="L40" s="98"/>
-      <c r="M40" s="102"/>
-      <c r="N40" s="103"/>
-      <c r="O40" s="103"/>
-      <c r="P40" s="103"/>
-      <c r="Q40" s="103"/>
-      <c r="R40" s="104"/>
-      <c r="S40" s="108"/>
-      <c r="T40" s="109"/>
-      <c r="U40" s="109"/>
-      <c r="V40" s="109"/>
-      <c r="W40" s="109"/>
-      <c r="X40" s="110"/>
+      <c r="N39" s="130"/>
+      <c r="O39" s="130"/>
+      <c r="P39" s="130"/>
+      <c r="Q39" s="130"/>
+      <c r="R39" s="131"/>
+      <c r="S39" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="T39" s="136"/>
+      <c r="U39" s="136"/>
+      <c r="V39" s="136"/>
+      <c r="W39" s="136"/>
+      <c r="X39" s="137"/>
+    </row>
+    <row r="40" spans="1:32" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D40" s="116"/>
+      <c r="E40" s="117"/>
+      <c r="F40" s="118"/>
+      <c r="G40" s="121"/>
+      <c r="H40" s="122"/>
+      <c r="I40" s="116"/>
+      <c r="J40" s="124"/>
+      <c r="K40" s="127"/>
+      <c r="L40" s="128"/>
+      <c r="M40" s="132"/>
+      <c r="N40" s="133"/>
+      <c r="O40" s="133"/>
+      <c r="P40" s="133"/>
+      <c r="Q40" s="133"/>
+      <c r="R40" s="134"/>
+      <c r="S40" s="138"/>
+      <c r="T40" s="139"/>
+      <c r="U40" s="139"/>
+      <c r="V40" s="139"/>
+      <c r="W40" s="139"/>
+      <c r="X40" s="140"/>
     </row>
   </sheetData>
   <mergeCells count="110">
+    <mergeCell ref="D39:F40"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="K39:L40"/>
+    <mergeCell ref="M39:R40"/>
+    <mergeCell ref="S39:X40"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="O21:V21"/>
+    <mergeCell ref="W21:AD21"/>
+    <mergeCell ref="C30:K31"/>
+    <mergeCell ref="C2:AD2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="W5:AD5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:V6"/>
+    <mergeCell ref="W6:AD6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="O5:V5"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="W7:AD7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="O8:V8"/>
+    <mergeCell ref="W8:AD8"/>
+    <mergeCell ref="O7:V7"/>
+    <mergeCell ref="W9:AD9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="O11:V11"/>
+    <mergeCell ref="W11:AD11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:V9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="W12:AD12"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O14:V14"/>
+    <mergeCell ref="W14:AD14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="O12:V12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="W15:AD15"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="O17:V17"/>
+    <mergeCell ref="W17:AD17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="O15:V15"/>
+    <mergeCell ref="K15:N15"/>
     <mergeCell ref="W18:AD18"/>
     <mergeCell ref="C25:K26"/>
     <mergeCell ref="O25:U25"/>
@@ -5235,93 +5417,6 @@
     <mergeCell ref="E21:F21"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="I21:J21"/>
-    <mergeCell ref="W15:AD15"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="O17:V17"/>
-    <mergeCell ref="W17:AD17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="O15:V15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="W12:AD12"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="O14:V14"/>
-    <mergeCell ref="W14:AD14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="O12:V12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="W9:AD9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="O11:V11"/>
-    <mergeCell ref="W11:AD11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:V9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="W7:AD7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="O8:V8"/>
-    <mergeCell ref="W8:AD8"/>
-    <mergeCell ref="O7:V7"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:V6"/>
-    <mergeCell ref="W6:AD6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="O5:V5"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="C2:AD2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="W5:AD5"/>
-    <mergeCell ref="D39:F40"/>
-    <mergeCell ref="G39:H40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="K39:L40"/>
-    <mergeCell ref="M39:R40"/>
-    <mergeCell ref="S39:X40"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="O21:V21"/>
-    <mergeCell ref="W21:AD21"/>
-    <mergeCell ref="C30:K31"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 E5 G5 I5 K5:L5 O5 W5 C7 E8 G8 I8 K8:L8 O8 W8 C10 E11 G11 I11 K11:L11 O11 W11 C13 E14 G14 I14 K14:L14 O14 W14 C16 E17 G17 I17 K17:L17 O17 W17">
     <cfRule type="expression" dxfId="7" priority="3">
@@ -5360,7 +5455,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AP39"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="12.6" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="3" width="5.5546875" style="3" customWidth="1"/>
     <col min="4" max="4" width="15.5546875" style="3" customWidth="1"/>
@@ -5378,7 +5473,7 @@
     <col min="35" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5412,42 +5507,42 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="2.15">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A2" s="29"/>
-      <c r="C2" s="114">
+      <c r="C2" s="111">
         <f ca="1">DATE(About!P8,11,1)</f>
         <v>46327</v>
       </c>
-      <c r="D2" s="114"/>
-      <c r="E2" s="114"/>
-      <c r="F2" s="114"/>
-      <c r="G2" s="114"/>
-      <c r="H2" s="114"/>
-      <c r="I2" s="114"/>
-      <c r="J2" s="114"/>
-      <c r="K2" s="114"/>
-      <c r="L2" s="114"/>
-      <c r="M2" s="114"/>
-      <c r="N2" s="114"/>
-      <c r="O2" s="114"/>
-      <c r="P2" s="114"/>
-      <c r="Q2" s="114"/>
-      <c r="R2" s="114"/>
-      <c r="S2" s="114"/>
-      <c r="T2" s="114"/>
-      <c r="U2" s="114"/>
-      <c r="V2" s="114"/>
-      <c r="W2" s="114"/>
-      <c r="X2" s="114"/>
-      <c r="Y2" s="114"/>
-      <c r="Z2" s="114"/>
-      <c r="AA2" s="114"/>
-      <c r="AB2" s="114"/>
-      <c r="AC2" s="114"/>
-      <c r="AD2" s="114"/>
+      <c r="D2" s="111"/>
+      <c r="E2" s="111"/>
+      <c r="F2" s="111"/>
+      <c r="G2" s="111"/>
+      <c r="H2" s="111"/>
+      <c r="I2" s="111"/>
+      <c r="J2" s="111"/>
+      <c r="K2" s="111"/>
+      <c r="L2" s="111"/>
+      <c r="M2" s="111"/>
+      <c r="N2" s="111"/>
+      <c r="O2" s="111"/>
+      <c r="P2" s="111"/>
+      <c r="Q2" s="111"/>
+      <c r="R2" s="111"/>
+      <c r="S2" s="111"/>
+      <c r="T2" s="111"/>
+      <c r="U2" s="111"/>
+      <c r="V2" s="111"/>
+      <c r="W2" s="111"/>
+      <c r="X2" s="111"/>
+      <c r="Y2" s="111"/>
+      <c r="Z2" s="111"/>
+      <c r="AA2" s="111"/>
+      <c r="AB2" s="111"/>
+      <c r="AC2" s="111"/>
+      <c r="AD2" s="111"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="2.15">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -5467,284 +5562,288 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="35"/>
-      <c r="C4" s="115">
+      <c r="C4" s="112">
         <f ca="1">C5</f>
         <v>46327</v>
       </c>
-      <c r="D4" s="115"/>
-      <c r="E4" s="115">
+      <c r="D4" s="112"/>
+      <c r="E4" s="112">
         <f ca="1">E5</f>
         <v>46328</v>
       </c>
-      <c r="F4" s="115"/>
-      <c r="G4" s="115">
+      <c r="F4" s="112"/>
+      <c r="G4" s="112">
         <f ca="1">G5</f>
         <v>46329</v>
       </c>
-      <c r="H4" s="115"/>
-      <c r="I4" s="115">
+      <c r="H4" s="112"/>
+      <c r="I4" s="112">
         <f ca="1">I5</f>
         <v>46330</v>
       </c>
-      <c r="J4" s="115"/>
-      <c r="K4" s="115">
+      <c r="J4" s="112"/>
+      <c r="K4" s="112">
         <f ca="1">K5</f>
         <v>46331</v>
       </c>
-      <c r="L4" s="115"/>
-      <c r="M4" s="115"/>
+      <c r="L4" s="112"/>
+      <c r="M4" s="112"/>
       <c r="N4" s="37"/>
-      <c r="O4" s="115">
+      <c r="O4" s="112">
         <f ca="1">O5</f>
         <v>46332</v>
       </c>
-      <c r="P4" s="115"/>
-      <c r="Q4" s="115"/>
-      <c r="R4" s="115"/>
-      <c r="S4" s="115"/>
-      <c r="T4" s="115"/>
-      <c r="U4" s="115"/>
-      <c r="V4" s="115"/>
-      <c r="W4" s="115">
+      <c r="P4" s="112"/>
+      <c r="Q4" s="112"/>
+      <c r="R4" s="112"/>
+      <c r="S4" s="112"/>
+      <c r="T4" s="112"/>
+      <c r="U4" s="112"/>
+      <c r="V4" s="112"/>
+      <c r="W4" s="112">
         <f ca="1">W5</f>
         <v>46333</v>
       </c>
-      <c r="X4" s="115"/>
-      <c r="Y4" s="115"/>
-      <c r="Z4" s="115"/>
-      <c r="AA4" s="115"/>
-      <c r="AB4" s="115"/>
-      <c r="AC4" s="115"/>
-      <c r="AD4" s="115"/>
+      <c r="X4" s="112"/>
+      <c r="Y4" s="112"/>
+      <c r="Z4" s="112"/>
+      <c r="AA4" s="112"/>
+      <c r="AB4" s="112"/>
+      <c r="AC4" s="112"/>
+      <c r="AD4" s="112"/>
       <c r="AF4" s="38"/>
       <c r="AG4" s="39"/>
       <c r="AH4" s="39"/>
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="C5" s="116">
+      <c r="C5" s="91">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46327</v>
       </c>
-      <c r="D5" s="118"/>
-      <c r="E5" s="116">
+      <c r="D5" s="92"/>
+      <c r="E5" s="91">
         <f ca="1">C5+1</f>
         <v>46328</v>
       </c>
-      <c r="F5" s="118"/>
-      <c r="G5" s="116">
+      <c r="F5" s="92"/>
+      <c r="G5" s="91">
         <f ca="1">E5+1</f>
         <v>46329</v>
       </c>
-      <c r="H5" s="118"/>
-      <c r="I5" s="116">
+      <c r="H5" s="92"/>
+      <c r="I5" s="91">
         <f ca="1">G5+1</f>
         <v>46330</v>
       </c>
-      <c r="J5" s="118"/>
-      <c r="K5" s="116">
+      <c r="J5" s="92"/>
+      <c r="K5" s="91">
         <f ca="1">I5+1</f>
         <v>46331</v>
       </c>
-      <c r="L5" s="117"/>
-      <c r="M5" s="117"/>
+      <c r="L5" s="110"/>
+      <c r="M5" s="110"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="116">
+      <c r="O5" s="91">
         <f ca="1">K5+1</f>
         <v>46332</v>
       </c>
-      <c r="P5" s="117"/>
-      <c r="Q5" s="117"/>
-      <c r="R5" s="117"/>
-      <c r="S5" s="117"/>
-      <c r="T5" s="117"/>
-      <c r="U5" s="117"/>
-      <c r="V5" s="118"/>
-      <c r="W5" s="116">
+      <c r="P5" s="110"/>
+      <c r="Q5" s="110"/>
+      <c r="R5" s="110"/>
+      <c r="S5" s="110"/>
+      <c r="T5" s="110"/>
+      <c r="U5" s="110"/>
+      <c r="V5" s="92"/>
+      <c r="W5" s="91">
         <f ca="1">O5+1</f>
         <v>46333</v>
       </c>
-      <c r="X5" s="117"/>
-      <c r="Y5" s="117"/>
-      <c r="Z5" s="117"/>
-      <c r="AA5" s="117"/>
-      <c r="AB5" s="117"/>
-      <c r="AC5" s="117"/>
-      <c r="AD5" s="118"/>
+      <c r="X5" s="110"/>
+      <c r="Y5" s="110"/>
+      <c r="Z5" s="110"/>
+      <c r="AA5" s="110"/>
+      <c r="AB5" s="110"/>
+      <c r="AC5" s="110"/>
+      <c r="AD5" s="92"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
       <c r="AI5" s="41"/>
       <c r="AJ5" s="41"/>
     </row>
-    <row r="6" spans="1:36" s="43" customFormat="1" ht="133.80000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:36" s="43" customFormat="1" ht="133.80000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="42"/>
-      <c r="C6" s="121"/>
-      <c r="D6" s="123"/>
-      <c r="E6" s="121"/>
-      <c r="F6" s="123"/>
-      <c r="G6" s="121"/>
-      <c r="H6" s="123"/>
-      <c r="I6" s="121"/>
-      <c r="J6" s="123"/>
-      <c r="K6" s="121"/>
-      <c r="L6" s="122"/>
-      <c r="M6" s="122"/>
-      <c r="N6" s="123"/>
-      <c r="O6" s="121" t="s">
-        <v>21</v>
-      </c>
-      <c r="P6" s="122"/>
-      <c r="Q6" s="122"/>
-      <c r="R6" s="122"/>
-      <c r="S6" s="122"/>
-      <c r="T6" s="122"/>
-      <c r="U6" s="122"/>
-      <c r="V6" s="123"/>
-      <c r="W6" s="121"/>
-      <c r="X6" s="122"/>
-      <c r="Y6" s="122"/>
-      <c r="Z6" s="122"/>
-      <c r="AA6" s="122"/>
-      <c r="AB6" s="122"/>
-      <c r="AC6" s="122"/>
-      <c r="AD6" s="123"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="90" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" s="85"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="85"/>
+      <c r="I6" s="83"/>
+      <c r="J6" s="85"/>
+      <c r="K6" s="83"/>
+      <c r="L6" s="84"/>
+      <c r="M6" s="84"/>
+      <c r="N6" s="85"/>
+      <c r="O6" s="90" t="s">
+        <v>43</v>
+      </c>
+      <c r="P6" s="84"/>
+      <c r="Q6" s="84"/>
+      <c r="R6" s="84"/>
+      <c r="S6" s="84"/>
+      <c r="T6" s="84"/>
+      <c r="U6" s="84"/>
+      <c r="V6" s="85"/>
+      <c r="W6" s="83"/>
+      <c r="X6" s="84"/>
+      <c r="Y6" s="84"/>
+      <c r="Z6" s="84"/>
+      <c r="AA6" s="84"/>
+      <c r="AB6" s="84"/>
+      <c r="AC6" s="84"/>
+      <c r="AD6" s="85"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
-    <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
-      <c r="C7" s="141">
+      <c r="C7" s="152">
         <f ca="1">W5+1</f>
         <v>46334</v>
       </c>
-      <c r="D7" s="142"/>
-      <c r="E7" s="143"/>
-      <c r="F7" s="144"/>
-      <c r="G7" s="143"/>
-      <c r="H7" s="144"/>
-      <c r="I7" s="143"/>
-      <c r="J7" s="144"/>
-      <c r="K7" s="143"/>
-      <c r="L7" s="145"/>
-      <c r="M7" s="145"/>
+      <c r="D7" s="153"/>
+      <c r="E7" s="157"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="157"/>
+      <c r="H7" s="158"/>
+      <c r="I7" s="157"/>
+      <c r="J7" s="158"/>
+      <c r="K7" s="157"/>
+      <c r="L7" s="159"/>
+      <c r="M7" s="159"/>
       <c r="N7" s="80"/>
-      <c r="O7" s="143"/>
-      <c r="P7" s="145"/>
-      <c r="Q7" s="145"/>
-      <c r="R7" s="145"/>
-      <c r="S7" s="145"/>
-      <c r="T7" s="145"/>
-      <c r="U7" s="145"/>
-      <c r="V7" s="144"/>
-      <c r="W7" s="143"/>
-      <c r="X7" s="145"/>
-      <c r="Y7" s="145"/>
-      <c r="Z7" s="145"/>
-      <c r="AA7" s="145"/>
-      <c r="AB7" s="145"/>
-      <c r="AC7" s="145"/>
-      <c r="AD7" s="144"/>
+      <c r="O7" s="157"/>
+      <c r="P7" s="159"/>
+      <c r="Q7" s="159"/>
+      <c r="R7" s="159"/>
+      <c r="S7" s="159"/>
+      <c r="T7" s="159"/>
+      <c r="U7" s="159"/>
+      <c r="V7" s="158"/>
+      <c r="W7" s="157"/>
+      <c r="X7" s="159"/>
+      <c r="Y7" s="159"/>
+      <c r="Z7" s="159"/>
+      <c r="AA7" s="159"/>
+      <c r="AB7" s="159"/>
+      <c r="AC7" s="159"/>
+      <c r="AD7" s="158"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
-      <c r="C8" s="141"/>
-      <c r="D8" s="142"/>
-      <c r="E8" s="141">
+      <c r="C8" s="152"/>
+      <c r="D8" s="153"/>
+      <c r="E8" s="152">
         <f ca="1">C7+1</f>
         <v>46335</v>
       </c>
-      <c r="F8" s="142"/>
-      <c r="G8" s="141">
+      <c r="F8" s="153"/>
+      <c r="G8" s="152">
         <f ca="1">E8+1</f>
         <v>46336</v>
       </c>
-      <c r="H8" s="142"/>
-      <c r="I8" s="141">
+      <c r="H8" s="153"/>
+      <c r="I8" s="152">
         <f ca="1">G8+1</f>
         <v>46337</v>
       </c>
-      <c r="J8" s="142"/>
-      <c r="K8" s="141">
+      <c r="J8" s="153"/>
+      <c r="K8" s="152">
         <f ca="1">I8+1</f>
         <v>46338</v>
       </c>
-      <c r="L8" s="146"/>
-      <c r="M8" s="146"/>
+      <c r="L8" s="154"/>
+      <c r="M8" s="154"/>
       <c r="N8" s="78"/>
-      <c r="O8" s="141">
+      <c r="O8" s="152">
         <f ca="1">K8+1</f>
         <v>46339</v>
       </c>
-      <c r="P8" s="146"/>
-      <c r="Q8" s="146"/>
-      <c r="R8" s="146"/>
-      <c r="S8" s="146"/>
-      <c r="T8" s="146"/>
-      <c r="U8" s="146"/>
-      <c r="V8" s="142"/>
-      <c r="W8" s="141">
+      <c r="P8" s="154"/>
+      <c r="Q8" s="154"/>
+      <c r="R8" s="154"/>
+      <c r="S8" s="154"/>
+      <c r="T8" s="154"/>
+      <c r="U8" s="154"/>
+      <c r="V8" s="153"/>
+      <c r="W8" s="152">
         <f ca="1">O8+1</f>
         <v>46340</v>
       </c>
-      <c r="X8" s="146"/>
-      <c r="Y8" s="146"/>
-      <c r="Z8" s="146"/>
-      <c r="AA8" s="146"/>
-      <c r="AB8" s="146"/>
-      <c r="AC8" s="146"/>
-      <c r="AD8" s="142"/>
+      <c r="X8" s="154"/>
+      <c r="Y8" s="154"/>
+      <c r="Z8" s="154"/>
+      <c r="AA8" s="154"/>
+      <c r="AB8" s="154"/>
+      <c r="AC8" s="154"/>
+      <c r="AD8" s="153"/>
       <c r="AF8" s="4"/>
     </row>
-    <row r="9" spans="1:36" s="43" customFormat="1" ht="146.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:36" s="43" customFormat="1" ht="146.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="42"/>
-      <c r="C9" s="121"/>
-      <c r="D9" s="123"/>
-      <c r="E9" s="121"/>
-      <c r="F9" s="123"/>
-      <c r="G9" s="121"/>
-      <c r="H9" s="123"/>
-      <c r="I9" s="121"/>
-      <c r="J9" s="123"/>
-      <c r="K9" s="121" t="s">
-        <v>22</v>
-      </c>
-      <c r="L9" s="122"/>
-      <c r="M9" s="122"/>
-      <c r="N9" s="123"/>
-      <c r="O9" s="148" t="s">
+      <c r="C9" s="83"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="90" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="85"/>
+      <c r="G9" s="83"/>
+      <c r="H9" s="85"/>
+      <c r="I9" s="83"/>
+      <c r="J9" s="85"/>
+      <c r="K9" s="83" t="s">
+        <v>18</v>
+      </c>
+      <c r="L9" s="84"/>
+      <c r="M9" s="84"/>
+      <c r="N9" s="85"/>
+      <c r="O9" s="155" t="s">
         <v>15</v>
       </c>
-      <c r="P9" s="147"/>
-      <c r="Q9" s="147"/>
-      <c r="R9" s="147"/>
-      <c r="S9" s="147"/>
-      <c r="T9" s="147"/>
-      <c r="U9" s="147"/>
-      <c r="V9" s="120"/>
-      <c r="W9" s="119"/>
-      <c r="X9" s="147"/>
-      <c r="Y9" s="147"/>
-      <c r="Z9" s="147"/>
-      <c r="AA9" s="147"/>
-      <c r="AB9" s="147"/>
-      <c r="AC9" s="147"/>
-      <c r="AD9" s="120"/>
+      <c r="P9" s="151"/>
+      <c r="Q9" s="151"/>
+      <c r="R9" s="151"/>
+      <c r="S9" s="151"/>
+      <c r="T9" s="151"/>
+      <c r="U9" s="151"/>
+      <c r="V9" s="103"/>
+      <c r="W9" s="102"/>
+      <c r="X9" s="151"/>
+      <c r="Y9" s="151"/>
+      <c r="Z9" s="151"/>
+      <c r="AA9" s="151"/>
+      <c r="AB9" s="151"/>
+      <c r="AC9" s="151"/>
+      <c r="AD9" s="103"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
-    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="42"/>
-      <c r="C10" s="141">
+      <c r="C10" s="152">
         <f ca="1">W8+1</f>
         <v>46341</v>
       </c>
-      <c r="D10" s="142"/>
+      <c r="D10" s="153"/>
       <c r="E10" s="79"/>
       <c r="F10" s="80"/>
       <c r="G10" s="79"/>
@@ -5774,99 +5873,99 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="42"/>
     </row>
-    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="4"/>
-      <c r="C11" s="141"/>
-      <c r="D11" s="142"/>
-      <c r="E11" s="141">
+      <c r="C11" s="152"/>
+      <c r="D11" s="153"/>
+      <c r="E11" s="152">
         <f ca="1">C10+1</f>
         <v>46342</v>
       </c>
-      <c r="F11" s="142"/>
-      <c r="G11" s="141">
+      <c r="F11" s="153"/>
+      <c r="G11" s="152">
         <f ca="1">E11+1</f>
         <v>46343</v>
       </c>
-      <c r="H11" s="142"/>
-      <c r="I11" s="141">
+      <c r="H11" s="153"/>
+      <c r="I11" s="152">
         <f ca="1">G11+1</f>
         <v>46344</v>
       </c>
-      <c r="J11" s="142"/>
-      <c r="K11" s="141">
+      <c r="J11" s="153"/>
+      <c r="K11" s="152">
         <f ca="1">I11+1</f>
         <v>46345</v>
       </c>
-      <c r="L11" s="146"/>
-      <c r="M11" s="146"/>
+      <c r="L11" s="154"/>
+      <c r="M11" s="154"/>
       <c r="N11" s="78"/>
-      <c r="O11" s="141">
+      <c r="O11" s="152">
         <f ca="1">K11+1</f>
         <v>46346</v>
       </c>
-      <c r="P11" s="146"/>
-      <c r="Q11" s="146"/>
-      <c r="R11" s="146"/>
-      <c r="S11" s="146"/>
-      <c r="T11" s="146"/>
-      <c r="U11" s="146"/>
-      <c r="V11" s="142"/>
-      <c r="W11" s="141">
+      <c r="P11" s="154"/>
+      <c r="Q11" s="154"/>
+      <c r="R11" s="154"/>
+      <c r="S11" s="154"/>
+      <c r="T11" s="154"/>
+      <c r="U11" s="154"/>
+      <c r="V11" s="153"/>
+      <c r="W11" s="152">
         <f ca="1">O11+1</f>
         <v>46347</v>
       </c>
-      <c r="X11" s="146"/>
-      <c r="Y11" s="146"/>
-      <c r="Z11" s="146"/>
-      <c r="AA11" s="146"/>
-      <c r="AB11" s="146"/>
-      <c r="AC11" s="146"/>
-      <c r="AD11" s="142"/>
+      <c r="X11" s="154"/>
+      <c r="Y11" s="154"/>
+      <c r="Z11" s="154"/>
+      <c r="AA11" s="154"/>
+      <c r="AB11" s="154"/>
+      <c r="AC11" s="154"/>
+      <c r="AD11" s="153"/>
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:36" s="43" customFormat="1" ht="134.69999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:36" s="43" customFormat="1" ht="134.69999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="42"/>
-      <c r="C12" s="119"/>
-      <c r="D12" s="120"/>
-      <c r="E12" s="148" t="s">
+      <c r="C12" s="102"/>
+      <c r="D12" s="103"/>
+      <c r="E12" s="155" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="149"/>
-      <c r="G12" s="119"/>
-      <c r="H12" s="120"/>
-      <c r="I12" s="119"/>
-      <c r="J12" s="120"/>
-      <c r="K12" s="119"/>
-      <c r="L12" s="147"/>
-      <c r="M12" s="147"/>
-      <c r="N12" s="120"/>
-      <c r="O12" s="119"/>
-      <c r="P12" s="147"/>
-      <c r="Q12" s="147"/>
-      <c r="R12" s="147"/>
-      <c r="S12" s="147"/>
-      <c r="T12" s="147"/>
-      <c r="U12" s="147"/>
-      <c r="V12" s="120"/>
-      <c r="W12" s="119"/>
-      <c r="X12" s="147"/>
-      <c r="Y12" s="147"/>
-      <c r="Z12" s="147"/>
-      <c r="AA12" s="147"/>
-      <c r="AB12" s="147"/>
-      <c r="AC12" s="147"/>
-      <c r="AD12" s="120"/>
+      <c r="F12" s="156"/>
+      <c r="G12" s="102"/>
+      <c r="H12" s="103"/>
+      <c r="I12" s="102"/>
+      <c r="J12" s="103"/>
+      <c r="K12" s="102"/>
+      <c r="L12" s="151"/>
+      <c r="M12" s="151"/>
+      <c r="N12" s="103"/>
+      <c r="O12" s="102"/>
+      <c r="P12" s="151"/>
+      <c r="Q12" s="151"/>
+      <c r="R12" s="151"/>
+      <c r="S12" s="151"/>
+      <c r="T12" s="151"/>
+      <c r="U12" s="151"/>
+      <c r="V12" s="103"/>
+      <c r="W12" s="102"/>
+      <c r="X12" s="151"/>
+      <c r="Y12" s="151"/>
+      <c r="Z12" s="151"/>
+      <c r="AA12" s="151"/>
+      <c r="AB12" s="151"/>
+      <c r="AC12" s="151"/>
+      <c r="AD12" s="103"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
-    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="42"/>
-      <c r="C13" s="141">
+      <c r="C13" s="152">
         <f ca="1">W11+1</f>
         <v>46348</v>
       </c>
-      <c r="D13" s="142"/>
+      <c r="D13" s="153"/>
       <c r="E13" s="79"/>
       <c r="F13" s="80"/>
       <c r="G13" s="79"/>
@@ -5896,102 +5995,102 @@
       <c r="AE13" s="7"/>
       <c r="AF13" s="42"/>
     </row>
-    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
-      <c r="C14" s="141"/>
-      <c r="D14" s="142"/>
-      <c r="E14" s="141">
+      <c r="C14" s="152"/>
+      <c r="D14" s="153"/>
+      <c r="E14" s="152">
         <f ca="1">C13+1</f>
         <v>46349</v>
       </c>
-      <c r="F14" s="142"/>
-      <c r="G14" s="141">
+      <c r="F14" s="153"/>
+      <c r="G14" s="152">
         <f ca="1">E14+1</f>
         <v>46350</v>
       </c>
-      <c r="H14" s="142"/>
-      <c r="I14" s="141">
+      <c r="H14" s="153"/>
+      <c r="I14" s="152">
         <f ca="1">G14+1</f>
         <v>46351</v>
       </c>
-      <c r="J14" s="142"/>
-      <c r="K14" s="141">
+      <c r="J14" s="153"/>
+      <c r="K14" s="152">
         <f ca="1">I14+1</f>
         <v>46352</v>
       </c>
-      <c r="L14" s="146"/>
-      <c r="M14" s="146"/>
+      <c r="L14" s="154"/>
+      <c r="M14" s="154"/>
       <c r="N14" s="78"/>
-      <c r="O14" s="141">
+      <c r="O14" s="152">
         <f ca="1">K14+1</f>
         <v>46353</v>
       </c>
-      <c r="P14" s="146"/>
-      <c r="Q14" s="146"/>
-      <c r="R14" s="146"/>
-      <c r="S14" s="146"/>
-      <c r="T14" s="146"/>
-      <c r="U14" s="146"/>
-      <c r="V14" s="142"/>
-      <c r="W14" s="141">
+      <c r="P14" s="154"/>
+      <c r="Q14" s="154"/>
+      <c r="R14" s="154"/>
+      <c r="S14" s="154"/>
+      <c r="T14" s="154"/>
+      <c r="U14" s="154"/>
+      <c r="V14" s="153"/>
+      <c r="W14" s="152">
         <f ca="1">O14+1</f>
         <v>46354</v>
       </c>
-      <c r="X14" s="146"/>
-      <c r="Y14" s="146"/>
-      <c r="Z14" s="146"/>
-      <c r="AA14" s="146"/>
-      <c r="AB14" s="146"/>
-      <c r="AC14" s="146"/>
-      <c r="AD14" s="142"/>
+      <c r="X14" s="154"/>
+      <c r="Y14" s="154"/>
+      <c r="Z14" s="154"/>
+      <c r="AA14" s="154"/>
+      <c r="AB14" s="154"/>
+      <c r="AC14" s="154"/>
+      <c r="AD14" s="153"/>
       <c r="AF14" s="4"/>
     </row>
-    <row r="15" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="42"/>
-      <c r="C15" s="119"/>
-      <c r="D15" s="120"/>
-      <c r="E15" s="119"/>
-      <c r="F15" s="120"/>
-      <c r="G15" s="119"/>
-      <c r="H15" s="120"/>
-      <c r="I15" s="119"/>
-      <c r="J15" s="120"/>
-      <c r="K15" s="119"/>
-      <c r="L15" s="147"/>
-      <c r="M15" s="147"/>
-      <c r="N15" s="120"/>
-      <c r="O15" s="119"/>
-      <c r="P15" s="147"/>
-      <c r="Q15" s="147"/>
-      <c r="R15" s="147"/>
-      <c r="S15" s="147"/>
-      <c r="T15" s="147"/>
-      <c r="U15" s="147"/>
-      <c r="V15" s="120"/>
-      <c r="W15" s="119"/>
-      <c r="X15" s="147"/>
-      <c r="Y15" s="147"/>
-      <c r="Z15" s="147"/>
-      <c r="AA15" s="147"/>
-      <c r="AB15" s="147"/>
-      <c r="AC15" s="147"/>
-      <c r="AD15" s="120"/>
+      <c r="C15" s="102"/>
+      <c r="D15" s="103"/>
+      <c r="E15" s="102"/>
+      <c r="F15" s="103"/>
+      <c r="G15" s="102"/>
+      <c r="H15" s="103"/>
+      <c r="I15" s="102"/>
+      <c r="J15" s="103"/>
+      <c r="K15" s="102"/>
+      <c r="L15" s="151"/>
+      <c r="M15" s="151"/>
+      <c r="N15" s="103"/>
+      <c r="O15" s="102"/>
+      <c r="P15" s="151"/>
+      <c r="Q15" s="151"/>
+      <c r="R15" s="151"/>
+      <c r="S15" s="151"/>
+      <c r="T15" s="151"/>
+      <c r="U15" s="151"/>
+      <c r="V15" s="103"/>
+      <c r="W15" s="102"/>
+      <c r="X15" s="151"/>
+      <c r="Y15" s="151"/>
+      <c r="Z15" s="151"/>
+      <c r="AA15" s="151"/>
+      <c r="AB15" s="151"/>
+      <c r="AC15" s="151"/>
+      <c r="AD15" s="103"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
-    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="42"/>
-      <c r="C16" s="116">
+      <c r="C16" s="91">
         <f ca="1">W14+1</f>
         <v>46355</v>
       </c>
-      <c r="D16" s="118"/>
+      <c r="D16" s="92"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
       <c r="H16" s="75"/>
-      <c r="I16" s="138"/>
-      <c r="J16" s="139"/>
+      <c r="I16" s="145"/>
+      <c r="J16" s="146"/>
       <c r="K16" s="66"/>
       <c r="L16" s="68"/>
       <c r="M16" s="68"/>
@@ -6015,103 +6114,102 @@
       <c r="AE16" s="7"/>
       <c r="AF16" s="42"/>
     </row>
-    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
-      <c r="C17" s="116"/>
-      <c r="D17" s="118"/>
-      <c r="E17" s="127">
+      <c r="C17" s="91"/>
+      <c r="D17" s="92"/>
+      <c r="E17" s="93">
         <f ca="1">C16+1</f>
         <v>46356</v>
       </c>
-      <c r="F17" s="128"/>
-      <c r="G17" s="127">
-        <f ca="1">E17+1</f>
-        <v>46357</v>
-      </c>
-      <c r="H17" s="128"/>
-      <c r="I17" s="127">
-        <f ca="1">G17+1</f>
-        <v>46358</v>
-      </c>
-      <c r="J17" s="128"/>
-      <c r="K17" s="127">
-        <f ca="1">I17+1</f>
-        <v>46359</v>
-      </c>
-      <c r="L17" s="129"/>
-      <c r="M17" s="129"/>
-      <c r="N17" s="128"/>
-      <c r="O17" s="127">
-        <f ca="1">K17+1</f>
-        <v>46360</v>
-      </c>
-      <c r="P17" s="129"/>
-      <c r="Q17" s="129"/>
-      <c r="R17" s="129"/>
-      <c r="S17" s="129"/>
-      <c r="T17" s="129"/>
-      <c r="U17" s="129"/>
-      <c r="V17" s="128"/>
-      <c r="W17" s="127">
-        <f ca="1">O17+1</f>
-        <v>46361</v>
-      </c>
-      <c r="X17" s="129"/>
-      <c r="Y17" s="129"/>
-      <c r="Z17" s="129"/>
-      <c r="AA17" s="129"/>
-      <c r="AB17" s="129"/>
-      <c r="AC17" s="129"/>
-      <c r="AD17" s="128"/>
+      <c r="F17" s="94"/>
+      <c r="G17" s="93">
+        <v>1</v>
+      </c>
+      <c r="H17" s="94"/>
+      <c r="I17" s="93">
+        <f>G17+1</f>
+        <v>2</v>
+      </c>
+      <c r="J17" s="94"/>
+      <c r="K17" s="93">
+        <f>I17+1</f>
+        <v>3</v>
+      </c>
+      <c r="L17" s="95"/>
+      <c r="M17" s="95"/>
+      <c r="N17" s="94"/>
+      <c r="O17" s="93">
+        <f>K17+1</f>
+        <v>4</v>
+      </c>
+      <c r="P17" s="95"/>
+      <c r="Q17" s="95"/>
+      <c r="R17" s="95"/>
+      <c r="S17" s="95"/>
+      <c r="T17" s="95"/>
+      <c r="U17" s="95"/>
+      <c r="V17" s="94"/>
+      <c r="W17" s="93">
+        <f>O17+1</f>
+        <v>5</v>
+      </c>
+      <c r="X17" s="95"/>
+      <c r="Y17" s="95"/>
+      <c r="Z17" s="95"/>
+      <c r="AA17" s="95"/>
+      <c r="AB17" s="95"/>
+      <c r="AC17" s="95"/>
+      <c r="AD17" s="94"/>
       <c r="AF17" s="4"/>
     </row>
-    <row r="18" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="42"/>
-      <c r="C18" s="111"/>
-      <c r="D18" s="113"/>
-      <c r="E18" s="111"/>
-      <c r="F18" s="113"/>
-      <c r="G18" s="111"/>
-      <c r="H18" s="113"/>
-      <c r="I18" s="111"/>
-      <c r="J18" s="113"/>
-      <c r="K18" s="111"/>
-      <c r="L18" s="112"/>
-      <c r="M18" s="112"/>
-      <c r="N18" s="113"/>
-      <c r="O18" s="111"/>
-      <c r="P18" s="112"/>
-      <c r="Q18" s="112"/>
-      <c r="R18" s="112"/>
-      <c r="S18" s="112"/>
-      <c r="T18" s="112"/>
-      <c r="U18" s="112"/>
-      <c r="V18" s="113"/>
-      <c r="W18" s="111"/>
-      <c r="X18" s="112"/>
-      <c r="Y18" s="112"/>
-      <c r="Z18" s="112"/>
-      <c r="AA18" s="112"/>
-      <c r="AB18" s="112"/>
-      <c r="AC18" s="112"/>
-      <c r="AD18" s="113"/>
+      <c r="C18" s="96"/>
+      <c r="D18" s="97"/>
+      <c r="E18" s="96"/>
+      <c r="F18" s="97"/>
+      <c r="G18" s="96"/>
+      <c r="H18" s="97"/>
+      <c r="I18" s="96"/>
+      <c r="J18" s="97"/>
+      <c r="K18" s="96"/>
+      <c r="L18" s="141"/>
+      <c r="M18" s="141"/>
+      <c r="N18" s="97"/>
+      <c r="O18" s="96"/>
+      <c r="P18" s="141"/>
+      <c r="Q18" s="141"/>
+      <c r="R18" s="141"/>
+      <c r="S18" s="141"/>
+      <c r="T18" s="141"/>
+      <c r="U18" s="141"/>
+      <c r="V18" s="97"/>
+      <c r="W18" s="96"/>
+      <c r="X18" s="141"/>
+      <c r="Y18" s="141"/>
+      <c r="Z18" s="141"/>
+      <c r="AA18" s="141"/>
+      <c r="AB18" s="141"/>
+      <c r="AC18" s="141"/>
+      <c r="AD18" s="97"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
-    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="42"/>
-      <c r="C19" s="116">
-        <f ca="1">W17+1</f>
-        <v>46362</v>
-      </c>
-      <c r="D19" s="118"/>
+      <c r="C19" s="91">
+        <f>W17+1</f>
+        <v>6</v>
+      </c>
+      <c r="D19" s="92"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
       <c r="H19" s="75"/>
-      <c r="I19" s="138"/>
-      <c r="J19" s="139"/>
+      <c r="I19" s="145"/>
+      <c r="J19" s="146"/>
       <c r="K19" s="66"/>
       <c r="L19" s="68"/>
       <c r="M19" s="68"/>
@@ -6135,91 +6233,91 @@
       <c r="AE19" s="7"/>
       <c r="AF19" s="42"/>
     </row>
-    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
-      <c r="C20" s="116"/>
-      <c r="D20" s="118"/>
-      <c r="E20" s="127">
-        <f ca="1">C19+1</f>
-        <v>46363</v>
-      </c>
-      <c r="F20" s="128"/>
-      <c r="G20" s="127">
-        <f ca="1">E20+1</f>
-        <v>46364</v>
-      </c>
-      <c r="H20" s="128"/>
-      <c r="I20" s="127">
-        <f ca="1">G20+1</f>
-        <v>46365</v>
-      </c>
-      <c r="J20" s="128"/>
-      <c r="K20" s="127">
-        <f ca="1">I20+1</f>
-        <v>46366</v>
-      </c>
-      <c r="L20" s="129"/>
-      <c r="M20" s="129"/>
-      <c r="N20" s="128"/>
-      <c r="O20" s="127">
-        <f ca="1">K20+1</f>
-        <v>46367</v>
-      </c>
-      <c r="P20" s="129"/>
-      <c r="Q20" s="129"/>
-      <c r="R20" s="129"/>
-      <c r="S20" s="129"/>
-      <c r="T20" s="129"/>
-      <c r="U20" s="129"/>
-      <c r="V20" s="128"/>
-      <c r="W20" s="127">
-        <f ca="1">O20+1</f>
-        <v>46368</v>
-      </c>
-      <c r="X20" s="129"/>
-      <c r="Y20" s="129"/>
-      <c r="Z20" s="129"/>
-      <c r="AA20" s="129"/>
-      <c r="AB20" s="129"/>
-      <c r="AC20" s="129"/>
-      <c r="AD20" s="128"/>
+      <c r="C20" s="91"/>
+      <c r="D20" s="92"/>
+      <c r="E20" s="93">
+        <f>C19+1</f>
+        <v>7</v>
+      </c>
+      <c r="F20" s="94"/>
+      <c r="G20" s="93">
+        <f>E20+1</f>
+        <v>8</v>
+      </c>
+      <c r="H20" s="94"/>
+      <c r="I20" s="93">
+        <f>G20+1</f>
+        <v>9</v>
+      </c>
+      <c r="J20" s="94"/>
+      <c r="K20" s="93">
+        <f>I20+1</f>
+        <v>10</v>
+      </c>
+      <c r="L20" s="95"/>
+      <c r="M20" s="95"/>
+      <c r="N20" s="94"/>
+      <c r="O20" s="93">
+        <f>K20+1</f>
+        <v>11</v>
+      </c>
+      <c r="P20" s="95"/>
+      <c r="Q20" s="95"/>
+      <c r="R20" s="95"/>
+      <c r="S20" s="95"/>
+      <c r="T20" s="95"/>
+      <c r="U20" s="95"/>
+      <c r="V20" s="94"/>
+      <c r="W20" s="93">
+        <f>O20+1</f>
+        <v>12</v>
+      </c>
+      <c r="X20" s="95"/>
+      <c r="Y20" s="95"/>
+      <c r="Z20" s="95"/>
+      <c r="AA20" s="95"/>
+      <c r="AB20" s="95"/>
+      <c r="AC20" s="95"/>
+      <c r="AD20" s="94"/>
       <c r="AF20" s="4"/>
     </row>
-    <row r="21" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="42"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="111"/>
-      <c r="H21" s="113"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="113"/>
-      <c r="K21" s="111"/>
-      <c r="L21" s="112"/>
-      <c r="M21" s="112"/>
-      <c r="N21" s="113"/>
-      <c r="O21" s="111"/>
-      <c r="P21" s="112"/>
-      <c r="Q21" s="112"/>
-      <c r="R21" s="112"/>
-      <c r="S21" s="112"/>
-      <c r="T21" s="112"/>
-      <c r="U21" s="112"/>
-      <c r="V21" s="113"/>
-      <c r="W21" s="111"/>
-      <c r="X21" s="112"/>
-      <c r="Y21" s="112"/>
-      <c r="Z21" s="112"/>
-      <c r="AA21" s="112"/>
-      <c r="AB21" s="112"/>
-      <c r="AC21" s="112"/>
-      <c r="AD21" s="113"/>
+      <c r="C21" s="96"/>
+      <c r="D21" s="97"/>
+      <c r="E21" s="96"/>
+      <c r="F21" s="97"/>
+      <c r="G21" s="96"/>
+      <c r="H21" s="97"/>
+      <c r="I21" s="96"/>
+      <c r="J21" s="97"/>
+      <c r="K21" s="96"/>
+      <c r="L21" s="141"/>
+      <c r="M21" s="141"/>
+      <c r="N21" s="97"/>
+      <c r="O21" s="96"/>
+      <c r="P21" s="141"/>
+      <c r="Q21" s="141"/>
+      <c r="R21" s="141"/>
+      <c r="S21" s="141"/>
+      <c r="T21" s="141"/>
+      <c r="U21" s="141"/>
+      <c r="V21" s="97"/>
+      <c r="W21" s="96"/>
+      <c r="X21" s="141"/>
+      <c r="Y21" s="141"/>
+      <c r="Z21" s="141"/>
+      <c r="AA21" s="141"/>
+      <c r="AB21" s="141"/>
+      <c r="AC21" s="141"/>
+      <c r="AD21" s="97"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
     </row>
-    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52"/>
@@ -6251,7 +6349,7 @@
       <c r="AD22" s="55"/>
       <c r="AF22" s="4"/>
     </row>
-    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="56"/>
@@ -6285,61 +6383,61 @@
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
     </row>
-    <row r="24" spans="1:42" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:42" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="M24" s="1"/>
       <c r="AF24" s="1"/>
     </row>
-    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="C25" s="132" t="s">
+      <c r="C25" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="132"/>
-      <c r="E25" s="132"/>
-      <c r="F25" s="132"/>
-      <c r="G25" s="132"/>
-      <c r="H25" s="132"/>
-      <c r="I25" s="132"/>
-      <c r="J25" s="132"/>
-      <c r="K25" s="132"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="86"/>
+      <c r="H25" s="86"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="86"/>
+      <c r="K25" s="86"/>
       <c r="L25" s="60"/>
       <c r="M25" s="1"/>
-      <c r="O25" s="133">
+      <c r="O25" s="87">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)-1,1)</f>
         <v>46296</v>
       </c>
-      <c r="P25" s="133"/>
-      <c r="Q25" s="133"/>
-      <c r="R25" s="133"/>
-      <c r="S25" s="133"/>
-      <c r="T25" s="133"/>
-      <c r="U25" s="133"/>
+      <c r="P25" s="87"/>
+      <c r="Q25" s="87"/>
+      <c r="R25" s="87"/>
+      <c r="S25" s="87"/>
+      <c r="T25" s="87"/>
+      <c r="U25" s="87"/>
       <c r="V25" s="61"/>
       <c r="W25" s="61"/>
-      <c r="X25" s="133">
+      <c r="X25" s="87">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)+1,1)</f>
         <v>46357</v>
       </c>
-      <c r="Y25" s="133"/>
-      <c r="Z25" s="133"/>
-      <c r="AA25" s="133"/>
-      <c r="AB25" s="133"/>
-      <c r="AC25" s="133"/>
-      <c r="AD25" s="133"/>
+      <c r="Y25" s="87"/>
+      <c r="Z25" s="87"/>
+      <c r="AA25" s="87"/>
+      <c r="AB25" s="87"/>
+      <c r="AC25" s="87"/>
+      <c r="AD25" s="87"/>
       <c r="AF25" s="1"/>
     </row>
-    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="C26" s="132"/>
-      <c r="D26" s="132"/>
-      <c r="E26" s="132"/>
-      <c r="F26" s="132"/>
-      <c r="G26" s="132"/>
-      <c r="H26" s="132"/>
-      <c r="I26" s="132"/>
-      <c r="J26" s="132"/>
-      <c r="K26" s="132"/>
+      <c r="C26" s="86"/>
+      <c r="D26" s="86"/>
+      <c r="E26" s="86"/>
+      <c r="F26" s="86"/>
+      <c r="G26" s="86"/>
+      <c r="H26" s="86"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="K26" s="86"/>
       <c r="L26" s="60"/>
       <c r="M26" s="1"/>
       <c r="O26" s="62" t="str">
@@ -6402,17 +6500,17 @@
       </c>
       <c r="AF26" s="1"/>
     </row>
-    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="C27" s="131"/>
-      <c r="D27" s="131"/>
-      <c r="E27" s="131"/>
-      <c r="F27" s="131"/>
-      <c r="G27" s="131"/>
-      <c r="H27" s="131"/>
-      <c r="I27" s="131"/>
-      <c r="J27" s="131"/>
-      <c r="K27" s="131"/>
+      <c r="C27" s="88"/>
+      <c r="D27" s="88"/>
+      <c r="E27" s="88"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="88"/>
+      <c r="H27" s="88"/>
+      <c r="I27" s="88"/>
+      <c r="J27" s="88"/>
+      <c r="K27" s="88"/>
       <c r="M27" s="1"/>
       <c r="O27" s="64" t="str">
         <f t="shared" ref="O27:U32" ca="1" si="0">IF(MONTH($O$25)&lt;&gt;MONTH($O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1)),"",$O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1))</f>
@@ -6474,17 +6572,17 @@
       </c>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="C28" s="130"/>
-      <c r="D28" s="130"/>
-      <c r="E28" s="130"/>
-      <c r="F28" s="130"/>
-      <c r="G28" s="130"/>
-      <c r="H28" s="130"/>
-      <c r="I28" s="130"/>
-      <c r="J28" s="130"/>
-      <c r="K28" s="130"/>
+      <c r="C28" s="89"/>
+      <c r="D28" s="89"/>
+      <c r="E28" s="89"/>
+      <c r="F28" s="89"/>
+      <c r="G28" s="89"/>
+      <c r="H28" s="89"/>
+      <c r="I28" s="89"/>
+      <c r="J28" s="89"/>
+      <c r="K28" s="89"/>
       <c r="M28" s="1"/>
       <c r="O28" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6546,17 +6644,17 @@
       </c>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="C29" s="131"/>
-      <c r="D29" s="131"/>
-      <c r="E29" s="131"/>
-      <c r="F29" s="131"/>
-      <c r="G29" s="131"/>
-      <c r="H29" s="131"/>
-      <c r="I29" s="131"/>
-      <c r="J29" s="131"/>
-      <c r="K29" s="131"/>
+      <c r="C29" s="88"/>
+      <c r="D29" s="88"/>
+      <c r="E29" s="88"/>
+      <c r="F29" s="88"/>
+      <c r="G29" s="88"/>
+      <c r="H29" s="88"/>
+      <c r="I29" s="88"/>
+      <c r="J29" s="88"/>
+      <c r="K29" s="88"/>
       <c r="M29" s="1"/>
       <c r="O29" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6618,17 +6716,17 @@
       </c>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="C30" s="130"/>
-      <c r="D30" s="130"/>
-      <c r="E30" s="130"/>
-      <c r="F30" s="130"/>
-      <c r="G30" s="130"/>
-      <c r="H30" s="130"/>
-      <c r="I30" s="130"/>
-      <c r="J30" s="130"/>
-      <c r="K30" s="130"/>
+      <c r="C30" s="89"/>
+      <c r="D30" s="89"/>
+      <c r="E30" s="89"/>
+      <c r="F30" s="89"/>
+      <c r="G30" s="89"/>
+      <c r="H30" s="89"/>
+      <c r="I30" s="89"/>
+      <c r="J30" s="89"/>
+      <c r="K30" s="89"/>
       <c r="M30" s="1"/>
       <c r="O30" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6690,17 +6788,17 @@
       </c>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="C31" s="131"/>
-      <c r="D31" s="131"/>
-      <c r="E31" s="131"/>
-      <c r="F31" s="131"/>
-      <c r="G31" s="131"/>
-      <c r="H31" s="131"/>
-      <c r="I31" s="131"/>
-      <c r="J31" s="131"/>
-      <c r="K31" s="131"/>
+      <c r="C31" s="88"/>
+      <c r="D31" s="88"/>
+      <c r="E31" s="88"/>
+      <c r="F31" s="88"/>
+      <c r="G31" s="88"/>
+      <c r="H31" s="88"/>
+      <c r="I31" s="88"/>
+      <c r="J31" s="88"/>
+      <c r="K31" s="88"/>
       <c r="M31" s="1"/>
       <c r="O31" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6762,7 +6860,7 @@
       </c>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="C32" s="77"/>
       <c r="D32" s="77"/>
@@ -6834,12 +6932,12 @@
       </c>
       <c r="AF32" s="1"/>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="M33" s="1"/>
       <c r="AF33" s="1"/>
     </row>
-    <row r="34" spans="1:32" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:32" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -6873,130 +6971,100 @@
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
     </row>
-    <row r="37" spans="1:32" ht="12.9" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="38" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D38" s="83" t="s">
-        <v>30</v>
-      </c>
-      <c r="E38" s="84"/>
-      <c r="F38" s="85"/>
-      <c r="G38" s="89">
+    <row r="37" spans="1:32" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="38" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D38" s="113" t="s">
+        <v>25</v>
+      </c>
+      <c r="E38" s="114"/>
+      <c r="F38" s="115"/>
+      <c r="G38" s="119">
         <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
         <v>5</v>
       </c>
-      <c r="H38" s="90"/>
-      <c r="I38" s="83" t="s">
-        <v>33</v>
-      </c>
-      <c r="J38" s="93"/>
-      <c r="K38" s="95" t="s">
-        <v>31</v>
-      </c>
-      <c r="L38" s="96"/>
-      <c r="M38" s="99">
+      <c r="H38" s="120"/>
+      <c r="I38" s="113" t="s">
+        <v>28</v>
+      </c>
+      <c r="J38" s="123"/>
+      <c r="K38" s="125" t="s">
+        <v>26</v>
+      </c>
+      <c r="L38" s="126"/>
+      <c r="M38" s="129">
         <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
         <v>5.9999999999999973</v>
       </c>
-      <c r="N38" s="100"/>
-      <c r="O38" s="100"/>
-      <c r="P38" s="100"/>
-      <c r="Q38" s="100"/>
-      <c r="R38" s="101"/>
-      <c r="S38" s="105" t="s">
-        <v>32</v>
-      </c>
-      <c r="T38" s="106"/>
-      <c r="U38" s="106"/>
-      <c r="V38" s="106"/>
-      <c r="W38" s="106"/>
-      <c r="X38" s="107"/>
-    </row>
-    <row r="39" spans="1:32" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D39" s="86"/>
-      <c r="E39" s="87"/>
-      <c r="F39" s="88"/>
-      <c r="G39" s="91"/>
-      <c r="H39" s="92"/>
-      <c r="I39" s="86"/>
-      <c r="J39" s="94"/>
-      <c r="K39" s="97"/>
-      <c r="L39" s="98"/>
-      <c r="M39" s="102"/>
-      <c r="N39" s="103"/>
-      <c r="O39" s="103"/>
-      <c r="P39" s="103"/>
-      <c r="Q39" s="103"/>
-      <c r="R39" s="104"/>
-      <c r="S39" s="108"/>
-      <c r="T39" s="109"/>
-      <c r="U39" s="109"/>
-      <c r="V39" s="109"/>
-      <c r="W39" s="109"/>
-      <c r="X39" s="110"/>
+      <c r="N38" s="130"/>
+      <c r="O38" s="130"/>
+      <c r="P38" s="130"/>
+      <c r="Q38" s="130"/>
+      <c r="R38" s="131"/>
+      <c r="S38" s="135" t="s">
+        <v>27</v>
+      </c>
+      <c r="T38" s="136"/>
+      <c r="U38" s="136"/>
+      <c r="V38" s="136"/>
+      <c r="W38" s="136"/>
+      <c r="X38" s="137"/>
+    </row>
+    <row r="39" spans="1:32" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D39" s="116"/>
+      <c r="E39" s="117"/>
+      <c r="F39" s="118"/>
+      <c r="G39" s="121"/>
+      <c r="H39" s="122"/>
+      <c r="I39" s="116"/>
+      <c r="J39" s="124"/>
+      <c r="K39" s="127"/>
+      <c r="L39" s="128"/>
+      <c r="M39" s="132"/>
+      <c r="N39" s="133"/>
+      <c r="O39" s="133"/>
+      <c r="P39" s="133"/>
+      <c r="Q39" s="133"/>
+      <c r="R39" s="134"/>
+      <c r="S39" s="138"/>
+      <c r="T39" s="139"/>
+      <c r="U39" s="139"/>
+      <c r="V39" s="139"/>
+      <c r="W39" s="139"/>
+      <c r="X39" s="140"/>
     </row>
   </sheetData>
   <mergeCells count="112">
-    <mergeCell ref="K18:N18"/>
-    <mergeCell ref="W18:AD18"/>
-    <mergeCell ref="C25:K26"/>
-    <mergeCell ref="O25:U25"/>
-    <mergeCell ref="X25:AD25"/>
-    <mergeCell ref="C27:K27"/>
-    <mergeCell ref="C28:K29"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="O18:V18"/>
-    <mergeCell ref="C19:D20"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:N20"/>
-    <mergeCell ref="W15:AD15"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="O17:V17"/>
-    <mergeCell ref="W17:AD17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="O15:V15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="W12:AD12"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="O14:V14"/>
-    <mergeCell ref="W14:AD14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="O12:V12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="W9:AD9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="O11:V11"/>
-    <mergeCell ref="W11:AD11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:V9"/>
-    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="D38:F39"/>
+    <mergeCell ref="G38:H39"/>
+    <mergeCell ref="I38:J39"/>
+    <mergeCell ref="K38:L39"/>
+    <mergeCell ref="M38:R39"/>
+    <mergeCell ref="S38:X39"/>
+    <mergeCell ref="C30:K31"/>
+    <mergeCell ref="O20:V20"/>
+    <mergeCell ref="W20:AD20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:N21"/>
+    <mergeCell ref="O21:V21"/>
+    <mergeCell ref="W21:AD21"/>
+    <mergeCell ref="C2:AD2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="W5:AD5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="O5:V5"/>
     <mergeCell ref="K6:N6"/>
     <mergeCell ref="C7:D8"/>
     <mergeCell ref="E7:F7"/>
@@ -7017,37 +7085,67 @@
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="O6:V6"/>
     <mergeCell ref="W6:AD6"/>
-    <mergeCell ref="C2:AD2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="W5:AD5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="O5:V5"/>
-    <mergeCell ref="D38:F39"/>
-    <mergeCell ref="G38:H39"/>
-    <mergeCell ref="I38:J39"/>
-    <mergeCell ref="K38:L39"/>
-    <mergeCell ref="M38:R39"/>
-    <mergeCell ref="S38:X39"/>
-    <mergeCell ref="C30:K31"/>
-    <mergeCell ref="O20:V20"/>
-    <mergeCell ref="W20:AD20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:N21"/>
-    <mergeCell ref="O21:V21"/>
-    <mergeCell ref="W21:AD21"/>
+    <mergeCell ref="W9:AD9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="O11:V11"/>
+    <mergeCell ref="W11:AD11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:V9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="W12:AD12"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O14:V14"/>
+    <mergeCell ref="W14:AD14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="O12:V12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="W15:AD15"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="O17:V17"/>
+    <mergeCell ref="W17:AD17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="O15:V15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="K18:N18"/>
+    <mergeCell ref="W18:AD18"/>
+    <mergeCell ref="C25:K26"/>
+    <mergeCell ref="O25:U25"/>
+    <mergeCell ref="X25:AD25"/>
+    <mergeCell ref="C27:K27"/>
+    <mergeCell ref="C28:K29"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="O18:V18"/>
+    <mergeCell ref="C19:D20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:N20"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 E5 G5 I5 K5:L5 O5 W5 C7 E8 G8 I8 K8:L8 O8 W8 C10 E11 G11 I11 K11:L11 O11 W11 C13 E14 G14 I14 K14:L14 O14 W14 C16 E17 G17 I17 K17 O17 W17">
     <cfRule type="expression" dxfId="3" priority="3">
@@ -7081,6 +7179,26 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="30" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cec0622158e8f13124e9e8fd4de31bd1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3b52f30ab005d15df08657af532e6e38" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -7398,26 +7516,6 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -7428,6 +7526,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B201CC6-7A0A-429C-B445-7EDA1CF4A1D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{652EDDE9-C911-407A-9906-647D87C81E69}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7448,18 +7558,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B201CC6-7A0A-429C-B445-7EDA1CF4A1D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F0D3479-5903-425F-9669-62B4E7216DE9}">
   <ds:schemaRefs>

--- a/Group_milestones.xlsx
+++ b/Group_milestones.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{916827F6-E579-45A9-A0BF-AC19F3C06EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{916827F6-E579-45A9-A0BF-AC19F3C06EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EBFEC64-9B58-4A68-AE17-EA29B3CD7733}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-16320" windowWidth="29040" windowHeight="15720" tabRatio="824" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="824" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="52" r:id="rId1"/>
@@ -167,9 +167,6 @@
     <t>MCTR1: carriage v2 test</t>
   </si>
   <si>
-    <t>MCTR1: Enclosure v1 test, ICD complete with- MCTR2?</t>
-  </si>
-  <si>
     <t>Shared milestone calendar sodat ons kan sien wanneer wie wat gedoen wil he, en sodat ons n volle prentjie het</t>
   </si>
   <si>
@@ -198,9 +195,6 @@
   </si>
   <si>
     <t>MCTR1: Carriage v2 build</t>
-  </si>
-  <si>
-    <t>MCTR1: ICD complete with- REII</t>
   </si>
   <si>
     <t>EEII1: ICD complete with REII and MCTR2</t>
@@ -263,9 +257,6 @@
     <t>EERI 321</t>
   </si>
   <si>
-    <t>EEII 321</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">EERI 325             </t>
     </r>
@@ -277,6 +268,26 @@
         <scheme val="minor"/>
       </rPr>
       <t>Group: Integration successful</t>
+    </r>
+  </si>
+  <si>
+    <t>MCTR1: Enclosure v1 test,  ICD complete with- REII, ICD complete with- MCTR2?</t>
+  </si>
+  <si>
+    <t>Group: Finish performance test reports and Individual portfolios</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">EEII 321                 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Group: Finalize all ICDs</t>
     </r>
   </si>
 </sst>
@@ -782,7 +793,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="160">
+  <cellXfs count="158">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1010,6 +1021,162 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -1019,182 +1186,29 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="166" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="39" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1205,40 +1219,31 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -1612,7 +1617,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R15"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.3" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
     <col min="1" max="4" width="5.5546875" style="3" customWidth="1"/>
     <col min="5" max="9" width="10.5546875" style="3" customWidth="1"/>
@@ -1624,7 +1629,7 @@
     <col min="19" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1644,7 +1649,7 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
     </row>
-    <row r="2" spans="1:18" s="7" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" s="7" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4"/>
       <c r="B2" s="5"/>
       <c r="C2" s="73" t="s">
@@ -1666,7 +1671,7 @@
       <c r="Q2" s="6"/>
       <c r="R2" s="4"/>
     </row>
-    <row r="3" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="3" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="2.15">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="8"/>
@@ -1686,7 +1691,7 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -1708,7 +1713,7 @@
       <c r="Q4" s="142"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1"/>
       <c r="B5" s="11"/>
       <c r="C5" s="13" t="s">
@@ -1732,7 +1737,7 @@
       <c r="Q5" s="142"/>
       <c r="R5" s="1"/>
     </row>
-    <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1"/>
       <c r="B6" s="11"/>
       <c r="C6" s="17"/>
@@ -1752,7 +1757,7 @@
       <c r="Q6" s="142"/>
       <c r="R6" s="1"/>
     </row>
-    <row r="7" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1"/>
       <c r="B7" s="11"/>
       <c r="C7" s="13" t="s">
@@ -1776,7 +1781,7 @@
       <c r="Q7" s="11"/>
       <c r="R7" s="1"/>
     </row>
-    <row r="8" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="1"/>
       <c r="B8" s="11"/>
       <c r="C8" s="17"/>
@@ -1800,7 +1805,7 @@
       </c>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="1"/>
       <c r="B9" s="11"/>
       <c r="C9" s="13" t="s">
@@ -1824,7 +1829,7 @@
       <c r="Q9" s="11"/>
       <c r="R9" s="1"/>
     </row>
-    <row r="10" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="1"/>
       <c r="B10" s="11"/>
       <c r="C10" s="24"/>
@@ -1850,7 +1855,7 @@
       <c r="Q10" s="18"/>
       <c r="R10" s="1"/>
     </row>
-    <row r="11" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1"/>
       <c r="B11" s="11"/>
       <c r="C11" s="24"/>
@@ -1870,7 +1875,7 @@
       <c r="Q11" s="18"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="1"/>
       <c r="B12" s="11"/>
       <c r="C12" s="13" t="s">
@@ -1894,7 +1899,7 @@
       <c r="Q12" s="18"/>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="1"/>
       <c r="B13" s="11"/>
       <c r="C13" s="25"/>
@@ -1916,7 +1921,7 @@
       <c r="Q13" s="18"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1"/>
       <c r="B14" s="11"/>
       <c r="C14" s="18"/>
@@ -1936,7 +1941,7 @@
       <c r="Q14" s="18"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1971,7 +1976,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AP40"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="12.6" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="3" width="5.5546875" style="3" customWidth="1"/>
     <col min="4" max="4" width="15.5546875" style="3" customWidth="1"/>
@@ -1989,7 +1994,7 @@
     <col min="35" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2023,42 +2028,42 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="2.15">
       <c r="A2" s="29"/>
-      <c r="C2" s="111">
+      <c r="C2" s="116">
         <f ca="1">DATE(About!P8,9,1)</f>
         <v>46266</v>
       </c>
-      <c r="D2" s="111"/>
-      <c r="E2" s="111"/>
-      <c r="F2" s="111"/>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="111"/>
-      <c r="J2" s="111"/>
-      <c r="K2" s="111"/>
-      <c r="L2" s="111"/>
-      <c r="M2" s="111"/>
-      <c r="N2" s="111"/>
-      <c r="O2" s="111"/>
-      <c r="P2" s="111"/>
-      <c r="Q2" s="111"/>
-      <c r="R2" s="111"/>
-      <c r="S2" s="111"/>
-      <c r="T2" s="111"/>
-      <c r="U2" s="111"/>
-      <c r="V2" s="111"/>
-      <c r="W2" s="111"/>
-      <c r="X2" s="111"/>
-      <c r="Y2" s="111"/>
-      <c r="Z2" s="111"/>
-      <c r="AA2" s="111"/>
-      <c r="AB2" s="111"/>
-      <c r="AC2" s="111"/>
-      <c r="AD2" s="111"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="116"/>
+      <c r="P2" s="116"/>
+      <c r="Q2" s="116"/>
+      <c r="R2" s="116"/>
+      <c r="S2" s="116"/>
+      <c r="T2" s="116"/>
+      <c r="U2" s="116"/>
+      <c r="V2" s="116"/>
+      <c r="W2" s="116"/>
+      <c r="X2" s="116"/>
+      <c r="Y2" s="116"/>
+      <c r="Z2" s="116"/>
+      <c r="AA2" s="116"/>
+      <c r="AB2" s="116"/>
+      <c r="AC2" s="116"/>
+      <c r="AD2" s="116"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="2.15">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -2078,278 +2083,278 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A4" s="35"/>
-      <c r="C4" s="112">
+      <c r="C4" s="117">
         <f ca="1">C5</f>
         <v>46264</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112">
+      <c r="D4" s="117"/>
+      <c r="E4" s="117">
         <f ca="1">E5</f>
         <v>46265</v>
       </c>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112">
+      <c r="F4" s="117"/>
+      <c r="G4" s="117">
         <f ca="1">G5</f>
         <v>46266</v>
       </c>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112">
+      <c r="H4" s="117"/>
+      <c r="I4" s="117">
         <f ca="1">I5</f>
         <v>46267</v>
       </c>
-      <c r="J4" s="112"/>
-      <c r="K4" s="112">
+      <c r="J4" s="117"/>
+      <c r="K4" s="117">
         <f ca="1">K5</f>
         <v>46268</v>
       </c>
-      <c r="L4" s="112"/>
-      <c r="M4" s="112"/>
+      <c r="L4" s="117"/>
+      <c r="M4" s="117"/>
       <c r="N4" s="37"/>
-      <c r="O4" s="112">
+      <c r="O4" s="117">
         <f ca="1">O5</f>
         <v>46269</v>
       </c>
-      <c r="P4" s="112"/>
-      <c r="Q4" s="112"/>
-      <c r="R4" s="112"/>
-      <c r="S4" s="112"/>
-      <c r="T4" s="112"/>
-      <c r="U4" s="112"/>
-      <c r="V4" s="112"/>
-      <c r="W4" s="112">
+      <c r="P4" s="117"/>
+      <c r="Q4" s="117"/>
+      <c r="R4" s="117"/>
+      <c r="S4" s="117"/>
+      <c r="T4" s="117"/>
+      <c r="U4" s="117"/>
+      <c r="V4" s="117"/>
+      <c r="W4" s="117">
         <f ca="1">W5</f>
         <v>46270</v>
       </c>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="112"/>
-      <c r="Z4" s="112"/>
-      <c r="AA4" s="112"/>
-      <c r="AB4" s="112"/>
-      <c r="AC4" s="112"/>
-      <c r="AD4" s="112"/>
+      <c r="X4" s="117"/>
+      <c r="Y4" s="117"/>
+      <c r="Z4" s="117"/>
+      <c r="AA4" s="117"/>
+      <c r="AB4" s="117"/>
+      <c r="AC4" s="117"/>
+      <c r="AD4" s="117"/>
       <c r="AF4" s="38"/>
       <c r="AG4" s="39"/>
       <c r="AH4" s="39"/>
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1"/>
-      <c r="C5" s="91">
+      <c r="C5" s="118">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46264</v>
       </c>
-      <c r="D5" s="92"/>
-      <c r="E5" s="91">
+      <c r="D5" s="120"/>
+      <c r="E5" s="118">
         <f ca="1">C5+1</f>
         <v>46265</v>
       </c>
-      <c r="F5" s="92"/>
-      <c r="G5" s="91">
+      <c r="F5" s="120"/>
+      <c r="G5" s="118">
         <f ca="1">E5+1</f>
         <v>46266</v>
       </c>
-      <c r="H5" s="92"/>
-      <c r="I5" s="91">
+      <c r="H5" s="120"/>
+      <c r="I5" s="118">
         <f ca="1">G5+1</f>
         <v>46267</v>
       </c>
-      <c r="J5" s="92"/>
-      <c r="K5" s="91">
+      <c r="J5" s="120"/>
+      <c r="K5" s="118">
         <f ca="1">I5+1</f>
         <v>46268</v>
       </c>
-      <c r="L5" s="110"/>
-      <c r="M5" s="110"/>
+      <c r="L5" s="119"/>
+      <c r="M5" s="119"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="91">
+      <c r="O5" s="118">
         <f ca="1">K5+1</f>
         <v>46269</v>
       </c>
-      <c r="P5" s="110"/>
-      <c r="Q5" s="110"/>
-      <c r="R5" s="110"/>
-      <c r="S5" s="110"/>
-      <c r="T5" s="110"/>
-      <c r="U5" s="110"/>
-      <c r="V5" s="92"/>
-      <c r="W5" s="91">
+      <c r="P5" s="119"/>
+      <c r="Q5" s="119"/>
+      <c r="R5" s="119"/>
+      <c r="S5" s="119"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="120"/>
+      <c r="W5" s="118">
         <f ca="1">O5+1</f>
         <v>46270</v>
       </c>
-      <c r="X5" s="110"/>
-      <c r="Y5" s="110"/>
-      <c r="Z5" s="110"/>
-      <c r="AA5" s="110"/>
-      <c r="AB5" s="110"/>
-      <c r="AC5" s="110"/>
-      <c r="AD5" s="92"/>
+      <c r="X5" s="119"/>
+      <c r="Y5" s="119"/>
+      <c r="Z5" s="119"/>
+      <c r="AA5" s="119"/>
+      <c r="AB5" s="119"/>
+      <c r="AC5" s="119"/>
+      <c r="AD5" s="120"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
       <c r="AI5" s="41"/>
       <c r="AJ5" s="41"/>
     </row>
-    <row r="6" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="42"/>
-      <c r="C6" s="96"/>
-      <c r="D6" s="97"/>
-      <c r="E6" s="96"/>
-      <c r="F6" s="97"/>
-      <c r="G6" s="148"/>
-      <c r="H6" s="149"/>
-      <c r="I6" s="148"/>
-      <c r="J6" s="149"/>
-      <c r="K6" s="148"/>
-      <c r="L6" s="150"/>
-      <c r="M6" s="150"/>
-      <c r="N6" s="149"/>
-      <c r="O6" s="148"/>
-      <c r="P6" s="150"/>
-      <c r="Q6" s="150"/>
-      <c r="R6" s="150"/>
-      <c r="S6" s="150"/>
-      <c r="T6" s="150"/>
-      <c r="U6" s="150"/>
-      <c r="V6" s="149"/>
-      <c r="W6" s="148"/>
-      <c r="X6" s="150"/>
-      <c r="Y6" s="150"/>
-      <c r="Z6" s="150"/>
-      <c r="AA6" s="150"/>
-      <c r="AB6" s="150"/>
-      <c r="AC6" s="150"/>
-      <c r="AD6" s="149"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="111"/>
+      <c r="F6" s="113"/>
+      <c r="G6" s="143"/>
+      <c r="H6" s="144"/>
+      <c r="I6" s="143"/>
+      <c r="J6" s="144"/>
+      <c r="K6" s="143"/>
+      <c r="L6" s="145"/>
+      <c r="M6" s="145"/>
+      <c r="N6" s="144"/>
+      <c r="O6" s="143"/>
+      <c r="P6" s="145"/>
+      <c r="Q6" s="145"/>
+      <c r="R6" s="145"/>
+      <c r="S6" s="145"/>
+      <c r="T6" s="145"/>
+      <c r="U6" s="145"/>
+      <c r="V6" s="144"/>
+      <c r="W6" s="143"/>
+      <c r="X6" s="145"/>
+      <c r="Y6" s="145"/>
+      <c r="Z6" s="145"/>
+      <c r="AA6" s="145"/>
+      <c r="AB6" s="145"/>
+      <c r="AC6" s="145"/>
+      <c r="AD6" s="144"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
-    <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1"/>
-      <c r="C7" s="91">
+      <c r="C7" s="118">
         <f ca="1">W5+1</f>
         <v>46271</v>
       </c>
-      <c r="D7" s="92"/>
-      <c r="E7" s="99"/>
-      <c r="F7" s="100"/>
-      <c r="G7" s="99"/>
-      <c r="H7" s="100"/>
-      <c r="I7" s="99"/>
-      <c r="J7" s="100"/>
-      <c r="K7" s="99"/>
-      <c r="L7" s="101"/>
-      <c r="M7" s="101"/>
+      <c r="D7" s="120"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="130"/>
+      <c r="G7" s="129"/>
+      <c r="H7" s="130"/>
+      <c r="I7" s="129"/>
+      <c r="J7" s="130"/>
+      <c r="K7" s="129"/>
+      <c r="L7" s="131"/>
+      <c r="M7" s="131"/>
       <c r="N7" s="75"/>
-      <c r="O7" s="99"/>
-      <c r="P7" s="101"/>
-      <c r="Q7" s="101"/>
-      <c r="R7" s="101"/>
-      <c r="S7" s="101"/>
-      <c r="T7" s="101"/>
-      <c r="U7" s="101"/>
-      <c r="V7" s="100"/>
-      <c r="W7" s="99"/>
-      <c r="X7" s="101"/>
-      <c r="Y7" s="101"/>
-      <c r="Z7" s="101"/>
-      <c r="AA7" s="101"/>
-      <c r="AB7" s="101"/>
-      <c r="AC7" s="101"/>
-      <c r="AD7" s="100"/>
+      <c r="O7" s="129"/>
+      <c r="P7" s="131"/>
+      <c r="Q7" s="131"/>
+      <c r="R7" s="131"/>
+      <c r="S7" s="131"/>
+      <c r="T7" s="131"/>
+      <c r="U7" s="131"/>
+      <c r="V7" s="130"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="131"/>
+      <c r="Y7" s="131"/>
+      <c r="Z7" s="131"/>
+      <c r="AA7" s="131"/>
+      <c r="AB7" s="131"/>
+      <c r="AC7" s="131"/>
+      <c r="AD7" s="130"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="4"/>
-      <c r="C8" s="91"/>
-      <c r="D8" s="92"/>
-      <c r="E8" s="93">
+      <c r="C8" s="118"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="132">
         <f ca="1">C7+1</f>
         <v>46272</v>
       </c>
-      <c r="F8" s="94"/>
-      <c r="G8" s="93">
+      <c r="F8" s="133"/>
+      <c r="G8" s="132">
         <f ca="1">E8+1</f>
         <v>46273</v>
       </c>
-      <c r="H8" s="94"/>
-      <c r="I8" s="93">
+      <c r="H8" s="133"/>
+      <c r="I8" s="132">
         <f ca="1">G8+1</f>
         <v>46274</v>
       </c>
-      <c r="J8" s="94"/>
-      <c r="K8" s="93">
+      <c r="J8" s="133"/>
+      <c r="K8" s="132">
         <f ca="1">I8+1</f>
         <v>46275</v>
       </c>
-      <c r="L8" s="95"/>
-      <c r="M8" s="95"/>
+      <c r="L8" s="134"/>
+      <c r="M8" s="134"/>
       <c r="N8" s="50"/>
-      <c r="O8" s="93">
+      <c r="O8" s="132">
         <f ca="1">K8+1</f>
         <v>46276</v>
       </c>
-      <c r="P8" s="95"/>
-      <c r="Q8" s="95"/>
-      <c r="R8" s="95"/>
-      <c r="S8" s="95"/>
-      <c r="T8" s="95"/>
-      <c r="U8" s="95"/>
-      <c r="V8" s="94"/>
-      <c r="W8" s="93">
+      <c r="P8" s="134"/>
+      <c r="Q8" s="134"/>
+      <c r="R8" s="134"/>
+      <c r="S8" s="134"/>
+      <c r="T8" s="134"/>
+      <c r="U8" s="134"/>
+      <c r="V8" s="133"/>
+      <c r="W8" s="132">
         <f ca="1">O8+1</f>
         <v>46277</v>
       </c>
-      <c r="X8" s="95"/>
-      <c r="Y8" s="95"/>
-      <c r="Z8" s="95"/>
-      <c r="AA8" s="95"/>
-      <c r="AB8" s="95"/>
-      <c r="AC8" s="95"/>
-      <c r="AD8" s="94"/>
+      <c r="X8" s="134"/>
+      <c r="Y8" s="134"/>
+      <c r="Z8" s="134"/>
+      <c r="AA8" s="134"/>
+      <c r="AB8" s="134"/>
+      <c r="AC8" s="134"/>
+      <c r="AD8" s="133"/>
       <c r="AF8" s="4"/>
     </row>
-    <row r="9" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="42"/>
-      <c r="C9" s="148"/>
-      <c r="D9" s="149"/>
-      <c r="E9" s="148"/>
-      <c r="F9" s="149"/>
-      <c r="G9" s="148"/>
-      <c r="H9" s="149"/>
-      <c r="I9" s="148"/>
-      <c r="J9" s="149"/>
-      <c r="K9" s="148"/>
-      <c r="L9" s="150"/>
-      <c r="M9" s="150"/>
-      <c r="N9" s="149"/>
-      <c r="O9" s="148"/>
-      <c r="P9" s="150"/>
-      <c r="Q9" s="150"/>
-      <c r="R9" s="150"/>
-      <c r="S9" s="150"/>
-      <c r="T9" s="150"/>
-      <c r="U9" s="150"/>
-      <c r="V9" s="149"/>
-      <c r="W9" s="148"/>
-      <c r="X9" s="150"/>
-      <c r="Y9" s="150"/>
-      <c r="Z9" s="150"/>
-      <c r="AA9" s="150"/>
-      <c r="AB9" s="150"/>
-      <c r="AC9" s="150"/>
-      <c r="AD9" s="149"/>
+      <c r="C9" s="143"/>
+      <c r="D9" s="144"/>
+      <c r="E9" s="143"/>
+      <c r="F9" s="144"/>
+      <c r="G9" s="143"/>
+      <c r="H9" s="144"/>
+      <c r="I9" s="143"/>
+      <c r="J9" s="144"/>
+      <c r="K9" s="143"/>
+      <c r="L9" s="145"/>
+      <c r="M9" s="145"/>
+      <c r="N9" s="144"/>
+      <c r="O9" s="143"/>
+      <c r="P9" s="145"/>
+      <c r="Q9" s="145"/>
+      <c r="R9" s="145"/>
+      <c r="S9" s="145"/>
+      <c r="T9" s="145"/>
+      <c r="U9" s="145"/>
+      <c r="V9" s="144"/>
+      <c r="W9" s="143"/>
+      <c r="X9" s="145"/>
+      <c r="Y9" s="145"/>
+      <c r="Z9" s="145"/>
+      <c r="AA9" s="145"/>
+      <c r="AB9" s="145"/>
+      <c r="AC9" s="145"/>
+      <c r="AD9" s="144"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
-    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="42"/>
-      <c r="C10" s="91">
+      <c r="C10" s="118">
         <f ca="1">W8+1</f>
         <v>46278</v>
       </c>
-      <c r="D10" s="92"/>
+      <c r="D10" s="120"/>
       <c r="E10" s="45"/>
       <c r="F10" s="75"/>
       <c r="G10" s="45"/>
@@ -2379,97 +2384,97 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="42"/>
     </row>
-    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="4"/>
-      <c r="C11" s="91"/>
-      <c r="D11" s="92"/>
-      <c r="E11" s="93">
+      <c r="C11" s="118"/>
+      <c r="D11" s="120"/>
+      <c r="E11" s="132">
         <f ca="1">C10+1</f>
         <v>46279</v>
       </c>
-      <c r="F11" s="94"/>
-      <c r="G11" s="93">
+      <c r="F11" s="133"/>
+      <c r="G11" s="132">
         <f ca="1">E11+1</f>
         <v>46280</v>
       </c>
-      <c r="H11" s="94"/>
-      <c r="I11" s="93">
+      <c r="H11" s="133"/>
+      <c r="I11" s="132">
         <f ca="1">G11+1</f>
         <v>46281</v>
       </c>
-      <c r="J11" s="94"/>
-      <c r="K11" s="93">
+      <c r="J11" s="133"/>
+      <c r="K11" s="132">
         <f ca="1">I11+1</f>
         <v>46282</v>
       </c>
-      <c r="L11" s="95"/>
-      <c r="M11" s="95"/>
+      <c r="L11" s="134"/>
+      <c r="M11" s="134"/>
       <c r="N11" s="50"/>
-      <c r="O11" s="93">
+      <c r="O11" s="132">
         <f ca="1">K11+1</f>
         <v>46283</v>
       </c>
-      <c r="P11" s="95"/>
-      <c r="Q11" s="95"/>
-      <c r="R11" s="95"/>
-      <c r="S11" s="95"/>
-      <c r="T11" s="95"/>
-      <c r="U11" s="95"/>
-      <c r="V11" s="94"/>
-      <c r="W11" s="93">
+      <c r="P11" s="134"/>
+      <c r="Q11" s="134"/>
+      <c r="R11" s="134"/>
+      <c r="S11" s="134"/>
+      <c r="T11" s="134"/>
+      <c r="U11" s="134"/>
+      <c r="V11" s="133"/>
+      <c r="W11" s="132">
         <f ca="1">O11+1</f>
         <v>46284</v>
       </c>
-      <c r="X11" s="95"/>
-      <c r="Y11" s="95"/>
-      <c r="Z11" s="95"/>
-      <c r="AA11" s="95"/>
-      <c r="AB11" s="95"/>
-      <c r="AC11" s="95"/>
-      <c r="AD11" s="94"/>
+      <c r="X11" s="134"/>
+      <c r="Y11" s="134"/>
+      <c r="Z11" s="134"/>
+      <c r="AA11" s="134"/>
+      <c r="AB11" s="134"/>
+      <c r="AC11" s="134"/>
+      <c r="AD11" s="133"/>
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="42"/>
-      <c r="C12" s="148"/>
-      <c r="D12" s="149"/>
-      <c r="E12" s="148"/>
-      <c r="F12" s="149"/>
-      <c r="G12" s="148"/>
-      <c r="H12" s="149"/>
-      <c r="I12" s="148"/>
-      <c r="J12" s="149"/>
-      <c r="K12" s="148"/>
-      <c r="L12" s="150"/>
-      <c r="M12" s="150"/>
-      <c r="N12" s="149"/>
-      <c r="O12" s="148"/>
-      <c r="P12" s="150"/>
-      <c r="Q12" s="150"/>
-      <c r="R12" s="150"/>
-      <c r="S12" s="150"/>
-      <c r="T12" s="150"/>
-      <c r="U12" s="150"/>
-      <c r="V12" s="149"/>
-      <c r="W12" s="148"/>
-      <c r="X12" s="150"/>
-      <c r="Y12" s="150"/>
-      <c r="Z12" s="150"/>
-      <c r="AA12" s="150"/>
-      <c r="AB12" s="150"/>
-      <c r="AC12" s="150"/>
-      <c r="AD12" s="149"/>
+      <c r="C12" s="143"/>
+      <c r="D12" s="144"/>
+      <c r="E12" s="143"/>
+      <c r="F12" s="144"/>
+      <c r="G12" s="143"/>
+      <c r="H12" s="144"/>
+      <c r="I12" s="143"/>
+      <c r="J12" s="144"/>
+      <c r="K12" s="143"/>
+      <c r="L12" s="145"/>
+      <c r="M12" s="145"/>
+      <c r="N12" s="144"/>
+      <c r="O12" s="143"/>
+      <c r="P12" s="145"/>
+      <c r="Q12" s="145"/>
+      <c r="R12" s="145"/>
+      <c r="S12" s="145"/>
+      <c r="T12" s="145"/>
+      <c r="U12" s="145"/>
+      <c r="V12" s="144"/>
+      <c r="W12" s="143"/>
+      <c r="X12" s="145"/>
+      <c r="Y12" s="145"/>
+      <c r="Z12" s="145"/>
+      <c r="AA12" s="145"/>
+      <c r="AB12" s="145"/>
+      <c r="AC12" s="145"/>
+      <c r="AD12" s="144"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
-    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="42"/>
-      <c r="C13" s="91">
+      <c r="C13" s="118">
         <f ca="1">W11+1</f>
         <v>46285</v>
       </c>
-      <c r="D13" s="92"/>
+      <c r="D13" s="120"/>
       <c r="E13" s="45"/>
       <c r="F13" s="75"/>
       <c r="G13" s="45"/>
@@ -2499,114 +2504,114 @@
       <c r="AE13" s="7"/>
       <c r="AF13" s="42"/>
     </row>
-    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="4"/>
-      <c r="C14" s="91"/>
-      <c r="D14" s="92"/>
-      <c r="E14" s="93">
+      <c r="C14" s="118"/>
+      <c r="D14" s="120"/>
+      <c r="E14" s="132">
         <f ca="1">C13+1</f>
         <v>46286</v>
       </c>
-      <c r="F14" s="94"/>
-      <c r="G14" s="93">
+      <c r="F14" s="133"/>
+      <c r="G14" s="132">
         <f ca="1">E14+1</f>
         <v>46287</v>
       </c>
-      <c r="H14" s="94"/>
-      <c r="I14" s="93">
+      <c r="H14" s="133"/>
+      <c r="I14" s="132">
         <f ca="1">G14+1</f>
         <v>46288</v>
       </c>
-      <c r="J14" s="94"/>
-      <c r="K14" s="93">
+      <c r="J14" s="133"/>
+      <c r="K14" s="132">
         <f ca="1">I14+1</f>
         <v>46289</v>
       </c>
-      <c r="L14" s="95"/>
-      <c r="M14" s="95"/>
+      <c r="L14" s="134"/>
+      <c r="M14" s="134"/>
       <c r="N14" s="50"/>
-      <c r="O14" s="93">
+      <c r="O14" s="132">
         <f ca="1">K14+1</f>
         <v>46290</v>
       </c>
-      <c r="P14" s="95"/>
-      <c r="Q14" s="95"/>
-      <c r="R14" s="95"/>
-      <c r="S14" s="95"/>
-      <c r="T14" s="95"/>
-      <c r="U14" s="95"/>
-      <c r="V14" s="94"/>
-      <c r="W14" s="93">
+      <c r="P14" s="134"/>
+      <c r="Q14" s="134"/>
+      <c r="R14" s="134"/>
+      <c r="S14" s="134"/>
+      <c r="T14" s="134"/>
+      <c r="U14" s="134"/>
+      <c r="V14" s="133"/>
+      <c r="W14" s="132">
         <f ca="1">O14+1</f>
         <v>46291</v>
       </c>
-      <c r="X14" s="95"/>
-      <c r="Y14" s="95"/>
-      <c r="Z14" s="95"/>
-      <c r="AA14" s="95"/>
-      <c r="AB14" s="95"/>
-      <c r="AC14" s="95"/>
-      <c r="AD14" s="94"/>
+      <c r="X14" s="134"/>
+      <c r="Y14" s="134"/>
+      <c r="Z14" s="134"/>
+      <c r="AA14" s="134"/>
+      <c r="AB14" s="134"/>
+      <c r="AC14" s="134"/>
+      <c r="AD14" s="133"/>
       <c r="AF14" s="4"/>
     </row>
-    <row r="15" spans="1:36" s="43" customFormat="1" ht="162.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" s="43" customFormat="1" ht="162.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="42"/>
-      <c r="C15" s="148"/>
-      <c r="D15" s="149"/>
-      <c r="E15" s="148"/>
-      <c r="F15" s="149"/>
-      <c r="G15" s="148"/>
-      <c r="H15" s="149"/>
-      <c r="I15" s="104"/>
-      <c r="J15" s="106"/>
-      <c r="K15" s="104"/>
-      <c r="L15" s="105"/>
-      <c r="M15" s="105"/>
-      <c r="N15" s="106"/>
-      <c r="O15" s="104"/>
-      <c r="P15" s="105"/>
-      <c r="Q15" s="105"/>
-      <c r="R15" s="105"/>
-      <c r="S15" s="105"/>
-      <c r="T15" s="105"/>
-      <c r="U15" s="105"/>
-      <c r="V15" s="106"/>
-      <c r="W15" s="104"/>
-      <c r="X15" s="105"/>
-      <c r="Y15" s="105"/>
-      <c r="Z15" s="105"/>
-      <c r="AA15" s="105"/>
-      <c r="AB15" s="105"/>
-      <c r="AC15" s="105"/>
-      <c r="AD15" s="106"/>
+      <c r="C15" s="143"/>
+      <c r="D15" s="144"/>
+      <c r="E15" s="143"/>
+      <c r="F15" s="144"/>
+      <c r="G15" s="143"/>
+      <c r="H15" s="144"/>
+      <c r="I15" s="123"/>
+      <c r="J15" s="125"/>
+      <c r="K15" s="123"/>
+      <c r="L15" s="124"/>
+      <c r="M15" s="124"/>
+      <c r="N15" s="125"/>
+      <c r="O15" s="123"/>
+      <c r="P15" s="124"/>
+      <c r="Q15" s="124"/>
+      <c r="R15" s="124"/>
+      <c r="S15" s="124"/>
+      <c r="T15" s="124"/>
+      <c r="U15" s="124"/>
+      <c r="V15" s="125"/>
+      <c r="W15" s="123"/>
+      <c r="X15" s="124"/>
+      <c r="Y15" s="124"/>
+      <c r="Z15" s="124"/>
+      <c r="AA15" s="124"/>
+      <c r="AB15" s="124"/>
+      <c r="AC15" s="124"/>
+      <c r="AD15" s="125"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
-    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="42"/>
-      <c r="C16" s="91">
+      <c r="C16" s="118">
         <f ca="1">W14+1</f>
         <v>46292</v>
       </c>
-      <c r="D16" s="92"/>
+      <c r="D16" s="120"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
       <c r="H16" s="75"/>
-      <c r="I16" s="145"/>
-      <c r="J16" s="146"/>
+      <c r="I16" s="146"/>
+      <c r="J16" s="147"/>
       <c r="K16" s="66"/>
       <c r="L16" s="68"/>
       <c r="M16" s="68"/>
       <c r="N16" s="67"/>
-      <c r="O16" s="145"/>
-      <c r="P16" s="147"/>
-      <c r="Q16" s="147"/>
-      <c r="R16" s="147"/>
-      <c r="S16" s="147"/>
-      <c r="T16" s="147"/>
-      <c r="U16" s="147"/>
-      <c r="V16" s="146"/>
+      <c r="O16" s="146"/>
+      <c r="P16" s="148"/>
+      <c r="Q16" s="148"/>
+      <c r="R16" s="148"/>
+      <c r="S16" s="148"/>
+      <c r="T16" s="148"/>
+      <c r="U16" s="148"/>
+      <c r="V16" s="147"/>
       <c r="W16" s="45"/>
       <c r="X16" s="76"/>
       <c r="Y16" s="76"/>
@@ -2618,25 +2623,25 @@
       <c r="AE16" s="7"/>
       <c r="AF16" s="42"/>
     </row>
-    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4"/>
-      <c r="C17" s="91"/>
-      <c r="D17" s="92"/>
-      <c r="E17" s="93">
+      <c r="C17" s="118"/>
+      <c r="D17" s="120"/>
+      <c r="E17" s="132">
         <f ca="1">C16+1</f>
         <v>46293</v>
       </c>
-      <c r="F17" s="94"/>
-      <c r="G17" s="93">
+      <c r="F17" s="133"/>
+      <c r="G17" s="132">
         <f ca="1">E17+1</f>
         <v>46294</v>
       </c>
-      <c r="H17" s="94"/>
-      <c r="I17" s="93">
+      <c r="H17" s="133"/>
+      <c r="I17" s="132">
         <f ca="1">G17+1</f>
         <v>46295</v>
       </c>
-      <c r="J17" s="94"/>
+      <c r="J17" s="133"/>
       <c r="K17" s="46">
         <f ca="1">I17+1</f>
         <v>46296</v>
@@ -2644,93 +2649,93 @@
       <c r="L17" s="51"/>
       <c r="M17" s="51"/>
       <c r="N17" s="69"/>
-      <c r="O17" s="93">
+      <c r="O17" s="132">
         <f ca="1">K17+1</f>
         <v>46297</v>
       </c>
-      <c r="P17" s="95"/>
-      <c r="Q17" s="95"/>
-      <c r="R17" s="95"/>
-      <c r="S17" s="95"/>
-      <c r="T17" s="95"/>
-      <c r="U17" s="95"/>
-      <c r="V17" s="94"/>
-      <c r="W17" s="93">
+      <c r="P17" s="134"/>
+      <c r="Q17" s="134"/>
+      <c r="R17" s="134"/>
+      <c r="S17" s="134"/>
+      <c r="T17" s="134"/>
+      <c r="U17" s="134"/>
+      <c r="V17" s="133"/>
+      <c r="W17" s="132">
         <f ca="1">O17+1</f>
         <v>46298</v>
       </c>
-      <c r="X17" s="95"/>
-      <c r="Y17" s="95"/>
-      <c r="Z17" s="95"/>
-      <c r="AA17" s="95"/>
-      <c r="AB17" s="95"/>
-      <c r="AC17" s="95"/>
-      <c r="AD17" s="94"/>
+      <c r="X17" s="134"/>
+      <c r="Y17" s="134"/>
+      <c r="Z17" s="134"/>
+      <c r="AA17" s="134"/>
+      <c r="AB17" s="134"/>
+      <c r="AC17" s="134"/>
+      <c r="AD17" s="133"/>
       <c r="AF17" s="4"/>
     </row>
-    <row r="18" spans="1:42" s="43" customFormat="1" ht="147.30000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:42" s="43" customFormat="1" ht="147.30000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="42"/>
-      <c r="C18" s="143" t="s">
+      <c r="C18" s="126" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="144"/>
-      <c r="E18" s="104"/>
-      <c r="F18" s="106"/>
-      <c r="G18" s="104"/>
-      <c r="H18" s="106"/>
-      <c r="I18" s="143" t="s">
+      <c r="D18" s="128"/>
+      <c r="E18" s="123"/>
+      <c r="F18" s="125"/>
+      <c r="G18" s="123"/>
+      <c r="H18" s="125"/>
+      <c r="I18" s="126" t="s">
         <v>17</v>
       </c>
-      <c r="J18" s="144"/>
+      <c r="J18" s="128"/>
       <c r="K18" s="70"/>
       <c r="L18" s="71"/>
       <c r="M18" s="71"/>
       <c r="N18" s="72"/>
-      <c r="O18" s="96"/>
-      <c r="P18" s="141"/>
-      <c r="Q18" s="141"/>
-      <c r="R18" s="141"/>
-      <c r="S18" s="141"/>
-      <c r="T18" s="141"/>
-      <c r="U18" s="141"/>
-      <c r="V18" s="97"/>
-      <c r="W18" s="96"/>
-      <c r="X18" s="141"/>
-      <c r="Y18" s="141"/>
-      <c r="Z18" s="141"/>
-      <c r="AA18" s="141"/>
-      <c r="AB18" s="141"/>
-      <c r="AC18" s="141"/>
-      <c r="AD18" s="97"/>
+      <c r="O18" s="111"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="112"/>
+      <c r="R18" s="112"/>
+      <c r="S18" s="112"/>
+      <c r="T18" s="112"/>
+      <c r="U18" s="112"/>
+      <c r="V18" s="113"/>
+      <c r="W18" s="111"/>
+      <c r="X18" s="112"/>
+      <c r="Y18" s="112"/>
+      <c r="Z18" s="112"/>
+      <c r="AA18" s="112"/>
+      <c r="AB18" s="112"/>
+      <c r="AC18" s="112"/>
+      <c r="AD18" s="113"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
-    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="42"/>
-      <c r="C19" s="91">
+      <c r="C19" s="118">
         <f ca="1">W17+1</f>
         <v>46299</v>
       </c>
-      <c r="D19" s="92"/>
+      <c r="D19" s="120"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
       <c r="H19" s="75"/>
-      <c r="I19" s="145"/>
-      <c r="J19" s="146"/>
+      <c r="I19" s="146"/>
+      <c r="J19" s="147"/>
       <c r="K19" s="66"/>
       <c r="L19" s="68"/>
       <c r="M19" s="68"/>
       <c r="N19" s="67"/>
-      <c r="O19" s="145"/>
-      <c r="P19" s="147"/>
-      <c r="Q19" s="147"/>
-      <c r="R19" s="147"/>
-      <c r="S19" s="147"/>
-      <c r="T19" s="147"/>
-      <c r="U19" s="147"/>
-      <c r="V19" s="146"/>
+      <c r="O19" s="146"/>
+      <c r="P19" s="148"/>
+      <c r="Q19" s="148"/>
+      <c r="R19" s="148"/>
+      <c r="S19" s="148"/>
+      <c r="T19" s="148"/>
+      <c r="U19" s="148"/>
+      <c r="V19" s="147"/>
       <c r="W19" s="45"/>
       <c r="X19" s="76"/>
       <c r="Y19" s="76"/>
@@ -2742,25 +2747,25 @@
       <c r="AE19" s="7"/>
       <c r="AF19" s="42"/>
     </row>
-    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4"/>
-      <c r="C20" s="91"/>
-      <c r="D20" s="92"/>
-      <c r="E20" s="93">
+      <c r="C20" s="118"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="132">
         <f ca="1">C19+1</f>
         <v>46300</v>
       </c>
-      <c r="F20" s="94"/>
-      <c r="G20" s="93">
+      <c r="F20" s="133"/>
+      <c r="G20" s="132">
         <f ca="1">E20+1</f>
         <v>46301</v>
       </c>
-      <c r="H20" s="94"/>
-      <c r="I20" s="93">
+      <c r="H20" s="133"/>
+      <c r="I20" s="132">
         <f ca="1">G20+1</f>
         <v>46302</v>
       </c>
-      <c r="J20" s="94"/>
+      <c r="J20" s="133"/>
       <c r="K20" s="46">
         <f ca="1">I20+1</f>
         <v>46303</v>
@@ -2768,65 +2773,65 @@
       <c r="L20" s="51"/>
       <c r="M20" s="51"/>
       <c r="N20" s="69"/>
-      <c r="O20" s="93">
+      <c r="O20" s="132">
         <f ca="1">K20+1</f>
         <v>46304</v>
       </c>
-      <c r="P20" s="95"/>
-      <c r="Q20" s="95"/>
-      <c r="R20" s="95"/>
-      <c r="S20" s="95"/>
-      <c r="T20" s="95"/>
-      <c r="U20" s="95"/>
-      <c r="V20" s="94"/>
-      <c r="W20" s="93">
+      <c r="P20" s="134"/>
+      <c r="Q20" s="134"/>
+      <c r="R20" s="134"/>
+      <c r="S20" s="134"/>
+      <c r="T20" s="134"/>
+      <c r="U20" s="134"/>
+      <c r="V20" s="133"/>
+      <c r="W20" s="132">
         <f ca="1">O20+1</f>
         <v>46305</v>
       </c>
-      <c r="X20" s="95"/>
-      <c r="Y20" s="95"/>
-      <c r="Z20" s="95"/>
-      <c r="AA20" s="95"/>
-      <c r="AB20" s="95"/>
-      <c r="AC20" s="95"/>
-      <c r="AD20" s="94"/>
+      <c r="X20" s="134"/>
+      <c r="Y20" s="134"/>
+      <c r="Z20" s="134"/>
+      <c r="AA20" s="134"/>
+      <c r="AB20" s="134"/>
+      <c r="AC20" s="134"/>
+      <c r="AD20" s="133"/>
       <c r="AF20" s="4"/>
     </row>
-    <row r="21" spans="1:42" s="43" customFormat="1" ht="166.8" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:42" s="43" customFormat="1" ht="166.8" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="42"/>
-      <c r="C21" s="96"/>
-      <c r="D21" s="97"/>
-      <c r="E21" s="96"/>
-      <c r="F21" s="97"/>
-      <c r="G21" s="96"/>
-      <c r="H21" s="97"/>
-      <c r="I21" s="96"/>
-      <c r="J21" s="97"/>
+      <c r="C21" s="111"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="113"/>
       <c r="K21" s="70"/>
       <c r="L21" s="71"/>
       <c r="M21" s="71"/>
       <c r="N21" s="72"/>
-      <c r="O21" s="96"/>
-      <c r="P21" s="141"/>
-      <c r="Q21" s="141"/>
-      <c r="R21" s="141"/>
-      <c r="S21" s="141"/>
-      <c r="T21" s="141"/>
-      <c r="U21" s="141"/>
-      <c r="V21" s="97"/>
-      <c r="W21" s="96"/>
-      <c r="X21" s="141"/>
-      <c r="Y21" s="141"/>
-      <c r="Z21" s="141"/>
-      <c r="AA21" s="141"/>
-      <c r="AB21" s="141"/>
-      <c r="AC21" s="141"/>
-      <c r="AD21" s="97"/>
+      <c r="O21" s="111"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="112"/>
+      <c r="R21" s="112"/>
+      <c r="S21" s="112"/>
+      <c r="T21" s="112"/>
+      <c r="U21" s="112"/>
+      <c r="V21" s="113"/>
+      <c r="W21" s="111"/>
+      <c r="X21" s="112"/>
+      <c r="Y21" s="112"/>
+      <c r="Z21" s="112"/>
+      <c r="AA21" s="112"/>
+      <c r="AB21" s="112"/>
+      <c r="AC21" s="112"/>
+      <c r="AD21" s="113"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
     </row>
-    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="4"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52"/>
@@ -2858,7 +2863,7 @@
       <c r="AD22" s="55"/>
       <c r="AF22" s="4"/>
     </row>
-    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="56"/>
@@ -2892,61 +2897,61 @@
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
     </row>
-    <row r="24" spans="1:42" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:42" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="1"/>
       <c r="M24" s="1"/>
       <c r="AF24" s="1"/>
     </row>
-    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="1"/>
-      <c r="C25" s="86" t="s">
+      <c r="C25" s="139" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="86"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="86"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="86"/>
-      <c r="J25" s="86"/>
-      <c r="K25" s="86"/>
+      <c r="D25" s="139"/>
+      <c r="E25" s="139"/>
+      <c r="F25" s="139"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="139"/>
+      <c r="I25" s="139"/>
+      <c r="J25" s="139"/>
+      <c r="K25" s="139"/>
       <c r="L25" s="60"/>
       <c r="M25" s="1"/>
-      <c r="O25" s="87">
+      <c r="O25" s="140">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)-1,1)</f>
         <v>46235</v>
       </c>
-      <c r="P25" s="87"/>
-      <c r="Q25" s="87"/>
-      <c r="R25" s="87"/>
-      <c r="S25" s="87"/>
-      <c r="T25" s="87"/>
-      <c r="U25" s="87"/>
+      <c r="P25" s="140"/>
+      <c r="Q25" s="140"/>
+      <c r="R25" s="140"/>
+      <c r="S25" s="140"/>
+      <c r="T25" s="140"/>
+      <c r="U25" s="140"/>
       <c r="V25" s="61"/>
       <c r="W25" s="61"/>
-      <c r="X25" s="87">
+      <c r="X25" s="140">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)+1,1)</f>
         <v>46296</v>
       </c>
-      <c r="Y25" s="87"/>
-      <c r="Z25" s="87"/>
-      <c r="AA25" s="87"/>
-      <c r="AB25" s="87"/>
-      <c r="AC25" s="87"/>
-      <c r="AD25" s="87"/>
+      <c r="Y25" s="140"/>
+      <c r="Z25" s="140"/>
+      <c r="AA25" s="140"/>
+      <c r="AB25" s="140"/>
+      <c r="AC25" s="140"/>
+      <c r="AD25" s="140"/>
       <c r="AF25" s="1"/>
     </row>
-    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="1"/>
-      <c r="C26" s="86"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="86"/>
-      <c r="G26" s="86"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="86"/>
-      <c r="J26" s="86"/>
-      <c r="K26" s="86"/>
+      <c r="C26" s="139"/>
+      <c r="D26" s="139"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="139"/>
+      <c r="H26" s="139"/>
+      <c r="I26" s="139"/>
+      <c r="J26" s="139"/>
+      <c r="K26" s="139"/>
       <c r="L26" s="60"/>
       <c r="M26" s="1"/>
       <c r="O26" s="62" t="str">
@@ -3009,19 +3014,19 @@
       </c>
       <c r="AF26" s="1"/>
     </row>
-    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="1"/>
-      <c r="C27" s="88" t="s">
-        <v>22</v>
-      </c>
-      <c r="D27" s="88"/>
-      <c r="E27" s="88"/>
-      <c r="F27" s="88"/>
-      <c r="G27" s="88"/>
-      <c r="H27" s="88"/>
-      <c r="I27" s="88"/>
-      <c r="J27" s="88"/>
-      <c r="K27" s="88"/>
+      <c r="C27" s="115" t="s">
+        <v>21</v>
+      </c>
+      <c r="D27" s="115"/>
+      <c r="E27" s="115"/>
+      <c r="F27" s="115"/>
+      <c r="G27" s="115"/>
+      <c r="H27" s="115"/>
+      <c r="I27" s="115"/>
+      <c r="J27" s="115"/>
+      <c r="K27" s="115"/>
       <c r="M27" s="1"/>
       <c r="O27" s="64" t="str">
         <f t="shared" ref="O27:U32" ca="1" si="0">IF(MONTH($O$25)&lt;&gt;MONTH($O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1)),"",$O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1))</f>
@@ -3083,19 +3088,19 @@
       </c>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="1"/>
-      <c r="C28" s="89" t="s">
-        <v>23</v>
-      </c>
-      <c r="D28" s="89"/>
-      <c r="E28" s="89"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="89"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="89"/>
-      <c r="K28" s="89"/>
+      <c r="C28" s="114" t="s">
+        <v>22</v>
+      </c>
+      <c r="D28" s="114"/>
+      <c r="E28" s="114"/>
+      <c r="F28" s="114"/>
+      <c r="G28" s="114"/>
+      <c r="H28" s="114"/>
+      <c r="I28" s="114"/>
+      <c r="J28" s="114"/>
+      <c r="K28" s="114"/>
       <c r="M28" s="1"/>
       <c r="O28" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3157,17 +3162,17 @@
       </c>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="1"/>
-      <c r="C29" s="88"/>
-      <c r="D29" s="88"/>
-      <c r="E29" s="88"/>
-      <c r="F29" s="88"/>
-      <c r="G29" s="88"/>
-      <c r="H29" s="88"/>
-      <c r="I29" s="88"/>
-      <c r="J29" s="88"/>
-      <c r="K29" s="88"/>
+      <c r="C29" s="115"/>
+      <c r="D29" s="115"/>
+      <c r="E29" s="115"/>
+      <c r="F29" s="115"/>
+      <c r="G29" s="115"/>
+      <c r="H29" s="115"/>
+      <c r="I29" s="115"/>
+      <c r="J29" s="115"/>
+      <c r="K29" s="115"/>
       <c r="M29" s="1"/>
       <c r="O29" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3229,19 +3234,19 @@
       </c>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="1"/>
-      <c r="C30" s="89" t="s">
-        <v>24</v>
-      </c>
-      <c r="D30" s="89"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="89"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="89"/>
-      <c r="K30" s="89"/>
+      <c r="C30" s="114" t="s">
+        <v>23</v>
+      </c>
+      <c r="D30" s="114"/>
+      <c r="E30" s="114"/>
+      <c r="F30" s="114"/>
+      <c r="G30" s="114"/>
+      <c r="H30" s="114"/>
+      <c r="I30" s="114"/>
+      <c r="J30" s="114"/>
+      <c r="K30" s="114"/>
       <c r="M30" s="1"/>
       <c r="O30" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3303,17 +3308,17 @@
       </c>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="1"/>
-      <c r="C31" s="88"/>
-      <c r="D31" s="88"/>
-      <c r="E31" s="88"/>
-      <c r="F31" s="88"/>
-      <c r="G31" s="88"/>
-      <c r="H31" s="88"/>
-      <c r="I31" s="88"/>
-      <c r="J31" s="88"/>
-      <c r="K31" s="88"/>
+      <c r="C31" s="115"/>
+      <c r="D31" s="115"/>
+      <c r="E31" s="115"/>
+      <c r="F31" s="115"/>
+      <c r="G31" s="115"/>
+      <c r="H31" s="115"/>
+      <c r="I31" s="115"/>
+      <c r="J31" s="115"/>
+      <c r="K31" s="115"/>
       <c r="M31" s="1"/>
       <c r="O31" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3375,7 +3380,7 @@
       </c>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.45">
       <c r="A32" s="1"/>
       <c r="M32" s="1"/>
       <c r="O32" s="64">
@@ -3438,7 +3443,7 @@
       </c>
       <c r="AF32" s="1"/>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A33" s="1"/>
       <c r="M33" s="1"/>
       <c r="O33" s="64"/>
@@ -3459,7 +3464,7 @@
       <c r="AD33" s="65"/>
       <c r="AF33" s="1"/>
     </row>
-    <row r="34" spans="1:32" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -3493,158 +3498,69 @@
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
     </row>
-    <row r="38" spans="1:32" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="113" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39" s="114"/>
-      <c r="F39" s="115"/>
-      <c r="G39" s="119">
+    <row r="38" spans="1:32" ht="12.9" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D39" s="83" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="84"/>
+      <c r="F39" s="85"/>
+      <c r="G39" s="89">
         <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
         <v>5</v>
       </c>
-      <c r="H39" s="120"/>
-      <c r="I39" s="113" t="s">
-        <v>28</v>
-      </c>
-      <c r="J39" s="123"/>
-      <c r="K39" s="125" t="s">
-        <v>26</v>
-      </c>
-      <c r="L39" s="126"/>
-      <c r="M39" s="129">
+      <c r="H39" s="90"/>
+      <c r="I39" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="J39" s="93"/>
+      <c r="K39" s="95" t="s">
+        <v>25</v>
+      </c>
+      <c r="L39" s="96"/>
+      <c r="M39" s="99">
         <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
         <v>5.9999999999999973</v>
       </c>
-      <c r="N39" s="130"/>
-      <c r="O39" s="130"/>
-      <c r="P39" s="130"/>
-      <c r="Q39" s="130"/>
-      <c r="R39" s="131"/>
-      <c r="S39" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="T39" s="136"/>
-      <c r="U39" s="136"/>
-      <c r="V39" s="136"/>
-      <c r="W39" s="136"/>
-      <c r="X39" s="137"/>
-    </row>
-    <row r="40" spans="1:32" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D40" s="116"/>
-      <c r="E40" s="117"/>
-      <c r="F40" s="118"/>
-      <c r="G40" s="121"/>
-      <c r="H40" s="122"/>
-      <c r="I40" s="116"/>
-      <c r="J40" s="124"/>
-      <c r="K40" s="127"/>
-      <c r="L40" s="128"/>
-      <c r="M40" s="132"/>
-      <c r="N40" s="133"/>
-      <c r="O40" s="133"/>
-      <c r="P40" s="133"/>
-      <c r="Q40" s="133"/>
-      <c r="R40" s="134"/>
-      <c r="S40" s="138"/>
-      <c r="T40" s="139"/>
-      <c r="U40" s="139"/>
-      <c r="V40" s="139"/>
-      <c r="W40" s="139"/>
-      <c r="X40" s="140"/>
+      <c r="N39" s="100"/>
+      <c r="O39" s="100"/>
+      <c r="P39" s="100"/>
+      <c r="Q39" s="100"/>
+      <c r="R39" s="101"/>
+      <c r="S39" s="105" t="s">
+        <v>26</v>
+      </c>
+      <c r="T39" s="106"/>
+      <c r="U39" s="106"/>
+      <c r="V39" s="106"/>
+      <c r="W39" s="106"/>
+      <c r="X39" s="107"/>
+    </row>
+    <row r="40" spans="1:32" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D40" s="86"/>
+      <c r="E40" s="87"/>
+      <c r="F40" s="88"/>
+      <c r="G40" s="91"/>
+      <c r="H40" s="92"/>
+      <c r="I40" s="86"/>
+      <c r="J40" s="94"/>
+      <c r="K40" s="97"/>
+      <c r="L40" s="98"/>
+      <c r="M40" s="102"/>
+      <c r="N40" s="103"/>
+      <c r="O40" s="103"/>
+      <c r="P40" s="103"/>
+      <c r="Q40" s="103"/>
+      <c r="R40" s="104"/>
+      <c r="S40" s="108"/>
+      <c r="T40" s="109"/>
+      <c r="U40" s="109"/>
+      <c r="V40" s="109"/>
+      <c r="W40" s="109"/>
+      <c r="X40" s="110"/>
     </row>
   </sheetData>
   <mergeCells count="110">
-    <mergeCell ref="D39:F40"/>
-    <mergeCell ref="G39:H40"/>
-    <mergeCell ref="K39:L40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="S39:X40"/>
-    <mergeCell ref="M39:R40"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="O20:V20"/>
-    <mergeCell ref="C30:K31"/>
-    <mergeCell ref="C2:AD2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="W5:AD5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:V6"/>
-    <mergeCell ref="W6:AD6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="O5:V5"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="W7:AD7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="O8:V8"/>
-    <mergeCell ref="W8:AD8"/>
-    <mergeCell ref="O7:V7"/>
-    <mergeCell ref="W9:AD9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="O11:V11"/>
-    <mergeCell ref="W11:AD11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:V9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="W12:AD12"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="O14:V14"/>
-    <mergeCell ref="W14:AD14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="O12:V12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="W15:AD15"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="O17:V17"/>
-    <mergeCell ref="W17:AD17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="O15:V15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="O16:V16"/>
     <mergeCell ref="W18:AD18"/>
     <mergeCell ref="C25:K26"/>
     <mergeCell ref="O25:U25"/>
@@ -3666,6 +3582,95 @@
     <mergeCell ref="O21:V21"/>
     <mergeCell ref="W21:AD21"/>
     <mergeCell ref="O19:V19"/>
+    <mergeCell ref="W15:AD15"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="O17:V17"/>
+    <mergeCell ref="W17:AD17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="O15:V15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="O16:V16"/>
+    <mergeCell ref="W12:AD12"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O14:V14"/>
+    <mergeCell ref="W14:AD14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="O12:V12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="W9:AD9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="O11:V11"/>
+    <mergeCell ref="W11:AD11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:V9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="W7:AD7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="O8:V8"/>
+    <mergeCell ref="W8:AD8"/>
+    <mergeCell ref="O7:V7"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:V6"/>
+    <mergeCell ref="W6:AD6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="O5:V5"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="C2:AD2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="W5:AD5"/>
+    <mergeCell ref="D39:F40"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="K39:L40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="S39:X40"/>
+    <mergeCell ref="M39:R40"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="O20:V20"/>
+    <mergeCell ref="C30:K31"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 E5 G5 I5 K5:L5 O5 W5 C7 E8 G8 I8 K8:L8 O8 W8 C10 E11 G11 I11 K11:L11 O11 W11 C13 E14 G14 I14 K14:L14 O14 W14 C16 E17 G17 I17 K17:L17 O17 W17">
     <cfRule type="expression" dxfId="11" priority="3">
@@ -3704,7 +3709,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AP40"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="12.6" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="3" width="5.5546875" style="3" customWidth="1"/>
     <col min="4" max="4" width="15.5546875" style="3" customWidth="1"/>
@@ -3722,7 +3727,7 @@
     <col min="35" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3756,42 +3761,42 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="2.15">
       <c r="A2" s="29"/>
-      <c r="C2" s="111">
+      <c r="C2" s="116">
         <f ca="1">DATE(About!P8,10,1)</f>
         <v>46296</v>
       </c>
-      <c r="D2" s="111"/>
-      <c r="E2" s="111"/>
-      <c r="F2" s="111"/>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="111"/>
-      <c r="J2" s="111"/>
-      <c r="K2" s="111"/>
-      <c r="L2" s="111"/>
-      <c r="M2" s="111"/>
-      <c r="N2" s="111"/>
-      <c r="O2" s="111"/>
-      <c r="P2" s="111"/>
-      <c r="Q2" s="111"/>
-      <c r="R2" s="111"/>
-      <c r="S2" s="111"/>
-      <c r="T2" s="111"/>
-      <c r="U2" s="111"/>
-      <c r="V2" s="111"/>
-      <c r="W2" s="111"/>
-      <c r="X2" s="111"/>
-      <c r="Y2" s="111"/>
-      <c r="Z2" s="111"/>
-      <c r="AA2" s="111"/>
-      <c r="AB2" s="111"/>
-      <c r="AC2" s="111"/>
-      <c r="AD2" s="111"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="116"/>
+      <c r="P2" s="116"/>
+      <c r="Q2" s="116"/>
+      <c r="R2" s="116"/>
+      <c r="S2" s="116"/>
+      <c r="T2" s="116"/>
+      <c r="U2" s="116"/>
+      <c r="V2" s="116"/>
+      <c r="W2" s="116"/>
+      <c r="X2" s="116"/>
+      <c r="Y2" s="116"/>
+      <c r="Z2" s="116"/>
+      <c r="AA2" s="116"/>
+      <c r="AB2" s="116"/>
+      <c r="AC2" s="116"/>
+      <c r="AD2" s="116"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="2.15">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -3811,290 +3816,288 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A4" s="35"/>
-      <c r="C4" s="112">
+      <c r="C4" s="117">
         <f ca="1">C5</f>
         <v>46292</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112">
+      <c r="D4" s="117"/>
+      <c r="E4" s="117">
         <f ca="1">E5</f>
         <v>46293</v>
       </c>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112">
+      <c r="F4" s="117"/>
+      <c r="G4" s="117">
         <f ca="1">G5</f>
         <v>46294</v>
       </c>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112">
+      <c r="H4" s="117"/>
+      <c r="I4" s="117">
         <f ca="1">I5</f>
         <v>46295</v>
       </c>
-      <c r="J4" s="112"/>
-      <c r="K4" s="112">
+      <c r="J4" s="117"/>
+      <c r="K4" s="117">
         <f ca="1">K5</f>
         <v>46296</v>
       </c>
-      <c r="L4" s="112"/>
-      <c r="M4" s="112"/>
+      <c r="L4" s="117"/>
+      <c r="M4" s="117"/>
       <c r="N4" s="37"/>
-      <c r="O4" s="112">
+      <c r="O4" s="117">
         <f ca="1">O5</f>
         <v>46297</v>
       </c>
-      <c r="P4" s="112"/>
-      <c r="Q4" s="112"/>
-      <c r="R4" s="112"/>
-      <c r="S4" s="112"/>
-      <c r="T4" s="112"/>
-      <c r="U4" s="112"/>
-      <c r="V4" s="112"/>
-      <c r="W4" s="112">
+      <c r="P4" s="117"/>
+      <c r="Q4" s="117"/>
+      <c r="R4" s="117"/>
+      <c r="S4" s="117"/>
+      <c r="T4" s="117"/>
+      <c r="U4" s="117"/>
+      <c r="V4" s="117"/>
+      <c r="W4" s="117">
         <f ca="1">W5</f>
         <v>46298</v>
       </c>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="112"/>
-      <c r="Z4" s="112"/>
-      <c r="AA4" s="112"/>
-      <c r="AB4" s="112"/>
-      <c r="AC4" s="112"/>
-      <c r="AD4" s="112"/>
+      <c r="X4" s="117"/>
+      <c r="Y4" s="117"/>
+      <c r="Z4" s="117"/>
+      <c r="AA4" s="117"/>
+      <c r="AB4" s="117"/>
+      <c r="AC4" s="117"/>
+      <c r="AD4" s="117"/>
       <c r="AF4" s="38"/>
       <c r="AG4" s="39"/>
       <c r="AH4" s="39"/>
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1"/>
-      <c r="C5" s="91">
+      <c r="C5" s="118">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46292</v>
       </c>
-      <c r="D5" s="92"/>
-      <c r="E5" s="91">
+      <c r="D5" s="120"/>
+      <c r="E5" s="118">
         <f ca="1">C5+1</f>
         <v>46293</v>
       </c>
-      <c r="F5" s="92"/>
-      <c r="G5" s="91">
+      <c r="F5" s="120"/>
+      <c r="G5" s="118">
         <f ca="1">E5+1</f>
         <v>46294</v>
       </c>
-      <c r="H5" s="92"/>
-      <c r="I5" s="91">
+      <c r="H5" s="120"/>
+      <c r="I5" s="118">
         <f ca="1">G5+1</f>
         <v>46295</v>
       </c>
-      <c r="J5" s="92"/>
-      <c r="K5" s="91">
+      <c r="J5" s="120"/>
+      <c r="K5" s="118">
         <f ca="1">I5+1</f>
         <v>46296</v>
       </c>
-      <c r="L5" s="110"/>
-      <c r="M5" s="110"/>
+      <c r="L5" s="119"/>
+      <c r="M5" s="119"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="91">
+      <c r="O5" s="118">
         <f ca="1">K5+1</f>
         <v>46297</v>
       </c>
-      <c r="P5" s="110"/>
-      <c r="Q5" s="110"/>
-      <c r="R5" s="110"/>
-      <c r="S5" s="110"/>
-      <c r="T5" s="110"/>
-      <c r="U5" s="110"/>
-      <c r="V5" s="92"/>
-      <c r="W5" s="91">
+      <c r="P5" s="119"/>
+      <c r="Q5" s="119"/>
+      <c r="R5" s="119"/>
+      <c r="S5" s="119"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="120"/>
+      <c r="W5" s="118">
         <f ca="1">O5+1</f>
         <v>46298</v>
       </c>
-      <c r="X5" s="110"/>
-      <c r="Y5" s="110"/>
-      <c r="Z5" s="110"/>
-      <c r="AA5" s="110"/>
-      <c r="AB5" s="110"/>
-      <c r="AC5" s="110"/>
-      <c r="AD5" s="92"/>
+      <c r="X5" s="119"/>
+      <c r="Y5" s="119"/>
+      <c r="Z5" s="119"/>
+      <c r="AA5" s="119"/>
+      <c r="AB5" s="119"/>
+      <c r="AC5" s="119"/>
+      <c r="AD5" s="120"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
       <c r="AI5" s="41"/>
       <c r="AJ5" s="41"/>
     </row>
-    <row r="6" spans="1:36" s="43" customFormat="1" ht="131.69999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" s="43" customFormat="1" ht="131.69999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="42"/>
-      <c r="C6" s="102"/>
-      <c r="D6" s="103"/>
-      <c r="E6" s="102"/>
-      <c r="F6" s="103"/>
-      <c r="G6" s="102"/>
-      <c r="H6" s="103"/>
-      <c r="I6" s="102"/>
-      <c r="J6" s="103"/>
-      <c r="K6" s="104"/>
-      <c r="L6" s="105"/>
-      <c r="M6" s="105"/>
-      <c r="N6" s="106"/>
-      <c r="O6" s="104"/>
-      <c r="P6" s="105"/>
-      <c r="Q6" s="105"/>
-      <c r="R6" s="105"/>
-      <c r="S6" s="105"/>
-      <c r="T6" s="105"/>
-      <c r="U6" s="105"/>
-      <c r="V6" s="106"/>
-      <c r="W6" s="107" t="s">
+      <c r="C6" s="121"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="121"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="121"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="121"/>
+      <c r="J6" s="122"/>
+      <c r="K6" s="123"/>
+      <c r="L6" s="124"/>
+      <c r="M6" s="124"/>
+      <c r="N6" s="125"/>
+      <c r="O6" s="123"/>
+      <c r="P6" s="124"/>
+      <c r="Q6" s="124"/>
+      <c r="R6" s="124"/>
+      <c r="S6" s="124"/>
+      <c r="T6" s="124"/>
+      <c r="U6" s="124"/>
+      <c r="V6" s="125"/>
+      <c r="W6" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="X6" s="108"/>
-      <c r="Y6" s="108"/>
-      <c r="Z6" s="108"/>
-      <c r="AA6" s="108"/>
-      <c r="AB6" s="108"/>
-      <c r="AC6" s="108"/>
-      <c r="AD6" s="109"/>
+      <c r="X6" s="127"/>
+      <c r="Y6" s="127"/>
+      <c r="Z6" s="127"/>
+      <c r="AA6" s="127"/>
+      <c r="AB6" s="127"/>
+      <c r="AC6" s="127"/>
+      <c r="AD6" s="128"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
-    <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1"/>
-      <c r="C7" s="91">
+      <c r="C7" s="118">
         <f ca="1">W5+1</f>
         <v>46299</v>
       </c>
-      <c r="D7" s="92"/>
-      <c r="E7" s="99"/>
-      <c r="F7" s="100"/>
-      <c r="G7" s="99"/>
-      <c r="H7" s="100"/>
-      <c r="I7" s="99"/>
-      <c r="J7" s="100"/>
-      <c r="K7" s="99"/>
-      <c r="L7" s="101"/>
-      <c r="M7" s="101"/>
+      <c r="D7" s="120"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="130"/>
+      <c r="G7" s="129"/>
+      <c r="H7" s="130"/>
+      <c r="I7" s="129"/>
+      <c r="J7" s="130"/>
+      <c r="K7" s="129"/>
+      <c r="L7" s="131"/>
+      <c r="M7" s="131"/>
       <c r="N7" s="75"/>
-      <c r="O7" s="99"/>
-      <c r="P7" s="101"/>
-      <c r="Q7" s="101"/>
-      <c r="R7" s="101"/>
-      <c r="S7" s="101"/>
-      <c r="T7" s="101"/>
-      <c r="U7" s="101"/>
-      <c r="V7" s="100"/>
-      <c r="W7" s="99"/>
-      <c r="X7" s="101"/>
-      <c r="Y7" s="101"/>
-      <c r="Z7" s="101"/>
-      <c r="AA7" s="101"/>
-      <c r="AB7" s="101"/>
-      <c r="AC7" s="101"/>
-      <c r="AD7" s="100"/>
+      <c r="O7" s="129"/>
+      <c r="P7" s="131"/>
+      <c r="Q7" s="131"/>
+      <c r="R7" s="131"/>
+      <c r="S7" s="131"/>
+      <c r="T7" s="131"/>
+      <c r="U7" s="131"/>
+      <c r="V7" s="130"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="131"/>
+      <c r="Y7" s="131"/>
+      <c r="Z7" s="131"/>
+      <c r="AA7" s="131"/>
+      <c r="AB7" s="131"/>
+      <c r="AC7" s="131"/>
+      <c r="AD7" s="130"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="4"/>
-      <c r="C8" s="91"/>
-      <c r="D8" s="92"/>
-      <c r="E8" s="93">
+      <c r="C8" s="118"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="132">
         <f ca="1">C7+1</f>
         <v>46300</v>
       </c>
-      <c r="F8" s="94"/>
-      <c r="G8" s="93">
+      <c r="F8" s="133"/>
+      <c r="G8" s="132">
         <f ca="1">E8+1</f>
         <v>46301</v>
       </c>
-      <c r="H8" s="94"/>
-      <c r="I8" s="93">
+      <c r="H8" s="133"/>
+      <c r="I8" s="132">
         <f ca="1">G8+1</f>
         <v>46302</v>
       </c>
-      <c r="J8" s="94"/>
-      <c r="K8" s="93">
+      <c r="J8" s="133"/>
+      <c r="K8" s="132">
         <f ca="1">I8+1</f>
         <v>46303</v>
       </c>
-      <c r="L8" s="95"/>
-      <c r="M8" s="95"/>
+      <c r="L8" s="134"/>
+      <c r="M8" s="134"/>
       <c r="N8" s="50"/>
-      <c r="O8" s="93">
+      <c r="O8" s="132">
         <f ca="1">K8+1</f>
         <v>46304</v>
       </c>
-      <c r="P8" s="95"/>
-      <c r="Q8" s="95"/>
-      <c r="R8" s="95"/>
-      <c r="S8" s="95"/>
-      <c r="T8" s="95"/>
-      <c r="U8" s="95"/>
-      <c r="V8" s="94"/>
-      <c r="W8" s="93">
+      <c r="P8" s="134"/>
+      <c r="Q8" s="134"/>
+      <c r="R8" s="134"/>
+      <c r="S8" s="134"/>
+      <c r="T8" s="134"/>
+      <c r="U8" s="134"/>
+      <c r="V8" s="133"/>
+      <c r="W8" s="132">
         <f ca="1">O8+1</f>
         <v>46305</v>
       </c>
-      <c r="X8" s="95"/>
-      <c r="Y8" s="95"/>
-      <c r="Z8" s="95"/>
-      <c r="AA8" s="95"/>
-      <c r="AB8" s="95"/>
-      <c r="AC8" s="95"/>
-      <c r="AD8" s="94"/>
+      <c r="X8" s="134"/>
+      <c r="Y8" s="134"/>
+      <c r="Z8" s="134"/>
+      <c r="AA8" s="134"/>
+      <c r="AB8" s="134"/>
+      <c r="AC8" s="134"/>
+      <c r="AD8" s="133"/>
       <c r="AF8" s="4"/>
     </row>
-    <row r="9" spans="1:36" s="43" customFormat="1" ht="149.69999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" s="43" customFormat="1" ht="149.69999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="42"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="85"/>
-      <c r="E9" s="83" t="s">
+      <c r="C9" s="135"/>
+      <c r="D9" s="137"/>
+      <c r="E9" s="135" t="s">
+        <v>29</v>
+      </c>
+      <c r="F9" s="137"/>
+      <c r="G9" s="135" t="s">
+        <v>28</v>
+      </c>
+      <c r="H9" s="137"/>
+      <c r="I9" s="135"/>
+      <c r="J9" s="137"/>
+      <c r="K9" s="135" t="s">
         <v>30</v>
       </c>
-      <c r="F9" s="85"/>
-      <c r="G9" s="83" t="s">
-        <v>29</v>
-      </c>
-      <c r="H9" s="85"/>
-      <c r="I9" s="83"/>
-      <c r="J9" s="85"/>
-      <c r="K9" s="83" t="s">
-        <v>31</v>
-      </c>
-      <c r="L9" s="84"/>
-      <c r="M9" s="84"/>
-      <c r="N9" s="85"/>
-      <c r="O9" s="83" t="s">
-        <v>34</v>
-      </c>
-      <c r="P9" s="84"/>
-      <c r="Q9" s="84"/>
-      <c r="R9" s="84"/>
-      <c r="S9" s="84"/>
-      <c r="T9" s="84"/>
-      <c r="U9" s="84"/>
-      <c r="V9" s="85"/>
-      <c r="W9" s="83" t="s">
+      <c r="L9" s="136"/>
+      <c r="M9" s="136"/>
+      <c r="N9" s="137"/>
+      <c r="O9" s="135" t="s">
         <v>32</v>
       </c>
-      <c r="X9" s="84"/>
-      <c r="Y9" s="84"/>
-      <c r="Z9" s="84"/>
-      <c r="AA9" s="84"/>
-      <c r="AB9" s="84"/>
-      <c r="AC9" s="84"/>
-      <c r="AD9" s="85"/>
+      <c r="P9" s="136"/>
+      <c r="Q9" s="136"/>
+      <c r="R9" s="136"/>
+      <c r="S9" s="136"/>
+      <c r="T9" s="136"/>
+      <c r="U9" s="136"/>
+      <c r="V9" s="137"/>
+      <c r="W9" s="135"/>
+      <c r="X9" s="136"/>
+      <c r="Y9" s="136"/>
+      <c r="Z9" s="136"/>
+      <c r="AA9" s="136"/>
+      <c r="AB9" s="136"/>
+      <c r="AC9" s="136"/>
+      <c r="AD9" s="137"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
-    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="42"/>
-      <c r="C10" s="91">
+      <c r="C10" s="118">
         <f ca="1">W8+1</f>
         <v>46306</v>
       </c>
-      <c r="D10" s="92"/>
+      <c r="D10" s="120"/>
       <c r="E10" s="45"/>
       <c r="F10" s="75"/>
       <c r="G10" s="45"/>
@@ -4124,101 +4127,101 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="42"/>
     </row>
-    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="4"/>
-      <c r="C11" s="91"/>
-      <c r="D11" s="92"/>
-      <c r="E11" s="93">
+      <c r="C11" s="118"/>
+      <c r="D11" s="120"/>
+      <c r="E11" s="132">
         <f ca="1">C10+1</f>
         <v>46307</v>
       </c>
-      <c r="F11" s="94"/>
-      <c r="G11" s="93">
+      <c r="F11" s="133"/>
+      <c r="G11" s="132">
         <f ca="1">E11+1</f>
         <v>46308</v>
       </c>
-      <c r="H11" s="94"/>
-      <c r="I11" s="93">
+      <c r="H11" s="133"/>
+      <c r="I11" s="132">
         <f ca="1">G11+1</f>
         <v>46309</v>
       </c>
-      <c r="J11" s="94"/>
-      <c r="K11" s="93">
+      <c r="J11" s="133"/>
+      <c r="K11" s="132">
         <f ca="1">I11+1</f>
         <v>46310</v>
       </c>
-      <c r="L11" s="95"/>
-      <c r="M11" s="95"/>
+      <c r="L11" s="134"/>
+      <c r="M11" s="134"/>
       <c r="N11" s="50"/>
-      <c r="O11" s="93">
+      <c r="O11" s="132">
         <f ca="1">K11+1</f>
         <v>46311</v>
       </c>
-      <c r="P11" s="95"/>
-      <c r="Q11" s="95"/>
-      <c r="R11" s="95"/>
-      <c r="S11" s="95"/>
-      <c r="T11" s="95"/>
-      <c r="U11" s="95"/>
-      <c r="V11" s="94"/>
-      <c r="W11" s="93">
+      <c r="P11" s="134"/>
+      <c r="Q11" s="134"/>
+      <c r="R11" s="134"/>
+      <c r="S11" s="134"/>
+      <c r="T11" s="134"/>
+      <c r="U11" s="134"/>
+      <c r="V11" s="133"/>
+      <c r="W11" s="132">
         <f ca="1">O11+1</f>
         <v>46312</v>
       </c>
-      <c r="X11" s="95"/>
-      <c r="Y11" s="95"/>
-      <c r="Z11" s="95"/>
-      <c r="AA11" s="95"/>
-      <c r="AB11" s="95"/>
-      <c r="AC11" s="95"/>
-      <c r="AD11" s="94"/>
+      <c r="X11" s="134"/>
+      <c r="Y11" s="134"/>
+      <c r="Z11" s="134"/>
+      <c r="AA11" s="134"/>
+      <c r="AB11" s="134"/>
+      <c r="AC11" s="134"/>
+      <c r="AD11" s="133"/>
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:36" s="43" customFormat="1" ht="134.69999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" s="43" customFormat="1" ht="134.69999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="42"/>
-      <c r="C12" s="83"/>
-      <c r="D12" s="85"/>
-      <c r="E12" s="83"/>
-      <c r="F12" s="85"/>
-      <c r="G12" s="83"/>
-      <c r="H12" s="85"/>
-      <c r="I12" s="83"/>
-      <c r="J12" s="85"/>
-      <c r="K12" s="83"/>
-      <c r="L12" s="84"/>
-      <c r="M12" s="84"/>
-      <c r="N12" s="85"/>
-      <c r="O12" s="83" t="s">
-        <v>21</v>
-      </c>
-      <c r="P12" s="84"/>
-      <c r="Q12" s="84"/>
-      <c r="R12" s="84"/>
-      <c r="S12" s="84"/>
-      <c r="T12" s="84"/>
-      <c r="U12" s="84"/>
-      <c r="V12" s="85"/>
-      <c r="W12" s="98" t="s">
-        <v>33</v>
-      </c>
-      <c r="X12" s="84"/>
-      <c r="Y12" s="84"/>
-      <c r="Z12" s="84"/>
-      <c r="AA12" s="84"/>
-      <c r="AB12" s="84"/>
-      <c r="AC12" s="84"/>
-      <c r="AD12" s="85"/>
+      <c r="C12" s="135"/>
+      <c r="D12" s="137"/>
+      <c r="E12" s="135"/>
+      <c r="F12" s="137"/>
+      <c r="G12" s="135"/>
+      <c r="H12" s="137"/>
+      <c r="I12" s="135"/>
+      <c r="J12" s="137"/>
+      <c r="K12" s="135"/>
+      <c r="L12" s="136"/>
+      <c r="M12" s="136"/>
+      <c r="N12" s="137"/>
+      <c r="O12" s="135" t="s">
+        <v>41</v>
+      </c>
+      <c r="P12" s="136"/>
+      <c r="Q12" s="136"/>
+      <c r="R12" s="136"/>
+      <c r="S12" s="136"/>
+      <c r="T12" s="136"/>
+      <c r="U12" s="136"/>
+      <c r="V12" s="137"/>
+      <c r="W12" s="138" t="s">
+        <v>31</v>
+      </c>
+      <c r="X12" s="136"/>
+      <c r="Y12" s="136"/>
+      <c r="Z12" s="136"/>
+      <c r="AA12" s="136"/>
+      <c r="AB12" s="136"/>
+      <c r="AC12" s="136"/>
+      <c r="AD12" s="137"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
-    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="42"/>
-      <c r="C13" s="91">
+      <c r="C13" s="118">
         <f ca="1">W11+1</f>
         <v>46313</v>
       </c>
-      <c r="D13" s="92"/>
+      <c r="D13" s="120"/>
       <c r="E13" s="45"/>
       <c r="F13" s="75"/>
       <c r="G13" s="45"/>
@@ -4248,104 +4251,104 @@
       <c r="AE13" s="7"/>
       <c r="AF13" s="42"/>
     </row>
-    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="4"/>
-      <c r="C14" s="91"/>
-      <c r="D14" s="92"/>
-      <c r="E14" s="93">
+      <c r="C14" s="118"/>
+      <c r="D14" s="120"/>
+      <c r="E14" s="132">
         <f ca="1">C13+1</f>
         <v>46314</v>
       </c>
-      <c r="F14" s="94"/>
-      <c r="G14" s="93">
+      <c r="F14" s="133"/>
+      <c r="G14" s="132">
         <f ca="1">E14+1</f>
         <v>46315</v>
       </c>
-      <c r="H14" s="94"/>
-      <c r="I14" s="93">
+      <c r="H14" s="133"/>
+      <c r="I14" s="132">
         <f ca="1">G14+1</f>
         <v>46316</v>
       </c>
-      <c r="J14" s="94"/>
-      <c r="K14" s="93">
+      <c r="J14" s="133"/>
+      <c r="K14" s="132">
         <f ca="1">I14+1</f>
         <v>46317</v>
       </c>
-      <c r="L14" s="95"/>
-      <c r="M14" s="95"/>
+      <c r="L14" s="134"/>
+      <c r="M14" s="134"/>
       <c r="N14" s="50"/>
-      <c r="O14" s="93">
+      <c r="O14" s="132">
         <f ca="1">K14+1</f>
         <v>46318</v>
       </c>
-      <c r="P14" s="95"/>
-      <c r="Q14" s="95"/>
-      <c r="R14" s="95"/>
-      <c r="S14" s="95"/>
-      <c r="T14" s="95"/>
-      <c r="U14" s="95"/>
-      <c r="V14" s="94"/>
-      <c r="W14" s="93">
+      <c r="P14" s="134"/>
+      <c r="Q14" s="134"/>
+      <c r="R14" s="134"/>
+      <c r="S14" s="134"/>
+      <c r="T14" s="134"/>
+      <c r="U14" s="134"/>
+      <c r="V14" s="133"/>
+      <c r="W14" s="132">
         <f ca="1">O14+1</f>
         <v>46319</v>
       </c>
-      <c r="X14" s="95"/>
-      <c r="Y14" s="95"/>
-      <c r="Z14" s="95"/>
-      <c r="AA14" s="95"/>
-      <c r="AB14" s="95"/>
-      <c r="AC14" s="95"/>
-      <c r="AD14" s="94"/>
+      <c r="X14" s="134"/>
+      <c r="Y14" s="134"/>
+      <c r="Z14" s="134"/>
+      <c r="AA14" s="134"/>
+      <c r="AB14" s="134"/>
+      <c r="AC14" s="134"/>
+      <c r="AD14" s="133"/>
       <c r="AF14" s="4"/>
     </row>
-    <row r="15" spans="1:36" s="43" customFormat="1" ht="140.69999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" s="43" customFormat="1" ht="140.69999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="42"/>
-      <c r="C15" s="98" t="s">
+      <c r="C15" s="138" t="s">
+        <v>33</v>
+      </c>
+      <c r="D15" s="137"/>
+      <c r="E15" s="135"/>
+      <c r="F15" s="137"/>
+      <c r="G15" s="135"/>
+      <c r="H15" s="137"/>
+      <c r="I15" s="138" t="s">
+        <v>37</v>
+      </c>
+      <c r="J15" s="137"/>
+      <c r="K15" s="135"/>
+      <c r="L15" s="136"/>
+      <c r="M15" s="136"/>
+      <c r="N15" s="137"/>
+      <c r="O15" s="135" t="s">
         <v>35</v>
       </c>
-      <c r="D15" s="85"/>
-      <c r="E15" s="83"/>
-      <c r="F15" s="85"/>
-      <c r="G15" s="83"/>
-      <c r="H15" s="85"/>
-      <c r="I15" s="98" t="s">
-        <v>39</v>
-      </c>
-      <c r="J15" s="85"/>
-      <c r="K15" s="83"/>
-      <c r="L15" s="84"/>
-      <c r="M15" s="84"/>
-      <c r="N15" s="85"/>
-      <c r="O15" s="83" t="s">
-        <v>37</v>
-      </c>
-      <c r="P15" s="84"/>
-      <c r="Q15" s="84"/>
-      <c r="R15" s="84"/>
-      <c r="S15" s="84"/>
-      <c r="T15" s="84"/>
-      <c r="U15" s="84"/>
-      <c r="V15" s="85"/>
-      <c r="W15" s="98" t="s">
-        <v>38</v>
-      </c>
-      <c r="X15" s="84"/>
-      <c r="Y15" s="84"/>
-      <c r="Z15" s="84"/>
-      <c r="AA15" s="84"/>
-      <c r="AB15" s="84"/>
-      <c r="AC15" s="84"/>
-      <c r="AD15" s="85"/>
+      <c r="P15" s="136"/>
+      <c r="Q15" s="136"/>
+      <c r="R15" s="136"/>
+      <c r="S15" s="136"/>
+      <c r="T15" s="136"/>
+      <c r="U15" s="136"/>
+      <c r="V15" s="137"/>
+      <c r="W15" s="138" t="s">
+        <v>36</v>
+      </c>
+      <c r="X15" s="136"/>
+      <c r="Y15" s="136"/>
+      <c r="Z15" s="136"/>
+      <c r="AA15" s="136"/>
+      <c r="AB15" s="136"/>
+      <c r="AC15" s="136"/>
+      <c r="AD15" s="137"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
-    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="42"/>
-      <c r="C16" s="91">
+      <c r="C16" s="118">
         <f ca="1">W14+1</f>
         <v>46320</v>
       </c>
-      <c r="D16" s="92"/>
+      <c r="D16" s="120"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
@@ -4375,101 +4378,101 @@
       <c r="AE16" s="7"/>
       <c r="AF16" s="42"/>
     </row>
-    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4"/>
-      <c r="C17" s="91"/>
-      <c r="D17" s="92"/>
-      <c r="E17" s="93">
+      <c r="C17" s="118"/>
+      <c r="D17" s="120"/>
+      <c r="E17" s="132">
         <f ca="1">C16+1</f>
         <v>46321</v>
       </c>
-      <c r="F17" s="94"/>
-      <c r="G17" s="93">
+      <c r="F17" s="133"/>
+      <c r="G17" s="132">
         <f ca="1">E17+1</f>
         <v>46322</v>
       </c>
-      <c r="H17" s="94"/>
-      <c r="I17" s="93">
+      <c r="H17" s="133"/>
+      <c r="I17" s="132">
         <f ca="1">G17+1</f>
         <v>46323</v>
       </c>
-      <c r="J17" s="94"/>
-      <c r="K17" s="93">
+      <c r="J17" s="133"/>
+      <c r="K17" s="132">
         <f ca="1">I17+1</f>
         <v>46324</v>
       </c>
-      <c r="L17" s="95"/>
-      <c r="M17" s="95"/>
+      <c r="L17" s="134"/>
+      <c r="M17" s="134"/>
       <c r="N17" s="50"/>
-      <c r="O17" s="93">
+      <c r="O17" s="132">
         <f ca="1">K17+1</f>
         <v>46325</v>
       </c>
-      <c r="P17" s="95"/>
-      <c r="Q17" s="95"/>
-      <c r="R17" s="95"/>
-      <c r="S17" s="95"/>
-      <c r="T17" s="95"/>
-      <c r="U17" s="95"/>
-      <c r="V17" s="94"/>
-      <c r="W17" s="93">
+      <c r="P17" s="134"/>
+      <c r="Q17" s="134"/>
+      <c r="R17" s="134"/>
+      <c r="S17" s="134"/>
+      <c r="T17" s="134"/>
+      <c r="U17" s="134"/>
+      <c r="V17" s="133"/>
+      <c r="W17" s="132">
         <f ca="1">O17+1</f>
         <v>46326</v>
       </c>
-      <c r="X17" s="95"/>
-      <c r="Y17" s="95"/>
-      <c r="Z17" s="95"/>
-      <c r="AA17" s="95"/>
-      <c r="AB17" s="95"/>
-      <c r="AC17" s="95"/>
-      <c r="AD17" s="94"/>
+      <c r="X17" s="134"/>
+      <c r="Y17" s="134"/>
+      <c r="Z17" s="134"/>
+      <c r="AA17" s="134"/>
+      <c r="AB17" s="134"/>
+      <c r="AC17" s="134"/>
+      <c r="AD17" s="133"/>
       <c r="AF17" s="4"/>
     </row>
-    <row r="18" spans="1:42" s="43" customFormat="1" ht="149.69999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:42" s="43" customFormat="1" ht="149.69999999999999" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="42"/>
-      <c r="C18" s="83"/>
-      <c r="D18" s="85"/>
-      <c r="E18" s="83" t="s">
-        <v>36</v>
-      </c>
-      <c r="F18" s="85"/>
-      <c r="G18" s="83"/>
-      <c r="H18" s="85"/>
-      <c r="I18" s="83"/>
-      <c r="J18" s="85"/>
-      <c r="K18" s="90" t="s">
-        <v>40</v>
-      </c>
-      <c r="L18" s="84"/>
-      <c r="M18" s="84"/>
+      <c r="C18" s="135"/>
+      <c r="D18" s="137"/>
+      <c r="E18" s="135" t="s">
+        <v>34</v>
+      </c>
+      <c r="F18" s="137"/>
+      <c r="G18" s="135"/>
+      <c r="H18" s="137"/>
+      <c r="I18" s="135"/>
+      <c r="J18" s="137"/>
+      <c r="K18" s="141" t="s">
+        <v>38</v>
+      </c>
+      <c r="L18" s="136"/>
+      <c r="M18" s="136"/>
       <c r="N18" s="82"/>
-      <c r="O18" s="83"/>
-      <c r="P18" s="84"/>
-      <c r="Q18" s="84"/>
-      <c r="R18" s="84"/>
-      <c r="S18" s="84"/>
-      <c r="T18" s="84"/>
-      <c r="U18" s="84"/>
-      <c r="V18" s="85"/>
-      <c r="W18" s="83"/>
-      <c r="X18" s="84"/>
-      <c r="Y18" s="84"/>
-      <c r="Z18" s="84"/>
-      <c r="AA18" s="84"/>
-      <c r="AB18" s="84"/>
-      <c r="AC18" s="84"/>
-      <c r="AD18" s="85"/>
+      <c r="O18" s="135"/>
+      <c r="P18" s="136"/>
+      <c r="Q18" s="136"/>
+      <c r="R18" s="136"/>
+      <c r="S18" s="136"/>
+      <c r="T18" s="136"/>
+      <c r="U18" s="136"/>
+      <c r="V18" s="137"/>
+      <c r="W18" s="135"/>
+      <c r="X18" s="136"/>
+      <c r="Y18" s="136"/>
+      <c r="Z18" s="136"/>
+      <c r="AA18" s="136"/>
+      <c r="AB18" s="136"/>
+      <c r="AC18" s="136"/>
+      <c r="AD18" s="137"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
-    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="42"/>
-      <c r="C19" s="91">
+      <c r="C19" s="118">
         <f ca="1">W17+1</f>
         <v>46327</v>
       </c>
-      <c r="D19" s="92"/>
+      <c r="D19" s="120"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
@@ -4499,91 +4502,91 @@
       <c r="AE19" s="7"/>
       <c r="AF19" s="42"/>
     </row>
-    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4"/>
-      <c r="C20" s="91"/>
-      <c r="D20" s="92"/>
-      <c r="E20" s="93">
+      <c r="C20" s="118"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="132">
         <f ca="1">C19+1</f>
         <v>46328</v>
       </c>
-      <c r="F20" s="94"/>
-      <c r="G20" s="93">
+      <c r="F20" s="133"/>
+      <c r="G20" s="132">
         <f ca="1">E20+1</f>
         <v>46329</v>
       </c>
-      <c r="H20" s="94"/>
-      <c r="I20" s="93">
+      <c r="H20" s="133"/>
+      <c r="I20" s="132">
         <f ca="1">G20+1</f>
         <v>46330</v>
       </c>
-      <c r="J20" s="94"/>
-      <c r="K20" s="93">
+      <c r="J20" s="133"/>
+      <c r="K20" s="132">
         <f ca="1">I20+1</f>
         <v>46331</v>
       </c>
-      <c r="L20" s="95"/>
-      <c r="M20" s="95"/>
+      <c r="L20" s="134"/>
+      <c r="M20" s="134"/>
       <c r="N20" s="50"/>
-      <c r="O20" s="93">
+      <c r="O20" s="132">
         <f ca="1">K20+1</f>
         <v>46332</v>
       </c>
-      <c r="P20" s="95"/>
-      <c r="Q20" s="95"/>
-      <c r="R20" s="95"/>
-      <c r="S20" s="95"/>
-      <c r="T20" s="95"/>
-      <c r="U20" s="95"/>
-      <c r="V20" s="94"/>
-      <c r="W20" s="93">
+      <c r="P20" s="134"/>
+      <c r="Q20" s="134"/>
+      <c r="R20" s="134"/>
+      <c r="S20" s="134"/>
+      <c r="T20" s="134"/>
+      <c r="U20" s="134"/>
+      <c r="V20" s="133"/>
+      <c r="W20" s="132">
         <f ca="1">O20+1</f>
         <v>46333</v>
       </c>
-      <c r="X20" s="95"/>
-      <c r="Y20" s="95"/>
-      <c r="Z20" s="95"/>
-      <c r="AA20" s="95"/>
-      <c r="AB20" s="95"/>
-      <c r="AC20" s="95"/>
-      <c r="AD20" s="94"/>
+      <c r="X20" s="134"/>
+      <c r="Y20" s="134"/>
+      <c r="Z20" s="134"/>
+      <c r="AA20" s="134"/>
+      <c r="AB20" s="134"/>
+      <c r="AC20" s="134"/>
+      <c r="AD20" s="133"/>
       <c r="AF20" s="4"/>
     </row>
-    <row r="21" spans="1:42" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:42" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="42"/>
-      <c r="C21" s="96"/>
-      <c r="D21" s="97"/>
-      <c r="E21" s="96"/>
-      <c r="F21" s="97"/>
-      <c r="G21" s="96"/>
-      <c r="H21" s="97"/>
-      <c r="I21" s="96"/>
-      <c r="J21" s="97"/>
-      <c r="K21" s="96"/>
-      <c r="L21" s="141"/>
-      <c r="M21" s="141"/>
+      <c r="C21" s="111"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="113"/>
+      <c r="K21" s="111"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
       <c r="N21" s="44"/>
-      <c r="O21" s="96"/>
-      <c r="P21" s="141"/>
-      <c r="Q21" s="141"/>
-      <c r="R21" s="141"/>
-      <c r="S21" s="141"/>
-      <c r="T21" s="141"/>
-      <c r="U21" s="141"/>
-      <c r="V21" s="97"/>
-      <c r="W21" s="96"/>
-      <c r="X21" s="141"/>
-      <c r="Y21" s="141"/>
-      <c r="Z21" s="141"/>
-      <c r="AA21" s="141"/>
-      <c r="AB21" s="141"/>
-      <c r="AC21" s="141"/>
-      <c r="AD21" s="97"/>
+      <c r="O21" s="111"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="112"/>
+      <c r="R21" s="112"/>
+      <c r="S21" s="112"/>
+      <c r="T21" s="112"/>
+      <c r="U21" s="112"/>
+      <c r="V21" s="113"/>
+      <c r="W21" s="111"/>
+      <c r="X21" s="112"/>
+      <c r="Y21" s="112"/>
+      <c r="Z21" s="112"/>
+      <c r="AA21" s="112"/>
+      <c r="AB21" s="112"/>
+      <c r="AC21" s="112"/>
+      <c r="AD21" s="113"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
     </row>
-    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="4"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52"/>
@@ -4615,7 +4618,7 @@
       <c r="AD22" s="55"/>
       <c r="AF22" s="4"/>
     </row>
-    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="56"/>
@@ -4649,61 +4652,61 @@
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
     </row>
-    <row r="24" spans="1:42" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:42" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="1"/>
       <c r="M24" s="1"/>
       <c r="AF24" s="1"/>
     </row>
-    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="1"/>
-      <c r="C25" s="86" t="s">
+      <c r="C25" s="139" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="86"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="86"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="86"/>
-      <c r="J25" s="86"/>
-      <c r="K25" s="86"/>
+      <c r="D25" s="139"/>
+      <c r="E25" s="139"/>
+      <c r="F25" s="139"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="139"/>
+      <c r="I25" s="139"/>
+      <c r="J25" s="139"/>
+      <c r="K25" s="139"/>
       <c r="L25" s="60"/>
       <c r="M25" s="1"/>
-      <c r="O25" s="87">
+      <c r="O25" s="140">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)-1,1)</f>
         <v>46266</v>
       </c>
-      <c r="P25" s="87"/>
-      <c r="Q25" s="87"/>
-      <c r="R25" s="87"/>
-      <c r="S25" s="87"/>
-      <c r="T25" s="87"/>
-      <c r="U25" s="87"/>
+      <c r="P25" s="140"/>
+      <c r="Q25" s="140"/>
+      <c r="R25" s="140"/>
+      <c r="S25" s="140"/>
+      <c r="T25" s="140"/>
+      <c r="U25" s="140"/>
       <c r="V25" s="61"/>
       <c r="W25" s="61"/>
-      <c r="X25" s="87">
+      <c r="X25" s="140">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)+1,1)</f>
         <v>46327</v>
       </c>
-      <c r="Y25" s="87"/>
-      <c r="Z25" s="87"/>
-      <c r="AA25" s="87"/>
-      <c r="AB25" s="87"/>
-      <c r="AC25" s="87"/>
-      <c r="AD25" s="87"/>
+      <c r="Y25" s="140"/>
+      <c r="Z25" s="140"/>
+      <c r="AA25" s="140"/>
+      <c r="AB25" s="140"/>
+      <c r="AC25" s="140"/>
+      <c r="AD25" s="140"/>
       <c r="AF25" s="1"/>
     </row>
-    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="1"/>
-      <c r="C26" s="86"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="86"/>
-      <c r="G26" s="86"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="86"/>
-      <c r="J26" s="86"/>
-      <c r="K26" s="86"/>
+      <c r="C26" s="139"/>
+      <c r="D26" s="139"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="139"/>
+      <c r="H26" s="139"/>
+      <c r="I26" s="139"/>
+      <c r="J26" s="139"/>
+      <c r="K26" s="139"/>
       <c r="L26" s="60"/>
       <c r="M26" s="1"/>
       <c r="O26" s="62" t="str">
@@ -4766,17 +4769,17 @@
       </c>
       <c r="AF26" s="1"/>
     </row>
-    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="1"/>
-      <c r="C27" s="88"/>
-      <c r="D27" s="88"/>
-      <c r="E27" s="88"/>
-      <c r="F27" s="88"/>
-      <c r="G27" s="88"/>
-      <c r="H27" s="88"/>
-      <c r="I27" s="88"/>
-      <c r="J27" s="88"/>
-      <c r="K27" s="88"/>
+      <c r="C27" s="115"/>
+      <c r="D27" s="115"/>
+      <c r="E27" s="115"/>
+      <c r="F27" s="115"/>
+      <c r="G27" s="115"/>
+      <c r="H27" s="115"/>
+      <c r="I27" s="115"/>
+      <c r="J27" s="115"/>
+      <c r="K27" s="115"/>
       <c r="M27" s="1"/>
       <c r="O27" s="64" t="str">
         <f t="shared" ref="O27:U32" ca="1" si="0">IF(MONTH($O$25)&lt;&gt;MONTH($O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1)),"",$O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1))</f>
@@ -4838,17 +4841,17 @@
       </c>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="1"/>
-      <c r="C28" s="89"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="89"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="89"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="89"/>
-      <c r="K28" s="89"/>
+      <c r="C28" s="114"/>
+      <c r="D28" s="114"/>
+      <c r="E28" s="114"/>
+      <c r="F28" s="114"/>
+      <c r="G28" s="114"/>
+      <c r="H28" s="114"/>
+      <c r="I28" s="114"/>
+      <c r="J28" s="114"/>
+      <c r="K28" s="114"/>
       <c r="M28" s="1"/>
       <c r="O28" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -4910,17 +4913,17 @@
       </c>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="1"/>
-      <c r="C29" s="88"/>
-      <c r="D29" s="88"/>
-      <c r="E29" s="88"/>
-      <c r="F29" s="88"/>
-      <c r="G29" s="88"/>
-      <c r="H29" s="88"/>
-      <c r="I29" s="88"/>
-      <c r="J29" s="88"/>
-      <c r="K29" s="88"/>
+      <c r="C29" s="115"/>
+      <c r="D29" s="115"/>
+      <c r="E29" s="115"/>
+      <c r="F29" s="115"/>
+      <c r="G29" s="115"/>
+      <c r="H29" s="115"/>
+      <c r="I29" s="115"/>
+      <c r="J29" s="115"/>
+      <c r="K29" s="115"/>
       <c r="M29" s="1"/>
       <c r="O29" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -4982,17 +4985,17 @@
       </c>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="1"/>
-      <c r="C30" s="89"/>
-      <c r="D30" s="89"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="89"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="89"/>
-      <c r="K30" s="89"/>
+      <c r="C30" s="114"/>
+      <c r="D30" s="114"/>
+      <c r="E30" s="114"/>
+      <c r="F30" s="114"/>
+      <c r="G30" s="114"/>
+      <c r="H30" s="114"/>
+      <c r="I30" s="114"/>
+      <c r="J30" s="114"/>
+      <c r="K30" s="114"/>
       <c r="M30" s="1"/>
       <c r="O30" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -5054,17 +5057,17 @@
       </c>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="1"/>
-      <c r="C31" s="88"/>
-      <c r="D31" s="88"/>
-      <c r="E31" s="88"/>
-      <c r="F31" s="88"/>
-      <c r="G31" s="88"/>
-      <c r="H31" s="88"/>
-      <c r="I31" s="88"/>
-      <c r="J31" s="88"/>
-      <c r="K31" s="88"/>
+      <c r="C31" s="115"/>
+      <c r="D31" s="115"/>
+      <c r="E31" s="115"/>
+      <c r="F31" s="115"/>
+      <c r="G31" s="115"/>
+      <c r="H31" s="115"/>
+      <c r="I31" s="115"/>
+      <c r="J31" s="115"/>
+      <c r="K31" s="115"/>
       <c r="M31" s="1"/>
       <c r="O31" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -5126,7 +5129,7 @@
       </c>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.45">
       <c r="A32" s="1"/>
       <c r="M32" s="1"/>
       <c r="O32" s="64" t="str">
@@ -5189,7 +5192,7 @@
       </c>
       <c r="AF32" s="1"/>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A33" s="1"/>
       <c r="M33" s="1"/>
       <c r="O33" s="64"/>
@@ -5210,7 +5213,7 @@
       <c r="AD33" s="65"/>
       <c r="AF33" s="1"/>
     </row>
-    <row r="34" spans="1:32" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -5244,156 +5247,69 @@
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
     </row>
-    <row r="38" spans="1:32" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="113" t="s">
-        <v>25</v>
-      </c>
-      <c r="E39" s="114"/>
-      <c r="F39" s="115"/>
-      <c r="G39" s="119">
+    <row r="38" spans="1:32" ht="12.9" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D39" s="83" t="s">
+        <v>24</v>
+      </c>
+      <c r="E39" s="84"/>
+      <c r="F39" s="85"/>
+      <c r="G39" s="89">
         <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
         <v>5</v>
       </c>
-      <c r="H39" s="120"/>
-      <c r="I39" s="113" t="s">
-        <v>28</v>
-      </c>
-      <c r="J39" s="123"/>
-      <c r="K39" s="125" t="s">
-        <v>26</v>
-      </c>
-      <c r="L39" s="126"/>
-      <c r="M39" s="129">
+      <c r="H39" s="90"/>
+      <c r="I39" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="J39" s="93"/>
+      <c r="K39" s="95" t="s">
+        <v>25</v>
+      </c>
+      <c r="L39" s="96"/>
+      <c r="M39" s="99">
         <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
         <v>5.9999999999999973</v>
       </c>
-      <c r="N39" s="130"/>
-      <c r="O39" s="130"/>
-      <c r="P39" s="130"/>
-      <c r="Q39" s="130"/>
-      <c r="R39" s="131"/>
-      <c r="S39" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="T39" s="136"/>
-      <c r="U39" s="136"/>
-      <c r="V39" s="136"/>
-      <c r="W39" s="136"/>
-      <c r="X39" s="137"/>
-    </row>
-    <row r="40" spans="1:32" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D40" s="116"/>
-      <c r="E40" s="117"/>
-      <c r="F40" s="118"/>
-      <c r="G40" s="121"/>
-      <c r="H40" s="122"/>
-      <c r="I40" s="116"/>
-      <c r="J40" s="124"/>
-      <c r="K40" s="127"/>
-      <c r="L40" s="128"/>
-      <c r="M40" s="132"/>
-      <c r="N40" s="133"/>
-      <c r="O40" s="133"/>
-      <c r="P40" s="133"/>
-      <c r="Q40" s="133"/>
-      <c r="R40" s="134"/>
-      <c r="S40" s="138"/>
-      <c r="T40" s="139"/>
-      <c r="U40" s="139"/>
-      <c r="V40" s="139"/>
-      <c r="W40" s="139"/>
-      <c r="X40" s="140"/>
+      <c r="N39" s="100"/>
+      <c r="O39" s="100"/>
+      <c r="P39" s="100"/>
+      <c r="Q39" s="100"/>
+      <c r="R39" s="101"/>
+      <c r="S39" s="105" t="s">
+        <v>26</v>
+      </c>
+      <c r="T39" s="106"/>
+      <c r="U39" s="106"/>
+      <c r="V39" s="106"/>
+      <c r="W39" s="106"/>
+      <c r="X39" s="107"/>
+    </row>
+    <row r="40" spans="1:32" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D40" s="86"/>
+      <c r="E40" s="87"/>
+      <c r="F40" s="88"/>
+      <c r="G40" s="91"/>
+      <c r="H40" s="92"/>
+      <c r="I40" s="86"/>
+      <c r="J40" s="94"/>
+      <c r="K40" s="97"/>
+      <c r="L40" s="98"/>
+      <c r="M40" s="102"/>
+      <c r="N40" s="103"/>
+      <c r="O40" s="103"/>
+      <c r="P40" s="103"/>
+      <c r="Q40" s="103"/>
+      <c r="R40" s="104"/>
+      <c r="S40" s="108"/>
+      <c r="T40" s="109"/>
+      <c r="U40" s="109"/>
+      <c r="V40" s="109"/>
+      <c r="W40" s="109"/>
+      <c r="X40" s="110"/>
     </row>
   </sheetData>
   <mergeCells count="110">
-    <mergeCell ref="D39:F40"/>
-    <mergeCell ref="G39:H40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="K39:L40"/>
-    <mergeCell ref="M39:R40"/>
-    <mergeCell ref="S39:X40"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="O21:V21"/>
-    <mergeCell ref="W21:AD21"/>
-    <mergeCell ref="C30:K31"/>
-    <mergeCell ref="C2:AD2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="W5:AD5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:V6"/>
-    <mergeCell ref="W6:AD6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="O5:V5"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="W7:AD7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="O8:V8"/>
-    <mergeCell ref="W8:AD8"/>
-    <mergeCell ref="O7:V7"/>
-    <mergeCell ref="W9:AD9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="O11:V11"/>
-    <mergeCell ref="W11:AD11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:V9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="W12:AD12"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="O14:V14"/>
-    <mergeCell ref="W14:AD14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="O12:V12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="W15:AD15"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="O17:V17"/>
-    <mergeCell ref="W17:AD17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="O15:V15"/>
-    <mergeCell ref="K15:N15"/>
     <mergeCell ref="W18:AD18"/>
     <mergeCell ref="C25:K26"/>
     <mergeCell ref="O25:U25"/>
@@ -5417,6 +5333,93 @@
     <mergeCell ref="E21:F21"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="I21:J21"/>
+    <mergeCell ref="W15:AD15"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="O17:V17"/>
+    <mergeCell ref="W17:AD17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="O15:V15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="W12:AD12"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O14:V14"/>
+    <mergeCell ref="W14:AD14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="O12:V12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="W9:AD9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="O11:V11"/>
+    <mergeCell ref="W11:AD11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:V9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="W7:AD7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="O8:V8"/>
+    <mergeCell ref="W8:AD8"/>
+    <mergeCell ref="O7:V7"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:V6"/>
+    <mergeCell ref="W6:AD6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="O5:V5"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="C2:AD2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="W5:AD5"/>
+    <mergeCell ref="D39:F40"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="K39:L40"/>
+    <mergeCell ref="M39:R40"/>
+    <mergeCell ref="S39:X40"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="O21:V21"/>
+    <mergeCell ref="W21:AD21"/>
+    <mergeCell ref="C30:K31"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 E5 G5 I5 K5:L5 O5 W5 C7 E8 G8 I8 K8:L8 O8 W8 C10 E11 G11 I11 K11:L11 O11 W11 C13 E14 G14 I14 K14:L14 O14 W14 C16 E17 G17 I17 K17:L17 O17 W17">
     <cfRule type="expression" dxfId="7" priority="3">
@@ -5455,7 +5458,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AP39"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.2" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="12.6" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="3" width="5.5546875" style="3" customWidth="1"/>
     <col min="4" max="4" width="15.5546875" style="3" customWidth="1"/>
@@ -5473,7 +5476,7 @@
     <col min="35" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5507,42 +5510,42 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="2.15">
       <c r="A2" s="29"/>
-      <c r="C2" s="111">
+      <c r="C2" s="116">
         <f ca="1">DATE(About!P8,11,1)</f>
         <v>46327</v>
       </c>
-      <c r="D2" s="111"/>
-      <c r="E2" s="111"/>
-      <c r="F2" s="111"/>
-      <c r="G2" s="111"/>
-      <c r="H2" s="111"/>
-      <c r="I2" s="111"/>
-      <c r="J2" s="111"/>
-      <c r="K2" s="111"/>
-      <c r="L2" s="111"/>
-      <c r="M2" s="111"/>
-      <c r="N2" s="111"/>
-      <c r="O2" s="111"/>
-      <c r="P2" s="111"/>
-      <c r="Q2" s="111"/>
-      <c r="R2" s="111"/>
-      <c r="S2" s="111"/>
-      <c r="T2" s="111"/>
-      <c r="U2" s="111"/>
-      <c r="V2" s="111"/>
-      <c r="W2" s="111"/>
-      <c r="X2" s="111"/>
-      <c r="Y2" s="111"/>
-      <c r="Z2" s="111"/>
-      <c r="AA2" s="111"/>
-      <c r="AB2" s="111"/>
-      <c r="AC2" s="111"/>
-      <c r="AD2" s="111"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="116"/>
+      <c r="P2" s="116"/>
+      <c r="Q2" s="116"/>
+      <c r="R2" s="116"/>
+      <c r="S2" s="116"/>
+      <c r="T2" s="116"/>
+      <c r="U2" s="116"/>
+      <c r="V2" s="116"/>
+      <c r="W2" s="116"/>
+      <c r="X2" s="116"/>
+      <c r="Y2" s="116"/>
+      <c r="Z2" s="116"/>
+      <c r="AA2" s="116"/>
+      <c r="AB2" s="116"/>
+      <c r="AC2" s="116"/>
+      <c r="AD2" s="116"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="2.15">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -5562,219 +5565,219 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A4" s="35"/>
-      <c r="C4" s="112">
+      <c r="C4" s="117">
         <f ca="1">C5</f>
         <v>46327</v>
       </c>
-      <c r="D4" s="112"/>
-      <c r="E4" s="112">
+      <c r="D4" s="117"/>
+      <c r="E4" s="117">
         <f ca="1">E5</f>
         <v>46328</v>
       </c>
-      <c r="F4" s="112"/>
-      <c r="G4" s="112">
+      <c r="F4" s="117"/>
+      <c r="G4" s="117">
         <f ca="1">G5</f>
         <v>46329</v>
       </c>
-      <c r="H4" s="112"/>
-      <c r="I4" s="112">
+      <c r="H4" s="117"/>
+      <c r="I4" s="117">
         <f ca="1">I5</f>
         <v>46330</v>
       </c>
-      <c r="J4" s="112"/>
-      <c r="K4" s="112">
+      <c r="J4" s="117"/>
+      <c r="K4" s="117">
         <f ca="1">K5</f>
         <v>46331</v>
       </c>
-      <c r="L4" s="112"/>
-      <c r="M4" s="112"/>
+      <c r="L4" s="117"/>
+      <c r="M4" s="117"/>
       <c r="N4" s="37"/>
-      <c r="O4" s="112">
+      <c r="O4" s="117">
         <f ca="1">O5</f>
         <v>46332</v>
       </c>
-      <c r="P4" s="112"/>
-      <c r="Q4" s="112"/>
-      <c r="R4" s="112"/>
-      <c r="S4" s="112"/>
-      <c r="T4" s="112"/>
-      <c r="U4" s="112"/>
-      <c r="V4" s="112"/>
-      <c r="W4" s="112">
+      <c r="P4" s="117"/>
+      <c r="Q4" s="117"/>
+      <c r="R4" s="117"/>
+      <c r="S4" s="117"/>
+      <c r="T4" s="117"/>
+      <c r="U4" s="117"/>
+      <c r="V4" s="117"/>
+      <c r="W4" s="117">
         <f ca="1">W5</f>
         <v>46333</v>
       </c>
-      <c r="X4" s="112"/>
-      <c r="Y4" s="112"/>
-      <c r="Z4" s="112"/>
-      <c r="AA4" s="112"/>
-      <c r="AB4" s="112"/>
-      <c r="AC4" s="112"/>
-      <c r="AD4" s="112"/>
+      <c r="X4" s="117"/>
+      <c r="Y4" s="117"/>
+      <c r="Z4" s="117"/>
+      <c r="AA4" s="117"/>
+      <c r="AB4" s="117"/>
+      <c r="AC4" s="117"/>
+      <c r="AD4" s="117"/>
       <c r="AF4" s="38"/>
       <c r="AG4" s="39"/>
       <c r="AH4" s="39"/>
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1"/>
-      <c r="C5" s="91">
+      <c r="C5" s="118">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46327</v>
       </c>
-      <c r="D5" s="92"/>
-      <c r="E5" s="91">
+      <c r="D5" s="120"/>
+      <c r="E5" s="118">
         <f ca="1">C5+1</f>
         <v>46328</v>
       </c>
-      <c r="F5" s="92"/>
-      <c r="G5" s="91">
+      <c r="F5" s="120"/>
+      <c r="G5" s="118">
         <f ca="1">E5+1</f>
         <v>46329</v>
       </c>
-      <c r="H5" s="92"/>
-      <c r="I5" s="91">
+      <c r="H5" s="120"/>
+      <c r="I5" s="118">
         <f ca="1">G5+1</f>
         <v>46330</v>
       </c>
-      <c r="J5" s="92"/>
-      <c r="K5" s="91">
+      <c r="J5" s="120"/>
+      <c r="K5" s="118">
         <f ca="1">I5+1</f>
         <v>46331</v>
       </c>
-      <c r="L5" s="110"/>
-      <c r="M5" s="110"/>
+      <c r="L5" s="119"/>
+      <c r="M5" s="119"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="91">
+      <c r="O5" s="118">
         <f ca="1">K5+1</f>
         <v>46332</v>
       </c>
-      <c r="P5" s="110"/>
-      <c r="Q5" s="110"/>
-      <c r="R5" s="110"/>
-      <c r="S5" s="110"/>
-      <c r="T5" s="110"/>
-      <c r="U5" s="110"/>
-      <c r="V5" s="92"/>
-      <c r="W5" s="91">
+      <c r="P5" s="119"/>
+      <c r="Q5" s="119"/>
+      <c r="R5" s="119"/>
+      <c r="S5" s="119"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="120"/>
+      <c r="W5" s="118">
         <f ca="1">O5+1</f>
         <v>46333</v>
       </c>
-      <c r="X5" s="110"/>
-      <c r="Y5" s="110"/>
-      <c r="Z5" s="110"/>
-      <c r="AA5" s="110"/>
-      <c r="AB5" s="110"/>
-      <c r="AC5" s="110"/>
-      <c r="AD5" s="92"/>
+      <c r="X5" s="119"/>
+      <c r="Y5" s="119"/>
+      <c r="Z5" s="119"/>
+      <c r="AA5" s="119"/>
+      <c r="AB5" s="119"/>
+      <c r="AC5" s="119"/>
+      <c r="AD5" s="120"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
       <c r="AI5" s="41"/>
       <c r="AJ5" s="41"/>
     </row>
-    <row r="6" spans="1:36" s="43" customFormat="1" ht="133.80000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" s="43" customFormat="1" ht="133.80000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="42"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="90" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" s="85"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="85"/>
-      <c r="I6" s="83"/>
-      <c r="J6" s="85"/>
-      <c r="K6" s="83"/>
-      <c r="L6" s="84"/>
-      <c r="M6" s="84"/>
-      <c r="N6" s="85"/>
-      <c r="O6" s="90" t="s">
-        <v>43</v>
-      </c>
-      <c r="P6" s="84"/>
-      <c r="Q6" s="84"/>
-      <c r="R6" s="84"/>
-      <c r="S6" s="84"/>
-      <c r="T6" s="84"/>
-      <c r="U6" s="84"/>
-      <c r="V6" s="85"/>
-      <c r="W6" s="83"/>
-      <c r="X6" s="84"/>
-      <c r="Y6" s="84"/>
-      <c r="Z6" s="84"/>
-      <c r="AA6" s="84"/>
-      <c r="AB6" s="84"/>
-      <c r="AC6" s="84"/>
-      <c r="AD6" s="85"/>
+      <c r="C6" s="135"/>
+      <c r="D6" s="137"/>
+      <c r="E6" s="141" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" s="137"/>
+      <c r="G6" s="135"/>
+      <c r="H6" s="137"/>
+      <c r="I6" s="135"/>
+      <c r="J6" s="137"/>
+      <c r="K6" s="135"/>
+      <c r="L6" s="136"/>
+      <c r="M6" s="136"/>
+      <c r="N6" s="137"/>
+      <c r="O6" s="141" t="s">
+        <v>40</v>
+      </c>
+      <c r="P6" s="136"/>
+      <c r="Q6" s="136"/>
+      <c r="R6" s="136"/>
+      <c r="S6" s="136"/>
+      <c r="T6" s="136"/>
+      <c r="U6" s="136"/>
+      <c r="V6" s="137"/>
+      <c r="W6" s="135"/>
+      <c r="X6" s="136"/>
+      <c r="Y6" s="136"/>
+      <c r="Z6" s="136"/>
+      <c r="AA6" s="136"/>
+      <c r="AB6" s="136"/>
+      <c r="AC6" s="136"/>
+      <c r="AD6" s="137"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
-    <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1"/>
-      <c r="C7" s="152">
+      <c r="C7" s="149">
         <f ca="1">W5+1</f>
         <v>46334</v>
       </c>
-      <c r="D7" s="153"/>
-      <c r="E7" s="157"/>
-      <c r="F7" s="158"/>
-      <c r="G7" s="157"/>
-      <c r="H7" s="158"/>
-      <c r="I7" s="157"/>
-      <c r="J7" s="158"/>
-      <c r="K7" s="157"/>
-      <c r="L7" s="159"/>
-      <c r="M7" s="159"/>
+      <c r="D7" s="150"/>
+      <c r="E7" s="151"/>
+      <c r="F7" s="152"/>
+      <c r="G7" s="151"/>
+      <c r="H7" s="152"/>
+      <c r="I7" s="151"/>
+      <c r="J7" s="152"/>
+      <c r="K7" s="151"/>
+      <c r="L7" s="153"/>
+      <c r="M7" s="153"/>
       <c r="N7" s="80"/>
-      <c r="O7" s="157"/>
-      <c r="P7" s="159"/>
-      <c r="Q7" s="159"/>
-      <c r="R7" s="159"/>
-      <c r="S7" s="159"/>
-      <c r="T7" s="159"/>
-      <c r="U7" s="159"/>
-      <c r="V7" s="158"/>
-      <c r="W7" s="157"/>
-      <c r="X7" s="159"/>
-      <c r="Y7" s="159"/>
-      <c r="Z7" s="159"/>
-      <c r="AA7" s="159"/>
-      <c r="AB7" s="159"/>
-      <c r="AC7" s="159"/>
-      <c r="AD7" s="158"/>
+      <c r="O7" s="151"/>
+      <c r="P7" s="153"/>
+      <c r="Q7" s="153"/>
+      <c r="R7" s="153"/>
+      <c r="S7" s="153"/>
+      <c r="T7" s="153"/>
+      <c r="U7" s="153"/>
+      <c r="V7" s="152"/>
+      <c r="W7" s="151"/>
+      <c r="X7" s="153"/>
+      <c r="Y7" s="153"/>
+      <c r="Z7" s="153"/>
+      <c r="AA7" s="153"/>
+      <c r="AB7" s="153"/>
+      <c r="AC7" s="153"/>
+      <c r="AD7" s="152"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="4"/>
-      <c r="C8" s="152"/>
-      <c r="D8" s="153"/>
-      <c r="E8" s="152">
+      <c r="C8" s="149"/>
+      <c r="D8" s="150"/>
+      <c r="E8" s="149">
         <f ca="1">C7+1</f>
         <v>46335</v>
       </c>
-      <c r="F8" s="153"/>
-      <c r="G8" s="152">
+      <c r="F8" s="150"/>
+      <c r="G8" s="149">
         <f ca="1">E8+1</f>
         <v>46336</v>
       </c>
-      <c r="H8" s="153"/>
-      <c r="I8" s="152">
+      <c r="H8" s="150"/>
+      <c r="I8" s="149">
         <f ca="1">G8+1</f>
         <v>46337</v>
       </c>
-      <c r="J8" s="153"/>
-      <c r="K8" s="152">
+      <c r="J8" s="150"/>
+      <c r="K8" s="149">
         <f ca="1">I8+1</f>
         <v>46338</v>
       </c>
       <c r="L8" s="154"/>
       <c r="M8" s="154"/>
       <c r="N8" s="78"/>
-      <c r="O8" s="152">
+      <c r="O8" s="149">
         <f ca="1">K8+1</f>
         <v>46339</v>
       </c>
@@ -5784,8 +5787,8 @@
       <c r="S8" s="154"/>
       <c r="T8" s="154"/>
       <c r="U8" s="154"/>
-      <c r="V8" s="153"/>
-      <c r="W8" s="152">
+      <c r="V8" s="150"/>
+      <c r="W8" s="149">
         <f ca="1">O8+1</f>
         <v>46340</v>
       </c>
@@ -5795,55 +5798,57 @@
       <c r="AA8" s="154"/>
       <c r="AB8" s="154"/>
       <c r="AC8" s="154"/>
-      <c r="AD8" s="153"/>
+      <c r="AD8" s="150"/>
       <c r="AF8" s="4"/>
     </row>
-    <row r="9" spans="1:36" s="43" customFormat="1" ht="146.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" s="43" customFormat="1" ht="146.4" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="42"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="85"/>
-      <c r="E9" s="90" t="s">
+      <c r="C9" s="135"/>
+      <c r="D9" s="137"/>
+      <c r="E9" s="141" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="137"/>
+      <c r="G9" s="135"/>
+      <c r="H9" s="137"/>
+      <c r="I9" s="135" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="85"/>
-      <c r="G9" s="83"/>
-      <c r="H9" s="85"/>
-      <c r="I9" s="83"/>
-      <c r="J9" s="85"/>
-      <c r="K9" s="83" t="s">
+      <c r="J9" s="137"/>
+      <c r="K9" s="135" t="s">
         <v>18</v>
       </c>
-      <c r="L9" s="84"/>
-      <c r="M9" s="84"/>
-      <c r="N9" s="85"/>
-      <c r="O9" s="155" t="s">
+      <c r="L9" s="136"/>
+      <c r="M9" s="136"/>
+      <c r="N9" s="137"/>
+      <c r="O9" s="156" t="s">
         <v>15</v>
       </c>
-      <c r="P9" s="151"/>
-      <c r="Q9" s="151"/>
-      <c r="R9" s="151"/>
-      <c r="S9" s="151"/>
-      <c r="T9" s="151"/>
-      <c r="U9" s="151"/>
-      <c r="V9" s="103"/>
-      <c r="W9" s="102"/>
-      <c r="X9" s="151"/>
-      <c r="Y9" s="151"/>
-      <c r="Z9" s="151"/>
-      <c r="AA9" s="151"/>
-      <c r="AB9" s="151"/>
-      <c r="AC9" s="151"/>
-      <c r="AD9" s="103"/>
+      <c r="P9" s="155"/>
+      <c r="Q9" s="155"/>
+      <c r="R9" s="155"/>
+      <c r="S9" s="155"/>
+      <c r="T9" s="155"/>
+      <c r="U9" s="155"/>
+      <c r="V9" s="122"/>
+      <c r="W9" s="121"/>
+      <c r="X9" s="155"/>
+      <c r="Y9" s="155"/>
+      <c r="Z9" s="155"/>
+      <c r="AA9" s="155"/>
+      <c r="AB9" s="155"/>
+      <c r="AC9" s="155"/>
+      <c r="AD9" s="122"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
-    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="42"/>
-      <c r="C10" s="152">
+      <c r="C10" s="149">
         <f ca="1">W8+1</f>
         <v>46341</v>
       </c>
-      <c r="D10" s="153"/>
+      <c r="D10" s="150"/>
       <c r="E10" s="79"/>
       <c r="F10" s="80"/>
       <c r="G10" s="79"/>
@@ -5873,33 +5878,33 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="42"/>
     </row>
-    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="4"/>
-      <c r="C11" s="152"/>
-      <c r="D11" s="153"/>
-      <c r="E11" s="152">
+      <c r="C11" s="149"/>
+      <c r="D11" s="150"/>
+      <c r="E11" s="149">
         <f ca="1">C10+1</f>
         <v>46342</v>
       </c>
-      <c r="F11" s="153"/>
-      <c r="G11" s="152">
+      <c r="F11" s="150"/>
+      <c r="G11" s="149">
         <f ca="1">E11+1</f>
         <v>46343</v>
       </c>
-      <c r="H11" s="153"/>
-      <c r="I11" s="152">
+      <c r="H11" s="150"/>
+      <c r="I11" s="149">
         <f ca="1">G11+1</f>
         <v>46344</v>
       </c>
-      <c r="J11" s="153"/>
-      <c r="K11" s="152">
+      <c r="J11" s="150"/>
+      <c r="K11" s="149">
         <f ca="1">I11+1</f>
         <v>46345</v>
       </c>
       <c r="L11" s="154"/>
       <c r="M11" s="154"/>
       <c r="N11" s="78"/>
-      <c r="O11" s="152">
+      <c r="O11" s="149">
         <f ca="1">K11+1</f>
         <v>46346</v>
       </c>
@@ -5909,8 +5914,8 @@
       <c r="S11" s="154"/>
       <c r="T11" s="154"/>
       <c r="U11" s="154"/>
-      <c r="V11" s="153"/>
-      <c r="W11" s="152">
+      <c r="V11" s="150"/>
+      <c r="W11" s="149">
         <f ca="1">O11+1</f>
         <v>46347</v>
       </c>
@@ -5920,52 +5925,52 @@
       <c r="AA11" s="154"/>
       <c r="AB11" s="154"/>
       <c r="AC11" s="154"/>
-      <c r="AD11" s="153"/>
+      <c r="AD11" s="150"/>
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:36" s="43" customFormat="1" ht="134.69999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" s="43" customFormat="1" ht="134.69999999999999" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="42"/>
-      <c r="C12" s="102"/>
-      <c r="D12" s="103"/>
-      <c r="E12" s="155" t="s">
+      <c r="C12" s="121"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="156" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="156"/>
-      <c r="G12" s="102"/>
-      <c r="H12" s="103"/>
-      <c r="I12" s="102"/>
-      <c r="J12" s="103"/>
-      <c r="K12" s="102"/>
-      <c r="L12" s="151"/>
-      <c r="M12" s="151"/>
-      <c r="N12" s="103"/>
-      <c r="O12" s="102"/>
-      <c r="P12" s="151"/>
-      <c r="Q12" s="151"/>
-      <c r="R12" s="151"/>
-      <c r="S12" s="151"/>
-      <c r="T12" s="151"/>
-      <c r="U12" s="151"/>
-      <c r="V12" s="103"/>
-      <c r="W12" s="102"/>
-      <c r="X12" s="151"/>
-      <c r="Y12" s="151"/>
-      <c r="Z12" s="151"/>
-      <c r="AA12" s="151"/>
-      <c r="AB12" s="151"/>
-      <c r="AC12" s="151"/>
-      <c r="AD12" s="103"/>
+      <c r="F12" s="157"/>
+      <c r="G12" s="121"/>
+      <c r="H12" s="122"/>
+      <c r="I12" s="121"/>
+      <c r="J12" s="122"/>
+      <c r="K12" s="121"/>
+      <c r="L12" s="155"/>
+      <c r="M12" s="155"/>
+      <c r="N12" s="122"/>
+      <c r="O12" s="121"/>
+      <c r="P12" s="155"/>
+      <c r="Q12" s="155"/>
+      <c r="R12" s="155"/>
+      <c r="S12" s="155"/>
+      <c r="T12" s="155"/>
+      <c r="U12" s="155"/>
+      <c r="V12" s="122"/>
+      <c r="W12" s="121"/>
+      <c r="X12" s="155"/>
+      <c r="Y12" s="155"/>
+      <c r="Z12" s="155"/>
+      <c r="AA12" s="155"/>
+      <c r="AB12" s="155"/>
+      <c r="AC12" s="155"/>
+      <c r="AD12" s="122"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
-    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="42"/>
-      <c r="C13" s="152">
+      <c r="C13" s="149">
         <f ca="1">W11+1</f>
         <v>46348</v>
       </c>
-      <c r="D13" s="153"/>
+      <c r="D13" s="150"/>
       <c r="E13" s="79"/>
       <c r="F13" s="80"/>
       <c r="G13" s="79"/>
@@ -5995,33 +6000,33 @@
       <c r="AE13" s="7"/>
       <c r="AF13" s="42"/>
     </row>
-    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="4"/>
-      <c r="C14" s="152"/>
-      <c r="D14" s="153"/>
-      <c r="E14" s="152">
+      <c r="C14" s="149"/>
+      <c r="D14" s="150"/>
+      <c r="E14" s="149">
         <f ca="1">C13+1</f>
         <v>46349</v>
       </c>
-      <c r="F14" s="153"/>
-      <c r="G14" s="152">
+      <c r="F14" s="150"/>
+      <c r="G14" s="149">
         <f ca="1">E14+1</f>
         <v>46350</v>
       </c>
-      <c r="H14" s="153"/>
-      <c r="I14" s="152">
+      <c r="H14" s="150"/>
+      <c r="I14" s="149">
         <f ca="1">G14+1</f>
         <v>46351</v>
       </c>
-      <c r="J14" s="153"/>
-      <c r="K14" s="152">
+      <c r="J14" s="150"/>
+      <c r="K14" s="149">
         <f ca="1">I14+1</f>
         <v>46352</v>
       </c>
       <c r="L14" s="154"/>
       <c r="M14" s="154"/>
       <c r="N14" s="78"/>
-      <c r="O14" s="152">
+      <c r="O14" s="149">
         <f ca="1">K14+1</f>
         <v>46353</v>
       </c>
@@ -6031,8 +6036,8 @@
       <c r="S14" s="154"/>
       <c r="T14" s="154"/>
       <c r="U14" s="154"/>
-      <c r="V14" s="153"/>
-      <c r="W14" s="152">
+      <c r="V14" s="150"/>
+      <c r="W14" s="149">
         <f ca="1">O14+1</f>
         <v>46354</v>
       </c>
@@ -6042,55 +6047,55 @@
       <c r="AA14" s="154"/>
       <c r="AB14" s="154"/>
       <c r="AC14" s="154"/>
-      <c r="AD14" s="153"/>
+      <c r="AD14" s="150"/>
       <c r="AF14" s="4"/>
     </row>
-    <row r="15" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="42"/>
-      <c r="C15" s="102"/>
-      <c r="D15" s="103"/>
-      <c r="E15" s="102"/>
-      <c r="F15" s="103"/>
-      <c r="G15" s="102"/>
-      <c r="H15" s="103"/>
-      <c r="I15" s="102"/>
-      <c r="J15" s="103"/>
-      <c r="K15" s="102"/>
-      <c r="L15" s="151"/>
-      <c r="M15" s="151"/>
-      <c r="N15" s="103"/>
-      <c r="O15" s="102"/>
-      <c r="P15" s="151"/>
-      <c r="Q15" s="151"/>
-      <c r="R15" s="151"/>
-      <c r="S15" s="151"/>
-      <c r="T15" s="151"/>
-      <c r="U15" s="151"/>
-      <c r="V15" s="103"/>
-      <c r="W15" s="102"/>
-      <c r="X15" s="151"/>
-      <c r="Y15" s="151"/>
-      <c r="Z15" s="151"/>
-      <c r="AA15" s="151"/>
-      <c r="AB15" s="151"/>
-      <c r="AC15" s="151"/>
-      <c r="AD15" s="103"/>
+      <c r="C15" s="121"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="121"/>
+      <c r="F15" s="122"/>
+      <c r="G15" s="121"/>
+      <c r="H15" s="122"/>
+      <c r="I15" s="121"/>
+      <c r="J15" s="122"/>
+      <c r="K15" s="121"/>
+      <c r="L15" s="155"/>
+      <c r="M15" s="155"/>
+      <c r="N15" s="122"/>
+      <c r="O15" s="121"/>
+      <c r="P15" s="155"/>
+      <c r="Q15" s="155"/>
+      <c r="R15" s="155"/>
+      <c r="S15" s="155"/>
+      <c r="T15" s="155"/>
+      <c r="U15" s="155"/>
+      <c r="V15" s="122"/>
+      <c r="W15" s="121"/>
+      <c r="X15" s="155"/>
+      <c r="Y15" s="155"/>
+      <c r="Z15" s="155"/>
+      <c r="AA15" s="155"/>
+      <c r="AB15" s="155"/>
+      <c r="AC15" s="155"/>
+      <c r="AD15" s="122"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
-    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="42"/>
-      <c r="C16" s="91">
+      <c r="C16" s="118">
         <f ca="1">W14+1</f>
         <v>46355</v>
       </c>
-      <c r="D16" s="92"/>
+      <c r="D16" s="120"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
       <c r="H16" s="75"/>
-      <c r="I16" s="145"/>
-      <c r="J16" s="146"/>
+      <c r="I16" s="146"/>
+      <c r="J16" s="147"/>
       <c r="K16" s="66"/>
       <c r="L16" s="68"/>
       <c r="M16" s="68"/>
@@ -6114,102 +6119,102 @@
       <c r="AE16" s="7"/>
       <c r="AF16" s="42"/>
     </row>
-    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4"/>
-      <c r="C17" s="91"/>
-      <c r="D17" s="92"/>
-      <c r="E17" s="93">
+      <c r="C17" s="118"/>
+      <c r="D17" s="120"/>
+      <c r="E17" s="132">
         <f ca="1">C16+1</f>
         <v>46356</v>
       </c>
-      <c r="F17" s="94"/>
-      <c r="G17" s="93">
+      <c r="F17" s="133"/>
+      <c r="G17" s="132">
         <v>1</v>
       </c>
-      <c r="H17" s="94"/>
-      <c r="I17" s="93">
+      <c r="H17" s="133"/>
+      <c r="I17" s="132">
         <f>G17+1</f>
         <v>2</v>
       </c>
-      <c r="J17" s="94"/>
-      <c r="K17" s="93">
+      <c r="J17" s="133"/>
+      <c r="K17" s="132">
         <f>I17+1</f>
         <v>3</v>
       </c>
-      <c r="L17" s="95"/>
-      <c r="M17" s="95"/>
-      <c r="N17" s="94"/>
-      <c r="O17" s="93">
+      <c r="L17" s="134"/>
+      <c r="M17" s="134"/>
+      <c r="N17" s="133"/>
+      <c r="O17" s="132">
         <f>K17+1</f>
         <v>4</v>
       </c>
-      <c r="P17" s="95"/>
-      <c r="Q17" s="95"/>
-      <c r="R17" s="95"/>
-      <c r="S17" s="95"/>
-      <c r="T17" s="95"/>
-      <c r="U17" s="95"/>
-      <c r="V17" s="94"/>
-      <c r="W17" s="93">
+      <c r="P17" s="134"/>
+      <c r="Q17" s="134"/>
+      <c r="R17" s="134"/>
+      <c r="S17" s="134"/>
+      <c r="T17" s="134"/>
+      <c r="U17" s="134"/>
+      <c r="V17" s="133"/>
+      <c r="W17" s="132">
         <f>O17+1</f>
         <v>5</v>
       </c>
-      <c r="X17" s="95"/>
-      <c r="Y17" s="95"/>
-      <c r="Z17" s="95"/>
-      <c r="AA17" s="95"/>
-      <c r="AB17" s="95"/>
-      <c r="AC17" s="95"/>
-      <c r="AD17" s="94"/>
+      <c r="X17" s="134"/>
+      <c r="Y17" s="134"/>
+      <c r="Z17" s="134"/>
+      <c r="AA17" s="134"/>
+      <c r="AB17" s="134"/>
+      <c r="AC17" s="134"/>
+      <c r="AD17" s="133"/>
       <c r="AF17" s="4"/>
     </row>
-    <row r="18" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="42"/>
-      <c r="C18" s="96"/>
-      <c r="D18" s="97"/>
-      <c r="E18" s="96"/>
-      <c r="F18" s="97"/>
-      <c r="G18" s="96"/>
-      <c r="H18" s="97"/>
-      <c r="I18" s="96"/>
-      <c r="J18" s="97"/>
-      <c r="K18" s="96"/>
-      <c r="L18" s="141"/>
-      <c r="M18" s="141"/>
-      <c r="N18" s="97"/>
-      <c r="O18" s="96"/>
-      <c r="P18" s="141"/>
-      <c r="Q18" s="141"/>
-      <c r="R18" s="141"/>
-      <c r="S18" s="141"/>
-      <c r="T18" s="141"/>
-      <c r="U18" s="141"/>
-      <c r="V18" s="97"/>
-      <c r="W18" s="96"/>
-      <c r="X18" s="141"/>
-      <c r="Y18" s="141"/>
-      <c r="Z18" s="141"/>
-      <c r="AA18" s="141"/>
-      <c r="AB18" s="141"/>
-      <c r="AC18" s="141"/>
-      <c r="AD18" s="97"/>
+      <c r="C18" s="111"/>
+      <c r="D18" s="113"/>
+      <c r="E18" s="111"/>
+      <c r="F18" s="113"/>
+      <c r="G18" s="111"/>
+      <c r="H18" s="113"/>
+      <c r="I18" s="111"/>
+      <c r="J18" s="113"/>
+      <c r="K18" s="111"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="113"/>
+      <c r="O18" s="111"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="112"/>
+      <c r="R18" s="112"/>
+      <c r="S18" s="112"/>
+      <c r="T18" s="112"/>
+      <c r="U18" s="112"/>
+      <c r="V18" s="113"/>
+      <c r="W18" s="111"/>
+      <c r="X18" s="112"/>
+      <c r="Y18" s="112"/>
+      <c r="Z18" s="112"/>
+      <c r="AA18" s="112"/>
+      <c r="AB18" s="112"/>
+      <c r="AC18" s="112"/>
+      <c r="AD18" s="113"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
-    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="42"/>
-      <c r="C19" s="91">
+      <c r="C19" s="118">
         <f>W17+1</f>
         <v>6</v>
       </c>
-      <c r="D19" s="92"/>
+      <c r="D19" s="120"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
       <c r="H19" s="75"/>
-      <c r="I19" s="145"/>
-      <c r="J19" s="146"/>
+      <c r="I19" s="146"/>
+      <c r="J19" s="147"/>
       <c r="K19" s="66"/>
       <c r="L19" s="68"/>
       <c r="M19" s="68"/>
@@ -6233,91 +6238,91 @@
       <c r="AE19" s="7"/>
       <c r="AF19" s="42"/>
     </row>
-    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4"/>
-      <c r="C20" s="91"/>
-      <c r="D20" s="92"/>
-      <c r="E20" s="93">
+      <c r="C20" s="118"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="132">
         <f>C19+1</f>
         <v>7</v>
       </c>
-      <c r="F20" s="94"/>
-      <c r="G20" s="93">
+      <c r="F20" s="133"/>
+      <c r="G20" s="132">
         <f>E20+1</f>
         <v>8</v>
       </c>
-      <c r="H20" s="94"/>
-      <c r="I20" s="93">
+      <c r="H20" s="133"/>
+      <c r="I20" s="132">
         <f>G20+1</f>
         <v>9</v>
       </c>
-      <c r="J20" s="94"/>
-      <c r="K20" s="93">
+      <c r="J20" s="133"/>
+      <c r="K20" s="132">
         <f>I20+1</f>
         <v>10</v>
       </c>
-      <c r="L20" s="95"/>
-      <c r="M20" s="95"/>
-      <c r="N20" s="94"/>
-      <c r="O20" s="93">
+      <c r="L20" s="134"/>
+      <c r="M20" s="134"/>
+      <c r="N20" s="133"/>
+      <c r="O20" s="132">
         <f>K20+1</f>
         <v>11</v>
       </c>
-      <c r="P20" s="95"/>
-      <c r="Q20" s="95"/>
-      <c r="R20" s="95"/>
-      <c r="S20" s="95"/>
-      <c r="T20" s="95"/>
-      <c r="U20" s="95"/>
-      <c r="V20" s="94"/>
-      <c r="W20" s="93">
+      <c r="P20" s="134"/>
+      <c r="Q20" s="134"/>
+      <c r="R20" s="134"/>
+      <c r="S20" s="134"/>
+      <c r="T20" s="134"/>
+      <c r="U20" s="134"/>
+      <c r="V20" s="133"/>
+      <c r="W20" s="132">
         <f>O20+1</f>
         <v>12</v>
       </c>
-      <c r="X20" s="95"/>
-      <c r="Y20" s="95"/>
-      <c r="Z20" s="95"/>
-      <c r="AA20" s="95"/>
-      <c r="AB20" s="95"/>
-      <c r="AC20" s="95"/>
-      <c r="AD20" s="94"/>
+      <c r="X20" s="134"/>
+      <c r="Y20" s="134"/>
+      <c r="Z20" s="134"/>
+      <c r="AA20" s="134"/>
+      <c r="AB20" s="134"/>
+      <c r="AC20" s="134"/>
+      <c r="AD20" s="133"/>
       <c r="AF20" s="4"/>
     </row>
-    <row r="21" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="42"/>
-      <c r="C21" s="96"/>
-      <c r="D21" s="97"/>
-      <c r="E21" s="96"/>
-      <c r="F21" s="97"/>
-      <c r="G21" s="96"/>
-      <c r="H21" s="97"/>
-      <c r="I21" s="96"/>
-      <c r="J21" s="97"/>
-      <c r="K21" s="96"/>
-      <c r="L21" s="141"/>
-      <c r="M21" s="141"/>
-      <c r="N21" s="97"/>
-      <c r="O21" s="96"/>
-      <c r="P21" s="141"/>
-      <c r="Q21" s="141"/>
-      <c r="R21" s="141"/>
-      <c r="S21" s="141"/>
-      <c r="T21" s="141"/>
-      <c r="U21" s="141"/>
-      <c r="V21" s="97"/>
-      <c r="W21" s="96"/>
-      <c r="X21" s="141"/>
-      <c r="Y21" s="141"/>
-      <c r="Z21" s="141"/>
-      <c r="AA21" s="141"/>
-      <c r="AB21" s="141"/>
-      <c r="AC21" s="141"/>
-      <c r="AD21" s="97"/>
+      <c r="C21" s="111"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="113"/>
+      <c r="K21" s="111"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="113"/>
+      <c r="O21" s="111"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="112"/>
+      <c r="R21" s="112"/>
+      <c r="S21" s="112"/>
+      <c r="T21" s="112"/>
+      <c r="U21" s="112"/>
+      <c r="V21" s="113"/>
+      <c r="W21" s="111"/>
+      <c r="X21" s="112"/>
+      <c r="Y21" s="112"/>
+      <c r="Z21" s="112"/>
+      <c r="AA21" s="112"/>
+      <c r="AB21" s="112"/>
+      <c r="AC21" s="112"/>
+      <c r="AD21" s="113"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
     </row>
-    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="4"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52"/>
@@ -6349,7 +6354,7 @@
       <c r="AD22" s="55"/>
       <c r="AF22" s="4"/>
     </row>
-    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="56"/>
@@ -6383,61 +6388,61 @@
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
     </row>
-    <row r="24" spans="1:42" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:42" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="1"/>
       <c r="M24" s="1"/>
       <c r="AF24" s="1"/>
     </row>
-    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="1"/>
-      <c r="C25" s="86" t="s">
+      <c r="C25" s="139" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="86"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="86"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="86"/>
-      <c r="J25" s="86"/>
-      <c r="K25" s="86"/>
+      <c r="D25" s="139"/>
+      <c r="E25" s="139"/>
+      <c r="F25" s="139"/>
+      <c r="G25" s="139"/>
+      <c r="H25" s="139"/>
+      <c r="I25" s="139"/>
+      <c r="J25" s="139"/>
+      <c r="K25" s="139"/>
       <c r="L25" s="60"/>
       <c r="M25" s="1"/>
-      <c r="O25" s="87">
+      <c r="O25" s="140">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)-1,1)</f>
         <v>46296</v>
       </c>
-      <c r="P25" s="87"/>
-      <c r="Q25" s="87"/>
-      <c r="R25" s="87"/>
-      <c r="S25" s="87"/>
-      <c r="T25" s="87"/>
-      <c r="U25" s="87"/>
+      <c r="P25" s="140"/>
+      <c r="Q25" s="140"/>
+      <c r="R25" s="140"/>
+      <c r="S25" s="140"/>
+      <c r="T25" s="140"/>
+      <c r="U25" s="140"/>
       <c r="V25" s="61"/>
       <c r="W25" s="61"/>
-      <c r="X25" s="87">
+      <c r="X25" s="140">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)+1,1)</f>
         <v>46357</v>
       </c>
-      <c r="Y25" s="87"/>
-      <c r="Z25" s="87"/>
-      <c r="AA25" s="87"/>
-      <c r="AB25" s="87"/>
-      <c r="AC25" s="87"/>
-      <c r="AD25" s="87"/>
+      <c r="Y25" s="140"/>
+      <c r="Z25" s="140"/>
+      <c r="AA25" s="140"/>
+      <c r="AB25" s="140"/>
+      <c r="AC25" s="140"/>
+      <c r="AD25" s="140"/>
       <c r="AF25" s="1"/>
     </row>
-    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="1"/>
-      <c r="C26" s="86"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="86"/>
-      <c r="G26" s="86"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="86"/>
-      <c r="J26" s="86"/>
-      <c r="K26" s="86"/>
+      <c r="C26" s="139"/>
+      <c r="D26" s="139"/>
+      <c r="E26" s="139"/>
+      <c r="F26" s="139"/>
+      <c r="G26" s="139"/>
+      <c r="H26" s="139"/>
+      <c r="I26" s="139"/>
+      <c r="J26" s="139"/>
+      <c r="K26" s="139"/>
       <c r="L26" s="60"/>
       <c r="M26" s="1"/>
       <c r="O26" s="62" t="str">
@@ -6500,17 +6505,17 @@
       </c>
       <c r="AF26" s="1"/>
     </row>
-    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="1"/>
-      <c r="C27" s="88"/>
-      <c r="D27" s="88"/>
-      <c r="E27" s="88"/>
-      <c r="F27" s="88"/>
-      <c r="G27" s="88"/>
-      <c r="H27" s="88"/>
-      <c r="I27" s="88"/>
-      <c r="J27" s="88"/>
-      <c r="K27" s="88"/>
+      <c r="C27" s="115"/>
+      <c r="D27" s="115"/>
+      <c r="E27" s="115"/>
+      <c r="F27" s="115"/>
+      <c r="G27" s="115"/>
+      <c r="H27" s="115"/>
+      <c r="I27" s="115"/>
+      <c r="J27" s="115"/>
+      <c r="K27" s="115"/>
       <c r="M27" s="1"/>
       <c r="O27" s="64" t="str">
         <f t="shared" ref="O27:U32" ca="1" si="0">IF(MONTH($O$25)&lt;&gt;MONTH($O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1)),"",$O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1))</f>
@@ -6572,17 +6577,17 @@
       </c>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="1"/>
-      <c r="C28" s="89"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="89"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="89"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="89"/>
-      <c r="K28" s="89"/>
+      <c r="C28" s="114"/>
+      <c r="D28" s="114"/>
+      <c r="E28" s="114"/>
+      <c r="F28" s="114"/>
+      <c r="G28" s="114"/>
+      <c r="H28" s="114"/>
+      <c r="I28" s="114"/>
+      <c r="J28" s="114"/>
+      <c r="K28" s="114"/>
       <c r="M28" s="1"/>
       <c r="O28" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6644,17 +6649,17 @@
       </c>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="1"/>
-      <c r="C29" s="88"/>
-      <c r="D29" s="88"/>
-      <c r="E29" s="88"/>
-      <c r="F29" s="88"/>
-      <c r="G29" s="88"/>
-      <c r="H29" s="88"/>
-      <c r="I29" s="88"/>
-      <c r="J29" s="88"/>
-      <c r="K29" s="88"/>
+      <c r="C29" s="115"/>
+      <c r="D29" s="115"/>
+      <c r="E29" s="115"/>
+      <c r="F29" s="115"/>
+      <c r="G29" s="115"/>
+      <c r="H29" s="115"/>
+      <c r="I29" s="115"/>
+      <c r="J29" s="115"/>
+      <c r="K29" s="115"/>
       <c r="M29" s="1"/>
       <c r="O29" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6716,17 +6721,17 @@
       </c>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="1"/>
-      <c r="C30" s="89"/>
-      <c r="D30" s="89"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="89"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="89"/>
-      <c r="K30" s="89"/>
+      <c r="C30" s="114"/>
+      <c r="D30" s="114"/>
+      <c r="E30" s="114"/>
+      <c r="F30" s="114"/>
+      <c r="G30" s="114"/>
+      <c r="H30" s="114"/>
+      <c r="I30" s="114"/>
+      <c r="J30" s="114"/>
+      <c r="K30" s="114"/>
       <c r="M30" s="1"/>
       <c r="O30" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6788,17 +6793,17 @@
       </c>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="1"/>
-      <c r="C31" s="88"/>
-      <c r="D31" s="88"/>
-      <c r="E31" s="88"/>
-      <c r="F31" s="88"/>
-      <c r="G31" s="88"/>
-      <c r="H31" s="88"/>
-      <c r="I31" s="88"/>
-      <c r="J31" s="88"/>
-      <c r="K31" s="88"/>
+      <c r="C31" s="115"/>
+      <c r="D31" s="115"/>
+      <c r="E31" s="115"/>
+      <c r="F31" s="115"/>
+      <c r="G31" s="115"/>
+      <c r="H31" s="115"/>
+      <c r="I31" s="115"/>
+      <c r="J31" s="115"/>
+      <c r="K31" s="115"/>
       <c r="M31" s="1"/>
       <c r="O31" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6860,7 +6865,7 @@
       </c>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="1"/>
       <c r="C32" s="77"/>
       <c r="D32" s="77"/>
@@ -6932,12 +6937,12 @@
       </c>
       <c r="AF32" s="1"/>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A33" s="1"/>
       <c r="M33" s="1"/>
       <c r="AF33" s="1"/>
     </row>
-    <row r="34" spans="1:32" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -6971,100 +6976,130 @@
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
     </row>
-    <row r="37" spans="1:32" ht="13.8" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="38" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="D38" s="113" t="s">
-        <v>25</v>
-      </c>
-      <c r="E38" s="114"/>
-      <c r="F38" s="115"/>
-      <c r="G38" s="119">
+    <row r="37" spans="1:32" ht="12.9" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="38" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D38" s="83" t="s">
+        <v>24</v>
+      </c>
+      <c r="E38" s="84"/>
+      <c r="F38" s="85"/>
+      <c r="G38" s="89">
         <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
         <v>5</v>
       </c>
-      <c r="H38" s="120"/>
-      <c r="I38" s="113" t="s">
-        <v>28</v>
-      </c>
-      <c r="J38" s="123"/>
-      <c r="K38" s="125" t="s">
-        <v>26</v>
-      </c>
-      <c r="L38" s="126"/>
-      <c r="M38" s="129">
+      <c r="H38" s="90"/>
+      <c r="I38" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="J38" s="93"/>
+      <c r="K38" s="95" t="s">
+        <v>25</v>
+      </c>
+      <c r="L38" s="96"/>
+      <c r="M38" s="99">
         <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
         <v>5.9999999999999973</v>
       </c>
-      <c r="N38" s="130"/>
-      <c r="O38" s="130"/>
-      <c r="P38" s="130"/>
-      <c r="Q38" s="130"/>
-      <c r="R38" s="131"/>
-      <c r="S38" s="135" t="s">
-        <v>27</v>
-      </c>
-      <c r="T38" s="136"/>
-      <c r="U38" s="136"/>
-      <c r="V38" s="136"/>
-      <c r="W38" s="136"/>
-      <c r="X38" s="137"/>
-    </row>
-    <row r="39" spans="1:32" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="D39" s="116"/>
-      <c r="E39" s="117"/>
-      <c r="F39" s="118"/>
-      <c r="G39" s="121"/>
-      <c r="H39" s="122"/>
-      <c r="I39" s="116"/>
-      <c r="J39" s="124"/>
-      <c r="K39" s="127"/>
-      <c r="L39" s="128"/>
-      <c r="M39" s="132"/>
-      <c r="N39" s="133"/>
-      <c r="O39" s="133"/>
-      <c r="P39" s="133"/>
-      <c r="Q39" s="133"/>
-      <c r="R39" s="134"/>
-      <c r="S39" s="138"/>
-      <c r="T39" s="139"/>
-      <c r="U39" s="139"/>
-      <c r="V39" s="139"/>
-      <c r="W39" s="139"/>
-      <c r="X39" s="140"/>
+      <c r="N38" s="100"/>
+      <c r="O38" s="100"/>
+      <c r="P38" s="100"/>
+      <c r="Q38" s="100"/>
+      <c r="R38" s="101"/>
+      <c r="S38" s="105" t="s">
+        <v>26</v>
+      </c>
+      <c r="T38" s="106"/>
+      <c r="U38" s="106"/>
+      <c r="V38" s="106"/>
+      <c r="W38" s="106"/>
+      <c r="X38" s="107"/>
+    </row>
+    <row r="39" spans="1:32" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D39" s="86"/>
+      <c r="E39" s="87"/>
+      <c r="F39" s="88"/>
+      <c r="G39" s="91"/>
+      <c r="H39" s="92"/>
+      <c r="I39" s="86"/>
+      <c r="J39" s="94"/>
+      <c r="K39" s="97"/>
+      <c r="L39" s="98"/>
+      <c r="M39" s="102"/>
+      <c r="N39" s="103"/>
+      <c r="O39" s="103"/>
+      <c r="P39" s="103"/>
+      <c r="Q39" s="103"/>
+      <c r="R39" s="104"/>
+      <c r="S39" s="108"/>
+      <c r="T39" s="109"/>
+      <c r="U39" s="109"/>
+      <c r="V39" s="109"/>
+      <c r="W39" s="109"/>
+      <c r="X39" s="110"/>
     </row>
   </sheetData>
   <mergeCells count="112">
-    <mergeCell ref="D38:F39"/>
-    <mergeCell ref="G38:H39"/>
-    <mergeCell ref="I38:J39"/>
-    <mergeCell ref="K38:L39"/>
-    <mergeCell ref="M38:R39"/>
-    <mergeCell ref="S38:X39"/>
-    <mergeCell ref="C30:K31"/>
-    <mergeCell ref="O20:V20"/>
-    <mergeCell ref="W20:AD20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:N21"/>
-    <mergeCell ref="O21:V21"/>
-    <mergeCell ref="W21:AD21"/>
-    <mergeCell ref="C2:AD2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="W5:AD5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="O5:V5"/>
+    <mergeCell ref="K18:N18"/>
+    <mergeCell ref="W18:AD18"/>
+    <mergeCell ref="C25:K26"/>
+    <mergeCell ref="O25:U25"/>
+    <mergeCell ref="X25:AD25"/>
+    <mergeCell ref="C27:K27"/>
+    <mergeCell ref="C28:K29"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="O18:V18"/>
+    <mergeCell ref="C19:D20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:N20"/>
+    <mergeCell ref="W15:AD15"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="O17:V17"/>
+    <mergeCell ref="W17:AD17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="O15:V15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="W12:AD12"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O14:V14"/>
+    <mergeCell ref="W14:AD14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="O12:V12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="W9:AD9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="O11:V11"/>
+    <mergeCell ref="W11:AD11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:V9"/>
+    <mergeCell ref="K9:N9"/>
     <mergeCell ref="K6:N6"/>
     <mergeCell ref="C7:D8"/>
     <mergeCell ref="E7:F7"/>
@@ -7085,67 +7120,37 @@
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="O6:V6"/>
     <mergeCell ref="W6:AD6"/>
-    <mergeCell ref="W9:AD9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="O11:V11"/>
-    <mergeCell ref="W11:AD11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:V9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="W12:AD12"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="O14:V14"/>
-    <mergeCell ref="W14:AD14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="O12:V12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="W15:AD15"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="O17:V17"/>
-    <mergeCell ref="W17:AD17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="O15:V15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="K18:N18"/>
-    <mergeCell ref="W18:AD18"/>
-    <mergeCell ref="C25:K26"/>
-    <mergeCell ref="O25:U25"/>
-    <mergeCell ref="X25:AD25"/>
-    <mergeCell ref="C27:K27"/>
-    <mergeCell ref="C28:K29"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="O18:V18"/>
-    <mergeCell ref="C19:D20"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:N20"/>
+    <mergeCell ref="C2:AD2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="W5:AD5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="O5:V5"/>
+    <mergeCell ref="D38:F39"/>
+    <mergeCell ref="G38:H39"/>
+    <mergeCell ref="I38:J39"/>
+    <mergeCell ref="K38:L39"/>
+    <mergeCell ref="M38:R39"/>
+    <mergeCell ref="S38:X39"/>
+    <mergeCell ref="C30:K31"/>
+    <mergeCell ref="O20:V20"/>
+    <mergeCell ref="W20:AD20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:N21"/>
+    <mergeCell ref="O21:V21"/>
+    <mergeCell ref="W21:AD21"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 E5 G5 I5 K5:L5 O5 W5 C7 E8 G8 I8 K8:L8 O8 W8 C10 E11 G11 I11 K11:L11 O11 W11 C13 E14 G14 I14 K14:L14 O14 W14 C16 E17 G17 I17 K17 O17 W17">
     <cfRule type="expression" dxfId="3" priority="3">
@@ -7179,23 +7184,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7517,22 +7511,29 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B201CC6-7A0A-429C-B445-7EDA1CF4A1D7}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F0D3479-5903-425F-9669-62B4E7216DE9}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -7559,9 +7560,13 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F0D3479-5903-425F-9669-62B4E7216DE9}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B201CC6-7A0A-429C-B445-7EDA1CF4A1D7}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/Group_milestones.xlsx
+++ b/Group_milestones.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="14" documentId="13_ncr:1_{916827F6-E579-45A9-A0BF-AC19F3C06EA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EBFEC64-9B58-4A68-AE17-EA29B3CD7733}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C40963E-D909-416B-A0DA-6975FE8EC327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="824" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="824" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="52" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="48">
   <si>
     <t>Notes</t>
   </si>
@@ -200,20 +200,6 @@
     <t>EEII1: ICD complete with REII and MCTR2</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">MCTR1: Carriage motor drive test, carriage v3 test </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Seaford"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>EEII1:Order heat sinks and power supply(at the latest)</t>
-    </r>
-  </si>
-  <si>
     <t>EEII1:Working low voltage switching circuit in thevinin lab(one IGBT +driver +opto)</t>
   </si>
   <si>
@@ -290,6 +276,41 @@
       <t>Group: Finalize all ICDs</t>
     </r>
   </si>
+  <si>
+    <t>MCTR2: Motor characterise in heavy current lab with avalable VFD's</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">MCTR1: Carriage motor drive test, carriage v3 test </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">EEII1:Order heat sinks and power supply(at the latest) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MCTR2: Starting with all final draft printing parts</t>
+    </r>
+  </si>
+  <si>
+    <t>MCTR2: Start with gearbox casing build</t>
+  </si>
+  <si>
+    <t>EERI321: PRACTICAL 2 submission</t>
+  </si>
+  <si>
+    <t>EERI321: Semester T3</t>
+  </si>
 </sst>
 </file>
 
@@ -302,7 +323,7 @@
     <numFmt numFmtId="167" formatCode="mmmm\ yyyy"/>
     <numFmt numFmtId="168" formatCode="dddd"/>
   </numFmts>
-  <fonts count="41" x14ac:knownFonts="1">
+  <fonts count="42" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -565,6 +586,13 @@
       <name val="Seaford"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Seaford"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -793,7 +821,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="158">
+  <cellXfs count="159">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1021,6 +1049,102 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1105,145 +1229,52 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="37" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -1617,7 +1648,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R15"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.3" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="4" width="5.5546875" style="3" customWidth="1"/>
     <col min="5" max="9" width="10.5546875" style="3" customWidth="1"/>
@@ -1629,7 +1660,7 @@
     <col min="19" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1649,7 +1680,7 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
     </row>
-    <row r="2" spans="1:18" s="7" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:18" s="7" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
       <c r="B2" s="5"/>
       <c r="C2" s="73" t="s">
@@ -1671,7 +1702,7 @@
       <c r="Q2" s="6"/>
       <c r="R2" s="4"/>
     </row>
-    <row r="3" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="2.15">
+    <row r="3" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="8"/>
@@ -1691,7 +1722,7 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="1"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -1705,15 +1736,15 @@
       <c r="K4" s="12"/>
       <c r="L4" s="11"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="142" t="s">
+      <c r="N4" s="143" t="s">
         <v>10</v>
       </c>
-      <c r="O4" s="142"/>
-      <c r="P4" s="142"/>
-      <c r="Q4" s="142"/>
+      <c r="O4" s="143"/>
+      <c r="P4" s="143"/>
+      <c r="Q4" s="143"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
       <c r="B5" s="11"/>
       <c r="C5" s="13" t="s">
@@ -1731,13 +1762,13 @@
       <c r="K5" s="15"/>
       <c r="L5" s="16"/>
       <c r="M5" s="4"/>
-      <c r="N5" s="142"/>
-      <c r="O5" s="142"/>
-      <c r="P5" s="142"/>
-      <c r="Q5" s="142"/>
+      <c r="N5" s="143"/>
+      <c r="O5" s="143"/>
+      <c r="P5" s="143"/>
+      <c r="Q5" s="143"/>
       <c r="R5" s="1"/>
     </row>
-    <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="1"/>
       <c r="B6" s="11"/>
       <c r="C6" s="17"/>
@@ -1751,13 +1782,13 @@
       <c r="K6" s="20"/>
       <c r="L6" s="19"/>
       <c r="M6" s="4"/>
-      <c r="N6" s="142"/>
-      <c r="O6" s="142"/>
-      <c r="P6" s="142"/>
-      <c r="Q6" s="142"/>
+      <c r="N6" s="143"/>
+      <c r="O6" s="143"/>
+      <c r="P6" s="143"/>
+      <c r="Q6" s="143"/>
       <c r="R6" s="1"/>
     </row>
-    <row r="7" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
       <c r="B7" s="11"/>
       <c r="C7" s="13" t="s">
@@ -1781,7 +1812,7 @@
       <c r="Q7" s="11"/>
       <c r="R7" s="1"/>
     </row>
-    <row r="8" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="11"/>
       <c r="C8" s="17"/>
@@ -1805,7 +1836,7 @@
       </c>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="11"/>
       <c r="C9" s="13" t="s">
@@ -1829,7 +1860,7 @@
       <c r="Q9" s="11"/>
       <c r="R9" s="1"/>
     </row>
-    <row r="10" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
       <c r="B10" s="11"/>
       <c r="C10" s="24"/>
@@ -1855,7 +1886,7 @@
       <c r="Q10" s="18"/>
       <c r="R10" s="1"/>
     </row>
-    <row r="11" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="1"/>
       <c r="B11" s="11"/>
       <c r="C11" s="24"/>
@@ -1875,7 +1906,7 @@
       <c r="Q11" s="18"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="1"/>
       <c r="B12" s="11"/>
       <c r="C12" s="13" t="s">
@@ -1899,7 +1930,7 @@
       <c r="Q12" s="18"/>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="1"/>
       <c r="B13" s="11"/>
       <c r="C13" s="25"/>
@@ -1921,7 +1952,7 @@
       <c r="Q13" s="18"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="1"/>
       <c r="B14" s="11"/>
       <c r="C14" s="18"/>
@@ -1941,7 +1972,7 @@
       <c r="Q14" s="18"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -1976,7 +2007,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AP40"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="12.6" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="5.5546875" style="3" customWidth="1"/>
     <col min="4" max="4" width="15.5546875" style="3" customWidth="1"/>
@@ -1994,7 +2025,7 @@
     <col min="35" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2028,42 +2059,42 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="2.15">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A2" s="29"/>
-      <c r="C2" s="116">
+      <c r="C2" s="112">
         <f ca="1">DATE(About!P8,9,1)</f>
         <v>46266</v>
       </c>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="116"/>
-      <c r="L2" s="116"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="116"/>
-      <c r="P2" s="116"/>
-      <c r="Q2" s="116"/>
-      <c r="R2" s="116"/>
-      <c r="S2" s="116"/>
-      <c r="T2" s="116"/>
-      <c r="U2" s="116"/>
-      <c r="V2" s="116"/>
-      <c r="W2" s="116"/>
-      <c r="X2" s="116"/>
-      <c r="Y2" s="116"/>
-      <c r="Z2" s="116"/>
-      <c r="AA2" s="116"/>
-      <c r="AB2" s="116"/>
-      <c r="AC2" s="116"/>
-      <c r="AD2" s="116"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
+      <c r="F2" s="112"/>
+      <c r="G2" s="112"/>
+      <c r="H2" s="112"/>
+      <c r="I2" s="112"/>
+      <c r="J2" s="112"/>
+      <c r="K2" s="112"/>
+      <c r="L2" s="112"/>
+      <c r="M2" s="112"/>
+      <c r="N2" s="112"/>
+      <c r="O2" s="112"/>
+      <c r="P2" s="112"/>
+      <c r="Q2" s="112"/>
+      <c r="R2" s="112"/>
+      <c r="S2" s="112"/>
+      <c r="T2" s="112"/>
+      <c r="U2" s="112"/>
+      <c r="V2" s="112"/>
+      <c r="W2" s="112"/>
+      <c r="X2" s="112"/>
+      <c r="Y2" s="112"/>
+      <c r="Z2" s="112"/>
+      <c r="AA2" s="112"/>
+      <c r="AB2" s="112"/>
+      <c r="AC2" s="112"/>
+      <c r="AD2" s="112"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="2.15">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -2083,278 +2114,278 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="35"/>
-      <c r="C4" s="117">
+      <c r="C4" s="113">
         <f ca="1">C5</f>
         <v>46264</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117">
+      <c r="D4" s="113"/>
+      <c r="E4" s="113">
         <f ca="1">E5</f>
         <v>46265</v>
       </c>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117">
+      <c r="F4" s="113"/>
+      <c r="G4" s="113">
         <f ca="1">G5</f>
         <v>46266</v>
       </c>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117">
+      <c r="H4" s="113"/>
+      <c r="I4" s="113">
         <f ca="1">I5</f>
         <v>46267</v>
       </c>
-      <c r="J4" s="117"/>
-      <c r="K4" s="117">
+      <c r="J4" s="113"/>
+      <c r="K4" s="113">
         <f ca="1">K5</f>
         <v>46268</v>
       </c>
-      <c r="L4" s="117"/>
-      <c r="M4" s="117"/>
+      <c r="L4" s="113"/>
+      <c r="M4" s="113"/>
       <c r="N4" s="37"/>
-      <c r="O4" s="117">
+      <c r="O4" s="113">
         <f ca="1">O5</f>
         <v>46269</v>
       </c>
-      <c r="P4" s="117"/>
-      <c r="Q4" s="117"/>
-      <c r="R4" s="117"/>
-      <c r="S4" s="117"/>
-      <c r="T4" s="117"/>
-      <c r="U4" s="117"/>
-      <c r="V4" s="117"/>
-      <c r="W4" s="117">
+      <c r="P4" s="113"/>
+      <c r="Q4" s="113"/>
+      <c r="R4" s="113"/>
+      <c r="S4" s="113"/>
+      <c r="T4" s="113"/>
+      <c r="U4" s="113"/>
+      <c r="V4" s="113"/>
+      <c r="W4" s="113">
         <f ca="1">W5</f>
         <v>46270</v>
       </c>
-      <c r="X4" s="117"/>
-      <c r="Y4" s="117"/>
-      <c r="Z4" s="117"/>
-      <c r="AA4" s="117"/>
-      <c r="AB4" s="117"/>
-      <c r="AC4" s="117"/>
-      <c r="AD4" s="117"/>
+      <c r="X4" s="113"/>
+      <c r="Y4" s="113"/>
+      <c r="Z4" s="113"/>
+      <c r="AA4" s="113"/>
+      <c r="AB4" s="113"/>
+      <c r="AC4" s="113"/>
+      <c r="AD4" s="113"/>
       <c r="AF4" s="38"/>
       <c r="AG4" s="39"/>
       <c r="AH4" s="39"/>
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="C5" s="118">
+      <c r="C5" s="90">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46264</v>
       </c>
-      <c r="D5" s="120"/>
-      <c r="E5" s="118">
+      <c r="D5" s="91"/>
+      <c r="E5" s="90">
         <f ca="1">C5+1</f>
         <v>46265</v>
       </c>
-      <c r="F5" s="120"/>
-      <c r="G5" s="118">
+      <c r="F5" s="91"/>
+      <c r="G5" s="90">
         <f ca="1">E5+1</f>
         <v>46266</v>
       </c>
-      <c r="H5" s="120"/>
-      <c r="I5" s="118">
+      <c r="H5" s="91"/>
+      <c r="I5" s="90">
         <f ca="1">G5+1</f>
         <v>46267</v>
       </c>
-      <c r="J5" s="120"/>
-      <c r="K5" s="118">
+      <c r="J5" s="91"/>
+      <c r="K5" s="90">
         <f ca="1">I5+1</f>
         <v>46268</v>
       </c>
-      <c r="L5" s="119"/>
-      <c r="M5" s="119"/>
+      <c r="L5" s="114"/>
+      <c r="M5" s="114"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="118">
+      <c r="O5" s="90">
         <f ca="1">K5+1</f>
         <v>46269</v>
       </c>
-      <c r="P5" s="119"/>
-      <c r="Q5" s="119"/>
-      <c r="R5" s="119"/>
-      <c r="S5" s="119"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="120"/>
-      <c r="W5" s="118">
+      <c r="P5" s="114"/>
+      <c r="Q5" s="114"/>
+      <c r="R5" s="114"/>
+      <c r="S5" s="114"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="114"/>
+      <c r="V5" s="91"/>
+      <c r="W5" s="90">
         <f ca="1">O5+1</f>
         <v>46270</v>
       </c>
-      <c r="X5" s="119"/>
-      <c r="Y5" s="119"/>
-      <c r="Z5" s="119"/>
-      <c r="AA5" s="119"/>
-      <c r="AB5" s="119"/>
-      <c r="AC5" s="119"/>
-      <c r="AD5" s="120"/>
+      <c r="X5" s="114"/>
+      <c r="Y5" s="114"/>
+      <c r="Z5" s="114"/>
+      <c r="AA5" s="114"/>
+      <c r="AB5" s="114"/>
+      <c r="AC5" s="114"/>
+      <c r="AD5" s="91"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
       <c r="AI5" s="41"/>
       <c r="AJ5" s="41"/>
     </row>
-    <row r="6" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="42"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="113"/>
-      <c r="E6" s="111"/>
-      <c r="F6" s="113"/>
-      <c r="G6" s="143"/>
-      <c r="H6" s="144"/>
-      <c r="I6" s="143"/>
-      <c r="J6" s="144"/>
-      <c r="K6" s="143"/>
-      <c r="L6" s="145"/>
-      <c r="M6" s="145"/>
-      <c r="N6" s="144"/>
-      <c r="O6" s="143"/>
-      <c r="P6" s="145"/>
-      <c r="Q6" s="145"/>
-      <c r="R6" s="145"/>
-      <c r="S6" s="145"/>
-      <c r="T6" s="145"/>
-      <c r="U6" s="145"/>
-      <c r="V6" s="144"/>
-      <c r="W6" s="143"/>
-      <c r="X6" s="145"/>
-      <c r="Y6" s="145"/>
-      <c r="Z6" s="145"/>
-      <c r="AA6" s="145"/>
-      <c r="AB6" s="145"/>
-      <c r="AC6" s="145"/>
-      <c r="AD6" s="144"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="83"/>
+      <c r="F6" s="85"/>
+      <c r="G6" s="150"/>
+      <c r="H6" s="151"/>
+      <c r="I6" s="150"/>
+      <c r="J6" s="151"/>
+      <c r="K6" s="150"/>
+      <c r="L6" s="152"/>
+      <c r="M6" s="152"/>
+      <c r="N6" s="151"/>
+      <c r="O6" s="150"/>
+      <c r="P6" s="152"/>
+      <c r="Q6" s="152"/>
+      <c r="R6" s="152"/>
+      <c r="S6" s="152"/>
+      <c r="T6" s="152"/>
+      <c r="U6" s="152"/>
+      <c r="V6" s="151"/>
+      <c r="W6" s="150"/>
+      <c r="X6" s="152"/>
+      <c r="Y6" s="152"/>
+      <c r="Z6" s="152"/>
+      <c r="AA6" s="152"/>
+      <c r="AB6" s="152"/>
+      <c r="AC6" s="152"/>
+      <c r="AD6" s="151"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
-    <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
-      <c r="C7" s="118">
+      <c r="C7" s="90">
         <f ca="1">W5+1</f>
         <v>46271</v>
       </c>
-      <c r="D7" s="120"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="130"/>
-      <c r="G7" s="129"/>
-      <c r="H7" s="130"/>
-      <c r="I7" s="129"/>
-      <c r="J7" s="130"/>
-      <c r="K7" s="129"/>
-      <c r="L7" s="131"/>
-      <c r="M7" s="131"/>
+      <c r="D7" s="91"/>
+      <c r="E7" s="153"/>
+      <c r="F7" s="154"/>
+      <c r="G7" s="153"/>
+      <c r="H7" s="154"/>
+      <c r="I7" s="153"/>
+      <c r="J7" s="154"/>
+      <c r="K7" s="153"/>
+      <c r="L7" s="155"/>
+      <c r="M7" s="155"/>
       <c r="N7" s="75"/>
-      <c r="O7" s="129"/>
-      <c r="P7" s="131"/>
-      <c r="Q7" s="131"/>
-      <c r="R7" s="131"/>
-      <c r="S7" s="131"/>
-      <c r="T7" s="131"/>
-      <c r="U7" s="131"/>
-      <c r="V7" s="130"/>
-      <c r="W7" s="129"/>
-      <c r="X7" s="131"/>
-      <c r="Y7" s="131"/>
-      <c r="Z7" s="131"/>
-      <c r="AA7" s="131"/>
-      <c r="AB7" s="131"/>
-      <c r="AC7" s="131"/>
-      <c r="AD7" s="130"/>
+      <c r="O7" s="153"/>
+      <c r="P7" s="155"/>
+      <c r="Q7" s="155"/>
+      <c r="R7" s="155"/>
+      <c r="S7" s="155"/>
+      <c r="T7" s="155"/>
+      <c r="U7" s="155"/>
+      <c r="V7" s="154"/>
+      <c r="W7" s="153"/>
+      <c r="X7" s="155"/>
+      <c r="Y7" s="155"/>
+      <c r="Z7" s="155"/>
+      <c r="AA7" s="155"/>
+      <c r="AB7" s="155"/>
+      <c r="AC7" s="155"/>
+      <c r="AD7" s="154"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
-      <c r="C8" s="118"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="132">
+      <c r="C8" s="90"/>
+      <c r="D8" s="91"/>
+      <c r="E8" s="94">
         <f ca="1">C7+1</f>
         <v>46272</v>
       </c>
-      <c r="F8" s="133"/>
-      <c r="G8" s="132">
+      <c r="F8" s="95"/>
+      <c r="G8" s="94">
         <f ca="1">E8+1</f>
         <v>46273</v>
       </c>
-      <c r="H8" s="133"/>
-      <c r="I8" s="132">
+      <c r="H8" s="95"/>
+      <c r="I8" s="94">
         <f ca="1">G8+1</f>
         <v>46274</v>
       </c>
-      <c r="J8" s="133"/>
-      <c r="K8" s="132">
+      <c r="J8" s="95"/>
+      <c r="K8" s="94">
         <f ca="1">I8+1</f>
         <v>46275</v>
       </c>
-      <c r="L8" s="134"/>
-      <c r="M8" s="134"/>
+      <c r="L8" s="96"/>
+      <c r="M8" s="96"/>
       <c r="N8" s="50"/>
-      <c r="O8" s="132">
+      <c r="O8" s="94">
         <f ca="1">K8+1</f>
         <v>46276</v>
       </c>
-      <c r="P8" s="134"/>
-      <c r="Q8" s="134"/>
-      <c r="R8" s="134"/>
-      <c r="S8" s="134"/>
-      <c r="T8" s="134"/>
-      <c r="U8" s="134"/>
-      <c r="V8" s="133"/>
-      <c r="W8" s="132">
+      <c r="P8" s="96"/>
+      <c r="Q8" s="96"/>
+      <c r="R8" s="96"/>
+      <c r="S8" s="96"/>
+      <c r="T8" s="96"/>
+      <c r="U8" s="96"/>
+      <c r="V8" s="95"/>
+      <c r="W8" s="94">
         <f ca="1">O8+1</f>
         <v>46277</v>
       </c>
-      <c r="X8" s="134"/>
-      <c r="Y8" s="134"/>
-      <c r="Z8" s="134"/>
-      <c r="AA8" s="134"/>
-      <c r="AB8" s="134"/>
-      <c r="AC8" s="134"/>
-      <c r="AD8" s="133"/>
+      <c r="X8" s="96"/>
+      <c r="Y8" s="96"/>
+      <c r="Z8" s="96"/>
+      <c r="AA8" s="96"/>
+      <c r="AB8" s="96"/>
+      <c r="AC8" s="96"/>
+      <c r="AD8" s="95"/>
       <c r="AF8" s="4"/>
     </row>
-    <row r="9" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="42"/>
-      <c r="C9" s="143"/>
-      <c r="D9" s="144"/>
-      <c r="E9" s="143"/>
-      <c r="F9" s="144"/>
-      <c r="G9" s="143"/>
-      <c r="H9" s="144"/>
-      <c r="I9" s="143"/>
-      <c r="J9" s="144"/>
-      <c r="K9" s="143"/>
-      <c r="L9" s="145"/>
-      <c r="M9" s="145"/>
-      <c r="N9" s="144"/>
-      <c r="O9" s="143"/>
-      <c r="P9" s="145"/>
-      <c r="Q9" s="145"/>
-      <c r="R9" s="145"/>
-      <c r="S9" s="145"/>
-      <c r="T9" s="145"/>
-      <c r="U9" s="145"/>
-      <c r="V9" s="144"/>
-      <c r="W9" s="143"/>
-      <c r="X9" s="145"/>
-      <c r="Y9" s="145"/>
-      <c r="Z9" s="145"/>
-      <c r="AA9" s="145"/>
-      <c r="AB9" s="145"/>
-      <c r="AC9" s="145"/>
-      <c r="AD9" s="144"/>
+      <c r="C9" s="150"/>
+      <c r="D9" s="151"/>
+      <c r="E9" s="150"/>
+      <c r="F9" s="151"/>
+      <c r="G9" s="150"/>
+      <c r="H9" s="151"/>
+      <c r="I9" s="150"/>
+      <c r="J9" s="151"/>
+      <c r="K9" s="150"/>
+      <c r="L9" s="152"/>
+      <c r="M9" s="152"/>
+      <c r="N9" s="151"/>
+      <c r="O9" s="150"/>
+      <c r="P9" s="152"/>
+      <c r="Q9" s="152"/>
+      <c r="R9" s="152"/>
+      <c r="S9" s="152"/>
+      <c r="T9" s="152"/>
+      <c r="U9" s="152"/>
+      <c r="V9" s="151"/>
+      <c r="W9" s="150"/>
+      <c r="X9" s="152"/>
+      <c r="Y9" s="152"/>
+      <c r="Z9" s="152"/>
+      <c r="AA9" s="152"/>
+      <c r="AB9" s="152"/>
+      <c r="AC9" s="152"/>
+      <c r="AD9" s="151"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
-    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="42"/>
-      <c r="C10" s="118">
+      <c r="C10" s="90">
         <f ca="1">W8+1</f>
         <v>46278</v>
       </c>
-      <c r="D10" s="120"/>
+      <c r="D10" s="91"/>
       <c r="E10" s="45"/>
       <c r="F10" s="75"/>
       <c r="G10" s="45"/>
@@ -2384,97 +2415,97 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="42"/>
     </row>
-    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
-      <c r="C11" s="118"/>
-      <c r="D11" s="120"/>
-      <c r="E11" s="132">
+      <c r="C11" s="90"/>
+      <c r="D11" s="91"/>
+      <c r="E11" s="94">
         <f ca="1">C10+1</f>
         <v>46279</v>
       </c>
-      <c r="F11" s="133"/>
-      <c r="G11" s="132">
+      <c r="F11" s="95"/>
+      <c r="G11" s="94">
         <f ca="1">E11+1</f>
         <v>46280</v>
       </c>
-      <c r="H11" s="133"/>
-      <c r="I11" s="132">
+      <c r="H11" s="95"/>
+      <c r="I11" s="94">
         <f ca="1">G11+1</f>
         <v>46281</v>
       </c>
-      <c r="J11" s="133"/>
-      <c r="K11" s="132">
+      <c r="J11" s="95"/>
+      <c r="K11" s="94">
         <f ca="1">I11+1</f>
         <v>46282</v>
       </c>
-      <c r="L11" s="134"/>
-      <c r="M11" s="134"/>
+      <c r="L11" s="96"/>
+      <c r="M11" s="96"/>
       <c r="N11" s="50"/>
-      <c r="O11" s="132">
+      <c r="O11" s="94">
         <f ca="1">K11+1</f>
         <v>46283</v>
       </c>
-      <c r="P11" s="134"/>
-      <c r="Q11" s="134"/>
-      <c r="R11" s="134"/>
-      <c r="S11" s="134"/>
-      <c r="T11" s="134"/>
-      <c r="U11" s="134"/>
-      <c r="V11" s="133"/>
-      <c r="W11" s="132">
+      <c r="P11" s="96"/>
+      <c r="Q11" s="96"/>
+      <c r="R11" s="96"/>
+      <c r="S11" s="96"/>
+      <c r="T11" s="96"/>
+      <c r="U11" s="96"/>
+      <c r="V11" s="95"/>
+      <c r="W11" s="94">
         <f ca="1">O11+1</f>
         <v>46284</v>
       </c>
-      <c r="X11" s="134"/>
-      <c r="Y11" s="134"/>
-      <c r="Z11" s="134"/>
-      <c r="AA11" s="134"/>
-      <c r="AB11" s="134"/>
-      <c r="AC11" s="134"/>
-      <c r="AD11" s="133"/>
+      <c r="X11" s="96"/>
+      <c r="Y11" s="96"/>
+      <c r="Z11" s="96"/>
+      <c r="AA11" s="96"/>
+      <c r="AB11" s="96"/>
+      <c r="AC11" s="96"/>
+      <c r="AD11" s="95"/>
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="42"/>
-      <c r="C12" s="143"/>
-      <c r="D12" s="144"/>
-      <c r="E12" s="143"/>
-      <c r="F12" s="144"/>
-      <c r="G12" s="143"/>
-      <c r="H12" s="144"/>
-      <c r="I12" s="143"/>
-      <c r="J12" s="144"/>
-      <c r="K12" s="143"/>
-      <c r="L12" s="145"/>
-      <c r="M12" s="145"/>
-      <c r="N12" s="144"/>
-      <c r="O12" s="143"/>
-      <c r="P12" s="145"/>
-      <c r="Q12" s="145"/>
-      <c r="R12" s="145"/>
-      <c r="S12" s="145"/>
-      <c r="T12" s="145"/>
-      <c r="U12" s="145"/>
-      <c r="V12" s="144"/>
-      <c r="W12" s="143"/>
-      <c r="X12" s="145"/>
-      <c r="Y12" s="145"/>
-      <c r="Z12" s="145"/>
-      <c r="AA12" s="145"/>
-      <c r="AB12" s="145"/>
-      <c r="AC12" s="145"/>
-      <c r="AD12" s="144"/>
+      <c r="C12" s="150"/>
+      <c r="D12" s="151"/>
+      <c r="E12" s="150"/>
+      <c r="F12" s="151"/>
+      <c r="G12" s="150"/>
+      <c r="H12" s="151"/>
+      <c r="I12" s="150"/>
+      <c r="J12" s="151"/>
+      <c r="K12" s="150"/>
+      <c r="L12" s="152"/>
+      <c r="M12" s="152"/>
+      <c r="N12" s="151"/>
+      <c r="O12" s="150"/>
+      <c r="P12" s="152"/>
+      <c r="Q12" s="152"/>
+      <c r="R12" s="152"/>
+      <c r="S12" s="152"/>
+      <c r="T12" s="152"/>
+      <c r="U12" s="152"/>
+      <c r="V12" s="151"/>
+      <c r="W12" s="150"/>
+      <c r="X12" s="152"/>
+      <c r="Y12" s="152"/>
+      <c r="Z12" s="152"/>
+      <c r="AA12" s="152"/>
+      <c r="AB12" s="152"/>
+      <c r="AC12" s="152"/>
+      <c r="AD12" s="151"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
-    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="42"/>
-      <c r="C13" s="118">
+      <c r="C13" s="90">
         <f ca="1">W11+1</f>
         <v>46285</v>
       </c>
-      <c r="D13" s="120"/>
+      <c r="D13" s="91"/>
       <c r="E13" s="45"/>
       <c r="F13" s="75"/>
       <c r="G13" s="45"/>
@@ -2504,114 +2535,114 @@
       <c r="AE13" s="7"/>
       <c r="AF13" s="42"/>
     </row>
-    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
-      <c r="C14" s="118"/>
-      <c r="D14" s="120"/>
-      <c r="E14" s="132">
+      <c r="C14" s="90"/>
+      <c r="D14" s="91"/>
+      <c r="E14" s="94">
         <f ca="1">C13+1</f>
         <v>46286</v>
       </c>
-      <c r="F14" s="133"/>
-      <c r="G14" s="132">
+      <c r="F14" s="95"/>
+      <c r="G14" s="94">
         <f ca="1">E14+1</f>
         <v>46287</v>
       </c>
-      <c r="H14" s="133"/>
-      <c r="I14" s="132">
+      <c r="H14" s="95"/>
+      <c r="I14" s="94">
         <f ca="1">G14+1</f>
         <v>46288</v>
       </c>
-      <c r="J14" s="133"/>
-      <c r="K14" s="132">
+      <c r="J14" s="95"/>
+      <c r="K14" s="94">
         <f ca="1">I14+1</f>
         <v>46289</v>
       </c>
-      <c r="L14" s="134"/>
-      <c r="M14" s="134"/>
+      <c r="L14" s="96"/>
+      <c r="M14" s="96"/>
       <c r="N14" s="50"/>
-      <c r="O14" s="132">
+      <c r="O14" s="94">
         <f ca="1">K14+1</f>
         <v>46290</v>
       </c>
-      <c r="P14" s="134"/>
-      <c r="Q14" s="134"/>
-      <c r="R14" s="134"/>
-      <c r="S14" s="134"/>
-      <c r="T14" s="134"/>
-      <c r="U14" s="134"/>
-      <c r="V14" s="133"/>
-      <c r="W14" s="132">
+      <c r="P14" s="96"/>
+      <c r="Q14" s="96"/>
+      <c r="R14" s="96"/>
+      <c r="S14" s="96"/>
+      <c r="T14" s="96"/>
+      <c r="U14" s="96"/>
+      <c r="V14" s="95"/>
+      <c r="W14" s="94">
         <f ca="1">O14+1</f>
         <v>46291</v>
       </c>
-      <c r="X14" s="134"/>
-      <c r="Y14" s="134"/>
-      <c r="Z14" s="134"/>
-      <c r="AA14" s="134"/>
-      <c r="AB14" s="134"/>
-      <c r="AC14" s="134"/>
-      <c r="AD14" s="133"/>
+      <c r="X14" s="96"/>
+      <c r="Y14" s="96"/>
+      <c r="Z14" s="96"/>
+      <c r="AA14" s="96"/>
+      <c r="AB14" s="96"/>
+      <c r="AC14" s="96"/>
+      <c r="AD14" s="95"/>
       <c r="AF14" s="4"/>
     </row>
-    <row r="15" spans="1:36" s="43" customFormat="1" ht="162.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:36" s="43" customFormat="1" ht="162.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="42"/>
-      <c r="C15" s="143"/>
-      <c r="D15" s="144"/>
-      <c r="E15" s="143"/>
-      <c r="F15" s="144"/>
-      <c r="G15" s="143"/>
-      <c r="H15" s="144"/>
-      <c r="I15" s="123"/>
-      <c r="J15" s="125"/>
-      <c r="K15" s="123"/>
-      <c r="L15" s="124"/>
-      <c r="M15" s="124"/>
-      <c r="N15" s="125"/>
-      <c r="O15" s="123"/>
-      <c r="P15" s="124"/>
-      <c r="Q15" s="124"/>
-      <c r="R15" s="124"/>
-      <c r="S15" s="124"/>
-      <c r="T15" s="124"/>
-      <c r="U15" s="124"/>
-      <c r="V15" s="125"/>
-      <c r="W15" s="123"/>
-      <c r="X15" s="124"/>
-      <c r="Y15" s="124"/>
-      <c r="Z15" s="124"/>
-      <c r="AA15" s="124"/>
-      <c r="AB15" s="124"/>
-      <c r="AC15" s="124"/>
-      <c r="AD15" s="125"/>
+      <c r="C15" s="150"/>
+      <c r="D15" s="151"/>
+      <c r="E15" s="150"/>
+      <c r="F15" s="151"/>
+      <c r="G15" s="150"/>
+      <c r="H15" s="151"/>
+      <c r="I15" s="146"/>
+      <c r="J15" s="147"/>
+      <c r="K15" s="146"/>
+      <c r="L15" s="149"/>
+      <c r="M15" s="149"/>
+      <c r="N15" s="147"/>
+      <c r="O15" s="146"/>
+      <c r="P15" s="149"/>
+      <c r="Q15" s="149"/>
+      <c r="R15" s="149"/>
+      <c r="S15" s="149"/>
+      <c r="T15" s="149"/>
+      <c r="U15" s="149"/>
+      <c r="V15" s="147"/>
+      <c r="W15" s="146"/>
+      <c r="X15" s="149"/>
+      <c r="Y15" s="149"/>
+      <c r="Z15" s="149"/>
+      <c r="AA15" s="149"/>
+      <c r="AB15" s="149"/>
+      <c r="AC15" s="149"/>
+      <c r="AD15" s="147"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
-    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="42"/>
-      <c r="C16" s="118">
+      <c r="C16" s="90">
         <f ca="1">W14+1</f>
         <v>46292</v>
       </c>
-      <c r="D16" s="120"/>
+      <c r="D16" s="91"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
       <c r="H16" s="75"/>
-      <c r="I16" s="146"/>
-      <c r="J16" s="147"/>
+      <c r="I16" s="92"/>
+      <c r="J16" s="93"/>
       <c r="K16" s="66"/>
       <c r="L16" s="68"/>
       <c r="M16" s="68"/>
       <c r="N16" s="67"/>
-      <c r="O16" s="146"/>
+      <c r="O16" s="92"/>
       <c r="P16" s="148"/>
       <c r="Q16" s="148"/>
       <c r="R16" s="148"/>
       <c r="S16" s="148"/>
       <c r="T16" s="148"/>
       <c r="U16" s="148"/>
-      <c r="V16" s="147"/>
+      <c r="V16" s="93"/>
       <c r="W16" s="45"/>
       <c r="X16" s="76"/>
       <c r="Y16" s="76"/>
@@ -2623,25 +2654,25 @@
       <c r="AE16" s="7"/>
       <c r="AF16" s="42"/>
     </row>
-    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
-      <c r="C17" s="118"/>
-      <c r="D17" s="120"/>
-      <c r="E17" s="132">
+      <c r="C17" s="90"/>
+      <c r="D17" s="91"/>
+      <c r="E17" s="94">
         <f ca="1">C16+1</f>
         <v>46293</v>
       </c>
-      <c r="F17" s="133"/>
-      <c r="G17" s="132">
+      <c r="F17" s="95"/>
+      <c r="G17" s="94">
         <f ca="1">E17+1</f>
         <v>46294</v>
       </c>
-      <c r="H17" s="133"/>
-      <c r="I17" s="132">
+      <c r="H17" s="95"/>
+      <c r="I17" s="94">
         <f ca="1">G17+1</f>
         <v>46295</v>
       </c>
-      <c r="J17" s="133"/>
+      <c r="J17" s="95"/>
       <c r="K17" s="46">
         <f ca="1">I17+1</f>
         <v>46296</v>
@@ -2649,93 +2680,93 @@
       <c r="L17" s="51"/>
       <c r="M17" s="51"/>
       <c r="N17" s="69"/>
-      <c r="O17" s="132">
+      <c r="O17" s="94">
         <f ca="1">K17+1</f>
         <v>46297</v>
       </c>
-      <c r="P17" s="134"/>
-      <c r="Q17" s="134"/>
-      <c r="R17" s="134"/>
-      <c r="S17" s="134"/>
-      <c r="T17" s="134"/>
-      <c r="U17" s="134"/>
-      <c r="V17" s="133"/>
-      <c r="W17" s="132">
+      <c r="P17" s="96"/>
+      <c r="Q17" s="96"/>
+      <c r="R17" s="96"/>
+      <c r="S17" s="96"/>
+      <c r="T17" s="96"/>
+      <c r="U17" s="96"/>
+      <c r="V17" s="95"/>
+      <c r="W17" s="94">
         <f ca="1">O17+1</f>
         <v>46298</v>
       </c>
-      <c r="X17" s="134"/>
-      <c r="Y17" s="134"/>
-      <c r="Z17" s="134"/>
-      <c r="AA17" s="134"/>
-      <c r="AB17" s="134"/>
-      <c r="AC17" s="134"/>
-      <c r="AD17" s="133"/>
+      <c r="X17" s="96"/>
+      <c r="Y17" s="96"/>
+      <c r="Z17" s="96"/>
+      <c r="AA17" s="96"/>
+      <c r="AB17" s="96"/>
+      <c r="AC17" s="96"/>
+      <c r="AD17" s="95"/>
       <c r="AF17" s="4"/>
     </row>
-    <row r="18" spans="1:42" s="43" customFormat="1" ht="147.30000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:42" s="43" customFormat="1" ht="147.30000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="42"/>
-      <c r="C18" s="126" t="s">
+      <c r="C18" s="144" t="s">
         <v>19</v>
       </c>
-      <c r="D18" s="128"/>
-      <c r="E18" s="123"/>
-      <c r="F18" s="125"/>
-      <c r="G18" s="123"/>
-      <c r="H18" s="125"/>
-      <c r="I18" s="126" t="s">
+      <c r="D18" s="145"/>
+      <c r="E18" s="146"/>
+      <c r="F18" s="147"/>
+      <c r="G18" s="146"/>
+      <c r="H18" s="147"/>
+      <c r="I18" s="144" t="s">
         <v>17</v>
       </c>
-      <c r="J18" s="128"/>
+      <c r="J18" s="145"/>
       <c r="K18" s="70"/>
       <c r="L18" s="71"/>
       <c r="M18" s="71"/>
       <c r="N18" s="72"/>
-      <c r="O18" s="111"/>
-      <c r="P18" s="112"/>
-      <c r="Q18" s="112"/>
-      <c r="R18" s="112"/>
-      <c r="S18" s="112"/>
-      <c r="T18" s="112"/>
-      <c r="U18" s="112"/>
-      <c r="V18" s="113"/>
-      <c r="W18" s="111"/>
-      <c r="X18" s="112"/>
-      <c r="Y18" s="112"/>
-      <c r="Z18" s="112"/>
-      <c r="AA18" s="112"/>
-      <c r="AB18" s="112"/>
-      <c r="AC18" s="112"/>
-      <c r="AD18" s="113"/>
+      <c r="O18" s="83"/>
+      <c r="P18" s="84"/>
+      <c r="Q18" s="84"/>
+      <c r="R18" s="84"/>
+      <c r="S18" s="84"/>
+      <c r="T18" s="84"/>
+      <c r="U18" s="84"/>
+      <c r="V18" s="85"/>
+      <c r="W18" s="83"/>
+      <c r="X18" s="84"/>
+      <c r="Y18" s="84"/>
+      <c r="Z18" s="84"/>
+      <c r="AA18" s="84"/>
+      <c r="AB18" s="84"/>
+      <c r="AC18" s="84"/>
+      <c r="AD18" s="85"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
-    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="42"/>
-      <c r="C19" s="118">
+      <c r="C19" s="90">
         <f ca="1">W17+1</f>
         <v>46299</v>
       </c>
-      <c r="D19" s="120"/>
+      <c r="D19" s="91"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
       <c r="H19" s="75"/>
-      <c r="I19" s="146"/>
-      <c r="J19" s="147"/>
+      <c r="I19" s="92"/>
+      <c r="J19" s="93"/>
       <c r="K19" s="66"/>
       <c r="L19" s="68"/>
       <c r="M19" s="68"/>
       <c r="N19" s="67"/>
-      <c r="O19" s="146"/>
+      <c r="O19" s="92"/>
       <c r="P19" s="148"/>
       <c r="Q19" s="148"/>
       <c r="R19" s="148"/>
       <c r="S19" s="148"/>
       <c r="T19" s="148"/>
       <c r="U19" s="148"/>
-      <c r="V19" s="147"/>
+      <c r="V19" s="93"/>
       <c r="W19" s="45"/>
       <c r="X19" s="76"/>
       <c r="Y19" s="76"/>
@@ -2747,25 +2778,25 @@
       <c r="AE19" s="7"/>
       <c r="AF19" s="42"/>
     </row>
-    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
-      <c r="C20" s="118"/>
-      <c r="D20" s="120"/>
-      <c r="E20" s="132">
+      <c r="C20" s="90"/>
+      <c r="D20" s="91"/>
+      <c r="E20" s="94">
         <f ca="1">C19+1</f>
         <v>46300</v>
       </c>
-      <c r="F20" s="133"/>
-      <c r="G20" s="132">
+      <c r="F20" s="95"/>
+      <c r="G20" s="94">
         <f ca="1">E20+1</f>
         <v>46301</v>
       </c>
-      <c r="H20" s="133"/>
-      <c r="I20" s="132">
+      <c r="H20" s="95"/>
+      <c r="I20" s="94">
         <f ca="1">G20+1</f>
         <v>46302</v>
       </c>
-      <c r="J20" s="133"/>
+      <c r="J20" s="95"/>
       <c r="K20" s="46">
         <f ca="1">I20+1</f>
         <v>46303</v>
@@ -2773,65 +2804,65 @@
       <c r="L20" s="51"/>
       <c r="M20" s="51"/>
       <c r="N20" s="69"/>
-      <c r="O20" s="132">
+      <c r="O20" s="94">
         <f ca="1">K20+1</f>
         <v>46304</v>
       </c>
-      <c r="P20" s="134"/>
-      <c r="Q20" s="134"/>
-      <c r="R20" s="134"/>
-      <c r="S20" s="134"/>
-      <c r="T20" s="134"/>
-      <c r="U20" s="134"/>
-      <c r="V20" s="133"/>
-      <c r="W20" s="132">
+      <c r="P20" s="96"/>
+      <c r="Q20" s="96"/>
+      <c r="R20" s="96"/>
+      <c r="S20" s="96"/>
+      <c r="T20" s="96"/>
+      <c r="U20" s="96"/>
+      <c r="V20" s="95"/>
+      <c r="W20" s="94">
         <f ca="1">O20+1</f>
         <v>46305</v>
       </c>
-      <c r="X20" s="134"/>
-      <c r="Y20" s="134"/>
-      <c r="Z20" s="134"/>
-      <c r="AA20" s="134"/>
-      <c r="AB20" s="134"/>
-      <c r="AC20" s="134"/>
-      <c r="AD20" s="133"/>
+      <c r="X20" s="96"/>
+      <c r="Y20" s="96"/>
+      <c r="Z20" s="96"/>
+      <c r="AA20" s="96"/>
+      <c r="AB20" s="96"/>
+      <c r="AC20" s="96"/>
+      <c r="AD20" s="95"/>
       <c r="AF20" s="4"/>
     </row>
-    <row r="21" spans="1:42" s="43" customFormat="1" ht="166.8" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:42" s="43" customFormat="1" ht="166.8" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="42"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="111"/>
-      <c r="H21" s="113"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="113"/>
+      <c r="C21" s="83"/>
+      <c r="D21" s="85"/>
+      <c r="E21" s="83"/>
+      <c r="F21" s="85"/>
+      <c r="G21" s="83"/>
+      <c r="H21" s="85"/>
+      <c r="I21" s="83"/>
+      <c r="J21" s="85"/>
       <c r="K21" s="70"/>
       <c r="L21" s="71"/>
       <c r="M21" s="71"/>
       <c r="N21" s="72"/>
-      <c r="O21" s="111"/>
-      <c r="P21" s="112"/>
-      <c r="Q21" s="112"/>
-      <c r="R21" s="112"/>
-      <c r="S21" s="112"/>
-      <c r="T21" s="112"/>
-      <c r="U21" s="112"/>
-      <c r="V21" s="113"/>
-      <c r="W21" s="111"/>
-      <c r="X21" s="112"/>
-      <c r="Y21" s="112"/>
-      <c r="Z21" s="112"/>
-      <c r="AA21" s="112"/>
-      <c r="AB21" s="112"/>
-      <c r="AC21" s="112"/>
-      <c r="AD21" s="113"/>
+      <c r="O21" s="83"/>
+      <c r="P21" s="84"/>
+      <c r="Q21" s="84"/>
+      <c r="R21" s="84"/>
+      <c r="S21" s="84"/>
+      <c r="T21" s="84"/>
+      <c r="U21" s="84"/>
+      <c r="V21" s="85"/>
+      <c r="W21" s="83"/>
+      <c r="X21" s="84"/>
+      <c r="Y21" s="84"/>
+      <c r="Z21" s="84"/>
+      <c r="AA21" s="84"/>
+      <c r="AB21" s="84"/>
+      <c r="AC21" s="84"/>
+      <c r="AD21" s="85"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
     </row>
-    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52"/>
@@ -2863,7 +2894,7 @@
       <c r="AD22" s="55"/>
       <c r="AF22" s="4"/>
     </row>
-    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="56"/>
@@ -2897,61 +2928,61 @@
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
     </row>
-    <row r="24" spans="1:42" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:42" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="M24" s="1"/>
       <c r="AF24" s="1"/>
     </row>
-    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="C25" s="139" t="s">
+      <c r="C25" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="139"/>
-      <c r="E25" s="139"/>
-      <c r="F25" s="139"/>
-      <c r="G25" s="139"/>
-      <c r="H25" s="139"/>
-      <c r="I25" s="139"/>
-      <c r="J25" s="139"/>
-      <c r="K25" s="139"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="86"/>
+      <c r="H25" s="86"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="86"/>
+      <c r="K25" s="86"/>
       <c r="L25" s="60"/>
       <c r="M25" s="1"/>
-      <c r="O25" s="140">
+      <c r="O25" s="87">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)-1,1)</f>
         <v>46235</v>
       </c>
-      <c r="P25" s="140"/>
-      <c r="Q25" s="140"/>
-      <c r="R25" s="140"/>
-      <c r="S25" s="140"/>
-      <c r="T25" s="140"/>
-      <c r="U25" s="140"/>
+      <c r="P25" s="87"/>
+      <c r="Q25" s="87"/>
+      <c r="R25" s="87"/>
+      <c r="S25" s="87"/>
+      <c r="T25" s="87"/>
+      <c r="U25" s="87"/>
       <c r="V25" s="61"/>
       <c r="W25" s="61"/>
-      <c r="X25" s="140">
+      <c r="X25" s="87">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)+1,1)</f>
         <v>46296</v>
       </c>
-      <c r="Y25" s="140"/>
-      <c r="Z25" s="140"/>
-      <c r="AA25" s="140"/>
-      <c r="AB25" s="140"/>
-      <c r="AC25" s="140"/>
-      <c r="AD25" s="140"/>
+      <c r="Y25" s="87"/>
+      <c r="Z25" s="87"/>
+      <c r="AA25" s="87"/>
+      <c r="AB25" s="87"/>
+      <c r="AC25" s="87"/>
+      <c r="AD25" s="87"/>
       <c r="AF25" s="1"/>
     </row>
-    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="C26" s="139"/>
-      <c r="D26" s="139"/>
-      <c r="E26" s="139"/>
-      <c r="F26" s="139"/>
-      <c r="G26" s="139"/>
-      <c r="H26" s="139"/>
-      <c r="I26" s="139"/>
-      <c r="J26" s="139"/>
-      <c r="K26" s="139"/>
+      <c r="C26" s="86"/>
+      <c r="D26" s="86"/>
+      <c r="E26" s="86"/>
+      <c r="F26" s="86"/>
+      <c r="G26" s="86"/>
+      <c r="H26" s="86"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="K26" s="86"/>
       <c r="L26" s="60"/>
       <c r="M26" s="1"/>
       <c r="O26" s="62" t="str">
@@ -3014,19 +3045,19 @@
       </c>
       <c r="AF26" s="1"/>
     </row>
-    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="C27" s="115" t="s">
+      <c r="C27" s="88" t="s">
         <v>21</v>
       </c>
-      <c r="D27" s="115"/>
-      <c r="E27" s="115"/>
-      <c r="F27" s="115"/>
-      <c r="G27" s="115"/>
-      <c r="H27" s="115"/>
-      <c r="I27" s="115"/>
-      <c r="J27" s="115"/>
-      <c r="K27" s="115"/>
+      <c r="D27" s="88"/>
+      <c r="E27" s="88"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="88"/>
+      <c r="H27" s="88"/>
+      <c r="I27" s="88"/>
+      <c r="J27" s="88"/>
+      <c r="K27" s="88"/>
       <c r="M27" s="1"/>
       <c r="O27" s="64" t="str">
         <f t="shared" ref="O27:U32" ca="1" si="0">IF(MONTH($O$25)&lt;&gt;MONTH($O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1)),"",$O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1))</f>
@@ -3088,19 +3119,19 @@
       </c>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="C28" s="114" t="s">
+      <c r="C28" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="D28" s="114"/>
-      <c r="E28" s="114"/>
-      <c r="F28" s="114"/>
-      <c r="G28" s="114"/>
-      <c r="H28" s="114"/>
-      <c r="I28" s="114"/>
-      <c r="J28" s="114"/>
-      <c r="K28" s="114"/>
+      <c r="D28" s="89"/>
+      <c r="E28" s="89"/>
+      <c r="F28" s="89"/>
+      <c r="G28" s="89"/>
+      <c r="H28" s="89"/>
+      <c r="I28" s="89"/>
+      <c r="J28" s="89"/>
+      <c r="K28" s="89"/>
       <c r="M28" s="1"/>
       <c r="O28" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3162,17 +3193,17 @@
       </c>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="C29" s="115"/>
-      <c r="D29" s="115"/>
-      <c r="E29" s="115"/>
-      <c r="F29" s="115"/>
-      <c r="G29" s="115"/>
-      <c r="H29" s="115"/>
-      <c r="I29" s="115"/>
-      <c r="J29" s="115"/>
-      <c r="K29" s="115"/>
+      <c r="C29" s="88"/>
+      <c r="D29" s="88"/>
+      <c r="E29" s="88"/>
+      <c r="F29" s="88"/>
+      <c r="G29" s="88"/>
+      <c r="H29" s="88"/>
+      <c r="I29" s="88"/>
+      <c r="J29" s="88"/>
+      <c r="K29" s="88"/>
       <c r="M29" s="1"/>
       <c r="O29" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3234,19 +3265,19 @@
       </c>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="C30" s="114" t="s">
+      <c r="C30" s="89" t="s">
         <v>23</v>
       </c>
-      <c r="D30" s="114"/>
-      <c r="E30" s="114"/>
-      <c r="F30" s="114"/>
-      <c r="G30" s="114"/>
-      <c r="H30" s="114"/>
-      <c r="I30" s="114"/>
-      <c r="J30" s="114"/>
-      <c r="K30" s="114"/>
+      <c r="D30" s="89"/>
+      <c r="E30" s="89"/>
+      <c r="F30" s="89"/>
+      <c r="G30" s="89"/>
+      <c r="H30" s="89"/>
+      <c r="I30" s="89"/>
+      <c r="J30" s="89"/>
+      <c r="K30" s="89"/>
       <c r="M30" s="1"/>
       <c r="O30" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3308,17 +3339,17 @@
       </c>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="C31" s="115"/>
-      <c r="D31" s="115"/>
-      <c r="E31" s="115"/>
-      <c r="F31" s="115"/>
-      <c r="G31" s="115"/>
-      <c r="H31" s="115"/>
-      <c r="I31" s="115"/>
-      <c r="J31" s="115"/>
-      <c r="K31" s="115"/>
+      <c r="C31" s="88"/>
+      <c r="D31" s="88"/>
+      <c r="E31" s="88"/>
+      <c r="F31" s="88"/>
+      <c r="G31" s="88"/>
+      <c r="H31" s="88"/>
+      <c r="I31" s="88"/>
+      <c r="J31" s="88"/>
+      <c r="K31" s="88"/>
       <c r="M31" s="1"/>
       <c r="O31" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3380,7 +3411,7 @@
       </c>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:42" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="M32" s="1"/>
       <c r="O32" s="64">
@@ -3443,7 +3474,7 @@
       </c>
       <c r="AF32" s="1"/>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:32" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="M33" s="1"/>
       <c r="O33" s="64"/>
@@ -3464,7 +3495,7 @@
       <c r="AD33" s="65"/>
       <c r="AF33" s="1"/>
     </row>
-    <row r="34" spans="1:32" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:32" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -3498,69 +3529,158 @@
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
     </row>
-    <row r="38" spans="1:32" ht="12.9" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D39" s="83" t="s">
+    <row r="38" spans="1:32" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D39" s="115" t="s">
         <v>24</v>
       </c>
-      <c r="E39" s="84"/>
-      <c r="F39" s="85"/>
-      <c r="G39" s="89">
+      <c r="E39" s="116"/>
+      <c r="F39" s="117"/>
+      <c r="G39" s="121">
         <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
         <v>5</v>
       </c>
-      <c r="H39" s="90"/>
-      <c r="I39" s="83" t="s">
+      <c r="H39" s="122"/>
+      <c r="I39" s="115" t="s">
         <v>27</v>
       </c>
-      <c r="J39" s="93"/>
-      <c r="K39" s="95" t="s">
+      <c r="J39" s="125"/>
+      <c r="K39" s="127" t="s">
         <v>25</v>
       </c>
-      <c r="L39" s="96"/>
-      <c r="M39" s="99">
+      <c r="L39" s="128"/>
+      <c r="M39" s="131">
         <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
-        <v>5.9999999999999973</v>
-      </c>
-      <c r="N39" s="100"/>
-      <c r="O39" s="100"/>
-      <c r="P39" s="100"/>
-      <c r="Q39" s="100"/>
-      <c r="R39" s="101"/>
-      <c r="S39" s="105" t="s">
+        <v>5.0000000000000009</v>
+      </c>
+      <c r="N39" s="132"/>
+      <c r="O39" s="132"/>
+      <c r="P39" s="132"/>
+      <c r="Q39" s="132"/>
+      <c r="R39" s="133"/>
+      <c r="S39" s="137" t="s">
         <v>26</v>
       </c>
-      <c r="T39" s="106"/>
-      <c r="U39" s="106"/>
-      <c r="V39" s="106"/>
-      <c r="W39" s="106"/>
-      <c r="X39" s="107"/>
-    </row>
-    <row r="40" spans="1:32" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D40" s="86"/>
-      <c r="E40" s="87"/>
-      <c r="F40" s="88"/>
-      <c r="G40" s="91"/>
-      <c r="H40" s="92"/>
-      <c r="I40" s="86"/>
-      <c r="J40" s="94"/>
-      <c r="K40" s="97"/>
-      <c r="L40" s="98"/>
-      <c r="M40" s="102"/>
-      <c r="N40" s="103"/>
-      <c r="O40" s="103"/>
-      <c r="P40" s="103"/>
-      <c r="Q40" s="103"/>
-      <c r="R40" s="104"/>
-      <c r="S40" s="108"/>
-      <c r="T40" s="109"/>
-      <c r="U40" s="109"/>
-      <c r="V40" s="109"/>
-      <c r="W40" s="109"/>
-      <c r="X40" s="110"/>
+      <c r="T39" s="138"/>
+      <c r="U39" s="138"/>
+      <c r="V39" s="138"/>
+      <c r="W39" s="138"/>
+      <c r="X39" s="139"/>
+    </row>
+    <row r="40" spans="1:32" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D40" s="118"/>
+      <c r="E40" s="119"/>
+      <c r="F40" s="120"/>
+      <c r="G40" s="123"/>
+      <c r="H40" s="124"/>
+      <c r="I40" s="118"/>
+      <c r="J40" s="126"/>
+      <c r="K40" s="129"/>
+      <c r="L40" s="130"/>
+      <c r="M40" s="134"/>
+      <c r="N40" s="135"/>
+      <c r="O40" s="135"/>
+      <c r="P40" s="135"/>
+      <c r="Q40" s="135"/>
+      <c r="R40" s="136"/>
+      <c r="S40" s="140"/>
+      <c r="T40" s="141"/>
+      <c r="U40" s="141"/>
+      <c r="V40" s="141"/>
+      <c r="W40" s="141"/>
+      <c r="X40" s="142"/>
     </row>
   </sheetData>
   <mergeCells count="110">
+    <mergeCell ref="D39:F40"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="K39:L40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="S39:X40"/>
+    <mergeCell ref="M39:R40"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="O20:V20"/>
+    <mergeCell ref="C30:K31"/>
+    <mergeCell ref="C2:AD2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="W5:AD5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:V6"/>
+    <mergeCell ref="W6:AD6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="O5:V5"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="W7:AD7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="O8:V8"/>
+    <mergeCell ref="W8:AD8"/>
+    <mergeCell ref="O7:V7"/>
+    <mergeCell ref="W9:AD9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="O11:V11"/>
+    <mergeCell ref="W11:AD11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:V9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="W12:AD12"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O14:V14"/>
+    <mergeCell ref="W14:AD14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="O12:V12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="W15:AD15"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="O17:V17"/>
+    <mergeCell ref="W17:AD17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="O15:V15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="O16:V16"/>
     <mergeCell ref="W18:AD18"/>
     <mergeCell ref="C25:K26"/>
     <mergeCell ref="O25:U25"/>
@@ -3582,95 +3702,6 @@
     <mergeCell ref="O21:V21"/>
     <mergeCell ref="W21:AD21"/>
     <mergeCell ref="O19:V19"/>
-    <mergeCell ref="W15:AD15"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="O17:V17"/>
-    <mergeCell ref="W17:AD17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="O15:V15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="O16:V16"/>
-    <mergeCell ref="W12:AD12"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="O14:V14"/>
-    <mergeCell ref="W14:AD14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="O12:V12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="W9:AD9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="O11:V11"/>
-    <mergeCell ref="W11:AD11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:V9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="W7:AD7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="O8:V8"/>
-    <mergeCell ref="W8:AD8"/>
-    <mergeCell ref="O7:V7"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:V6"/>
-    <mergeCell ref="W6:AD6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="O5:V5"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="C2:AD2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="W5:AD5"/>
-    <mergeCell ref="D39:F40"/>
-    <mergeCell ref="G39:H40"/>
-    <mergeCell ref="K39:L40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="S39:X40"/>
-    <mergeCell ref="M39:R40"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="O20:V20"/>
-    <mergeCell ref="C30:K31"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 E5 G5 I5 K5:L5 O5 W5 C7 E8 G8 I8 K8:L8 O8 W8 C10 E11 G11 I11 K11:L11 O11 W11 C13 E14 G14 I14 K14:L14 O14 W14 C16 E17 G17 I17 K17:L17 O17 W17">
     <cfRule type="expression" dxfId="11" priority="3">
@@ -3709,7 +3740,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AP40"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="12.6" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="5.5546875" style="3" customWidth="1"/>
     <col min="4" max="4" width="15.5546875" style="3" customWidth="1"/>
@@ -3727,7 +3758,7 @@
     <col min="35" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3761,42 +3792,42 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="2.15">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A2" s="29"/>
-      <c r="C2" s="116">
+      <c r="C2" s="112">
         <f ca="1">DATE(About!P8,10,1)</f>
         <v>46296</v>
       </c>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="116"/>
-      <c r="L2" s="116"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="116"/>
-      <c r="P2" s="116"/>
-      <c r="Q2" s="116"/>
-      <c r="R2" s="116"/>
-      <c r="S2" s="116"/>
-      <c r="T2" s="116"/>
-      <c r="U2" s="116"/>
-      <c r="V2" s="116"/>
-      <c r="W2" s="116"/>
-      <c r="X2" s="116"/>
-      <c r="Y2" s="116"/>
-      <c r="Z2" s="116"/>
-      <c r="AA2" s="116"/>
-      <c r="AB2" s="116"/>
-      <c r="AC2" s="116"/>
-      <c r="AD2" s="116"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
+      <c r="F2" s="112"/>
+      <c r="G2" s="112"/>
+      <c r="H2" s="112"/>
+      <c r="I2" s="112"/>
+      <c r="J2" s="112"/>
+      <c r="K2" s="112"/>
+      <c r="L2" s="112"/>
+      <c r="M2" s="112"/>
+      <c r="N2" s="112"/>
+      <c r="O2" s="112"/>
+      <c r="P2" s="112"/>
+      <c r="Q2" s="112"/>
+      <c r="R2" s="112"/>
+      <c r="S2" s="112"/>
+      <c r="T2" s="112"/>
+      <c r="U2" s="112"/>
+      <c r="V2" s="112"/>
+      <c r="W2" s="112"/>
+      <c r="X2" s="112"/>
+      <c r="Y2" s="112"/>
+      <c r="Z2" s="112"/>
+      <c r="AA2" s="112"/>
+      <c r="AB2" s="112"/>
+      <c r="AC2" s="112"/>
+      <c r="AD2" s="112"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="2.15">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -3816,288 +3847,290 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="35"/>
-      <c r="C4" s="117">
+      <c r="C4" s="113">
         <f ca="1">C5</f>
         <v>46292</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117">
+      <c r="D4" s="113"/>
+      <c r="E4" s="113">
         <f ca="1">E5</f>
         <v>46293</v>
       </c>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117">
+      <c r="F4" s="113"/>
+      <c r="G4" s="113">
         <f ca="1">G5</f>
         <v>46294</v>
       </c>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117">
+      <c r="H4" s="113"/>
+      <c r="I4" s="113">
         <f ca="1">I5</f>
         <v>46295</v>
       </c>
-      <c r="J4" s="117"/>
-      <c r="K4" s="117">
+      <c r="J4" s="113"/>
+      <c r="K4" s="113">
         <f ca="1">K5</f>
         <v>46296</v>
       </c>
-      <c r="L4" s="117"/>
-      <c r="M4" s="117"/>
+      <c r="L4" s="113"/>
+      <c r="M4" s="113"/>
       <c r="N4" s="37"/>
-      <c r="O4" s="117">
+      <c r="O4" s="113">
         <f ca="1">O5</f>
         <v>46297</v>
       </c>
-      <c r="P4" s="117"/>
-      <c r="Q4" s="117"/>
-      <c r="R4" s="117"/>
-      <c r="S4" s="117"/>
-      <c r="T4" s="117"/>
-      <c r="U4" s="117"/>
-      <c r="V4" s="117"/>
-      <c r="W4" s="117">
+      <c r="P4" s="113"/>
+      <c r="Q4" s="113"/>
+      <c r="R4" s="113"/>
+      <c r="S4" s="113"/>
+      <c r="T4" s="113"/>
+      <c r="U4" s="113"/>
+      <c r="V4" s="113"/>
+      <c r="W4" s="113">
         <f ca="1">W5</f>
         <v>46298</v>
       </c>
-      <c r="X4" s="117"/>
-      <c r="Y4" s="117"/>
-      <c r="Z4" s="117"/>
-      <c r="AA4" s="117"/>
-      <c r="AB4" s="117"/>
-      <c r="AC4" s="117"/>
-      <c r="AD4" s="117"/>
+      <c r="X4" s="113"/>
+      <c r="Y4" s="113"/>
+      <c r="Z4" s="113"/>
+      <c r="AA4" s="113"/>
+      <c r="AB4" s="113"/>
+      <c r="AC4" s="113"/>
+      <c r="AD4" s="113"/>
       <c r="AF4" s="38"/>
       <c r="AG4" s="39"/>
       <c r="AH4" s="39"/>
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="C5" s="118">
+      <c r="C5" s="90">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46292</v>
       </c>
-      <c r="D5" s="120"/>
-      <c r="E5" s="118">
+      <c r="D5" s="91"/>
+      <c r="E5" s="90">
         <f ca="1">C5+1</f>
         <v>46293</v>
       </c>
-      <c r="F5" s="120"/>
-      <c r="G5" s="118">
+      <c r="F5" s="91"/>
+      <c r="G5" s="90">
         <f ca="1">E5+1</f>
         <v>46294</v>
       </c>
-      <c r="H5" s="120"/>
-      <c r="I5" s="118">
+      <c r="H5" s="91"/>
+      <c r="I5" s="90">
         <f ca="1">G5+1</f>
         <v>46295</v>
       </c>
-      <c r="J5" s="120"/>
-      <c r="K5" s="118">
+      <c r="J5" s="91"/>
+      <c r="K5" s="90">
         <f ca="1">I5+1</f>
         <v>46296</v>
       </c>
-      <c r="L5" s="119"/>
-      <c r="M5" s="119"/>
+      <c r="L5" s="114"/>
+      <c r="M5" s="114"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="118">
+      <c r="O5" s="90">
         <f ca="1">K5+1</f>
         <v>46297</v>
       </c>
-      <c r="P5" s="119"/>
-      <c r="Q5" s="119"/>
-      <c r="R5" s="119"/>
-      <c r="S5" s="119"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="120"/>
-      <c r="W5" s="118">
+      <c r="P5" s="114"/>
+      <c r="Q5" s="114"/>
+      <c r="R5" s="114"/>
+      <c r="S5" s="114"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="114"/>
+      <c r="V5" s="91"/>
+      <c r="W5" s="90">
         <f ca="1">O5+1</f>
         <v>46298</v>
       </c>
-      <c r="X5" s="119"/>
-      <c r="Y5" s="119"/>
-      <c r="Z5" s="119"/>
-      <c r="AA5" s="119"/>
-      <c r="AB5" s="119"/>
-      <c r="AC5" s="119"/>
-      <c r="AD5" s="120"/>
+      <c r="X5" s="114"/>
+      <c r="Y5" s="114"/>
+      <c r="Z5" s="114"/>
+      <c r="AA5" s="114"/>
+      <c r="AB5" s="114"/>
+      <c r="AC5" s="114"/>
+      <c r="AD5" s="91"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
       <c r="AI5" s="41"/>
       <c r="AJ5" s="41"/>
     </row>
-    <row r="6" spans="1:36" s="43" customFormat="1" ht="131.69999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:36" s="43" customFormat="1" ht="131.69999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="42"/>
-      <c r="C6" s="121"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="121"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="121"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="121"/>
-      <c r="J6" s="122"/>
-      <c r="K6" s="123"/>
-      <c r="L6" s="124"/>
-      <c r="M6" s="124"/>
-      <c r="N6" s="125"/>
-      <c r="O6" s="123"/>
-      <c r="P6" s="124"/>
-      <c r="Q6" s="124"/>
-      <c r="R6" s="124"/>
-      <c r="S6" s="124"/>
-      <c r="T6" s="124"/>
-      <c r="U6" s="124"/>
-      <c r="V6" s="125"/>
-      <c r="W6" s="126" t="s">
+      <c r="C6" s="97"/>
+      <c r="D6" s="99"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="99"/>
+      <c r="G6" s="97"/>
+      <c r="H6" s="99"/>
+      <c r="I6" s="97"/>
+      <c r="J6" s="99"/>
+      <c r="K6" s="146"/>
+      <c r="L6" s="149"/>
+      <c r="M6" s="149"/>
+      <c r="N6" s="147"/>
+      <c r="O6" s="146"/>
+      <c r="P6" s="149"/>
+      <c r="Q6" s="149"/>
+      <c r="R6" s="149"/>
+      <c r="S6" s="149"/>
+      <c r="T6" s="149"/>
+      <c r="U6" s="149"/>
+      <c r="V6" s="147"/>
+      <c r="W6" s="144" t="s">
         <v>20</v>
       </c>
-      <c r="X6" s="127"/>
-      <c r="Y6" s="127"/>
-      <c r="Z6" s="127"/>
-      <c r="AA6" s="127"/>
-      <c r="AB6" s="127"/>
-      <c r="AC6" s="127"/>
-      <c r="AD6" s="128"/>
+      <c r="X6" s="157"/>
+      <c r="Y6" s="157"/>
+      <c r="Z6" s="157"/>
+      <c r="AA6" s="157"/>
+      <c r="AB6" s="157"/>
+      <c r="AC6" s="157"/>
+      <c r="AD6" s="145"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
-    <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
-      <c r="C7" s="118">
+      <c r="C7" s="90">
         <f ca="1">W5+1</f>
         <v>46299</v>
       </c>
-      <c r="D7" s="120"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="130"/>
-      <c r="G7" s="129"/>
-      <c r="H7" s="130"/>
-      <c r="I7" s="129"/>
-      <c r="J7" s="130"/>
-      <c r="K7" s="129"/>
-      <c r="L7" s="131"/>
-      <c r="M7" s="131"/>
+      <c r="D7" s="91"/>
+      <c r="E7" s="153"/>
+      <c r="F7" s="154"/>
+      <c r="G7" s="153"/>
+      <c r="H7" s="154"/>
+      <c r="I7" s="153"/>
+      <c r="J7" s="154"/>
+      <c r="K7" s="153"/>
+      <c r="L7" s="155"/>
+      <c r="M7" s="155"/>
       <c r="N7" s="75"/>
-      <c r="O7" s="129"/>
-      <c r="P7" s="131"/>
-      <c r="Q7" s="131"/>
-      <c r="R7" s="131"/>
-      <c r="S7" s="131"/>
-      <c r="T7" s="131"/>
-      <c r="U7" s="131"/>
-      <c r="V7" s="130"/>
-      <c r="W7" s="129"/>
-      <c r="X7" s="131"/>
-      <c r="Y7" s="131"/>
-      <c r="Z7" s="131"/>
-      <c r="AA7" s="131"/>
-      <c r="AB7" s="131"/>
-      <c r="AC7" s="131"/>
-      <c r="AD7" s="130"/>
+      <c r="O7" s="153"/>
+      <c r="P7" s="155"/>
+      <c r="Q7" s="155"/>
+      <c r="R7" s="155"/>
+      <c r="S7" s="155"/>
+      <c r="T7" s="155"/>
+      <c r="U7" s="155"/>
+      <c r="V7" s="154"/>
+      <c r="W7" s="153"/>
+      <c r="X7" s="155"/>
+      <c r="Y7" s="155"/>
+      <c r="Z7" s="155"/>
+      <c r="AA7" s="155"/>
+      <c r="AB7" s="155"/>
+      <c r="AC7" s="155"/>
+      <c r="AD7" s="154"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
-      <c r="C8" s="118"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="132">
+      <c r="C8" s="90"/>
+      <c r="D8" s="91"/>
+      <c r="E8" s="94">
         <f ca="1">C7+1</f>
         <v>46300</v>
       </c>
-      <c r="F8" s="133"/>
-      <c r="G8" s="132">
+      <c r="F8" s="95"/>
+      <c r="G8" s="94">
         <f ca="1">E8+1</f>
         <v>46301</v>
       </c>
-      <c r="H8" s="133"/>
-      <c r="I8" s="132">
+      <c r="H8" s="95"/>
+      <c r="I8" s="94">
         <f ca="1">G8+1</f>
         <v>46302</v>
       </c>
-      <c r="J8" s="133"/>
-      <c r="K8" s="132">
+      <c r="J8" s="95"/>
+      <c r="K8" s="94">
         <f ca="1">I8+1</f>
         <v>46303</v>
       </c>
-      <c r="L8" s="134"/>
-      <c r="M8" s="134"/>
+      <c r="L8" s="96"/>
+      <c r="M8" s="96"/>
       <c r="N8" s="50"/>
-      <c r="O8" s="132">
+      <c r="O8" s="94">
         <f ca="1">K8+1</f>
         <v>46304</v>
       </c>
-      <c r="P8" s="134"/>
-      <c r="Q8" s="134"/>
-      <c r="R8" s="134"/>
-      <c r="S8" s="134"/>
-      <c r="T8" s="134"/>
-      <c r="U8" s="134"/>
-      <c r="V8" s="133"/>
-      <c r="W8" s="132">
+      <c r="P8" s="96"/>
+      <c r="Q8" s="96"/>
+      <c r="R8" s="96"/>
+      <c r="S8" s="96"/>
+      <c r="T8" s="96"/>
+      <c r="U8" s="96"/>
+      <c r="V8" s="95"/>
+      <c r="W8" s="94">
         <f ca="1">O8+1</f>
         <v>46305</v>
       </c>
-      <c r="X8" s="134"/>
-      <c r="Y8" s="134"/>
-      <c r="Z8" s="134"/>
-      <c r="AA8" s="134"/>
-      <c r="AB8" s="134"/>
-      <c r="AC8" s="134"/>
-      <c r="AD8" s="133"/>
+      <c r="X8" s="96"/>
+      <c r="Y8" s="96"/>
+      <c r="Z8" s="96"/>
+      <c r="AA8" s="96"/>
+      <c r="AB8" s="96"/>
+      <c r="AC8" s="96"/>
+      <c r="AD8" s="95"/>
       <c r="AF8" s="4"/>
     </row>
-    <row r="9" spans="1:36" s="43" customFormat="1" ht="149.69999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:36" s="43" customFormat="1" ht="149.69999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="42"/>
-      <c r="C9" s="135"/>
-      <c r="D9" s="137"/>
-      <c r="E9" s="135" t="s">
+      <c r="C9" s="105"/>
+      <c r="D9" s="106"/>
+      <c r="E9" s="105" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="137"/>
-      <c r="G9" s="135" t="s">
+      <c r="F9" s="106"/>
+      <c r="G9" s="105" t="s">
         <v>28</v>
       </c>
-      <c r="H9" s="137"/>
-      <c r="I9" s="135"/>
-      <c r="J9" s="137"/>
-      <c r="K9" s="135" t="s">
+      <c r="H9" s="106"/>
+      <c r="I9" s="105" t="s">
+        <v>43</v>
+      </c>
+      <c r="J9" s="106"/>
+      <c r="K9" s="105" t="s">
         <v>30</v>
       </c>
-      <c r="L9" s="136"/>
-      <c r="M9" s="136"/>
-      <c r="N9" s="137"/>
-      <c r="O9" s="135" t="s">
-        <v>32</v>
-      </c>
-      <c r="P9" s="136"/>
-      <c r="Q9" s="136"/>
-      <c r="R9" s="136"/>
-      <c r="S9" s="136"/>
-      <c r="T9" s="136"/>
-      <c r="U9" s="136"/>
-      <c r="V9" s="137"/>
-      <c r="W9" s="135"/>
-      <c r="X9" s="136"/>
-      <c r="Y9" s="136"/>
-      <c r="Z9" s="136"/>
-      <c r="AA9" s="136"/>
-      <c r="AB9" s="136"/>
-      <c r="AC9" s="136"/>
-      <c r="AD9" s="137"/>
+      <c r="L9" s="108"/>
+      <c r="M9" s="108"/>
+      <c r="N9" s="106"/>
+      <c r="O9" s="105" t="s">
+        <v>44</v>
+      </c>
+      <c r="P9" s="108"/>
+      <c r="Q9" s="108"/>
+      <c r="R9" s="108"/>
+      <c r="S9" s="108"/>
+      <c r="T9" s="108"/>
+      <c r="U9" s="108"/>
+      <c r="V9" s="106"/>
+      <c r="W9" s="105"/>
+      <c r="X9" s="108"/>
+      <c r="Y9" s="108"/>
+      <c r="Z9" s="108"/>
+      <c r="AA9" s="108"/>
+      <c r="AB9" s="108"/>
+      <c r="AC9" s="108"/>
+      <c r="AD9" s="106"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
-    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="42"/>
-      <c r="C10" s="118">
+      <c r="C10" s="90">
         <f ca="1">W8+1</f>
         <v>46306</v>
       </c>
-      <c r="D10" s="120"/>
+      <c r="D10" s="91"/>
       <c r="E10" s="45"/>
       <c r="F10" s="75"/>
       <c r="G10" s="45"/>
@@ -4127,101 +4160,107 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="42"/>
     </row>
-    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
-      <c r="C11" s="118"/>
-      <c r="D11" s="120"/>
-      <c r="E11" s="132">
+      <c r="C11" s="90"/>
+      <c r="D11" s="91"/>
+      <c r="E11" s="94">
         <f ca="1">C10+1</f>
         <v>46307</v>
       </c>
-      <c r="F11" s="133"/>
-      <c r="G11" s="132">
+      <c r="F11" s="95"/>
+      <c r="G11" s="94">
         <f ca="1">E11+1</f>
         <v>46308</v>
       </c>
-      <c r="H11" s="133"/>
-      <c r="I11" s="132">
+      <c r="H11" s="95"/>
+      <c r="I11" s="94">
         <f ca="1">G11+1</f>
         <v>46309</v>
       </c>
-      <c r="J11" s="133"/>
-      <c r="K11" s="132">
+      <c r="J11" s="95"/>
+      <c r="K11" s="94">
         <f ca="1">I11+1</f>
         <v>46310</v>
       </c>
-      <c r="L11" s="134"/>
-      <c r="M11" s="134"/>
+      <c r="L11" s="96"/>
+      <c r="M11" s="96"/>
       <c r="N11" s="50"/>
-      <c r="O11" s="132">
+      <c r="O11" s="94">
         <f ca="1">K11+1</f>
         <v>46311</v>
       </c>
-      <c r="P11" s="134"/>
-      <c r="Q11" s="134"/>
-      <c r="R11" s="134"/>
-      <c r="S11" s="134"/>
-      <c r="T11" s="134"/>
-      <c r="U11" s="134"/>
-      <c r="V11" s="133"/>
-      <c r="W11" s="132">
+      <c r="P11" s="96"/>
+      <c r="Q11" s="96"/>
+      <c r="R11" s="96"/>
+      <c r="S11" s="96"/>
+      <c r="T11" s="96"/>
+      <c r="U11" s="96"/>
+      <c r="V11" s="95"/>
+      <c r="W11" s="94">
         <f ca="1">O11+1</f>
         <v>46312</v>
       </c>
-      <c r="X11" s="134"/>
-      <c r="Y11" s="134"/>
-      <c r="Z11" s="134"/>
-      <c r="AA11" s="134"/>
-      <c r="AB11" s="134"/>
-      <c r="AC11" s="134"/>
-      <c r="AD11" s="133"/>
+      <c r="X11" s="96"/>
+      <c r="Y11" s="96"/>
+      <c r="Z11" s="96"/>
+      <c r="AA11" s="96"/>
+      <c r="AB11" s="96"/>
+      <c r="AC11" s="96"/>
+      <c r="AD11" s="95"/>
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:36" s="43" customFormat="1" ht="134.69999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:36" s="43" customFormat="1" ht="134.69999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="42"/>
-      <c r="C12" s="135"/>
-      <c r="D12" s="137"/>
-      <c r="E12" s="135"/>
-      <c r="F12" s="137"/>
-      <c r="G12" s="135"/>
-      <c r="H12" s="137"/>
-      <c r="I12" s="135"/>
-      <c r="J12" s="137"/>
-      <c r="K12" s="135"/>
-      <c r="L12" s="136"/>
-      <c r="M12" s="136"/>
-      <c r="N12" s="137"/>
-      <c r="O12" s="135" t="s">
-        <v>41</v>
-      </c>
-      <c r="P12" s="136"/>
-      <c r="Q12" s="136"/>
-      <c r="R12" s="136"/>
-      <c r="S12" s="136"/>
-      <c r="T12" s="136"/>
-      <c r="U12" s="136"/>
-      <c r="V12" s="137"/>
-      <c r="W12" s="138" t="s">
+      <c r="C12" s="105"/>
+      <c r="D12" s="106"/>
+      <c r="E12" s="158" t="s">
+        <v>46</v>
+      </c>
+      <c r="F12" s="106"/>
+      <c r="G12" s="105" t="s">
+        <v>45</v>
+      </c>
+      <c r="H12" s="106"/>
+      <c r="I12" s="105"/>
+      <c r="J12" s="106"/>
+      <c r="K12" s="158" t="s">
+        <v>47</v>
+      </c>
+      <c r="L12" s="108"/>
+      <c r="M12" s="108"/>
+      <c r="N12" s="106"/>
+      <c r="O12" s="105" t="s">
+        <v>40</v>
+      </c>
+      <c r="P12" s="108"/>
+      <c r="Q12" s="108"/>
+      <c r="R12" s="108"/>
+      <c r="S12" s="108"/>
+      <c r="T12" s="108"/>
+      <c r="U12" s="108"/>
+      <c r="V12" s="106"/>
+      <c r="W12" s="156" t="s">
         <v>31</v>
       </c>
-      <c r="X12" s="136"/>
-      <c r="Y12" s="136"/>
-      <c r="Z12" s="136"/>
-      <c r="AA12" s="136"/>
-      <c r="AB12" s="136"/>
-      <c r="AC12" s="136"/>
-      <c r="AD12" s="137"/>
+      <c r="X12" s="108"/>
+      <c r="Y12" s="108"/>
+      <c r="Z12" s="108"/>
+      <c r="AA12" s="108"/>
+      <c r="AB12" s="108"/>
+      <c r="AC12" s="108"/>
+      <c r="AD12" s="106"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
-    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="42"/>
-      <c r="C13" s="118">
+      <c r="C13" s="90">
         <f ca="1">W11+1</f>
         <v>46313</v>
       </c>
-      <c r="D13" s="120"/>
+      <c r="D13" s="91"/>
       <c r="E13" s="45"/>
       <c r="F13" s="75"/>
       <c r="G13" s="45"/>
@@ -4251,104 +4290,104 @@
       <c r="AE13" s="7"/>
       <c r="AF13" s="42"/>
     </row>
-    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
-      <c r="C14" s="118"/>
-      <c r="D14" s="120"/>
-      <c r="E14" s="132">
+      <c r="C14" s="90"/>
+      <c r="D14" s="91"/>
+      <c r="E14" s="94">
         <f ca="1">C13+1</f>
         <v>46314</v>
       </c>
-      <c r="F14" s="133"/>
-      <c r="G14" s="132">
+      <c r="F14" s="95"/>
+      <c r="G14" s="94">
         <f ca="1">E14+1</f>
         <v>46315</v>
       </c>
-      <c r="H14" s="133"/>
-      <c r="I14" s="132">
+      <c r="H14" s="95"/>
+      <c r="I14" s="94">
         <f ca="1">G14+1</f>
         <v>46316</v>
       </c>
-      <c r="J14" s="133"/>
-      <c r="K14" s="132">
+      <c r="J14" s="95"/>
+      <c r="K14" s="94">
         <f ca="1">I14+1</f>
         <v>46317</v>
       </c>
-      <c r="L14" s="134"/>
-      <c r="M14" s="134"/>
+      <c r="L14" s="96"/>
+      <c r="M14" s="96"/>
       <c r="N14" s="50"/>
-      <c r="O14" s="132">
+      <c r="O14" s="94">
         <f ca="1">K14+1</f>
         <v>46318</v>
       </c>
-      <c r="P14" s="134"/>
-      <c r="Q14" s="134"/>
-      <c r="R14" s="134"/>
-      <c r="S14" s="134"/>
-      <c r="T14" s="134"/>
-      <c r="U14" s="134"/>
-      <c r="V14" s="133"/>
-      <c r="W14" s="132">
+      <c r="P14" s="96"/>
+      <c r="Q14" s="96"/>
+      <c r="R14" s="96"/>
+      <c r="S14" s="96"/>
+      <c r="T14" s="96"/>
+      <c r="U14" s="96"/>
+      <c r="V14" s="95"/>
+      <c r="W14" s="94">
         <f ca="1">O14+1</f>
         <v>46319</v>
       </c>
-      <c r="X14" s="134"/>
-      <c r="Y14" s="134"/>
-      <c r="Z14" s="134"/>
-      <c r="AA14" s="134"/>
-      <c r="AB14" s="134"/>
-      <c r="AC14" s="134"/>
-      <c r="AD14" s="133"/>
+      <c r="X14" s="96"/>
+      <c r="Y14" s="96"/>
+      <c r="Z14" s="96"/>
+      <c r="AA14" s="96"/>
+      <c r="AB14" s="96"/>
+      <c r="AC14" s="96"/>
+      <c r="AD14" s="95"/>
       <c r="AF14" s="4"/>
     </row>
-    <row r="15" spans="1:36" s="43" customFormat="1" ht="140.69999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:36" s="43" customFormat="1" ht="140.69999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="42"/>
-      <c r="C15" s="138" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="137"/>
-      <c r="E15" s="135"/>
-      <c r="F15" s="137"/>
-      <c r="G15" s="135"/>
-      <c r="H15" s="137"/>
-      <c r="I15" s="138" t="s">
-        <v>37</v>
-      </c>
-      <c r="J15" s="137"/>
-      <c r="K15" s="135"/>
-      <c r="L15" s="136"/>
-      <c r="M15" s="136"/>
-      <c r="N15" s="137"/>
-      <c r="O15" s="135" t="s">
+      <c r="C15" s="156" t="s">
+        <v>32</v>
+      </c>
+      <c r="D15" s="106"/>
+      <c r="E15" s="105"/>
+      <c r="F15" s="106"/>
+      <c r="G15" s="105"/>
+      <c r="H15" s="106"/>
+      <c r="I15" s="156" t="s">
+        <v>36</v>
+      </c>
+      <c r="J15" s="106"/>
+      <c r="K15" s="105"/>
+      <c r="L15" s="108"/>
+      <c r="M15" s="108"/>
+      <c r="N15" s="106"/>
+      <c r="O15" s="105" t="s">
+        <v>34</v>
+      </c>
+      <c r="P15" s="108"/>
+      <c r="Q15" s="108"/>
+      <c r="R15" s="108"/>
+      <c r="S15" s="108"/>
+      <c r="T15" s="108"/>
+      <c r="U15" s="108"/>
+      <c r="V15" s="106"/>
+      <c r="W15" s="156" t="s">
         <v>35</v>
       </c>
-      <c r="P15" s="136"/>
-      <c r="Q15" s="136"/>
-      <c r="R15" s="136"/>
-      <c r="S15" s="136"/>
-      <c r="T15" s="136"/>
-      <c r="U15" s="136"/>
-      <c r="V15" s="137"/>
-      <c r="W15" s="138" t="s">
-        <v>36</v>
-      </c>
-      <c r="X15" s="136"/>
-      <c r="Y15" s="136"/>
-      <c r="Z15" s="136"/>
-      <c r="AA15" s="136"/>
-      <c r="AB15" s="136"/>
-      <c r="AC15" s="136"/>
-      <c r="AD15" s="137"/>
+      <c r="X15" s="108"/>
+      <c r="Y15" s="108"/>
+      <c r="Z15" s="108"/>
+      <c r="AA15" s="108"/>
+      <c r="AB15" s="108"/>
+      <c r="AC15" s="108"/>
+      <c r="AD15" s="106"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
-    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="42"/>
-      <c r="C16" s="118">
+      <c r="C16" s="90">
         <f ca="1">W14+1</f>
         <v>46320</v>
       </c>
-      <c r="D16" s="120"/>
+      <c r="D16" s="91"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
@@ -4378,101 +4417,101 @@
       <c r="AE16" s="7"/>
       <c r="AF16" s="42"/>
     </row>
-    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
-      <c r="C17" s="118"/>
-      <c r="D17" s="120"/>
-      <c r="E17" s="132">
+      <c r="C17" s="90"/>
+      <c r="D17" s="91"/>
+      <c r="E17" s="94">
         <f ca="1">C16+1</f>
         <v>46321</v>
       </c>
-      <c r="F17" s="133"/>
-      <c r="G17" s="132">
+      <c r="F17" s="95"/>
+      <c r="G17" s="94">
         <f ca="1">E17+1</f>
         <v>46322</v>
       </c>
-      <c r="H17" s="133"/>
-      <c r="I17" s="132">
+      <c r="H17" s="95"/>
+      <c r="I17" s="94">
         <f ca="1">G17+1</f>
         <v>46323</v>
       </c>
-      <c r="J17" s="133"/>
-      <c r="K17" s="132">
+      <c r="J17" s="95"/>
+      <c r="K17" s="94">
         <f ca="1">I17+1</f>
         <v>46324</v>
       </c>
-      <c r="L17" s="134"/>
-      <c r="M17" s="134"/>
+      <c r="L17" s="96"/>
+      <c r="M17" s="96"/>
       <c r="N17" s="50"/>
-      <c r="O17" s="132">
+      <c r="O17" s="94">
         <f ca="1">K17+1</f>
         <v>46325</v>
       </c>
-      <c r="P17" s="134"/>
-      <c r="Q17" s="134"/>
-      <c r="R17" s="134"/>
-      <c r="S17" s="134"/>
-      <c r="T17" s="134"/>
-      <c r="U17" s="134"/>
-      <c r="V17" s="133"/>
-      <c r="W17" s="132">
+      <c r="P17" s="96"/>
+      <c r="Q17" s="96"/>
+      <c r="R17" s="96"/>
+      <c r="S17" s="96"/>
+      <c r="T17" s="96"/>
+      <c r="U17" s="96"/>
+      <c r="V17" s="95"/>
+      <c r="W17" s="94">
         <f ca="1">O17+1</f>
         <v>46326</v>
       </c>
-      <c r="X17" s="134"/>
-      <c r="Y17" s="134"/>
-      <c r="Z17" s="134"/>
-      <c r="AA17" s="134"/>
-      <c r="AB17" s="134"/>
-      <c r="AC17" s="134"/>
-      <c r="AD17" s="133"/>
+      <c r="X17" s="96"/>
+      <c r="Y17" s="96"/>
+      <c r="Z17" s="96"/>
+      <c r="AA17" s="96"/>
+      <c r="AB17" s="96"/>
+      <c r="AC17" s="96"/>
+      <c r="AD17" s="95"/>
       <c r="AF17" s="4"/>
     </row>
-    <row r="18" spans="1:42" s="43" customFormat="1" ht="149.69999999999999" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:42" s="43" customFormat="1" ht="149.69999999999999" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="42"/>
-      <c r="C18" s="135"/>
-      <c r="D18" s="137"/>
-      <c r="E18" s="135" t="s">
-        <v>34</v>
-      </c>
-      <c r="F18" s="137"/>
-      <c r="G18" s="135"/>
-      <c r="H18" s="137"/>
-      <c r="I18" s="135"/>
-      <c r="J18" s="137"/>
-      <c r="K18" s="141" t="s">
-        <v>38</v>
-      </c>
-      <c r="L18" s="136"/>
-      <c r="M18" s="136"/>
+      <c r="C18" s="105"/>
+      <c r="D18" s="106"/>
+      <c r="E18" s="105" t="s">
+        <v>33</v>
+      </c>
+      <c r="F18" s="106"/>
+      <c r="G18" s="105"/>
+      <c r="H18" s="106"/>
+      <c r="I18" s="105"/>
+      <c r="J18" s="106"/>
+      <c r="K18" s="107" t="s">
+        <v>37</v>
+      </c>
+      <c r="L18" s="108"/>
+      <c r="M18" s="108"/>
       <c r="N18" s="82"/>
-      <c r="O18" s="135"/>
-      <c r="P18" s="136"/>
-      <c r="Q18" s="136"/>
-      <c r="R18" s="136"/>
-      <c r="S18" s="136"/>
-      <c r="T18" s="136"/>
-      <c r="U18" s="136"/>
-      <c r="V18" s="137"/>
-      <c r="W18" s="135"/>
-      <c r="X18" s="136"/>
-      <c r="Y18" s="136"/>
-      <c r="Z18" s="136"/>
-      <c r="AA18" s="136"/>
-      <c r="AB18" s="136"/>
-      <c r="AC18" s="136"/>
-      <c r="AD18" s="137"/>
+      <c r="O18" s="105"/>
+      <c r="P18" s="108"/>
+      <c r="Q18" s="108"/>
+      <c r="R18" s="108"/>
+      <c r="S18" s="108"/>
+      <c r="T18" s="108"/>
+      <c r="U18" s="108"/>
+      <c r="V18" s="106"/>
+      <c r="W18" s="105"/>
+      <c r="X18" s="108"/>
+      <c r="Y18" s="108"/>
+      <c r="Z18" s="108"/>
+      <c r="AA18" s="108"/>
+      <c r="AB18" s="108"/>
+      <c r="AC18" s="108"/>
+      <c r="AD18" s="106"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
-    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="42"/>
-      <c r="C19" s="118">
+      <c r="C19" s="90">
         <f ca="1">W17+1</f>
         <v>46327</v>
       </c>
-      <c r="D19" s="120"/>
+      <c r="D19" s="91"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
@@ -4502,91 +4541,91 @@
       <c r="AE19" s="7"/>
       <c r="AF19" s="42"/>
     </row>
-    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
-      <c r="C20" s="118"/>
-      <c r="D20" s="120"/>
-      <c r="E20" s="132">
+      <c r="C20" s="90"/>
+      <c r="D20" s="91"/>
+      <c r="E20" s="94">
         <f ca="1">C19+1</f>
         <v>46328</v>
       </c>
-      <c r="F20" s="133"/>
-      <c r="G20" s="132">
+      <c r="F20" s="95"/>
+      <c r="G20" s="94">
         <f ca="1">E20+1</f>
         <v>46329</v>
       </c>
-      <c r="H20" s="133"/>
-      <c r="I20" s="132">
+      <c r="H20" s="95"/>
+      <c r="I20" s="94">
         <f ca="1">G20+1</f>
         <v>46330</v>
       </c>
-      <c r="J20" s="133"/>
-      <c r="K20" s="132">
+      <c r="J20" s="95"/>
+      <c r="K20" s="94">
         <f ca="1">I20+1</f>
         <v>46331</v>
       </c>
-      <c r="L20" s="134"/>
-      <c r="M20" s="134"/>
+      <c r="L20" s="96"/>
+      <c r="M20" s="96"/>
       <c r="N20" s="50"/>
-      <c r="O20" s="132">
+      <c r="O20" s="94">
         <f ca="1">K20+1</f>
         <v>46332</v>
       </c>
-      <c r="P20" s="134"/>
-      <c r="Q20" s="134"/>
-      <c r="R20" s="134"/>
-      <c r="S20" s="134"/>
-      <c r="T20" s="134"/>
-      <c r="U20" s="134"/>
-      <c r="V20" s="133"/>
-      <c r="W20" s="132">
+      <c r="P20" s="96"/>
+      <c r="Q20" s="96"/>
+      <c r="R20" s="96"/>
+      <c r="S20" s="96"/>
+      <c r="T20" s="96"/>
+      <c r="U20" s="96"/>
+      <c r="V20" s="95"/>
+      <c r="W20" s="94">
         <f ca="1">O20+1</f>
         <v>46333</v>
       </c>
-      <c r="X20" s="134"/>
-      <c r="Y20" s="134"/>
-      <c r="Z20" s="134"/>
-      <c r="AA20" s="134"/>
-      <c r="AB20" s="134"/>
-      <c r="AC20" s="134"/>
-      <c r="AD20" s="133"/>
+      <c r="X20" s="96"/>
+      <c r="Y20" s="96"/>
+      <c r="Z20" s="96"/>
+      <c r="AA20" s="96"/>
+      <c r="AB20" s="96"/>
+      <c r="AC20" s="96"/>
+      <c r="AD20" s="95"/>
       <c r="AF20" s="4"/>
     </row>
-    <row r="21" spans="1:42" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:42" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="42"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="111"/>
-      <c r="H21" s="113"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="113"/>
-      <c r="K21" s="111"/>
-      <c r="L21" s="112"/>
-      <c r="M21" s="112"/>
+      <c r="C21" s="83"/>
+      <c r="D21" s="85"/>
+      <c r="E21" s="83"/>
+      <c r="F21" s="85"/>
+      <c r="G21" s="83"/>
+      <c r="H21" s="85"/>
+      <c r="I21" s="83"/>
+      <c r="J21" s="85"/>
+      <c r="K21" s="83"/>
+      <c r="L21" s="84"/>
+      <c r="M21" s="84"/>
       <c r="N21" s="44"/>
-      <c r="O21" s="111"/>
-      <c r="P21" s="112"/>
-      <c r="Q21" s="112"/>
-      <c r="R21" s="112"/>
-      <c r="S21" s="112"/>
-      <c r="T21" s="112"/>
-      <c r="U21" s="112"/>
-      <c r="V21" s="113"/>
-      <c r="W21" s="111"/>
-      <c r="X21" s="112"/>
-      <c r="Y21" s="112"/>
-      <c r="Z21" s="112"/>
-      <c r="AA21" s="112"/>
-      <c r="AB21" s="112"/>
-      <c r="AC21" s="112"/>
-      <c r="AD21" s="113"/>
+      <c r="O21" s="83"/>
+      <c r="P21" s="84"/>
+      <c r="Q21" s="84"/>
+      <c r="R21" s="84"/>
+      <c r="S21" s="84"/>
+      <c r="T21" s="84"/>
+      <c r="U21" s="84"/>
+      <c r="V21" s="85"/>
+      <c r="W21" s="83"/>
+      <c r="X21" s="84"/>
+      <c r="Y21" s="84"/>
+      <c r="Z21" s="84"/>
+      <c r="AA21" s="84"/>
+      <c r="AB21" s="84"/>
+      <c r="AC21" s="84"/>
+      <c r="AD21" s="85"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
     </row>
-    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52"/>
@@ -4618,7 +4657,7 @@
       <c r="AD22" s="55"/>
       <c r="AF22" s="4"/>
     </row>
-    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="56"/>
@@ -4652,61 +4691,61 @@
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
     </row>
-    <row r="24" spans="1:42" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:42" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1"/>
       <c r="M24" s="1"/>
       <c r="AF24" s="1"/>
     </row>
-    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1"/>
-      <c r="C25" s="139" t="s">
+      <c r="C25" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="139"/>
-      <c r="E25" s="139"/>
-      <c r="F25" s="139"/>
-      <c r="G25" s="139"/>
-      <c r="H25" s="139"/>
-      <c r="I25" s="139"/>
-      <c r="J25" s="139"/>
-      <c r="K25" s="139"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="86"/>
+      <c r="H25" s="86"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="86"/>
+      <c r="K25" s="86"/>
       <c r="L25" s="60"/>
       <c r="M25" s="1"/>
-      <c r="O25" s="140">
+      <c r="O25" s="87">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)-1,1)</f>
         <v>46266</v>
       </c>
-      <c r="P25" s="140"/>
-      <c r="Q25" s="140"/>
-      <c r="R25" s="140"/>
-      <c r="S25" s="140"/>
-      <c r="T25" s="140"/>
-      <c r="U25" s="140"/>
+      <c r="P25" s="87"/>
+      <c r="Q25" s="87"/>
+      <c r="R25" s="87"/>
+      <c r="S25" s="87"/>
+      <c r="T25" s="87"/>
+      <c r="U25" s="87"/>
       <c r="V25" s="61"/>
       <c r="W25" s="61"/>
-      <c r="X25" s="140">
+      <c r="X25" s="87">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)+1,1)</f>
         <v>46327</v>
       </c>
-      <c r="Y25" s="140"/>
-      <c r="Z25" s="140"/>
-      <c r="AA25" s="140"/>
-      <c r="AB25" s="140"/>
-      <c r="AC25" s="140"/>
-      <c r="AD25" s="140"/>
+      <c r="Y25" s="87"/>
+      <c r="Z25" s="87"/>
+      <c r="AA25" s="87"/>
+      <c r="AB25" s="87"/>
+      <c r="AC25" s="87"/>
+      <c r="AD25" s="87"/>
       <c r="AF25" s="1"/>
     </row>
-    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1"/>
-      <c r="C26" s="139"/>
-      <c r="D26" s="139"/>
-      <c r="E26" s="139"/>
-      <c r="F26" s="139"/>
-      <c r="G26" s="139"/>
-      <c r="H26" s="139"/>
-      <c r="I26" s="139"/>
-      <c r="J26" s="139"/>
-      <c r="K26" s="139"/>
+      <c r="C26" s="86"/>
+      <c r="D26" s="86"/>
+      <c r="E26" s="86"/>
+      <c r="F26" s="86"/>
+      <c r="G26" s="86"/>
+      <c r="H26" s="86"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="K26" s="86"/>
       <c r="L26" s="60"/>
       <c r="M26" s="1"/>
       <c r="O26" s="62" t="str">
@@ -4769,17 +4808,17 @@
       </c>
       <c r="AF26" s="1"/>
     </row>
-    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1"/>
-      <c r="C27" s="115"/>
-      <c r="D27" s="115"/>
-      <c r="E27" s="115"/>
-      <c r="F27" s="115"/>
-      <c r="G27" s="115"/>
-      <c r="H27" s="115"/>
-      <c r="I27" s="115"/>
-      <c r="J27" s="115"/>
-      <c r="K27" s="115"/>
+      <c r="C27" s="88"/>
+      <c r="D27" s="88"/>
+      <c r="E27" s="88"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="88"/>
+      <c r="H27" s="88"/>
+      <c r="I27" s="88"/>
+      <c r="J27" s="88"/>
+      <c r="K27" s="88"/>
       <c r="M27" s="1"/>
       <c r="O27" s="64" t="str">
         <f t="shared" ref="O27:U32" ca="1" si="0">IF(MONTH($O$25)&lt;&gt;MONTH($O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1)),"",$O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1))</f>
@@ -4841,17 +4880,17 @@
       </c>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1"/>
-      <c r="C28" s="114"/>
-      <c r="D28" s="114"/>
-      <c r="E28" s="114"/>
-      <c r="F28" s="114"/>
-      <c r="G28" s="114"/>
-      <c r="H28" s="114"/>
-      <c r="I28" s="114"/>
-      <c r="J28" s="114"/>
-      <c r="K28" s="114"/>
+      <c r="C28" s="89"/>
+      <c r="D28" s="89"/>
+      <c r="E28" s="89"/>
+      <c r="F28" s="89"/>
+      <c r="G28" s="89"/>
+      <c r="H28" s="89"/>
+      <c r="I28" s="89"/>
+      <c r="J28" s="89"/>
+      <c r="K28" s="89"/>
       <c r="M28" s="1"/>
       <c r="O28" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -4913,17 +4952,17 @@
       </c>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1"/>
-      <c r="C29" s="115"/>
-      <c r="D29" s="115"/>
-      <c r="E29" s="115"/>
-      <c r="F29" s="115"/>
-      <c r="G29" s="115"/>
-      <c r="H29" s="115"/>
-      <c r="I29" s="115"/>
-      <c r="J29" s="115"/>
-      <c r="K29" s="115"/>
+      <c r="C29" s="88"/>
+      <c r="D29" s="88"/>
+      <c r="E29" s="88"/>
+      <c r="F29" s="88"/>
+      <c r="G29" s="88"/>
+      <c r="H29" s="88"/>
+      <c r="I29" s="88"/>
+      <c r="J29" s="88"/>
+      <c r="K29" s="88"/>
       <c r="M29" s="1"/>
       <c r="O29" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -4985,17 +5024,17 @@
       </c>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1"/>
-      <c r="C30" s="114"/>
-      <c r="D30" s="114"/>
-      <c r="E30" s="114"/>
-      <c r="F30" s="114"/>
-      <c r="G30" s="114"/>
-      <c r="H30" s="114"/>
-      <c r="I30" s="114"/>
-      <c r="J30" s="114"/>
-      <c r="K30" s="114"/>
+      <c r="C30" s="89"/>
+      <c r="D30" s="89"/>
+      <c r="E30" s="89"/>
+      <c r="F30" s="89"/>
+      <c r="G30" s="89"/>
+      <c r="H30" s="89"/>
+      <c r="I30" s="89"/>
+      <c r="J30" s="89"/>
+      <c r="K30" s="89"/>
       <c r="M30" s="1"/>
       <c r="O30" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -5057,17 +5096,17 @@
       </c>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1"/>
-      <c r="C31" s="115"/>
-      <c r="D31" s="115"/>
-      <c r="E31" s="115"/>
-      <c r="F31" s="115"/>
-      <c r="G31" s="115"/>
-      <c r="H31" s="115"/>
-      <c r="I31" s="115"/>
-      <c r="J31" s="115"/>
-      <c r="K31" s="115"/>
+      <c r="C31" s="88"/>
+      <c r="D31" s="88"/>
+      <c r="E31" s="88"/>
+      <c r="F31" s="88"/>
+      <c r="G31" s="88"/>
+      <c r="H31" s="88"/>
+      <c r="I31" s="88"/>
+      <c r="J31" s="88"/>
+      <c r="K31" s="88"/>
       <c r="M31" s="1"/>
       <c r="O31" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -5129,7 +5168,7 @@
       </c>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:42" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A32" s="1"/>
       <c r="M32" s="1"/>
       <c r="O32" s="64" t="str">
@@ -5192,7 +5231,7 @@
       </c>
       <c r="AF32" s="1"/>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:32" ht="13.2" x14ac:dyDescent="0.25">
       <c r="A33" s="1"/>
       <c r="M33" s="1"/>
       <c r="O33" s="64"/>
@@ -5213,7 +5252,7 @@
       <c r="AD33" s="65"/>
       <c r="AF33" s="1"/>
     </row>
-    <row r="34" spans="1:32" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:32" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -5247,69 +5286,156 @@
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
     </row>
-    <row r="38" spans="1:32" ht="12.9" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D39" s="83" t="s">
+    <row r="38" spans="1:32" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D39" s="115" t="s">
         <v>24</v>
       </c>
-      <c r="E39" s="84"/>
-      <c r="F39" s="85"/>
-      <c r="G39" s="89">
+      <c r="E39" s="116"/>
+      <c r="F39" s="117"/>
+      <c r="G39" s="121">
         <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
         <v>5</v>
       </c>
-      <c r="H39" s="90"/>
-      <c r="I39" s="83" t="s">
+      <c r="H39" s="122"/>
+      <c r="I39" s="115" t="s">
         <v>27</v>
       </c>
-      <c r="J39" s="93"/>
-      <c r="K39" s="95" t="s">
+      <c r="J39" s="125"/>
+      <c r="K39" s="127" t="s">
         <v>25</v>
       </c>
-      <c r="L39" s="96"/>
-      <c r="M39" s="99">
+      <c r="L39" s="128"/>
+      <c r="M39" s="131">
         <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
-        <v>5.9999999999999973</v>
-      </c>
-      <c r="N39" s="100"/>
-      <c r="O39" s="100"/>
-      <c r="P39" s="100"/>
-      <c r="Q39" s="100"/>
-      <c r="R39" s="101"/>
-      <c r="S39" s="105" t="s">
+        <v>5.0000000000000009</v>
+      </c>
+      <c r="N39" s="132"/>
+      <c r="O39" s="132"/>
+      <c r="P39" s="132"/>
+      <c r="Q39" s="132"/>
+      <c r="R39" s="133"/>
+      <c r="S39" s="137" t="s">
         <v>26</v>
       </c>
-      <c r="T39" s="106"/>
-      <c r="U39" s="106"/>
-      <c r="V39" s="106"/>
-      <c r="W39" s="106"/>
-      <c r="X39" s="107"/>
-    </row>
-    <row r="40" spans="1:32" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D40" s="86"/>
-      <c r="E40" s="87"/>
-      <c r="F40" s="88"/>
-      <c r="G40" s="91"/>
-      <c r="H40" s="92"/>
-      <c r="I40" s="86"/>
-      <c r="J40" s="94"/>
-      <c r="K40" s="97"/>
-      <c r="L40" s="98"/>
-      <c r="M40" s="102"/>
-      <c r="N40" s="103"/>
-      <c r="O40" s="103"/>
-      <c r="P40" s="103"/>
-      <c r="Q40" s="103"/>
-      <c r="R40" s="104"/>
-      <c r="S40" s="108"/>
-      <c r="T40" s="109"/>
-      <c r="U40" s="109"/>
-      <c r="V40" s="109"/>
-      <c r="W40" s="109"/>
-      <c r="X40" s="110"/>
+      <c r="T39" s="138"/>
+      <c r="U39" s="138"/>
+      <c r="V39" s="138"/>
+      <c r="W39" s="138"/>
+      <c r="X39" s="139"/>
+    </row>
+    <row r="40" spans="1:32" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="D40" s="118"/>
+      <c r="E40" s="119"/>
+      <c r="F40" s="120"/>
+      <c r="G40" s="123"/>
+      <c r="H40" s="124"/>
+      <c r="I40" s="118"/>
+      <c r="J40" s="126"/>
+      <c r="K40" s="129"/>
+      <c r="L40" s="130"/>
+      <c r="M40" s="134"/>
+      <c r="N40" s="135"/>
+      <c r="O40" s="135"/>
+      <c r="P40" s="135"/>
+      <c r="Q40" s="135"/>
+      <c r="R40" s="136"/>
+      <c r="S40" s="140"/>
+      <c r="T40" s="141"/>
+      <c r="U40" s="141"/>
+      <c r="V40" s="141"/>
+      <c r="W40" s="141"/>
+      <c r="X40" s="142"/>
     </row>
   </sheetData>
   <mergeCells count="110">
+    <mergeCell ref="D39:F40"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="K39:L40"/>
+    <mergeCell ref="M39:R40"/>
+    <mergeCell ref="S39:X40"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="O21:V21"/>
+    <mergeCell ref="W21:AD21"/>
+    <mergeCell ref="C30:K31"/>
+    <mergeCell ref="C2:AD2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="W5:AD5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:V6"/>
+    <mergeCell ref="W6:AD6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="O5:V5"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="W7:AD7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="O8:V8"/>
+    <mergeCell ref="W8:AD8"/>
+    <mergeCell ref="O7:V7"/>
+    <mergeCell ref="W9:AD9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="O11:V11"/>
+    <mergeCell ref="W11:AD11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:V9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="W12:AD12"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O14:V14"/>
+    <mergeCell ref="W14:AD14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="O12:V12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="W15:AD15"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="O17:V17"/>
+    <mergeCell ref="W17:AD17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="O15:V15"/>
+    <mergeCell ref="K15:N15"/>
     <mergeCell ref="W18:AD18"/>
     <mergeCell ref="C25:K26"/>
     <mergeCell ref="O25:U25"/>
@@ -5333,93 +5459,6 @@
     <mergeCell ref="E21:F21"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="I21:J21"/>
-    <mergeCell ref="W15:AD15"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="O17:V17"/>
-    <mergeCell ref="W17:AD17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="O15:V15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="W12:AD12"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="O14:V14"/>
-    <mergeCell ref="W14:AD14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="O12:V12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="W9:AD9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="O11:V11"/>
-    <mergeCell ref="W11:AD11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:V9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="W7:AD7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="O8:V8"/>
-    <mergeCell ref="W8:AD8"/>
-    <mergeCell ref="O7:V7"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:V6"/>
-    <mergeCell ref="W6:AD6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="O5:V5"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="C2:AD2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="W5:AD5"/>
-    <mergeCell ref="D39:F40"/>
-    <mergeCell ref="G39:H40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="K39:L40"/>
-    <mergeCell ref="M39:R40"/>
-    <mergeCell ref="S39:X40"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="O21:V21"/>
-    <mergeCell ref="W21:AD21"/>
-    <mergeCell ref="C30:K31"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 E5 G5 I5 K5:L5 O5 W5 C7 E8 G8 I8 K8:L8 O8 W8 C10 E11 G11 I11 K11:L11 O11 W11 C13 E14 G14 I14 K14:L14 O14 W14 C16 E17 G17 I17 K17:L17 O17 W17">
     <cfRule type="expression" dxfId="7" priority="3">
@@ -5458,7 +5497,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AP39"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="12.6" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="3" width="5.5546875" style="3" customWidth="1"/>
     <col min="4" max="4" width="15.5546875" style="3" customWidth="1"/>
@@ -5476,7 +5515,7 @@
     <col min="35" max="16384" width="8.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5510,42 +5549,42 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="2.15">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A2" s="29"/>
-      <c r="C2" s="116">
+      <c r="C2" s="112">
         <f ca="1">DATE(About!P8,11,1)</f>
         <v>46327</v>
       </c>
-      <c r="D2" s="116"/>
-      <c r="E2" s="116"/>
-      <c r="F2" s="116"/>
-      <c r="G2" s="116"/>
-      <c r="H2" s="116"/>
-      <c r="I2" s="116"/>
-      <c r="J2" s="116"/>
-      <c r="K2" s="116"/>
-      <c r="L2" s="116"/>
-      <c r="M2" s="116"/>
-      <c r="N2" s="116"/>
-      <c r="O2" s="116"/>
-      <c r="P2" s="116"/>
-      <c r="Q2" s="116"/>
-      <c r="R2" s="116"/>
-      <c r="S2" s="116"/>
-      <c r="T2" s="116"/>
-      <c r="U2" s="116"/>
-      <c r="V2" s="116"/>
-      <c r="W2" s="116"/>
-      <c r="X2" s="116"/>
-      <c r="Y2" s="116"/>
-      <c r="Z2" s="116"/>
-      <c r="AA2" s="116"/>
-      <c r="AB2" s="116"/>
-      <c r="AC2" s="116"/>
-      <c r="AD2" s="116"/>
+      <c r="D2" s="112"/>
+      <c r="E2" s="112"/>
+      <c r="F2" s="112"/>
+      <c r="G2" s="112"/>
+      <c r="H2" s="112"/>
+      <c r="I2" s="112"/>
+      <c r="J2" s="112"/>
+      <c r="K2" s="112"/>
+      <c r="L2" s="112"/>
+      <c r="M2" s="112"/>
+      <c r="N2" s="112"/>
+      <c r="O2" s="112"/>
+      <c r="P2" s="112"/>
+      <c r="Q2" s="112"/>
+      <c r="R2" s="112"/>
+      <c r="S2" s="112"/>
+      <c r="T2" s="112"/>
+      <c r="U2" s="112"/>
+      <c r="V2" s="112"/>
+      <c r="W2" s="112"/>
+      <c r="X2" s="112"/>
+      <c r="Y2" s="112"/>
+      <c r="Z2" s="112"/>
+      <c r="AA2" s="112"/>
+      <c r="AB2" s="112"/>
+      <c r="AC2" s="112"/>
+      <c r="AD2" s="112"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="2.15">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="1.1000000000000001">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -5565,290 +5604,290 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="35"/>
-      <c r="C4" s="117">
+      <c r="C4" s="113">
         <f ca="1">C5</f>
         <v>46327</v>
       </c>
-      <c r="D4" s="117"/>
-      <c r="E4" s="117">
+      <c r="D4" s="113"/>
+      <c r="E4" s="113">
         <f ca="1">E5</f>
         <v>46328</v>
       </c>
-      <c r="F4" s="117"/>
-      <c r="G4" s="117">
+      <c r="F4" s="113"/>
+      <c r="G4" s="113">
         <f ca="1">G5</f>
         <v>46329</v>
       </c>
-      <c r="H4" s="117"/>
-      <c r="I4" s="117">
+      <c r="H4" s="113"/>
+      <c r="I4" s="113">
         <f ca="1">I5</f>
         <v>46330</v>
       </c>
-      <c r="J4" s="117"/>
-      <c r="K4" s="117">
+      <c r="J4" s="113"/>
+      <c r="K4" s="113">
         <f ca="1">K5</f>
         <v>46331</v>
       </c>
-      <c r="L4" s="117"/>
-      <c r="M4" s="117"/>
+      <c r="L4" s="113"/>
+      <c r="M4" s="113"/>
       <c r="N4" s="37"/>
-      <c r="O4" s="117">
+      <c r="O4" s="113">
         <f ca="1">O5</f>
         <v>46332</v>
       </c>
-      <c r="P4" s="117"/>
-      <c r="Q4" s="117"/>
-      <c r="R4" s="117"/>
-      <c r="S4" s="117"/>
-      <c r="T4" s="117"/>
-      <c r="U4" s="117"/>
-      <c r="V4" s="117"/>
-      <c r="W4" s="117">
+      <c r="P4" s="113"/>
+      <c r="Q4" s="113"/>
+      <c r="R4" s="113"/>
+      <c r="S4" s="113"/>
+      <c r="T4" s="113"/>
+      <c r="U4" s="113"/>
+      <c r="V4" s="113"/>
+      <c r="W4" s="113">
         <f ca="1">W5</f>
         <v>46333</v>
       </c>
-      <c r="X4" s="117"/>
-      <c r="Y4" s="117"/>
-      <c r="Z4" s="117"/>
-      <c r="AA4" s="117"/>
-      <c r="AB4" s="117"/>
-      <c r="AC4" s="117"/>
-      <c r="AD4" s="117"/>
+      <c r="X4" s="113"/>
+      <c r="Y4" s="113"/>
+      <c r="Z4" s="113"/>
+      <c r="AA4" s="113"/>
+      <c r="AB4" s="113"/>
+      <c r="AC4" s="113"/>
+      <c r="AD4" s="113"/>
       <c r="AF4" s="38"/>
       <c r="AG4" s="39"/>
       <c r="AH4" s="39"/>
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="1"/>
-      <c r="C5" s="118">
+      <c r="C5" s="90">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46327</v>
       </c>
-      <c r="D5" s="120"/>
-      <c r="E5" s="118">
+      <c r="D5" s="91"/>
+      <c r="E5" s="90">
         <f ca="1">C5+1</f>
         <v>46328</v>
       </c>
-      <c r="F5" s="120"/>
-      <c r="G5" s="118">
+      <c r="F5" s="91"/>
+      <c r="G5" s="90">
         <f ca="1">E5+1</f>
         <v>46329</v>
       </c>
-      <c r="H5" s="120"/>
-      <c r="I5" s="118">
+      <c r="H5" s="91"/>
+      <c r="I5" s="90">
         <f ca="1">G5+1</f>
         <v>46330</v>
       </c>
-      <c r="J5" s="120"/>
-      <c r="K5" s="118">
+      <c r="J5" s="91"/>
+      <c r="K5" s="90">
         <f ca="1">I5+1</f>
         <v>46331</v>
       </c>
-      <c r="L5" s="119"/>
-      <c r="M5" s="119"/>
+      <c r="L5" s="114"/>
+      <c r="M5" s="114"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="118">
+      <c r="O5" s="90">
         <f ca="1">K5+1</f>
         <v>46332</v>
       </c>
-      <c r="P5" s="119"/>
-      <c r="Q5" s="119"/>
-      <c r="R5" s="119"/>
-      <c r="S5" s="119"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="120"/>
-      <c r="W5" s="118">
+      <c r="P5" s="114"/>
+      <c r="Q5" s="114"/>
+      <c r="R5" s="114"/>
+      <c r="S5" s="114"/>
+      <c r="T5" s="114"/>
+      <c r="U5" s="114"/>
+      <c r="V5" s="91"/>
+      <c r="W5" s="90">
         <f ca="1">O5+1</f>
         <v>46333</v>
       </c>
-      <c r="X5" s="119"/>
-      <c r="Y5" s="119"/>
-      <c r="Z5" s="119"/>
-      <c r="AA5" s="119"/>
-      <c r="AB5" s="119"/>
-      <c r="AC5" s="119"/>
-      <c r="AD5" s="120"/>
+      <c r="X5" s="114"/>
+      <c r="Y5" s="114"/>
+      <c r="Z5" s="114"/>
+      <c r="AA5" s="114"/>
+      <c r="AB5" s="114"/>
+      <c r="AC5" s="114"/>
+      <c r="AD5" s="91"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
       <c r="AI5" s="41"/>
       <c r="AJ5" s="41"/>
     </row>
-    <row r="6" spans="1:36" s="43" customFormat="1" ht="133.80000000000001" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:36" s="43" customFormat="1" ht="133.80000000000001" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="42"/>
-      <c r="C6" s="135"/>
-      <c r="D6" s="137"/>
-      <c r="E6" s="141" t="s">
+      <c r="C6" s="105"/>
+      <c r="D6" s="106"/>
+      <c r="E6" s="107" t="s">
+        <v>38</v>
+      </c>
+      <c r="F6" s="106"/>
+      <c r="G6" s="105"/>
+      <c r="H6" s="106"/>
+      <c r="I6" s="105"/>
+      <c r="J6" s="106"/>
+      <c r="K6" s="105"/>
+      <c r="L6" s="108"/>
+      <c r="M6" s="108"/>
+      <c r="N6" s="106"/>
+      <c r="O6" s="107" t="s">
         <v>39</v>
       </c>
-      <c r="F6" s="137"/>
-      <c r="G6" s="135"/>
-      <c r="H6" s="137"/>
-      <c r="I6" s="135"/>
-      <c r="J6" s="137"/>
-      <c r="K6" s="135"/>
-      <c r="L6" s="136"/>
-      <c r="M6" s="136"/>
-      <c r="N6" s="137"/>
-      <c r="O6" s="141" t="s">
-        <v>40</v>
-      </c>
-      <c r="P6" s="136"/>
-      <c r="Q6" s="136"/>
-      <c r="R6" s="136"/>
-      <c r="S6" s="136"/>
-      <c r="T6" s="136"/>
-      <c r="U6" s="136"/>
-      <c r="V6" s="137"/>
-      <c r="W6" s="135"/>
-      <c r="X6" s="136"/>
-      <c r="Y6" s="136"/>
-      <c r="Z6" s="136"/>
-      <c r="AA6" s="136"/>
-      <c r="AB6" s="136"/>
-      <c r="AC6" s="136"/>
-      <c r="AD6" s="137"/>
+      <c r="P6" s="108"/>
+      <c r="Q6" s="108"/>
+      <c r="R6" s="108"/>
+      <c r="S6" s="108"/>
+      <c r="T6" s="108"/>
+      <c r="U6" s="108"/>
+      <c r="V6" s="106"/>
+      <c r="W6" s="105"/>
+      <c r="X6" s="108"/>
+      <c r="Y6" s="108"/>
+      <c r="Z6" s="108"/>
+      <c r="AA6" s="108"/>
+      <c r="AB6" s="108"/>
+      <c r="AC6" s="108"/>
+      <c r="AD6" s="106"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
-    <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="1"/>
-      <c r="C7" s="149">
+      <c r="C7" s="100">
         <f ca="1">W5+1</f>
         <v>46334</v>
       </c>
-      <c r="D7" s="150"/>
-      <c r="E7" s="151"/>
-      <c r="F7" s="152"/>
-      <c r="G7" s="151"/>
-      <c r="H7" s="152"/>
-      <c r="I7" s="151"/>
-      <c r="J7" s="152"/>
-      <c r="K7" s="151"/>
-      <c r="L7" s="153"/>
-      <c r="M7" s="153"/>
+      <c r="D7" s="101"/>
+      <c r="E7" s="109"/>
+      <c r="F7" s="110"/>
+      <c r="G7" s="109"/>
+      <c r="H7" s="110"/>
+      <c r="I7" s="109"/>
+      <c r="J7" s="110"/>
+      <c r="K7" s="109"/>
+      <c r="L7" s="111"/>
+      <c r="M7" s="111"/>
       <c r="N7" s="80"/>
-      <c r="O7" s="151"/>
-      <c r="P7" s="153"/>
-      <c r="Q7" s="153"/>
-      <c r="R7" s="153"/>
-      <c r="S7" s="153"/>
-      <c r="T7" s="153"/>
-      <c r="U7" s="153"/>
-      <c r="V7" s="152"/>
-      <c r="W7" s="151"/>
-      <c r="X7" s="153"/>
-      <c r="Y7" s="153"/>
-      <c r="Z7" s="153"/>
-      <c r="AA7" s="153"/>
-      <c r="AB7" s="153"/>
-      <c r="AC7" s="153"/>
-      <c r="AD7" s="152"/>
+      <c r="O7" s="109"/>
+      <c r="P7" s="111"/>
+      <c r="Q7" s="111"/>
+      <c r="R7" s="111"/>
+      <c r="S7" s="111"/>
+      <c r="T7" s="111"/>
+      <c r="U7" s="111"/>
+      <c r="V7" s="110"/>
+      <c r="W7" s="109"/>
+      <c r="X7" s="111"/>
+      <c r="Y7" s="111"/>
+      <c r="Z7" s="111"/>
+      <c r="AA7" s="111"/>
+      <c r="AB7" s="111"/>
+      <c r="AC7" s="111"/>
+      <c r="AD7" s="110"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="4"/>
-      <c r="C8" s="149"/>
-      <c r="D8" s="150"/>
-      <c r="E8" s="149">
+      <c r="C8" s="100"/>
+      <c r="D8" s="101"/>
+      <c r="E8" s="100">
         <f ca="1">C7+1</f>
         <v>46335</v>
       </c>
-      <c r="F8" s="150"/>
-      <c r="G8" s="149">
+      <c r="F8" s="101"/>
+      <c r="G8" s="100">
         <f ca="1">E8+1</f>
         <v>46336</v>
       </c>
-      <c r="H8" s="150"/>
-      <c r="I8" s="149">
+      <c r="H8" s="101"/>
+      <c r="I8" s="100">
         <f ca="1">G8+1</f>
         <v>46337</v>
       </c>
-      <c r="J8" s="150"/>
-      <c r="K8" s="149">
+      <c r="J8" s="101"/>
+      <c r="K8" s="100">
         <f ca="1">I8+1</f>
         <v>46338</v>
       </c>
-      <c r="L8" s="154"/>
-      <c r="M8" s="154"/>
+      <c r="L8" s="102"/>
+      <c r="M8" s="102"/>
       <c r="N8" s="78"/>
-      <c r="O8" s="149">
+      <c r="O8" s="100">
         <f ca="1">K8+1</f>
         <v>46339</v>
       </c>
-      <c r="P8" s="154"/>
-      <c r="Q8" s="154"/>
-      <c r="R8" s="154"/>
-      <c r="S8" s="154"/>
-      <c r="T8" s="154"/>
-      <c r="U8" s="154"/>
-      <c r="V8" s="150"/>
-      <c r="W8" s="149">
+      <c r="P8" s="102"/>
+      <c r="Q8" s="102"/>
+      <c r="R8" s="102"/>
+      <c r="S8" s="102"/>
+      <c r="T8" s="102"/>
+      <c r="U8" s="102"/>
+      <c r="V8" s="101"/>
+      <c r="W8" s="100">
         <f ca="1">O8+1</f>
         <v>46340</v>
       </c>
-      <c r="X8" s="154"/>
-      <c r="Y8" s="154"/>
-      <c r="Z8" s="154"/>
-      <c r="AA8" s="154"/>
-      <c r="AB8" s="154"/>
-      <c r="AC8" s="154"/>
-      <c r="AD8" s="150"/>
+      <c r="X8" s="102"/>
+      <c r="Y8" s="102"/>
+      <c r="Z8" s="102"/>
+      <c r="AA8" s="102"/>
+      <c r="AB8" s="102"/>
+      <c r="AC8" s="102"/>
+      <c r="AD8" s="101"/>
       <c r="AF8" s="4"/>
     </row>
-    <row r="9" spans="1:36" s="43" customFormat="1" ht="146.4" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:36" s="43" customFormat="1" ht="146.4" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="42"/>
-      <c r="C9" s="135"/>
-      <c r="D9" s="137"/>
-      <c r="E9" s="141" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="137"/>
-      <c r="G9" s="135"/>
-      <c r="H9" s="137"/>
-      <c r="I9" s="135" t="s">
+      <c r="C9" s="105"/>
+      <c r="D9" s="106"/>
+      <c r="E9" s="107" t="s">
         <v>42</v>
       </c>
-      <c r="J9" s="137"/>
-      <c r="K9" s="135" t="s">
+      <c r="F9" s="106"/>
+      <c r="G9" s="105"/>
+      <c r="H9" s="106"/>
+      <c r="I9" s="105" t="s">
+        <v>41</v>
+      </c>
+      <c r="J9" s="106"/>
+      <c r="K9" s="105" t="s">
         <v>18</v>
       </c>
-      <c r="L9" s="136"/>
-      <c r="M9" s="136"/>
-      <c r="N9" s="137"/>
-      <c r="O9" s="156" t="s">
+      <c r="L9" s="108"/>
+      <c r="M9" s="108"/>
+      <c r="N9" s="106"/>
+      <c r="O9" s="103" t="s">
         <v>15</v>
       </c>
-      <c r="P9" s="155"/>
-      <c r="Q9" s="155"/>
-      <c r="R9" s="155"/>
-      <c r="S9" s="155"/>
-      <c r="T9" s="155"/>
-      <c r="U9" s="155"/>
-      <c r="V9" s="122"/>
-      <c r="W9" s="121"/>
-      <c r="X9" s="155"/>
-      <c r="Y9" s="155"/>
-      <c r="Z9" s="155"/>
-      <c r="AA9" s="155"/>
-      <c r="AB9" s="155"/>
-      <c r="AC9" s="155"/>
-      <c r="AD9" s="122"/>
+      <c r="P9" s="98"/>
+      <c r="Q9" s="98"/>
+      <c r="R9" s="98"/>
+      <c r="S9" s="98"/>
+      <c r="T9" s="98"/>
+      <c r="U9" s="98"/>
+      <c r="V9" s="99"/>
+      <c r="W9" s="97"/>
+      <c r="X9" s="98"/>
+      <c r="Y9" s="98"/>
+      <c r="Z9" s="98"/>
+      <c r="AA9" s="98"/>
+      <c r="AB9" s="98"/>
+      <c r="AC9" s="98"/>
+      <c r="AD9" s="99"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
-    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="42"/>
-      <c r="C10" s="149">
+      <c r="C10" s="100">
         <f ca="1">W8+1</f>
         <v>46341</v>
       </c>
-      <c r="D10" s="150"/>
+      <c r="D10" s="101"/>
       <c r="E10" s="79"/>
       <c r="F10" s="80"/>
       <c r="G10" s="79"/>
@@ -5878,99 +5917,99 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="42"/>
     </row>
-    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4"/>
-      <c r="C11" s="149"/>
-      <c r="D11" s="150"/>
-      <c r="E11" s="149">
+      <c r="C11" s="100"/>
+      <c r="D11" s="101"/>
+      <c r="E11" s="100">
         <f ca="1">C10+1</f>
         <v>46342</v>
       </c>
-      <c r="F11" s="150"/>
-      <c r="G11" s="149">
+      <c r="F11" s="101"/>
+      <c r="G11" s="100">
         <f ca="1">E11+1</f>
         <v>46343</v>
       </c>
-      <c r="H11" s="150"/>
-      <c r="I11" s="149">
+      <c r="H11" s="101"/>
+      <c r="I11" s="100">
         <f ca="1">G11+1</f>
         <v>46344</v>
       </c>
-      <c r="J11" s="150"/>
-      <c r="K11" s="149">
+      <c r="J11" s="101"/>
+      <c r="K11" s="100">
         <f ca="1">I11+1</f>
         <v>46345</v>
       </c>
-      <c r="L11" s="154"/>
-      <c r="M11" s="154"/>
+      <c r="L11" s="102"/>
+      <c r="M11" s="102"/>
       <c r="N11" s="78"/>
-      <c r="O11" s="149">
+      <c r="O11" s="100">
         <f ca="1">K11+1</f>
         <v>46346</v>
       </c>
-      <c r="P11" s="154"/>
-      <c r="Q11" s="154"/>
-      <c r="R11" s="154"/>
-      <c r="S11" s="154"/>
-      <c r="T11" s="154"/>
-      <c r="U11" s="154"/>
-      <c r="V11" s="150"/>
-      <c r="W11" s="149">
+      <c r="P11" s="102"/>
+      <c r="Q11" s="102"/>
+      <c r="R11" s="102"/>
+      <c r="S11" s="102"/>
+      <c r="T11" s="102"/>
+      <c r="U11" s="102"/>
+      <c r="V11" s="101"/>
+      <c r="W11" s="100">
         <f ca="1">O11+1</f>
         <v>46347</v>
       </c>
-      <c r="X11" s="154"/>
-      <c r="Y11" s="154"/>
-      <c r="Z11" s="154"/>
-      <c r="AA11" s="154"/>
-      <c r="AB11" s="154"/>
-      <c r="AC11" s="154"/>
-      <c r="AD11" s="150"/>
+      <c r="X11" s="102"/>
+      <c r="Y11" s="102"/>
+      <c r="Z11" s="102"/>
+      <c r="AA11" s="102"/>
+      <c r="AB11" s="102"/>
+      <c r="AC11" s="102"/>
+      <c r="AD11" s="101"/>
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:36" s="43" customFormat="1" ht="134.69999999999999" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:36" s="43" customFormat="1" ht="134.69999999999999" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="42"/>
-      <c r="C12" s="121"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="156" t="s">
+      <c r="C12" s="97"/>
+      <c r="D12" s="99"/>
+      <c r="E12" s="103" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="157"/>
-      <c r="G12" s="121"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="121"/>
-      <c r="J12" s="122"/>
-      <c r="K12" s="121"/>
-      <c r="L12" s="155"/>
-      <c r="M12" s="155"/>
-      <c r="N12" s="122"/>
-      <c r="O12" s="121"/>
-      <c r="P12" s="155"/>
-      <c r="Q12" s="155"/>
-      <c r="R12" s="155"/>
-      <c r="S12" s="155"/>
-      <c r="T12" s="155"/>
-      <c r="U12" s="155"/>
-      <c r="V12" s="122"/>
-      <c r="W12" s="121"/>
-      <c r="X12" s="155"/>
-      <c r="Y12" s="155"/>
-      <c r="Z12" s="155"/>
-      <c r="AA12" s="155"/>
-      <c r="AB12" s="155"/>
-      <c r="AC12" s="155"/>
-      <c r="AD12" s="122"/>
+      <c r="F12" s="104"/>
+      <c r="G12" s="97"/>
+      <c r="H12" s="99"/>
+      <c r="I12" s="97"/>
+      <c r="J12" s="99"/>
+      <c r="K12" s="97"/>
+      <c r="L12" s="98"/>
+      <c r="M12" s="98"/>
+      <c r="N12" s="99"/>
+      <c r="O12" s="97"/>
+      <c r="P12" s="98"/>
+      <c r="Q12" s="98"/>
+      <c r="R12" s="98"/>
+      <c r="S12" s="98"/>
+      <c r="T12" s="98"/>
+      <c r="U12" s="98"/>
+      <c r="V12" s="99"/>
+      <c r="W12" s="97"/>
+      <c r="X12" s="98"/>
+      <c r="Y12" s="98"/>
+      <c r="Z12" s="98"/>
+      <c r="AA12" s="98"/>
+      <c r="AB12" s="98"/>
+      <c r="AC12" s="98"/>
+      <c r="AD12" s="99"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
-    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="42"/>
-      <c r="C13" s="149">
+      <c r="C13" s="100">
         <f ca="1">W11+1</f>
         <v>46348</v>
       </c>
-      <c r="D13" s="150"/>
+      <c r="D13" s="101"/>
       <c r="E13" s="79"/>
       <c r="F13" s="80"/>
       <c r="G13" s="79"/>
@@ -6000,102 +6039,102 @@
       <c r="AE13" s="7"/>
       <c r="AF13" s="42"/>
     </row>
-    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
-      <c r="C14" s="149"/>
-      <c r="D14" s="150"/>
-      <c r="E14" s="149">
+      <c r="C14" s="100"/>
+      <c r="D14" s="101"/>
+      <c r="E14" s="100">
         <f ca="1">C13+1</f>
         <v>46349</v>
       </c>
-      <c r="F14" s="150"/>
-      <c r="G14" s="149">
+      <c r="F14" s="101"/>
+      <c r="G14" s="100">
         <f ca="1">E14+1</f>
         <v>46350</v>
       </c>
-      <c r="H14" s="150"/>
-      <c r="I14" s="149">
+      <c r="H14" s="101"/>
+      <c r="I14" s="100">
         <f ca="1">G14+1</f>
         <v>46351</v>
       </c>
-      <c r="J14" s="150"/>
-      <c r="K14" s="149">
+      <c r="J14" s="101"/>
+      <c r="K14" s="100">
         <f ca="1">I14+1</f>
         <v>46352</v>
       </c>
-      <c r="L14" s="154"/>
-      <c r="M14" s="154"/>
+      <c r="L14" s="102"/>
+      <c r="M14" s="102"/>
       <c r="N14" s="78"/>
-      <c r="O14" s="149">
+      <c r="O14" s="100">
         <f ca="1">K14+1</f>
         <v>46353</v>
       </c>
-      <c r="P14" s="154"/>
-      <c r="Q14" s="154"/>
-      <c r="R14" s="154"/>
-      <c r="S14" s="154"/>
-      <c r="T14" s="154"/>
-      <c r="U14" s="154"/>
-      <c r="V14" s="150"/>
-      <c r="W14" s="149">
+      <c r="P14" s="102"/>
+      <c r="Q14" s="102"/>
+      <c r="R14" s="102"/>
+      <c r="S14" s="102"/>
+      <c r="T14" s="102"/>
+      <c r="U14" s="102"/>
+      <c r="V14" s="101"/>
+      <c r="W14" s="100">
         <f ca="1">O14+1</f>
         <v>46354</v>
       </c>
-      <c r="X14" s="154"/>
-      <c r="Y14" s="154"/>
-      <c r="Z14" s="154"/>
-      <c r="AA14" s="154"/>
-      <c r="AB14" s="154"/>
-      <c r="AC14" s="154"/>
-      <c r="AD14" s="150"/>
+      <c r="X14" s="102"/>
+      <c r="Y14" s="102"/>
+      <c r="Z14" s="102"/>
+      <c r="AA14" s="102"/>
+      <c r="AB14" s="102"/>
+      <c r="AC14" s="102"/>
+      <c r="AD14" s="101"/>
       <c r="AF14" s="4"/>
     </row>
-    <row r="15" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="42"/>
-      <c r="C15" s="121"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="121"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="121"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="121"/>
-      <c r="J15" s="122"/>
-      <c r="K15" s="121"/>
-      <c r="L15" s="155"/>
-      <c r="M15" s="155"/>
-      <c r="N15" s="122"/>
-      <c r="O15" s="121"/>
-      <c r="P15" s="155"/>
-      <c r="Q15" s="155"/>
-      <c r="R15" s="155"/>
-      <c r="S15" s="155"/>
-      <c r="T15" s="155"/>
-      <c r="U15" s="155"/>
-      <c r="V15" s="122"/>
-      <c r="W15" s="121"/>
-      <c r="X15" s="155"/>
-      <c r="Y15" s="155"/>
-      <c r="Z15" s="155"/>
-      <c r="AA15" s="155"/>
-      <c r="AB15" s="155"/>
-      <c r="AC15" s="155"/>
-      <c r="AD15" s="122"/>
+      <c r="C15" s="97"/>
+      <c r="D15" s="99"/>
+      <c r="E15" s="97"/>
+      <c r="F15" s="99"/>
+      <c r="G15" s="97"/>
+      <c r="H15" s="99"/>
+      <c r="I15" s="97"/>
+      <c r="J15" s="99"/>
+      <c r="K15" s="97"/>
+      <c r="L15" s="98"/>
+      <c r="M15" s="98"/>
+      <c r="N15" s="99"/>
+      <c r="O15" s="97"/>
+      <c r="P15" s="98"/>
+      <c r="Q15" s="98"/>
+      <c r="R15" s="98"/>
+      <c r="S15" s="98"/>
+      <c r="T15" s="98"/>
+      <c r="U15" s="98"/>
+      <c r="V15" s="99"/>
+      <c r="W15" s="97"/>
+      <c r="X15" s="98"/>
+      <c r="Y15" s="98"/>
+      <c r="Z15" s="98"/>
+      <c r="AA15" s="98"/>
+      <c r="AB15" s="98"/>
+      <c r="AC15" s="98"/>
+      <c r="AD15" s="99"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
-    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="42"/>
-      <c r="C16" s="118">
+      <c r="C16" s="90">
         <f ca="1">W14+1</f>
         <v>46355</v>
       </c>
-      <c r="D16" s="120"/>
+      <c r="D16" s="91"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
       <c r="H16" s="75"/>
-      <c r="I16" s="146"/>
-      <c r="J16" s="147"/>
+      <c r="I16" s="92"/>
+      <c r="J16" s="93"/>
       <c r="K16" s="66"/>
       <c r="L16" s="68"/>
       <c r="M16" s="68"/>
@@ -6119,102 +6158,102 @@
       <c r="AE16" s="7"/>
       <c r="AF16" s="42"/>
     </row>
-    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="4"/>
-      <c r="C17" s="118"/>
-      <c r="D17" s="120"/>
-      <c r="E17" s="132">
+      <c r="C17" s="90"/>
+      <c r="D17" s="91"/>
+      <c r="E17" s="94">
         <f ca="1">C16+1</f>
         <v>46356</v>
       </c>
-      <c r="F17" s="133"/>
-      <c r="G17" s="132">
+      <c r="F17" s="95"/>
+      <c r="G17" s="94">
         <v>1</v>
       </c>
-      <c r="H17" s="133"/>
-      <c r="I17" s="132">
+      <c r="H17" s="95"/>
+      <c r="I17" s="94">
         <f>G17+1</f>
         <v>2</v>
       </c>
-      <c r="J17" s="133"/>
-      <c r="K17" s="132">
+      <c r="J17" s="95"/>
+      <c r="K17" s="94">
         <f>I17+1</f>
         <v>3</v>
       </c>
-      <c r="L17" s="134"/>
-      <c r="M17" s="134"/>
-      <c r="N17" s="133"/>
-      <c r="O17" s="132">
+      <c r="L17" s="96"/>
+      <c r="M17" s="96"/>
+      <c r="N17" s="95"/>
+      <c r="O17" s="94">
         <f>K17+1</f>
         <v>4</v>
       </c>
-      <c r="P17" s="134"/>
-      <c r="Q17" s="134"/>
-      <c r="R17" s="134"/>
-      <c r="S17" s="134"/>
-      <c r="T17" s="134"/>
-      <c r="U17" s="134"/>
-      <c r="V17" s="133"/>
-      <c r="W17" s="132">
+      <c r="P17" s="96"/>
+      <c r="Q17" s="96"/>
+      <c r="R17" s="96"/>
+      <c r="S17" s="96"/>
+      <c r="T17" s="96"/>
+      <c r="U17" s="96"/>
+      <c r="V17" s="95"/>
+      <c r="W17" s="94">
         <f>O17+1</f>
         <v>5</v>
       </c>
-      <c r="X17" s="134"/>
-      <c r="Y17" s="134"/>
-      <c r="Z17" s="134"/>
-      <c r="AA17" s="134"/>
-      <c r="AB17" s="134"/>
-      <c r="AC17" s="134"/>
-      <c r="AD17" s="133"/>
+      <c r="X17" s="96"/>
+      <c r="Y17" s="96"/>
+      <c r="Z17" s="96"/>
+      <c r="AA17" s="96"/>
+      <c r="AB17" s="96"/>
+      <c r="AC17" s="96"/>
+      <c r="AD17" s="95"/>
       <c r="AF17" s="4"/>
     </row>
-    <row r="18" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="42"/>
-      <c r="C18" s="111"/>
-      <c r="D18" s="113"/>
-      <c r="E18" s="111"/>
-      <c r="F18" s="113"/>
-      <c r="G18" s="111"/>
-      <c r="H18" s="113"/>
-      <c r="I18" s="111"/>
-      <c r="J18" s="113"/>
-      <c r="K18" s="111"/>
-      <c r="L18" s="112"/>
-      <c r="M18" s="112"/>
-      <c r="N18" s="113"/>
-      <c r="O18" s="111"/>
-      <c r="P18" s="112"/>
-      <c r="Q18" s="112"/>
-      <c r="R18" s="112"/>
-      <c r="S18" s="112"/>
-      <c r="T18" s="112"/>
-      <c r="U18" s="112"/>
-      <c r="V18" s="113"/>
-      <c r="W18" s="111"/>
-      <c r="X18" s="112"/>
-      <c r="Y18" s="112"/>
-      <c r="Z18" s="112"/>
-      <c r="AA18" s="112"/>
-      <c r="AB18" s="112"/>
-      <c r="AC18" s="112"/>
-      <c r="AD18" s="113"/>
+      <c r="C18" s="83"/>
+      <c r="D18" s="85"/>
+      <c r="E18" s="83"/>
+      <c r="F18" s="85"/>
+      <c r="G18" s="83"/>
+      <c r="H18" s="85"/>
+      <c r="I18" s="83"/>
+      <c r="J18" s="85"/>
+      <c r="K18" s="83"/>
+      <c r="L18" s="84"/>
+      <c r="M18" s="84"/>
+      <c r="N18" s="85"/>
+      <c r="O18" s="83"/>
+      <c r="P18" s="84"/>
+      <c r="Q18" s="84"/>
+      <c r="R18" s="84"/>
+      <c r="S18" s="84"/>
+      <c r="T18" s="84"/>
+      <c r="U18" s="84"/>
+      <c r="V18" s="85"/>
+      <c r="W18" s="83"/>
+      <c r="X18" s="84"/>
+      <c r="Y18" s="84"/>
+      <c r="Z18" s="84"/>
+      <c r="AA18" s="84"/>
+      <c r="AB18" s="84"/>
+      <c r="AC18" s="84"/>
+      <c r="AD18" s="85"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
-    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="42"/>
-      <c r="C19" s="118">
+      <c r="C19" s="90">
         <f>W17+1</f>
         <v>6</v>
       </c>
-      <c r="D19" s="120"/>
+      <c r="D19" s="91"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
       <c r="H19" s="75"/>
-      <c r="I19" s="146"/>
-      <c r="J19" s="147"/>
+      <c r="I19" s="92"/>
+      <c r="J19" s="93"/>
       <c r="K19" s="66"/>
       <c r="L19" s="68"/>
       <c r="M19" s="68"/>
@@ -6238,91 +6277,91 @@
       <c r="AE19" s="7"/>
       <c r="AF19" s="42"/>
     </row>
-    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="4"/>
-      <c r="C20" s="118"/>
-      <c r="D20" s="120"/>
-      <c r="E20" s="132">
+      <c r="C20" s="90"/>
+      <c r="D20" s="91"/>
+      <c r="E20" s="94">
         <f>C19+1</f>
         <v>7</v>
       </c>
-      <c r="F20" s="133"/>
-      <c r="G20" s="132">
+      <c r="F20" s="95"/>
+      <c r="G20" s="94">
         <f>E20+1</f>
         <v>8</v>
       </c>
-      <c r="H20" s="133"/>
-      <c r="I20" s="132">
+      <c r="H20" s="95"/>
+      <c r="I20" s="94">
         <f>G20+1</f>
         <v>9</v>
       </c>
-      <c r="J20" s="133"/>
-      <c r="K20" s="132">
+      <c r="J20" s="95"/>
+      <c r="K20" s="94">
         <f>I20+1</f>
         <v>10</v>
       </c>
-      <c r="L20" s="134"/>
-      <c r="M20" s="134"/>
-      <c r="N20" s="133"/>
-      <c r="O20" s="132">
+      <c r="L20" s="96"/>
+      <c r="M20" s="96"/>
+      <c r="N20" s="95"/>
+      <c r="O20" s="94">
         <f>K20+1</f>
         <v>11</v>
       </c>
-      <c r="P20" s="134"/>
-      <c r="Q20" s="134"/>
-      <c r="R20" s="134"/>
-      <c r="S20" s="134"/>
-      <c r="T20" s="134"/>
-      <c r="U20" s="134"/>
-      <c r="V20" s="133"/>
-      <c r="W20" s="132">
+      <c r="P20" s="96"/>
+      <c r="Q20" s="96"/>
+      <c r="R20" s="96"/>
+      <c r="S20" s="96"/>
+      <c r="T20" s="96"/>
+      <c r="U20" s="96"/>
+      <c r="V20" s="95"/>
+      <c r="W20" s="94">
         <f>O20+1</f>
         <v>12</v>
       </c>
-      <c r="X20" s="134"/>
-      <c r="Y20" s="134"/>
-      <c r="Z20" s="134"/>
-      <c r="AA20" s="134"/>
-      <c r="AB20" s="134"/>
-      <c r="AC20" s="134"/>
-      <c r="AD20" s="133"/>
+      <c r="X20" s="96"/>
+      <c r="Y20" s="96"/>
+      <c r="Z20" s="96"/>
+      <c r="AA20" s="96"/>
+      <c r="AB20" s="96"/>
+      <c r="AC20" s="96"/>
+      <c r="AD20" s="95"/>
       <c r="AF20" s="4"/>
     </row>
-    <row r="21" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="42"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="111"/>
-      <c r="H21" s="113"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="113"/>
-      <c r="K21" s="111"/>
-      <c r="L21" s="112"/>
-      <c r="M21" s="112"/>
-      <c r="N21" s="113"/>
-      <c r="O21" s="111"/>
-      <c r="P21" s="112"/>
-      <c r="Q21" s="112"/>
-      <c r="R21" s="112"/>
-      <c r="S21" s="112"/>
-      <c r="T21" s="112"/>
-      <c r="U21" s="112"/>
-      <c r="V21" s="113"/>
-      <c r="W21" s="111"/>
-      <c r="X21" s="112"/>
-      <c r="Y21" s="112"/>
-      <c r="Z21" s="112"/>
-      <c r="AA21" s="112"/>
-      <c r="AB21" s="112"/>
-      <c r="AC21" s="112"/>
-      <c r="AD21" s="113"/>
+      <c r="C21" s="83"/>
+      <c r="D21" s="85"/>
+      <c r="E21" s="83"/>
+      <c r="F21" s="85"/>
+      <c r="G21" s="83"/>
+      <c r="H21" s="85"/>
+      <c r="I21" s="83"/>
+      <c r="J21" s="85"/>
+      <c r="K21" s="83"/>
+      <c r="L21" s="84"/>
+      <c r="M21" s="84"/>
+      <c r="N21" s="85"/>
+      <c r="O21" s="83"/>
+      <c r="P21" s="84"/>
+      <c r="Q21" s="84"/>
+      <c r="R21" s="84"/>
+      <c r="S21" s="84"/>
+      <c r="T21" s="84"/>
+      <c r="U21" s="84"/>
+      <c r="V21" s="85"/>
+      <c r="W21" s="83"/>
+      <c r="X21" s="84"/>
+      <c r="Y21" s="84"/>
+      <c r="Z21" s="84"/>
+      <c r="AA21" s="84"/>
+      <c r="AB21" s="84"/>
+      <c r="AC21" s="84"/>
+      <c r="AD21" s="85"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
     </row>
-    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="4"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52"/>
@@ -6354,7 +6393,7 @@
       <c r="AD22" s="55"/>
       <c r="AF22" s="4"/>
     </row>
-    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="56"/>
@@ -6388,61 +6427,61 @@
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
     </row>
-    <row r="24" spans="1:42" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:42" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="1"/>
       <c r="M24" s="1"/>
       <c r="AF24" s="1"/>
     </row>
-    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="1"/>
-      <c r="C25" s="139" t="s">
+      <c r="C25" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="139"/>
-      <c r="E25" s="139"/>
-      <c r="F25" s="139"/>
-      <c r="G25" s="139"/>
-      <c r="H25" s="139"/>
-      <c r="I25" s="139"/>
-      <c r="J25" s="139"/>
-      <c r="K25" s="139"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="86"/>
+      <c r="H25" s="86"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="86"/>
+      <c r="K25" s="86"/>
       <c r="L25" s="60"/>
       <c r="M25" s="1"/>
-      <c r="O25" s="140">
+      <c r="O25" s="87">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)-1,1)</f>
         <v>46296</v>
       </c>
-      <c r="P25" s="140"/>
-      <c r="Q25" s="140"/>
-      <c r="R25" s="140"/>
-      <c r="S25" s="140"/>
-      <c r="T25" s="140"/>
-      <c r="U25" s="140"/>
+      <c r="P25" s="87"/>
+      <c r="Q25" s="87"/>
+      <c r="R25" s="87"/>
+      <c r="S25" s="87"/>
+      <c r="T25" s="87"/>
+      <c r="U25" s="87"/>
       <c r="V25" s="61"/>
       <c r="W25" s="61"/>
-      <c r="X25" s="140">
+      <c r="X25" s="87">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)+1,1)</f>
         <v>46357</v>
       </c>
-      <c r="Y25" s="140"/>
-      <c r="Z25" s="140"/>
-      <c r="AA25" s="140"/>
-      <c r="AB25" s="140"/>
-      <c r="AC25" s="140"/>
-      <c r="AD25" s="140"/>
+      <c r="Y25" s="87"/>
+      <c r="Z25" s="87"/>
+      <c r="AA25" s="87"/>
+      <c r="AB25" s="87"/>
+      <c r="AC25" s="87"/>
+      <c r="AD25" s="87"/>
       <c r="AF25" s="1"/>
     </row>
-    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="1"/>
-      <c r="C26" s="139"/>
-      <c r="D26" s="139"/>
-      <c r="E26" s="139"/>
-      <c r="F26" s="139"/>
-      <c r="G26" s="139"/>
-      <c r="H26" s="139"/>
-      <c r="I26" s="139"/>
-      <c r="J26" s="139"/>
-      <c r="K26" s="139"/>
+      <c r="C26" s="86"/>
+      <c r="D26" s="86"/>
+      <c r="E26" s="86"/>
+      <c r="F26" s="86"/>
+      <c r="G26" s="86"/>
+      <c r="H26" s="86"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="K26" s="86"/>
       <c r="L26" s="60"/>
       <c r="M26" s="1"/>
       <c r="O26" s="62" t="str">
@@ -6505,17 +6544,17 @@
       </c>
       <c r="AF26" s="1"/>
     </row>
-    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="1"/>
-      <c r="C27" s="115"/>
-      <c r="D27" s="115"/>
-      <c r="E27" s="115"/>
-      <c r="F27" s="115"/>
-      <c r="G27" s="115"/>
-      <c r="H27" s="115"/>
-      <c r="I27" s="115"/>
-      <c r="J27" s="115"/>
-      <c r="K27" s="115"/>
+      <c r="C27" s="88"/>
+      <c r="D27" s="88"/>
+      <c r="E27" s="88"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="88"/>
+      <c r="H27" s="88"/>
+      <c r="I27" s="88"/>
+      <c r="J27" s="88"/>
+      <c r="K27" s="88"/>
       <c r="M27" s="1"/>
       <c r="O27" s="64" t="str">
         <f t="shared" ref="O27:U32" ca="1" si="0">IF(MONTH($O$25)&lt;&gt;MONTH($O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1)),"",$O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1))</f>
@@ -6577,17 +6616,17 @@
       </c>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="1"/>
-      <c r="C28" s="114"/>
-      <c r="D28" s="114"/>
-      <c r="E28" s="114"/>
-      <c r="F28" s="114"/>
-      <c r="G28" s="114"/>
-      <c r="H28" s="114"/>
-      <c r="I28" s="114"/>
-      <c r="J28" s="114"/>
-      <c r="K28" s="114"/>
+      <c r="C28" s="89"/>
+      <c r="D28" s="89"/>
+      <c r="E28" s="89"/>
+      <c r="F28" s="89"/>
+      <c r="G28" s="89"/>
+      <c r="H28" s="89"/>
+      <c r="I28" s="89"/>
+      <c r="J28" s="89"/>
+      <c r="K28" s="89"/>
       <c r="M28" s="1"/>
       <c r="O28" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6649,17 +6688,17 @@
       </c>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="1"/>
-      <c r="C29" s="115"/>
-      <c r="D29" s="115"/>
-      <c r="E29" s="115"/>
-      <c r="F29" s="115"/>
-      <c r="G29" s="115"/>
-      <c r="H29" s="115"/>
-      <c r="I29" s="115"/>
-      <c r="J29" s="115"/>
-      <c r="K29" s="115"/>
+      <c r="C29" s="88"/>
+      <c r="D29" s="88"/>
+      <c r="E29" s="88"/>
+      <c r="F29" s="88"/>
+      <c r="G29" s="88"/>
+      <c r="H29" s="88"/>
+      <c r="I29" s="88"/>
+      <c r="J29" s="88"/>
+      <c r="K29" s="88"/>
       <c r="M29" s="1"/>
       <c r="O29" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6721,17 +6760,17 @@
       </c>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="1"/>
-      <c r="C30" s="114"/>
-      <c r="D30" s="114"/>
-      <c r="E30" s="114"/>
-      <c r="F30" s="114"/>
-      <c r="G30" s="114"/>
-      <c r="H30" s="114"/>
-      <c r="I30" s="114"/>
-      <c r="J30" s="114"/>
-      <c r="K30" s="114"/>
+      <c r="C30" s="89"/>
+      <c r="D30" s="89"/>
+      <c r="E30" s="89"/>
+      <c r="F30" s="89"/>
+      <c r="G30" s="89"/>
+      <c r="H30" s="89"/>
+      <c r="I30" s="89"/>
+      <c r="J30" s="89"/>
+      <c r="K30" s="89"/>
       <c r="M30" s="1"/>
       <c r="O30" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6793,17 +6832,17 @@
       </c>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A31" s="1"/>
-      <c r="C31" s="115"/>
-      <c r="D31" s="115"/>
-      <c r="E31" s="115"/>
-      <c r="F31" s="115"/>
-      <c r="G31" s="115"/>
-      <c r="H31" s="115"/>
-      <c r="I31" s="115"/>
-      <c r="J31" s="115"/>
-      <c r="K31" s="115"/>
+      <c r="C31" s="88"/>
+      <c r="D31" s="88"/>
+      <c r="E31" s="88"/>
+      <c r="F31" s="88"/>
+      <c r="G31" s="88"/>
+      <c r="H31" s="88"/>
+      <c r="I31" s="88"/>
+      <c r="J31" s="88"/>
+      <c r="K31" s="88"/>
       <c r="M31" s="1"/>
       <c r="O31" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6865,7 +6904,7 @@
       </c>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="1"/>
       <c r="C32" s="77"/>
       <c r="D32" s="77"/>
@@ -6937,12 +6976,12 @@
       </c>
       <c r="AF32" s="1"/>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A33" s="1"/>
       <c r="M33" s="1"/>
       <c r="AF33" s="1"/>
     </row>
-    <row r="34" spans="1:32" ht="24.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:32" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -6976,130 +7015,100 @@
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
     </row>
-    <row r="37" spans="1:32" ht="12.9" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="38" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D38" s="83" t="s">
+    <row r="37" spans="1:32" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="38" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D38" s="115" t="s">
         <v>24</v>
       </c>
-      <c r="E38" s="84"/>
-      <c r="F38" s="85"/>
-      <c r="G38" s="89">
+      <c r="E38" s="116"/>
+      <c r="F38" s="117"/>
+      <c r="G38" s="121">
         <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
         <v>5</v>
       </c>
-      <c r="H38" s="90"/>
-      <c r="I38" s="83" t="s">
+      <c r="H38" s="122"/>
+      <c r="I38" s="115" t="s">
         <v>27</v>
       </c>
-      <c r="J38" s="93"/>
-      <c r="K38" s="95" t="s">
+      <c r="J38" s="125"/>
+      <c r="K38" s="127" t="s">
         <v>25</v>
       </c>
-      <c r="L38" s="96"/>
-      <c r="M38" s="99">
+      <c r="L38" s="128"/>
+      <c r="M38" s="131">
         <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
-        <v>5.9999999999999973</v>
-      </c>
-      <c r="N38" s="100"/>
-      <c r="O38" s="100"/>
-      <c r="P38" s="100"/>
-      <c r="Q38" s="100"/>
-      <c r="R38" s="101"/>
-      <c r="S38" s="105" t="s">
+        <v>5.0000000000000009</v>
+      </c>
+      <c r="N38" s="132"/>
+      <c r="O38" s="132"/>
+      <c r="P38" s="132"/>
+      <c r="Q38" s="132"/>
+      <c r="R38" s="133"/>
+      <c r="S38" s="137" t="s">
         <v>26</v>
       </c>
-      <c r="T38" s="106"/>
-      <c r="U38" s="106"/>
-      <c r="V38" s="106"/>
-      <c r="W38" s="106"/>
-      <c r="X38" s="107"/>
-    </row>
-    <row r="39" spans="1:32" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D39" s="86"/>
-      <c r="E39" s="87"/>
-      <c r="F39" s="88"/>
-      <c r="G39" s="91"/>
-      <c r="H39" s="92"/>
-      <c r="I39" s="86"/>
-      <c r="J39" s="94"/>
-      <c r="K39" s="97"/>
-      <c r="L39" s="98"/>
-      <c r="M39" s="102"/>
-      <c r="N39" s="103"/>
-      <c r="O39" s="103"/>
-      <c r="P39" s="103"/>
-      <c r="Q39" s="103"/>
-      <c r="R39" s="104"/>
-      <c r="S39" s="108"/>
-      <c r="T39" s="109"/>
-      <c r="U39" s="109"/>
-      <c r="V39" s="109"/>
-      <c r="W39" s="109"/>
-      <c r="X39" s="110"/>
+      <c r="T38" s="138"/>
+      <c r="U38" s="138"/>
+      <c r="V38" s="138"/>
+      <c r="W38" s="138"/>
+      <c r="X38" s="139"/>
+    </row>
+    <row r="39" spans="1:32" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="D39" s="118"/>
+      <c r="E39" s="119"/>
+      <c r="F39" s="120"/>
+      <c r="G39" s="123"/>
+      <c r="H39" s="124"/>
+      <c r="I39" s="118"/>
+      <c r="J39" s="126"/>
+      <c r="K39" s="129"/>
+      <c r="L39" s="130"/>
+      <c r="M39" s="134"/>
+      <c r="N39" s="135"/>
+      <c r="O39" s="135"/>
+      <c r="P39" s="135"/>
+      <c r="Q39" s="135"/>
+      <c r="R39" s="136"/>
+      <c r="S39" s="140"/>
+      <c r="T39" s="141"/>
+      <c r="U39" s="141"/>
+      <c r="V39" s="141"/>
+      <c r="W39" s="141"/>
+      <c r="X39" s="142"/>
     </row>
   </sheetData>
   <mergeCells count="112">
-    <mergeCell ref="K18:N18"/>
-    <mergeCell ref="W18:AD18"/>
-    <mergeCell ref="C25:K26"/>
-    <mergeCell ref="O25:U25"/>
-    <mergeCell ref="X25:AD25"/>
-    <mergeCell ref="C27:K27"/>
-    <mergeCell ref="C28:K29"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="O18:V18"/>
-    <mergeCell ref="C19:D20"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:N20"/>
-    <mergeCell ref="W15:AD15"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="O17:V17"/>
-    <mergeCell ref="W17:AD17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="O15:V15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="W12:AD12"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="O14:V14"/>
-    <mergeCell ref="W14:AD14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="O12:V12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="W9:AD9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="O11:V11"/>
-    <mergeCell ref="W11:AD11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:V9"/>
-    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="D38:F39"/>
+    <mergeCell ref="G38:H39"/>
+    <mergeCell ref="I38:J39"/>
+    <mergeCell ref="K38:L39"/>
+    <mergeCell ref="M38:R39"/>
+    <mergeCell ref="S38:X39"/>
+    <mergeCell ref="C30:K31"/>
+    <mergeCell ref="O20:V20"/>
+    <mergeCell ref="W20:AD20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:N21"/>
+    <mergeCell ref="O21:V21"/>
+    <mergeCell ref="W21:AD21"/>
+    <mergeCell ref="C2:AD2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="W5:AD5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="O5:V5"/>
     <mergeCell ref="K6:N6"/>
     <mergeCell ref="C7:D8"/>
     <mergeCell ref="E7:F7"/>
@@ -7120,37 +7129,67 @@
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="O6:V6"/>
     <mergeCell ref="W6:AD6"/>
-    <mergeCell ref="C2:AD2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="W5:AD5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="O5:V5"/>
-    <mergeCell ref="D38:F39"/>
-    <mergeCell ref="G38:H39"/>
-    <mergeCell ref="I38:J39"/>
-    <mergeCell ref="K38:L39"/>
-    <mergeCell ref="M38:R39"/>
-    <mergeCell ref="S38:X39"/>
-    <mergeCell ref="C30:K31"/>
-    <mergeCell ref="O20:V20"/>
-    <mergeCell ref="W20:AD20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:N21"/>
-    <mergeCell ref="O21:V21"/>
-    <mergeCell ref="W21:AD21"/>
+    <mergeCell ref="W9:AD9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="O11:V11"/>
+    <mergeCell ref="W11:AD11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:V9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="W12:AD12"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O14:V14"/>
+    <mergeCell ref="W14:AD14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="O12:V12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="W15:AD15"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="O17:V17"/>
+    <mergeCell ref="W17:AD17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="O15:V15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="K18:N18"/>
+    <mergeCell ref="W18:AD18"/>
+    <mergeCell ref="C25:K26"/>
+    <mergeCell ref="O25:U25"/>
+    <mergeCell ref="X25:AD25"/>
+    <mergeCell ref="C27:K27"/>
+    <mergeCell ref="C28:K29"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="O18:V18"/>
+    <mergeCell ref="C19:D20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:N20"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 E5 G5 I5 K5:L5 O5 W5 C7 E8 G8 I8 K8:L8 O8 W8 C10 E11 G11 I11 K11:L11 O11 W11 C13 E14 G14 I14 K14:L14 O14 W14 C16 E17 G17 I17 K17 O17 W17">
     <cfRule type="expression" dxfId="3" priority="3">
@@ -7184,15 +7223,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="30" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cec0622158e8f13124e9e8fd4de31bd1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3b52f30ab005d15df08657af532e6e38" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -7510,6 +7540,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
@@ -7531,14 +7570,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F0D3479-5903-425F-9669-62B4E7216DE9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{652EDDE9-C911-407A-9906-647D87C81E69}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7559,6 +7590,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F0D3479-5903-425F-9669-62B4E7216DE9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B201CC6-7A0A-429C-B445-7EDA1CF4A1D7}">
   <ds:schemaRefs>

--- a/Group_milestones.xlsx
+++ b/Group_milestones.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C40963E-D909-416B-A0DA-6975FE8EC327}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2F1A88-5E4C-4A1B-983F-CCDEB225E021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="824" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" tabRatio="824" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="52" r:id="rId1"/>
@@ -29,6 +29,7 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
         <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="58" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="62">
   <si>
     <t>Notes</t>
   </si>
@@ -158,9 +159,6 @@
     <t>MCTR1: ICD templates, carriage build</t>
   </si>
   <si>
-    <t>Group: Final touches</t>
-  </si>
-  <si>
     <t>MCTR1: Design of carriage v2</t>
   </si>
   <si>
@@ -204,20 +202,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">Group: First integration test                               </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Seaford"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>EEII1: Testing with PWM of REII in Heavy current lab</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">MCTR1: Enclosure final + fit test                    </t>
     </r>
     <r>
@@ -243,64 +227,7 @@
     <t>EERI 321</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">EERI 325             </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Seaford"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Group: Integration successful</t>
-    </r>
-  </si>
-  <si>
-    <t>MCTR1: Enclosure v1 test,  ICD complete with- REII, ICD complete with- MCTR2?</t>
-  </si>
-  <si>
-    <t>Group: Finish performance test reports and Individual portfolios</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">EEII 321                 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Seaford"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Group: Finalize all ICDs</t>
-    </r>
-  </si>
-  <si>
     <t>MCTR2: Motor characterise in heavy current lab with avalable VFD's</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">MCTR1: Carriage motor drive test, carriage v3 test </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Seaford"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">EEII1:Order heat sinks and power supply(at the latest) </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color theme="1"/>
-        <rFont val="Seaford"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>MCTR2: Starting with all final draft printing parts</t>
-    </r>
   </si>
   <si>
     <t>MCTR2: Start with gearbox casing build</t>
@@ -310,6 +237,114 @@
   </si>
   <si>
     <t>EERI321: Semester T3</t>
+  </si>
+  <si>
+    <t>REII: Individual checkpoint due - nRF24 link characterisation report + recommended config</t>
+  </si>
+  <si>
+    <t>REII: I3 begins - ICD_REII drafted &amp; signed off in week 1</t>
+  </si>
+  <si>
+    <t>EEII 321                 Group: Finalize all ICDs
+REII: ICD_REII signed (v1.0, v1.1 if pins/timings changed)</t>
+  </si>
+  <si>
+    <t>Group: Finish performance test reports and Individual portfolios
+REII: RF/rail test report + individual portfolio</t>
+  </si>
+  <si>
+    <t>Group: First integration test                               EEII1: Testing with PWM of REII in Heavy current lab
+REII: dashboard + dongle + controller link</t>
+  </si>
+  <si>
+    <t>REII: participation evidence captured - scope TBD, confirm w/ lecturer (F-08)</t>
+  </si>
+  <si>
+    <t>REII: gate - Controller Spec + ESP32 codebase obtained; board powered (planned, not agreed)</t>
+  </si>
+  <si>
+    <t>MCTR1: Carriage motor drive test, carriage v3 test EEII1:Order heat sinks and power supply(at the latest) MCTR2: Starting with all final draft printing parts
+REII: controller board delivery (estimate, Checkpoint2) - input to ESP32 nRF stub + integration</t>
+  </si>
+  <si>
+    <t>Group: Final touches
+REII: demo dry-run + evidence pack check (planned, not agreed)</t>
+  </si>
+  <si>
+    <t>REII: STM32F411 dongle bring-up (planned, not agreed)
+· CDC echo capture
+· SPI + Table 2 radio init read-back
+· USB&lt;-&gt;RF bridge PING/PONG</t>
+  </si>
+  <si>
+    <t>REII: dashboard cmd + telemetry path (planned, not agreed)
+· Idle/Move/E-stop/Magnet cmd exec
+· telemetry no sequence gaps
+· fault display capture (internal target)</t>
+  </si>
+  <si>
+    <t>REII: anti-sway model + open-loop profile generator (planned, not agreed)
+· pendulum model; sway freq identified
+· else S-curve baseline only (D-04)</t>
+  </si>
+  <si>
+    <t>REII: on-rail integration - INTERFACE_MATRIX rows (planned, not agreed)
+· rail RF re-survey + group channel plan
+· 5/10 m N=1000 ACK runs + NLOS point
+· evidence: results/i3_rail/ + TEST_LOG</t>
+  </si>
+  <si>
+    <t>REII: rail sway measurement (planned, not agreed)
+· flat vs shaped profile
+· log + plot position/time
+· pass bound = internal, not SysRS</t>
+  </si>
+  <si>
+    <t>REII: obstacle/path-planning gate (planned, not agreed)
+· known-obstacle map source cited
+· planner output = MCTR cmd format
+· run vs modelled path evidence</t>
+  </si>
+  <si>
+    <t>REII: I3 handoff pack + demo evidence (planned, not agreed)
+· INTERFACE_MATRIX + TEST_LOG filled
+· NCR list w/ owners + sign-off
+· demo run-through capture</t>
+  </si>
+  <si>
+    <t>EERI 325             Group: Integration successful
+REII: REII integration verified gate (link + dashboard + sway)
+· INTERFACE_MATRIX all-pass or NCRs w/ owners</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">MCTR1: Enclosure v1 test,  ICD complete with- REII, ICD complete with- MCTR2?
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="9"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>REII: ESP32 nRF24 stub complete - RX mode + Table 2 SPI read-back (planned, not agreed)</t>
+    </r>
+  </si>
+  <si>
+    <t>REII: ICD Sec 4 payload freeze w/ MCTR+EEII (planned, not agreed)
+· D-01 byte maps + version byte rule</t>
+  </si>
+  <si>
+    <t>REII: bench  for 26 Oct (planned, not agreed)
+· PING-&gt;PONG ch77/2M, 200-pkt smoke CSV
+· 32-B pack/unpack byte-exact loopback
+· else raise NCRs before group test</t>
+  </si>
+  <si>
+    <t>REII: pre-integration (planned, not agreed)
+· isolation bench-verify + HW E-stop path (pre-live drivers)
+· MCTR-I profile format D-04 + encoder handoff</t>
   </si>
 </sst>
 </file>
@@ -323,7 +358,7 @@
     <numFmt numFmtId="167" formatCode="mmmm\ yyyy"/>
     <numFmt numFmtId="168" formatCode="dddd"/>
   </numFmts>
-  <fonts count="42" x14ac:knownFonts="1">
+  <fonts count="43" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -581,15 +616,21 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
-      <color theme="1"/>
+      <color rgb="FFFF0000"/>
       <name val="Seaford"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF00B050"/>
+      <name val="Seaford"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="9"/>
       <name val="Seaford"/>
       <scheme val="minor"/>
     </font>
@@ -821,7 +862,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="159">
+  <cellXfs count="166">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1049,32 +1090,191 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1082,24 +1282,30 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
     </xf>
@@ -1115,18 +1321,6 @@
     <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -1136,145 +1330,13 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -1648,19 +1710,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R15"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="5.5546875" style="3" customWidth="1"/>
-    <col min="5" max="9" width="10.5546875" style="3" customWidth="1"/>
-    <col min="10" max="11" width="10.5546875" style="28" customWidth="1"/>
-    <col min="12" max="14" width="5.5546875" style="3" customWidth="1"/>
-    <col min="15" max="15" width="25.5546875" style="3" customWidth="1"/>
-    <col min="16" max="16" width="10.5546875" style="3" customWidth="1"/>
-    <col min="17" max="18" width="5.5546875" style="3" customWidth="1"/>
-    <col min="19" max="16384" width="8.6640625" style="3"/>
+    <col min="1" max="4" width="5.5703125" style="3" customWidth="1"/>
+    <col min="5" max="9" width="10.5703125" style="3" customWidth="1"/>
+    <col min="10" max="11" width="10.5703125" style="28" customWidth="1"/>
+    <col min="12" max="14" width="5.5703125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="25.5703125" style="3" customWidth="1"/>
+    <col min="16" max="16" width="10.5703125" style="3" customWidth="1"/>
+    <col min="17" max="18" width="5.5703125" style="3" customWidth="1"/>
+    <col min="19" max="16384" width="8.7109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1680,7 +1742,7 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
     </row>
-    <row r="2" spans="1:18" s="7" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:18" s="7" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
       <c r="B2" s="5"/>
       <c r="C2" s="73" t="s">
@@ -1702,7 +1764,7 @@
       <c r="Q2" s="6"/>
       <c r="R2" s="4"/>
     </row>
-    <row r="3" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="3" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="8"/>
@@ -1722,7 +1784,7 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -1736,15 +1798,15 @@
       <c r="K4" s="12"/>
       <c r="L4" s="11"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="143" t="s">
+      <c r="N4" s="144" t="s">
         <v>10</v>
       </c>
-      <c r="O4" s="143"/>
-      <c r="P4" s="143"/>
-      <c r="Q4" s="143"/>
+      <c r="O4" s="144"/>
+      <c r="P4" s="144"/>
+      <c r="Q4" s="144"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="11"/>
       <c r="C5" s="13" t="s">
@@ -1762,13 +1824,13 @@
       <c r="K5" s="15"/>
       <c r="L5" s="16"/>
       <c r="M5" s="4"/>
-      <c r="N5" s="143"/>
-      <c r="O5" s="143"/>
-      <c r="P5" s="143"/>
-      <c r="Q5" s="143"/>
+      <c r="N5" s="144"/>
+      <c r="O5" s="144"/>
+      <c r="P5" s="144"/>
+      <c r="Q5" s="144"/>
       <c r="R5" s="1"/>
     </row>
-    <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="11"/>
       <c r="C6" s="17"/>
@@ -1782,13 +1844,13 @@
       <c r="K6" s="20"/>
       <c r="L6" s="19"/>
       <c r="M6" s="4"/>
-      <c r="N6" s="143"/>
-      <c r="O6" s="143"/>
-      <c r="P6" s="143"/>
-      <c r="Q6" s="143"/>
+      <c r="N6" s="144"/>
+      <c r="O6" s="144"/>
+      <c r="P6" s="144"/>
+      <c r="Q6" s="144"/>
       <c r="R6" s="1"/>
     </row>
-    <row r="7" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="11"/>
       <c r="C7" s="13" t="s">
@@ -1812,7 +1874,7 @@
       <c r="Q7" s="11"/>
       <c r="R7" s="1"/>
     </row>
-    <row r="8" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="11"/>
       <c r="C8" s="17"/>
@@ -1836,7 +1898,7 @@
       </c>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="11"/>
       <c r="C9" s="13" t="s">
@@ -1860,7 +1922,7 @@
       <c r="Q9" s="11"/>
       <c r="R9" s="1"/>
     </row>
-    <row r="10" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="11"/>
       <c r="C10" s="24"/>
@@ -1886,7 +1948,7 @@
       <c r="Q10" s="18"/>
       <c r="R10" s="1"/>
     </row>
-    <row r="11" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="11"/>
       <c r="C11" s="24"/>
@@ -1906,7 +1968,7 @@
       <c r="Q11" s="18"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="11"/>
       <c r="C12" s="13" t="s">
@@ -1930,7 +1992,7 @@
       <c r="Q12" s="18"/>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="11"/>
       <c r="C13" s="25"/>
@@ -1952,7 +2014,7 @@
       <c r="Q13" s="18"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="11"/>
       <c r="C14" s="18"/>
@@ -1972,7 +2034,7 @@
       <c r="Q14" s="18"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:18" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -2007,25 +2069,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AP40"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="5.5546875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="5.5546875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="5.5546875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.5546875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="5.5546875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="15.5546875" style="3" customWidth="1"/>
-    <col min="11" max="14" width="5.5546875" style="3" customWidth="1"/>
-    <col min="15" max="30" width="2.5546875" style="3" customWidth="1"/>
-    <col min="31" max="32" width="5.5546875" style="3" customWidth="1"/>
-    <col min="33" max="33" width="17.109375" style="3" customWidth="1"/>
-    <col min="34" max="34" width="10.44140625" style="3" customWidth="1"/>
-    <col min="35" max="16384" width="8.6640625" style="3"/>
+    <col min="1" max="3" width="5.5703125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="5.5703125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="5.5703125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="5.5703125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="3" customWidth="1"/>
+    <col min="11" max="14" width="5.5703125" style="3" customWidth="1"/>
+    <col min="15" max="30" width="2.5703125" style="3" customWidth="1"/>
+    <col min="31" max="32" width="5.5703125" style="3" customWidth="1"/>
+    <col min="33" max="33" width="17.140625" style="3" customWidth="1"/>
+    <col min="34" max="34" width="10.42578125" style="3" customWidth="1"/>
+    <col min="35" max="16384" width="8.7109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2059,42 +2121,42 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A2" s="29"/>
-      <c r="C2" s="112">
+      <c r="C2" s="113">
         <f ca="1">DATE(About!P8,9,1)</f>
         <v>46266</v>
       </c>
-      <c r="D2" s="112"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="112"/>
-      <c r="G2" s="112"/>
-      <c r="H2" s="112"/>
-      <c r="I2" s="112"/>
-      <c r="J2" s="112"/>
-      <c r="K2" s="112"/>
-      <c r="L2" s="112"/>
-      <c r="M2" s="112"/>
-      <c r="N2" s="112"/>
-      <c r="O2" s="112"/>
-      <c r="P2" s="112"/>
-      <c r="Q2" s="112"/>
-      <c r="R2" s="112"/>
-      <c r="S2" s="112"/>
-      <c r="T2" s="112"/>
-      <c r="U2" s="112"/>
-      <c r="V2" s="112"/>
-      <c r="W2" s="112"/>
-      <c r="X2" s="112"/>
-      <c r="Y2" s="112"/>
-      <c r="Z2" s="112"/>
-      <c r="AA2" s="112"/>
-      <c r="AB2" s="112"/>
-      <c r="AC2" s="112"/>
-      <c r="AD2" s="112"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="113"/>
+      <c r="M2" s="113"/>
+      <c r="N2" s="113"/>
+      <c r="O2" s="113"/>
+      <c r="P2" s="113"/>
+      <c r="Q2" s="113"/>
+      <c r="R2" s="113"/>
+      <c r="S2" s="113"/>
+      <c r="T2" s="113"/>
+      <c r="U2" s="113"/>
+      <c r="V2" s="113"/>
+      <c r="W2" s="113"/>
+      <c r="X2" s="113"/>
+      <c r="Y2" s="113"/>
+      <c r="Z2" s="113"/>
+      <c r="AA2" s="113"/>
+      <c r="AB2" s="113"/>
+      <c r="AC2" s="113"/>
+      <c r="AD2" s="113"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -2114,192 +2176,192 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="35"/>
-      <c r="C4" s="113">
+      <c r="C4" s="114">
         <f ca="1">C5</f>
         <v>46264</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113">
+      <c r="D4" s="114"/>
+      <c r="E4" s="114">
         <f ca="1">E5</f>
         <v>46265</v>
       </c>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113">
+      <c r="F4" s="114"/>
+      <c r="G4" s="114">
         <f ca="1">G5</f>
         <v>46266</v>
       </c>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113">
+      <c r="H4" s="114"/>
+      <c r="I4" s="114">
         <f ca="1">I5</f>
         <v>46267</v>
       </c>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113">
+      <c r="J4" s="114"/>
+      <c r="K4" s="114">
         <f ca="1">K5</f>
         <v>46268</v>
       </c>
-      <c r="L4" s="113"/>
-      <c r="M4" s="113"/>
+      <c r="L4" s="114"/>
+      <c r="M4" s="114"/>
       <c r="N4" s="37"/>
-      <c r="O4" s="113">
+      <c r="O4" s="114">
         <f ca="1">O5</f>
         <v>46269</v>
       </c>
-      <c r="P4" s="113"/>
-      <c r="Q4" s="113"/>
-      <c r="R4" s="113"/>
-      <c r="S4" s="113"/>
-      <c r="T4" s="113"/>
-      <c r="U4" s="113"/>
-      <c r="V4" s="113"/>
-      <c r="W4" s="113">
+      <c r="P4" s="114"/>
+      <c r="Q4" s="114"/>
+      <c r="R4" s="114"/>
+      <c r="S4" s="114"/>
+      <c r="T4" s="114"/>
+      <c r="U4" s="114"/>
+      <c r="V4" s="114"/>
+      <c r="W4" s="114">
         <f ca="1">W5</f>
         <v>46270</v>
       </c>
-      <c r="X4" s="113"/>
-      <c r="Y4" s="113"/>
-      <c r="Z4" s="113"/>
-      <c r="AA4" s="113"/>
-      <c r="AB4" s="113"/>
-      <c r="AC4" s="113"/>
-      <c r="AD4" s="113"/>
+      <c r="X4" s="114"/>
+      <c r="Y4" s="114"/>
+      <c r="Z4" s="114"/>
+      <c r="AA4" s="114"/>
+      <c r="AB4" s="114"/>
+      <c r="AC4" s="114"/>
+      <c r="AD4" s="114"/>
       <c r="AF4" s="38"/>
       <c r="AG4" s="39"/>
       <c r="AH4" s="39"/>
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="C5" s="90">
+      <c r="C5" s="92">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46264</v>
       </c>
-      <c r="D5" s="91"/>
-      <c r="E5" s="90">
+      <c r="D5" s="93"/>
+      <c r="E5" s="92">
         <f ca="1">C5+1</f>
         <v>46265</v>
       </c>
-      <c r="F5" s="91"/>
-      <c r="G5" s="90">
+      <c r="F5" s="93"/>
+      <c r="G5" s="92">
         <f ca="1">E5+1</f>
         <v>46266</v>
       </c>
-      <c r="H5" s="91"/>
-      <c r="I5" s="90">
+      <c r="H5" s="93"/>
+      <c r="I5" s="92">
         <f ca="1">G5+1</f>
         <v>46267</v>
       </c>
-      <c r="J5" s="91"/>
-      <c r="K5" s="90">
+      <c r="J5" s="93"/>
+      <c r="K5" s="92">
         <f ca="1">I5+1</f>
         <v>46268</v>
       </c>
-      <c r="L5" s="114"/>
-      <c r="M5" s="114"/>
+      <c r="L5" s="112"/>
+      <c r="M5" s="112"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="90">
+      <c r="O5" s="92">
         <f ca="1">K5+1</f>
         <v>46269</v>
       </c>
-      <c r="P5" s="114"/>
-      <c r="Q5" s="114"/>
-      <c r="R5" s="114"/>
-      <c r="S5" s="114"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="114"/>
-      <c r="V5" s="91"/>
-      <c r="W5" s="90">
+      <c r="P5" s="112"/>
+      <c r="Q5" s="112"/>
+      <c r="R5" s="112"/>
+      <c r="S5" s="112"/>
+      <c r="T5" s="112"/>
+      <c r="U5" s="112"/>
+      <c r="V5" s="93"/>
+      <c r="W5" s="92">
         <f ca="1">O5+1</f>
         <v>46270</v>
       </c>
-      <c r="X5" s="114"/>
-      <c r="Y5" s="114"/>
-      <c r="Z5" s="114"/>
-      <c r="AA5" s="114"/>
-      <c r="AB5" s="114"/>
-      <c r="AC5" s="114"/>
-      <c r="AD5" s="91"/>
+      <c r="X5" s="112"/>
+      <c r="Y5" s="112"/>
+      <c r="Z5" s="112"/>
+      <c r="AA5" s="112"/>
+      <c r="AB5" s="112"/>
+      <c r="AC5" s="112"/>
+      <c r="AD5" s="93"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
       <c r="AI5" s="41"/>
       <c r="AJ5" s="41"/>
     </row>
-    <row r="6" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="42"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="83"/>
-      <c r="F6" s="85"/>
-      <c r="G6" s="150"/>
-      <c r="H6" s="151"/>
-      <c r="I6" s="150"/>
-      <c r="J6" s="151"/>
-      <c r="K6" s="150"/>
-      <c r="L6" s="152"/>
-      <c r="M6" s="152"/>
-      <c r="N6" s="151"/>
-      <c r="O6" s="150"/>
-      <c r="P6" s="152"/>
-      <c r="Q6" s="152"/>
-      <c r="R6" s="152"/>
-      <c r="S6" s="152"/>
-      <c r="T6" s="152"/>
-      <c r="U6" s="152"/>
-      <c r="V6" s="151"/>
-      <c r="W6" s="150"/>
-      <c r="X6" s="152"/>
-      <c r="Y6" s="152"/>
-      <c r="Z6" s="152"/>
-      <c r="AA6" s="152"/>
-      <c r="AB6" s="152"/>
-      <c r="AC6" s="152"/>
-      <c r="AD6" s="151"/>
+      <c r="C6" s="97"/>
+      <c r="D6" s="98"/>
+      <c r="E6" s="97"/>
+      <c r="F6" s="98"/>
+      <c r="G6" s="148"/>
+      <c r="H6" s="149"/>
+      <c r="I6" s="148"/>
+      <c r="J6" s="149"/>
+      <c r="K6" s="148"/>
+      <c r="L6" s="150"/>
+      <c r="M6" s="150"/>
+      <c r="N6" s="149"/>
+      <c r="O6" s="148"/>
+      <c r="P6" s="150"/>
+      <c r="Q6" s="150"/>
+      <c r="R6" s="150"/>
+      <c r="S6" s="150"/>
+      <c r="T6" s="150"/>
+      <c r="U6" s="150"/>
+      <c r="V6" s="149"/>
+      <c r="W6" s="148"/>
+      <c r="X6" s="150"/>
+      <c r="Y6" s="150"/>
+      <c r="Z6" s="150"/>
+      <c r="AA6" s="150"/>
+      <c r="AB6" s="150"/>
+      <c r="AC6" s="150"/>
+      <c r="AD6" s="149"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
-    <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="C7" s="90">
+      <c r="C7" s="92">
         <f ca="1">W5+1</f>
         <v>46271</v>
       </c>
-      <c r="D7" s="91"/>
-      <c r="E7" s="153"/>
-      <c r="F7" s="154"/>
-      <c r="G7" s="153"/>
-      <c r="H7" s="154"/>
-      <c r="I7" s="153"/>
-      <c r="J7" s="154"/>
-      <c r="K7" s="153"/>
-      <c r="L7" s="155"/>
-      <c r="M7" s="155"/>
+      <c r="D7" s="93"/>
+      <c r="E7" s="101"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="101"/>
+      <c r="H7" s="102"/>
+      <c r="I7" s="101"/>
+      <c r="J7" s="102"/>
+      <c r="K7" s="101"/>
+      <c r="L7" s="103"/>
+      <c r="M7" s="103"/>
       <c r="N7" s="75"/>
-      <c r="O7" s="153"/>
-      <c r="P7" s="155"/>
-      <c r="Q7" s="155"/>
-      <c r="R7" s="155"/>
-      <c r="S7" s="155"/>
-      <c r="T7" s="155"/>
-      <c r="U7" s="155"/>
-      <c r="V7" s="154"/>
-      <c r="W7" s="153"/>
-      <c r="X7" s="155"/>
-      <c r="Y7" s="155"/>
-      <c r="Z7" s="155"/>
-      <c r="AA7" s="155"/>
-      <c r="AB7" s="155"/>
-      <c r="AC7" s="155"/>
-      <c r="AD7" s="154"/>
+      <c r="O7" s="101"/>
+      <c r="P7" s="103"/>
+      <c r="Q7" s="103"/>
+      <c r="R7" s="103"/>
+      <c r="S7" s="103"/>
+      <c r="T7" s="103"/>
+      <c r="U7" s="103"/>
+      <c r="V7" s="102"/>
+      <c r="W7" s="101"/>
+      <c r="X7" s="103"/>
+      <c r="Y7" s="103"/>
+      <c r="Z7" s="103"/>
+      <c r="AA7" s="103"/>
+      <c r="AB7" s="103"/>
+      <c r="AC7" s="103"/>
+      <c r="AD7" s="102"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
-      <c r="C8" s="90"/>
-      <c r="D8" s="91"/>
+      <c r="C8" s="92"/>
+      <c r="D8" s="93"/>
       <c r="E8" s="94">
         <f ca="1">C7+1</f>
         <v>46272</v>
@@ -2346,46 +2408,48 @@
       <c r="AD8" s="95"/>
       <c r="AF8" s="4"/>
     </row>
-    <row r="9" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="42"/>
-      <c r="C9" s="150"/>
-      <c r="D9" s="151"/>
-      <c r="E9" s="150"/>
-      <c r="F9" s="151"/>
-      <c r="G9" s="150"/>
-      <c r="H9" s="151"/>
-      <c r="I9" s="150"/>
-      <c r="J9" s="151"/>
-      <c r="K9" s="150"/>
-      <c r="L9" s="152"/>
-      <c r="M9" s="152"/>
-      <c r="N9" s="151"/>
-      <c r="O9" s="150"/>
-      <c r="P9" s="152"/>
-      <c r="Q9" s="152"/>
-      <c r="R9" s="152"/>
-      <c r="S9" s="152"/>
-      <c r="T9" s="152"/>
-      <c r="U9" s="152"/>
-      <c r="V9" s="151"/>
-      <c r="W9" s="150"/>
-      <c r="X9" s="152"/>
-      <c r="Y9" s="152"/>
-      <c r="Z9" s="152"/>
-      <c r="AA9" s="152"/>
-      <c r="AB9" s="152"/>
-      <c r="AC9" s="152"/>
-      <c r="AD9" s="151"/>
+      <c r="C9" s="148"/>
+      <c r="D9" s="149"/>
+      <c r="E9" s="148"/>
+      <c r="F9" s="149"/>
+      <c r="G9" s="148"/>
+      <c r="H9" s="149"/>
+      <c r="I9" s="148"/>
+      <c r="J9" s="149"/>
+      <c r="K9" s="148"/>
+      <c r="L9" s="150"/>
+      <c r="M9" s="150"/>
+      <c r="N9" s="149"/>
+      <c r="O9" s="151" t="s">
+        <v>41</v>
+      </c>
+      <c r="P9" s="153"/>
+      <c r="Q9" s="153"/>
+      <c r="R9" s="153"/>
+      <c r="S9" s="153"/>
+      <c r="T9" s="153"/>
+      <c r="U9" s="153"/>
+      <c r="V9" s="152"/>
+      <c r="W9" s="148"/>
+      <c r="X9" s="150"/>
+      <c r="Y9" s="150"/>
+      <c r="Z9" s="150"/>
+      <c r="AA9" s="150"/>
+      <c r="AB9" s="150"/>
+      <c r="AC9" s="150"/>
+      <c r="AD9" s="149"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
-    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="42"/>
-      <c r="C10" s="90">
+      <c r="C10" s="92">
         <f ca="1">W8+1</f>
         <v>46278</v>
       </c>
-      <c r="D10" s="91"/>
+      <c r="D10" s="93"/>
       <c r="E10" s="45"/>
       <c r="F10" s="75"/>
       <c r="G10" s="45"/>
@@ -2415,10 +2479,10 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="42"/>
     </row>
-    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
-      <c r="C11" s="90"/>
-      <c r="D11" s="91"/>
+      <c r="C11" s="92"/>
+      <c r="D11" s="93"/>
       <c r="E11" s="94">
         <f ca="1">C10+1</f>
         <v>46279</v>
@@ -2466,46 +2530,48 @@
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="42"/>
-      <c r="C12" s="150"/>
-      <c r="D12" s="151"/>
-      <c r="E12" s="150"/>
-      <c r="F12" s="151"/>
-      <c r="G12" s="150"/>
-      <c r="H12" s="151"/>
-      <c r="I12" s="150"/>
-      <c r="J12" s="151"/>
-      <c r="K12" s="150"/>
-      <c r="L12" s="152"/>
-      <c r="M12" s="152"/>
-      <c r="N12" s="151"/>
-      <c r="O12" s="150"/>
-      <c r="P12" s="152"/>
-      <c r="Q12" s="152"/>
-      <c r="R12" s="152"/>
-      <c r="S12" s="152"/>
-      <c r="T12" s="152"/>
-      <c r="U12" s="152"/>
-      <c r="V12" s="151"/>
-      <c r="W12" s="150"/>
-      <c r="X12" s="152"/>
-      <c r="Y12" s="152"/>
-      <c r="Z12" s="152"/>
-      <c r="AA12" s="152"/>
-      <c r="AB12" s="152"/>
-      <c r="AC12" s="152"/>
-      <c r="AD12" s="151"/>
+      <c r="C12" s="148"/>
+      <c r="D12" s="149"/>
+      <c r="E12" s="151" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="152"/>
+      <c r="G12" s="148"/>
+      <c r="H12" s="149"/>
+      <c r="I12" s="148"/>
+      <c r="J12" s="149"/>
+      <c r="K12" s="148"/>
+      <c r="L12" s="150"/>
+      <c r="M12" s="150"/>
+      <c r="N12" s="149"/>
+      <c r="O12" s="148"/>
+      <c r="P12" s="150"/>
+      <c r="Q12" s="150"/>
+      <c r="R12" s="150"/>
+      <c r="S12" s="150"/>
+      <c r="T12" s="150"/>
+      <c r="U12" s="150"/>
+      <c r="V12" s="149"/>
+      <c r="W12" s="148"/>
+      <c r="X12" s="150"/>
+      <c r="Y12" s="150"/>
+      <c r="Z12" s="150"/>
+      <c r="AA12" s="150"/>
+      <c r="AB12" s="150"/>
+      <c r="AC12" s="150"/>
+      <c r="AD12" s="149"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
-    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="42"/>
-      <c r="C13" s="90">
+      <c r="C13" s="92">
         <f ca="1">W11+1</f>
         <v>46285</v>
       </c>
-      <c r="D13" s="91"/>
+      <c r="D13" s="93"/>
       <c r="E13" s="45"/>
       <c r="F13" s="75"/>
       <c r="G13" s="45"/>
@@ -2535,10 +2601,10 @@
       <c r="AE13" s="7"/>
       <c r="AF13" s="42"/>
     </row>
-    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4"/>
-      <c r="C14" s="90"/>
-      <c r="D14" s="91"/>
+      <c r="C14" s="92"/>
+      <c r="D14" s="93"/>
       <c r="E14" s="94">
         <f ca="1">C13+1</f>
         <v>46286</v>
@@ -2585,64 +2651,64 @@
       <c r="AD14" s="95"/>
       <c r="AF14" s="4"/>
     </row>
-    <row r="15" spans="1:36" s="43" customFormat="1" ht="162.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" s="43" customFormat="1" ht="162.94999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="42"/>
-      <c r="C15" s="150"/>
-      <c r="D15" s="151"/>
-      <c r="E15" s="150"/>
-      <c r="F15" s="151"/>
-      <c r="G15" s="150"/>
-      <c r="H15" s="151"/>
-      <c r="I15" s="146"/>
-      <c r="J15" s="147"/>
-      <c r="K15" s="146"/>
-      <c r="L15" s="149"/>
-      <c r="M15" s="149"/>
-      <c r="N15" s="147"/>
-      <c r="O15" s="146"/>
-      <c r="P15" s="149"/>
-      <c r="Q15" s="149"/>
-      <c r="R15" s="149"/>
-      <c r="S15" s="149"/>
-      <c r="T15" s="149"/>
-      <c r="U15" s="149"/>
-      <c r="V15" s="147"/>
-      <c r="W15" s="146"/>
-      <c r="X15" s="149"/>
-      <c r="Y15" s="149"/>
-      <c r="Z15" s="149"/>
-      <c r="AA15" s="149"/>
-      <c r="AB15" s="149"/>
-      <c r="AC15" s="149"/>
-      <c r="AD15" s="147"/>
+      <c r="C15" s="148"/>
+      <c r="D15" s="149"/>
+      <c r="E15" s="148"/>
+      <c r="F15" s="149"/>
+      <c r="G15" s="148"/>
+      <c r="H15" s="149"/>
+      <c r="I15" s="106"/>
+      <c r="J15" s="108"/>
+      <c r="K15" s="106"/>
+      <c r="L15" s="107"/>
+      <c r="M15" s="107"/>
+      <c r="N15" s="108"/>
+      <c r="O15" s="106"/>
+      <c r="P15" s="107"/>
+      <c r="Q15" s="107"/>
+      <c r="R15" s="107"/>
+      <c r="S15" s="107"/>
+      <c r="T15" s="107"/>
+      <c r="U15" s="107"/>
+      <c r="V15" s="108"/>
+      <c r="W15" s="106"/>
+      <c r="X15" s="107"/>
+      <c r="Y15" s="107"/>
+      <c r="Z15" s="107"/>
+      <c r="AA15" s="107"/>
+      <c r="AB15" s="107"/>
+      <c r="AC15" s="107"/>
+      <c r="AD15" s="108"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
-    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="42"/>
-      <c r="C16" s="90">
+      <c r="C16" s="92">
         <f ca="1">W14+1</f>
         <v>46292</v>
       </c>
-      <c r="D16" s="91"/>
+      <c r="D16" s="93"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
       <c r="H16" s="75"/>
-      <c r="I16" s="92"/>
-      <c r="J16" s="93"/>
+      <c r="I16" s="145"/>
+      <c r="J16" s="146"/>
       <c r="K16" s="66"/>
       <c r="L16" s="68"/>
       <c r="M16" s="68"/>
       <c r="N16" s="67"/>
-      <c r="O16" s="92"/>
-      <c r="P16" s="148"/>
-      <c r="Q16" s="148"/>
-      <c r="R16" s="148"/>
-      <c r="S16" s="148"/>
-      <c r="T16" s="148"/>
-      <c r="U16" s="148"/>
-      <c r="V16" s="93"/>
+      <c r="O16" s="145"/>
+      <c r="P16" s="147"/>
+      <c r="Q16" s="147"/>
+      <c r="R16" s="147"/>
+      <c r="S16" s="147"/>
+      <c r="T16" s="147"/>
+      <c r="U16" s="147"/>
+      <c r="V16" s="146"/>
       <c r="W16" s="45"/>
       <c r="X16" s="76"/>
       <c r="Y16" s="76"/>
@@ -2654,10 +2720,10 @@
       <c r="AE16" s="7"/>
       <c r="AF16" s="42"/>
     </row>
-    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
-      <c r="C17" s="90"/>
-      <c r="D17" s="91"/>
+      <c r="C17" s="92"/>
+      <c r="D17" s="93"/>
       <c r="E17" s="94">
         <f ca="1">C16+1</f>
         <v>46293</v>
@@ -2704,69 +2770,69 @@
       <c r="AD17" s="95"/>
       <c r="AF17" s="4"/>
     </row>
-    <row r="18" spans="1:42" s="43" customFormat="1" ht="147.30000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:42" s="43" customFormat="1" ht="147.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="42"/>
-      <c r="C18" s="144" t="s">
-        <v>19</v>
-      </c>
-      <c r="D18" s="145"/>
-      <c r="E18" s="146"/>
-      <c r="F18" s="147"/>
-      <c r="G18" s="146"/>
-      <c r="H18" s="147"/>
-      <c r="I18" s="144" t="s">
+      <c r="C18" s="109" t="s">
+        <v>18</v>
+      </c>
+      <c r="D18" s="111"/>
+      <c r="E18" s="106"/>
+      <c r="F18" s="108"/>
+      <c r="G18" s="106"/>
+      <c r="H18" s="108"/>
+      <c r="I18" s="109" t="s">
         <v>17</v>
       </c>
-      <c r="J18" s="145"/>
+      <c r="J18" s="111"/>
       <c r="K18" s="70"/>
       <c r="L18" s="71"/>
       <c r="M18" s="71"/>
       <c r="N18" s="72"/>
-      <c r="O18" s="83"/>
-      <c r="P18" s="84"/>
-      <c r="Q18" s="84"/>
-      <c r="R18" s="84"/>
-      <c r="S18" s="84"/>
-      <c r="T18" s="84"/>
-      <c r="U18" s="84"/>
-      <c r="V18" s="85"/>
-      <c r="W18" s="83"/>
-      <c r="X18" s="84"/>
-      <c r="Y18" s="84"/>
-      <c r="Z18" s="84"/>
-      <c r="AA18" s="84"/>
-      <c r="AB18" s="84"/>
-      <c r="AC18" s="84"/>
-      <c r="AD18" s="85"/>
+      <c r="O18" s="97"/>
+      <c r="P18" s="143"/>
+      <c r="Q18" s="143"/>
+      <c r="R18" s="143"/>
+      <c r="S18" s="143"/>
+      <c r="T18" s="143"/>
+      <c r="U18" s="143"/>
+      <c r="V18" s="98"/>
+      <c r="W18" s="97"/>
+      <c r="X18" s="143"/>
+      <c r="Y18" s="143"/>
+      <c r="Z18" s="143"/>
+      <c r="AA18" s="143"/>
+      <c r="AB18" s="143"/>
+      <c r="AC18" s="143"/>
+      <c r="AD18" s="98"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
-    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="42"/>
-      <c r="C19" s="90">
+      <c r="C19" s="92">
         <f ca="1">W17+1</f>
         <v>46299</v>
       </c>
-      <c r="D19" s="91"/>
+      <c r="D19" s="93"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
       <c r="H19" s="75"/>
-      <c r="I19" s="92"/>
-      <c r="J19" s="93"/>
+      <c r="I19" s="145"/>
+      <c r="J19" s="146"/>
       <c r="K19" s="66"/>
       <c r="L19" s="68"/>
       <c r="M19" s="68"/>
       <c r="N19" s="67"/>
-      <c r="O19" s="92"/>
-      <c r="P19" s="148"/>
-      <c r="Q19" s="148"/>
-      <c r="R19" s="148"/>
-      <c r="S19" s="148"/>
-      <c r="T19" s="148"/>
-      <c r="U19" s="148"/>
-      <c r="V19" s="93"/>
+      <c r="O19" s="145"/>
+      <c r="P19" s="147"/>
+      <c r="Q19" s="147"/>
+      <c r="R19" s="147"/>
+      <c r="S19" s="147"/>
+      <c r="T19" s="147"/>
+      <c r="U19" s="147"/>
+      <c r="V19" s="146"/>
       <c r="W19" s="45"/>
       <c r="X19" s="76"/>
       <c r="Y19" s="76"/>
@@ -2778,10 +2844,10 @@
       <c r="AE19" s="7"/>
       <c r="AF19" s="42"/>
     </row>
-    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="91"/>
+      <c r="C20" s="92"/>
+      <c r="D20" s="93"/>
       <c r="E20" s="94">
         <f ca="1">C19+1</f>
         <v>46300</v>
@@ -2828,41 +2894,41 @@
       <c r="AD20" s="95"/>
       <c r="AF20" s="4"/>
     </row>
-    <row r="21" spans="1:42" s="43" customFormat="1" ht="166.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:42" s="43" customFormat="1" ht="166.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="42"/>
-      <c r="C21" s="83"/>
-      <c r="D21" s="85"/>
-      <c r="E21" s="83"/>
-      <c r="F21" s="85"/>
-      <c r="G21" s="83"/>
-      <c r="H21" s="85"/>
-      <c r="I21" s="83"/>
-      <c r="J21" s="85"/>
+      <c r="C21" s="97"/>
+      <c r="D21" s="98"/>
+      <c r="E21" s="97"/>
+      <c r="F21" s="98"/>
+      <c r="G21" s="97"/>
+      <c r="H21" s="98"/>
+      <c r="I21" s="97"/>
+      <c r="J21" s="98"/>
       <c r="K21" s="70"/>
       <c r="L21" s="71"/>
       <c r="M21" s="71"/>
       <c r="N21" s="72"/>
-      <c r="O21" s="83"/>
-      <c r="P21" s="84"/>
-      <c r="Q21" s="84"/>
-      <c r="R21" s="84"/>
-      <c r="S21" s="84"/>
-      <c r="T21" s="84"/>
-      <c r="U21" s="84"/>
-      <c r="V21" s="85"/>
-      <c r="W21" s="83"/>
-      <c r="X21" s="84"/>
-      <c r="Y21" s="84"/>
-      <c r="Z21" s="84"/>
-      <c r="AA21" s="84"/>
-      <c r="AB21" s="84"/>
-      <c r="AC21" s="84"/>
-      <c r="AD21" s="85"/>
+      <c r="O21" s="97"/>
+      <c r="P21" s="143"/>
+      <c r="Q21" s="143"/>
+      <c r="R21" s="143"/>
+      <c r="S21" s="143"/>
+      <c r="T21" s="143"/>
+      <c r="U21" s="143"/>
+      <c r="V21" s="98"/>
+      <c r="W21" s="97"/>
+      <c r="X21" s="143"/>
+      <c r="Y21" s="143"/>
+      <c r="Z21" s="143"/>
+      <c r="AA21" s="143"/>
+      <c r="AB21" s="143"/>
+      <c r="AC21" s="143"/>
+      <c r="AD21" s="98"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
     </row>
-    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52"/>
@@ -2894,7 +2960,7 @@
       <c r="AD22" s="55"/>
       <c r="AF22" s="4"/>
     </row>
-    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="56"/>
@@ -2928,12 +2994,12 @@
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
     </row>
-    <row r="24" spans="1:42" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:42" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="M24" s="1"/>
       <c r="AF24" s="1"/>
     </row>
-    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="C25" s="86" t="s">
         <v>0</v>
@@ -2972,7 +3038,7 @@
       <c r="AD25" s="87"/>
       <c r="AF25" s="1"/>
     </row>
-    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="C26" s="86"/>
       <c r="D26" s="86"/>
@@ -3045,10 +3111,10 @@
       </c>
       <c r="AF26" s="1"/>
     </row>
-    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="C27" s="88" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D27" s="88"/>
       <c r="E27" s="88"/>
@@ -3119,10 +3185,10 @@
       </c>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="C28" s="89" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D28" s="89"/>
       <c r="E28" s="89"/>
@@ -3193,7 +3259,7 @@
       </c>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="C29" s="88"/>
       <c r="D29" s="88"/>
@@ -3265,10 +3331,10 @@
       </c>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="C30" s="89" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D30" s="89"/>
       <c r="E30" s="89"/>
@@ -3339,7 +3405,7 @@
       </c>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="C31" s="88"/>
       <c r="D31" s="88"/>
@@ -3411,7 +3477,7 @@
       </c>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="M32" s="1"/>
       <c r="O32" s="64">
@@ -3474,7 +3540,7 @@
       </c>
       <c r="AF32" s="1"/>
     </row>
-    <row r="33" spans="1:32" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="M33" s="1"/>
       <c r="O33" s="64"/>
@@ -3495,7 +3561,7 @@
       <c r="AD33" s="65"/>
       <c r="AF33" s="1"/>
     </row>
-    <row r="34" spans="1:32" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -3529,10 +3595,10 @@
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
     </row>
-    <row r="38" spans="1:32" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:32" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D39" s="115" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E39" s="116"/>
       <c r="F39" s="117"/>
@@ -3542,16 +3608,16 @@
       </c>
       <c r="H39" s="122"/>
       <c r="I39" s="115" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J39" s="125"/>
       <c r="K39" s="127" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L39" s="128"/>
       <c r="M39" s="131">
         <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
-        <v>5.0000000000000009</v>
+        <v>3.9999999999999982</v>
       </c>
       <c r="N39" s="132"/>
       <c r="O39" s="132"/>
@@ -3559,7 +3625,7 @@
       <c r="Q39" s="132"/>
       <c r="R39" s="133"/>
       <c r="S39" s="137" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T39" s="138"/>
       <c r="U39" s="138"/>
@@ -3567,7 +3633,7 @@
       <c r="W39" s="138"/>
       <c r="X39" s="139"/>
     </row>
-    <row r="40" spans="1:32" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:32" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D40" s="118"/>
       <c r="E40" s="119"/>
       <c r="F40" s="120"/>
@@ -3740,25 +3806,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AP40"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="5.5546875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="5.5546875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="5.5546875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.5546875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="5.5546875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="15.5546875" style="3" customWidth="1"/>
-    <col min="11" max="14" width="5.5546875" style="3" customWidth="1"/>
-    <col min="15" max="30" width="2.5546875" style="3" customWidth="1"/>
-    <col min="31" max="32" width="5.5546875" style="3" customWidth="1"/>
-    <col min="33" max="33" width="17.109375" style="3" customWidth="1"/>
-    <col min="34" max="34" width="10.44140625" style="3" customWidth="1"/>
-    <col min="35" max="16384" width="8.6640625" style="3"/>
+    <col min="1" max="3" width="5.5703125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="5.5703125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="5.5703125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="5.5703125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="3" customWidth="1"/>
+    <col min="11" max="14" width="5.5703125" style="3" customWidth="1"/>
+    <col min="15" max="30" width="2.5703125" style="3" customWidth="1"/>
+    <col min="31" max="32" width="5.5703125" style="3" customWidth="1"/>
+    <col min="33" max="33" width="17.140625" style="3" customWidth="1"/>
+    <col min="34" max="34" width="10.42578125" style="3" customWidth="1"/>
+    <col min="35" max="16384" width="8.7109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3792,42 +3858,42 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A2" s="29"/>
-      <c r="C2" s="112">
+      <c r="C2" s="113">
         <f ca="1">DATE(About!P8,10,1)</f>
         <v>46296</v>
       </c>
-      <c r="D2" s="112"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="112"/>
-      <c r="G2" s="112"/>
-      <c r="H2" s="112"/>
-      <c r="I2" s="112"/>
-      <c r="J2" s="112"/>
-      <c r="K2" s="112"/>
-      <c r="L2" s="112"/>
-      <c r="M2" s="112"/>
-      <c r="N2" s="112"/>
-      <c r="O2" s="112"/>
-      <c r="P2" s="112"/>
-      <c r="Q2" s="112"/>
-      <c r="R2" s="112"/>
-      <c r="S2" s="112"/>
-      <c r="T2" s="112"/>
-      <c r="U2" s="112"/>
-      <c r="V2" s="112"/>
-      <c r="W2" s="112"/>
-      <c r="X2" s="112"/>
-      <c r="Y2" s="112"/>
-      <c r="Z2" s="112"/>
-      <c r="AA2" s="112"/>
-      <c r="AB2" s="112"/>
-      <c r="AC2" s="112"/>
-      <c r="AD2" s="112"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="113"/>
+      <c r="M2" s="113"/>
+      <c r="N2" s="113"/>
+      <c r="O2" s="113"/>
+      <c r="P2" s="113"/>
+      <c r="Q2" s="113"/>
+      <c r="R2" s="113"/>
+      <c r="S2" s="113"/>
+      <c r="T2" s="113"/>
+      <c r="U2" s="113"/>
+      <c r="V2" s="113"/>
+      <c r="W2" s="113"/>
+      <c r="X2" s="113"/>
+      <c r="Y2" s="113"/>
+      <c r="Z2" s="113"/>
+      <c r="AA2" s="113"/>
+      <c r="AB2" s="113"/>
+      <c r="AC2" s="113"/>
+      <c r="AD2" s="113"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -3847,194 +3913,194 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="35"/>
-      <c r="C4" s="113">
+      <c r="C4" s="114">
         <f ca="1">C5</f>
         <v>46292</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113">
+      <c r="D4" s="114"/>
+      <c r="E4" s="114">
         <f ca="1">E5</f>
         <v>46293</v>
       </c>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113">
+      <c r="F4" s="114"/>
+      <c r="G4" s="114">
         <f ca="1">G5</f>
         <v>46294</v>
       </c>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113">
+      <c r="H4" s="114"/>
+      <c r="I4" s="114">
         <f ca="1">I5</f>
         <v>46295</v>
       </c>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113">
+      <c r="J4" s="114"/>
+      <c r="K4" s="114">
         <f ca="1">K5</f>
         <v>46296</v>
       </c>
-      <c r="L4" s="113"/>
-      <c r="M4" s="113"/>
+      <c r="L4" s="114"/>
+      <c r="M4" s="114"/>
       <c r="N4" s="37"/>
-      <c r="O4" s="113">
+      <c r="O4" s="114">
         <f ca="1">O5</f>
         <v>46297</v>
       </c>
-      <c r="P4" s="113"/>
-      <c r="Q4" s="113"/>
-      <c r="R4" s="113"/>
-      <c r="S4" s="113"/>
-      <c r="T4" s="113"/>
-      <c r="U4" s="113"/>
-      <c r="V4" s="113"/>
-      <c r="W4" s="113">
+      <c r="P4" s="114"/>
+      <c r="Q4" s="114"/>
+      <c r="R4" s="114"/>
+      <c r="S4" s="114"/>
+      <c r="T4" s="114"/>
+      <c r="U4" s="114"/>
+      <c r="V4" s="114"/>
+      <c r="W4" s="114">
         <f ca="1">W5</f>
         <v>46298</v>
       </c>
-      <c r="X4" s="113"/>
-      <c r="Y4" s="113"/>
-      <c r="Z4" s="113"/>
-      <c r="AA4" s="113"/>
-      <c r="AB4" s="113"/>
-      <c r="AC4" s="113"/>
-      <c r="AD4" s="113"/>
+      <c r="X4" s="114"/>
+      <c r="Y4" s="114"/>
+      <c r="Z4" s="114"/>
+      <c r="AA4" s="114"/>
+      <c r="AB4" s="114"/>
+      <c r="AC4" s="114"/>
+      <c r="AD4" s="114"/>
       <c r="AF4" s="38"/>
       <c r="AG4" s="39"/>
       <c r="AH4" s="39"/>
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="C5" s="90">
+      <c r="C5" s="92">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46292</v>
       </c>
-      <c r="D5" s="91"/>
-      <c r="E5" s="90">
+      <c r="D5" s="93"/>
+      <c r="E5" s="92">
         <f ca="1">C5+1</f>
         <v>46293</v>
       </c>
-      <c r="F5" s="91"/>
-      <c r="G5" s="90">
+      <c r="F5" s="93"/>
+      <c r="G5" s="92">
         <f ca="1">E5+1</f>
         <v>46294</v>
       </c>
-      <c r="H5" s="91"/>
-      <c r="I5" s="90">
+      <c r="H5" s="93"/>
+      <c r="I5" s="92">
         <f ca="1">G5+1</f>
         <v>46295</v>
       </c>
-      <c r="J5" s="91"/>
-      <c r="K5" s="90">
+      <c r="J5" s="93"/>
+      <c r="K5" s="92">
         <f ca="1">I5+1</f>
         <v>46296</v>
       </c>
-      <c r="L5" s="114"/>
-      <c r="M5" s="114"/>
+      <c r="L5" s="112"/>
+      <c r="M5" s="112"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="90">
+      <c r="O5" s="92">
         <f ca="1">K5+1</f>
         <v>46297</v>
       </c>
-      <c r="P5" s="114"/>
-      <c r="Q5" s="114"/>
-      <c r="R5" s="114"/>
-      <c r="S5" s="114"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="114"/>
-      <c r="V5" s="91"/>
-      <c r="W5" s="90">
+      <c r="P5" s="112"/>
+      <c r="Q5" s="112"/>
+      <c r="R5" s="112"/>
+      <c r="S5" s="112"/>
+      <c r="T5" s="112"/>
+      <c r="U5" s="112"/>
+      <c r="V5" s="93"/>
+      <c r="W5" s="92">
         <f ca="1">O5+1</f>
         <v>46298</v>
       </c>
-      <c r="X5" s="114"/>
-      <c r="Y5" s="114"/>
-      <c r="Z5" s="114"/>
-      <c r="AA5" s="114"/>
-      <c r="AB5" s="114"/>
-      <c r="AC5" s="114"/>
-      <c r="AD5" s="91"/>
+      <c r="X5" s="112"/>
+      <c r="Y5" s="112"/>
+      <c r="Z5" s="112"/>
+      <c r="AA5" s="112"/>
+      <c r="AB5" s="112"/>
+      <c r="AC5" s="112"/>
+      <c r="AD5" s="93"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
       <c r="AI5" s="41"/>
       <c r="AJ5" s="41"/>
     </row>
-    <row r="6" spans="1:36" s="43" customFormat="1" ht="131.69999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" s="43" customFormat="1" ht="131.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="42"/>
-      <c r="C6" s="97"/>
-      <c r="D6" s="99"/>
-      <c r="E6" s="97"/>
-      <c r="F6" s="99"/>
-      <c r="G6" s="97"/>
-      <c r="H6" s="99"/>
-      <c r="I6" s="97"/>
-      <c r="J6" s="99"/>
-      <c r="K6" s="146"/>
-      <c r="L6" s="149"/>
-      <c r="M6" s="149"/>
-      <c r="N6" s="147"/>
-      <c r="O6" s="146"/>
-      <c r="P6" s="149"/>
-      <c r="Q6" s="149"/>
-      <c r="R6" s="149"/>
-      <c r="S6" s="149"/>
-      <c r="T6" s="149"/>
-      <c r="U6" s="149"/>
-      <c r="V6" s="147"/>
-      <c r="W6" s="144" t="s">
-        <v>20</v>
-      </c>
-      <c r="X6" s="157"/>
-      <c r="Y6" s="157"/>
-      <c r="Z6" s="157"/>
-      <c r="AA6" s="157"/>
-      <c r="AB6" s="157"/>
-      <c r="AC6" s="157"/>
-      <c r="AD6" s="145"/>
+      <c r="C6" s="104"/>
+      <c r="D6" s="105"/>
+      <c r="E6" s="104"/>
+      <c r="F6" s="105"/>
+      <c r="G6" s="104"/>
+      <c r="H6" s="105"/>
+      <c r="I6" s="104"/>
+      <c r="J6" s="105"/>
+      <c r="K6" s="106"/>
+      <c r="L6" s="107"/>
+      <c r="M6" s="107"/>
+      <c r="N6" s="108"/>
+      <c r="O6" s="106"/>
+      <c r="P6" s="107"/>
+      <c r="Q6" s="107"/>
+      <c r="R6" s="107"/>
+      <c r="S6" s="107"/>
+      <c r="T6" s="107"/>
+      <c r="U6" s="107"/>
+      <c r="V6" s="108"/>
+      <c r="W6" s="109" t="s">
+        <v>19</v>
+      </c>
+      <c r="X6" s="110"/>
+      <c r="Y6" s="110"/>
+      <c r="Z6" s="110"/>
+      <c r="AA6" s="110"/>
+      <c r="AB6" s="110"/>
+      <c r="AC6" s="110"/>
+      <c r="AD6" s="111"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
-    <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="C7" s="90">
+      <c r="C7" s="92">
         <f ca="1">W5+1</f>
         <v>46299</v>
       </c>
-      <c r="D7" s="91"/>
-      <c r="E7" s="153"/>
-      <c r="F7" s="154"/>
-      <c r="G7" s="153"/>
-      <c r="H7" s="154"/>
-      <c r="I7" s="153"/>
-      <c r="J7" s="154"/>
-      <c r="K7" s="153"/>
-      <c r="L7" s="155"/>
-      <c r="M7" s="155"/>
+      <c r="D7" s="93"/>
+      <c r="E7" s="101"/>
+      <c r="F7" s="102"/>
+      <c r="G7" s="101"/>
+      <c r="H7" s="102"/>
+      <c r="I7" s="101"/>
+      <c r="J7" s="102"/>
+      <c r="K7" s="101"/>
+      <c r="L7" s="103"/>
+      <c r="M7" s="103"/>
       <c r="N7" s="75"/>
-      <c r="O7" s="153"/>
-      <c r="P7" s="155"/>
-      <c r="Q7" s="155"/>
-      <c r="R7" s="155"/>
-      <c r="S7" s="155"/>
-      <c r="T7" s="155"/>
-      <c r="U7" s="155"/>
-      <c r="V7" s="154"/>
-      <c r="W7" s="153"/>
-      <c r="X7" s="155"/>
-      <c r="Y7" s="155"/>
-      <c r="Z7" s="155"/>
-      <c r="AA7" s="155"/>
-      <c r="AB7" s="155"/>
-      <c r="AC7" s="155"/>
-      <c r="AD7" s="154"/>
+      <c r="O7" s="101"/>
+      <c r="P7" s="103"/>
+      <c r="Q7" s="103"/>
+      <c r="R7" s="103"/>
+      <c r="S7" s="103"/>
+      <c r="T7" s="103"/>
+      <c r="U7" s="103"/>
+      <c r="V7" s="102"/>
+      <c r="W7" s="101"/>
+      <c r="X7" s="103"/>
+      <c r="Y7" s="103"/>
+      <c r="Z7" s="103"/>
+      <c r="AA7" s="103"/>
+      <c r="AB7" s="103"/>
+      <c r="AC7" s="103"/>
+      <c r="AD7" s="102"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
-      <c r="C8" s="90"/>
-      <c r="D8" s="91"/>
+      <c r="C8" s="92"/>
+      <c r="D8" s="93"/>
       <c r="E8" s="94">
         <f ca="1">C7+1</f>
         <v>46300</v>
@@ -4081,56 +4147,56 @@
       <c r="AD8" s="95"/>
       <c r="AF8" s="4"/>
     </row>
-    <row r="9" spans="1:36" s="43" customFormat="1" ht="149.69999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" s="43" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="42"/>
-      <c r="C9" s="105"/>
-      <c r="D9" s="106"/>
-      <c r="E9" s="105" t="s">
+      <c r="C9" s="83"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="83" t="s">
+        <v>28</v>
+      </c>
+      <c r="F9" s="85"/>
+      <c r="G9" s="83" t="s">
+        <v>27</v>
+      </c>
+      <c r="H9" s="85"/>
+      <c r="I9" s="83" t="s">
+        <v>37</v>
+      </c>
+      <c r="J9" s="85"/>
+      <c r="K9" s="83" t="s">
         <v>29</v>
       </c>
-      <c r="F9" s="106"/>
-      <c r="G9" s="105" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="106"/>
-      <c r="I9" s="105" t="s">
-        <v>43</v>
-      </c>
-      <c r="J9" s="106"/>
-      <c r="K9" s="105" t="s">
-        <v>30</v>
-      </c>
-      <c r="L9" s="108"/>
-      <c r="M9" s="108"/>
-      <c r="N9" s="106"/>
-      <c r="O9" s="105" t="s">
-        <v>44</v>
-      </c>
-      <c r="P9" s="108"/>
-      <c r="Q9" s="108"/>
-      <c r="R9" s="108"/>
-      <c r="S9" s="108"/>
-      <c r="T9" s="108"/>
-      <c r="U9" s="108"/>
-      <c r="V9" s="106"/>
-      <c r="W9" s="105"/>
-      <c r="X9" s="108"/>
-      <c r="Y9" s="108"/>
-      <c r="Z9" s="108"/>
-      <c r="AA9" s="108"/>
-      <c r="AB9" s="108"/>
-      <c r="AC9" s="108"/>
-      <c r="AD9" s="106"/>
+      <c r="L9" s="84"/>
+      <c r="M9" s="84"/>
+      <c r="N9" s="85"/>
+      <c r="O9" s="83" t="s">
+        <v>48</v>
+      </c>
+      <c r="P9" s="84"/>
+      <c r="Q9" s="84"/>
+      <c r="R9" s="84"/>
+      <c r="S9" s="84"/>
+      <c r="T9" s="84"/>
+      <c r="U9" s="84"/>
+      <c r="V9" s="85"/>
+      <c r="W9" s="83"/>
+      <c r="X9" s="84"/>
+      <c r="Y9" s="84"/>
+      <c r="Z9" s="84"/>
+      <c r="AA9" s="84"/>
+      <c r="AB9" s="84"/>
+      <c r="AC9" s="84"/>
+      <c r="AD9" s="85"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
-    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="42"/>
-      <c r="C10" s="90">
+      <c r="C10" s="92">
         <f ca="1">W8+1</f>
         <v>46306</v>
       </c>
-      <c r="D10" s="91"/>
+      <c r="D10" s="93"/>
       <c r="E10" s="45"/>
       <c r="F10" s="75"/>
       <c r="G10" s="45"/>
@@ -4160,10 +4226,10 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="42"/>
     </row>
-    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
-      <c r="C11" s="90"/>
-      <c r="D11" s="91"/>
+      <c r="C11" s="92"/>
+      <c r="D11" s="93"/>
       <c r="E11" s="94">
         <f ca="1">C10+1</f>
         <v>46307</v>
@@ -4211,56 +4277,60 @@
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:36" s="43" customFormat="1" ht="134.69999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" s="43" customFormat="1" ht="134.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="42"/>
-      <c r="C12" s="105"/>
-      <c r="D12" s="106"/>
-      <c r="E12" s="158" t="s">
-        <v>46</v>
-      </c>
-      <c r="F12" s="106"/>
-      <c r="G12" s="105" t="s">
-        <v>45</v>
-      </c>
-      <c r="H12" s="106"/>
-      <c r="I12" s="105"/>
-      <c r="J12" s="106"/>
-      <c r="K12" s="158" t="s">
+      <c r="C12" s="163" t="s">
         <v>47</v>
       </c>
-      <c r="L12" s="108"/>
-      <c r="M12" s="108"/>
-      <c r="N12" s="106"/>
-      <c r="O12" s="105" t="s">
+      <c r="D12" s="164"/>
+      <c r="E12" s="100" t="s">
+        <v>39</v>
+      </c>
+      <c r="F12" s="85"/>
+      <c r="G12" s="83" t="s">
+        <v>38</v>
+      </c>
+      <c r="H12" s="85"/>
+      <c r="I12" s="163" t="s">
+        <v>59</v>
+      </c>
+      <c r="J12" s="164"/>
+      <c r="K12" s="100" t="s">
         <v>40</v>
       </c>
-      <c r="P12" s="108"/>
-      <c r="Q12" s="108"/>
-      <c r="R12" s="108"/>
-      <c r="S12" s="108"/>
-      <c r="T12" s="108"/>
-      <c r="U12" s="108"/>
-      <c r="V12" s="106"/>
-      <c r="W12" s="156" t="s">
-        <v>31</v>
-      </c>
-      <c r="X12" s="108"/>
-      <c r="Y12" s="108"/>
-      <c r="Z12" s="108"/>
-      <c r="AA12" s="108"/>
-      <c r="AB12" s="108"/>
-      <c r="AC12" s="108"/>
-      <c r="AD12" s="106"/>
+      <c r="L12" s="84"/>
+      <c r="M12" s="84"/>
+      <c r="N12" s="85"/>
+      <c r="O12" s="83" t="s">
+        <v>58</v>
+      </c>
+      <c r="P12" s="84"/>
+      <c r="Q12" s="84"/>
+      <c r="R12" s="84"/>
+      <c r="S12" s="84"/>
+      <c r="T12" s="84"/>
+      <c r="U12" s="84"/>
+      <c r="V12" s="85"/>
+      <c r="W12" s="99" t="s">
+        <v>30</v>
+      </c>
+      <c r="X12" s="84"/>
+      <c r="Y12" s="84"/>
+      <c r="Z12" s="84"/>
+      <c r="AA12" s="84"/>
+      <c r="AB12" s="84"/>
+      <c r="AC12" s="84"/>
+      <c r="AD12" s="85"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
-    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="42"/>
-      <c r="C13" s="90">
+      <c r="C13" s="92">
         <f ca="1">W11+1</f>
         <v>46313</v>
       </c>
-      <c r="D13" s="91"/>
+      <c r="D13" s="93"/>
       <c r="E13" s="45"/>
       <c r="F13" s="75"/>
       <c r="G13" s="45"/>
@@ -4290,10 +4360,10 @@
       <c r="AE13" s="7"/>
       <c r="AF13" s="42"/>
     </row>
-    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4"/>
-      <c r="C14" s="90"/>
-      <c r="D14" s="91"/>
+      <c r="C14" s="92"/>
+      <c r="D14" s="93"/>
       <c r="E14" s="94">
         <f ca="1">C13+1</f>
         <v>46314</v>
@@ -4340,54 +4410,60 @@
       <c r="AD14" s="95"/>
       <c r="AF14" s="4"/>
     </row>
-    <row r="15" spans="1:36" s="43" customFormat="1" ht="140.69999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" s="43" customFormat="1" ht="140.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="42"/>
-      <c r="C15" s="156" t="s">
+      <c r="C15" s="99" t="s">
+        <v>31</v>
+      </c>
+      <c r="D15" s="85"/>
+      <c r="E15" s="163" t="s">
+        <v>50</v>
+      </c>
+      <c r="F15" s="164"/>
+      <c r="G15" s="163" t="s">
+        <v>51</v>
+      </c>
+      <c r="H15" s="164"/>
+      <c r="I15" s="99" t="s">
+        <v>34</v>
+      </c>
+      <c r="J15" s="85"/>
+      <c r="K15" s="163" t="s">
+        <v>60</v>
+      </c>
+      <c r="L15" s="165"/>
+      <c r="M15" s="165"/>
+      <c r="N15" s="164"/>
+      <c r="O15" s="83" t="s">
         <v>32</v>
       </c>
-      <c r="D15" s="106"/>
-      <c r="E15" s="105"/>
-      <c r="F15" s="106"/>
-      <c r="G15" s="105"/>
-      <c r="H15" s="106"/>
-      <c r="I15" s="156" t="s">
-        <v>36</v>
-      </c>
-      <c r="J15" s="106"/>
-      <c r="K15" s="105"/>
-      <c r="L15" s="108"/>
-      <c r="M15" s="108"/>
-      <c r="N15" s="106"/>
-      <c r="O15" s="105" t="s">
-        <v>34</v>
-      </c>
-      <c r="P15" s="108"/>
-      <c r="Q15" s="108"/>
-      <c r="R15" s="108"/>
-      <c r="S15" s="108"/>
-      <c r="T15" s="108"/>
-      <c r="U15" s="108"/>
-      <c r="V15" s="106"/>
-      <c r="W15" s="156" t="s">
-        <v>35</v>
-      </c>
-      <c r="X15" s="108"/>
-      <c r="Y15" s="108"/>
-      <c r="Z15" s="108"/>
-      <c r="AA15" s="108"/>
-      <c r="AB15" s="108"/>
-      <c r="AC15" s="108"/>
-      <c r="AD15" s="106"/>
+      <c r="P15" s="84"/>
+      <c r="Q15" s="84"/>
+      <c r="R15" s="84"/>
+      <c r="S15" s="84"/>
+      <c r="T15" s="84"/>
+      <c r="U15" s="84"/>
+      <c r="V15" s="85"/>
+      <c r="W15" s="99" t="s">
+        <v>33</v>
+      </c>
+      <c r="X15" s="84"/>
+      <c r="Y15" s="84"/>
+      <c r="Z15" s="84"/>
+      <c r="AA15" s="84"/>
+      <c r="AB15" s="84"/>
+      <c r="AC15" s="84"/>
+      <c r="AD15" s="85"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
-    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="42"/>
-      <c r="C16" s="90">
+      <c r="C16" s="92">
         <f ca="1">W14+1</f>
         <v>46320</v>
       </c>
-      <c r="D16" s="91"/>
+      <c r="D16" s="93"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
@@ -4417,10 +4493,10 @@
       <c r="AE16" s="7"/>
       <c r="AF16" s="42"/>
     </row>
-    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
-      <c r="C17" s="90"/>
-      <c r="D17" s="91"/>
+      <c r="C17" s="92"/>
+      <c r="D17" s="93"/>
       <c r="E17" s="94">
         <f ca="1">C16+1</f>
         <v>46321</v>
@@ -4467,51 +4543,59 @@
       <c r="AD17" s="95"/>
       <c r="AF17" s="4"/>
     </row>
-    <row r="18" spans="1:42" s="43" customFormat="1" ht="149.69999999999999" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:42" s="43" customFormat="1" ht="149.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="42"/>
-      <c r="C18" s="105"/>
-      <c r="D18" s="106"/>
-      <c r="E18" s="105" t="s">
-        <v>33</v>
-      </c>
-      <c r="F18" s="106"/>
-      <c r="G18" s="105"/>
-      <c r="H18" s="106"/>
-      <c r="I18" s="105"/>
-      <c r="J18" s="106"/>
-      <c r="K18" s="107" t="s">
-        <v>37</v>
-      </c>
-      <c r="L18" s="108"/>
-      <c r="M18" s="108"/>
+      <c r="C18" s="163" t="s">
+        <v>61</v>
+      </c>
+      <c r="D18" s="164"/>
+      <c r="E18" s="83" t="s">
+        <v>45</v>
+      </c>
+      <c r="F18" s="85"/>
+      <c r="G18" s="163" t="s">
+        <v>46</v>
+      </c>
+      <c r="H18" s="164"/>
+      <c r="I18" s="163" t="s">
+        <v>52</v>
+      </c>
+      <c r="J18" s="164"/>
+      <c r="K18" s="91" t="s">
+        <v>35</v>
+      </c>
+      <c r="L18" s="84"/>
+      <c r="M18" s="84"/>
       <c r="N18" s="82"/>
-      <c r="O18" s="105"/>
-      <c r="P18" s="108"/>
-      <c r="Q18" s="108"/>
-      <c r="R18" s="108"/>
-      <c r="S18" s="108"/>
-      <c r="T18" s="108"/>
-      <c r="U18" s="108"/>
-      <c r="V18" s="106"/>
-      <c r="W18" s="105"/>
-      <c r="X18" s="108"/>
-      <c r="Y18" s="108"/>
-      <c r="Z18" s="108"/>
-      <c r="AA18" s="108"/>
-      <c r="AB18" s="108"/>
-      <c r="AC18" s="108"/>
-      <c r="AD18" s="106"/>
+      <c r="O18" s="163" t="s">
+        <v>53</v>
+      </c>
+      <c r="P18" s="165"/>
+      <c r="Q18" s="165"/>
+      <c r="R18" s="165"/>
+      <c r="S18" s="165"/>
+      <c r="T18" s="165"/>
+      <c r="U18" s="165"/>
+      <c r="V18" s="164"/>
+      <c r="W18" s="83"/>
+      <c r="X18" s="84"/>
+      <c r="Y18" s="84"/>
+      <c r="Z18" s="84"/>
+      <c r="AA18" s="84"/>
+      <c r="AB18" s="84"/>
+      <c r="AC18" s="84"/>
+      <c r="AD18" s="85"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
-    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="42"/>
-      <c r="C19" s="90">
+      <c r="C19" s="92">
         <f ca="1">W17+1</f>
         <v>46327</v>
       </c>
-      <c r="D19" s="91"/>
+      <c r="D19" s="93"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
@@ -4541,10 +4625,10 @@
       <c r="AE19" s="7"/>
       <c r="AF19" s="42"/>
     </row>
-    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="91"/>
+      <c r="C20" s="92"/>
+      <c r="D20" s="93"/>
       <c r="E20" s="94">
         <f ca="1">C19+1</f>
         <v>46328</v>
@@ -4591,41 +4675,41 @@
       <c r="AD20" s="95"/>
       <c r="AF20" s="4"/>
     </row>
-    <row r="21" spans="1:42" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:42" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="42"/>
-      <c r="C21" s="83"/>
-      <c r="D21" s="85"/>
-      <c r="E21" s="83"/>
-      <c r="F21" s="85"/>
-      <c r="G21" s="83"/>
-      <c r="H21" s="85"/>
-      <c r="I21" s="83"/>
-      <c r="J21" s="85"/>
-      <c r="K21" s="83"/>
-      <c r="L21" s="84"/>
-      <c r="M21" s="84"/>
+      <c r="C21" s="97"/>
+      <c r="D21" s="98"/>
+      <c r="E21" s="97"/>
+      <c r="F21" s="98"/>
+      <c r="G21" s="97"/>
+      <c r="H21" s="98"/>
+      <c r="I21" s="97"/>
+      <c r="J21" s="98"/>
+      <c r="K21" s="97"/>
+      <c r="L21" s="143"/>
+      <c r="M21" s="143"/>
       <c r="N21" s="44"/>
-      <c r="O21" s="83"/>
-      <c r="P21" s="84"/>
-      <c r="Q21" s="84"/>
-      <c r="R21" s="84"/>
-      <c r="S21" s="84"/>
-      <c r="T21" s="84"/>
-      <c r="U21" s="84"/>
-      <c r="V21" s="85"/>
-      <c r="W21" s="83"/>
-      <c r="X21" s="84"/>
-      <c r="Y21" s="84"/>
-      <c r="Z21" s="84"/>
-      <c r="AA21" s="84"/>
-      <c r="AB21" s="84"/>
-      <c r="AC21" s="84"/>
-      <c r="AD21" s="85"/>
+      <c r="O21" s="97"/>
+      <c r="P21" s="143"/>
+      <c r="Q21" s="143"/>
+      <c r="R21" s="143"/>
+      <c r="S21" s="143"/>
+      <c r="T21" s="143"/>
+      <c r="U21" s="143"/>
+      <c r="V21" s="98"/>
+      <c r="W21" s="97"/>
+      <c r="X21" s="143"/>
+      <c r="Y21" s="143"/>
+      <c r="Z21" s="143"/>
+      <c r="AA21" s="143"/>
+      <c r="AB21" s="143"/>
+      <c r="AC21" s="143"/>
+      <c r="AD21" s="98"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
     </row>
-    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52"/>
@@ -4657,7 +4741,7 @@
       <c r="AD22" s="55"/>
       <c r="AF22" s="4"/>
     </row>
-    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="56"/>
@@ -4691,12 +4775,12 @@
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
     </row>
-    <row r="24" spans="1:42" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:42" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="M24" s="1"/>
       <c r="AF24" s="1"/>
     </row>
-    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="C25" s="86" t="s">
         <v>0</v>
@@ -4735,7 +4819,7 @@
       <c r="AD25" s="87"/>
       <c r="AF25" s="1"/>
     </row>
-    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="C26" s="86"/>
       <c r="D26" s="86"/>
@@ -4808,7 +4892,7 @@
       </c>
       <c r="AF26" s="1"/>
     </row>
-    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="C27" s="88"/>
       <c r="D27" s="88"/>
@@ -4880,7 +4964,7 @@
       </c>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="C28" s="89"/>
       <c r="D28" s="89"/>
@@ -4952,7 +5036,7 @@
       </c>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="C29" s="88"/>
       <c r="D29" s="88"/>
@@ -5024,7 +5108,7 @@
       </c>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="C30" s="89"/>
       <c r="D30" s="89"/>
@@ -5096,7 +5180,7 @@
       </c>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="C31" s="88"/>
       <c r="D31" s="88"/>
@@ -5168,7 +5252,7 @@
       </c>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="M32" s="1"/>
       <c r="O32" s="64" t="str">
@@ -5231,7 +5315,7 @@
       </c>
       <c r="AF32" s="1"/>
     </row>
-    <row r="33" spans="1:32" ht="13.2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="M33" s="1"/>
       <c r="O33" s="64"/>
@@ -5252,7 +5336,7 @@
       <c r="AD33" s="65"/>
       <c r="AF33" s="1"/>
     </row>
-    <row r="34" spans="1:32" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -5286,10 +5370,10 @@
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
     </row>
-    <row r="38" spans="1:32" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:32" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D39" s="115" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E39" s="116"/>
       <c r="F39" s="117"/>
@@ -5299,16 +5383,16 @@
       </c>
       <c r="H39" s="122"/>
       <c r="I39" s="115" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J39" s="125"/>
       <c r="K39" s="127" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L39" s="128"/>
       <c r="M39" s="131">
         <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
-        <v>5.0000000000000009</v>
+        <v>3.9999999999999982</v>
       </c>
       <c r="N39" s="132"/>
       <c r="O39" s="132"/>
@@ -5316,7 +5400,7 @@
       <c r="Q39" s="132"/>
       <c r="R39" s="133"/>
       <c r="S39" s="137" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T39" s="138"/>
       <c r="U39" s="138"/>
@@ -5324,7 +5408,7 @@
       <c r="W39" s="138"/>
       <c r="X39" s="139"/>
     </row>
-    <row r="40" spans="1:32" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:32" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D40" s="118"/>
       <c r="E40" s="119"/>
       <c r="F40" s="120"/>
@@ -5497,25 +5581,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AP39"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="13.8" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="5.5546875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="5.5546875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="5.5546875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.5546875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="5.5546875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="15.5546875" style="3" customWidth="1"/>
-    <col min="11" max="14" width="5.5546875" style="3" customWidth="1"/>
-    <col min="15" max="30" width="2.5546875" style="3" customWidth="1"/>
-    <col min="31" max="32" width="5.5546875" style="3" customWidth="1"/>
-    <col min="33" max="33" width="17.109375" style="3" customWidth="1"/>
-    <col min="34" max="34" width="10.44140625" style="3" customWidth="1"/>
-    <col min="35" max="16384" width="8.6640625" style="3"/>
+    <col min="1" max="3" width="5.5703125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="5.5703125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="5.5703125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="5.5703125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="3" customWidth="1"/>
+    <col min="11" max="14" width="5.5703125" style="3" customWidth="1"/>
+    <col min="15" max="30" width="2.5703125" style="3" customWidth="1"/>
+    <col min="31" max="32" width="5.5703125" style="3" customWidth="1"/>
+    <col min="33" max="33" width="17.140625" style="3" customWidth="1"/>
+    <col min="34" max="34" width="10.42578125" style="3" customWidth="1"/>
+    <col min="35" max="16384" width="8.7109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5549,42 +5633,42 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A2" s="29"/>
-      <c r="C2" s="112">
+      <c r="C2" s="113">
         <f ca="1">DATE(About!P8,11,1)</f>
         <v>46327</v>
       </c>
-      <c r="D2" s="112"/>
-      <c r="E2" s="112"/>
-      <c r="F2" s="112"/>
-      <c r="G2" s="112"/>
-      <c r="H2" s="112"/>
-      <c r="I2" s="112"/>
-      <c r="J2" s="112"/>
-      <c r="K2" s="112"/>
-      <c r="L2" s="112"/>
-      <c r="M2" s="112"/>
-      <c r="N2" s="112"/>
-      <c r="O2" s="112"/>
-      <c r="P2" s="112"/>
-      <c r="Q2" s="112"/>
-      <c r="R2" s="112"/>
-      <c r="S2" s="112"/>
-      <c r="T2" s="112"/>
-      <c r="U2" s="112"/>
-      <c r="V2" s="112"/>
-      <c r="W2" s="112"/>
-      <c r="X2" s="112"/>
-      <c r="Y2" s="112"/>
-      <c r="Z2" s="112"/>
-      <c r="AA2" s="112"/>
-      <c r="AB2" s="112"/>
-      <c r="AC2" s="112"/>
-      <c r="AD2" s="112"/>
+      <c r="D2" s="113"/>
+      <c r="E2" s="113"/>
+      <c r="F2" s="113"/>
+      <c r="G2" s="113"/>
+      <c r="H2" s="113"/>
+      <c r="I2" s="113"/>
+      <c r="J2" s="113"/>
+      <c r="K2" s="113"/>
+      <c r="L2" s="113"/>
+      <c r="M2" s="113"/>
+      <c r="N2" s="113"/>
+      <c r="O2" s="113"/>
+      <c r="P2" s="113"/>
+      <c r="Q2" s="113"/>
+      <c r="R2" s="113"/>
+      <c r="S2" s="113"/>
+      <c r="T2" s="113"/>
+      <c r="U2" s="113"/>
+      <c r="V2" s="113"/>
+      <c r="W2" s="113"/>
+      <c r="X2" s="113"/>
+      <c r="Y2" s="113"/>
+      <c r="Z2" s="113"/>
+      <c r="AA2" s="113"/>
+      <c r="AB2" s="113"/>
+      <c r="AC2" s="113"/>
+      <c r="AD2" s="113"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="1.1000000000000001">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -5604,290 +5688,296 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="35"/>
-      <c r="C4" s="113">
+      <c r="C4" s="114">
         <f ca="1">C5</f>
         <v>46327</v>
       </c>
-      <c r="D4" s="113"/>
-      <c r="E4" s="113">
+      <c r="D4" s="114"/>
+      <c r="E4" s="114">
         <f ca="1">E5</f>
         <v>46328</v>
       </c>
-      <c r="F4" s="113"/>
-      <c r="G4" s="113">
+      <c r="F4" s="114"/>
+      <c r="G4" s="114">
         <f ca="1">G5</f>
         <v>46329</v>
       </c>
-      <c r="H4" s="113"/>
-      <c r="I4" s="113">
+      <c r="H4" s="114"/>
+      <c r="I4" s="114">
         <f ca="1">I5</f>
         <v>46330</v>
       </c>
-      <c r="J4" s="113"/>
-      <c r="K4" s="113">
+      <c r="J4" s="114"/>
+      <c r="K4" s="114">
         <f ca="1">K5</f>
         <v>46331</v>
       </c>
-      <c r="L4" s="113"/>
-      <c r="M4" s="113"/>
+      <c r="L4" s="114"/>
+      <c r="M4" s="114"/>
       <c r="N4" s="37"/>
-      <c r="O4" s="113">
+      <c r="O4" s="114">
         <f ca="1">O5</f>
         <v>46332</v>
       </c>
-      <c r="P4" s="113"/>
-      <c r="Q4" s="113"/>
-      <c r="R4" s="113"/>
-      <c r="S4" s="113"/>
-      <c r="T4" s="113"/>
-      <c r="U4" s="113"/>
-      <c r="V4" s="113"/>
-      <c r="W4" s="113">
+      <c r="P4" s="114"/>
+      <c r="Q4" s="114"/>
+      <c r="R4" s="114"/>
+      <c r="S4" s="114"/>
+      <c r="T4" s="114"/>
+      <c r="U4" s="114"/>
+      <c r="V4" s="114"/>
+      <c r="W4" s="114">
         <f ca="1">W5</f>
         <v>46333</v>
       </c>
-      <c r="X4" s="113"/>
-      <c r="Y4" s="113"/>
-      <c r="Z4" s="113"/>
-      <c r="AA4" s="113"/>
-      <c r="AB4" s="113"/>
-      <c r="AC4" s="113"/>
-      <c r="AD4" s="113"/>
+      <c r="X4" s="114"/>
+      <c r="Y4" s="114"/>
+      <c r="Z4" s="114"/>
+      <c r="AA4" s="114"/>
+      <c r="AB4" s="114"/>
+      <c r="AC4" s="114"/>
+      <c r="AD4" s="114"/>
       <c r="AF4" s="38"/>
       <c r="AG4" s="39"/>
       <c r="AH4" s="39"/>
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="C5" s="90">
+      <c r="C5" s="92">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46327</v>
       </c>
-      <c r="D5" s="91"/>
-      <c r="E5" s="90">
+      <c r="D5" s="93"/>
+      <c r="E5" s="92">
         <f ca="1">C5+1</f>
         <v>46328</v>
       </c>
-      <c r="F5" s="91"/>
-      <c r="G5" s="90">
+      <c r="F5" s="93"/>
+      <c r="G5" s="92">
         <f ca="1">E5+1</f>
         <v>46329</v>
       </c>
-      <c r="H5" s="91"/>
-      <c r="I5" s="90">
+      <c r="H5" s="93"/>
+      <c r="I5" s="92">
         <f ca="1">G5+1</f>
         <v>46330</v>
       </c>
-      <c r="J5" s="91"/>
-      <c r="K5" s="90">
+      <c r="J5" s="93"/>
+      <c r="K5" s="92">
         <f ca="1">I5+1</f>
         <v>46331</v>
       </c>
-      <c r="L5" s="114"/>
-      <c r="M5" s="114"/>
+      <c r="L5" s="112"/>
+      <c r="M5" s="112"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="90">
+      <c r="O5" s="92">
         <f ca="1">K5+1</f>
         <v>46332</v>
       </c>
-      <c r="P5" s="114"/>
-      <c r="Q5" s="114"/>
-      <c r="R5" s="114"/>
-      <c r="S5" s="114"/>
-      <c r="T5" s="114"/>
-      <c r="U5" s="114"/>
-      <c r="V5" s="91"/>
-      <c r="W5" s="90">
+      <c r="P5" s="112"/>
+      <c r="Q5" s="112"/>
+      <c r="R5" s="112"/>
+      <c r="S5" s="112"/>
+      <c r="T5" s="112"/>
+      <c r="U5" s="112"/>
+      <c r="V5" s="93"/>
+      <c r="W5" s="92">
         <f ca="1">O5+1</f>
         <v>46333</v>
       </c>
-      <c r="X5" s="114"/>
-      <c r="Y5" s="114"/>
-      <c r="Z5" s="114"/>
-      <c r="AA5" s="114"/>
-      <c r="AB5" s="114"/>
-      <c r="AC5" s="114"/>
-      <c r="AD5" s="91"/>
+      <c r="X5" s="112"/>
+      <c r="Y5" s="112"/>
+      <c r="Z5" s="112"/>
+      <c r="AA5" s="112"/>
+      <c r="AB5" s="112"/>
+      <c r="AC5" s="112"/>
+      <c r="AD5" s="93"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
       <c r="AI5" s="41"/>
       <c r="AJ5" s="41"/>
     </row>
-    <row r="6" spans="1:36" s="43" customFormat="1" ht="133.80000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:36" s="43" customFormat="1" ht="133.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="42"/>
-      <c r="C6" s="105"/>
-      <c r="D6" s="106"/>
-      <c r="E6" s="107" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" s="106"/>
-      <c r="G6" s="105"/>
-      <c r="H6" s="106"/>
-      <c r="I6" s="105"/>
-      <c r="J6" s="106"/>
-      <c r="K6" s="105"/>
-      <c r="L6" s="108"/>
-      <c r="M6" s="108"/>
-      <c r="N6" s="106"/>
-      <c r="O6" s="107" t="s">
-        <v>39</v>
-      </c>
-      <c r="P6" s="108"/>
-      <c r="Q6" s="108"/>
-      <c r="R6" s="108"/>
-      <c r="S6" s="108"/>
-      <c r="T6" s="108"/>
-      <c r="U6" s="108"/>
-      <c r="V6" s="106"/>
-      <c r="W6" s="105"/>
-      <c r="X6" s="108"/>
-      <c r="Y6" s="108"/>
-      <c r="Z6" s="108"/>
-      <c r="AA6" s="108"/>
-      <c r="AB6" s="108"/>
-      <c r="AC6" s="108"/>
-      <c r="AD6" s="106"/>
+      <c r="C6" s="83"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="91" t="s">
+        <v>36</v>
+      </c>
+      <c r="F6" s="85"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="85"/>
+      <c r="I6" s="90" t="s">
+        <v>54</v>
+      </c>
+      <c r="J6" s="85"/>
+      <c r="K6" s="90" t="s">
+        <v>55</v>
+      </c>
+      <c r="L6" s="84"/>
+      <c r="M6" s="84"/>
+      <c r="N6" s="85"/>
+      <c r="O6" s="91" t="s">
+        <v>57</v>
+      </c>
+      <c r="P6" s="84"/>
+      <c r="Q6" s="84"/>
+      <c r="R6" s="84"/>
+      <c r="S6" s="84"/>
+      <c r="T6" s="84"/>
+      <c r="U6" s="84"/>
+      <c r="V6" s="85"/>
+      <c r="W6" s="83"/>
+      <c r="X6" s="84"/>
+      <c r="Y6" s="84"/>
+      <c r="Z6" s="84"/>
+      <c r="AA6" s="84"/>
+      <c r="AB6" s="84"/>
+      <c r="AC6" s="84"/>
+      <c r="AD6" s="85"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
-    <row r="7" spans="1:36" ht="9.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="C7" s="100">
+      <c r="C7" s="155">
         <f ca="1">W5+1</f>
         <v>46334</v>
       </c>
-      <c r="D7" s="101"/>
-      <c r="E7" s="109"/>
-      <c r="F7" s="110"/>
-      <c r="G7" s="109"/>
-      <c r="H7" s="110"/>
-      <c r="I7" s="109"/>
-      <c r="J7" s="110"/>
-      <c r="K7" s="109"/>
-      <c r="L7" s="111"/>
-      <c r="M7" s="111"/>
+      <c r="D7" s="156"/>
+      <c r="E7" s="160"/>
+      <c r="F7" s="161"/>
+      <c r="G7" s="160"/>
+      <c r="H7" s="161"/>
+      <c r="I7" s="160"/>
+      <c r="J7" s="161"/>
+      <c r="K7" s="160"/>
+      <c r="L7" s="162"/>
+      <c r="M7" s="162"/>
       <c r="N7" s="80"/>
-      <c r="O7" s="109"/>
-      <c r="P7" s="111"/>
-      <c r="Q7" s="111"/>
-      <c r="R7" s="111"/>
-      <c r="S7" s="111"/>
-      <c r="T7" s="111"/>
-      <c r="U7" s="111"/>
-      <c r="V7" s="110"/>
-      <c r="W7" s="109"/>
-      <c r="X7" s="111"/>
-      <c r="Y7" s="111"/>
-      <c r="Z7" s="111"/>
-      <c r="AA7" s="111"/>
-      <c r="AB7" s="111"/>
-      <c r="AC7" s="111"/>
-      <c r="AD7" s="110"/>
+      <c r="O7" s="160"/>
+      <c r="P7" s="162"/>
+      <c r="Q7" s="162"/>
+      <c r="R7" s="162"/>
+      <c r="S7" s="162"/>
+      <c r="T7" s="162"/>
+      <c r="U7" s="162"/>
+      <c r="V7" s="161"/>
+      <c r="W7" s="160"/>
+      <c r="X7" s="162"/>
+      <c r="Y7" s="162"/>
+      <c r="Z7" s="162"/>
+      <c r="AA7" s="162"/>
+      <c r="AB7" s="162"/>
+      <c r="AC7" s="162"/>
+      <c r="AD7" s="161"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
-      <c r="C8" s="100"/>
-      <c r="D8" s="101"/>
-      <c r="E8" s="100">
+      <c r="C8" s="155"/>
+      <c r="D8" s="156"/>
+      <c r="E8" s="155">
         <f ca="1">C7+1</f>
         <v>46335</v>
       </c>
-      <c r="F8" s="101"/>
-      <c r="G8" s="100">
+      <c r="F8" s="156"/>
+      <c r="G8" s="155">
         <f ca="1">E8+1</f>
         <v>46336</v>
       </c>
-      <c r="H8" s="101"/>
-      <c r="I8" s="100">
+      <c r="H8" s="156"/>
+      <c r="I8" s="155">
         <f ca="1">G8+1</f>
         <v>46337</v>
       </c>
-      <c r="J8" s="101"/>
-      <c r="K8" s="100">
+      <c r="J8" s="156"/>
+      <c r="K8" s="155">
         <f ca="1">I8+1</f>
         <v>46338</v>
       </c>
-      <c r="L8" s="102"/>
-      <c r="M8" s="102"/>
+      <c r="L8" s="157"/>
+      <c r="M8" s="157"/>
       <c r="N8" s="78"/>
-      <c r="O8" s="100">
+      <c r="O8" s="155">
         <f ca="1">K8+1</f>
         <v>46339</v>
       </c>
-      <c r="P8" s="102"/>
-      <c r="Q8" s="102"/>
-      <c r="R8" s="102"/>
-      <c r="S8" s="102"/>
-      <c r="T8" s="102"/>
-      <c r="U8" s="102"/>
-      <c r="V8" s="101"/>
-      <c r="W8" s="100">
+      <c r="P8" s="157"/>
+      <c r="Q8" s="157"/>
+      <c r="R8" s="157"/>
+      <c r="S8" s="157"/>
+      <c r="T8" s="157"/>
+      <c r="U8" s="157"/>
+      <c r="V8" s="156"/>
+      <c r="W8" s="155">
         <f ca="1">O8+1</f>
         <v>46340</v>
       </c>
-      <c r="X8" s="102"/>
-      <c r="Y8" s="102"/>
-      <c r="Z8" s="102"/>
-      <c r="AA8" s="102"/>
-      <c r="AB8" s="102"/>
-      <c r="AC8" s="102"/>
-      <c r="AD8" s="101"/>
+      <c r="X8" s="157"/>
+      <c r="Y8" s="157"/>
+      <c r="Z8" s="157"/>
+      <c r="AA8" s="157"/>
+      <c r="AB8" s="157"/>
+      <c r="AC8" s="157"/>
+      <c r="AD8" s="156"/>
       <c r="AF8" s="4"/>
     </row>
-    <row r="9" spans="1:36" s="43" customFormat="1" ht="146.4" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:36" s="43" customFormat="1" ht="146.44999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="42"/>
-      <c r="C9" s="105"/>
-      <c r="D9" s="106"/>
-      <c r="E9" s="107" t="s">
-        <v>42</v>
-      </c>
-      <c r="F9" s="106"/>
-      <c r="G9" s="105"/>
-      <c r="H9" s="106"/>
-      <c r="I9" s="105" t="s">
-        <v>41</v>
-      </c>
-      <c r="J9" s="106"/>
-      <c r="K9" s="105" t="s">
-        <v>18</v>
-      </c>
-      <c r="L9" s="108"/>
-      <c r="M9" s="108"/>
-      <c r="N9" s="106"/>
-      <c r="O9" s="103" t="s">
+      <c r="C9" s="83"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="91" t="s">
+        <v>43</v>
+      </c>
+      <c r="F9" s="85"/>
+      <c r="G9" s="90" t="s">
+        <v>56</v>
+      </c>
+      <c r="H9" s="85"/>
+      <c r="I9" s="83" t="s">
+        <v>44</v>
+      </c>
+      <c r="J9" s="85"/>
+      <c r="K9" s="83" t="s">
+        <v>49</v>
+      </c>
+      <c r="L9" s="84"/>
+      <c r="M9" s="84"/>
+      <c r="N9" s="85"/>
+      <c r="O9" s="158" t="s">
         <v>15</v>
       </c>
-      <c r="P9" s="98"/>
-      <c r="Q9" s="98"/>
-      <c r="R9" s="98"/>
-      <c r="S9" s="98"/>
-      <c r="T9" s="98"/>
-      <c r="U9" s="98"/>
-      <c r="V9" s="99"/>
-      <c r="W9" s="97"/>
-      <c r="X9" s="98"/>
-      <c r="Y9" s="98"/>
-      <c r="Z9" s="98"/>
-      <c r="AA9" s="98"/>
-      <c r="AB9" s="98"/>
-      <c r="AC9" s="98"/>
-      <c r="AD9" s="99"/>
+      <c r="P9" s="154"/>
+      <c r="Q9" s="154"/>
+      <c r="R9" s="154"/>
+      <c r="S9" s="154"/>
+      <c r="T9" s="154"/>
+      <c r="U9" s="154"/>
+      <c r="V9" s="105"/>
+      <c r="W9" s="104"/>
+      <c r="X9" s="154"/>
+      <c r="Y9" s="154"/>
+      <c r="Z9" s="154"/>
+      <c r="AA9" s="154"/>
+      <c r="AB9" s="154"/>
+      <c r="AC9" s="154"/>
+      <c r="AD9" s="105"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
-    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="42"/>
-      <c r="C10" s="100">
+      <c r="C10" s="155">
         <f ca="1">W8+1</f>
         <v>46341</v>
       </c>
-      <c r="D10" s="101"/>
+      <c r="D10" s="156"/>
       <c r="E10" s="79"/>
       <c r="F10" s="80"/>
       <c r="G10" s="79"/>
@@ -5917,99 +6007,99 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="42"/>
     </row>
-    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
-      <c r="C11" s="100"/>
-      <c r="D11" s="101"/>
-      <c r="E11" s="100">
+      <c r="C11" s="155"/>
+      <c r="D11" s="156"/>
+      <c r="E11" s="155">
         <f ca="1">C10+1</f>
         <v>46342</v>
       </c>
-      <c r="F11" s="101"/>
-      <c r="G11" s="100">
+      <c r="F11" s="156"/>
+      <c r="G11" s="155">
         <f ca="1">E11+1</f>
         <v>46343</v>
       </c>
-      <c r="H11" s="101"/>
-      <c r="I11" s="100">
+      <c r="H11" s="156"/>
+      <c r="I11" s="155">
         <f ca="1">G11+1</f>
         <v>46344</v>
       </c>
-      <c r="J11" s="101"/>
-      <c r="K11" s="100">
+      <c r="J11" s="156"/>
+      <c r="K11" s="155">
         <f ca="1">I11+1</f>
         <v>46345</v>
       </c>
-      <c r="L11" s="102"/>
-      <c r="M11" s="102"/>
+      <c r="L11" s="157"/>
+      <c r="M11" s="157"/>
       <c r="N11" s="78"/>
-      <c r="O11" s="100">
+      <c r="O11" s="155">
         <f ca="1">K11+1</f>
         <v>46346</v>
       </c>
-      <c r="P11" s="102"/>
-      <c r="Q11" s="102"/>
-      <c r="R11" s="102"/>
-      <c r="S11" s="102"/>
-      <c r="T11" s="102"/>
-      <c r="U11" s="102"/>
-      <c r="V11" s="101"/>
-      <c r="W11" s="100">
+      <c r="P11" s="157"/>
+      <c r="Q11" s="157"/>
+      <c r="R11" s="157"/>
+      <c r="S11" s="157"/>
+      <c r="T11" s="157"/>
+      <c r="U11" s="157"/>
+      <c r="V11" s="156"/>
+      <c r="W11" s="155">
         <f ca="1">O11+1</f>
         <v>46347</v>
       </c>
-      <c r="X11" s="102"/>
-      <c r="Y11" s="102"/>
-      <c r="Z11" s="102"/>
-      <c r="AA11" s="102"/>
-      <c r="AB11" s="102"/>
-      <c r="AC11" s="102"/>
-      <c r="AD11" s="101"/>
+      <c r="X11" s="157"/>
+      <c r="Y11" s="157"/>
+      <c r="Z11" s="157"/>
+      <c r="AA11" s="157"/>
+      <c r="AB11" s="157"/>
+      <c r="AC11" s="157"/>
+      <c r="AD11" s="156"/>
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:36" s="43" customFormat="1" ht="134.69999999999999" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:36" s="43" customFormat="1" ht="134.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="42"/>
-      <c r="C12" s="97"/>
-      <c r="D12" s="99"/>
-      <c r="E12" s="103" t="s">
+      <c r="C12" s="104"/>
+      <c r="D12" s="105"/>
+      <c r="E12" s="158" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="104"/>
-      <c r="G12" s="97"/>
-      <c r="H12" s="99"/>
-      <c r="I12" s="97"/>
-      <c r="J12" s="99"/>
-      <c r="K12" s="97"/>
-      <c r="L12" s="98"/>
-      <c r="M12" s="98"/>
-      <c r="N12" s="99"/>
-      <c r="O12" s="97"/>
-      <c r="P12" s="98"/>
-      <c r="Q12" s="98"/>
-      <c r="R12" s="98"/>
-      <c r="S12" s="98"/>
-      <c r="T12" s="98"/>
-      <c r="U12" s="98"/>
-      <c r="V12" s="99"/>
-      <c r="W12" s="97"/>
-      <c r="X12" s="98"/>
-      <c r="Y12" s="98"/>
-      <c r="Z12" s="98"/>
-      <c r="AA12" s="98"/>
-      <c r="AB12" s="98"/>
-      <c r="AC12" s="98"/>
-      <c r="AD12" s="99"/>
+      <c r="F12" s="159"/>
+      <c r="G12" s="104"/>
+      <c r="H12" s="105"/>
+      <c r="I12" s="104"/>
+      <c r="J12" s="105"/>
+      <c r="K12" s="104"/>
+      <c r="L12" s="154"/>
+      <c r="M12" s="154"/>
+      <c r="N12" s="105"/>
+      <c r="O12" s="104"/>
+      <c r="P12" s="154"/>
+      <c r="Q12" s="154"/>
+      <c r="R12" s="154"/>
+      <c r="S12" s="154"/>
+      <c r="T12" s="154"/>
+      <c r="U12" s="154"/>
+      <c r="V12" s="105"/>
+      <c r="W12" s="104"/>
+      <c r="X12" s="154"/>
+      <c r="Y12" s="154"/>
+      <c r="Z12" s="154"/>
+      <c r="AA12" s="154"/>
+      <c r="AB12" s="154"/>
+      <c r="AC12" s="154"/>
+      <c r="AD12" s="105"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
-    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="42"/>
-      <c r="C13" s="100">
+      <c r="C13" s="155">
         <f ca="1">W11+1</f>
         <v>46348</v>
       </c>
-      <c r="D13" s="101"/>
+      <c r="D13" s="156"/>
       <c r="E13" s="79"/>
       <c r="F13" s="80"/>
       <c r="G13" s="79"/>
@@ -6039,102 +6129,102 @@
       <c r="AE13" s="7"/>
       <c r="AF13" s="42"/>
     </row>
-    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4"/>
-      <c r="C14" s="100"/>
-      <c r="D14" s="101"/>
-      <c r="E14" s="100">
+      <c r="C14" s="155"/>
+      <c r="D14" s="156"/>
+      <c r="E14" s="155">
         <f ca="1">C13+1</f>
         <v>46349</v>
       </c>
-      <c r="F14" s="101"/>
-      <c r="G14" s="100">
+      <c r="F14" s="156"/>
+      <c r="G14" s="155">
         <f ca="1">E14+1</f>
         <v>46350</v>
       </c>
-      <c r="H14" s="101"/>
-      <c r="I14" s="100">
+      <c r="H14" s="156"/>
+      <c r="I14" s="155">
         <f ca="1">G14+1</f>
         <v>46351</v>
       </c>
-      <c r="J14" s="101"/>
-      <c r="K14" s="100">
+      <c r="J14" s="156"/>
+      <c r="K14" s="155">
         <f ca="1">I14+1</f>
         <v>46352</v>
       </c>
-      <c r="L14" s="102"/>
-      <c r="M14" s="102"/>
+      <c r="L14" s="157"/>
+      <c r="M14" s="157"/>
       <c r="N14" s="78"/>
-      <c r="O14" s="100">
+      <c r="O14" s="155">
         <f ca="1">K14+1</f>
         <v>46353</v>
       </c>
-      <c r="P14" s="102"/>
-      <c r="Q14" s="102"/>
-      <c r="R14" s="102"/>
-      <c r="S14" s="102"/>
-      <c r="T14" s="102"/>
-      <c r="U14" s="102"/>
-      <c r="V14" s="101"/>
-      <c r="W14" s="100">
+      <c r="P14" s="157"/>
+      <c r="Q14" s="157"/>
+      <c r="R14" s="157"/>
+      <c r="S14" s="157"/>
+      <c r="T14" s="157"/>
+      <c r="U14" s="157"/>
+      <c r="V14" s="156"/>
+      <c r="W14" s="155">
         <f ca="1">O14+1</f>
         <v>46354</v>
       </c>
-      <c r="X14" s="102"/>
-      <c r="Y14" s="102"/>
-      <c r="Z14" s="102"/>
-      <c r="AA14" s="102"/>
-      <c r="AB14" s="102"/>
-      <c r="AC14" s="102"/>
-      <c r="AD14" s="101"/>
+      <c r="X14" s="157"/>
+      <c r="Y14" s="157"/>
+      <c r="Z14" s="157"/>
+      <c r="AA14" s="157"/>
+      <c r="AB14" s="157"/>
+      <c r="AC14" s="157"/>
+      <c r="AD14" s="156"/>
       <c r="AF14" s="4"/>
     </row>
-    <row r="15" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="42"/>
-      <c r="C15" s="97"/>
-      <c r="D15" s="99"/>
-      <c r="E15" s="97"/>
-      <c r="F15" s="99"/>
-      <c r="G15" s="97"/>
-      <c r="H15" s="99"/>
-      <c r="I15" s="97"/>
-      <c r="J15" s="99"/>
-      <c r="K15" s="97"/>
-      <c r="L15" s="98"/>
-      <c r="M15" s="98"/>
-      <c r="N15" s="99"/>
-      <c r="O15" s="97"/>
-      <c r="P15" s="98"/>
-      <c r="Q15" s="98"/>
-      <c r="R15" s="98"/>
-      <c r="S15" s="98"/>
-      <c r="T15" s="98"/>
-      <c r="U15" s="98"/>
-      <c r="V15" s="99"/>
-      <c r="W15" s="97"/>
-      <c r="X15" s="98"/>
-      <c r="Y15" s="98"/>
-      <c r="Z15" s="98"/>
-      <c r="AA15" s="98"/>
-      <c r="AB15" s="98"/>
-      <c r="AC15" s="98"/>
-      <c r="AD15" s="99"/>
+      <c r="C15" s="104"/>
+      <c r="D15" s="105"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="104"/>
+      <c r="H15" s="105"/>
+      <c r="I15" s="104"/>
+      <c r="J15" s="105"/>
+      <c r="K15" s="104"/>
+      <c r="L15" s="154"/>
+      <c r="M15" s="154"/>
+      <c r="N15" s="105"/>
+      <c r="O15" s="104"/>
+      <c r="P15" s="154"/>
+      <c r="Q15" s="154"/>
+      <c r="R15" s="154"/>
+      <c r="S15" s="154"/>
+      <c r="T15" s="154"/>
+      <c r="U15" s="154"/>
+      <c r="V15" s="105"/>
+      <c r="W15" s="104"/>
+      <c r="X15" s="154"/>
+      <c r="Y15" s="154"/>
+      <c r="Z15" s="154"/>
+      <c r="AA15" s="154"/>
+      <c r="AB15" s="154"/>
+      <c r="AC15" s="154"/>
+      <c r="AD15" s="105"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
-    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="42"/>
-      <c r="C16" s="90">
+      <c r="C16" s="92">
         <f ca="1">W14+1</f>
         <v>46355</v>
       </c>
-      <c r="D16" s="91"/>
+      <c r="D16" s="93"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
       <c r="H16" s="75"/>
-      <c r="I16" s="92"/>
-      <c r="J16" s="93"/>
+      <c r="I16" s="145"/>
+      <c r="J16" s="146"/>
       <c r="K16" s="66"/>
       <c r="L16" s="68"/>
       <c r="M16" s="68"/>
@@ -6158,34 +6248,35 @@
       <c r="AE16" s="7"/>
       <c r="AF16" s="42"/>
     </row>
-    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
-      <c r="C17" s="90"/>
-      <c r="D17" s="91"/>
+      <c r="C17" s="92"/>
+      <c r="D17" s="93"/>
       <c r="E17" s="94">
         <f ca="1">C16+1</f>
         <v>46356</v>
       </c>
       <c r="F17" s="95"/>
       <c r="G17" s="94">
-        <v>1</v>
+        <f ca="1">E17+1</f>
+        <v>46357</v>
       </c>
       <c r="H17" s="95"/>
       <c r="I17" s="94">
-        <f>G17+1</f>
-        <v>2</v>
+        <f ca="1">G17+1</f>
+        <v>46358</v>
       </c>
       <c r="J17" s="95"/>
       <c r="K17" s="94">
-        <f>I17+1</f>
-        <v>3</v>
+        <f ca="1">I17+1</f>
+        <v>46359</v>
       </c>
       <c r="L17" s="96"/>
       <c r="M17" s="96"/>
       <c r="N17" s="95"/>
       <c r="O17" s="94">
-        <f>K17+1</f>
-        <v>4</v>
+        <f ca="1">K17+1</f>
+        <v>46360</v>
       </c>
       <c r="P17" s="96"/>
       <c r="Q17" s="96"/>
@@ -6195,8 +6286,8 @@
       <c r="U17" s="96"/>
       <c r="V17" s="95"/>
       <c r="W17" s="94">
-        <f>O17+1</f>
-        <v>5</v>
+        <f ca="1">O17+1</f>
+        <v>46361</v>
       </c>
       <c r="X17" s="96"/>
       <c r="Y17" s="96"/>
@@ -6207,53 +6298,53 @@
       <c r="AD17" s="95"/>
       <c r="AF17" s="4"/>
     </row>
-    <row r="18" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="42"/>
-      <c r="C18" s="83"/>
-      <c r="D18" s="85"/>
-      <c r="E18" s="83"/>
-      <c r="F18" s="85"/>
-      <c r="G18" s="83"/>
-      <c r="H18" s="85"/>
-      <c r="I18" s="83"/>
-      <c r="J18" s="85"/>
-      <c r="K18" s="83"/>
-      <c r="L18" s="84"/>
-      <c r="M18" s="84"/>
-      <c r="N18" s="85"/>
-      <c r="O18" s="83"/>
-      <c r="P18" s="84"/>
-      <c r="Q18" s="84"/>
-      <c r="R18" s="84"/>
-      <c r="S18" s="84"/>
-      <c r="T18" s="84"/>
-      <c r="U18" s="84"/>
-      <c r="V18" s="85"/>
-      <c r="W18" s="83"/>
-      <c r="X18" s="84"/>
-      <c r="Y18" s="84"/>
-      <c r="Z18" s="84"/>
-      <c r="AA18" s="84"/>
-      <c r="AB18" s="84"/>
-      <c r="AC18" s="84"/>
-      <c r="AD18" s="85"/>
+      <c r="C18" s="97"/>
+      <c r="D18" s="98"/>
+      <c r="E18" s="97"/>
+      <c r="F18" s="98"/>
+      <c r="G18" s="97"/>
+      <c r="H18" s="98"/>
+      <c r="I18" s="97"/>
+      <c r="J18" s="98"/>
+      <c r="K18" s="97"/>
+      <c r="L18" s="143"/>
+      <c r="M18" s="143"/>
+      <c r="N18" s="98"/>
+      <c r="O18" s="97"/>
+      <c r="P18" s="143"/>
+      <c r="Q18" s="143"/>
+      <c r="R18" s="143"/>
+      <c r="S18" s="143"/>
+      <c r="T18" s="143"/>
+      <c r="U18" s="143"/>
+      <c r="V18" s="98"/>
+      <c r="W18" s="97"/>
+      <c r="X18" s="143"/>
+      <c r="Y18" s="143"/>
+      <c r="Z18" s="143"/>
+      <c r="AA18" s="143"/>
+      <c r="AB18" s="143"/>
+      <c r="AC18" s="143"/>
+      <c r="AD18" s="98"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
-    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="42"/>
-      <c r="C19" s="90">
-        <f>W17+1</f>
-        <v>6</v>
-      </c>
-      <c r="D19" s="91"/>
+      <c r="C19" s="92">
+        <f ca="1">W17+1</f>
+        <v>46362</v>
+      </c>
+      <c r="D19" s="93"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
       <c r="H19" s="75"/>
-      <c r="I19" s="92"/>
-      <c r="J19" s="93"/>
+      <c r="I19" s="145"/>
+      <c r="J19" s="146"/>
       <c r="K19" s="66"/>
       <c r="L19" s="68"/>
       <c r="M19" s="68"/>
@@ -6277,35 +6368,35 @@
       <c r="AE19" s="7"/>
       <c r="AF19" s="42"/>
     </row>
-    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
-      <c r="C20" s="90"/>
-      <c r="D20" s="91"/>
+      <c r="C20" s="92"/>
+      <c r="D20" s="93"/>
       <c r="E20" s="94">
-        <f>C19+1</f>
-        <v>7</v>
+        <f ca="1">C19+1</f>
+        <v>46363</v>
       </c>
       <c r="F20" s="95"/>
       <c r="G20" s="94">
-        <f>E20+1</f>
-        <v>8</v>
+        <f ca="1">E20+1</f>
+        <v>46364</v>
       </c>
       <c r="H20" s="95"/>
       <c r="I20" s="94">
-        <f>G20+1</f>
-        <v>9</v>
+        <f ca="1">G20+1</f>
+        <v>46365</v>
       </c>
       <c r="J20" s="95"/>
       <c r="K20" s="94">
-        <f>I20+1</f>
-        <v>10</v>
+        <f ca="1">I20+1</f>
+        <v>46366</v>
       </c>
       <c r="L20" s="96"/>
       <c r="M20" s="96"/>
       <c r="N20" s="95"/>
       <c r="O20" s="94">
-        <f>K20+1</f>
-        <v>11</v>
+        <f ca="1">K20+1</f>
+        <v>46367</v>
       </c>
       <c r="P20" s="96"/>
       <c r="Q20" s="96"/>
@@ -6315,8 +6406,8 @@
       <c r="U20" s="96"/>
       <c r="V20" s="95"/>
       <c r="W20" s="94">
-        <f>O20+1</f>
-        <v>12</v>
+        <f ca="1">O20+1</f>
+        <v>46368</v>
       </c>
       <c r="X20" s="96"/>
       <c r="Y20" s="96"/>
@@ -6327,41 +6418,41 @@
       <c r="AD20" s="95"/>
       <c r="AF20" s="4"/>
     </row>
-    <row r="21" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="42"/>
-      <c r="C21" s="83"/>
-      <c r="D21" s="85"/>
-      <c r="E21" s="83"/>
-      <c r="F21" s="85"/>
-      <c r="G21" s="83"/>
-      <c r="H21" s="85"/>
-      <c r="I21" s="83"/>
-      <c r="J21" s="85"/>
-      <c r="K21" s="83"/>
-      <c r="L21" s="84"/>
-      <c r="M21" s="84"/>
-      <c r="N21" s="85"/>
-      <c r="O21" s="83"/>
-      <c r="P21" s="84"/>
-      <c r="Q21" s="84"/>
-      <c r="R21" s="84"/>
-      <c r="S21" s="84"/>
-      <c r="T21" s="84"/>
-      <c r="U21" s="84"/>
-      <c r="V21" s="85"/>
-      <c r="W21" s="83"/>
-      <c r="X21" s="84"/>
-      <c r="Y21" s="84"/>
-      <c r="Z21" s="84"/>
-      <c r="AA21" s="84"/>
-      <c r="AB21" s="84"/>
-      <c r="AC21" s="84"/>
-      <c r="AD21" s="85"/>
+      <c r="C21" s="97"/>
+      <c r="D21" s="98"/>
+      <c r="E21" s="97"/>
+      <c r="F21" s="98"/>
+      <c r="G21" s="97"/>
+      <c r="H21" s="98"/>
+      <c r="I21" s="97"/>
+      <c r="J21" s="98"/>
+      <c r="K21" s="97"/>
+      <c r="L21" s="143"/>
+      <c r="M21" s="143"/>
+      <c r="N21" s="98"/>
+      <c r="O21" s="97"/>
+      <c r="P21" s="143"/>
+      <c r="Q21" s="143"/>
+      <c r="R21" s="143"/>
+      <c r="S21" s="143"/>
+      <c r="T21" s="143"/>
+      <c r="U21" s="143"/>
+      <c r="V21" s="98"/>
+      <c r="W21" s="97"/>
+      <c r="X21" s="143"/>
+      <c r="Y21" s="143"/>
+      <c r="Z21" s="143"/>
+      <c r="AA21" s="143"/>
+      <c r="AB21" s="143"/>
+      <c r="AC21" s="143"/>
+      <c r="AD21" s="98"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
     </row>
-    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52"/>
@@ -6393,7 +6484,7 @@
       <c r="AD22" s="55"/>
       <c r="AF22" s="4"/>
     </row>
-    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.9" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="56"/>
@@ -6427,12 +6518,12 @@
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
     </row>
-    <row r="24" spans="1:42" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:42" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="M24" s="1"/>
       <c r="AF24" s="1"/>
     </row>
-    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
       <c r="C25" s="86" t="s">
         <v>0</v>
@@ -6471,7 +6562,7 @@
       <c r="AD25" s="87"/>
       <c r="AF25" s="1"/>
     </row>
-    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
       <c r="C26" s="86"/>
       <c r="D26" s="86"/>
@@ -6544,7 +6635,7 @@
       </c>
       <c r="AF26" s="1"/>
     </row>
-    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
       <c r="C27" s="88"/>
       <c r="D27" s="88"/>
@@ -6616,7 +6707,7 @@
       </c>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
       <c r="C28" s="89"/>
       <c r="D28" s="89"/>
@@ -6688,7 +6779,7 @@
       </c>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
       <c r="C29" s="88"/>
       <c r="D29" s="88"/>
@@ -6760,7 +6851,7 @@
       </c>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
       <c r="C30" s="89"/>
       <c r="D30" s="89"/>
@@ -6832,7 +6923,7 @@
       </c>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
       <c r="C31" s="88"/>
       <c r="D31" s="88"/>
@@ -6904,7 +6995,7 @@
       </c>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="C32" s="77"/>
       <c r="D32" s="77"/>
@@ -6976,12 +7067,12 @@
       </c>
       <c r="AF32" s="1"/>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="M33" s="1"/>
       <c r="AF33" s="1"/>
     </row>
-    <row r="34" spans="1:32" ht="24.9" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -7015,10 +7106,10 @@
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
     </row>
-    <row r="37" spans="1:32" ht="14.4" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="38" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:32" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
       <c r="D38" s="115" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E38" s="116"/>
       <c r="F38" s="117"/>
@@ -7028,16 +7119,16 @@
       </c>
       <c r="H38" s="122"/>
       <c r="I38" s="115" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="J38" s="125"/>
       <c r="K38" s="127" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="L38" s="128"/>
       <c r="M38" s="131">
         <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
-        <v>5.0000000000000009</v>
+        <v>3.9999999999999982</v>
       </c>
       <c r="N38" s="132"/>
       <c r="O38" s="132"/>
@@ -7045,7 +7136,7 @@
       <c r="Q38" s="132"/>
       <c r="R38" s="133"/>
       <c r="S38" s="137" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="T38" s="138"/>
       <c r="U38" s="138"/>
@@ -7053,7 +7144,7 @@
       <c r="W38" s="138"/>
       <c r="X38" s="139"/>
     </row>
-    <row r="39" spans="1:32" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:32" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D39" s="118"/>
       <c r="E39" s="119"/>
       <c r="F39" s="120"/>

--- a/Group_milestones.xlsx
+++ b/Group_milestones.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2F1A88-5E4C-4A1B-983F-CCDEB225E021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{6D2F1A88-5E4C-4A1B-983F-CCDEB225E021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C8FCD8C-DF16-42FB-BEAE-93AA2A70C77E}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" tabRatio="824" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="824" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="52" r:id="rId1"/>
@@ -192,33 +192,13 @@
     <t>MCTR1: Carraige v2 design</t>
   </si>
   <si>
-    <t>MCTR1: Carriage v2 build</t>
-  </si>
-  <si>
     <t>EEII1: ICD complete with REII and MCTR2</t>
   </si>
   <si>
     <t>EEII1:Working low voltage switching circuit in thevinin lab(one IGBT +driver +opto)</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">MCTR1: Enclosure final + fit test                    </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="10"/>
-        <color rgb="FF00B0F0"/>
-        <rFont val="Seaford"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
     <t xml:space="preserve"> EEII1: Final Drive circuit complete+DB box wired</t>
-  </si>
-  <si>
-    <t>EEII1: PCB manufactured by MR van Huysteen</t>
   </si>
   <si>
     <t>EERI 324</t>
@@ -233,9 +213,6 @@
     <t>MCTR2: Start with gearbox casing build</t>
   </si>
   <si>
-    <t>EERI321: PRACTICAL 2 submission</t>
-  </si>
-  <si>
     <t>EERI321: Semester T3</t>
   </si>
   <si>
@@ -245,30 +222,10 @@
     <t>REII: I3 begins - ICD_REII drafted &amp; signed off in week 1</t>
   </si>
   <si>
-    <t>EEII 321                 Group: Finalize all ICDs
-REII: ICD_REII signed (v1.0, v1.1 if pins/timings changed)</t>
-  </si>
-  <si>
-    <t>Group: Finish performance test reports and Individual portfolios
-REII: RF/rail test report + individual portfolio</t>
-  </si>
-  <si>
-    <t>Group: First integration test                               EEII1: Testing with PWM of REII in Heavy current lab
-REII: dashboard + dongle + controller link</t>
-  </si>
-  <si>
     <t>REII: participation evidence captured - scope TBD, confirm w/ lecturer (F-08)</t>
   </si>
   <si>
     <t>REII: gate - Controller Spec + ESP32 codebase obtained; board powered (planned, not agreed)</t>
-  </si>
-  <si>
-    <t>MCTR1: Carriage motor drive test, carriage v3 test EEII1:Order heat sinks and power supply(at the latest) MCTR2: Starting with all final draft printing parts
-REII: controller board delivery (estimate, Checkpoint2) - input to ESP32 nRF stub + integration</t>
-  </si>
-  <si>
-    <t>Group: Final touches
-REII: demo dry-run + evidence pack check (planned, not agreed)</t>
   </si>
   <si>
     <t>REII: STM32F411 dongle bring-up (planned, not agreed)
@@ -312,13 +269,60 @@
 · demo run-through capture</t>
   </si>
   <si>
-    <t>EERI 325             Group: Integration successful
-REII: REII integration verified gate (link + dashboard + sway)
-· INTERFACE_MATRIX all-pass or NCRs w/ owners</t>
+    <t>REII: ICD Sec 4 payload freeze w/ MCTR+EEII (planned, not agreed)
+· D-01 byte maps + version byte rule</t>
+  </si>
+  <si>
+    <t>REII: pre-integration (planned, not agreed)
+· isolation bench-verify + HW E-stop path (pre-live drivers)
+· MCTR-I profile format D-04 + encoder handoff</t>
+  </si>
+  <si>
+    <t>EEII1:Order heat sinks and power supply(at the latest) MCTR2: Starting with all final draft printing parts
+REII: controller board delivery (estimate, Checkpoint2) - input to ESP32 nRF stub + integration</t>
+  </si>
+  <si>
+    <t>MCTR1: Carriage v2 build, Carriage motor drive test</t>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">MCTR1: Enclosure v1 test,  ICD complete with- REII, ICD complete with- MCTR2?
+      <t xml:space="preserve">EEII1: PCB manufactured by MR van Huysteen. </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Group: Report on interfaces and test plan</t>
+    </r>
+  </si>
+  <si>
+    <t>MCTR1: Power supply+possible encoders order</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">MCTR1: ICD start with- REII, ICD start with- MCTR2? </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EERI321: PRACTICAL 2 submission</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="2" tint="-0.89999084444715716"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 </t>
     </r>
     <r>
@@ -332,19 +336,177 @@
     </r>
   </si>
   <si>
-    <t>REII: ICD Sec 4 payload freeze w/ MCTR+EEII (planned, not agreed)
-· D-01 byte maps + version byte rule</t>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">Group: Initial integration attempt demo </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="2" tint="-0.89999084444715716"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF00B0F0"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
   </si>
   <si>
-    <t>REII: bench  for 26 Oct (planned, not agreed)
+    <r>
+      <t>REII: bench  for 26 Oct (planned, not agreed).</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="9"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
 · PING-&gt;PONG ch77/2M, 200-pkt smoke CSV
 · 32-B pack/unpack byte-exact loopback
-· else raise NCRs before group test</t>
+· else raise NCRs before group test.           </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> MCTR1: mounting final fit test. </t>
+    </r>
   </si>
   <si>
-    <t>REII: pre-integration (planned, not agreed)
-· isolation bench-verify + HW E-stop path (pre-live drivers)
-· MCTR-I profile format D-04 + encoder handoff</t>
+    <t>EEII1: Testing with PWM of REII in Heavy current lab
+REII: dashboard + dongle + controller link</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">EEII 321 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                Group: Finalize all ICDs
+REII: ICD_REII signed (v1.0, v1.1 if pins/timings changed)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">EERI 325 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Group: Integration successful</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FF7030A0"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+REII: REII integration verified gate (link + dashboard + sway)
+· INTERFACE_MATRIX all-pass or NCRs w/ owners</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Group: Finish performance test reports and Individual portfolios</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="2" tint="-0.89999084444715716"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+REII: RF/rail test report + individual portfolio</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Group: Final touches</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="2" tint="-0.89999084444715716"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+REII: demo dry-run + evidence pack check (planned, not agreed)</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -358,7 +520,7 @@
     <numFmt numFmtId="167" formatCode="mmmm\ yyyy"/>
     <numFmt numFmtId="168" formatCode="dddd"/>
   </numFmts>
-  <fonts count="43" x14ac:knownFonts="1">
+  <fonts count="45" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -634,6 +796,18 @@
       <name val="Seaford"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Seaford"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Seaford"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -862,7 +1036,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="166">
+  <cellXfs count="167">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1090,6 +1264,162 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -1099,244 +1429,91 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="166" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="44" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -1710,19 +1887,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R15"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.71875" defaultRowHeight="15.3" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
-    <col min="1" max="4" width="5.5703125" style="3" customWidth="1"/>
-    <col min="5" max="9" width="10.5703125" style="3" customWidth="1"/>
-    <col min="10" max="11" width="10.5703125" style="28" customWidth="1"/>
-    <col min="12" max="14" width="5.5703125" style="3" customWidth="1"/>
-    <col min="15" max="15" width="25.5703125" style="3" customWidth="1"/>
-    <col min="16" max="16" width="10.5703125" style="3" customWidth="1"/>
-    <col min="17" max="18" width="5.5703125" style="3" customWidth="1"/>
-    <col min="19" max="16384" width="8.7109375" style="3"/>
+    <col min="1" max="4" width="5.5546875" style="3" customWidth="1"/>
+    <col min="5" max="9" width="10.5546875" style="3" customWidth="1"/>
+    <col min="10" max="11" width="10.5546875" style="28" customWidth="1"/>
+    <col min="12" max="14" width="5.5546875" style="3" customWidth="1"/>
+    <col min="15" max="15" width="25.5546875" style="3" customWidth="1"/>
+    <col min="16" max="16" width="10.5546875" style="3" customWidth="1"/>
+    <col min="17" max="18" width="5.5546875" style="3" customWidth="1"/>
+    <col min="19" max="16384" width="8.71875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1742,7 +1919,7 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
     </row>
-    <row r="2" spans="1:18" s="7" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:18" s="7" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A2" s="4"/>
       <c r="B2" s="5"/>
       <c r="C2" s="73" t="s">
@@ -1764,7 +1941,7 @@
       <c r="Q2" s="6"/>
       <c r="R2" s="4"/>
     </row>
-    <row r="3" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.9">
+    <row r="3" spans="1:18" ht="25" customHeight="1" x14ac:dyDescent="2.15">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="8"/>
@@ -1784,7 +1961,7 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A4" s="1"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -1798,15 +1975,15 @@
       <c r="K4" s="12"/>
       <c r="L4" s="11"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="144" t="s">
+      <c r="N4" s="146" t="s">
         <v>10</v>
       </c>
-      <c r="O4" s="144"/>
-      <c r="P4" s="144"/>
-      <c r="Q4" s="144"/>
+      <c r="O4" s="146"/>
+      <c r="P4" s="146"/>
+      <c r="Q4" s="146"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="1"/>
       <c r="B5" s="11"/>
       <c r="C5" s="13" t="s">
@@ -1824,13 +2001,13 @@
       <c r="K5" s="15"/>
       <c r="L5" s="16"/>
       <c r="M5" s="4"/>
-      <c r="N5" s="144"/>
-      <c r="O5" s="144"/>
-      <c r="P5" s="144"/>
-      <c r="Q5" s="144"/>
+      <c r="N5" s="146"/>
+      <c r="O5" s="146"/>
+      <c r="P5" s="146"/>
+      <c r="Q5" s="146"/>
       <c r="R5" s="1"/>
     </row>
-    <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="1"/>
       <c r="B6" s="11"/>
       <c r="C6" s="17"/>
@@ -1844,13 +2021,13 @@
       <c r="K6" s="20"/>
       <c r="L6" s="19"/>
       <c r="M6" s="4"/>
-      <c r="N6" s="144"/>
-      <c r="O6" s="144"/>
-      <c r="P6" s="144"/>
-      <c r="Q6" s="144"/>
+      <c r="N6" s="146"/>
+      <c r="O6" s="146"/>
+      <c r="P6" s="146"/>
+      <c r="Q6" s="146"/>
       <c r="R6" s="1"/>
     </row>
-    <row r="7" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1"/>
       <c r="B7" s="11"/>
       <c r="C7" s="13" t="s">
@@ -1874,7 +2051,7 @@
       <c r="Q7" s="11"/>
       <c r="R7" s="1"/>
     </row>
-    <row r="8" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="1"/>
       <c r="B8" s="11"/>
       <c r="C8" s="17"/>
@@ -1898,7 +2075,7 @@
       </c>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="1"/>
       <c r="B9" s="11"/>
       <c r="C9" s="13" t="s">
@@ -1922,7 +2099,7 @@
       <c r="Q9" s="11"/>
       <c r="R9" s="1"/>
     </row>
-    <row r="10" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="1"/>
       <c r="B10" s="11"/>
       <c r="C10" s="24"/>
@@ -1948,7 +2125,7 @@
       <c r="Q10" s="18"/>
       <c r="R10" s="1"/>
     </row>
-    <row r="11" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="1"/>
       <c r="B11" s="11"/>
       <c r="C11" s="24"/>
@@ -1968,7 +2145,7 @@
       <c r="Q11" s="18"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="1"/>
       <c r="B12" s="11"/>
       <c r="C12" s="13" t="s">
@@ -1992,7 +2169,7 @@
       <c r="Q12" s="18"/>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A13" s="1"/>
       <c r="B13" s="11"/>
       <c r="C13" s="25"/>
@@ -2014,7 +2191,7 @@
       <c r="Q13" s="18"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="1"/>
       <c r="B14" s="11"/>
       <c r="C14" s="18"/>
@@ -2034,7 +2211,7 @@
       <c r="Q14" s="18"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -2069,25 +2246,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AP40"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.71875" defaultRowHeight="12.6" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="3" width="5.5703125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="5.5703125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="5.5703125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="5.5703125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" style="3" customWidth="1"/>
-    <col min="11" max="14" width="5.5703125" style="3" customWidth="1"/>
-    <col min="15" max="30" width="2.5703125" style="3" customWidth="1"/>
-    <col min="31" max="32" width="5.5703125" style="3" customWidth="1"/>
-    <col min="33" max="33" width="17.140625" style="3" customWidth="1"/>
-    <col min="34" max="34" width="10.42578125" style="3" customWidth="1"/>
-    <col min="35" max="16384" width="8.7109375" style="3"/>
+    <col min="1" max="3" width="5.5546875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="5.5546875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="5.5546875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="15.5546875" style="3" customWidth="1"/>
+    <col min="11" max="14" width="5.5546875" style="3" customWidth="1"/>
+    <col min="15" max="30" width="2.5546875" style="3" customWidth="1"/>
+    <col min="31" max="32" width="5.5546875" style="3" customWidth="1"/>
+    <col min="33" max="33" width="17.1640625" style="3" customWidth="1"/>
+    <col min="34" max="34" width="10.44140625" style="3" customWidth="1"/>
+    <col min="35" max="16384" width="8.71875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" ht="25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2121,42 +2298,42 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.9">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="2.15">
       <c r="A2" s="29"/>
-      <c r="C2" s="113">
+      <c r="C2" s="116">
         <f ca="1">DATE(About!P8,9,1)</f>
         <v>46266</v>
       </c>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
-      <c r="P2" s="113"/>
-      <c r="Q2" s="113"/>
-      <c r="R2" s="113"/>
-      <c r="S2" s="113"/>
-      <c r="T2" s="113"/>
-      <c r="U2" s="113"/>
-      <c r="V2" s="113"/>
-      <c r="W2" s="113"/>
-      <c r="X2" s="113"/>
-      <c r="Y2" s="113"/>
-      <c r="Z2" s="113"/>
-      <c r="AA2" s="113"/>
-      <c r="AB2" s="113"/>
-      <c r="AC2" s="113"/>
-      <c r="AD2" s="113"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="116"/>
+      <c r="P2" s="116"/>
+      <c r="Q2" s="116"/>
+      <c r="R2" s="116"/>
+      <c r="S2" s="116"/>
+      <c r="T2" s="116"/>
+      <c r="U2" s="116"/>
+      <c r="V2" s="116"/>
+      <c r="W2" s="116"/>
+      <c r="X2" s="116"/>
+      <c r="Y2" s="116"/>
+      <c r="Z2" s="116"/>
+      <c r="AA2" s="116"/>
+      <c r="AB2" s="116"/>
+      <c r="AC2" s="116"/>
+      <c r="AD2" s="116"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.9">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="2.15">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -2176,280 +2353,280 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A4" s="35"/>
-      <c r="C4" s="114">
+      <c r="C4" s="117">
         <f ca="1">C5</f>
         <v>46264</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114">
+      <c r="D4" s="117"/>
+      <c r="E4" s="117">
         <f ca="1">E5</f>
         <v>46265</v>
       </c>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114">
+      <c r="F4" s="117"/>
+      <c r="G4" s="117">
         <f ca="1">G5</f>
         <v>46266</v>
       </c>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114">
+      <c r="H4" s="117"/>
+      <c r="I4" s="117">
         <f ca="1">I5</f>
         <v>46267</v>
       </c>
-      <c r="J4" s="114"/>
-      <c r="K4" s="114">
+      <c r="J4" s="117"/>
+      <c r="K4" s="117">
         <f ca="1">K5</f>
         <v>46268</v>
       </c>
-      <c r="L4" s="114"/>
-      <c r="M4" s="114"/>
+      <c r="L4" s="117"/>
+      <c r="M4" s="117"/>
       <c r="N4" s="37"/>
-      <c r="O4" s="114">
+      <c r="O4" s="117">
         <f ca="1">O5</f>
         <v>46269</v>
       </c>
-      <c r="P4" s="114"/>
-      <c r="Q4" s="114"/>
-      <c r="R4" s="114"/>
-      <c r="S4" s="114"/>
-      <c r="T4" s="114"/>
-      <c r="U4" s="114"/>
-      <c r="V4" s="114"/>
-      <c r="W4" s="114">
+      <c r="P4" s="117"/>
+      <c r="Q4" s="117"/>
+      <c r="R4" s="117"/>
+      <c r="S4" s="117"/>
+      <c r="T4" s="117"/>
+      <c r="U4" s="117"/>
+      <c r="V4" s="117"/>
+      <c r="W4" s="117">
         <f ca="1">W5</f>
         <v>46270</v>
       </c>
-      <c r="X4" s="114"/>
-      <c r="Y4" s="114"/>
-      <c r="Z4" s="114"/>
-      <c r="AA4" s="114"/>
-      <c r="AB4" s="114"/>
-      <c r="AC4" s="114"/>
-      <c r="AD4" s="114"/>
+      <c r="X4" s="117"/>
+      <c r="Y4" s="117"/>
+      <c r="Z4" s="117"/>
+      <c r="AA4" s="117"/>
+      <c r="AB4" s="117"/>
+      <c r="AC4" s="117"/>
+      <c r="AD4" s="117"/>
       <c r="AF4" s="38"/>
       <c r="AG4" s="39"/>
       <c r="AH4" s="39"/>
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1"/>
-      <c r="C5" s="92">
+      <c r="C5" s="118">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46264</v>
       </c>
-      <c r="D5" s="93"/>
-      <c r="E5" s="92">
+      <c r="D5" s="120"/>
+      <c r="E5" s="118">
         <f ca="1">C5+1</f>
         <v>46265</v>
       </c>
-      <c r="F5" s="93"/>
-      <c r="G5" s="92">
+      <c r="F5" s="120"/>
+      <c r="G5" s="118">
         <f ca="1">E5+1</f>
         <v>46266</v>
       </c>
-      <c r="H5" s="93"/>
-      <c r="I5" s="92">
+      <c r="H5" s="120"/>
+      <c r="I5" s="118">
         <f ca="1">G5+1</f>
         <v>46267</v>
       </c>
-      <c r="J5" s="93"/>
-      <c r="K5" s="92">
+      <c r="J5" s="120"/>
+      <c r="K5" s="118">
         <f ca="1">I5+1</f>
         <v>46268</v>
       </c>
-      <c r="L5" s="112"/>
-      <c r="M5" s="112"/>
+      <c r="L5" s="119"/>
+      <c r="M5" s="119"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="92">
+      <c r="O5" s="118">
         <f ca="1">K5+1</f>
         <v>46269</v>
       </c>
-      <c r="P5" s="112"/>
-      <c r="Q5" s="112"/>
-      <c r="R5" s="112"/>
-      <c r="S5" s="112"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="112"/>
-      <c r="V5" s="93"/>
-      <c r="W5" s="92">
+      <c r="P5" s="119"/>
+      <c r="Q5" s="119"/>
+      <c r="R5" s="119"/>
+      <c r="S5" s="119"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="120"/>
+      <c r="W5" s="118">
         <f ca="1">O5+1</f>
         <v>46270</v>
       </c>
-      <c r="X5" s="112"/>
-      <c r="Y5" s="112"/>
-      <c r="Z5" s="112"/>
-      <c r="AA5" s="112"/>
-      <c r="AB5" s="112"/>
-      <c r="AC5" s="112"/>
-      <c r="AD5" s="93"/>
+      <c r="X5" s="119"/>
+      <c r="Y5" s="119"/>
+      <c r="Z5" s="119"/>
+      <c r="AA5" s="119"/>
+      <c r="AB5" s="119"/>
+      <c r="AC5" s="119"/>
+      <c r="AD5" s="120"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
       <c r="AI5" s="41"/>
       <c r="AJ5" s="41"/>
     </row>
-    <row r="6" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="42"/>
-      <c r="C6" s="97"/>
-      <c r="D6" s="98"/>
-      <c r="E6" s="97"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="148"/>
-      <c r="H6" s="149"/>
-      <c r="I6" s="148"/>
-      <c r="J6" s="149"/>
-      <c r="K6" s="148"/>
-      <c r="L6" s="150"/>
-      <c r="M6" s="150"/>
-      <c r="N6" s="149"/>
-      <c r="O6" s="148"/>
-      <c r="P6" s="150"/>
-      <c r="Q6" s="150"/>
-      <c r="R6" s="150"/>
-      <c r="S6" s="150"/>
-      <c r="T6" s="150"/>
-      <c r="U6" s="150"/>
-      <c r="V6" s="149"/>
-      <c r="W6" s="148"/>
-      <c r="X6" s="150"/>
-      <c r="Y6" s="150"/>
-      <c r="Z6" s="150"/>
-      <c r="AA6" s="150"/>
-      <c r="AB6" s="150"/>
-      <c r="AC6" s="150"/>
-      <c r="AD6" s="149"/>
+      <c r="C6" s="111"/>
+      <c r="D6" s="113"/>
+      <c r="E6" s="111"/>
+      <c r="F6" s="113"/>
+      <c r="G6" s="147"/>
+      <c r="H6" s="148"/>
+      <c r="I6" s="147"/>
+      <c r="J6" s="148"/>
+      <c r="K6" s="147"/>
+      <c r="L6" s="149"/>
+      <c r="M6" s="149"/>
+      <c r="N6" s="148"/>
+      <c r="O6" s="147"/>
+      <c r="P6" s="149"/>
+      <c r="Q6" s="149"/>
+      <c r="R6" s="149"/>
+      <c r="S6" s="149"/>
+      <c r="T6" s="149"/>
+      <c r="U6" s="149"/>
+      <c r="V6" s="148"/>
+      <c r="W6" s="147"/>
+      <c r="X6" s="149"/>
+      <c r="Y6" s="149"/>
+      <c r="Z6" s="149"/>
+      <c r="AA6" s="149"/>
+      <c r="AB6" s="149"/>
+      <c r="AC6" s="149"/>
+      <c r="AD6" s="148"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
-    <row r="7" spans="1:36" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" ht="10" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1"/>
-      <c r="C7" s="92">
+      <c r="C7" s="118">
         <f ca="1">W5+1</f>
         <v>46271</v>
       </c>
-      <c r="D7" s="93"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="102"/>
-      <c r="G7" s="101"/>
-      <c r="H7" s="102"/>
-      <c r="I7" s="101"/>
-      <c r="J7" s="102"/>
-      <c r="K7" s="101"/>
-      <c r="L7" s="103"/>
-      <c r="M7" s="103"/>
+      <c r="D7" s="120"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="130"/>
+      <c r="G7" s="129"/>
+      <c r="H7" s="130"/>
+      <c r="I7" s="129"/>
+      <c r="J7" s="130"/>
+      <c r="K7" s="129"/>
+      <c r="L7" s="131"/>
+      <c r="M7" s="131"/>
       <c r="N7" s="75"/>
-      <c r="O7" s="101"/>
-      <c r="P7" s="103"/>
-      <c r="Q7" s="103"/>
-      <c r="R7" s="103"/>
-      <c r="S7" s="103"/>
-      <c r="T7" s="103"/>
-      <c r="U7" s="103"/>
-      <c r="V7" s="102"/>
-      <c r="W7" s="101"/>
-      <c r="X7" s="103"/>
-      <c r="Y7" s="103"/>
-      <c r="Z7" s="103"/>
-      <c r="AA7" s="103"/>
-      <c r="AB7" s="103"/>
-      <c r="AC7" s="103"/>
-      <c r="AD7" s="102"/>
+      <c r="O7" s="129"/>
+      <c r="P7" s="131"/>
+      <c r="Q7" s="131"/>
+      <c r="R7" s="131"/>
+      <c r="S7" s="131"/>
+      <c r="T7" s="131"/>
+      <c r="U7" s="131"/>
+      <c r="V7" s="130"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="131"/>
+      <c r="Y7" s="131"/>
+      <c r="Z7" s="131"/>
+      <c r="AA7" s="131"/>
+      <c r="AB7" s="131"/>
+      <c r="AC7" s="131"/>
+      <c r="AD7" s="130"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="4"/>
-      <c r="C8" s="92"/>
-      <c r="D8" s="93"/>
-      <c r="E8" s="94">
+      <c r="C8" s="118"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="132">
         <f ca="1">C7+1</f>
         <v>46272</v>
       </c>
-      <c r="F8" s="95"/>
-      <c r="G8" s="94">
+      <c r="F8" s="133"/>
+      <c r="G8" s="132">
         <f ca="1">E8+1</f>
         <v>46273</v>
       </c>
-      <c r="H8" s="95"/>
-      <c r="I8" s="94">
+      <c r="H8" s="133"/>
+      <c r="I8" s="132">
         <f ca="1">G8+1</f>
         <v>46274</v>
       </c>
-      <c r="J8" s="95"/>
-      <c r="K8" s="94">
+      <c r="J8" s="133"/>
+      <c r="K8" s="132">
         <f ca="1">I8+1</f>
         <v>46275</v>
       </c>
-      <c r="L8" s="96"/>
-      <c r="M8" s="96"/>
+      <c r="L8" s="134"/>
+      <c r="M8" s="134"/>
       <c r="N8" s="50"/>
-      <c r="O8" s="94">
+      <c r="O8" s="132">
         <f ca="1">K8+1</f>
         <v>46276</v>
       </c>
-      <c r="P8" s="96"/>
-      <c r="Q8" s="96"/>
-      <c r="R8" s="96"/>
-      <c r="S8" s="96"/>
-      <c r="T8" s="96"/>
-      <c r="U8" s="96"/>
-      <c r="V8" s="95"/>
-      <c r="W8" s="94">
+      <c r="P8" s="134"/>
+      <c r="Q8" s="134"/>
+      <c r="R8" s="134"/>
+      <c r="S8" s="134"/>
+      <c r="T8" s="134"/>
+      <c r="U8" s="134"/>
+      <c r="V8" s="133"/>
+      <c r="W8" s="132">
         <f ca="1">O8+1</f>
         <v>46277</v>
       </c>
-      <c r="X8" s="96"/>
-      <c r="Y8" s="96"/>
-      <c r="Z8" s="96"/>
-      <c r="AA8" s="96"/>
-      <c r="AB8" s="96"/>
-      <c r="AC8" s="96"/>
-      <c r="AD8" s="95"/>
+      <c r="X8" s="134"/>
+      <c r="Y8" s="134"/>
+      <c r="Z8" s="134"/>
+      <c r="AA8" s="134"/>
+      <c r="AB8" s="134"/>
+      <c r="AC8" s="134"/>
+      <c r="AD8" s="133"/>
       <c r="AF8" s="4"/>
     </row>
-    <row r="9" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="42"/>
-      <c r="C9" s="148"/>
-      <c r="D9" s="149"/>
-      <c r="E9" s="148"/>
-      <c r="F9" s="149"/>
-      <c r="G9" s="148"/>
-      <c r="H9" s="149"/>
-      <c r="I9" s="148"/>
-      <c r="J9" s="149"/>
-      <c r="K9" s="148"/>
-      <c r="L9" s="150"/>
-      <c r="M9" s="150"/>
-      <c r="N9" s="149"/>
-      <c r="O9" s="151" t="s">
-        <v>41</v>
-      </c>
-      <c r="P9" s="153"/>
-      <c r="Q9" s="153"/>
-      <c r="R9" s="153"/>
-      <c r="S9" s="153"/>
-      <c r="T9" s="153"/>
-      <c r="U9" s="153"/>
+      <c r="C9" s="147"/>
+      <c r="D9" s="148"/>
+      <c r="E9" s="147"/>
+      <c r="F9" s="148"/>
+      <c r="G9" s="147"/>
+      <c r="H9" s="148"/>
+      <c r="I9" s="147"/>
+      <c r="J9" s="148"/>
+      <c r="K9" s="147"/>
+      <c r="L9" s="149"/>
+      <c r="M9" s="149"/>
+      <c r="N9" s="148"/>
+      <c r="O9" s="150" t="s">
+        <v>37</v>
+      </c>
+      <c r="P9" s="151"/>
+      <c r="Q9" s="151"/>
+      <c r="R9" s="151"/>
+      <c r="S9" s="151"/>
+      <c r="T9" s="151"/>
+      <c r="U9" s="151"/>
       <c r="V9" s="152"/>
-      <c r="W9" s="148"/>
-      <c r="X9" s="150"/>
-      <c r="Y9" s="150"/>
-      <c r="Z9" s="150"/>
-      <c r="AA9" s="150"/>
-      <c r="AB9" s="150"/>
-      <c r="AC9" s="150"/>
-      <c r="AD9" s="149"/>
+      <c r="W9" s="147"/>
+      <c r="X9" s="149"/>
+      <c r="Y9" s="149"/>
+      <c r="Z9" s="149"/>
+      <c r="AA9" s="149"/>
+      <c r="AB9" s="149"/>
+      <c r="AC9" s="149"/>
+      <c r="AD9" s="148"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
-    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" s="43" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="42"/>
-      <c r="C10" s="92">
+      <c r="C10" s="118">
         <f ca="1">W8+1</f>
         <v>46278</v>
       </c>
-      <c r="D10" s="93"/>
+      <c r="D10" s="120"/>
       <c r="E10" s="45"/>
       <c r="F10" s="75"/>
       <c r="G10" s="45"/>
@@ -2479,99 +2656,99 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="42"/>
     </row>
-    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="4"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="93"/>
-      <c r="E11" s="94">
+      <c r="C11" s="118"/>
+      <c r="D11" s="120"/>
+      <c r="E11" s="132">
         <f ca="1">C10+1</f>
         <v>46279</v>
       </c>
-      <c r="F11" s="95"/>
-      <c r="G11" s="94">
+      <c r="F11" s="133"/>
+      <c r="G11" s="132">
         <f ca="1">E11+1</f>
         <v>46280</v>
       </c>
-      <c r="H11" s="95"/>
-      <c r="I11" s="94">
+      <c r="H11" s="133"/>
+      <c r="I11" s="132">
         <f ca="1">G11+1</f>
         <v>46281</v>
       </c>
-      <c r="J11" s="95"/>
-      <c r="K11" s="94">
+      <c r="J11" s="133"/>
+      <c r="K11" s="132">
         <f ca="1">I11+1</f>
         <v>46282</v>
       </c>
-      <c r="L11" s="96"/>
-      <c r="M11" s="96"/>
+      <c r="L11" s="134"/>
+      <c r="M11" s="134"/>
       <c r="N11" s="50"/>
-      <c r="O11" s="94">
+      <c r="O11" s="132">
         <f ca="1">K11+1</f>
         <v>46283</v>
       </c>
-      <c r="P11" s="96"/>
-      <c r="Q11" s="96"/>
-      <c r="R11" s="96"/>
-      <c r="S11" s="96"/>
-      <c r="T11" s="96"/>
-      <c r="U11" s="96"/>
-      <c r="V11" s="95"/>
-      <c r="W11" s="94">
+      <c r="P11" s="134"/>
+      <c r="Q11" s="134"/>
+      <c r="R11" s="134"/>
+      <c r="S11" s="134"/>
+      <c r="T11" s="134"/>
+      <c r="U11" s="134"/>
+      <c r="V11" s="133"/>
+      <c r="W11" s="132">
         <f ca="1">O11+1</f>
         <v>46284</v>
       </c>
-      <c r="X11" s="96"/>
-      <c r="Y11" s="96"/>
-      <c r="Z11" s="96"/>
-      <c r="AA11" s="96"/>
-      <c r="AB11" s="96"/>
-      <c r="AC11" s="96"/>
-      <c r="AD11" s="95"/>
+      <c r="X11" s="134"/>
+      <c r="Y11" s="134"/>
+      <c r="Z11" s="134"/>
+      <c r="AA11" s="134"/>
+      <c r="AB11" s="134"/>
+      <c r="AC11" s="134"/>
+      <c r="AD11" s="133"/>
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="42"/>
-      <c r="C12" s="148"/>
-      <c r="D12" s="149"/>
-      <c r="E12" s="151" t="s">
-        <v>42</v>
+      <c r="C12" s="147"/>
+      <c r="D12" s="148"/>
+      <c r="E12" s="150" t="s">
+        <v>38</v>
       </c>
       <c r="F12" s="152"/>
-      <c r="G12" s="148"/>
-      <c r="H12" s="149"/>
-      <c r="I12" s="148"/>
-      <c r="J12" s="149"/>
-      <c r="K12" s="148"/>
-      <c r="L12" s="150"/>
-      <c r="M12" s="150"/>
-      <c r="N12" s="149"/>
-      <c r="O12" s="148"/>
-      <c r="P12" s="150"/>
-      <c r="Q12" s="150"/>
-      <c r="R12" s="150"/>
-      <c r="S12" s="150"/>
-      <c r="T12" s="150"/>
-      <c r="U12" s="150"/>
-      <c r="V12" s="149"/>
-      <c r="W12" s="148"/>
-      <c r="X12" s="150"/>
-      <c r="Y12" s="150"/>
-      <c r="Z12" s="150"/>
-      <c r="AA12" s="150"/>
-      <c r="AB12" s="150"/>
-      <c r="AC12" s="150"/>
-      <c r="AD12" s="149"/>
+      <c r="G12" s="147"/>
+      <c r="H12" s="148"/>
+      <c r="I12" s="147"/>
+      <c r="J12" s="148"/>
+      <c r="K12" s="147"/>
+      <c r="L12" s="149"/>
+      <c r="M12" s="149"/>
+      <c r="N12" s="148"/>
+      <c r="O12" s="147"/>
+      <c r="P12" s="149"/>
+      <c r="Q12" s="149"/>
+      <c r="R12" s="149"/>
+      <c r="S12" s="149"/>
+      <c r="T12" s="149"/>
+      <c r="U12" s="149"/>
+      <c r="V12" s="148"/>
+      <c r="W12" s="147"/>
+      <c r="X12" s="149"/>
+      <c r="Y12" s="149"/>
+      <c r="Z12" s="149"/>
+      <c r="AA12" s="149"/>
+      <c r="AB12" s="149"/>
+      <c r="AC12" s="149"/>
+      <c r="AD12" s="148"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
-    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" s="43" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="42"/>
-      <c r="C13" s="92">
+      <c r="C13" s="118">
         <f ca="1">W11+1</f>
         <v>46285</v>
       </c>
-      <c r="D13" s="93"/>
+      <c r="D13" s="120"/>
       <c r="E13" s="45"/>
       <c r="F13" s="75"/>
       <c r="G13" s="45"/>
@@ -2601,114 +2778,114 @@
       <c r="AE13" s="7"/>
       <c r="AF13" s="42"/>
     </row>
-    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="4"/>
-      <c r="C14" s="92"/>
-      <c r="D14" s="93"/>
-      <c r="E14" s="94">
+      <c r="C14" s="118"/>
+      <c r="D14" s="120"/>
+      <c r="E14" s="132">
         <f ca="1">C13+1</f>
         <v>46286</v>
       </c>
-      <c r="F14" s="95"/>
-      <c r="G14" s="94">
+      <c r="F14" s="133"/>
+      <c r="G14" s="132">
         <f ca="1">E14+1</f>
         <v>46287</v>
       </c>
-      <c r="H14" s="95"/>
-      <c r="I14" s="94">
+      <c r="H14" s="133"/>
+      <c r="I14" s="132">
         <f ca="1">G14+1</f>
         <v>46288</v>
       </c>
-      <c r="J14" s="95"/>
-      <c r="K14" s="94">
+      <c r="J14" s="133"/>
+      <c r="K14" s="132">
         <f ca="1">I14+1</f>
         <v>46289</v>
       </c>
-      <c r="L14" s="96"/>
-      <c r="M14" s="96"/>
+      <c r="L14" s="134"/>
+      <c r="M14" s="134"/>
       <c r="N14" s="50"/>
-      <c r="O14" s="94">
+      <c r="O14" s="132">
         <f ca="1">K14+1</f>
         <v>46290</v>
       </c>
-      <c r="P14" s="96"/>
-      <c r="Q14" s="96"/>
-      <c r="R14" s="96"/>
-      <c r="S14" s="96"/>
-      <c r="T14" s="96"/>
-      <c r="U14" s="96"/>
-      <c r="V14" s="95"/>
-      <c r="W14" s="94">
+      <c r="P14" s="134"/>
+      <c r="Q14" s="134"/>
+      <c r="R14" s="134"/>
+      <c r="S14" s="134"/>
+      <c r="T14" s="134"/>
+      <c r="U14" s="134"/>
+      <c r="V14" s="133"/>
+      <c r="W14" s="132">
         <f ca="1">O14+1</f>
         <v>46291</v>
       </c>
-      <c r="X14" s="96"/>
-      <c r="Y14" s="96"/>
-      <c r="Z14" s="96"/>
-      <c r="AA14" s="96"/>
-      <c r="AB14" s="96"/>
-      <c r="AC14" s="96"/>
-      <c r="AD14" s="95"/>
+      <c r="X14" s="134"/>
+      <c r="Y14" s="134"/>
+      <c r="Z14" s="134"/>
+      <c r="AA14" s="134"/>
+      <c r="AB14" s="134"/>
+      <c r="AC14" s="134"/>
+      <c r="AD14" s="133"/>
       <c r="AF14" s="4"/>
     </row>
-    <row r="15" spans="1:36" s="43" customFormat="1" ht="162.94999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" s="43" customFormat="1" ht="163" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="42"/>
-      <c r="C15" s="148"/>
-      <c r="D15" s="149"/>
-      <c r="E15" s="148"/>
-      <c r="F15" s="149"/>
-      <c r="G15" s="148"/>
-      <c r="H15" s="149"/>
-      <c r="I15" s="106"/>
-      <c r="J15" s="108"/>
-      <c r="K15" s="106"/>
-      <c r="L15" s="107"/>
-      <c r="M15" s="107"/>
-      <c r="N15" s="108"/>
-      <c r="O15" s="106"/>
-      <c r="P15" s="107"/>
-      <c r="Q15" s="107"/>
-      <c r="R15" s="107"/>
-      <c r="S15" s="107"/>
-      <c r="T15" s="107"/>
-      <c r="U15" s="107"/>
-      <c r="V15" s="108"/>
-      <c r="W15" s="106"/>
-      <c r="X15" s="107"/>
-      <c r="Y15" s="107"/>
-      <c r="Z15" s="107"/>
-      <c r="AA15" s="107"/>
-      <c r="AB15" s="107"/>
-      <c r="AC15" s="107"/>
-      <c r="AD15" s="108"/>
+      <c r="C15" s="147"/>
+      <c r="D15" s="148"/>
+      <c r="E15" s="147"/>
+      <c r="F15" s="148"/>
+      <c r="G15" s="147"/>
+      <c r="H15" s="148"/>
+      <c r="I15" s="123"/>
+      <c r="J15" s="125"/>
+      <c r="K15" s="123"/>
+      <c r="L15" s="124"/>
+      <c r="M15" s="124"/>
+      <c r="N15" s="125"/>
+      <c r="O15" s="123"/>
+      <c r="P15" s="124"/>
+      <c r="Q15" s="124"/>
+      <c r="R15" s="124"/>
+      <c r="S15" s="124"/>
+      <c r="T15" s="124"/>
+      <c r="U15" s="124"/>
+      <c r="V15" s="125"/>
+      <c r="W15" s="123"/>
+      <c r="X15" s="124"/>
+      <c r="Y15" s="124"/>
+      <c r="Z15" s="124"/>
+      <c r="AA15" s="124"/>
+      <c r="AB15" s="124"/>
+      <c r="AC15" s="124"/>
+      <c r="AD15" s="125"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
-    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" s="43" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="42"/>
-      <c r="C16" s="92">
+      <c r="C16" s="118">
         <f ca="1">W14+1</f>
         <v>46292</v>
       </c>
-      <c r="D16" s="93"/>
+      <c r="D16" s="120"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
       <c r="H16" s="75"/>
-      <c r="I16" s="145"/>
-      <c r="J16" s="146"/>
+      <c r="I16" s="153"/>
+      <c r="J16" s="154"/>
       <c r="K16" s="66"/>
       <c r="L16" s="68"/>
       <c r="M16" s="68"/>
       <c r="N16" s="67"/>
-      <c r="O16" s="145"/>
-      <c r="P16" s="147"/>
-      <c r="Q16" s="147"/>
-      <c r="R16" s="147"/>
-      <c r="S16" s="147"/>
-      <c r="T16" s="147"/>
-      <c r="U16" s="147"/>
-      <c r="V16" s="146"/>
+      <c r="O16" s="153"/>
+      <c r="P16" s="155"/>
+      <c r="Q16" s="155"/>
+      <c r="R16" s="155"/>
+      <c r="S16" s="155"/>
+      <c r="T16" s="155"/>
+      <c r="U16" s="155"/>
+      <c r="V16" s="154"/>
       <c r="W16" s="45"/>
       <c r="X16" s="76"/>
       <c r="Y16" s="76"/>
@@ -2720,25 +2897,25 @@
       <c r="AE16" s="7"/>
       <c r="AF16" s="42"/>
     </row>
-    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4"/>
-      <c r="C17" s="92"/>
-      <c r="D17" s="93"/>
-      <c r="E17" s="94">
+      <c r="C17" s="118"/>
+      <c r="D17" s="120"/>
+      <c r="E17" s="132">
         <f ca="1">C16+1</f>
         <v>46293</v>
       </c>
-      <c r="F17" s="95"/>
-      <c r="G17" s="94">
+      <c r="F17" s="133"/>
+      <c r="G17" s="132">
         <f ca="1">E17+1</f>
         <v>46294</v>
       </c>
-      <c r="H17" s="95"/>
-      <c r="I17" s="94">
+      <c r="H17" s="133"/>
+      <c r="I17" s="132">
         <f ca="1">G17+1</f>
         <v>46295</v>
       </c>
-      <c r="J17" s="95"/>
+      <c r="J17" s="133"/>
       <c r="K17" s="46">
         <f ca="1">I17+1</f>
         <v>46296</v>
@@ -2746,93 +2923,93 @@
       <c r="L17" s="51"/>
       <c r="M17" s="51"/>
       <c r="N17" s="69"/>
-      <c r="O17" s="94">
+      <c r="O17" s="132">
         <f ca="1">K17+1</f>
         <v>46297</v>
       </c>
-      <c r="P17" s="96"/>
-      <c r="Q17" s="96"/>
-      <c r="R17" s="96"/>
-      <c r="S17" s="96"/>
-      <c r="T17" s="96"/>
-      <c r="U17" s="96"/>
-      <c r="V17" s="95"/>
-      <c r="W17" s="94">
+      <c r="P17" s="134"/>
+      <c r="Q17" s="134"/>
+      <c r="R17" s="134"/>
+      <c r="S17" s="134"/>
+      <c r="T17" s="134"/>
+      <c r="U17" s="134"/>
+      <c r="V17" s="133"/>
+      <c r="W17" s="132">
         <f ca="1">O17+1</f>
         <v>46298</v>
       </c>
-      <c r="X17" s="96"/>
-      <c r="Y17" s="96"/>
-      <c r="Z17" s="96"/>
-      <c r="AA17" s="96"/>
-      <c r="AB17" s="96"/>
-      <c r="AC17" s="96"/>
-      <c r="AD17" s="95"/>
+      <c r="X17" s="134"/>
+      <c r="Y17" s="134"/>
+      <c r="Z17" s="134"/>
+      <c r="AA17" s="134"/>
+      <c r="AB17" s="134"/>
+      <c r="AC17" s="134"/>
+      <c r="AD17" s="133"/>
       <c r="AF17" s="4"/>
     </row>
-    <row r="18" spans="1:42" s="43" customFormat="1" ht="147.4" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:42" s="43" customFormat="1" ht="147.4" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="42"/>
-      <c r="C18" s="109" t="s">
+      <c r="C18" s="126" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="111"/>
-      <c r="E18" s="106"/>
-      <c r="F18" s="108"/>
-      <c r="G18" s="106"/>
-      <c r="H18" s="108"/>
-      <c r="I18" s="109" t="s">
+      <c r="D18" s="128"/>
+      <c r="E18" s="123"/>
+      <c r="F18" s="125"/>
+      <c r="G18" s="123"/>
+      <c r="H18" s="125"/>
+      <c r="I18" s="126" t="s">
         <v>17</v>
       </c>
-      <c r="J18" s="111"/>
+      <c r="J18" s="128"/>
       <c r="K18" s="70"/>
       <c r="L18" s="71"/>
       <c r="M18" s="71"/>
       <c r="N18" s="72"/>
-      <c r="O18" s="97"/>
-      <c r="P18" s="143"/>
-      <c r="Q18" s="143"/>
-      <c r="R18" s="143"/>
-      <c r="S18" s="143"/>
-      <c r="T18" s="143"/>
-      <c r="U18" s="143"/>
-      <c r="V18" s="98"/>
-      <c r="W18" s="97"/>
-      <c r="X18" s="143"/>
-      <c r="Y18" s="143"/>
-      <c r="Z18" s="143"/>
-      <c r="AA18" s="143"/>
-      <c r="AB18" s="143"/>
-      <c r="AC18" s="143"/>
-      <c r="AD18" s="98"/>
+      <c r="O18" s="111"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="112"/>
+      <c r="R18" s="112"/>
+      <c r="S18" s="112"/>
+      <c r="T18" s="112"/>
+      <c r="U18" s="112"/>
+      <c r="V18" s="113"/>
+      <c r="W18" s="111"/>
+      <c r="X18" s="112"/>
+      <c r="Y18" s="112"/>
+      <c r="Z18" s="112"/>
+      <c r="AA18" s="112"/>
+      <c r="AB18" s="112"/>
+      <c r="AC18" s="112"/>
+      <c r="AD18" s="113"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
-    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:42" s="43" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="42"/>
-      <c r="C19" s="92">
+      <c r="C19" s="118">
         <f ca="1">W17+1</f>
         <v>46299</v>
       </c>
-      <c r="D19" s="93"/>
+      <c r="D19" s="120"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
       <c r="H19" s="75"/>
-      <c r="I19" s="145"/>
-      <c r="J19" s="146"/>
+      <c r="I19" s="153"/>
+      <c r="J19" s="154"/>
       <c r="K19" s="66"/>
       <c r="L19" s="68"/>
       <c r="M19" s="68"/>
       <c r="N19" s="67"/>
-      <c r="O19" s="145"/>
-      <c r="P19" s="147"/>
-      <c r="Q19" s="147"/>
-      <c r="R19" s="147"/>
-      <c r="S19" s="147"/>
-      <c r="T19" s="147"/>
-      <c r="U19" s="147"/>
-      <c r="V19" s="146"/>
+      <c r="O19" s="153"/>
+      <c r="P19" s="155"/>
+      <c r="Q19" s="155"/>
+      <c r="R19" s="155"/>
+      <c r="S19" s="155"/>
+      <c r="T19" s="155"/>
+      <c r="U19" s="155"/>
+      <c r="V19" s="154"/>
       <c r="W19" s="45"/>
       <c r="X19" s="76"/>
       <c r="Y19" s="76"/>
@@ -2844,25 +3021,25 @@
       <c r="AE19" s="7"/>
       <c r="AF19" s="42"/>
     </row>
-    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4"/>
-      <c r="C20" s="92"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="94">
+      <c r="C20" s="118"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="132">
         <f ca="1">C19+1</f>
         <v>46300</v>
       </c>
-      <c r="F20" s="95"/>
-      <c r="G20" s="94">
+      <c r="F20" s="133"/>
+      <c r="G20" s="132">
         <f ca="1">E20+1</f>
         <v>46301</v>
       </c>
-      <c r="H20" s="95"/>
-      <c r="I20" s="94">
+      <c r="H20" s="133"/>
+      <c r="I20" s="132">
         <f ca="1">G20+1</f>
         <v>46302</v>
       </c>
-      <c r="J20" s="95"/>
+      <c r="J20" s="133"/>
       <c r="K20" s="46">
         <f ca="1">I20+1</f>
         <v>46303</v>
@@ -2870,65 +3047,65 @@
       <c r="L20" s="51"/>
       <c r="M20" s="51"/>
       <c r="N20" s="69"/>
-      <c r="O20" s="94">
+      <c r="O20" s="132">
         <f ca="1">K20+1</f>
         <v>46304</v>
       </c>
-      <c r="P20" s="96"/>
-      <c r="Q20" s="96"/>
-      <c r="R20" s="96"/>
-      <c r="S20" s="96"/>
-      <c r="T20" s="96"/>
-      <c r="U20" s="96"/>
-      <c r="V20" s="95"/>
-      <c r="W20" s="94">
+      <c r="P20" s="134"/>
+      <c r="Q20" s="134"/>
+      <c r="R20" s="134"/>
+      <c r="S20" s="134"/>
+      <c r="T20" s="134"/>
+      <c r="U20" s="134"/>
+      <c r="V20" s="133"/>
+      <c r="W20" s="132">
         <f ca="1">O20+1</f>
         <v>46305</v>
       </c>
-      <c r="X20" s="96"/>
-      <c r="Y20" s="96"/>
-      <c r="Z20" s="96"/>
-      <c r="AA20" s="96"/>
-      <c r="AB20" s="96"/>
-      <c r="AC20" s="96"/>
-      <c r="AD20" s="95"/>
+      <c r="X20" s="134"/>
+      <c r="Y20" s="134"/>
+      <c r="Z20" s="134"/>
+      <c r="AA20" s="134"/>
+      <c r="AB20" s="134"/>
+      <c r="AC20" s="134"/>
+      <c r="AD20" s="133"/>
       <c r="AF20" s="4"/>
     </row>
-    <row r="21" spans="1:42" s="43" customFormat="1" ht="166.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:42" s="43" customFormat="1" ht="166.9" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="42"/>
-      <c r="C21" s="97"/>
-      <c r="D21" s="98"/>
-      <c r="E21" s="97"/>
-      <c r="F21" s="98"/>
-      <c r="G21" s="97"/>
-      <c r="H21" s="98"/>
-      <c r="I21" s="97"/>
-      <c r="J21" s="98"/>
+      <c r="C21" s="111"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="113"/>
       <c r="K21" s="70"/>
       <c r="L21" s="71"/>
       <c r="M21" s="71"/>
       <c r="N21" s="72"/>
-      <c r="O21" s="97"/>
-      <c r="P21" s="143"/>
-      <c r="Q21" s="143"/>
-      <c r="R21" s="143"/>
-      <c r="S21" s="143"/>
-      <c r="T21" s="143"/>
-      <c r="U21" s="143"/>
-      <c r="V21" s="98"/>
-      <c r="W21" s="97"/>
-      <c r="X21" s="143"/>
-      <c r="Y21" s="143"/>
-      <c r="Z21" s="143"/>
-      <c r="AA21" s="143"/>
-      <c r="AB21" s="143"/>
-      <c r="AC21" s="143"/>
-      <c r="AD21" s="98"/>
+      <c r="O21" s="111"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="112"/>
+      <c r="R21" s="112"/>
+      <c r="S21" s="112"/>
+      <c r="T21" s="112"/>
+      <c r="U21" s="112"/>
+      <c r="V21" s="113"/>
+      <c r="W21" s="111"/>
+      <c r="X21" s="112"/>
+      <c r="Y21" s="112"/>
+      <c r="Z21" s="112"/>
+      <c r="AA21" s="112"/>
+      <c r="AB21" s="112"/>
+      <c r="AC21" s="112"/>
+      <c r="AD21" s="113"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
     </row>
-    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:42" s="7" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="4"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52"/>
@@ -2960,7 +3137,7 @@
       <c r="AD22" s="55"/>
       <c r="AF22" s="4"/>
     </row>
-    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:42" s="7" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="56"/>
@@ -2994,61 +3171,61 @@
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
     </row>
-    <row r="24" spans="1:42" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:42" ht="25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="1"/>
       <c r="M24" s="1"/>
       <c r="AF24" s="1"/>
     </row>
-    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="1"/>
-      <c r="C25" s="86" t="s">
+      <c r="C25" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="86"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="86"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="86"/>
-      <c r="J25" s="86"/>
-      <c r="K25" s="86"/>
+      <c r="D25" s="143"/>
+      <c r="E25" s="143"/>
+      <c r="F25" s="143"/>
+      <c r="G25" s="143"/>
+      <c r="H25" s="143"/>
+      <c r="I25" s="143"/>
+      <c r="J25" s="143"/>
+      <c r="K25" s="143"/>
       <c r="L25" s="60"/>
       <c r="M25" s="1"/>
-      <c r="O25" s="87">
+      <c r="O25" s="144">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)-1,1)</f>
         <v>46235</v>
       </c>
-      <c r="P25" s="87"/>
-      <c r="Q25" s="87"/>
-      <c r="R25" s="87"/>
-      <c r="S25" s="87"/>
-      <c r="T25" s="87"/>
-      <c r="U25" s="87"/>
+      <c r="P25" s="144"/>
+      <c r="Q25" s="144"/>
+      <c r="R25" s="144"/>
+      <c r="S25" s="144"/>
+      <c r="T25" s="144"/>
+      <c r="U25" s="144"/>
       <c r="V25" s="61"/>
       <c r="W25" s="61"/>
-      <c r="X25" s="87">
+      <c r="X25" s="144">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)+1,1)</f>
         <v>46296</v>
       </c>
-      <c r="Y25" s="87"/>
-      <c r="Z25" s="87"/>
-      <c r="AA25" s="87"/>
-      <c r="AB25" s="87"/>
-      <c r="AC25" s="87"/>
-      <c r="AD25" s="87"/>
+      <c r="Y25" s="144"/>
+      <c r="Z25" s="144"/>
+      <c r="AA25" s="144"/>
+      <c r="AB25" s="144"/>
+      <c r="AC25" s="144"/>
+      <c r="AD25" s="144"/>
       <c r="AF25" s="1"/>
     </row>
-    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="1"/>
-      <c r="C26" s="86"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="86"/>
-      <c r="G26" s="86"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="86"/>
-      <c r="J26" s="86"/>
-      <c r="K26" s="86"/>
+      <c r="C26" s="143"/>
+      <c r="D26" s="143"/>
+      <c r="E26" s="143"/>
+      <c r="F26" s="143"/>
+      <c r="G26" s="143"/>
+      <c r="H26" s="143"/>
+      <c r="I26" s="143"/>
+      <c r="J26" s="143"/>
+      <c r="K26" s="143"/>
       <c r="L26" s="60"/>
       <c r="M26" s="1"/>
       <c r="O26" s="62" t="str">
@@ -3111,19 +3288,19 @@
       </c>
       <c r="AF26" s="1"/>
     </row>
-    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="1"/>
-      <c r="C27" s="88" t="s">
+      <c r="C27" s="115" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="88"/>
-      <c r="E27" s="88"/>
-      <c r="F27" s="88"/>
-      <c r="G27" s="88"/>
-      <c r="H27" s="88"/>
-      <c r="I27" s="88"/>
-      <c r="J27" s="88"/>
-      <c r="K27" s="88"/>
+      <c r="D27" s="115"/>
+      <c r="E27" s="115"/>
+      <c r="F27" s="115"/>
+      <c r="G27" s="115"/>
+      <c r="H27" s="115"/>
+      <c r="I27" s="115"/>
+      <c r="J27" s="115"/>
+      <c r="K27" s="115"/>
       <c r="M27" s="1"/>
       <c r="O27" s="64" t="str">
         <f t="shared" ref="O27:U32" ca="1" si="0">IF(MONTH($O$25)&lt;&gt;MONTH($O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1)),"",$O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1))</f>
@@ -3185,19 +3362,19 @@
       </c>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="1"/>
-      <c r="C28" s="89" t="s">
+      <c r="C28" s="114" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="89"/>
-      <c r="E28" s="89"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="89"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="89"/>
-      <c r="K28" s="89"/>
+      <c r="D28" s="114"/>
+      <c r="E28" s="114"/>
+      <c r="F28" s="114"/>
+      <c r="G28" s="114"/>
+      <c r="H28" s="114"/>
+      <c r="I28" s="114"/>
+      <c r="J28" s="114"/>
+      <c r="K28" s="114"/>
       <c r="M28" s="1"/>
       <c r="O28" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3259,17 +3436,17 @@
       </c>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="1"/>
-      <c r="C29" s="88"/>
-      <c r="D29" s="88"/>
-      <c r="E29" s="88"/>
-      <c r="F29" s="88"/>
-      <c r="G29" s="88"/>
-      <c r="H29" s="88"/>
-      <c r="I29" s="88"/>
-      <c r="J29" s="88"/>
-      <c r="K29" s="88"/>
+      <c r="C29" s="115"/>
+      <c r="D29" s="115"/>
+      <c r="E29" s="115"/>
+      <c r="F29" s="115"/>
+      <c r="G29" s="115"/>
+      <c r="H29" s="115"/>
+      <c r="I29" s="115"/>
+      <c r="J29" s="115"/>
+      <c r="K29" s="115"/>
       <c r="M29" s="1"/>
       <c r="O29" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3331,19 +3508,19 @@
       </c>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="1"/>
-      <c r="C30" s="89" t="s">
+      <c r="C30" s="114" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="89"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="89"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="89"/>
-      <c r="K30" s="89"/>
+      <c r="D30" s="114"/>
+      <c r="E30" s="114"/>
+      <c r="F30" s="114"/>
+      <c r="G30" s="114"/>
+      <c r="H30" s="114"/>
+      <c r="I30" s="114"/>
+      <c r="J30" s="114"/>
+      <c r="K30" s="114"/>
       <c r="M30" s="1"/>
       <c r="O30" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3405,17 +3582,17 @@
       </c>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="1"/>
-      <c r="C31" s="88"/>
-      <c r="D31" s="88"/>
-      <c r="E31" s="88"/>
-      <c r="F31" s="88"/>
-      <c r="G31" s="88"/>
-      <c r="H31" s="88"/>
-      <c r="I31" s="88"/>
-      <c r="J31" s="88"/>
-      <c r="K31" s="88"/>
+      <c r="C31" s="115"/>
+      <c r="D31" s="115"/>
+      <c r="E31" s="115"/>
+      <c r="F31" s="115"/>
+      <c r="G31" s="115"/>
+      <c r="H31" s="115"/>
+      <c r="I31" s="115"/>
+      <c r="J31" s="115"/>
+      <c r="K31" s="115"/>
       <c r="M31" s="1"/>
       <c r="O31" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3477,7 +3654,7 @@
       </c>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.45">
       <c r="A32" s="1"/>
       <c r="M32" s="1"/>
       <c r="O32" s="64">
@@ -3540,7 +3717,7 @@
       </c>
       <c r="AF32" s="1"/>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A33" s="1"/>
       <c r="M33" s="1"/>
       <c r="O33" s="64"/>
@@ -3561,7 +3738,7 @@
       <c r="AD33" s="65"/>
       <c r="AF33" s="1"/>
     </row>
-    <row r="34" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -3595,158 +3772,69 @@
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
     </row>
-    <row r="38" spans="1:32" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D39" s="115" t="s">
+    <row r="38" spans="1:32" ht="12.9" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D39" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="E39" s="116"/>
-      <c r="F39" s="117"/>
-      <c r="G39" s="121">
+      <c r="E39" s="84"/>
+      <c r="F39" s="85"/>
+      <c r="G39" s="89">
         <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
         <v>5</v>
       </c>
-      <c r="H39" s="122"/>
-      <c r="I39" s="115" t="s">
+      <c r="H39" s="90"/>
+      <c r="I39" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="J39" s="125"/>
-      <c r="K39" s="127" t="s">
+      <c r="J39" s="93"/>
+      <c r="K39" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="L39" s="128"/>
-      <c r="M39" s="131">
+      <c r="L39" s="96"/>
+      <c r="M39" s="99">
         <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
-        <v>3.9999999999999982</v>
-      </c>
-      <c r="N39" s="132"/>
-      <c r="O39" s="132"/>
-      <c r="P39" s="132"/>
-      <c r="Q39" s="132"/>
-      <c r="R39" s="133"/>
-      <c r="S39" s="137" t="s">
+        <v>1.0000000000000027</v>
+      </c>
+      <c r="N39" s="100"/>
+      <c r="O39" s="100"/>
+      <c r="P39" s="100"/>
+      <c r="Q39" s="100"/>
+      <c r="R39" s="101"/>
+      <c r="S39" s="105" t="s">
         <v>25</v>
       </c>
-      <c r="T39" s="138"/>
-      <c r="U39" s="138"/>
-      <c r="V39" s="138"/>
-      <c r="W39" s="138"/>
-      <c r="X39" s="139"/>
-    </row>
-    <row r="40" spans="1:32" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="118"/>
-      <c r="E40" s="119"/>
-      <c r="F40" s="120"/>
-      <c r="G40" s="123"/>
-      <c r="H40" s="124"/>
-      <c r="I40" s="118"/>
-      <c r="J40" s="126"/>
-      <c r="K40" s="129"/>
-      <c r="L40" s="130"/>
-      <c r="M40" s="134"/>
-      <c r="N40" s="135"/>
-      <c r="O40" s="135"/>
-      <c r="P40" s="135"/>
-      <c r="Q40" s="135"/>
-      <c r="R40" s="136"/>
-      <c r="S40" s="140"/>
-      <c r="T40" s="141"/>
-      <c r="U40" s="141"/>
-      <c r="V40" s="141"/>
-      <c r="W40" s="141"/>
-      <c r="X40" s="142"/>
+      <c r="T39" s="106"/>
+      <c r="U39" s="106"/>
+      <c r="V39" s="106"/>
+      <c r="W39" s="106"/>
+      <c r="X39" s="107"/>
+    </row>
+    <row r="40" spans="1:32" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D40" s="86"/>
+      <c r="E40" s="87"/>
+      <c r="F40" s="88"/>
+      <c r="G40" s="91"/>
+      <c r="H40" s="92"/>
+      <c r="I40" s="86"/>
+      <c r="J40" s="94"/>
+      <c r="K40" s="97"/>
+      <c r="L40" s="98"/>
+      <c r="M40" s="102"/>
+      <c r="N40" s="103"/>
+      <c r="O40" s="103"/>
+      <c r="P40" s="103"/>
+      <c r="Q40" s="103"/>
+      <c r="R40" s="104"/>
+      <c r="S40" s="108"/>
+      <c r="T40" s="109"/>
+      <c r="U40" s="109"/>
+      <c r="V40" s="109"/>
+      <c r="W40" s="109"/>
+      <c r="X40" s="110"/>
     </row>
   </sheetData>
   <mergeCells count="110">
-    <mergeCell ref="D39:F40"/>
-    <mergeCell ref="G39:H40"/>
-    <mergeCell ref="K39:L40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="S39:X40"/>
-    <mergeCell ref="M39:R40"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="O20:V20"/>
-    <mergeCell ref="C30:K31"/>
-    <mergeCell ref="C2:AD2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="W5:AD5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:V6"/>
-    <mergeCell ref="W6:AD6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="O5:V5"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="W7:AD7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="O8:V8"/>
-    <mergeCell ref="W8:AD8"/>
-    <mergeCell ref="O7:V7"/>
-    <mergeCell ref="W9:AD9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="O11:V11"/>
-    <mergeCell ref="W11:AD11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:V9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="W12:AD12"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="O14:V14"/>
-    <mergeCell ref="W14:AD14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="O12:V12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="W15:AD15"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="O17:V17"/>
-    <mergeCell ref="W17:AD17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="O15:V15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="O16:V16"/>
     <mergeCell ref="W18:AD18"/>
     <mergeCell ref="C25:K26"/>
     <mergeCell ref="O25:U25"/>
@@ -3768,6 +3856,95 @@
     <mergeCell ref="O21:V21"/>
     <mergeCell ref="W21:AD21"/>
     <mergeCell ref="O19:V19"/>
+    <mergeCell ref="W15:AD15"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="O17:V17"/>
+    <mergeCell ref="W17:AD17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="O15:V15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="O16:V16"/>
+    <mergeCell ref="W12:AD12"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O14:V14"/>
+    <mergeCell ref="W14:AD14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="O12:V12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="W9:AD9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="O11:V11"/>
+    <mergeCell ref="W11:AD11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:V9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="W7:AD7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="O8:V8"/>
+    <mergeCell ref="W8:AD8"/>
+    <mergeCell ref="O7:V7"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:V6"/>
+    <mergeCell ref="W6:AD6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="O5:V5"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="C2:AD2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="W5:AD5"/>
+    <mergeCell ref="D39:F40"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="K39:L40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="S39:X40"/>
+    <mergeCell ref="M39:R40"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="O20:V20"/>
+    <mergeCell ref="C30:K31"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 E5 G5 I5 K5:L5 O5 W5 C7 E8 G8 I8 K8:L8 O8 W8 C10 E11 G11 I11 K11:L11 O11 W11 C13 E14 G14 I14 K14:L14 O14 W14 C16 E17 G17 I17 K17:L17 O17 W17">
     <cfRule type="expression" dxfId="11" priority="3">
@@ -3806,25 +3983,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AP40"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.71875" defaultRowHeight="12.6" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="3" width="5.5703125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="5.5703125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="5.5703125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="5.5703125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" style="3" customWidth="1"/>
-    <col min="11" max="14" width="5.5703125" style="3" customWidth="1"/>
-    <col min="15" max="30" width="2.5703125" style="3" customWidth="1"/>
-    <col min="31" max="32" width="5.5703125" style="3" customWidth="1"/>
-    <col min="33" max="33" width="17.140625" style="3" customWidth="1"/>
-    <col min="34" max="34" width="10.42578125" style="3" customWidth="1"/>
-    <col min="35" max="16384" width="8.7109375" style="3"/>
+    <col min="1" max="3" width="5.5546875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="5.5546875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="5.5546875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="15.5546875" style="3" customWidth="1"/>
+    <col min="11" max="14" width="5.5546875" style="3" customWidth="1"/>
+    <col min="15" max="30" width="2.5546875" style="3" customWidth="1"/>
+    <col min="31" max="32" width="5.5546875" style="3" customWidth="1"/>
+    <col min="33" max="33" width="17.1640625" style="3" customWidth="1"/>
+    <col min="34" max="34" width="10.44140625" style="3" customWidth="1"/>
+    <col min="35" max="16384" width="8.71875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" ht="25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3858,42 +4035,42 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.9">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="2.15">
       <c r="A2" s="29"/>
-      <c r="C2" s="113">
+      <c r="C2" s="116">
         <f ca="1">DATE(About!P8,10,1)</f>
         <v>46296</v>
       </c>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
-      <c r="P2" s="113"/>
-      <c r="Q2" s="113"/>
-      <c r="R2" s="113"/>
-      <c r="S2" s="113"/>
-      <c r="T2" s="113"/>
-      <c r="U2" s="113"/>
-      <c r="V2" s="113"/>
-      <c r="W2" s="113"/>
-      <c r="X2" s="113"/>
-      <c r="Y2" s="113"/>
-      <c r="Z2" s="113"/>
-      <c r="AA2" s="113"/>
-      <c r="AB2" s="113"/>
-      <c r="AC2" s="113"/>
-      <c r="AD2" s="113"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="116"/>
+      <c r="P2" s="116"/>
+      <c r="Q2" s="116"/>
+      <c r="R2" s="116"/>
+      <c r="S2" s="116"/>
+      <c r="T2" s="116"/>
+      <c r="U2" s="116"/>
+      <c r="V2" s="116"/>
+      <c r="W2" s="116"/>
+      <c r="X2" s="116"/>
+      <c r="Y2" s="116"/>
+      <c r="Z2" s="116"/>
+      <c r="AA2" s="116"/>
+      <c r="AB2" s="116"/>
+      <c r="AC2" s="116"/>
+      <c r="AD2" s="116"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.9">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="2.15">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -3913,290 +4090,290 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A4" s="35"/>
-      <c r="C4" s="114">
+      <c r="C4" s="117">
         <f ca="1">C5</f>
         <v>46292</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114">
+      <c r="D4" s="117"/>
+      <c r="E4" s="117">
         <f ca="1">E5</f>
         <v>46293</v>
       </c>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114">
+      <c r="F4" s="117"/>
+      <c r="G4" s="117">
         <f ca="1">G5</f>
         <v>46294</v>
       </c>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114">
+      <c r="H4" s="117"/>
+      <c r="I4" s="117">
         <f ca="1">I5</f>
         <v>46295</v>
       </c>
-      <c r="J4" s="114"/>
-      <c r="K4" s="114">
+      <c r="J4" s="117"/>
+      <c r="K4" s="117">
         <f ca="1">K5</f>
         <v>46296</v>
       </c>
-      <c r="L4" s="114"/>
-      <c r="M4" s="114"/>
+      <c r="L4" s="117"/>
+      <c r="M4" s="117"/>
       <c r="N4" s="37"/>
-      <c r="O4" s="114">
+      <c r="O4" s="117">
         <f ca="1">O5</f>
         <v>46297</v>
       </c>
-      <c r="P4" s="114"/>
-      <c r="Q4" s="114"/>
-      <c r="R4" s="114"/>
-      <c r="S4" s="114"/>
-      <c r="T4" s="114"/>
-      <c r="U4" s="114"/>
-      <c r="V4" s="114"/>
-      <c r="W4" s="114">
+      <c r="P4" s="117"/>
+      <c r="Q4" s="117"/>
+      <c r="R4" s="117"/>
+      <c r="S4" s="117"/>
+      <c r="T4" s="117"/>
+      <c r="U4" s="117"/>
+      <c r="V4" s="117"/>
+      <c r="W4" s="117">
         <f ca="1">W5</f>
         <v>46298</v>
       </c>
-      <c r="X4" s="114"/>
-      <c r="Y4" s="114"/>
-      <c r="Z4" s="114"/>
-      <c r="AA4" s="114"/>
-      <c r="AB4" s="114"/>
-      <c r="AC4" s="114"/>
-      <c r="AD4" s="114"/>
+      <c r="X4" s="117"/>
+      <c r="Y4" s="117"/>
+      <c r="Z4" s="117"/>
+      <c r="AA4" s="117"/>
+      <c r="AB4" s="117"/>
+      <c r="AC4" s="117"/>
+      <c r="AD4" s="117"/>
       <c r="AF4" s="38"/>
       <c r="AG4" s="39"/>
       <c r="AH4" s="39"/>
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1"/>
-      <c r="C5" s="92">
+      <c r="C5" s="118">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46292</v>
       </c>
-      <c r="D5" s="93"/>
-      <c r="E5" s="92">
+      <c r="D5" s="120"/>
+      <c r="E5" s="118">
         <f ca="1">C5+1</f>
         <v>46293</v>
       </c>
-      <c r="F5" s="93"/>
-      <c r="G5" s="92">
+      <c r="F5" s="120"/>
+      <c r="G5" s="118">
         <f ca="1">E5+1</f>
         <v>46294</v>
       </c>
-      <c r="H5" s="93"/>
-      <c r="I5" s="92">
+      <c r="H5" s="120"/>
+      <c r="I5" s="118">
         <f ca="1">G5+1</f>
         <v>46295</v>
       </c>
-      <c r="J5" s="93"/>
-      <c r="K5" s="92">
+      <c r="J5" s="120"/>
+      <c r="K5" s="118">
         <f ca="1">I5+1</f>
         <v>46296</v>
       </c>
-      <c r="L5" s="112"/>
-      <c r="M5" s="112"/>
+      <c r="L5" s="119"/>
+      <c r="M5" s="119"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="92">
+      <c r="O5" s="118">
         <f ca="1">K5+1</f>
         <v>46297</v>
       </c>
-      <c r="P5" s="112"/>
-      <c r="Q5" s="112"/>
-      <c r="R5" s="112"/>
-      <c r="S5" s="112"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="112"/>
-      <c r="V5" s="93"/>
-      <c r="W5" s="92">
+      <c r="P5" s="119"/>
+      <c r="Q5" s="119"/>
+      <c r="R5" s="119"/>
+      <c r="S5" s="119"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="120"/>
+      <c r="W5" s="118">
         <f ca="1">O5+1</f>
         <v>46298</v>
       </c>
-      <c r="X5" s="112"/>
-      <c r="Y5" s="112"/>
-      <c r="Z5" s="112"/>
-      <c r="AA5" s="112"/>
-      <c r="AB5" s="112"/>
-      <c r="AC5" s="112"/>
-      <c r="AD5" s="93"/>
+      <c r="X5" s="119"/>
+      <c r="Y5" s="119"/>
+      <c r="Z5" s="119"/>
+      <c r="AA5" s="119"/>
+      <c r="AB5" s="119"/>
+      <c r="AC5" s="119"/>
+      <c r="AD5" s="120"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
       <c r="AI5" s="41"/>
       <c r="AJ5" s="41"/>
     </row>
-    <row r="6" spans="1:36" s="43" customFormat="1" ht="131.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" s="43" customFormat="1" ht="131.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="42"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="105"/>
-      <c r="E6" s="104"/>
-      <c r="F6" s="105"/>
-      <c r="G6" s="104"/>
-      <c r="H6" s="105"/>
-      <c r="I6" s="104"/>
-      <c r="J6" s="105"/>
-      <c r="K6" s="106"/>
-      <c r="L6" s="107"/>
-      <c r="M6" s="107"/>
-      <c r="N6" s="108"/>
-      <c r="O6" s="106"/>
-      <c r="P6" s="107"/>
-      <c r="Q6" s="107"/>
-      <c r="R6" s="107"/>
-      <c r="S6" s="107"/>
-      <c r="T6" s="107"/>
-      <c r="U6" s="107"/>
-      <c r="V6" s="108"/>
-      <c r="W6" s="109" t="s">
+      <c r="C6" s="121"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="121"/>
+      <c r="F6" s="122"/>
+      <c r="G6" s="121"/>
+      <c r="H6" s="122"/>
+      <c r="I6" s="121"/>
+      <c r="J6" s="122"/>
+      <c r="K6" s="123"/>
+      <c r="L6" s="124"/>
+      <c r="M6" s="124"/>
+      <c r="N6" s="125"/>
+      <c r="O6" s="123"/>
+      <c r="P6" s="124"/>
+      <c r="Q6" s="124"/>
+      <c r="R6" s="124"/>
+      <c r="S6" s="124"/>
+      <c r="T6" s="124"/>
+      <c r="U6" s="124"/>
+      <c r="V6" s="125"/>
+      <c r="W6" s="126" t="s">
         <v>19</v>
       </c>
-      <c r="X6" s="110"/>
-      <c r="Y6" s="110"/>
-      <c r="Z6" s="110"/>
-      <c r="AA6" s="110"/>
-      <c r="AB6" s="110"/>
-      <c r="AC6" s="110"/>
-      <c r="AD6" s="111"/>
+      <c r="X6" s="127"/>
+      <c r="Y6" s="127"/>
+      <c r="Z6" s="127"/>
+      <c r="AA6" s="127"/>
+      <c r="AB6" s="127"/>
+      <c r="AC6" s="127"/>
+      <c r="AD6" s="128"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
-    <row r="7" spans="1:36" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" ht="10" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1"/>
-      <c r="C7" s="92">
+      <c r="C7" s="118">
         <f ca="1">W5+1</f>
         <v>46299</v>
       </c>
-      <c r="D7" s="93"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="102"/>
-      <c r="G7" s="101"/>
-      <c r="H7" s="102"/>
-      <c r="I7" s="101"/>
-      <c r="J7" s="102"/>
-      <c r="K7" s="101"/>
-      <c r="L7" s="103"/>
-      <c r="M7" s="103"/>
+      <c r="D7" s="120"/>
+      <c r="E7" s="129"/>
+      <c r="F7" s="130"/>
+      <c r="G7" s="129"/>
+      <c r="H7" s="130"/>
+      <c r="I7" s="129"/>
+      <c r="J7" s="130"/>
+      <c r="K7" s="129"/>
+      <c r="L7" s="131"/>
+      <c r="M7" s="131"/>
       <c r="N7" s="75"/>
-      <c r="O7" s="101"/>
-      <c r="P7" s="103"/>
-      <c r="Q7" s="103"/>
-      <c r="R7" s="103"/>
-      <c r="S7" s="103"/>
-      <c r="T7" s="103"/>
-      <c r="U7" s="103"/>
-      <c r="V7" s="102"/>
-      <c r="W7" s="101"/>
-      <c r="X7" s="103"/>
-      <c r="Y7" s="103"/>
-      <c r="Z7" s="103"/>
-      <c r="AA7" s="103"/>
-      <c r="AB7" s="103"/>
-      <c r="AC7" s="103"/>
-      <c r="AD7" s="102"/>
+      <c r="O7" s="129"/>
+      <c r="P7" s="131"/>
+      <c r="Q7" s="131"/>
+      <c r="R7" s="131"/>
+      <c r="S7" s="131"/>
+      <c r="T7" s="131"/>
+      <c r="U7" s="131"/>
+      <c r="V7" s="130"/>
+      <c r="W7" s="129"/>
+      <c r="X7" s="131"/>
+      <c r="Y7" s="131"/>
+      <c r="Z7" s="131"/>
+      <c r="AA7" s="131"/>
+      <c r="AB7" s="131"/>
+      <c r="AC7" s="131"/>
+      <c r="AD7" s="130"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="4"/>
-      <c r="C8" s="92"/>
-      <c r="D8" s="93"/>
-      <c r="E8" s="94">
+      <c r="C8" s="118"/>
+      <c r="D8" s="120"/>
+      <c r="E8" s="132">
         <f ca="1">C7+1</f>
         <v>46300</v>
       </c>
-      <c r="F8" s="95"/>
-      <c r="G8" s="94">
+      <c r="F8" s="133"/>
+      <c r="G8" s="132">
         <f ca="1">E8+1</f>
         <v>46301</v>
       </c>
-      <c r="H8" s="95"/>
-      <c r="I8" s="94">
+      <c r="H8" s="133"/>
+      <c r="I8" s="132">
         <f ca="1">G8+1</f>
         <v>46302</v>
       </c>
-      <c r="J8" s="95"/>
-      <c r="K8" s="94">
+      <c r="J8" s="133"/>
+      <c r="K8" s="132">
         <f ca="1">I8+1</f>
         <v>46303</v>
       </c>
-      <c r="L8" s="96"/>
-      <c r="M8" s="96"/>
+      <c r="L8" s="134"/>
+      <c r="M8" s="134"/>
       <c r="N8" s="50"/>
-      <c r="O8" s="94">
+      <c r="O8" s="132">
         <f ca="1">K8+1</f>
         <v>46304</v>
       </c>
-      <c r="P8" s="96"/>
-      <c r="Q8" s="96"/>
-      <c r="R8" s="96"/>
-      <c r="S8" s="96"/>
-      <c r="T8" s="96"/>
-      <c r="U8" s="96"/>
-      <c r="V8" s="95"/>
-      <c r="W8" s="94">
+      <c r="P8" s="134"/>
+      <c r="Q8" s="134"/>
+      <c r="R8" s="134"/>
+      <c r="S8" s="134"/>
+      <c r="T8" s="134"/>
+      <c r="U8" s="134"/>
+      <c r="V8" s="133"/>
+      <c r="W8" s="132">
         <f ca="1">O8+1</f>
         <v>46305</v>
       </c>
-      <c r="X8" s="96"/>
-      <c r="Y8" s="96"/>
-      <c r="Z8" s="96"/>
-      <c r="AA8" s="96"/>
-      <c r="AB8" s="96"/>
-      <c r="AC8" s="96"/>
-      <c r="AD8" s="95"/>
+      <c r="X8" s="134"/>
+      <c r="Y8" s="134"/>
+      <c r="Z8" s="134"/>
+      <c r="AA8" s="134"/>
+      <c r="AB8" s="134"/>
+      <c r="AC8" s="134"/>
+      <c r="AD8" s="133"/>
       <c r="AF8" s="4"/>
     </row>
-    <row r="9" spans="1:36" s="43" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" s="43" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="42"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="85"/>
-      <c r="E9" s="83" t="s">
+      <c r="C9" s="123"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="126" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="85"/>
-      <c r="G9" s="83" t="s">
+      <c r="F9" s="128"/>
+      <c r="G9" s="126" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="85"/>
-      <c r="I9" s="83" t="s">
-        <v>37</v>
-      </c>
-      <c r="J9" s="85"/>
-      <c r="K9" s="83" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9" s="84"/>
-      <c r="M9" s="84"/>
-      <c r="N9" s="85"/>
-      <c r="O9" s="83" t="s">
-        <v>48</v>
-      </c>
-      <c r="P9" s="84"/>
-      <c r="Q9" s="84"/>
-      <c r="R9" s="84"/>
-      <c r="S9" s="84"/>
-      <c r="T9" s="84"/>
-      <c r="U9" s="84"/>
-      <c r="V9" s="85"/>
-      <c r="W9" s="83"/>
-      <c r="X9" s="84"/>
-      <c r="Y9" s="84"/>
-      <c r="Z9" s="84"/>
-      <c r="AA9" s="84"/>
-      <c r="AB9" s="84"/>
-      <c r="AC9" s="84"/>
-      <c r="AD9" s="85"/>
+      <c r="H9" s="128"/>
+      <c r="I9" s="123" t="s">
+        <v>34</v>
+      </c>
+      <c r="J9" s="125"/>
+      <c r="K9" s="135"/>
+      <c r="L9" s="136"/>
+      <c r="M9" s="136"/>
+      <c r="N9" s="137"/>
+      <c r="O9" s="135" t="s">
+        <v>50</v>
+      </c>
+      <c r="P9" s="136"/>
+      <c r="Q9" s="136"/>
+      <c r="R9" s="136"/>
+      <c r="S9" s="136"/>
+      <c r="T9" s="136"/>
+      <c r="U9" s="136"/>
+      <c r="V9" s="137"/>
+      <c r="W9" s="135" t="s">
+        <v>51</v>
+      </c>
+      <c r="X9" s="136"/>
+      <c r="Y9" s="136"/>
+      <c r="Z9" s="136"/>
+      <c r="AA9" s="136"/>
+      <c r="AB9" s="136"/>
+      <c r="AC9" s="136"/>
+      <c r="AD9" s="137"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
-    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" s="43" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="42"/>
-      <c r="C10" s="92">
+      <c r="C10" s="118">
         <f ca="1">W8+1</f>
         <v>46306</v>
       </c>
-      <c r="D10" s="93"/>
+      <c r="D10" s="120"/>
       <c r="E10" s="45"/>
       <c r="F10" s="75"/>
       <c r="G10" s="45"/>
@@ -4226,111 +4403,111 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="42"/>
     </row>
-    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="4"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="93"/>
-      <c r="E11" s="94">
+      <c r="C11" s="118"/>
+      <c r="D11" s="120"/>
+      <c r="E11" s="132">
         <f ca="1">C10+1</f>
         <v>46307</v>
       </c>
-      <c r="F11" s="95"/>
-      <c r="G11" s="94">
+      <c r="F11" s="133"/>
+      <c r="G11" s="132">
         <f ca="1">E11+1</f>
         <v>46308</v>
       </c>
-      <c r="H11" s="95"/>
-      <c r="I11" s="94">
+      <c r="H11" s="133"/>
+      <c r="I11" s="132">
         <f ca="1">G11+1</f>
         <v>46309</v>
       </c>
-      <c r="J11" s="95"/>
-      <c r="K11" s="94">
+      <c r="J11" s="133"/>
+      <c r="K11" s="132">
         <f ca="1">I11+1</f>
         <v>46310</v>
       </c>
-      <c r="L11" s="96"/>
-      <c r="M11" s="96"/>
+      <c r="L11" s="134"/>
+      <c r="M11" s="134"/>
       <c r="N11" s="50"/>
-      <c r="O11" s="94">
+      <c r="O11" s="132">
         <f ca="1">K11+1</f>
         <v>46311</v>
       </c>
-      <c r="P11" s="96"/>
-      <c r="Q11" s="96"/>
-      <c r="R11" s="96"/>
-      <c r="S11" s="96"/>
-      <c r="T11" s="96"/>
-      <c r="U11" s="96"/>
-      <c r="V11" s="95"/>
-      <c r="W11" s="94">
+      <c r="P11" s="134"/>
+      <c r="Q11" s="134"/>
+      <c r="R11" s="134"/>
+      <c r="S11" s="134"/>
+      <c r="T11" s="134"/>
+      <c r="U11" s="134"/>
+      <c r="V11" s="133"/>
+      <c r="W11" s="132">
         <f ca="1">O11+1</f>
         <v>46312</v>
       </c>
-      <c r="X11" s="96"/>
-      <c r="Y11" s="96"/>
-      <c r="Z11" s="96"/>
-      <c r="AA11" s="96"/>
-      <c r="AB11" s="96"/>
-      <c r="AC11" s="96"/>
-      <c r="AD11" s="95"/>
+      <c r="X11" s="134"/>
+      <c r="Y11" s="134"/>
+      <c r="Z11" s="134"/>
+      <c r="AA11" s="134"/>
+      <c r="AB11" s="134"/>
+      <c r="AC11" s="134"/>
+      <c r="AD11" s="133"/>
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:36" s="43" customFormat="1" ht="134.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" s="43" customFormat="1" ht="169.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="42"/>
-      <c r="C12" s="163" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="164"/>
-      <c r="E12" s="100" t="s">
-        <v>39</v>
-      </c>
-      <c r="F12" s="85"/>
-      <c r="G12" s="83" t="s">
-        <v>38</v>
-      </c>
-      <c r="H12" s="85"/>
-      <c r="I12" s="163" t="s">
-        <v>59</v>
-      </c>
-      <c r="J12" s="164"/>
-      <c r="K12" s="100" t="s">
+      <c r="C12" s="139" t="s">
         <v>40</v>
       </c>
-      <c r="L12" s="84"/>
-      <c r="M12" s="84"/>
-      <c r="N12" s="85"/>
-      <c r="O12" s="83" t="s">
-        <v>58</v>
-      </c>
-      <c r="P12" s="84"/>
-      <c r="Q12" s="84"/>
-      <c r="R12" s="84"/>
-      <c r="S12" s="84"/>
-      <c r="T12" s="84"/>
-      <c r="U12" s="84"/>
-      <c r="V12" s="85"/>
-      <c r="W12" s="99" t="s">
-        <v>30</v>
-      </c>
-      <c r="X12" s="84"/>
-      <c r="Y12" s="84"/>
-      <c r="Z12" s="84"/>
-      <c r="AA12" s="84"/>
-      <c r="AB12" s="84"/>
-      <c r="AC12" s="84"/>
-      <c r="AD12" s="85"/>
+      <c r="D12" s="140"/>
+      <c r="E12" s="166" t="s">
+        <v>53</v>
+      </c>
+      <c r="F12" s="137"/>
+      <c r="G12" s="135" t="s">
+        <v>35</v>
+      </c>
+      <c r="H12" s="137"/>
+      <c r="I12" s="139" t="s">
+        <v>48</v>
+      </c>
+      <c r="J12" s="140"/>
+      <c r="K12" s="141" t="s">
+        <v>36</v>
+      </c>
+      <c r="L12" s="136"/>
+      <c r="M12" s="136"/>
+      <c r="N12" s="137"/>
+      <c r="O12" s="135" t="s">
+        <v>54</v>
+      </c>
+      <c r="P12" s="136"/>
+      <c r="Q12" s="136"/>
+      <c r="R12" s="136"/>
+      <c r="S12" s="136"/>
+      <c r="T12" s="136"/>
+      <c r="U12" s="136"/>
+      <c r="V12" s="137"/>
+      <c r="W12" s="138" t="s">
+        <v>29</v>
+      </c>
+      <c r="X12" s="136"/>
+      <c r="Y12" s="136"/>
+      <c r="Z12" s="136"/>
+      <c r="AA12" s="136"/>
+      <c r="AB12" s="136"/>
+      <c r="AC12" s="136"/>
+      <c r="AD12" s="137"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
-    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" s="43" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="42"/>
-      <c r="C13" s="92">
+      <c r="C13" s="118">
         <f ca="1">W11+1</f>
         <v>46313</v>
       </c>
-      <c r="D13" s="93"/>
+      <c r="D13" s="120"/>
       <c r="E13" s="45"/>
       <c r="F13" s="75"/>
       <c r="G13" s="45"/>
@@ -4360,110 +4537,110 @@
       <c r="AE13" s="7"/>
       <c r="AF13" s="42"/>
     </row>
-    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" s="7" customFormat="1" ht="21.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="4"/>
-      <c r="C14" s="92"/>
-      <c r="D14" s="93"/>
-      <c r="E14" s="94">
+      <c r="C14" s="118"/>
+      <c r="D14" s="120"/>
+      <c r="E14" s="132">
         <f ca="1">C13+1</f>
         <v>46314</v>
       </c>
-      <c r="F14" s="95"/>
-      <c r="G14" s="94">
+      <c r="F14" s="133"/>
+      <c r="G14" s="132">
         <f ca="1">E14+1</f>
         <v>46315</v>
       </c>
-      <c r="H14" s="95"/>
-      <c r="I14" s="94">
+      <c r="H14" s="133"/>
+      <c r="I14" s="132">
         <f ca="1">G14+1</f>
         <v>46316</v>
       </c>
-      <c r="J14" s="95"/>
-      <c r="K14" s="94">
+      <c r="J14" s="133"/>
+      <c r="K14" s="132">
         <f ca="1">I14+1</f>
         <v>46317</v>
       </c>
-      <c r="L14" s="96"/>
-      <c r="M14" s="96"/>
+      <c r="L14" s="134"/>
+      <c r="M14" s="134"/>
       <c r="N14" s="50"/>
-      <c r="O14" s="94">
+      <c r="O14" s="132">
         <f ca="1">K14+1</f>
         <v>46318</v>
       </c>
-      <c r="P14" s="96"/>
-      <c r="Q14" s="96"/>
-      <c r="R14" s="96"/>
-      <c r="S14" s="96"/>
-      <c r="T14" s="96"/>
-      <c r="U14" s="96"/>
-      <c r="V14" s="95"/>
-      <c r="W14" s="94">
+      <c r="P14" s="134"/>
+      <c r="Q14" s="134"/>
+      <c r="R14" s="134"/>
+      <c r="S14" s="134"/>
+      <c r="T14" s="134"/>
+      <c r="U14" s="134"/>
+      <c r="V14" s="133"/>
+      <c r="W14" s="132">
         <f ca="1">O14+1</f>
         <v>46319</v>
       </c>
-      <c r="X14" s="96"/>
-      <c r="Y14" s="96"/>
-      <c r="Z14" s="96"/>
-      <c r="AA14" s="96"/>
-      <c r="AB14" s="96"/>
-      <c r="AC14" s="96"/>
-      <c r="AD14" s="95"/>
+      <c r="X14" s="134"/>
+      <c r="Y14" s="134"/>
+      <c r="Z14" s="134"/>
+      <c r="AA14" s="134"/>
+      <c r="AB14" s="134"/>
+      <c r="AC14" s="134"/>
+      <c r="AD14" s="133"/>
       <c r="AF14" s="4"/>
     </row>
-    <row r="15" spans="1:36" s="43" customFormat="1" ht="140.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" s="43" customFormat="1" ht="171" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="42"/>
-      <c r="C15" s="99" t="s">
+      <c r="C15" s="138" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="137"/>
+      <c r="E15" s="139" t="s">
+        <v>41</v>
+      </c>
+      <c r="F15" s="140"/>
+      <c r="G15" s="139" t="s">
+        <v>42</v>
+      </c>
+      <c r="H15" s="140"/>
+      <c r="I15" s="138" t="s">
+        <v>52</v>
+      </c>
+      <c r="J15" s="137"/>
+      <c r="K15" s="139" t="s">
+        <v>56</v>
+      </c>
+      <c r="L15" s="142"/>
+      <c r="M15" s="142"/>
+      <c r="N15" s="140"/>
+      <c r="O15" s="135" t="s">
+        <v>55</v>
+      </c>
+      <c r="P15" s="136"/>
+      <c r="Q15" s="136"/>
+      <c r="R15" s="136"/>
+      <c r="S15" s="136"/>
+      <c r="T15" s="136"/>
+      <c r="U15" s="136"/>
+      <c r="V15" s="137"/>
+      <c r="W15" s="138" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="85"/>
-      <c r="E15" s="163" t="s">
-        <v>50</v>
-      </c>
-      <c r="F15" s="164"/>
-      <c r="G15" s="163" t="s">
-        <v>51</v>
-      </c>
-      <c r="H15" s="164"/>
-      <c r="I15" s="99" t="s">
-        <v>34</v>
-      </c>
-      <c r="J15" s="85"/>
-      <c r="K15" s="163" t="s">
-        <v>60</v>
-      </c>
-      <c r="L15" s="165"/>
-      <c r="M15" s="165"/>
-      <c r="N15" s="164"/>
-      <c r="O15" s="83" t="s">
-        <v>32</v>
-      </c>
-      <c r="P15" s="84"/>
-      <c r="Q15" s="84"/>
-      <c r="R15" s="84"/>
-      <c r="S15" s="84"/>
-      <c r="T15" s="84"/>
-      <c r="U15" s="84"/>
-      <c r="V15" s="85"/>
-      <c r="W15" s="99" t="s">
-        <v>33</v>
-      </c>
-      <c r="X15" s="84"/>
-      <c r="Y15" s="84"/>
-      <c r="Z15" s="84"/>
-      <c r="AA15" s="84"/>
-      <c r="AB15" s="84"/>
-      <c r="AC15" s="84"/>
-      <c r="AD15" s="85"/>
+      <c r="X15" s="136"/>
+      <c r="Y15" s="136"/>
+      <c r="Z15" s="136"/>
+      <c r="AA15" s="136"/>
+      <c r="AB15" s="136"/>
+      <c r="AC15" s="136"/>
+      <c r="AD15" s="137"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
-    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" s="43" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="42"/>
-      <c r="C16" s="92">
+      <c r="C16" s="118">
         <f ca="1">W14+1</f>
         <v>46320</v>
       </c>
-      <c r="D16" s="93"/>
+      <c r="D16" s="120"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
@@ -4493,109 +4670,109 @@
       <c r="AE16" s="7"/>
       <c r="AF16" s="42"/>
     </row>
-    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4"/>
-      <c r="C17" s="92"/>
-      <c r="D17" s="93"/>
-      <c r="E17" s="94">
+      <c r="C17" s="118"/>
+      <c r="D17" s="120"/>
+      <c r="E17" s="132">
         <f ca="1">C16+1</f>
         <v>46321</v>
       </c>
-      <c r="F17" s="95"/>
-      <c r="G17" s="94">
+      <c r="F17" s="133"/>
+      <c r="G17" s="132">
         <f ca="1">E17+1</f>
         <v>46322</v>
       </c>
-      <c r="H17" s="95"/>
-      <c r="I17" s="94">
+      <c r="H17" s="133"/>
+      <c r="I17" s="132">
         <f ca="1">G17+1</f>
         <v>46323</v>
       </c>
-      <c r="J17" s="95"/>
-      <c r="K17" s="94">
+      <c r="J17" s="133"/>
+      <c r="K17" s="132">
         <f ca="1">I17+1</f>
         <v>46324</v>
       </c>
-      <c r="L17" s="96"/>
-      <c r="M17" s="96"/>
+      <c r="L17" s="134"/>
+      <c r="M17" s="134"/>
       <c r="N17" s="50"/>
-      <c r="O17" s="94">
+      <c r="O17" s="132">
         <f ca="1">K17+1</f>
         <v>46325</v>
       </c>
-      <c r="P17" s="96"/>
-      <c r="Q17" s="96"/>
-      <c r="R17" s="96"/>
-      <c r="S17" s="96"/>
-      <c r="T17" s="96"/>
-      <c r="U17" s="96"/>
-      <c r="V17" s="95"/>
-      <c r="W17" s="94">
+      <c r="P17" s="134"/>
+      <c r="Q17" s="134"/>
+      <c r="R17" s="134"/>
+      <c r="S17" s="134"/>
+      <c r="T17" s="134"/>
+      <c r="U17" s="134"/>
+      <c r="V17" s="133"/>
+      <c r="W17" s="132">
         <f ca="1">O17+1</f>
         <v>46326</v>
       </c>
-      <c r="X17" s="96"/>
-      <c r="Y17" s="96"/>
-      <c r="Z17" s="96"/>
-      <c r="AA17" s="96"/>
-      <c r="AB17" s="96"/>
-      <c r="AC17" s="96"/>
-      <c r="AD17" s="95"/>
+      <c r="X17" s="134"/>
+      <c r="Y17" s="134"/>
+      <c r="Z17" s="134"/>
+      <c r="AA17" s="134"/>
+      <c r="AB17" s="134"/>
+      <c r="AC17" s="134"/>
+      <c r="AD17" s="133"/>
       <c r="AF17" s="4"/>
     </row>
-    <row r="18" spans="1:42" s="43" customFormat="1" ht="149.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:42" s="43" customFormat="1" ht="171" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="42"/>
-      <c r="C18" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="D18" s="164"/>
-      <c r="E18" s="83" t="s">
-        <v>45</v>
-      </c>
-      <c r="F18" s="85"/>
-      <c r="G18" s="163" t="s">
-        <v>46</v>
-      </c>
-      <c r="H18" s="164"/>
-      <c r="I18" s="163" t="s">
-        <v>52</v>
-      </c>
-      <c r="J18" s="164"/>
-      <c r="K18" s="91" t="s">
-        <v>35</v>
-      </c>
-      <c r="L18" s="84"/>
-      <c r="M18" s="84"/>
+      <c r="C18" s="139" t="s">
+        <v>49</v>
+      </c>
+      <c r="D18" s="140"/>
+      <c r="E18" s="135" t="s">
+        <v>57</v>
+      </c>
+      <c r="F18" s="137"/>
+      <c r="G18" s="139" t="s">
+        <v>39</v>
+      </c>
+      <c r="H18" s="140"/>
+      <c r="I18" s="139" t="s">
+        <v>43</v>
+      </c>
+      <c r="J18" s="140"/>
+      <c r="K18" s="145" t="s">
+        <v>32</v>
+      </c>
+      <c r="L18" s="136"/>
+      <c r="M18" s="136"/>
       <c r="N18" s="82"/>
-      <c r="O18" s="163" t="s">
-        <v>53</v>
-      </c>
-      <c r="P18" s="165"/>
-      <c r="Q18" s="165"/>
-      <c r="R18" s="165"/>
-      <c r="S18" s="165"/>
-      <c r="T18" s="165"/>
-      <c r="U18" s="165"/>
-      <c r="V18" s="164"/>
-      <c r="W18" s="83"/>
-      <c r="X18" s="84"/>
-      <c r="Y18" s="84"/>
-      <c r="Z18" s="84"/>
-      <c r="AA18" s="84"/>
-      <c r="AB18" s="84"/>
-      <c r="AC18" s="84"/>
-      <c r="AD18" s="85"/>
+      <c r="O18" s="139" t="s">
+        <v>44</v>
+      </c>
+      <c r="P18" s="142"/>
+      <c r="Q18" s="142"/>
+      <c r="R18" s="142"/>
+      <c r="S18" s="142"/>
+      <c r="T18" s="142"/>
+      <c r="U18" s="142"/>
+      <c r="V18" s="140"/>
+      <c r="W18" s="135"/>
+      <c r="X18" s="136"/>
+      <c r="Y18" s="136"/>
+      <c r="Z18" s="136"/>
+      <c r="AA18" s="136"/>
+      <c r="AB18" s="136"/>
+      <c r="AC18" s="136"/>
+      <c r="AD18" s="137"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
-    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:42" s="43" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="42"/>
-      <c r="C19" s="92">
+      <c r="C19" s="118">
         <f ca="1">W17+1</f>
         <v>46327</v>
       </c>
-      <c r="D19" s="93"/>
+      <c r="D19" s="120"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
@@ -4625,91 +4802,91 @@
       <c r="AE19" s="7"/>
       <c r="AF19" s="42"/>
     </row>
-    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4"/>
-      <c r="C20" s="92"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="94">
+      <c r="C20" s="118"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="132">
         <f ca="1">C19+1</f>
         <v>46328</v>
       </c>
-      <c r="F20" s="95"/>
-      <c r="G20" s="94">
+      <c r="F20" s="133"/>
+      <c r="G20" s="132">
         <f ca="1">E20+1</f>
         <v>46329</v>
       </c>
-      <c r="H20" s="95"/>
-      <c r="I20" s="94">
+      <c r="H20" s="133"/>
+      <c r="I20" s="132">
         <f ca="1">G20+1</f>
         <v>46330</v>
       </c>
-      <c r="J20" s="95"/>
-      <c r="K20" s="94">
+      <c r="J20" s="133"/>
+      <c r="K20" s="132">
         <f ca="1">I20+1</f>
         <v>46331</v>
       </c>
-      <c r="L20" s="96"/>
-      <c r="M20" s="96"/>
+      <c r="L20" s="134"/>
+      <c r="M20" s="134"/>
       <c r="N20" s="50"/>
-      <c r="O20" s="94">
+      <c r="O20" s="132">
         <f ca="1">K20+1</f>
         <v>46332</v>
       </c>
-      <c r="P20" s="96"/>
-      <c r="Q20" s="96"/>
-      <c r="R20" s="96"/>
-      <c r="S20" s="96"/>
-      <c r="T20" s="96"/>
-      <c r="U20" s="96"/>
-      <c r="V20" s="95"/>
-      <c r="W20" s="94">
+      <c r="P20" s="134"/>
+      <c r="Q20" s="134"/>
+      <c r="R20" s="134"/>
+      <c r="S20" s="134"/>
+      <c r="T20" s="134"/>
+      <c r="U20" s="134"/>
+      <c r="V20" s="133"/>
+      <c r="W20" s="132">
         <f ca="1">O20+1</f>
         <v>46333</v>
       </c>
-      <c r="X20" s="96"/>
-      <c r="Y20" s="96"/>
-      <c r="Z20" s="96"/>
-      <c r="AA20" s="96"/>
-      <c r="AB20" s="96"/>
-      <c r="AC20" s="96"/>
-      <c r="AD20" s="95"/>
+      <c r="X20" s="134"/>
+      <c r="Y20" s="134"/>
+      <c r="Z20" s="134"/>
+      <c r="AA20" s="134"/>
+      <c r="AB20" s="134"/>
+      <c r="AC20" s="134"/>
+      <c r="AD20" s="133"/>
       <c r="AF20" s="4"/>
     </row>
-    <row r="21" spans="1:42" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:42" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="42"/>
-      <c r="C21" s="97"/>
-      <c r="D21" s="98"/>
-      <c r="E21" s="97"/>
-      <c r="F21" s="98"/>
-      <c r="G21" s="97"/>
-      <c r="H21" s="98"/>
-      <c r="I21" s="97"/>
-      <c r="J21" s="98"/>
-      <c r="K21" s="97"/>
-      <c r="L21" s="143"/>
-      <c r="M21" s="143"/>
+      <c r="C21" s="111"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="113"/>
+      <c r="K21" s="111"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
       <c r="N21" s="44"/>
-      <c r="O21" s="97"/>
-      <c r="P21" s="143"/>
-      <c r="Q21" s="143"/>
-      <c r="R21" s="143"/>
-      <c r="S21" s="143"/>
-      <c r="T21" s="143"/>
-      <c r="U21" s="143"/>
-      <c r="V21" s="98"/>
-      <c r="W21" s="97"/>
-      <c r="X21" s="143"/>
-      <c r="Y21" s="143"/>
-      <c r="Z21" s="143"/>
-      <c r="AA21" s="143"/>
-      <c r="AB21" s="143"/>
-      <c r="AC21" s="143"/>
-      <c r="AD21" s="98"/>
+      <c r="O21" s="111"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="112"/>
+      <c r="R21" s="112"/>
+      <c r="S21" s="112"/>
+      <c r="T21" s="112"/>
+      <c r="U21" s="112"/>
+      <c r="V21" s="113"/>
+      <c r="W21" s="111"/>
+      <c r="X21" s="112"/>
+      <c r="Y21" s="112"/>
+      <c r="Z21" s="112"/>
+      <c r="AA21" s="112"/>
+      <c r="AB21" s="112"/>
+      <c r="AC21" s="112"/>
+      <c r="AD21" s="113"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
     </row>
-    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:42" s="7" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="4"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52"/>
@@ -4741,7 +4918,7 @@
       <c r="AD22" s="55"/>
       <c r="AF22" s="4"/>
     </row>
-    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:42" s="7" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="56"/>
@@ -4775,61 +4952,61 @@
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
     </row>
-    <row r="24" spans="1:42" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:42" ht="25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="1"/>
       <c r="M24" s="1"/>
       <c r="AF24" s="1"/>
     </row>
-    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="1"/>
-      <c r="C25" s="86" t="s">
+      <c r="C25" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="86"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="86"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="86"/>
-      <c r="J25" s="86"/>
-      <c r="K25" s="86"/>
+      <c r="D25" s="143"/>
+      <c r="E25" s="143"/>
+      <c r="F25" s="143"/>
+      <c r="G25" s="143"/>
+      <c r="H25" s="143"/>
+      <c r="I25" s="143"/>
+      <c r="J25" s="143"/>
+      <c r="K25" s="143"/>
       <c r="L25" s="60"/>
       <c r="M25" s="1"/>
-      <c r="O25" s="87">
+      <c r="O25" s="144">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)-1,1)</f>
         <v>46266</v>
       </c>
-      <c r="P25" s="87"/>
-      <c r="Q25" s="87"/>
-      <c r="R25" s="87"/>
-      <c r="S25" s="87"/>
-      <c r="T25" s="87"/>
-      <c r="U25" s="87"/>
+      <c r="P25" s="144"/>
+      <c r="Q25" s="144"/>
+      <c r="R25" s="144"/>
+      <c r="S25" s="144"/>
+      <c r="T25" s="144"/>
+      <c r="U25" s="144"/>
       <c r="V25" s="61"/>
       <c r="W25" s="61"/>
-      <c r="X25" s="87">
+      <c r="X25" s="144">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)+1,1)</f>
         <v>46327</v>
       </c>
-      <c r="Y25" s="87"/>
-      <c r="Z25" s="87"/>
-      <c r="AA25" s="87"/>
-      <c r="AB25" s="87"/>
-      <c r="AC25" s="87"/>
-      <c r="AD25" s="87"/>
+      <c r="Y25" s="144"/>
+      <c r="Z25" s="144"/>
+      <c r="AA25" s="144"/>
+      <c r="AB25" s="144"/>
+      <c r="AC25" s="144"/>
+      <c r="AD25" s="144"/>
       <c r="AF25" s="1"/>
     </row>
-    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="1"/>
-      <c r="C26" s="86"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="86"/>
-      <c r="G26" s="86"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="86"/>
-      <c r="J26" s="86"/>
-      <c r="K26" s="86"/>
+      <c r="C26" s="143"/>
+      <c r="D26" s="143"/>
+      <c r="E26" s="143"/>
+      <c r="F26" s="143"/>
+      <c r="G26" s="143"/>
+      <c r="H26" s="143"/>
+      <c r="I26" s="143"/>
+      <c r="J26" s="143"/>
+      <c r="K26" s="143"/>
       <c r="L26" s="60"/>
       <c r="M26" s="1"/>
       <c r="O26" s="62" t="str">
@@ -4892,17 +5069,17 @@
       </c>
       <c r="AF26" s="1"/>
     </row>
-    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="1"/>
-      <c r="C27" s="88"/>
-      <c r="D27" s="88"/>
-      <c r="E27" s="88"/>
-      <c r="F27" s="88"/>
-      <c r="G27" s="88"/>
-      <c r="H27" s="88"/>
-      <c r="I27" s="88"/>
-      <c r="J27" s="88"/>
-      <c r="K27" s="88"/>
+      <c r="C27" s="115"/>
+      <c r="D27" s="115"/>
+      <c r="E27" s="115"/>
+      <c r="F27" s="115"/>
+      <c r="G27" s="115"/>
+      <c r="H27" s="115"/>
+      <c r="I27" s="115"/>
+      <c r="J27" s="115"/>
+      <c r="K27" s="115"/>
       <c r="M27" s="1"/>
       <c r="O27" s="64" t="str">
         <f t="shared" ref="O27:U32" ca="1" si="0">IF(MONTH($O$25)&lt;&gt;MONTH($O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1)),"",$O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1))</f>
@@ -4964,17 +5141,17 @@
       </c>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="1"/>
-      <c r="C28" s="89"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="89"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="89"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="89"/>
-      <c r="K28" s="89"/>
+      <c r="C28" s="114"/>
+      <c r="D28" s="114"/>
+      <c r="E28" s="114"/>
+      <c r="F28" s="114"/>
+      <c r="G28" s="114"/>
+      <c r="H28" s="114"/>
+      <c r="I28" s="114"/>
+      <c r="J28" s="114"/>
+      <c r="K28" s="114"/>
       <c r="M28" s="1"/>
       <c r="O28" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -5036,17 +5213,17 @@
       </c>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="1"/>
-      <c r="C29" s="88"/>
-      <c r="D29" s="88"/>
-      <c r="E29" s="88"/>
-      <c r="F29" s="88"/>
-      <c r="G29" s="88"/>
-      <c r="H29" s="88"/>
-      <c r="I29" s="88"/>
-      <c r="J29" s="88"/>
-      <c r="K29" s="88"/>
+      <c r="C29" s="115"/>
+      <c r="D29" s="115"/>
+      <c r="E29" s="115"/>
+      <c r="F29" s="115"/>
+      <c r="G29" s="115"/>
+      <c r="H29" s="115"/>
+      <c r="I29" s="115"/>
+      <c r="J29" s="115"/>
+      <c r="K29" s="115"/>
       <c r="M29" s="1"/>
       <c r="O29" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -5108,17 +5285,17 @@
       </c>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="1"/>
-      <c r="C30" s="89"/>
-      <c r="D30" s="89"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="89"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="89"/>
-      <c r="K30" s="89"/>
+      <c r="C30" s="114"/>
+      <c r="D30" s="114"/>
+      <c r="E30" s="114"/>
+      <c r="F30" s="114"/>
+      <c r="G30" s="114"/>
+      <c r="H30" s="114"/>
+      <c r="I30" s="114"/>
+      <c r="J30" s="114"/>
+      <c r="K30" s="114"/>
       <c r="M30" s="1"/>
       <c r="O30" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -5180,17 +5357,17 @@
       </c>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="1"/>
-      <c r="C31" s="88"/>
-      <c r="D31" s="88"/>
-      <c r="E31" s="88"/>
-      <c r="F31" s="88"/>
-      <c r="G31" s="88"/>
-      <c r="H31" s="88"/>
-      <c r="I31" s="88"/>
-      <c r="J31" s="88"/>
-      <c r="K31" s="88"/>
+      <c r="C31" s="115"/>
+      <c r="D31" s="115"/>
+      <c r="E31" s="115"/>
+      <c r="F31" s="115"/>
+      <c r="G31" s="115"/>
+      <c r="H31" s="115"/>
+      <c r="I31" s="115"/>
+      <c r="J31" s="115"/>
+      <c r="K31" s="115"/>
       <c r="M31" s="1"/>
       <c r="O31" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -5252,7 +5429,7 @@
       </c>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.45">
       <c r="A32" s="1"/>
       <c r="M32" s="1"/>
       <c r="O32" s="64" t="str">
@@ -5315,7 +5492,7 @@
       </c>
       <c r="AF32" s="1"/>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A33" s="1"/>
       <c r="M33" s="1"/>
       <c r="O33" s="64"/>
@@ -5336,7 +5513,7 @@
       <c r="AD33" s="65"/>
       <c r="AF33" s="1"/>
     </row>
-    <row r="34" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -5370,156 +5547,69 @@
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
     </row>
-    <row r="38" spans="1:32" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D39" s="115" t="s">
+    <row r="38" spans="1:32" ht="12.9" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D39" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="E39" s="116"/>
-      <c r="F39" s="117"/>
-      <c r="G39" s="121">
+      <c r="E39" s="84"/>
+      <c r="F39" s="85"/>
+      <c r="G39" s="89">
         <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
         <v>5</v>
       </c>
-      <c r="H39" s="122"/>
-      <c r="I39" s="115" t="s">
+      <c r="H39" s="90"/>
+      <c r="I39" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="J39" s="125"/>
-      <c r="K39" s="127" t="s">
+      <c r="J39" s="93"/>
+      <c r="K39" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="L39" s="128"/>
-      <c r="M39" s="131">
+      <c r="L39" s="96"/>
+      <c r="M39" s="99">
         <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
-        <v>3.9999999999999982</v>
-      </c>
-      <c r="N39" s="132"/>
-      <c r="O39" s="132"/>
-      <c r="P39" s="132"/>
-      <c r="Q39" s="132"/>
-      <c r="R39" s="133"/>
-      <c r="S39" s="137" t="s">
+        <v>1.0000000000000027</v>
+      </c>
+      <c r="N39" s="100"/>
+      <c r="O39" s="100"/>
+      <c r="P39" s="100"/>
+      <c r="Q39" s="100"/>
+      <c r="R39" s="101"/>
+      <c r="S39" s="105" t="s">
         <v>25</v>
       </c>
-      <c r="T39" s="138"/>
-      <c r="U39" s="138"/>
-      <c r="V39" s="138"/>
-      <c r="W39" s="138"/>
-      <c r="X39" s="139"/>
-    </row>
-    <row r="40" spans="1:32" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="118"/>
-      <c r="E40" s="119"/>
-      <c r="F40" s="120"/>
-      <c r="G40" s="123"/>
-      <c r="H40" s="124"/>
-      <c r="I40" s="118"/>
-      <c r="J40" s="126"/>
-      <c r="K40" s="129"/>
-      <c r="L40" s="130"/>
-      <c r="M40" s="134"/>
-      <c r="N40" s="135"/>
-      <c r="O40" s="135"/>
-      <c r="P40" s="135"/>
-      <c r="Q40" s="135"/>
-      <c r="R40" s="136"/>
-      <c r="S40" s="140"/>
-      <c r="T40" s="141"/>
-      <c r="U40" s="141"/>
-      <c r="V40" s="141"/>
-      <c r="W40" s="141"/>
-      <c r="X40" s="142"/>
+      <c r="T39" s="106"/>
+      <c r="U39" s="106"/>
+      <c r="V39" s="106"/>
+      <c r="W39" s="106"/>
+      <c r="X39" s="107"/>
+    </row>
+    <row r="40" spans="1:32" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D40" s="86"/>
+      <c r="E40" s="87"/>
+      <c r="F40" s="88"/>
+      <c r="G40" s="91"/>
+      <c r="H40" s="92"/>
+      <c r="I40" s="86"/>
+      <c r="J40" s="94"/>
+      <c r="K40" s="97"/>
+      <c r="L40" s="98"/>
+      <c r="M40" s="102"/>
+      <c r="N40" s="103"/>
+      <c r="O40" s="103"/>
+      <c r="P40" s="103"/>
+      <c r="Q40" s="103"/>
+      <c r="R40" s="104"/>
+      <c r="S40" s="108"/>
+      <c r="T40" s="109"/>
+      <c r="U40" s="109"/>
+      <c r="V40" s="109"/>
+      <c r="W40" s="109"/>
+      <c r="X40" s="110"/>
     </row>
   </sheetData>
   <mergeCells count="110">
-    <mergeCell ref="D39:F40"/>
-    <mergeCell ref="G39:H40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="K39:L40"/>
-    <mergeCell ref="M39:R40"/>
-    <mergeCell ref="S39:X40"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="O21:V21"/>
-    <mergeCell ref="W21:AD21"/>
-    <mergeCell ref="C30:K31"/>
-    <mergeCell ref="C2:AD2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="W5:AD5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:V6"/>
-    <mergeCell ref="W6:AD6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="O5:V5"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="W7:AD7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="O8:V8"/>
-    <mergeCell ref="W8:AD8"/>
-    <mergeCell ref="O7:V7"/>
-    <mergeCell ref="W9:AD9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="O11:V11"/>
-    <mergeCell ref="W11:AD11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:V9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="W12:AD12"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="O14:V14"/>
-    <mergeCell ref="W14:AD14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="O12:V12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="W15:AD15"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="O17:V17"/>
-    <mergeCell ref="W17:AD17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="O15:V15"/>
-    <mergeCell ref="K15:N15"/>
     <mergeCell ref="W18:AD18"/>
     <mergeCell ref="C25:K26"/>
     <mergeCell ref="O25:U25"/>
@@ -5543,6 +5633,93 @@
     <mergeCell ref="E21:F21"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="I21:J21"/>
+    <mergeCell ref="W15:AD15"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="O17:V17"/>
+    <mergeCell ref="W17:AD17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="O15:V15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="W12:AD12"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O14:V14"/>
+    <mergeCell ref="W14:AD14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="O12:V12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="W9:AD9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="O11:V11"/>
+    <mergeCell ref="W11:AD11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:V9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="W7:AD7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="O8:V8"/>
+    <mergeCell ref="W8:AD8"/>
+    <mergeCell ref="O7:V7"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:V6"/>
+    <mergeCell ref="W6:AD6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="O5:V5"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="C2:AD2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="W5:AD5"/>
+    <mergeCell ref="D39:F40"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="K39:L40"/>
+    <mergeCell ref="M39:R40"/>
+    <mergeCell ref="S39:X40"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="O21:V21"/>
+    <mergeCell ref="W21:AD21"/>
+    <mergeCell ref="C30:K31"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 E5 G5 I5 K5:L5 O5 W5 C7 E8 G8 I8 K8:L8 O8 W8 C10 E11 G11 I11 K11:L11 O11 W11 C13 E14 G14 I14 K14:L14 O14 W14 C16 E17 G17 I17 K17:L17 O17 W17">
     <cfRule type="expression" dxfId="7" priority="3">
@@ -5581,25 +5758,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AP39"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.71875" defaultRowHeight="12.6" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="3" width="5.5703125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15.5703125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="5.5703125" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" style="3" customWidth="1"/>
-    <col min="7" max="7" width="5.5703125" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.5703125" style="3" customWidth="1"/>
-    <col min="9" max="9" width="5.5703125" style="3" customWidth="1"/>
-    <col min="10" max="10" width="15.5703125" style="3" customWidth="1"/>
-    <col min="11" max="14" width="5.5703125" style="3" customWidth="1"/>
-    <col min="15" max="30" width="2.5703125" style="3" customWidth="1"/>
-    <col min="31" max="32" width="5.5703125" style="3" customWidth="1"/>
-    <col min="33" max="33" width="17.140625" style="3" customWidth="1"/>
-    <col min="34" max="34" width="10.42578125" style="3" customWidth="1"/>
-    <col min="35" max="16384" width="8.7109375" style="3"/>
+    <col min="1" max="3" width="5.5546875" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.5546875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="5.5546875" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" style="3" customWidth="1"/>
+    <col min="7" max="7" width="5.5546875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" style="3" customWidth="1"/>
+    <col min="9" max="9" width="5.5546875" style="3" customWidth="1"/>
+    <col min="10" max="10" width="15.5546875" style="3" customWidth="1"/>
+    <col min="11" max="14" width="5.5546875" style="3" customWidth="1"/>
+    <col min="15" max="30" width="2.5546875" style="3" customWidth="1"/>
+    <col min="31" max="32" width="5.5546875" style="3" customWidth="1"/>
+    <col min="33" max="33" width="17.1640625" style="3" customWidth="1"/>
+    <col min="34" max="34" width="10.44140625" style="3" customWidth="1"/>
+    <col min="35" max="16384" width="8.71875" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:36" ht="25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5633,42 +5810,42 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.9">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="2.15">
       <c r="A2" s="29"/>
-      <c r="C2" s="113">
+      <c r="C2" s="116">
         <f ca="1">DATE(About!P8,11,1)</f>
         <v>46327</v>
       </c>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
-      <c r="P2" s="113"/>
-      <c r="Q2" s="113"/>
-      <c r="R2" s="113"/>
-      <c r="S2" s="113"/>
-      <c r="T2" s="113"/>
-      <c r="U2" s="113"/>
-      <c r="V2" s="113"/>
-      <c r="W2" s="113"/>
-      <c r="X2" s="113"/>
-      <c r="Y2" s="113"/>
-      <c r="Z2" s="113"/>
-      <c r="AA2" s="113"/>
-      <c r="AB2" s="113"/>
-      <c r="AC2" s="113"/>
-      <c r="AD2" s="113"/>
+      <c r="D2" s="116"/>
+      <c r="E2" s="116"/>
+      <c r="F2" s="116"/>
+      <c r="G2" s="116"/>
+      <c r="H2" s="116"/>
+      <c r="I2" s="116"/>
+      <c r="J2" s="116"/>
+      <c r="K2" s="116"/>
+      <c r="L2" s="116"/>
+      <c r="M2" s="116"/>
+      <c r="N2" s="116"/>
+      <c r="O2" s="116"/>
+      <c r="P2" s="116"/>
+      <c r="Q2" s="116"/>
+      <c r="R2" s="116"/>
+      <c r="S2" s="116"/>
+      <c r="T2" s="116"/>
+      <c r="U2" s="116"/>
+      <c r="V2" s="116"/>
+      <c r="W2" s="116"/>
+      <c r="X2" s="116"/>
+      <c r="Y2" s="116"/>
+      <c r="Z2" s="116"/>
+      <c r="AA2" s="116"/>
+      <c r="AB2" s="116"/>
+      <c r="AC2" s="116"/>
+      <c r="AD2" s="116"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.9">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="2.15">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -5688,296 +5865,296 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
       <c r="A4" s="35"/>
-      <c r="C4" s="114">
+      <c r="C4" s="117">
         <f ca="1">C5</f>
         <v>46327</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114">
+      <c r="D4" s="117"/>
+      <c r="E4" s="117">
         <f ca="1">E5</f>
         <v>46328</v>
       </c>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114">
+      <c r="F4" s="117"/>
+      <c r="G4" s="117">
         <f ca="1">G5</f>
         <v>46329</v>
       </c>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114">
+      <c r="H4" s="117"/>
+      <c r="I4" s="117">
         <f ca="1">I5</f>
         <v>46330</v>
       </c>
-      <c r="J4" s="114"/>
-      <c r="K4" s="114">
+      <c r="J4" s="117"/>
+      <c r="K4" s="117">
         <f ca="1">K5</f>
         <v>46331</v>
       </c>
-      <c r="L4" s="114"/>
-      <c r="M4" s="114"/>
+      <c r="L4" s="117"/>
+      <c r="M4" s="117"/>
       <c r="N4" s="37"/>
-      <c r="O4" s="114">
+      <c r="O4" s="117">
         <f ca="1">O5</f>
         <v>46332</v>
       </c>
-      <c r="P4" s="114"/>
-      <c r="Q4" s="114"/>
-      <c r="R4" s="114"/>
-      <c r="S4" s="114"/>
-      <c r="T4" s="114"/>
-      <c r="U4" s="114"/>
-      <c r="V4" s="114"/>
-      <c r="W4" s="114">
+      <c r="P4" s="117"/>
+      <c r="Q4" s="117"/>
+      <c r="R4" s="117"/>
+      <c r="S4" s="117"/>
+      <c r="T4" s="117"/>
+      <c r="U4" s="117"/>
+      <c r="V4" s="117"/>
+      <c r="W4" s="117">
         <f ca="1">W5</f>
         <v>46333</v>
       </c>
-      <c r="X4" s="114"/>
-      <c r="Y4" s="114"/>
-      <c r="Z4" s="114"/>
-      <c r="AA4" s="114"/>
-      <c r="AB4" s="114"/>
-      <c r="AC4" s="114"/>
-      <c r="AD4" s="114"/>
+      <c r="X4" s="117"/>
+      <c r="Y4" s="117"/>
+      <c r="Z4" s="117"/>
+      <c r="AA4" s="117"/>
+      <c r="AB4" s="117"/>
+      <c r="AC4" s="117"/>
+      <c r="AD4" s="117"/>
       <c r="AF4" s="38"/>
       <c r="AG4" s="39"/>
       <c r="AH4" s="39"/>
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
       <c r="A5" s="1"/>
-      <c r="C5" s="92">
+      <c r="C5" s="118">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46327</v>
       </c>
-      <c r="D5" s="93"/>
-      <c r="E5" s="92">
+      <c r="D5" s="120"/>
+      <c r="E5" s="118">
         <f ca="1">C5+1</f>
         <v>46328</v>
       </c>
-      <c r="F5" s="93"/>
-      <c r="G5" s="92">
+      <c r="F5" s="120"/>
+      <c r="G5" s="118">
         <f ca="1">E5+1</f>
         <v>46329</v>
       </c>
-      <c r="H5" s="93"/>
-      <c r="I5" s="92">
+      <c r="H5" s="120"/>
+      <c r="I5" s="118">
         <f ca="1">G5+1</f>
         <v>46330</v>
       </c>
-      <c r="J5" s="93"/>
-      <c r="K5" s="92">
+      <c r="J5" s="120"/>
+      <c r="K5" s="118">
         <f ca="1">I5+1</f>
         <v>46331</v>
       </c>
-      <c r="L5" s="112"/>
-      <c r="M5" s="112"/>
+      <c r="L5" s="119"/>
+      <c r="M5" s="119"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="92">
+      <c r="O5" s="118">
         <f ca="1">K5+1</f>
         <v>46332</v>
       </c>
-      <c r="P5" s="112"/>
-      <c r="Q5" s="112"/>
-      <c r="R5" s="112"/>
-      <c r="S5" s="112"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="112"/>
-      <c r="V5" s="93"/>
-      <c r="W5" s="92">
+      <c r="P5" s="119"/>
+      <c r="Q5" s="119"/>
+      <c r="R5" s="119"/>
+      <c r="S5" s="119"/>
+      <c r="T5" s="119"/>
+      <c r="U5" s="119"/>
+      <c r="V5" s="120"/>
+      <c r="W5" s="118">
         <f ca="1">O5+1</f>
         <v>46333</v>
       </c>
-      <c r="X5" s="112"/>
-      <c r="Y5" s="112"/>
-      <c r="Z5" s="112"/>
-      <c r="AA5" s="112"/>
-      <c r="AB5" s="112"/>
-      <c r="AC5" s="112"/>
-      <c r="AD5" s="93"/>
+      <c r="X5" s="119"/>
+      <c r="Y5" s="119"/>
+      <c r="Z5" s="119"/>
+      <c r="AA5" s="119"/>
+      <c r="AB5" s="119"/>
+      <c r="AC5" s="119"/>
+      <c r="AD5" s="120"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
       <c r="AI5" s="41"/>
       <c r="AJ5" s="41"/>
     </row>
-    <row r="6" spans="1:36" s="43" customFormat="1" ht="133.9" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" s="43" customFormat="1" ht="133.9" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="42"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="91" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="85"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="85"/>
-      <c r="I6" s="90" t="s">
-        <v>54</v>
-      </c>
-      <c r="J6" s="85"/>
-      <c r="K6" s="90" t="s">
-        <v>55</v>
-      </c>
-      <c r="L6" s="84"/>
-      <c r="M6" s="84"/>
-      <c r="N6" s="85"/>
-      <c r="O6" s="91" t="s">
-        <v>57</v>
-      </c>
-      <c r="P6" s="84"/>
-      <c r="Q6" s="84"/>
-      <c r="R6" s="84"/>
-      <c r="S6" s="84"/>
-      <c r="T6" s="84"/>
-      <c r="U6" s="84"/>
-      <c r="V6" s="85"/>
-      <c r="W6" s="83"/>
-      <c r="X6" s="84"/>
-      <c r="Y6" s="84"/>
-      <c r="Z6" s="84"/>
-      <c r="AA6" s="84"/>
-      <c r="AB6" s="84"/>
-      <c r="AC6" s="84"/>
-      <c r="AD6" s="85"/>
+      <c r="C6" s="135"/>
+      <c r="D6" s="137"/>
+      <c r="E6" s="141" t="s">
+        <v>33</v>
+      </c>
+      <c r="F6" s="137"/>
+      <c r="G6" s="135"/>
+      <c r="H6" s="137"/>
+      <c r="I6" s="156" t="s">
+        <v>45</v>
+      </c>
+      <c r="J6" s="137"/>
+      <c r="K6" s="156" t="s">
+        <v>46</v>
+      </c>
+      <c r="L6" s="136"/>
+      <c r="M6" s="136"/>
+      <c r="N6" s="137"/>
+      <c r="O6" s="145" t="s">
+        <v>59</v>
+      </c>
+      <c r="P6" s="136"/>
+      <c r="Q6" s="136"/>
+      <c r="R6" s="136"/>
+      <c r="S6" s="136"/>
+      <c r="T6" s="136"/>
+      <c r="U6" s="136"/>
+      <c r="V6" s="137"/>
+      <c r="W6" s="135"/>
+      <c r="X6" s="136"/>
+      <c r="Y6" s="136"/>
+      <c r="Z6" s="136"/>
+      <c r="AA6" s="136"/>
+      <c r="AB6" s="136"/>
+      <c r="AC6" s="136"/>
+      <c r="AD6" s="137"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
-    <row r="7" spans="1:36" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" ht="10" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A7" s="1"/>
-      <c r="C7" s="155">
+      <c r="C7" s="157">
         <f ca="1">W5+1</f>
         <v>46334</v>
       </c>
-      <c r="D7" s="156"/>
-      <c r="E7" s="160"/>
-      <c r="F7" s="161"/>
-      <c r="G7" s="160"/>
-      <c r="H7" s="161"/>
-      <c r="I7" s="160"/>
-      <c r="J7" s="161"/>
-      <c r="K7" s="160"/>
-      <c r="L7" s="162"/>
-      <c r="M7" s="162"/>
+      <c r="D7" s="158"/>
+      <c r="E7" s="159"/>
+      <c r="F7" s="160"/>
+      <c r="G7" s="159"/>
+      <c r="H7" s="160"/>
+      <c r="I7" s="159"/>
+      <c r="J7" s="160"/>
+      <c r="K7" s="159"/>
+      <c r="L7" s="161"/>
+      <c r="M7" s="161"/>
       <c r="N7" s="80"/>
-      <c r="O7" s="160"/>
-      <c r="P7" s="162"/>
-      <c r="Q7" s="162"/>
-      <c r="R7" s="162"/>
-      <c r="S7" s="162"/>
-      <c r="T7" s="162"/>
-      <c r="U7" s="162"/>
-      <c r="V7" s="161"/>
-      <c r="W7" s="160"/>
-      <c r="X7" s="162"/>
-      <c r="Y7" s="162"/>
-      <c r="Z7" s="162"/>
-      <c r="AA7" s="162"/>
-      <c r="AB7" s="162"/>
-      <c r="AC7" s="162"/>
-      <c r="AD7" s="161"/>
+      <c r="O7" s="159"/>
+      <c r="P7" s="161"/>
+      <c r="Q7" s="161"/>
+      <c r="R7" s="161"/>
+      <c r="S7" s="161"/>
+      <c r="T7" s="161"/>
+      <c r="U7" s="161"/>
+      <c r="V7" s="160"/>
+      <c r="W7" s="159"/>
+      <c r="X7" s="161"/>
+      <c r="Y7" s="161"/>
+      <c r="Z7" s="161"/>
+      <c r="AA7" s="161"/>
+      <c r="AB7" s="161"/>
+      <c r="AC7" s="161"/>
+      <c r="AD7" s="160"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="4"/>
-      <c r="C8" s="155"/>
-      <c r="D8" s="156"/>
-      <c r="E8" s="155">
+      <c r="C8" s="157"/>
+      <c r="D8" s="158"/>
+      <c r="E8" s="157">
         <f ca="1">C7+1</f>
         <v>46335</v>
       </c>
-      <c r="F8" s="156"/>
-      <c r="G8" s="155">
+      <c r="F8" s="158"/>
+      <c r="G8" s="157">
         <f ca="1">E8+1</f>
         <v>46336</v>
       </c>
-      <c r="H8" s="156"/>
-      <c r="I8" s="155">
+      <c r="H8" s="158"/>
+      <c r="I8" s="157">
         <f ca="1">G8+1</f>
         <v>46337</v>
       </c>
-      <c r="J8" s="156"/>
-      <c r="K8" s="155">
+      <c r="J8" s="158"/>
+      <c r="K8" s="157">
         <f ca="1">I8+1</f>
         <v>46338</v>
       </c>
-      <c r="L8" s="157"/>
-      <c r="M8" s="157"/>
+      <c r="L8" s="162"/>
+      <c r="M8" s="162"/>
       <c r="N8" s="78"/>
-      <c r="O8" s="155">
+      <c r="O8" s="157">
         <f ca="1">K8+1</f>
         <v>46339</v>
       </c>
-      <c r="P8" s="157"/>
-      <c r="Q8" s="157"/>
-      <c r="R8" s="157"/>
-      <c r="S8" s="157"/>
-      <c r="T8" s="157"/>
-      <c r="U8" s="157"/>
-      <c r="V8" s="156"/>
-      <c r="W8" s="155">
+      <c r="P8" s="162"/>
+      <c r="Q8" s="162"/>
+      <c r="R8" s="162"/>
+      <c r="S8" s="162"/>
+      <c r="T8" s="162"/>
+      <c r="U8" s="162"/>
+      <c r="V8" s="158"/>
+      <c r="W8" s="157">
         <f ca="1">O8+1</f>
         <v>46340</v>
       </c>
-      <c r="X8" s="157"/>
-      <c r="Y8" s="157"/>
-      <c r="Z8" s="157"/>
-      <c r="AA8" s="157"/>
-      <c r="AB8" s="157"/>
-      <c r="AC8" s="157"/>
-      <c r="AD8" s="156"/>
+      <c r="X8" s="162"/>
+      <c r="Y8" s="162"/>
+      <c r="Z8" s="162"/>
+      <c r="AA8" s="162"/>
+      <c r="AB8" s="162"/>
+      <c r="AC8" s="162"/>
+      <c r="AD8" s="158"/>
       <c r="AF8" s="4"/>
     </row>
-    <row r="9" spans="1:36" s="43" customFormat="1" ht="146.44999999999999" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" s="43" customFormat="1" ht="146.5" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="42"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="85"/>
-      <c r="E9" s="91" t="s">
-        <v>43</v>
-      </c>
-      <c r="F9" s="85"/>
-      <c r="G9" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="85"/>
-      <c r="I9" s="83" t="s">
-        <v>44</v>
-      </c>
-      <c r="J9" s="85"/>
-      <c r="K9" s="83" t="s">
-        <v>49</v>
-      </c>
-      <c r="L9" s="84"/>
-      <c r="M9" s="84"/>
-      <c r="N9" s="85"/>
-      <c r="O9" s="158" t="s">
+      <c r="C9" s="135"/>
+      <c r="D9" s="137"/>
+      <c r="E9" s="145" t="s">
+        <v>58</v>
+      </c>
+      <c r="F9" s="137"/>
+      <c r="G9" s="156" t="s">
+        <v>47</v>
+      </c>
+      <c r="H9" s="137"/>
+      <c r="I9" s="135" t="s">
+        <v>60</v>
+      </c>
+      <c r="J9" s="137"/>
+      <c r="K9" s="135" t="s">
+        <v>61</v>
+      </c>
+      <c r="L9" s="136"/>
+      <c r="M9" s="136"/>
+      <c r="N9" s="137"/>
+      <c r="O9" s="164" t="s">
         <v>15</v>
       </c>
-      <c r="P9" s="154"/>
-      <c r="Q9" s="154"/>
-      <c r="R9" s="154"/>
-      <c r="S9" s="154"/>
-      <c r="T9" s="154"/>
-      <c r="U9" s="154"/>
-      <c r="V9" s="105"/>
-      <c r="W9" s="104"/>
-      <c r="X9" s="154"/>
-      <c r="Y9" s="154"/>
-      <c r="Z9" s="154"/>
-      <c r="AA9" s="154"/>
-      <c r="AB9" s="154"/>
-      <c r="AC9" s="154"/>
-      <c r="AD9" s="105"/>
+      <c r="P9" s="163"/>
+      <c r="Q9" s="163"/>
+      <c r="R9" s="163"/>
+      <c r="S9" s="163"/>
+      <c r="T9" s="163"/>
+      <c r="U9" s="163"/>
+      <c r="V9" s="122"/>
+      <c r="W9" s="121"/>
+      <c r="X9" s="163"/>
+      <c r="Y9" s="163"/>
+      <c r="Z9" s="163"/>
+      <c r="AA9" s="163"/>
+      <c r="AB9" s="163"/>
+      <c r="AC9" s="163"/>
+      <c r="AD9" s="122"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
-    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" s="43" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="42"/>
-      <c r="C10" s="155">
+      <c r="C10" s="157">
         <f ca="1">W8+1</f>
         <v>46341</v>
       </c>
-      <c r="D10" s="156"/>
+      <c r="D10" s="158"/>
       <c r="E10" s="79"/>
       <c r="F10" s="80"/>
       <c r="G10" s="79"/>
@@ -6007,99 +6184,99 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="42"/>
     </row>
-    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="4"/>
-      <c r="C11" s="155"/>
-      <c r="D11" s="156"/>
-      <c r="E11" s="155">
+      <c r="C11" s="157"/>
+      <c r="D11" s="158"/>
+      <c r="E11" s="157">
         <f ca="1">C10+1</f>
         <v>46342</v>
       </c>
-      <c r="F11" s="156"/>
-      <c r="G11" s="155">
+      <c r="F11" s="158"/>
+      <c r="G11" s="157">
         <f ca="1">E11+1</f>
         <v>46343</v>
       </c>
-      <c r="H11" s="156"/>
-      <c r="I11" s="155">
+      <c r="H11" s="158"/>
+      <c r="I11" s="157">
         <f ca="1">G11+1</f>
         <v>46344</v>
       </c>
-      <c r="J11" s="156"/>
-      <c r="K11" s="155">
+      <c r="J11" s="158"/>
+      <c r="K11" s="157">
         <f ca="1">I11+1</f>
         <v>46345</v>
       </c>
-      <c r="L11" s="157"/>
-      <c r="M11" s="157"/>
+      <c r="L11" s="162"/>
+      <c r="M11" s="162"/>
       <c r="N11" s="78"/>
-      <c r="O11" s="155">
+      <c r="O11" s="157">
         <f ca="1">K11+1</f>
         <v>46346</v>
       </c>
-      <c r="P11" s="157"/>
-      <c r="Q11" s="157"/>
-      <c r="R11" s="157"/>
-      <c r="S11" s="157"/>
-      <c r="T11" s="157"/>
-      <c r="U11" s="157"/>
-      <c r="V11" s="156"/>
-      <c r="W11" s="155">
+      <c r="P11" s="162"/>
+      <c r="Q11" s="162"/>
+      <c r="R11" s="162"/>
+      <c r="S11" s="162"/>
+      <c r="T11" s="162"/>
+      <c r="U11" s="162"/>
+      <c r="V11" s="158"/>
+      <c r="W11" s="157">
         <f ca="1">O11+1</f>
         <v>46347</v>
       </c>
-      <c r="X11" s="157"/>
-      <c r="Y11" s="157"/>
-      <c r="Z11" s="157"/>
-      <c r="AA11" s="157"/>
-      <c r="AB11" s="157"/>
-      <c r="AC11" s="157"/>
-      <c r="AD11" s="156"/>
+      <c r="X11" s="162"/>
+      <c r="Y11" s="162"/>
+      <c r="Z11" s="162"/>
+      <c r="AA11" s="162"/>
+      <c r="AB11" s="162"/>
+      <c r="AC11" s="162"/>
+      <c r="AD11" s="158"/>
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:36" s="43" customFormat="1" ht="134.65" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" s="43" customFormat="1" ht="134.65" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="42"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="105"/>
-      <c r="E12" s="158" t="s">
+      <c r="C12" s="121"/>
+      <c r="D12" s="122"/>
+      <c r="E12" s="164" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="159"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="105"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="105"/>
-      <c r="K12" s="104"/>
-      <c r="L12" s="154"/>
-      <c r="M12" s="154"/>
-      <c r="N12" s="105"/>
-      <c r="O12" s="104"/>
-      <c r="P12" s="154"/>
-      <c r="Q12" s="154"/>
-      <c r="R12" s="154"/>
-      <c r="S12" s="154"/>
-      <c r="T12" s="154"/>
-      <c r="U12" s="154"/>
-      <c r="V12" s="105"/>
-      <c r="W12" s="104"/>
-      <c r="X12" s="154"/>
-      <c r="Y12" s="154"/>
-      <c r="Z12" s="154"/>
-      <c r="AA12" s="154"/>
-      <c r="AB12" s="154"/>
-      <c r="AC12" s="154"/>
-      <c r="AD12" s="105"/>
+      <c r="F12" s="165"/>
+      <c r="G12" s="121"/>
+      <c r="H12" s="122"/>
+      <c r="I12" s="121"/>
+      <c r="J12" s="122"/>
+      <c r="K12" s="121"/>
+      <c r="L12" s="163"/>
+      <c r="M12" s="163"/>
+      <c r="N12" s="122"/>
+      <c r="O12" s="121"/>
+      <c r="P12" s="163"/>
+      <c r="Q12" s="163"/>
+      <c r="R12" s="163"/>
+      <c r="S12" s="163"/>
+      <c r="T12" s="163"/>
+      <c r="U12" s="163"/>
+      <c r="V12" s="122"/>
+      <c r="W12" s="121"/>
+      <c r="X12" s="163"/>
+      <c r="Y12" s="163"/>
+      <c r="Z12" s="163"/>
+      <c r="AA12" s="163"/>
+      <c r="AB12" s="163"/>
+      <c r="AC12" s="163"/>
+      <c r="AD12" s="122"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
-    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" s="43" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A13" s="42"/>
-      <c r="C13" s="155">
+      <c r="C13" s="157">
         <f ca="1">W11+1</f>
         <v>46348</v>
       </c>
-      <c r="D13" s="156"/>
+      <c r="D13" s="158"/>
       <c r="E13" s="79"/>
       <c r="F13" s="80"/>
       <c r="G13" s="79"/>
@@ -6129,102 +6306,102 @@
       <c r="AE13" s="7"/>
       <c r="AF13" s="42"/>
     </row>
-    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A14" s="4"/>
-      <c r="C14" s="155"/>
-      <c r="D14" s="156"/>
-      <c r="E14" s="155">
+      <c r="C14" s="157"/>
+      <c r="D14" s="158"/>
+      <c r="E14" s="157">
         <f ca="1">C13+1</f>
         <v>46349</v>
       </c>
-      <c r="F14" s="156"/>
-      <c r="G14" s="155">
+      <c r="F14" s="158"/>
+      <c r="G14" s="157">
         <f ca="1">E14+1</f>
         <v>46350</v>
       </c>
-      <c r="H14" s="156"/>
-      <c r="I14" s="155">
+      <c r="H14" s="158"/>
+      <c r="I14" s="157">
         <f ca="1">G14+1</f>
         <v>46351</v>
       </c>
-      <c r="J14" s="156"/>
-      <c r="K14" s="155">
+      <c r="J14" s="158"/>
+      <c r="K14" s="157">
         <f ca="1">I14+1</f>
         <v>46352</v>
       </c>
-      <c r="L14" s="157"/>
-      <c r="M14" s="157"/>
+      <c r="L14" s="162"/>
+      <c r="M14" s="162"/>
       <c r="N14" s="78"/>
-      <c r="O14" s="155">
+      <c r="O14" s="157">
         <f ca="1">K14+1</f>
         <v>46353</v>
       </c>
-      <c r="P14" s="157"/>
-      <c r="Q14" s="157"/>
-      <c r="R14" s="157"/>
-      <c r="S14" s="157"/>
-      <c r="T14" s="157"/>
-      <c r="U14" s="157"/>
-      <c r="V14" s="156"/>
-      <c r="W14" s="155">
+      <c r="P14" s="162"/>
+      <c r="Q14" s="162"/>
+      <c r="R14" s="162"/>
+      <c r="S14" s="162"/>
+      <c r="T14" s="162"/>
+      <c r="U14" s="162"/>
+      <c r="V14" s="158"/>
+      <c r="W14" s="157">
         <f ca="1">O14+1</f>
         <v>46354</v>
       </c>
-      <c r="X14" s="157"/>
-      <c r="Y14" s="157"/>
-      <c r="Z14" s="157"/>
-      <c r="AA14" s="157"/>
-      <c r="AB14" s="157"/>
-      <c r="AC14" s="157"/>
-      <c r="AD14" s="156"/>
+      <c r="X14" s="162"/>
+      <c r="Y14" s="162"/>
+      <c r="Z14" s="162"/>
+      <c r="AA14" s="162"/>
+      <c r="AB14" s="162"/>
+      <c r="AC14" s="162"/>
+      <c r="AD14" s="158"/>
       <c r="AF14" s="4"/>
     </row>
-    <row r="15" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="42"/>
-      <c r="C15" s="104"/>
-      <c r="D15" s="105"/>
-      <c r="E15" s="104"/>
-      <c r="F15" s="105"/>
-      <c r="G15" s="104"/>
-      <c r="H15" s="105"/>
-      <c r="I15" s="104"/>
-      <c r="J15" s="105"/>
-      <c r="K15" s="104"/>
-      <c r="L15" s="154"/>
-      <c r="M15" s="154"/>
-      <c r="N15" s="105"/>
-      <c r="O15" s="104"/>
-      <c r="P15" s="154"/>
-      <c r="Q15" s="154"/>
-      <c r="R15" s="154"/>
-      <c r="S15" s="154"/>
-      <c r="T15" s="154"/>
-      <c r="U15" s="154"/>
-      <c r="V15" s="105"/>
-      <c r="W15" s="104"/>
-      <c r="X15" s="154"/>
-      <c r="Y15" s="154"/>
-      <c r="Z15" s="154"/>
-      <c r="AA15" s="154"/>
-      <c r="AB15" s="154"/>
-      <c r="AC15" s="154"/>
-      <c r="AD15" s="105"/>
+      <c r="C15" s="121"/>
+      <c r="D15" s="122"/>
+      <c r="E15" s="121"/>
+      <c r="F15" s="122"/>
+      <c r="G15" s="121"/>
+      <c r="H15" s="122"/>
+      <c r="I15" s="121"/>
+      <c r="J15" s="122"/>
+      <c r="K15" s="121"/>
+      <c r="L15" s="163"/>
+      <c r="M15" s="163"/>
+      <c r="N15" s="122"/>
+      <c r="O15" s="121"/>
+      <c r="P15" s="163"/>
+      <c r="Q15" s="163"/>
+      <c r="R15" s="163"/>
+      <c r="S15" s="163"/>
+      <c r="T15" s="163"/>
+      <c r="U15" s="163"/>
+      <c r="V15" s="122"/>
+      <c r="W15" s="121"/>
+      <c r="X15" s="163"/>
+      <c r="Y15" s="163"/>
+      <c r="Z15" s="163"/>
+      <c r="AA15" s="163"/>
+      <c r="AB15" s="163"/>
+      <c r="AC15" s="163"/>
+      <c r="AD15" s="122"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
-    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" s="43" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="42"/>
-      <c r="C16" s="92">
+      <c r="C16" s="118">
         <f ca="1">W14+1</f>
         <v>46355</v>
       </c>
-      <c r="D16" s="93"/>
+      <c r="D16" s="120"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
       <c r="H16" s="75"/>
-      <c r="I16" s="145"/>
-      <c r="J16" s="146"/>
+      <c r="I16" s="153"/>
+      <c r="J16" s="154"/>
       <c r="K16" s="66"/>
       <c r="L16" s="68"/>
       <c r="M16" s="68"/>
@@ -6248,103 +6425,103 @@
       <c r="AE16" s="7"/>
       <c r="AF16" s="42"/>
     </row>
-    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A17" s="4"/>
-      <c r="C17" s="92"/>
-      <c r="D17" s="93"/>
-      <c r="E17" s="94">
+      <c r="C17" s="118"/>
+      <c r="D17" s="120"/>
+      <c r="E17" s="132">
         <f ca="1">C16+1</f>
         <v>46356</v>
       </c>
-      <c r="F17" s="95"/>
-      <c r="G17" s="94">
+      <c r="F17" s="133"/>
+      <c r="G17" s="132">
         <f ca="1">E17+1</f>
         <v>46357</v>
       </c>
-      <c r="H17" s="95"/>
-      <c r="I17" s="94">
+      <c r="H17" s="133"/>
+      <c r="I17" s="132">
         <f ca="1">G17+1</f>
         <v>46358</v>
       </c>
-      <c r="J17" s="95"/>
-      <c r="K17" s="94">
+      <c r="J17" s="133"/>
+      <c r="K17" s="132">
         <f ca="1">I17+1</f>
         <v>46359</v>
       </c>
-      <c r="L17" s="96"/>
-      <c r="M17" s="96"/>
-      <c r="N17" s="95"/>
-      <c r="O17" s="94">
+      <c r="L17" s="134"/>
+      <c r="M17" s="134"/>
+      <c r="N17" s="133"/>
+      <c r="O17" s="132">
         <f ca="1">K17+1</f>
         <v>46360</v>
       </c>
-      <c r="P17" s="96"/>
-      <c r="Q17" s="96"/>
-      <c r="R17" s="96"/>
-      <c r="S17" s="96"/>
-      <c r="T17" s="96"/>
-      <c r="U17" s="96"/>
-      <c r="V17" s="95"/>
-      <c r="W17" s="94">
+      <c r="P17" s="134"/>
+      <c r="Q17" s="134"/>
+      <c r="R17" s="134"/>
+      <c r="S17" s="134"/>
+      <c r="T17" s="134"/>
+      <c r="U17" s="134"/>
+      <c r="V17" s="133"/>
+      <c r="W17" s="132">
         <f ca="1">O17+1</f>
         <v>46361</v>
       </c>
-      <c r="X17" s="96"/>
-      <c r="Y17" s="96"/>
-      <c r="Z17" s="96"/>
-      <c r="AA17" s="96"/>
-      <c r="AB17" s="96"/>
-      <c r="AC17" s="96"/>
-      <c r="AD17" s="95"/>
+      <c r="X17" s="134"/>
+      <c r="Y17" s="134"/>
+      <c r="Z17" s="134"/>
+      <c r="AA17" s="134"/>
+      <c r="AB17" s="134"/>
+      <c r="AC17" s="134"/>
+      <c r="AD17" s="133"/>
       <c r="AF17" s="4"/>
     </row>
-    <row r="18" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="42"/>
-      <c r="C18" s="97"/>
-      <c r="D18" s="98"/>
-      <c r="E18" s="97"/>
-      <c r="F18" s="98"/>
-      <c r="G18" s="97"/>
-      <c r="H18" s="98"/>
-      <c r="I18" s="97"/>
-      <c r="J18" s="98"/>
-      <c r="K18" s="97"/>
-      <c r="L18" s="143"/>
-      <c r="M18" s="143"/>
-      <c r="N18" s="98"/>
-      <c r="O18" s="97"/>
-      <c r="P18" s="143"/>
-      <c r="Q18" s="143"/>
-      <c r="R18" s="143"/>
-      <c r="S18" s="143"/>
-      <c r="T18" s="143"/>
-      <c r="U18" s="143"/>
-      <c r="V18" s="98"/>
-      <c r="W18" s="97"/>
-      <c r="X18" s="143"/>
-      <c r="Y18" s="143"/>
-      <c r="Z18" s="143"/>
-      <c r="AA18" s="143"/>
-      <c r="AB18" s="143"/>
-      <c r="AC18" s="143"/>
-      <c r="AD18" s="98"/>
+      <c r="C18" s="111"/>
+      <c r="D18" s="113"/>
+      <c r="E18" s="111"/>
+      <c r="F18" s="113"/>
+      <c r="G18" s="111"/>
+      <c r="H18" s="113"/>
+      <c r="I18" s="111"/>
+      <c r="J18" s="113"/>
+      <c r="K18" s="111"/>
+      <c r="L18" s="112"/>
+      <c r="M18" s="112"/>
+      <c r="N18" s="113"/>
+      <c r="O18" s="111"/>
+      <c r="P18" s="112"/>
+      <c r="Q18" s="112"/>
+      <c r="R18" s="112"/>
+      <c r="S18" s="112"/>
+      <c r="T18" s="112"/>
+      <c r="U18" s="112"/>
+      <c r="V18" s="113"/>
+      <c r="W18" s="111"/>
+      <c r="X18" s="112"/>
+      <c r="Y18" s="112"/>
+      <c r="Z18" s="112"/>
+      <c r="AA18" s="112"/>
+      <c r="AB18" s="112"/>
+      <c r="AC18" s="112"/>
+      <c r="AD18" s="113"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
-    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:42" s="43" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A19" s="42"/>
-      <c r="C19" s="92">
+      <c r="C19" s="118">
         <f ca="1">W17+1</f>
         <v>46362</v>
       </c>
-      <c r="D19" s="93"/>
+      <c r="D19" s="120"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
       <c r="H19" s="75"/>
-      <c r="I19" s="145"/>
-      <c r="J19" s="146"/>
+      <c r="I19" s="153"/>
+      <c r="J19" s="154"/>
       <c r="K19" s="66"/>
       <c r="L19" s="68"/>
       <c r="M19" s="68"/>
@@ -6368,91 +6545,91 @@
       <c r="AE19" s="7"/>
       <c r="AF19" s="42"/>
     </row>
-    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A20" s="4"/>
-      <c r="C20" s="92"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="94">
+      <c r="C20" s="118"/>
+      <c r="D20" s="120"/>
+      <c r="E20" s="132">
         <f ca="1">C19+1</f>
         <v>46363</v>
       </c>
-      <c r="F20" s="95"/>
-      <c r="G20" s="94">
+      <c r="F20" s="133"/>
+      <c r="G20" s="132">
         <f ca="1">E20+1</f>
         <v>46364</v>
       </c>
-      <c r="H20" s="95"/>
-      <c r="I20" s="94">
+      <c r="H20" s="133"/>
+      <c r="I20" s="132">
         <f ca="1">G20+1</f>
         <v>46365</v>
       </c>
-      <c r="J20" s="95"/>
-      <c r="K20" s="94">
+      <c r="J20" s="133"/>
+      <c r="K20" s="132">
         <f ca="1">I20+1</f>
         <v>46366</v>
       </c>
-      <c r="L20" s="96"/>
-      <c r="M20" s="96"/>
-      <c r="N20" s="95"/>
-      <c r="O20" s="94">
+      <c r="L20" s="134"/>
+      <c r="M20" s="134"/>
+      <c r="N20" s="133"/>
+      <c r="O20" s="132">
         <f ca="1">K20+1</f>
         <v>46367</v>
       </c>
-      <c r="P20" s="96"/>
-      <c r="Q20" s="96"/>
-      <c r="R20" s="96"/>
-      <c r="S20" s="96"/>
-      <c r="T20" s="96"/>
-      <c r="U20" s="96"/>
-      <c r="V20" s="95"/>
-      <c r="W20" s="94">
+      <c r="P20" s="134"/>
+      <c r="Q20" s="134"/>
+      <c r="R20" s="134"/>
+      <c r="S20" s="134"/>
+      <c r="T20" s="134"/>
+      <c r="U20" s="134"/>
+      <c r="V20" s="133"/>
+      <c r="W20" s="132">
         <f ca="1">O20+1</f>
         <v>46368</v>
       </c>
-      <c r="X20" s="96"/>
-      <c r="Y20" s="96"/>
-      <c r="Z20" s="96"/>
-      <c r="AA20" s="96"/>
-      <c r="AB20" s="96"/>
-      <c r="AC20" s="96"/>
-      <c r="AD20" s="95"/>
+      <c r="X20" s="134"/>
+      <c r="Y20" s="134"/>
+      <c r="Z20" s="134"/>
+      <c r="AA20" s="134"/>
+      <c r="AB20" s="134"/>
+      <c r="AC20" s="134"/>
+      <c r="AD20" s="133"/>
       <c r="AF20" s="4"/>
     </row>
-    <row r="21" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="42"/>
-      <c r="C21" s="97"/>
-      <c r="D21" s="98"/>
-      <c r="E21" s="97"/>
-      <c r="F21" s="98"/>
-      <c r="G21" s="97"/>
-      <c r="H21" s="98"/>
-      <c r="I21" s="97"/>
-      <c r="J21" s="98"/>
-      <c r="K21" s="97"/>
-      <c r="L21" s="143"/>
-      <c r="M21" s="143"/>
-      <c r="N21" s="98"/>
-      <c r="O21" s="97"/>
-      <c r="P21" s="143"/>
-      <c r="Q21" s="143"/>
-      <c r="R21" s="143"/>
-      <c r="S21" s="143"/>
-      <c r="T21" s="143"/>
-      <c r="U21" s="143"/>
-      <c r="V21" s="98"/>
-      <c r="W21" s="97"/>
-      <c r="X21" s="143"/>
-      <c r="Y21" s="143"/>
-      <c r="Z21" s="143"/>
-      <c r="AA21" s="143"/>
-      <c r="AB21" s="143"/>
-      <c r="AC21" s="143"/>
-      <c r="AD21" s="98"/>
+      <c r="C21" s="111"/>
+      <c r="D21" s="113"/>
+      <c r="E21" s="111"/>
+      <c r="F21" s="113"/>
+      <c r="G21" s="111"/>
+      <c r="H21" s="113"/>
+      <c r="I21" s="111"/>
+      <c r="J21" s="113"/>
+      <c r="K21" s="111"/>
+      <c r="L21" s="112"/>
+      <c r="M21" s="112"/>
+      <c r="N21" s="113"/>
+      <c r="O21" s="111"/>
+      <c r="P21" s="112"/>
+      <c r="Q21" s="112"/>
+      <c r="R21" s="112"/>
+      <c r="S21" s="112"/>
+      <c r="T21" s="112"/>
+      <c r="U21" s="112"/>
+      <c r="V21" s="113"/>
+      <c r="W21" s="111"/>
+      <c r="X21" s="112"/>
+      <c r="Y21" s="112"/>
+      <c r="Z21" s="112"/>
+      <c r="AA21" s="112"/>
+      <c r="AB21" s="112"/>
+      <c r="AC21" s="112"/>
+      <c r="AD21" s="113"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
     </row>
-    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:42" s="7" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="4"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52"/>
@@ -6484,7 +6661,7 @@
       <c r="AD22" s="55"/>
       <c r="AF22" s="4"/>
     </row>
-    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:42" s="7" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="56"/>
@@ -6518,61 +6695,61 @@
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
     </row>
-    <row r="24" spans="1:42" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:42" ht="25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="1"/>
       <c r="M24" s="1"/>
       <c r="AF24" s="1"/>
     </row>
-    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="1"/>
-      <c r="C25" s="86" t="s">
+      <c r="C25" s="143" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="86"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="86"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="86"/>
-      <c r="J25" s="86"/>
-      <c r="K25" s="86"/>
+      <c r="D25" s="143"/>
+      <c r="E25" s="143"/>
+      <c r="F25" s="143"/>
+      <c r="G25" s="143"/>
+      <c r="H25" s="143"/>
+      <c r="I25" s="143"/>
+      <c r="J25" s="143"/>
+      <c r="K25" s="143"/>
       <c r="L25" s="60"/>
       <c r="M25" s="1"/>
-      <c r="O25" s="87">
+      <c r="O25" s="144">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)-1,1)</f>
         <v>46296</v>
       </c>
-      <c r="P25" s="87"/>
-      <c r="Q25" s="87"/>
-      <c r="R25" s="87"/>
-      <c r="S25" s="87"/>
-      <c r="T25" s="87"/>
-      <c r="U25" s="87"/>
+      <c r="P25" s="144"/>
+      <c r="Q25" s="144"/>
+      <c r="R25" s="144"/>
+      <c r="S25" s="144"/>
+      <c r="T25" s="144"/>
+      <c r="U25" s="144"/>
       <c r="V25" s="61"/>
       <c r="W25" s="61"/>
-      <c r="X25" s="87">
+      <c r="X25" s="144">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)+1,1)</f>
         <v>46357</v>
       </c>
-      <c r="Y25" s="87"/>
-      <c r="Z25" s="87"/>
-      <c r="AA25" s="87"/>
-      <c r="AB25" s="87"/>
-      <c r="AC25" s="87"/>
-      <c r="AD25" s="87"/>
+      <c r="Y25" s="144"/>
+      <c r="Z25" s="144"/>
+      <c r="AA25" s="144"/>
+      <c r="AB25" s="144"/>
+      <c r="AC25" s="144"/>
+      <c r="AD25" s="144"/>
       <c r="AF25" s="1"/>
     </row>
-    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A26" s="1"/>
-      <c r="C26" s="86"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="86"/>
-      <c r="G26" s="86"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="86"/>
-      <c r="J26" s="86"/>
-      <c r="K26" s="86"/>
+      <c r="C26" s="143"/>
+      <c r="D26" s="143"/>
+      <c r="E26" s="143"/>
+      <c r="F26" s="143"/>
+      <c r="G26" s="143"/>
+      <c r="H26" s="143"/>
+      <c r="I26" s="143"/>
+      <c r="J26" s="143"/>
+      <c r="K26" s="143"/>
       <c r="L26" s="60"/>
       <c r="M26" s="1"/>
       <c r="O26" s="62" t="str">
@@ -6635,17 +6812,17 @@
       </c>
       <c r="AF26" s="1"/>
     </row>
-    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="1"/>
-      <c r="C27" s="88"/>
-      <c r="D27" s="88"/>
-      <c r="E27" s="88"/>
-      <c r="F27" s="88"/>
-      <c r="G27" s="88"/>
-      <c r="H27" s="88"/>
-      <c r="I27" s="88"/>
-      <c r="J27" s="88"/>
-      <c r="K27" s="88"/>
+      <c r="C27" s="115"/>
+      <c r="D27" s="115"/>
+      <c r="E27" s="115"/>
+      <c r="F27" s="115"/>
+      <c r="G27" s="115"/>
+      <c r="H27" s="115"/>
+      <c r="I27" s="115"/>
+      <c r="J27" s="115"/>
+      <c r="K27" s="115"/>
       <c r="M27" s="1"/>
       <c r="O27" s="64" t="str">
         <f t="shared" ref="O27:U32" ca="1" si="0">IF(MONTH($O$25)&lt;&gt;MONTH($O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1)),"",$O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1))</f>
@@ -6707,17 +6884,17 @@
       </c>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A28" s="1"/>
-      <c r="C28" s="89"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="89"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="89"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="89"/>
-      <c r="K28" s="89"/>
+      <c r="C28" s="114"/>
+      <c r="D28" s="114"/>
+      <c r="E28" s="114"/>
+      <c r="F28" s="114"/>
+      <c r="G28" s="114"/>
+      <c r="H28" s="114"/>
+      <c r="I28" s="114"/>
+      <c r="J28" s="114"/>
+      <c r="K28" s="114"/>
       <c r="M28" s="1"/>
       <c r="O28" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6779,17 +6956,17 @@
       </c>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="1"/>
-      <c r="C29" s="88"/>
-      <c r="D29" s="88"/>
-      <c r="E29" s="88"/>
-      <c r="F29" s="88"/>
-      <c r="G29" s="88"/>
-      <c r="H29" s="88"/>
-      <c r="I29" s="88"/>
-      <c r="J29" s="88"/>
-      <c r="K29" s="88"/>
+      <c r="C29" s="115"/>
+      <c r="D29" s="115"/>
+      <c r="E29" s="115"/>
+      <c r="F29" s="115"/>
+      <c r="G29" s="115"/>
+      <c r="H29" s="115"/>
+      <c r="I29" s="115"/>
+      <c r="J29" s="115"/>
+      <c r="K29" s="115"/>
       <c r="M29" s="1"/>
       <c r="O29" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6851,17 +7028,17 @@
       </c>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A30" s="1"/>
-      <c r="C30" s="89"/>
-      <c r="D30" s="89"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="89"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="89"/>
-      <c r="K30" s="89"/>
+      <c r="C30" s="114"/>
+      <c r="D30" s="114"/>
+      <c r="E30" s="114"/>
+      <c r="F30" s="114"/>
+      <c r="G30" s="114"/>
+      <c r="H30" s="114"/>
+      <c r="I30" s="114"/>
+      <c r="J30" s="114"/>
+      <c r="K30" s="114"/>
       <c r="M30" s="1"/>
       <c r="O30" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6923,17 +7100,17 @@
       </c>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="1"/>
-      <c r="C31" s="88"/>
-      <c r="D31" s="88"/>
-      <c r="E31" s="88"/>
-      <c r="F31" s="88"/>
-      <c r="G31" s="88"/>
-      <c r="H31" s="88"/>
-      <c r="I31" s="88"/>
-      <c r="J31" s="88"/>
-      <c r="K31" s="88"/>
+      <c r="C31" s="115"/>
+      <c r="D31" s="115"/>
+      <c r="E31" s="115"/>
+      <c r="F31" s="115"/>
+      <c r="G31" s="115"/>
+      <c r="H31" s="115"/>
+      <c r="I31" s="115"/>
+      <c r="J31" s="115"/>
+      <c r="K31" s="115"/>
       <c r="M31" s="1"/>
       <c r="O31" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6995,7 +7172,7 @@
       </c>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="1"/>
       <c r="C32" s="77"/>
       <c r="D32" s="77"/>
@@ -7067,12 +7244,12 @@
       </c>
       <c r="AF32" s="1"/>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.45">
       <c r="A33" s="1"/>
       <c r="M33" s="1"/>
       <c r="AF33" s="1"/>
     </row>
-    <row r="34" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -7106,100 +7283,130 @@
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
     </row>
-    <row r="37" spans="1:32" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="38" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D38" s="115" t="s">
+    <row r="37" spans="1:32" ht="12.9" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="38" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D38" s="83" t="s">
         <v>23</v>
       </c>
-      <c r="E38" s="116"/>
-      <c r="F38" s="117"/>
-      <c r="G38" s="121">
+      <c r="E38" s="84"/>
+      <c r="F38" s="85"/>
+      <c r="G38" s="89">
         <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
         <v>5</v>
       </c>
-      <c r="H38" s="122"/>
-      <c r="I38" s="115" t="s">
+      <c r="H38" s="90"/>
+      <c r="I38" s="83" t="s">
         <v>26</v>
       </c>
-      <c r="J38" s="125"/>
-      <c r="K38" s="127" t="s">
+      <c r="J38" s="93"/>
+      <c r="K38" s="95" t="s">
         <v>24</v>
       </c>
-      <c r="L38" s="128"/>
-      <c r="M38" s="131">
+      <c r="L38" s="96"/>
+      <c r="M38" s="99">
         <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
-        <v>3.9999999999999982</v>
-      </c>
-      <c r="N38" s="132"/>
-      <c r="O38" s="132"/>
-      <c r="P38" s="132"/>
-      <c r="Q38" s="132"/>
-      <c r="R38" s="133"/>
-      <c r="S38" s="137" t="s">
+        <v>1.0000000000000027</v>
+      </c>
+      <c r="N38" s="100"/>
+      <c r="O38" s="100"/>
+      <c r="P38" s="100"/>
+      <c r="Q38" s="100"/>
+      <c r="R38" s="101"/>
+      <c r="S38" s="105" t="s">
         <v>25</v>
       </c>
-      <c r="T38" s="138"/>
-      <c r="U38" s="138"/>
-      <c r="V38" s="138"/>
-      <c r="W38" s="138"/>
-      <c r="X38" s="139"/>
-    </row>
-    <row r="39" spans="1:32" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="118"/>
-      <c r="E39" s="119"/>
-      <c r="F39" s="120"/>
-      <c r="G39" s="123"/>
-      <c r="H39" s="124"/>
-      <c r="I39" s="118"/>
-      <c r="J39" s="126"/>
-      <c r="K39" s="129"/>
-      <c r="L39" s="130"/>
-      <c r="M39" s="134"/>
-      <c r="N39" s="135"/>
-      <c r="O39" s="135"/>
-      <c r="P39" s="135"/>
-      <c r="Q39" s="135"/>
-      <c r="R39" s="136"/>
-      <c r="S39" s="140"/>
-      <c r="T39" s="141"/>
-      <c r="U39" s="141"/>
-      <c r="V39" s="141"/>
-      <c r="W39" s="141"/>
-      <c r="X39" s="142"/>
+      <c r="T38" s="106"/>
+      <c r="U38" s="106"/>
+      <c r="V38" s="106"/>
+      <c r="W38" s="106"/>
+      <c r="X38" s="107"/>
+    </row>
+    <row r="39" spans="1:32" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D39" s="86"/>
+      <c r="E39" s="87"/>
+      <c r="F39" s="88"/>
+      <c r="G39" s="91"/>
+      <c r="H39" s="92"/>
+      <c r="I39" s="86"/>
+      <c r="J39" s="94"/>
+      <c r="K39" s="97"/>
+      <c r="L39" s="98"/>
+      <c r="M39" s="102"/>
+      <c r="N39" s="103"/>
+      <c r="O39" s="103"/>
+      <c r="P39" s="103"/>
+      <c r="Q39" s="103"/>
+      <c r="R39" s="104"/>
+      <c r="S39" s="108"/>
+      <c r="T39" s="109"/>
+      <c r="U39" s="109"/>
+      <c r="V39" s="109"/>
+      <c r="W39" s="109"/>
+      <c r="X39" s="110"/>
     </row>
   </sheetData>
   <mergeCells count="112">
-    <mergeCell ref="D38:F39"/>
-    <mergeCell ref="G38:H39"/>
-    <mergeCell ref="I38:J39"/>
-    <mergeCell ref="K38:L39"/>
-    <mergeCell ref="M38:R39"/>
-    <mergeCell ref="S38:X39"/>
-    <mergeCell ref="C30:K31"/>
-    <mergeCell ref="O20:V20"/>
-    <mergeCell ref="W20:AD20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:N21"/>
-    <mergeCell ref="O21:V21"/>
-    <mergeCell ref="W21:AD21"/>
-    <mergeCell ref="C2:AD2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="W5:AD5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="O5:V5"/>
+    <mergeCell ref="K18:N18"/>
+    <mergeCell ref="W18:AD18"/>
+    <mergeCell ref="C25:K26"/>
+    <mergeCell ref="O25:U25"/>
+    <mergeCell ref="X25:AD25"/>
+    <mergeCell ref="C27:K27"/>
+    <mergeCell ref="C28:K29"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="O18:V18"/>
+    <mergeCell ref="C19:D20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:N20"/>
+    <mergeCell ref="W15:AD15"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="O17:V17"/>
+    <mergeCell ref="W17:AD17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="O15:V15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="W12:AD12"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O14:V14"/>
+    <mergeCell ref="W14:AD14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="O12:V12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="W9:AD9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="O11:V11"/>
+    <mergeCell ref="W11:AD11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:V9"/>
+    <mergeCell ref="K9:N9"/>
     <mergeCell ref="K6:N6"/>
     <mergeCell ref="C7:D8"/>
     <mergeCell ref="E7:F7"/>
@@ -7220,67 +7427,37 @@
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="O6:V6"/>
     <mergeCell ref="W6:AD6"/>
-    <mergeCell ref="W9:AD9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="O11:V11"/>
-    <mergeCell ref="W11:AD11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:V9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="W12:AD12"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="O14:V14"/>
-    <mergeCell ref="W14:AD14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="O12:V12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="W15:AD15"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="O17:V17"/>
-    <mergeCell ref="W17:AD17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="O15:V15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="K18:N18"/>
-    <mergeCell ref="W18:AD18"/>
-    <mergeCell ref="C25:K26"/>
-    <mergeCell ref="O25:U25"/>
-    <mergeCell ref="X25:AD25"/>
-    <mergeCell ref="C27:K27"/>
-    <mergeCell ref="C28:K29"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="O18:V18"/>
-    <mergeCell ref="C19:D20"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:N20"/>
+    <mergeCell ref="C2:AD2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="W5:AD5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="O5:V5"/>
+    <mergeCell ref="D38:F39"/>
+    <mergeCell ref="G38:H39"/>
+    <mergeCell ref="I38:J39"/>
+    <mergeCell ref="K38:L39"/>
+    <mergeCell ref="M38:R39"/>
+    <mergeCell ref="S38:X39"/>
+    <mergeCell ref="C30:K31"/>
+    <mergeCell ref="O20:V20"/>
+    <mergeCell ref="W20:AD20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:N21"/>
+    <mergeCell ref="O21:V21"/>
+    <mergeCell ref="W21:AD21"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 E5 G5 I5 K5:L5 O5 W5 C7 E8 G8 I8 K8:L8 O8 W8 C10 E11 G11 I11 K11:L11 O11 W11 C13 E14 G14 I14 K14:L14 O14 W14 C16 E17 G17 I17 K17 O17 W17">
     <cfRule type="expression" dxfId="3" priority="3">
@@ -7314,6 +7491,35 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="30" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cec0622158e8f13124e9e8fd4de31bd1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3b52f30ab005d15df08657af532e6e38" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -7631,36 +7837,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B201CC6-7A0A-429C-B445-7EDA1CF4A1D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F0D3479-5903-425F-9669-62B4E7216DE9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{652EDDE9-C911-407A-9906-647D87C81E69}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7681,26 +7878,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F0D3479-5903-425F-9669-62B4E7216DE9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B201CC6-7A0A-429C-B445-7EDA1CF4A1D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata"/>
 </file>
--- a/Group_milestones.xlsx
+++ b/Group_milestones.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D2F1A88-5E4C-4A1B-983F-CCDEB225E021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39CAEE9-AD7F-4550-8EC3-283B9F427DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-135" yWindow="-135" windowWidth="29070" windowHeight="15750" tabRatio="824" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="824" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="52" r:id="rId1"/>
@@ -28,9 +28,10 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -192,9 +193,6 @@
     <t>MCTR1: Carraige v2 design</t>
   </si>
   <si>
-    <t>MCTR1: Carriage v2 build</t>
-  </si>
-  <si>
     <t>EEII1: ICD complete with REII and MCTR2</t>
   </si>
   <si>
@@ -346,6 +344,38 @@
 · isolation bench-verify + HW E-stop path (pre-live drivers)
 · MCTR-I profile format D-04 + encoder handoff</t>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">MCTR1: Carriage v2 build                            </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EEII2: Contact suppliers for material quotes, Femm simulation tests, Speak to Hopewell on campus</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="2" tint="-0.89999084444715716"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">                                  </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Obtain winding wire</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -358,7 +388,7 @@
     <numFmt numFmtId="167" formatCode="mmmm\ yyyy"/>
     <numFmt numFmtId="168" formatCode="dddd"/>
   </numFmts>
-  <fonts count="43" x14ac:knownFonts="1">
+  <fonts count="44" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -634,6 +664,12 @@
       <name val="Seaford"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFFC000"/>
+      <name val="Seaford"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1090,6 +1126,198 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -1099,244 +1327,52 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="35" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="36" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -1710,7 +1746,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R15"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="4" width="5.5703125" style="3" customWidth="1"/>
     <col min="5" max="9" width="10.5703125" style="3" customWidth="1"/>
@@ -1722,7 +1758,7 @@
     <col min="19" max="16384" width="8.7109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1764,7 +1800,7 @@
       <c r="Q2" s="6"/>
       <c r="R2" s="4"/>
     </row>
-    <row r="3" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.9">
+    <row r="3" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="8"/>
@@ -1784,7 +1820,7 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -1798,12 +1834,12 @@
       <c r="K4" s="12"/>
       <c r="L4" s="11"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="144" t="s">
+      <c r="N4" s="83" t="s">
         <v>10</v>
       </c>
-      <c r="O4" s="144"/>
-      <c r="P4" s="144"/>
-      <c r="Q4" s="144"/>
+      <c r="O4" s="83"/>
+      <c r="P4" s="83"/>
+      <c r="Q4" s="83"/>
       <c r="R4" s="1"/>
     </row>
     <row r="5" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1824,10 +1860,10 @@
       <c r="K5" s="15"/>
       <c r="L5" s="16"/>
       <c r="M5" s="4"/>
-      <c r="N5" s="144"/>
-      <c r="O5" s="144"/>
-      <c r="P5" s="144"/>
-      <c r="Q5" s="144"/>
+      <c r="N5" s="83"/>
+      <c r="O5" s="83"/>
+      <c r="P5" s="83"/>
+      <c r="Q5" s="83"/>
       <c r="R5" s="1"/>
     </row>
     <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -1844,10 +1880,10 @@
       <c r="K6" s="20"/>
       <c r="L6" s="19"/>
       <c r="M6" s="4"/>
-      <c r="N6" s="144"/>
-      <c r="O6" s="144"/>
-      <c r="P6" s="144"/>
-      <c r="Q6" s="144"/>
+      <c r="N6" s="83"/>
+      <c r="O6" s="83"/>
+      <c r="P6" s="83"/>
+      <c r="Q6" s="83"/>
       <c r="R6" s="1"/>
     </row>
     <row r="7" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
@@ -2034,7 +2070,7 @@
       <c r="Q14" s="18"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -2121,42 +2157,42 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.9">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A2" s="29"/>
-      <c r="C2" s="113">
+      <c r="C2" s="117">
         <f ca="1">DATE(About!P8,9,1)</f>
         <v>46266</v>
       </c>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
-      <c r="P2" s="113"/>
-      <c r="Q2" s="113"/>
-      <c r="R2" s="113"/>
-      <c r="S2" s="113"/>
-      <c r="T2" s="113"/>
-      <c r="U2" s="113"/>
-      <c r="V2" s="113"/>
-      <c r="W2" s="113"/>
-      <c r="X2" s="113"/>
-      <c r="Y2" s="113"/>
-      <c r="Z2" s="113"/>
-      <c r="AA2" s="113"/>
-      <c r="AB2" s="113"/>
-      <c r="AC2" s="113"/>
-      <c r="AD2" s="113"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="117"/>
+      <c r="M2" s="117"/>
+      <c r="N2" s="117"/>
+      <c r="O2" s="117"/>
+      <c r="P2" s="117"/>
+      <c r="Q2" s="117"/>
+      <c r="R2" s="117"/>
+      <c r="S2" s="117"/>
+      <c r="T2" s="117"/>
+      <c r="U2" s="117"/>
+      <c r="V2" s="117"/>
+      <c r="W2" s="117"/>
+      <c r="X2" s="117"/>
+      <c r="Y2" s="117"/>
+      <c r="Z2" s="117"/>
+      <c r="AA2" s="117"/>
+      <c r="AB2" s="117"/>
+      <c r="AC2" s="117"/>
+      <c r="AD2" s="117"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.9">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -2176,114 +2212,114 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="35"/>
-      <c r="C4" s="114">
+      <c r="C4" s="118">
         <f ca="1">C5</f>
         <v>46264</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114">
+      <c r="D4" s="118"/>
+      <c r="E4" s="118">
         <f ca="1">E5</f>
         <v>46265</v>
       </c>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114">
+      <c r="F4" s="118"/>
+      <c r="G4" s="118">
         <f ca="1">G5</f>
         <v>46266</v>
       </c>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114">
+      <c r="H4" s="118"/>
+      <c r="I4" s="118">
         <f ca="1">I5</f>
         <v>46267</v>
       </c>
-      <c r="J4" s="114"/>
-      <c r="K4" s="114">
+      <c r="J4" s="118"/>
+      <c r="K4" s="118">
         <f ca="1">K5</f>
         <v>46268</v>
       </c>
-      <c r="L4" s="114"/>
-      <c r="M4" s="114"/>
+      <c r="L4" s="118"/>
+      <c r="M4" s="118"/>
       <c r="N4" s="37"/>
-      <c r="O4" s="114">
+      <c r="O4" s="118">
         <f ca="1">O5</f>
         <v>46269</v>
       </c>
-      <c r="P4" s="114"/>
-      <c r="Q4" s="114"/>
-      <c r="R4" s="114"/>
-      <c r="S4" s="114"/>
-      <c r="T4" s="114"/>
-      <c r="U4" s="114"/>
-      <c r="V4" s="114"/>
-      <c r="W4" s="114">
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118"/>
+      <c r="S4" s="118"/>
+      <c r="T4" s="118"/>
+      <c r="U4" s="118"/>
+      <c r="V4" s="118"/>
+      <c r="W4" s="118">
         <f ca="1">W5</f>
         <v>46270</v>
       </c>
-      <c r="X4" s="114"/>
-      <c r="Y4" s="114"/>
-      <c r="Z4" s="114"/>
-      <c r="AA4" s="114"/>
-      <c r="AB4" s="114"/>
-      <c r="AC4" s="114"/>
-      <c r="AD4" s="114"/>
+      <c r="X4" s="118"/>
+      <c r="Y4" s="118"/>
+      <c r="Z4" s="118"/>
+      <c r="AA4" s="118"/>
+      <c r="AB4" s="118"/>
+      <c r="AC4" s="118"/>
+      <c r="AD4" s="118"/>
       <c r="AF4" s="38"/>
       <c r="AG4" s="39"/>
       <c r="AH4" s="39"/>
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
-      <c r="C5" s="92">
+      <c r="C5" s="119">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46264</v>
       </c>
-      <c r="D5" s="93"/>
-      <c r="E5" s="92">
+      <c r="D5" s="121"/>
+      <c r="E5" s="119">
         <f ca="1">C5+1</f>
         <v>46265</v>
       </c>
-      <c r="F5" s="93"/>
-      <c r="G5" s="92">
+      <c r="F5" s="121"/>
+      <c r="G5" s="119">
         <f ca="1">E5+1</f>
         <v>46266</v>
       </c>
-      <c r="H5" s="93"/>
-      <c r="I5" s="92">
+      <c r="H5" s="121"/>
+      <c r="I5" s="119">
         <f ca="1">G5+1</f>
         <v>46267</v>
       </c>
-      <c r="J5" s="93"/>
-      <c r="K5" s="92">
+      <c r="J5" s="121"/>
+      <c r="K5" s="119">
         <f ca="1">I5+1</f>
         <v>46268</v>
       </c>
-      <c r="L5" s="112"/>
-      <c r="M5" s="112"/>
+      <c r="L5" s="120"/>
+      <c r="M5" s="120"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="92">
+      <c r="O5" s="119">
         <f ca="1">K5+1</f>
         <v>46269</v>
       </c>
-      <c r="P5" s="112"/>
-      <c r="Q5" s="112"/>
-      <c r="R5" s="112"/>
-      <c r="S5" s="112"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="112"/>
-      <c r="V5" s="93"/>
-      <c r="W5" s="92">
+      <c r="P5" s="120"/>
+      <c r="Q5" s="120"/>
+      <c r="R5" s="120"/>
+      <c r="S5" s="120"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="121"/>
+      <c r="W5" s="119">
         <f ca="1">O5+1</f>
         <v>46270</v>
       </c>
-      <c r="X5" s="112"/>
-      <c r="Y5" s="112"/>
-      <c r="Z5" s="112"/>
-      <c r="AA5" s="112"/>
-      <c r="AB5" s="112"/>
-      <c r="AC5" s="112"/>
-      <c r="AD5" s="93"/>
+      <c r="X5" s="120"/>
+      <c r="Y5" s="120"/>
+      <c r="Z5" s="120"/>
+      <c r="AA5" s="120"/>
+      <c r="AB5" s="120"/>
+      <c r="AC5" s="120"/>
+      <c r="AD5" s="121"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
@@ -2292,164 +2328,164 @@
     </row>
     <row r="6" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="42"/>
-      <c r="C6" s="97"/>
-      <c r="D6" s="98"/>
-      <c r="E6" s="97"/>
-      <c r="F6" s="98"/>
-      <c r="G6" s="148"/>
-      <c r="H6" s="149"/>
-      <c r="I6" s="148"/>
-      <c r="J6" s="149"/>
-      <c r="K6" s="148"/>
-      <c r="L6" s="150"/>
-      <c r="M6" s="150"/>
-      <c r="N6" s="149"/>
-      <c r="O6" s="148"/>
-      <c r="P6" s="150"/>
-      <c r="Q6" s="150"/>
-      <c r="R6" s="150"/>
-      <c r="S6" s="150"/>
-      <c r="T6" s="150"/>
-      <c r="U6" s="150"/>
-      <c r="V6" s="149"/>
-      <c r="W6" s="148"/>
-      <c r="X6" s="150"/>
-      <c r="Y6" s="150"/>
-      <c r="Z6" s="150"/>
-      <c r="AA6" s="150"/>
-      <c r="AB6" s="150"/>
-      <c r="AC6" s="150"/>
-      <c r="AD6" s="149"/>
+      <c r="C6" s="122"/>
+      <c r="D6" s="123"/>
+      <c r="E6" s="122"/>
+      <c r="F6" s="123"/>
+      <c r="G6" s="124"/>
+      <c r="H6" s="125"/>
+      <c r="I6" s="124"/>
+      <c r="J6" s="125"/>
+      <c r="K6" s="124"/>
+      <c r="L6" s="126"/>
+      <c r="M6" s="126"/>
+      <c r="N6" s="125"/>
+      <c r="O6" s="124"/>
+      <c r="P6" s="126"/>
+      <c r="Q6" s="126"/>
+      <c r="R6" s="126"/>
+      <c r="S6" s="126"/>
+      <c r="T6" s="126"/>
+      <c r="U6" s="126"/>
+      <c r="V6" s="125"/>
+      <c r="W6" s="124"/>
+      <c r="X6" s="126"/>
+      <c r="Y6" s="126"/>
+      <c r="Z6" s="126"/>
+      <c r="AA6" s="126"/>
+      <c r="AB6" s="126"/>
+      <c r="AC6" s="126"/>
+      <c r="AD6" s="125"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
     <row r="7" spans="1:36" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="C7" s="92">
+      <c r="C7" s="119">
         <f ca="1">W5+1</f>
         <v>46271</v>
       </c>
-      <c r="D7" s="93"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="102"/>
-      <c r="G7" s="101"/>
-      <c r="H7" s="102"/>
-      <c r="I7" s="101"/>
-      <c r="J7" s="102"/>
-      <c r="K7" s="101"/>
-      <c r="L7" s="103"/>
-      <c r="M7" s="103"/>
+      <c r="D7" s="121"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="128"/>
+      <c r="G7" s="127"/>
+      <c r="H7" s="128"/>
+      <c r="I7" s="127"/>
+      <c r="J7" s="128"/>
+      <c r="K7" s="127"/>
+      <c r="L7" s="129"/>
+      <c r="M7" s="129"/>
       <c r="N7" s="75"/>
-      <c r="O7" s="101"/>
-      <c r="P7" s="103"/>
-      <c r="Q7" s="103"/>
-      <c r="R7" s="103"/>
-      <c r="S7" s="103"/>
-      <c r="T7" s="103"/>
-      <c r="U7" s="103"/>
-      <c r="V7" s="102"/>
-      <c r="W7" s="101"/>
-      <c r="X7" s="103"/>
-      <c r="Y7" s="103"/>
-      <c r="Z7" s="103"/>
-      <c r="AA7" s="103"/>
-      <c r="AB7" s="103"/>
-      <c r="AC7" s="103"/>
-      <c r="AD7" s="102"/>
+      <c r="O7" s="127"/>
+      <c r="P7" s="129"/>
+      <c r="Q7" s="129"/>
+      <c r="R7" s="129"/>
+      <c r="S7" s="129"/>
+      <c r="T7" s="129"/>
+      <c r="U7" s="129"/>
+      <c r="V7" s="128"/>
+      <c r="W7" s="127"/>
+      <c r="X7" s="129"/>
+      <c r="Y7" s="129"/>
+      <c r="Z7" s="129"/>
+      <c r="AA7" s="129"/>
+      <c r="AB7" s="129"/>
+      <c r="AC7" s="129"/>
+      <c r="AD7" s="128"/>
       <c r="AF7" s="1"/>
     </row>
     <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
-      <c r="C8" s="92"/>
-      <c r="D8" s="93"/>
-      <c r="E8" s="94">
+      <c r="C8" s="119"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="112">
         <f ca="1">C7+1</f>
         <v>46272</v>
       </c>
-      <c r="F8" s="95"/>
-      <c r="G8" s="94">
+      <c r="F8" s="113"/>
+      <c r="G8" s="112">
         <f ca="1">E8+1</f>
         <v>46273</v>
       </c>
-      <c r="H8" s="95"/>
-      <c r="I8" s="94">
+      <c r="H8" s="113"/>
+      <c r="I8" s="112">
         <f ca="1">G8+1</f>
         <v>46274</v>
       </c>
-      <c r="J8" s="95"/>
-      <c r="K8" s="94">
+      <c r="J8" s="113"/>
+      <c r="K8" s="112">
         <f ca="1">I8+1</f>
         <v>46275</v>
       </c>
-      <c r="L8" s="96"/>
-      <c r="M8" s="96"/>
+      <c r="L8" s="114"/>
+      <c r="M8" s="114"/>
       <c r="N8" s="50"/>
-      <c r="O8" s="94">
+      <c r="O8" s="112">
         <f ca="1">K8+1</f>
         <v>46276</v>
       </c>
-      <c r="P8" s="96"/>
-      <c r="Q8" s="96"/>
-      <c r="R8" s="96"/>
-      <c r="S8" s="96"/>
-      <c r="T8" s="96"/>
-      <c r="U8" s="96"/>
-      <c r="V8" s="95"/>
-      <c r="W8" s="94">
+      <c r="P8" s="114"/>
+      <c r="Q8" s="114"/>
+      <c r="R8" s="114"/>
+      <c r="S8" s="114"/>
+      <c r="T8" s="114"/>
+      <c r="U8" s="114"/>
+      <c r="V8" s="113"/>
+      <c r="W8" s="112">
         <f ca="1">O8+1</f>
         <v>46277</v>
       </c>
-      <c r="X8" s="96"/>
-      <c r="Y8" s="96"/>
-      <c r="Z8" s="96"/>
-      <c r="AA8" s="96"/>
-      <c r="AB8" s="96"/>
-      <c r="AC8" s="96"/>
-      <c r="AD8" s="95"/>
+      <c r="X8" s="114"/>
+      <c r="Y8" s="114"/>
+      <c r="Z8" s="114"/>
+      <c r="AA8" s="114"/>
+      <c r="AB8" s="114"/>
+      <c r="AC8" s="114"/>
+      <c r="AD8" s="113"/>
       <c r="AF8" s="4"/>
     </row>
     <row r="9" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="42"/>
-      <c r="C9" s="148"/>
-      <c r="D9" s="149"/>
-      <c r="E9" s="148"/>
-      <c r="F9" s="149"/>
-      <c r="G9" s="148"/>
-      <c r="H9" s="149"/>
-      <c r="I9" s="148"/>
-      <c r="J9" s="149"/>
-      <c r="K9" s="148"/>
-      <c r="L9" s="150"/>
-      <c r="M9" s="150"/>
-      <c r="N9" s="149"/>
-      <c r="O9" s="151" t="s">
-        <v>41</v>
-      </c>
-      <c r="P9" s="153"/>
-      <c r="Q9" s="153"/>
-      <c r="R9" s="153"/>
-      <c r="S9" s="153"/>
-      <c r="T9" s="153"/>
-      <c r="U9" s="153"/>
-      <c r="V9" s="152"/>
-      <c r="W9" s="148"/>
-      <c r="X9" s="150"/>
-      <c r="Y9" s="150"/>
-      <c r="Z9" s="150"/>
-      <c r="AA9" s="150"/>
-      <c r="AB9" s="150"/>
-      <c r="AC9" s="150"/>
-      <c r="AD9" s="149"/>
+      <c r="C9" s="124"/>
+      <c r="D9" s="125"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="125"/>
+      <c r="G9" s="124"/>
+      <c r="H9" s="125"/>
+      <c r="I9" s="124"/>
+      <c r="J9" s="125"/>
+      <c r="K9" s="124"/>
+      <c r="L9" s="126"/>
+      <c r="M9" s="126"/>
+      <c r="N9" s="125"/>
+      <c r="O9" s="130" t="s">
+        <v>40</v>
+      </c>
+      <c r="P9" s="131"/>
+      <c r="Q9" s="131"/>
+      <c r="R9" s="131"/>
+      <c r="S9" s="131"/>
+      <c r="T9" s="131"/>
+      <c r="U9" s="131"/>
+      <c r="V9" s="132"/>
+      <c r="W9" s="124"/>
+      <c r="X9" s="126"/>
+      <c r="Y9" s="126"/>
+      <c r="Z9" s="126"/>
+      <c r="AA9" s="126"/>
+      <c r="AB9" s="126"/>
+      <c r="AC9" s="126"/>
+      <c r="AD9" s="125"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
     <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="42"/>
-      <c r="C10" s="92">
+      <c r="C10" s="119">
         <f ca="1">W8+1</f>
         <v>46278</v>
       </c>
-      <c r="D10" s="93"/>
+      <c r="D10" s="121"/>
       <c r="E10" s="45"/>
       <c r="F10" s="75"/>
       <c r="G10" s="45"/>
@@ -2481,97 +2517,97 @@
     </row>
     <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="93"/>
-      <c r="E11" s="94">
+      <c r="C11" s="119"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="112">
         <f ca="1">C10+1</f>
         <v>46279</v>
       </c>
-      <c r="F11" s="95"/>
-      <c r="G11" s="94">
+      <c r="F11" s="113"/>
+      <c r="G11" s="112">
         <f ca="1">E11+1</f>
         <v>46280</v>
       </c>
-      <c r="H11" s="95"/>
-      <c r="I11" s="94">
+      <c r="H11" s="113"/>
+      <c r="I11" s="112">
         <f ca="1">G11+1</f>
         <v>46281</v>
       </c>
-      <c r="J11" s="95"/>
-      <c r="K11" s="94">
+      <c r="J11" s="113"/>
+      <c r="K11" s="112">
         <f ca="1">I11+1</f>
         <v>46282</v>
       </c>
-      <c r="L11" s="96"/>
-      <c r="M11" s="96"/>
+      <c r="L11" s="114"/>
+      <c r="M11" s="114"/>
       <c r="N11" s="50"/>
-      <c r="O11" s="94">
+      <c r="O11" s="112">
         <f ca="1">K11+1</f>
         <v>46283</v>
       </c>
-      <c r="P11" s="96"/>
-      <c r="Q11" s="96"/>
-      <c r="R11" s="96"/>
-      <c r="S11" s="96"/>
-      <c r="T11" s="96"/>
-      <c r="U11" s="96"/>
-      <c r="V11" s="95"/>
-      <c r="W11" s="94">
+      <c r="P11" s="114"/>
+      <c r="Q11" s="114"/>
+      <c r="R11" s="114"/>
+      <c r="S11" s="114"/>
+      <c r="T11" s="114"/>
+      <c r="U11" s="114"/>
+      <c r="V11" s="113"/>
+      <c r="W11" s="112">
         <f ca="1">O11+1</f>
         <v>46284</v>
       </c>
-      <c r="X11" s="96"/>
-      <c r="Y11" s="96"/>
-      <c r="Z11" s="96"/>
-      <c r="AA11" s="96"/>
-      <c r="AB11" s="96"/>
-      <c r="AC11" s="96"/>
-      <c r="AD11" s="95"/>
+      <c r="X11" s="114"/>
+      <c r="Y11" s="114"/>
+      <c r="Z11" s="114"/>
+      <c r="AA11" s="114"/>
+      <c r="AB11" s="114"/>
+      <c r="AC11" s="114"/>
+      <c r="AD11" s="113"/>
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
     <row r="12" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="42"/>
-      <c r="C12" s="148"/>
-      <c r="D12" s="149"/>
-      <c r="E12" s="151" t="s">
-        <v>42</v>
-      </c>
-      <c r="F12" s="152"/>
-      <c r="G12" s="148"/>
-      <c r="H12" s="149"/>
-      <c r="I12" s="148"/>
-      <c r="J12" s="149"/>
-      <c r="K12" s="148"/>
-      <c r="L12" s="150"/>
-      <c r="M12" s="150"/>
-      <c r="N12" s="149"/>
-      <c r="O12" s="148"/>
-      <c r="P12" s="150"/>
-      <c r="Q12" s="150"/>
-      <c r="R12" s="150"/>
-      <c r="S12" s="150"/>
-      <c r="T12" s="150"/>
-      <c r="U12" s="150"/>
-      <c r="V12" s="149"/>
-      <c r="W12" s="148"/>
-      <c r="X12" s="150"/>
-      <c r="Y12" s="150"/>
-      <c r="Z12" s="150"/>
-      <c r="AA12" s="150"/>
-      <c r="AB12" s="150"/>
-      <c r="AC12" s="150"/>
-      <c r="AD12" s="149"/>
+      <c r="C12" s="124"/>
+      <c r="D12" s="125"/>
+      <c r="E12" s="130" t="s">
+        <v>41</v>
+      </c>
+      <c r="F12" s="132"/>
+      <c r="G12" s="124"/>
+      <c r="H12" s="125"/>
+      <c r="I12" s="124"/>
+      <c r="J12" s="125"/>
+      <c r="K12" s="124"/>
+      <c r="L12" s="126"/>
+      <c r="M12" s="126"/>
+      <c r="N12" s="125"/>
+      <c r="O12" s="124"/>
+      <c r="P12" s="126"/>
+      <c r="Q12" s="126"/>
+      <c r="R12" s="126"/>
+      <c r="S12" s="126"/>
+      <c r="T12" s="126"/>
+      <c r="U12" s="126"/>
+      <c r="V12" s="125"/>
+      <c r="W12" s="124"/>
+      <c r="X12" s="126"/>
+      <c r="Y12" s="126"/>
+      <c r="Z12" s="126"/>
+      <c r="AA12" s="126"/>
+      <c r="AB12" s="126"/>
+      <c r="AC12" s="126"/>
+      <c r="AD12" s="125"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
     <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="42"/>
-      <c r="C13" s="92">
+      <c r="C13" s="119">
         <f ca="1">W11+1</f>
         <v>46285</v>
       </c>
-      <c r="D13" s="93"/>
+      <c r="D13" s="121"/>
       <c r="E13" s="45"/>
       <c r="F13" s="75"/>
       <c r="G13" s="45"/>
@@ -2603,112 +2639,112 @@
     </row>
     <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4"/>
-      <c r="C14" s="92"/>
-      <c r="D14" s="93"/>
-      <c r="E14" s="94">
+      <c r="C14" s="119"/>
+      <c r="D14" s="121"/>
+      <c r="E14" s="112">
         <f ca="1">C13+1</f>
         <v>46286</v>
       </c>
-      <c r="F14" s="95"/>
-      <c r="G14" s="94">
+      <c r="F14" s="113"/>
+      <c r="G14" s="112">
         <f ca="1">E14+1</f>
         <v>46287</v>
       </c>
-      <c r="H14" s="95"/>
-      <c r="I14" s="94">
+      <c r="H14" s="113"/>
+      <c r="I14" s="112">
         <f ca="1">G14+1</f>
         <v>46288</v>
       </c>
-      <c r="J14" s="95"/>
-      <c r="K14" s="94">
+      <c r="J14" s="113"/>
+      <c r="K14" s="112">
         <f ca="1">I14+1</f>
         <v>46289</v>
       </c>
-      <c r="L14" s="96"/>
-      <c r="M14" s="96"/>
+      <c r="L14" s="114"/>
+      <c r="M14" s="114"/>
       <c r="N14" s="50"/>
-      <c r="O14" s="94">
+      <c r="O14" s="112">
         <f ca="1">K14+1</f>
         <v>46290</v>
       </c>
-      <c r="P14" s="96"/>
-      <c r="Q14" s="96"/>
-      <c r="R14" s="96"/>
-      <c r="S14" s="96"/>
-      <c r="T14" s="96"/>
-      <c r="U14" s="96"/>
-      <c r="V14" s="95"/>
-      <c r="W14" s="94">
+      <c r="P14" s="114"/>
+      <c r="Q14" s="114"/>
+      <c r="R14" s="114"/>
+      <c r="S14" s="114"/>
+      <c r="T14" s="114"/>
+      <c r="U14" s="114"/>
+      <c r="V14" s="113"/>
+      <c r="W14" s="112">
         <f ca="1">O14+1</f>
         <v>46291</v>
       </c>
-      <c r="X14" s="96"/>
-      <c r="Y14" s="96"/>
-      <c r="Z14" s="96"/>
-      <c r="AA14" s="96"/>
-      <c r="AB14" s="96"/>
-      <c r="AC14" s="96"/>
-      <c r="AD14" s="95"/>
+      <c r="X14" s="114"/>
+      <c r="Y14" s="114"/>
+      <c r="Z14" s="114"/>
+      <c r="AA14" s="114"/>
+      <c r="AB14" s="114"/>
+      <c r="AC14" s="114"/>
+      <c r="AD14" s="113"/>
       <c r="AF14" s="4"/>
     </row>
     <row r="15" spans="1:36" s="43" customFormat="1" ht="162.94999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="42"/>
-      <c r="C15" s="148"/>
-      <c r="D15" s="149"/>
-      <c r="E15" s="148"/>
-      <c r="F15" s="149"/>
-      <c r="G15" s="148"/>
-      <c r="H15" s="149"/>
-      <c r="I15" s="106"/>
-      <c r="J15" s="108"/>
-      <c r="K15" s="106"/>
-      <c r="L15" s="107"/>
-      <c r="M15" s="107"/>
-      <c r="N15" s="108"/>
-      <c r="O15" s="106"/>
-      <c r="P15" s="107"/>
-      <c r="Q15" s="107"/>
-      <c r="R15" s="107"/>
-      <c r="S15" s="107"/>
-      <c r="T15" s="107"/>
-      <c r="U15" s="107"/>
-      <c r="V15" s="108"/>
-      <c r="W15" s="106"/>
-      <c r="X15" s="107"/>
-      <c r="Y15" s="107"/>
-      <c r="Z15" s="107"/>
-      <c r="AA15" s="107"/>
-      <c r="AB15" s="107"/>
-      <c r="AC15" s="107"/>
-      <c r="AD15" s="108"/>
+      <c r="C15" s="124"/>
+      <c r="D15" s="125"/>
+      <c r="E15" s="124"/>
+      <c r="F15" s="125"/>
+      <c r="G15" s="124"/>
+      <c r="H15" s="125"/>
+      <c r="I15" s="133"/>
+      <c r="J15" s="135"/>
+      <c r="K15" s="133"/>
+      <c r="L15" s="134"/>
+      <c r="M15" s="134"/>
+      <c r="N15" s="135"/>
+      <c r="O15" s="133"/>
+      <c r="P15" s="134"/>
+      <c r="Q15" s="134"/>
+      <c r="R15" s="134"/>
+      <c r="S15" s="134"/>
+      <c r="T15" s="134"/>
+      <c r="U15" s="134"/>
+      <c r="V15" s="135"/>
+      <c r="W15" s="133"/>
+      <c r="X15" s="134"/>
+      <c r="Y15" s="134"/>
+      <c r="Z15" s="134"/>
+      <c r="AA15" s="134"/>
+      <c r="AB15" s="134"/>
+      <c r="AC15" s="134"/>
+      <c r="AD15" s="135"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
     <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="42"/>
-      <c r="C16" s="92">
+      <c r="C16" s="119">
         <f ca="1">W14+1</f>
         <v>46292</v>
       </c>
-      <c r="D16" s="93"/>
+      <c r="D16" s="121"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
       <c r="H16" s="75"/>
-      <c r="I16" s="145"/>
-      <c r="J16" s="146"/>
+      <c r="I16" s="136"/>
+      <c r="J16" s="137"/>
       <c r="K16" s="66"/>
       <c r="L16" s="68"/>
       <c r="M16" s="68"/>
       <c r="N16" s="67"/>
-      <c r="O16" s="145"/>
-      <c r="P16" s="147"/>
-      <c r="Q16" s="147"/>
-      <c r="R16" s="147"/>
-      <c r="S16" s="147"/>
-      <c r="T16" s="147"/>
-      <c r="U16" s="147"/>
-      <c r="V16" s="146"/>
+      <c r="O16" s="136"/>
+      <c r="P16" s="138"/>
+      <c r="Q16" s="138"/>
+      <c r="R16" s="138"/>
+      <c r="S16" s="138"/>
+      <c r="T16" s="138"/>
+      <c r="U16" s="138"/>
+      <c r="V16" s="137"/>
       <c r="W16" s="45"/>
       <c r="X16" s="76"/>
       <c r="Y16" s="76"/>
@@ -2722,23 +2758,23 @@
     </row>
     <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
-      <c r="C17" s="92"/>
-      <c r="D17" s="93"/>
-      <c r="E17" s="94">
+      <c r="C17" s="119"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="112">
         <f ca="1">C16+1</f>
         <v>46293</v>
       </c>
-      <c r="F17" s="95"/>
-      <c r="G17" s="94">
+      <c r="F17" s="113"/>
+      <c r="G17" s="112">
         <f ca="1">E17+1</f>
         <v>46294</v>
       </c>
-      <c r="H17" s="95"/>
-      <c r="I17" s="94">
+      <c r="H17" s="113"/>
+      <c r="I17" s="112">
         <f ca="1">G17+1</f>
         <v>46295</v>
       </c>
-      <c r="J17" s="95"/>
+      <c r="J17" s="113"/>
       <c r="K17" s="46">
         <f ca="1">I17+1</f>
         <v>46296</v>
@@ -2746,93 +2782,93 @@
       <c r="L17" s="51"/>
       <c r="M17" s="51"/>
       <c r="N17" s="69"/>
-      <c r="O17" s="94">
+      <c r="O17" s="112">
         <f ca="1">K17+1</f>
         <v>46297</v>
       </c>
-      <c r="P17" s="96"/>
-      <c r="Q17" s="96"/>
-      <c r="R17" s="96"/>
-      <c r="S17" s="96"/>
-      <c r="T17" s="96"/>
-      <c r="U17" s="96"/>
-      <c r="V17" s="95"/>
-      <c r="W17" s="94">
+      <c r="P17" s="114"/>
+      <c r="Q17" s="114"/>
+      <c r="R17" s="114"/>
+      <c r="S17" s="114"/>
+      <c r="T17" s="114"/>
+      <c r="U17" s="114"/>
+      <c r="V17" s="113"/>
+      <c r="W17" s="112">
         <f ca="1">O17+1</f>
         <v>46298</v>
       </c>
-      <c r="X17" s="96"/>
-      <c r="Y17" s="96"/>
-      <c r="Z17" s="96"/>
-      <c r="AA17" s="96"/>
-      <c r="AB17" s="96"/>
-      <c r="AC17" s="96"/>
-      <c r="AD17" s="95"/>
+      <c r="X17" s="114"/>
+      <c r="Y17" s="114"/>
+      <c r="Z17" s="114"/>
+      <c r="AA17" s="114"/>
+      <c r="AB17" s="114"/>
+      <c r="AC17" s="114"/>
+      <c r="AD17" s="113"/>
       <c r="AF17" s="4"/>
     </row>
     <row r="18" spans="1:42" s="43" customFormat="1" ht="147.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="42"/>
-      <c r="C18" s="109" t="s">
+      <c r="C18" s="142" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="111"/>
-      <c r="E18" s="106"/>
-      <c r="F18" s="108"/>
-      <c r="G18" s="106"/>
-      <c r="H18" s="108"/>
-      <c r="I18" s="109" t="s">
+      <c r="D18" s="143"/>
+      <c r="E18" s="133"/>
+      <c r="F18" s="135"/>
+      <c r="G18" s="133"/>
+      <c r="H18" s="135"/>
+      <c r="I18" s="142" t="s">
         <v>17</v>
       </c>
-      <c r="J18" s="111"/>
+      <c r="J18" s="143"/>
       <c r="K18" s="70"/>
       <c r="L18" s="71"/>
       <c r="M18" s="71"/>
       <c r="N18" s="72"/>
-      <c r="O18" s="97"/>
-      <c r="P18" s="143"/>
-      <c r="Q18" s="143"/>
-      <c r="R18" s="143"/>
-      <c r="S18" s="143"/>
-      <c r="T18" s="143"/>
-      <c r="U18" s="143"/>
-      <c r="V18" s="98"/>
-      <c r="W18" s="97"/>
-      <c r="X18" s="143"/>
-      <c r="Y18" s="143"/>
-      <c r="Z18" s="143"/>
-      <c r="AA18" s="143"/>
-      <c r="AB18" s="143"/>
-      <c r="AC18" s="143"/>
-      <c r="AD18" s="98"/>
+      <c r="O18" s="122"/>
+      <c r="P18" s="139"/>
+      <c r="Q18" s="139"/>
+      <c r="R18" s="139"/>
+      <c r="S18" s="139"/>
+      <c r="T18" s="139"/>
+      <c r="U18" s="139"/>
+      <c r="V18" s="123"/>
+      <c r="W18" s="122"/>
+      <c r="X18" s="139"/>
+      <c r="Y18" s="139"/>
+      <c r="Z18" s="139"/>
+      <c r="AA18" s="139"/>
+      <c r="AB18" s="139"/>
+      <c r="AC18" s="139"/>
+      <c r="AD18" s="123"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
     <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="42"/>
-      <c r="C19" s="92">
+      <c r="C19" s="119">
         <f ca="1">W17+1</f>
         <v>46299</v>
       </c>
-      <c r="D19" s="93"/>
+      <c r="D19" s="121"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
       <c r="H19" s="75"/>
-      <c r="I19" s="145"/>
-      <c r="J19" s="146"/>
+      <c r="I19" s="136"/>
+      <c r="J19" s="137"/>
       <c r="K19" s="66"/>
       <c r="L19" s="68"/>
       <c r="M19" s="68"/>
       <c r="N19" s="67"/>
-      <c r="O19" s="145"/>
-      <c r="P19" s="147"/>
-      <c r="Q19" s="147"/>
-      <c r="R19" s="147"/>
-      <c r="S19" s="147"/>
-      <c r="T19" s="147"/>
-      <c r="U19" s="147"/>
-      <c r="V19" s="146"/>
+      <c r="O19" s="136"/>
+      <c r="P19" s="138"/>
+      <c r="Q19" s="138"/>
+      <c r="R19" s="138"/>
+      <c r="S19" s="138"/>
+      <c r="T19" s="138"/>
+      <c r="U19" s="138"/>
+      <c r="V19" s="137"/>
       <c r="W19" s="45"/>
       <c r="X19" s="76"/>
       <c r="Y19" s="76"/>
@@ -2846,23 +2882,23 @@
     </row>
     <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
-      <c r="C20" s="92"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="94">
+      <c r="C20" s="119"/>
+      <c r="D20" s="121"/>
+      <c r="E20" s="112">
         <f ca="1">C19+1</f>
         <v>46300</v>
       </c>
-      <c r="F20" s="95"/>
-      <c r="G20" s="94">
+      <c r="F20" s="113"/>
+      <c r="G20" s="112">
         <f ca="1">E20+1</f>
         <v>46301</v>
       </c>
-      <c r="H20" s="95"/>
-      <c r="I20" s="94">
+      <c r="H20" s="113"/>
+      <c r="I20" s="112">
         <f ca="1">G20+1</f>
         <v>46302</v>
       </c>
-      <c r="J20" s="95"/>
+      <c r="J20" s="113"/>
       <c r="K20" s="46">
         <f ca="1">I20+1</f>
         <v>46303</v>
@@ -2870,60 +2906,60 @@
       <c r="L20" s="51"/>
       <c r="M20" s="51"/>
       <c r="N20" s="69"/>
-      <c r="O20" s="94">
+      <c r="O20" s="112">
         <f ca="1">K20+1</f>
         <v>46304</v>
       </c>
-      <c r="P20" s="96"/>
-      <c r="Q20" s="96"/>
-      <c r="R20" s="96"/>
-      <c r="S20" s="96"/>
-      <c r="T20" s="96"/>
-      <c r="U20" s="96"/>
-      <c r="V20" s="95"/>
-      <c r="W20" s="94">
+      <c r="P20" s="114"/>
+      <c r="Q20" s="114"/>
+      <c r="R20" s="114"/>
+      <c r="S20" s="114"/>
+      <c r="T20" s="114"/>
+      <c r="U20" s="114"/>
+      <c r="V20" s="113"/>
+      <c r="W20" s="112">
         <f ca="1">O20+1</f>
         <v>46305</v>
       </c>
-      <c r="X20" s="96"/>
-      <c r="Y20" s="96"/>
-      <c r="Z20" s="96"/>
-      <c r="AA20" s="96"/>
-      <c r="AB20" s="96"/>
-      <c r="AC20" s="96"/>
-      <c r="AD20" s="95"/>
+      <c r="X20" s="114"/>
+      <c r="Y20" s="114"/>
+      <c r="Z20" s="114"/>
+      <c r="AA20" s="114"/>
+      <c r="AB20" s="114"/>
+      <c r="AC20" s="114"/>
+      <c r="AD20" s="113"/>
       <c r="AF20" s="4"/>
     </row>
     <row r="21" spans="1:42" s="43" customFormat="1" ht="166.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="42"/>
-      <c r="C21" s="97"/>
-      <c r="D21" s="98"/>
-      <c r="E21" s="97"/>
-      <c r="F21" s="98"/>
-      <c r="G21" s="97"/>
-      <c r="H21" s="98"/>
-      <c r="I21" s="97"/>
-      <c r="J21" s="98"/>
+      <c r="C21" s="122"/>
+      <c r="D21" s="123"/>
+      <c r="E21" s="122"/>
+      <c r="F21" s="123"/>
+      <c r="G21" s="122"/>
+      <c r="H21" s="123"/>
+      <c r="I21" s="122"/>
+      <c r="J21" s="123"/>
       <c r="K21" s="70"/>
       <c r="L21" s="71"/>
       <c r="M21" s="71"/>
       <c r="N21" s="72"/>
-      <c r="O21" s="97"/>
-      <c r="P21" s="143"/>
-      <c r="Q21" s="143"/>
-      <c r="R21" s="143"/>
-      <c r="S21" s="143"/>
-      <c r="T21" s="143"/>
-      <c r="U21" s="143"/>
-      <c r="V21" s="98"/>
-      <c r="W21" s="97"/>
-      <c r="X21" s="143"/>
-      <c r="Y21" s="143"/>
-      <c r="Z21" s="143"/>
-      <c r="AA21" s="143"/>
-      <c r="AB21" s="143"/>
-      <c r="AC21" s="143"/>
-      <c r="AD21" s="98"/>
+      <c r="O21" s="122"/>
+      <c r="P21" s="139"/>
+      <c r="Q21" s="139"/>
+      <c r="R21" s="139"/>
+      <c r="S21" s="139"/>
+      <c r="T21" s="139"/>
+      <c r="U21" s="139"/>
+      <c r="V21" s="123"/>
+      <c r="W21" s="122"/>
+      <c r="X21" s="139"/>
+      <c r="Y21" s="139"/>
+      <c r="Z21" s="139"/>
+      <c r="AA21" s="139"/>
+      <c r="AB21" s="139"/>
+      <c r="AC21" s="139"/>
+      <c r="AD21" s="123"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
@@ -3001,54 +3037,54 @@
     </row>
     <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
-      <c r="C25" s="86" t="s">
+      <c r="C25" s="140" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="86"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="86"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="86"/>
-      <c r="J25" s="86"/>
-      <c r="K25" s="86"/>
+      <c r="D25" s="140"/>
+      <c r="E25" s="140"/>
+      <c r="F25" s="140"/>
+      <c r="G25" s="140"/>
+      <c r="H25" s="140"/>
+      <c r="I25" s="140"/>
+      <c r="J25" s="140"/>
+      <c r="K25" s="140"/>
       <c r="L25" s="60"/>
       <c r="M25" s="1"/>
-      <c r="O25" s="87">
+      <c r="O25" s="141">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)-1,1)</f>
         <v>46235</v>
       </c>
-      <c r="P25" s="87"/>
-      <c r="Q25" s="87"/>
-      <c r="R25" s="87"/>
-      <c r="S25" s="87"/>
-      <c r="T25" s="87"/>
-      <c r="U25" s="87"/>
+      <c r="P25" s="141"/>
+      <c r="Q25" s="141"/>
+      <c r="R25" s="141"/>
+      <c r="S25" s="141"/>
+      <c r="T25" s="141"/>
+      <c r="U25" s="141"/>
       <c r="V25" s="61"/>
       <c r="W25" s="61"/>
-      <c r="X25" s="87">
+      <c r="X25" s="141">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)+1,1)</f>
         <v>46296</v>
       </c>
-      <c r="Y25" s="87"/>
-      <c r="Z25" s="87"/>
-      <c r="AA25" s="87"/>
-      <c r="AB25" s="87"/>
-      <c r="AC25" s="87"/>
-      <c r="AD25" s="87"/>
+      <c r="Y25" s="141"/>
+      <c r="Z25" s="141"/>
+      <c r="AA25" s="141"/>
+      <c r="AB25" s="141"/>
+      <c r="AC25" s="141"/>
+      <c r="AD25" s="141"/>
       <c r="AF25" s="1"/>
     </row>
     <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
-      <c r="C26" s="86"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="86"/>
-      <c r="G26" s="86"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="86"/>
-      <c r="J26" s="86"/>
-      <c r="K26" s="86"/>
+      <c r="C26" s="140"/>
+      <c r="D26" s="140"/>
+      <c r="E26" s="140"/>
+      <c r="F26" s="140"/>
+      <c r="G26" s="140"/>
+      <c r="H26" s="140"/>
+      <c r="I26" s="140"/>
+      <c r="J26" s="140"/>
+      <c r="K26" s="140"/>
       <c r="L26" s="60"/>
       <c r="M26" s="1"/>
       <c r="O26" s="62" t="str">
@@ -3113,17 +3149,17 @@
     </row>
     <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
-      <c r="C27" s="88" t="s">
+      <c r="C27" s="116" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="88"/>
-      <c r="E27" s="88"/>
-      <c r="F27" s="88"/>
-      <c r="G27" s="88"/>
-      <c r="H27" s="88"/>
-      <c r="I27" s="88"/>
-      <c r="J27" s="88"/>
-      <c r="K27" s="88"/>
+      <c r="D27" s="116"/>
+      <c r="E27" s="116"/>
+      <c r="F27" s="116"/>
+      <c r="G27" s="116"/>
+      <c r="H27" s="116"/>
+      <c r="I27" s="116"/>
+      <c r="J27" s="116"/>
+      <c r="K27" s="116"/>
       <c r="M27" s="1"/>
       <c r="O27" s="64" t="str">
         <f t="shared" ref="O27:U32" ca="1" si="0">IF(MONTH($O$25)&lt;&gt;MONTH($O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1)),"",$O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1))</f>
@@ -3187,17 +3223,17 @@
     </row>
     <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
-      <c r="C28" s="89" t="s">
+      <c r="C28" s="115" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="89"/>
-      <c r="E28" s="89"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="89"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="89"/>
-      <c r="K28" s="89"/>
+      <c r="D28" s="115"/>
+      <c r="E28" s="115"/>
+      <c r="F28" s="115"/>
+      <c r="G28" s="115"/>
+      <c r="H28" s="115"/>
+      <c r="I28" s="115"/>
+      <c r="J28" s="115"/>
+      <c r="K28" s="115"/>
       <c r="M28" s="1"/>
       <c r="O28" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3261,15 +3297,15 @@
     </row>
     <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
-      <c r="C29" s="88"/>
-      <c r="D29" s="88"/>
-      <c r="E29" s="88"/>
-      <c r="F29" s="88"/>
-      <c r="G29" s="88"/>
-      <c r="H29" s="88"/>
-      <c r="I29" s="88"/>
-      <c r="J29" s="88"/>
-      <c r="K29" s="88"/>
+      <c r="C29" s="116"/>
+      <c r="D29" s="116"/>
+      <c r="E29" s="116"/>
+      <c r="F29" s="116"/>
+      <c r="G29" s="116"/>
+      <c r="H29" s="116"/>
+      <c r="I29" s="116"/>
+      <c r="J29" s="116"/>
+      <c r="K29" s="116"/>
       <c r="M29" s="1"/>
       <c r="O29" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3333,17 +3369,17 @@
     </row>
     <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
-      <c r="C30" s="89" t="s">
+      <c r="C30" s="115" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="89"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="89"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="89"/>
-      <c r="K30" s="89"/>
+      <c r="D30" s="115"/>
+      <c r="E30" s="115"/>
+      <c r="F30" s="115"/>
+      <c r="G30" s="115"/>
+      <c r="H30" s="115"/>
+      <c r="I30" s="115"/>
+      <c r="J30" s="115"/>
+      <c r="K30" s="115"/>
       <c r="M30" s="1"/>
       <c r="O30" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3407,15 +3443,15 @@
     </row>
     <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
-      <c r="C31" s="88"/>
-      <c r="D31" s="88"/>
-      <c r="E31" s="88"/>
-      <c r="F31" s="88"/>
-      <c r="G31" s="88"/>
-      <c r="H31" s="88"/>
-      <c r="I31" s="88"/>
-      <c r="J31" s="88"/>
-      <c r="K31" s="88"/>
+      <c r="C31" s="116"/>
+      <c r="D31" s="116"/>
+      <c r="E31" s="116"/>
+      <c r="F31" s="116"/>
+      <c r="G31" s="116"/>
+      <c r="H31" s="116"/>
+      <c r="I31" s="116"/>
+      <c r="J31" s="116"/>
+      <c r="K31" s="116"/>
       <c r="M31" s="1"/>
       <c r="O31" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3597,156 +3633,67 @@
     </row>
     <row r="38" spans="1:32" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D39" s="115" t="s">
+      <c r="D39" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="E39" s="116"/>
-      <c r="F39" s="117"/>
-      <c r="G39" s="121">
+      <c r="E39" s="85"/>
+      <c r="F39" s="86"/>
+      <c r="G39" s="90">
         <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
-        <v>5</v>
-      </c>
-      <c r="H39" s="122"/>
-      <c r="I39" s="115" t="s">
+        <v>4</v>
+      </c>
+      <c r="H39" s="91"/>
+      <c r="I39" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="J39" s="125"/>
-      <c r="K39" s="127" t="s">
+      <c r="J39" s="98"/>
+      <c r="K39" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="L39" s="128"/>
-      <c r="M39" s="131">
+      <c r="L39" s="95"/>
+      <c r="M39" s="106">
         <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
-        <v>3.9999999999999982</v>
-      </c>
-      <c r="N39" s="132"/>
-      <c r="O39" s="132"/>
-      <c r="P39" s="132"/>
-      <c r="Q39" s="132"/>
-      <c r="R39" s="133"/>
-      <c r="S39" s="137" t="s">
+        <v>5.0000000000000009</v>
+      </c>
+      <c r="N39" s="107"/>
+      <c r="O39" s="107"/>
+      <c r="P39" s="107"/>
+      <c r="Q39" s="107"/>
+      <c r="R39" s="108"/>
+      <c r="S39" s="100" t="s">
         <v>25</v>
       </c>
-      <c r="T39" s="138"/>
-      <c r="U39" s="138"/>
-      <c r="V39" s="138"/>
-      <c r="W39" s="138"/>
-      <c r="X39" s="139"/>
+      <c r="T39" s="101"/>
+      <c r="U39" s="101"/>
+      <c r="V39" s="101"/>
+      <c r="W39" s="101"/>
+      <c r="X39" s="102"/>
     </row>
     <row r="40" spans="1:32" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="118"/>
-      <c r="E40" s="119"/>
-      <c r="F40" s="120"/>
-      <c r="G40" s="123"/>
-      <c r="H40" s="124"/>
-      <c r="I40" s="118"/>
-      <c r="J40" s="126"/>
-      <c r="K40" s="129"/>
-      <c r="L40" s="130"/>
-      <c r="M40" s="134"/>
-      <c r="N40" s="135"/>
-      <c r="O40" s="135"/>
-      <c r="P40" s="135"/>
-      <c r="Q40" s="135"/>
-      <c r="R40" s="136"/>
-      <c r="S40" s="140"/>
-      <c r="T40" s="141"/>
-      <c r="U40" s="141"/>
-      <c r="V40" s="141"/>
-      <c r="W40" s="141"/>
-      <c r="X40" s="142"/>
+      <c r="D40" s="87"/>
+      <c r="E40" s="88"/>
+      <c r="F40" s="89"/>
+      <c r="G40" s="92"/>
+      <c r="H40" s="93"/>
+      <c r="I40" s="87"/>
+      <c r="J40" s="99"/>
+      <c r="K40" s="96"/>
+      <c r="L40" s="97"/>
+      <c r="M40" s="109"/>
+      <c r="N40" s="110"/>
+      <c r="O40" s="110"/>
+      <c r="P40" s="110"/>
+      <c r="Q40" s="110"/>
+      <c r="R40" s="111"/>
+      <c r="S40" s="103"/>
+      <c r="T40" s="104"/>
+      <c r="U40" s="104"/>
+      <c r="V40" s="104"/>
+      <c r="W40" s="104"/>
+      <c r="X40" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="110">
-    <mergeCell ref="D39:F40"/>
-    <mergeCell ref="G39:H40"/>
-    <mergeCell ref="K39:L40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="S39:X40"/>
-    <mergeCell ref="M39:R40"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="O20:V20"/>
-    <mergeCell ref="C30:K31"/>
-    <mergeCell ref="C2:AD2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="W5:AD5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:V6"/>
-    <mergeCell ref="W6:AD6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="O5:V5"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="W7:AD7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="O8:V8"/>
-    <mergeCell ref="W8:AD8"/>
-    <mergeCell ref="O7:V7"/>
-    <mergeCell ref="W9:AD9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="O11:V11"/>
-    <mergeCell ref="W11:AD11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:V9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="W12:AD12"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="O14:V14"/>
-    <mergeCell ref="W14:AD14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="O12:V12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="W15:AD15"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="O17:V17"/>
-    <mergeCell ref="W17:AD17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="O15:V15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="O16:V16"/>
     <mergeCell ref="W18:AD18"/>
     <mergeCell ref="C25:K26"/>
     <mergeCell ref="O25:U25"/>
@@ -3768,6 +3715,95 @@
     <mergeCell ref="O21:V21"/>
     <mergeCell ref="W21:AD21"/>
     <mergeCell ref="O19:V19"/>
+    <mergeCell ref="W15:AD15"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="O17:V17"/>
+    <mergeCell ref="W17:AD17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="O15:V15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="O16:V16"/>
+    <mergeCell ref="W12:AD12"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O14:V14"/>
+    <mergeCell ref="W14:AD14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="O12:V12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="W9:AD9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="O11:V11"/>
+    <mergeCell ref="W11:AD11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:V9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="W7:AD7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="O8:V8"/>
+    <mergeCell ref="W8:AD8"/>
+    <mergeCell ref="O7:V7"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:V6"/>
+    <mergeCell ref="W6:AD6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="O5:V5"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="C2:AD2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="W5:AD5"/>
+    <mergeCell ref="D39:F40"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="K39:L40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="S39:X40"/>
+    <mergeCell ref="M39:R40"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="O20:V20"/>
+    <mergeCell ref="C30:K31"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 E5 G5 I5 K5:L5 O5 W5 C7 E8 G8 I8 K8:L8 O8 W8 C10 E11 G11 I11 K11:L11 O11 W11 C13 E14 G14 I14 K14:L14 O14 W14 C16 E17 G17 I17 K17:L17 O17 W17">
     <cfRule type="expression" dxfId="11" priority="3">
@@ -3858,42 +3894,42 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.9">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A2" s="29"/>
-      <c r="C2" s="113">
+      <c r="C2" s="117">
         <f ca="1">DATE(About!P8,10,1)</f>
         <v>46296</v>
       </c>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
-      <c r="P2" s="113"/>
-      <c r="Q2" s="113"/>
-      <c r="R2" s="113"/>
-      <c r="S2" s="113"/>
-      <c r="T2" s="113"/>
-      <c r="U2" s="113"/>
-      <c r="V2" s="113"/>
-      <c r="W2" s="113"/>
-      <c r="X2" s="113"/>
-      <c r="Y2" s="113"/>
-      <c r="Z2" s="113"/>
-      <c r="AA2" s="113"/>
-      <c r="AB2" s="113"/>
-      <c r="AC2" s="113"/>
-      <c r="AD2" s="113"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="117"/>
+      <c r="M2" s="117"/>
+      <c r="N2" s="117"/>
+      <c r="O2" s="117"/>
+      <c r="P2" s="117"/>
+      <c r="Q2" s="117"/>
+      <c r="R2" s="117"/>
+      <c r="S2" s="117"/>
+      <c r="T2" s="117"/>
+      <c r="U2" s="117"/>
+      <c r="V2" s="117"/>
+      <c r="W2" s="117"/>
+      <c r="X2" s="117"/>
+      <c r="Y2" s="117"/>
+      <c r="Z2" s="117"/>
+      <c r="AA2" s="117"/>
+      <c r="AB2" s="117"/>
+      <c r="AC2" s="117"/>
+      <c r="AD2" s="117"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.9">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -3913,114 +3949,114 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="35"/>
-      <c r="C4" s="114">
+      <c r="C4" s="118">
         <f ca="1">C5</f>
         <v>46292</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114">
+      <c r="D4" s="118"/>
+      <c r="E4" s="118">
         <f ca="1">E5</f>
         <v>46293</v>
       </c>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114">
+      <c r="F4" s="118"/>
+      <c r="G4" s="118">
         <f ca="1">G5</f>
         <v>46294</v>
       </c>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114">
+      <c r="H4" s="118"/>
+      <c r="I4" s="118">
         <f ca="1">I5</f>
         <v>46295</v>
       </c>
-      <c r="J4" s="114"/>
-      <c r="K4" s="114">
+      <c r="J4" s="118"/>
+      <c r="K4" s="118">
         <f ca="1">K5</f>
         <v>46296</v>
       </c>
-      <c r="L4" s="114"/>
-      <c r="M4" s="114"/>
+      <c r="L4" s="118"/>
+      <c r="M4" s="118"/>
       <c r="N4" s="37"/>
-      <c r="O4" s="114">
+      <c r="O4" s="118">
         <f ca="1">O5</f>
         <v>46297</v>
       </c>
-      <c r="P4" s="114"/>
-      <c r="Q4" s="114"/>
-      <c r="R4" s="114"/>
-      <c r="S4" s="114"/>
-      <c r="T4" s="114"/>
-      <c r="U4" s="114"/>
-      <c r="V4" s="114"/>
-      <c r="W4" s="114">
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118"/>
+      <c r="S4" s="118"/>
+      <c r="T4" s="118"/>
+      <c r="U4" s="118"/>
+      <c r="V4" s="118"/>
+      <c r="W4" s="118">
         <f ca="1">W5</f>
         <v>46298</v>
       </c>
-      <c r="X4" s="114"/>
-      <c r="Y4" s="114"/>
-      <c r="Z4" s="114"/>
-      <c r="AA4" s="114"/>
-      <c r="AB4" s="114"/>
-      <c r="AC4" s="114"/>
-      <c r="AD4" s="114"/>
+      <c r="X4" s="118"/>
+      <c r="Y4" s="118"/>
+      <c r="Z4" s="118"/>
+      <c r="AA4" s="118"/>
+      <c r="AB4" s="118"/>
+      <c r="AC4" s="118"/>
+      <c r="AD4" s="118"/>
       <c r="AF4" s="38"/>
       <c r="AG4" s="39"/>
       <c r="AH4" s="39"/>
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
-      <c r="C5" s="92">
+      <c r="C5" s="119">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46292</v>
       </c>
-      <c r="D5" s="93"/>
-      <c r="E5" s="92">
+      <c r="D5" s="121"/>
+      <c r="E5" s="119">
         <f ca="1">C5+1</f>
         <v>46293</v>
       </c>
-      <c r="F5" s="93"/>
-      <c r="G5" s="92">
+      <c r="F5" s="121"/>
+      <c r="G5" s="119">
         <f ca="1">E5+1</f>
         <v>46294</v>
       </c>
-      <c r="H5" s="93"/>
-      <c r="I5" s="92">
+      <c r="H5" s="121"/>
+      <c r="I5" s="119">
         <f ca="1">G5+1</f>
         <v>46295</v>
       </c>
-      <c r="J5" s="93"/>
-      <c r="K5" s="92">
+      <c r="J5" s="121"/>
+      <c r="K5" s="119">
         <f ca="1">I5+1</f>
         <v>46296</v>
       </c>
-      <c r="L5" s="112"/>
-      <c r="M5" s="112"/>
+      <c r="L5" s="120"/>
+      <c r="M5" s="120"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="92">
+      <c r="O5" s="119">
         <f ca="1">K5+1</f>
         <v>46297</v>
       </c>
-      <c r="P5" s="112"/>
-      <c r="Q5" s="112"/>
-      <c r="R5" s="112"/>
-      <c r="S5" s="112"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="112"/>
-      <c r="V5" s="93"/>
-      <c r="W5" s="92">
+      <c r="P5" s="120"/>
+      <c r="Q5" s="120"/>
+      <c r="R5" s="120"/>
+      <c r="S5" s="120"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="121"/>
+      <c r="W5" s="119">
         <f ca="1">O5+1</f>
         <v>46298</v>
       </c>
-      <c r="X5" s="112"/>
-      <c r="Y5" s="112"/>
-      <c r="Z5" s="112"/>
-      <c r="AA5" s="112"/>
-      <c r="AB5" s="112"/>
-      <c r="AC5" s="112"/>
-      <c r="AD5" s="93"/>
+      <c r="X5" s="120"/>
+      <c r="Y5" s="120"/>
+      <c r="Z5" s="120"/>
+      <c r="AA5" s="120"/>
+      <c r="AB5" s="120"/>
+      <c r="AC5" s="120"/>
+      <c r="AD5" s="121"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
@@ -4029,174 +4065,174 @@
     </row>
     <row r="6" spans="1:36" s="43" customFormat="1" ht="131.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="42"/>
-      <c r="C6" s="104"/>
-      <c r="D6" s="105"/>
-      <c r="E6" s="104"/>
-      <c r="F6" s="105"/>
-      <c r="G6" s="104"/>
-      <c r="H6" s="105"/>
-      <c r="I6" s="104"/>
-      <c r="J6" s="105"/>
-      <c r="K6" s="106"/>
-      <c r="L6" s="107"/>
-      <c r="M6" s="107"/>
-      <c r="N6" s="108"/>
-      <c r="O6" s="106"/>
-      <c r="P6" s="107"/>
-      <c r="Q6" s="107"/>
-      <c r="R6" s="107"/>
-      <c r="S6" s="107"/>
-      <c r="T6" s="107"/>
-      <c r="U6" s="107"/>
-      <c r="V6" s="108"/>
-      <c r="W6" s="109" t="s">
+      <c r="C6" s="144"/>
+      <c r="D6" s="145"/>
+      <c r="E6" s="144"/>
+      <c r="F6" s="145"/>
+      <c r="G6" s="144"/>
+      <c r="H6" s="145"/>
+      <c r="I6" s="144"/>
+      <c r="J6" s="145"/>
+      <c r="K6" s="133"/>
+      <c r="L6" s="134"/>
+      <c r="M6" s="134"/>
+      <c r="N6" s="135"/>
+      <c r="O6" s="133"/>
+      <c r="P6" s="134"/>
+      <c r="Q6" s="134"/>
+      <c r="R6" s="134"/>
+      <c r="S6" s="134"/>
+      <c r="T6" s="134"/>
+      <c r="U6" s="134"/>
+      <c r="V6" s="135"/>
+      <c r="W6" s="142" t="s">
         <v>19</v>
       </c>
-      <c r="X6" s="110"/>
-      <c r="Y6" s="110"/>
-      <c r="Z6" s="110"/>
-      <c r="AA6" s="110"/>
-      <c r="AB6" s="110"/>
-      <c r="AC6" s="110"/>
-      <c r="AD6" s="111"/>
+      <c r="X6" s="146"/>
+      <c r="Y6" s="146"/>
+      <c r="Z6" s="146"/>
+      <c r="AA6" s="146"/>
+      <c r="AB6" s="146"/>
+      <c r="AC6" s="146"/>
+      <c r="AD6" s="143"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
     <row r="7" spans="1:36" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="C7" s="92">
+      <c r="C7" s="119">
         <f ca="1">W5+1</f>
         <v>46299</v>
       </c>
-      <c r="D7" s="93"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="102"/>
-      <c r="G7" s="101"/>
-      <c r="H7" s="102"/>
-      <c r="I7" s="101"/>
-      <c r="J7" s="102"/>
-      <c r="K7" s="101"/>
-      <c r="L7" s="103"/>
-      <c r="M7" s="103"/>
+      <c r="D7" s="121"/>
+      <c r="E7" s="127"/>
+      <c r="F7" s="128"/>
+      <c r="G7" s="127"/>
+      <c r="H7" s="128"/>
+      <c r="I7" s="127"/>
+      <c r="J7" s="128"/>
+      <c r="K7" s="127"/>
+      <c r="L7" s="129"/>
+      <c r="M7" s="129"/>
       <c r="N7" s="75"/>
-      <c r="O7" s="101"/>
-      <c r="P7" s="103"/>
-      <c r="Q7" s="103"/>
-      <c r="R7" s="103"/>
-      <c r="S7" s="103"/>
-      <c r="T7" s="103"/>
-      <c r="U7" s="103"/>
-      <c r="V7" s="102"/>
-      <c r="W7" s="101"/>
-      <c r="X7" s="103"/>
-      <c r="Y7" s="103"/>
-      <c r="Z7" s="103"/>
-      <c r="AA7" s="103"/>
-      <c r="AB7" s="103"/>
-      <c r="AC7" s="103"/>
-      <c r="AD7" s="102"/>
+      <c r="O7" s="127"/>
+      <c r="P7" s="129"/>
+      <c r="Q7" s="129"/>
+      <c r="R7" s="129"/>
+      <c r="S7" s="129"/>
+      <c r="T7" s="129"/>
+      <c r="U7" s="129"/>
+      <c r="V7" s="128"/>
+      <c r="W7" s="127"/>
+      <c r="X7" s="129"/>
+      <c r="Y7" s="129"/>
+      <c r="Z7" s="129"/>
+      <c r="AA7" s="129"/>
+      <c r="AB7" s="129"/>
+      <c r="AC7" s="129"/>
+      <c r="AD7" s="128"/>
       <c r="AF7" s="1"/>
     </row>
     <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
-      <c r="C8" s="92"/>
-      <c r="D8" s="93"/>
-      <c r="E8" s="94">
+      <c r="C8" s="119"/>
+      <c r="D8" s="121"/>
+      <c r="E8" s="112">
         <f ca="1">C7+1</f>
         <v>46300</v>
       </c>
-      <c r="F8" s="95"/>
-      <c r="G8" s="94">
+      <c r="F8" s="113"/>
+      <c r="G8" s="112">
         <f ca="1">E8+1</f>
         <v>46301</v>
       </c>
-      <c r="H8" s="95"/>
-      <c r="I8" s="94">
+      <c r="H8" s="113"/>
+      <c r="I8" s="112">
         <f ca="1">G8+1</f>
         <v>46302</v>
       </c>
-      <c r="J8" s="95"/>
-      <c r="K8" s="94">
+      <c r="J8" s="113"/>
+      <c r="K8" s="112">
         <f ca="1">I8+1</f>
         <v>46303</v>
       </c>
-      <c r="L8" s="96"/>
-      <c r="M8" s="96"/>
+      <c r="L8" s="114"/>
+      <c r="M8" s="114"/>
       <c r="N8" s="50"/>
-      <c r="O8" s="94">
+      <c r="O8" s="112">
         <f ca="1">K8+1</f>
         <v>46304</v>
       </c>
-      <c r="P8" s="96"/>
-      <c r="Q8" s="96"/>
-      <c r="R8" s="96"/>
-      <c r="S8" s="96"/>
-      <c r="T8" s="96"/>
-      <c r="U8" s="96"/>
-      <c r="V8" s="95"/>
-      <c r="W8" s="94">
+      <c r="P8" s="114"/>
+      <c r="Q8" s="114"/>
+      <c r="R8" s="114"/>
+      <c r="S8" s="114"/>
+      <c r="T8" s="114"/>
+      <c r="U8" s="114"/>
+      <c r="V8" s="113"/>
+      <c r="W8" s="112">
         <f ca="1">O8+1</f>
         <v>46305</v>
       </c>
-      <c r="X8" s="96"/>
-      <c r="Y8" s="96"/>
-      <c r="Z8" s="96"/>
-      <c r="AA8" s="96"/>
-      <c r="AB8" s="96"/>
-      <c r="AC8" s="96"/>
-      <c r="AD8" s="95"/>
+      <c r="X8" s="114"/>
+      <c r="Y8" s="114"/>
+      <c r="Z8" s="114"/>
+      <c r="AA8" s="114"/>
+      <c r="AB8" s="114"/>
+      <c r="AC8" s="114"/>
+      <c r="AD8" s="113"/>
       <c r="AF8" s="4"/>
     </row>
     <row r="9" spans="1:36" s="43" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="42"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="85"/>
-      <c r="E9" s="83" t="s">
+      <c r="C9" s="147"/>
+      <c r="D9" s="149"/>
+      <c r="E9" s="147" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="85"/>
-      <c r="G9" s="83" t="s">
+      <c r="F9" s="149"/>
+      <c r="G9" s="147" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="85"/>
-      <c r="I9" s="83" t="s">
-        <v>37</v>
-      </c>
-      <c r="J9" s="85"/>
-      <c r="K9" s="83" t="s">
-        <v>29</v>
-      </c>
-      <c r="L9" s="84"/>
-      <c r="M9" s="84"/>
-      <c r="N9" s="85"/>
-      <c r="O9" s="83" t="s">
-        <v>48</v>
-      </c>
-      <c r="P9" s="84"/>
-      <c r="Q9" s="84"/>
-      <c r="R9" s="84"/>
-      <c r="S9" s="84"/>
-      <c r="T9" s="84"/>
-      <c r="U9" s="84"/>
-      <c r="V9" s="85"/>
-      <c r="W9" s="83"/>
-      <c r="X9" s="84"/>
-      <c r="Y9" s="84"/>
-      <c r="Z9" s="84"/>
-      <c r="AA9" s="84"/>
-      <c r="AB9" s="84"/>
-      <c r="AC9" s="84"/>
-      <c r="AD9" s="85"/>
+      <c r="H9" s="149"/>
+      <c r="I9" s="147" t="s">
+        <v>36</v>
+      </c>
+      <c r="J9" s="149"/>
+      <c r="K9" s="147" t="s">
+        <v>61</v>
+      </c>
+      <c r="L9" s="148"/>
+      <c r="M9" s="148"/>
+      <c r="N9" s="149"/>
+      <c r="O9" s="147" t="s">
+        <v>47</v>
+      </c>
+      <c r="P9" s="148"/>
+      <c r="Q9" s="148"/>
+      <c r="R9" s="148"/>
+      <c r="S9" s="148"/>
+      <c r="T9" s="148"/>
+      <c r="U9" s="148"/>
+      <c r="V9" s="149"/>
+      <c r="W9" s="147"/>
+      <c r="X9" s="148"/>
+      <c r="Y9" s="148"/>
+      <c r="Z9" s="148"/>
+      <c r="AA9" s="148"/>
+      <c r="AB9" s="148"/>
+      <c r="AC9" s="148"/>
+      <c r="AD9" s="149"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
     <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="42"/>
-      <c r="C10" s="92">
+      <c r="C10" s="119">
         <f ca="1">W8+1</f>
         <v>46306</v>
       </c>
-      <c r="D10" s="93"/>
+      <c r="D10" s="121"/>
       <c r="E10" s="45"/>
       <c r="F10" s="75"/>
       <c r="G10" s="45"/>
@@ -4228,109 +4264,109 @@
     </row>
     <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
-      <c r="C11" s="92"/>
-      <c r="D11" s="93"/>
-      <c r="E11" s="94">
+      <c r="C11" s="119"/>
+      <c r="D11" s="121"/>
+      <c r="E11" s="112">
         <f ca="1">C10+1</f>
         <v>46307</v>
       </c>
-      <c r="F11" s="95"/>
-      <c r="G11" s="94">
+      <c r="F11" s="113"/>
+      <c r="G11" s="112">
         <f ca="1">E11+1</f>
         <v>46308</v>
       </c>
-      <c r="H11" s="95"/>
-      <c r="I11" s="94">
+      <c r="H11" s="113"/>
+      <c r="I11" s="112">
         <f ca="1">G11+1</f>
         <v>46309</v>
       </c>
-      <c r="J11" s="95"/>
-      <c r="K11" s="94">
+      <c r="J11" s="113"/>
+      <c r="K11" s="112">
         <f ca="1">I11+1</f>
         <v>46310</v>
       </c>
-      <c r="L11" s="96"/>
-      <c r="M11" s="96"/>
+      <c r="L11" s="114"/>
+      <c r="M11" s="114"/>
       <c r="N11" s="50"/>
-      <c r="O11" s="94">
+      <c r="O11" s="112">
         <f ca="1">K11+1</f>
         <v>46311</v>
       </c>
-      <c r="P11" s="96"/>
-      <c r="Q11" s="96"/>
-      <c r="R11" s="96"/>
-      <c r="S11" s="96"/>
-      <c r="T11" s="96"/>
-      <c r="U11" s="96"/>
-      <c r="V11" s="95"/>
-      <c r="W11" s="94">
+      <c r="P11" s="114"/>
+      <c r="Q11" s="114"/>
+      <c r="R11" s="114"/>
+      <c r="S11" s="114"/>
+      <c r="T11" s="114"/>
+      <c r="U11" s="114"/>
+      <c r="V11" s="113"/>
+      <c r="W11" s="112">
         <f ca="1">O11+1</f>
         <v>46312</v>
       </c>
-      <c r="X11" s="96"/>
-      <c r="Y11" s="96"/>
-      <c r="Z11" s="96"/>
-      <c r="AA11" s="96"/>
-      <c r="AB11" s="96"/>
-      <c r="AC11" s="96"/>
-      <c r="AD11" s="95"/>
+      <c r="X11" s="114"/>
+      <c r="Y11" s="114"/>
+      <c r="Z11" s="114"/>
+      <c r="AA11" s="114"/>
+      <c r="AB11" s="114"/>
+      <c r="AC11" s="114"/>
+      <c r="AD11" s="113"/>
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
     <row r="12" spans="1:36" s="43" customFormat="1" ht="134.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="42"/>
-      <c r="C12" s="163" t="s">
-        <v>47</v>
-      </c>
-      <c r="D12" s="164"/>
-      <c r="E12" s="100" t="s">
+      <c r="C12" s="151" t="s">
+        <v>46</v>
+      </c>
+      <c r="D12" s="152"/>
+      <c r="E12" s="153" t="s">
+        <v>38</v>
+      </c>
+      <c r="F12" s="149"/>
+      <c r="G12" s="147" t="s">
+        <v>37</v>
+      </c>
+      <c r="H12" s="149"/>
+      <c r="I12" s="151" t="s">
+        <v>58</v>
+      </c>
+      <c r="J12" s="152"/>
+      <c r="K12" s="153" t="s">
         <v>39</v>
       </c>
-      <c r="F12" s="85"/>
-      <c r="G12" s="83" t="s">
-        <v>38</v>
-      </c>
-      <c r="H12" s="85"/>
-      <c r="I12" s="163" t="s">
-        <v>59</v>
-      </c>
-      <c r="J12" s="164"/>
-      <c r="K12" s="100" t="s">
-        <v>40</v>
-      </c>
-      <c r="L12" s="84"/>
-      <c r="M12" s="84"/>
-      <c r="N12" s="85"/>
-      <c r="O12" s="83" t="s">
-        <v>58</v>
-      </c>
-      <c r="P12" s="84"/>
-      <c r="Q12" s="84"/>
-      <c r="R12" s="84"/>
-      <c r="S12" s="84"/>
-      <c r="T12" s="84"/>
-      <c r="U12" s="84"/>
-      <c r="V12" s="85"/>
-      <c r="W12" s="99" t="s">
-        <v>30</v>
-      </c>
-      <c r="X12" s="84"/>
-      <c r="Y12" s="84"/>
-      <c r="Z12" s="84"/>
-      <c r="AA12" s="84"/>
-      <c r="AB12" s="84"/>
-      <c r="AC12" s="84"/>
-      <c r="AD12" s="85"/>
+      <c r="L12" s="148"/>
+      <c r="M12" s="148"/>
+      <c r="N12" s="149"/>
+      <c r="O12" s="147" t="s">
+        <v>57</v>
+      </c>
+      <c r="P12" s="148"/>
+      <c r="Q12" s="148"/>
+      <c r="R12" s="148"/>
+      <c r="S12" s="148"/>
+      <c r="T12" s="148"/>
+      <c r="U12" s="148"/>
+      <c r="V12" s="149"/>
+      <c r="W12" s="150" t="s">
+        <v>29</v>
+      </c>
+      <c r="X12" s="148"/>
+      <c r="Y12" s="148"/>
+      <c r="Z12" s="148"/>
+      <c r="AA12" s="148"/>
+      <c r="AB12" s="148"/>
+      <c r="AC12" s="148"/>
+      <c r="AD12" s="149"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
     <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="42"/>
-      <c r="C13" s="92">
+      <c r="C13" s="119">
         <f ca="1">W11+1</f>
         <v>46313</v>
       </c>
-      <c r="D13" s="93"/>
+      <c r="D13" s="121"/>
       <c r="E13" s="45"/>
       <c r="F13" s="75"/>
       <c r="G13" s="45"/>
@@ -4362,108 +4398,108 @@
     </row>
     <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4"/>
-      <c r="C14" s="92"/>
-      <c r="D14" s="93"/>
-      <c r="E14" s="94">
+      <c r="C14" s="119"/>
+      <c r="D14" s="121"/>
+      <c r="E14" s="112">
         <f ca="1">C13+1</f>
         <v>46314</v>
       </c>
-      <c r="F14" s="95"/>
-      <c r="G14" s="94">
+      <c r="F14" s="113"/>
+      <c r="G14" s="112">
         <f ca="1">E14+1</f>
         <v>46315</v>
       </c>
-      <c r="H14" s="95"/>
-      <c r="I14" s="94">
+      <c r="H14" s="113"/>
+      <c r="I14" s="112">
         <f ca="1">G14+1</f>
         <v>46316</v>
       </c>
-      <c r="J14" s="95"/>
-      <c r="K14" s="94">
+      <c r="J14" s="113"/>
+      <c r="K14" s="112">
         <f ca="1">I14+1</f>
         <v>46317</v>
       </c>
-      <c r="L14" s="96"/>
-      <c r="M14" s="96"/>
+      <c r="L14" s="114"/>
+      <c r="M14" s="114"/>
       <c r="N14" s="50"/>
-      <c r="O14" s="94">
+      <c r="O14" s="112">
         <f ca="1">K14+1</f>
         <v>46318</v>
       </c>
-      <c r="P14" s="96"/>
-      <c r="Q14" s="96"/>
-      <c r="R14" s="96"/>
-      <c r="S14" s="96"/>
-      <c r="T14" s="96"/>
-      <c r="U14" s="96"/>
-      <c r="V14" s="95"/>
-      <c r="W14" s="94">
+      <c r="P14" s="114"/>
+      <c r="Q14" s="114"/>
+      <c r="R14" s="114"/>
+      <c r="S14" s="114"/>
+      <c r="T14" s="114"/>
+      <c r="U14" s="114"/>
+      <c r="V14" s="113"/>
+      <c r="W14" s="112">
         <f ca="1">O14+1</f>
         <v>46319</v>
       </c>
-      <c r="X14" s="96"/>
-      <c r="Y14" s="96"/>
-      <c r="Z14" s="96"/>
-      <c r="AA14" s="96"/>
-      <c r="AB14" s="96"/>
-      <c r="AC14" s="96"/>
-      <c r="AD14" s="95"/>
+      <c r="X14" s="114"/>
+      <c r="Y14" s="114"/>
+      <c r="Z14" s="114"/>
+      <c r="AA14" s="114"/>
+      <c r="AB14" s="114"/>
+      <c r="AC14" s="114"/>
+      <c r="AD14" s="113"/>
       <c r="AF14" s="4"/>
     </row>
     <row r="15" spans="1:36" s="43" customFormat="1" ht="140.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="42"/>
-      <c r="C15" s="99" t="s">
+      <c r="C15" s="150" t="s">
+        <v>30</v>
+      </c>
+      <c r="D15" s="149"/>
+      <c r="E15" s="151" t="s">
+        <v>49</v>
+      </c>
+      <c r="F15" s="152"/>
+      <c r="G15" s="151" t="s">
+        <v>50</v>
+      </c>
+      <c r="H15" s="152"/>
+      <c r="I15" s="150" t="s">
+        <v>33</v>
+      </c>
+      <c r="J15" s="149"/>
+      <c r="K15" s="151" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15" s="154"/>
+      <c r="M15" s="154"/>
+      <c r="N15" s="152"/>
+      <c r="O15" s="147" t="s">
         <v>31</v>
       </c>
-      <c r="D15" s="85"/>
-      <c r="E15" s="163" t="s">
-        <v>50</v>
-      </c>
-      <c r="F15" s="164"/>
-      <c r="G15" s="163" t="s">
-        <v>51</v>
-      </c>
-      <c r="H15" s="164"/>
-      <c r="I15" s="99" t="s">
-        <v>34</v>
-      </c>
-      <c r="J15" s="85"/>
-      <c r="K15" s="163" t="s">
-        <v>60</v>
-      </c>
-      <c r="L15" s="165"/>
-      <c r="M15" s="165"/>
-      <c r="N15" s="164"/>
-      <c r="O15" s="83" t="s">
+      <c r="P15" s="148"/>
+      <c r="Q15" s="148"/>
+      <c r="R15" s="148"/>
+      <c r="S15" s="148"/>
+      <c r="T15" s="148"/>
+      <c r="U15" s="148"/>
+      <c r="V15" s="149"/>
+      <c r="W15" s="150" t="s">
         <v>32</v>
       </c>
-      <c r="P15" s="84"/>
-      <c r="Q15" s="84"/>
-      <c r="R15" s="84"/>
-      <c r="S15" s="84"/>
-      <c r="T15" s="84"/>
-      <c r="U15" s="84"/>
-      <c r="V15" s="85"/>
-      <c r="W15" s="99" t="s">
-        <v>33</v>
-      </c>
-      <c r="X15" s="84"/>
-      <c r="Y15" s="84"/>
-      <c r="Z15" s="84"/>
-      <c r="AA15" s="84"/>
-      <c r="AB15" s="84"/>
-      <c r="AC15" s="84"/>
-      <c r="AD15" s="85"/>
+      <c r="X15" s="148"/>
+      <c r="Y15" s="148"/>
+      <c r="Z15" s="148"/>
+      <c r="AA15" s="148"/>
+      <c r="AB15" s="148"/>
+      <c r="AC15" s="148"/>
+      <c r="AD15" s="149"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
     <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="42"/>
-      <c r="C16" s="92">
+      <c r="C16" s="119">
         <f ca="1">W14+1</f>
         <v>46320</v>
       </c>
-      <c r="D16" s="93"/>
+      <c r="D16" s="121"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
@@ -4495,107 +4531,107 @@
     </row>
     <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
-      <c r="C17" s="92"/>
-      <c r="D17" s="93"/>
-      <c r="E17" s="94">
+      <c r="C17" s="119"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="112">
         <f ca="1">C16+1</f>
         <v>46321</v>
       </c>
-      <c r="F17" s="95"/>
-      <c r="G17" s="94">
+      <c r="F17" s="113"/>
+      <c r="G17" s="112">
         <f ca="1">E17+1</f>
         <v>46322</v>
       </c>
-      <c r="H17" s="95"/>
-      <c r="I17" s="94">
+      <c r="H17" s="113"/>
+      <c r="I17" s="112">
         <f ca="1">G17+1</f>
         <v>46323</v>
       </c>
-      <c r="J17" s="95"/>
-      <c r="K17" s="94">
+      <c r="J17" s="113"/>
+      <c r="K17" s="112">
         <f ca="1">I17+1</f>
         <v>46324</v>
       </c>
-      <c r="L17" s="96"/>
-      <c r="M17" s="96"/>
+      <c r="L17" s="114"/>
+      <c r="M17" s="114"/>
       <c r="N17" s="50"/>
-      <c r="O17" s="94">
+      <c r="O17" s="112">
         <f ca="1">K17+1</f>
         <v>46325</v>
       </c>
-      <c r="P17" s="96"/>
-      <c r="Q17" s="96"/>
-      <c r="R17" s="96"/>
-      <c r="S17" s="96"/>
-      <c r="T17" s="96"/>
-      <c r="U17" s="96"/>
-      <c r="V17" s="95"/>
-      <c r="W17" s="94">
+      <c r="P17" s="114"/>
+      <c r="Q17" s="114"/>
+      <c r="R17" s="114"/>
+      <c r="S17" s="114"/>
+      <c r="T17" s="114"/>
+      <c r="U17" s="114"/>
+      <c r="V17" s="113"/>
+      <c r="W17" s="112">
         <f ca="1">O17+1</f>
         <v>46326</v>
       </c>
-      <c r="X17" s="96"/>
-      <c r="Y17" s="96"/>
-      <c r="Z17" s="96"/>
-      <c r="AA17" s="96"/>
-      <c r="AB17" s="96"/>
-      <c r="AC17" s="96"/>
-      <c r="AD17" s="95"/>
+      <c r="X17" s="114"/>
+      <c r="Y17" s="114"/>
+      <c r="Z17" s="114"/>
+      <c r="AA17" s="114"/>
+      <c r="AB17" s="114"/>
+      <c r="AC17" s="114"/>
+      <c r="AD17" s="113"/>
       <c r="AF17" s="4"/>
     </row>
     <row r="18" spans="1:42" s="43" customFormat="1" ht="149.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="42"/>
-      <c r="C18" s="163" t="s">
-        <v>61</v>
-      </c>
-      <c r="D18" s="164"/>
-      <c r="E18" s="83" t="s">
+      <c r="C18" s="151" t="s">
+        <v>60</v>
+      </c>
+      <c r="D18" s="152"/>
+      <c r="E18" s="147" t="s">
+        <v>44</v>
+      </c>
+      <c r="F18" s="149"/>
+      <c r="G18" s="151" t="s">
         <v>45</v>
       </c>
-      <c r="F18" s="85"/>
-      <c r="G18" s="163" t="s">
-        <v>46</v>
-      </c>
-      <c r="H18" s="164"/>
-      <c r="I18" s="163" t="s">
+      <c r="H18" s="152"/>
+      <c r="I18" s="151" t="s">
+        <v>51</v>
+      </c>
+      <c r="J18" s="152"/>
+      <c r="K18" s="155" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="148"/>
+      <c r="M18" s="148"/>
+      <c r="N18" s="82"/>
+      <c r="O18" s="151" t="s">
         <v>52</v>
       </c>
-      <c r="J18" s="164"/>
-      <c r="K18" s="91" t="s">
-        <v>35</v>
-      </c>
-      <c r="L18" s="84"/>
-      <c r="M18" s="84"/>
-      <c r="N18" s="82"/>
-      <c r="O18" s="163" t="s">
-        <v>53</v>
-      </c>
-      <c r="P18" s="165"/>
-      <c r="Q18" s="165"/>
-      <c r="R18" s="165"/>
-      <c r="S18" s="165"/>
-      <c r="T18" s="165"/>
-      <c r="U18" s="165"/>
-      <c r="V18" s="164"/>
-      <c r="W18" s="83"/>
-      <c r="X18" s="84"/>
-      <c r="Y18" s="84"/>
-      <c r="Z18" s="84"/>
-      <c r="AA18" s="84"/>
-      <c r="AB18" s="84"/>
-      <c r="AC18" s="84"/>
-      <c r="AD18" s="85"/>
+      <c r="P18" s="154"/>
+      <c r="Q18" s="154"/>
+      <c r="R18" s="154"/>
+      <c r="S18" s="154"/>
+      <c r="T18" s="154"/>
+      <c r="U18" s="154"/>
+      <c r="V18" s="152"/>
+      <c r="W18" s="147"/>
+      <c r="X18" s="148"/>
+      <c r="Y18" s="148"/>
+      <c r="Z18" s="148"/>
+      <c r="AA18" s="148"/>
+      <c r="AB18" s="148"/>
+      <c r="AC18" s="148"/>
+      <c r="AD18" s="149"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
     <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="42"/>
-      <c r="C19" s="92">
+      <c r="C19" s="119">
         <f ca="1">W17+1</f>
         <v>46327</v>
       </c>
-      <c r="D19" s="93"/>
+      <c r="D19" s="121"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
@@ -4627,84 +4663,84 @@
     </row>
     <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
-      <c r="C20" s="92"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="94">
+      <c r="C20" s="119"/>
+      <c r="D20" s="121"/>
+      <c r="E20" s="112">
         <f ca="1">C19+1</f>
         <v>46328</v>
       </c>
-      <c r="F20" s="95"/>
-      <c r="G20" s="94">
+      <c r="F20" s="113"/>
+      <c r="G20" s="112">
         <f ca="1">E20+1</f>
         <v>46329</v>
       </c>
-      <c r="H20" s="95"/>
-      <c r="I20" s="94">
+      <c r="H20" s="113"/>
+      <c r="I20" s="112">
         <f ca="1">G20+1</f>
         <v>46330</v>
       </c>
-      <c r="J20" s="95"/>
-      <c r="K20" s="94">
+      <c r="J20" s="113"/>
+      <c r="K20" s="112">
         <f ca="1">I20+1</f>
         <v>46331</v>
       </c>
-      <c r="L20" s="96"/>
-      <c r="M20" s="96"/>
+      <c r="L20" s="114"/>
+      <c r="M20" s="114"/>
       <c r="N20" s="50"/>
-      <c r="O20" s="94">
+      <c r="O20" s="112">
         <f ca="1">K20+1</f>
         <v>46332</v>
       </c>
-      <c r="P20" s="96"/>
-      <c r="Q20" s="96"/>
-      <c r="R20" s="96"/>
-      <c r="S20" s="96"/>
-      <c r="T20" s="96"/>
-      <c r="U20" s="96"/>
-      <c r="V20" s="95"/>
-      <c r="W20" s="94">
+      <c r="P20" s="114"/>
+      <c r="Q20" s="114"/>
+      <c r="R20" s="114"/>
+      <c r="S20" s="114"/>
+      <c r="T20" s="114"/>
+      <c r="U20" s="114"/>
+      <c r="V20" s="113"/>
+      <c r="W20" s="112">
         <f ca="1">O20+1</f>
         <v>46333</v>
       </c>
-      <c r="X20" s="96"/>
-      <c r="Y20" s="96"/>
-      <c r="Z20" s="96"/>
-      <c r="AA20" s="96"/>
-      <c r="AB20" s="96"/>
-      <c r="AC20" s="96"/>
-      <c r="AD20" s="95"/>
+      <c r="X20" s="114"/>
+      <c r="Y20" s="114"/>
+      <c r="Z20" s="114"/>
+      <c r="AA20" s="114"/>
+      <c r="AB20" s="114"/>
+      <c r="AC20" s="114"/>
+      <c r="AD20" s="113"/>
       <c r="AF20" s="4"/>
     </row>
     <row r="21" spans="1:42" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="42"/>
-      <c r="C21" s="97"/>
-      <c r="D21" s="98"/>
-      <c r="E21" s="97"/>
-      <c r="F21" s="98"/>
-      <c r="G21" s="97"/>
-      <c r="H21" s="98"/>
-      <c r="I21" s="97"/>
-      <c r="J21" s="98"/>
-      <c r="K21" s="97"/>
-      <c r="L21" s="143"/>
-      <c r="M21" s="143"/>
+      <c r="C21" s="122"/>
+      <c r="D21" s="123"/>
+      <c r="E21" s="122"/>
+      <c r="F21" s="123"/>
+      <c r="G21" s="122"/>
+      <c r="H21" s="123"/>
+      <c r="I21" s="122"/>
+      <c r="J21" s="123"/>
+      <c r="K21" s="122"/>
+      <c r="L21" s="139"/>
+      <c r="M21" s="139"/>
       <c r="N21" s="44"/>
-      <c r="O21" s="97"/>
-      <c r="P21" s="143"/>
-      <c r="Q21" s="143"/>
-      <c r="R21" s="143"/>
-      <c r="S21" s="143"/>
-      <c r="T21" s="143"/>
-      <c r="U21" s="143"/>
-      <c r="V21" s="98"/>
-      <c r="W21" s="97"/>
-      <c r="X21" s="143"/>
-      <c r="Y21" s="143"/>
-      <c r="Z21" s="143"/>
-      <c r="AA21" s="143"/>
-      <c r="AB21" s="143"/>
-      <c r="AC21" s="143"/>
-      <c r="AD21" s="98"/>
+      <c r="O21" s="122"/>
+      <c r="P21" s="139"/>
+      <c r="Q21" s="139"/>
+      <c r="R21" s="139"/>
+      <c r="S21" s="139"/>
+      <c r="T21" s="139"/>
+      <c r="U21" s="139"/>
+      <c r="V21" s="123"/>
+      <c r="W21" s="122"/>
+      <c r="X21" s="139"/>
+      <c r="Y21" s="139"/>
+      <c r="Z21" s="139"/>
+      <c r="AA21" s="139"/>
+      <c r="AB21" s="139"/>
+      <c r="AC21" s="139"/>
+      <c r="AD21" s="123"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
@@ -4782,54 +4818,54 @@
     </row>
     <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
-      <c r="C25" s="86" t="s">
+      <c r="C25" s="140" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="86"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="86"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="86"/>
-      <c r="J25" s="86"/>
-      <c r="K25" s="86"/>
+      <c r="D25" s="140"/>
+      <c r="E25" s="140"/>
+      <c r="F25" s="140"/>
+      <c r="G25" s="140"/>
+      <c r="H25" s="140"/>
+      <c r="I25" s="140"/>
+      <c r="J25" s="140"/>
+      <c r="K25" s="140"/>
       <c r="L25" s="60"/>
       <c r="M25" s="1"/>
-      <c r="O25" s="87">
+      <c r="O25" s="141">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)-1,1)</f>
         <v>46266</v>
       </c>
-      <c r="P25" s="87"/>
-      <c r="Q25" s="87"/>
-      <c r="R25" s="87"/>
-      <c r="S25" s="87"/>
-      <c r="T25" s="87"/>
-      <c r="U25" s="87"/>
+      <c r="P25" s="141"/>
+      <c r="Q25" s="141"/>
+      <c r="R25" s="141"/>
+      <c r="S25" s="141"/>
+      <c r="T25" s="141"/>
+      <c r="U25" s="141"/>
       <c r="V25" s="61"/>
       <c r="W25" s="61"/>
-      <c r="X25" s="87">
+      <c r="X25" s="141">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)+1,1)</f>
         <v>46327</v>
       </c>
-      <c r="Y25" s="87"/>
-      <c r="Z25" s="87"/>
-      <c r="AA25" s="87"/>
-      <c r="AB25" s="87"/>
-      <c r="AC25" s="87"/>
-      <c r="AD25" s="87"/>
+      <c r="Y25" s="141"/>
+      <c r="Z25" s="141"/>
+      <c r="AA25" s="141"/>
+      <c r="AB25" s="141"/>
+      <c r="AC25" s="141"/>
+      <c r="AD25" s="141"/>
       <c r="AF25" s="1"/>
     </row>
     <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
-      <c r="C26" s="86"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="86"/>
-      <c r="G26" s="86"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="86"/>
-      <c r="J26" s="86"/>
-      <c r="K26" s="86"/>
+      <c r="C26" s="140"/>
+      <c r="D26" s="140"/>
+      <c r="E26" s="140"/>
+      <c r="F26" s="140"/>
+      <c r="G26" s="140"/>
+      <c r="H26" s="140"/>
+      <c r="I26" s="140"/>
+      <c r="J26" s="140"/>
+      <c r="K26" s="140"/>
       <c r="L26" s="60"/>
       <c r="M26" s="1"/>
       <c r="O26" s="62" t="str">
@@ -4894,15 +4930,15 @@
     </row>
     <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
-      <c r="C27" s="88"/>
-      <c r="D27" s="88"/>
-      <c r="E27" s="88"/>
-      <c r="F27" s="88"/>
-      <c r="G27" s="88"/>
-      <c r="H27" s="88"/>
-      <c r="I27" s="88"/>
-      <c r="J27" s="88"/>
-      <c r="K27" s="88"/>
+      <c r="C27" s="116"/>
+      <c r="D27" s="116"/>
+      <c r="E27" s="116"/>
+      <c r="F27" s="116"/>
+      <c r="G27" s="116"/>
+      <c r="H27" s="116"/>
+      <c r="I27" s="116"/>
+      <c r="J27" s="116"/>
+      <c r="K27" s="116"/>
       <c r="M27" s="1"/>
       <c r="O27" s="64" t="str">
         <f t="shared" ref="O27:U32" ca="1" si="0">IF(MONTH($O$25)&lt;&gt;MONTH($O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1)),"",$O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1))</f>
@@ -4966,15 +5002,15 @@
     </row>
     <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
-      <c r="C28" s="89"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="89"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="89"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="89"/>
-      <c r="K28" s="89"/>
+      <c r="C28" s="115"/>
+      <c r="D28" s="115"/>
+      <c r="E28" s="115"/>
+      <c r="F28" s="115"/>
+      <c r="G28" s="115"/>
+      <c r="H28" s="115"/>
+      <c r="I28" s="115"/>
+      <c r="J28" s="115"/>
+      <c r="K28" s="115"/>
       <c r="M28" s="1"/>
       <c r="O28" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -5038,15 +5074,15 @@
     </row>
     <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
-      <c r="C29" s="88"/>
-      <c r="D29" s="88"/>
-      <c r="E29" s="88"/>
-      <c r="F29" s="88"/>
-      <c r="G29" s="88"/>
-      <c r="H29" s="88"/>
-      <c r="I29" s="88"/>
-      <c r="J29" s="88"/>
-      <c r="K29" s="88"/>
+      <c r="C29" s="116"/>
+      <c r="D29" s="116"/>
+      <c r="E29" s="116"/>
+      <c r="F29" s="116"/>
+      <c r="G29" s="116"/>
+      <c r="H29" s="116"/>
+      <c r="I29" s="116"/>
+      <c r="J29" s="116"/>
+      <c r="K29" s="116"/>
       <c r="M29" s="1"/>
       <c r="O29" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -5110,15 +5146,15 @@
     </row>
     <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
-      <c r="C30" s="89"/>
-      <c r="D30" s="89"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="89"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="89"/>
-      <c r="K30" s="89"/>
+      <c r="C30" s="115"/>
+      <c r="D30" s="115"/>
+      <c r="E30" s="115"/>
+      <c r="F30" s="115"/>
+      <c r="G30" s="115"/>
+      <c r="H30" s="115"/>
+      <c r="I30" s="115"/>
+      <c r="J30" s="115"/>
+      <c r="K30" s="115"/>
       <c r="M30" s="1"/>
       <c r="O30" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -5182,15 +5218,15 @@
     </row>
     <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
-      <c r="C31" s="88"/>
-      <c r="D31" s="88"/>
-      <c r="E31" s="88"/>
-      <c r="F31" s="88"/>
-      <c r="G31" s="88"/>
-      <c r="H31" s="88"/>
-      <c r="I31" s="88"/>
-      <c r="J31" s="88"/>
-      <c r="K31" s="88"/>
+      <c r="C31" s="116"/>
+      <c r="D31" s="116"/>
+      <c r="E31" s="116"/>
+      <c r="F31" s="116"/>
+      <c r="G31" s="116"/>
+      <c r="H31" s="116"/>
+      <c r="I31" s="116"/>
+      <c r="J31" s="116"/>
+      <c r="K31" s="116"/>
       <c r="M31" s="1"/>
       <c r="O31" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -5372,154 +5408,67 @@
     </row>
     <row r="38" spans="1:32" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D39" s="115" t="s">
+      <c r="D39" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="E39" s="116"/>
-      <c r="F39" s="117"/>
-      <c r="G39" s="121">
+      <c r="E39" s="85"/>
+      <c r="F39" s="86"/>
+      <c r="G39" s="90">
         <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
-        <v>5</v>
-      </c>
-      <c r="H39" s="122"/>
-      <c r="I39" s="115" t="s">
+        <v>4</v>
+      </c>
+      <c r="H39" s="91"/>
+      <c r="I39" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="J39" s="125"/>
-      <c r="K39" s="127" t="s">
+      <c r="J39" s="98"/>
+      <c r="K39" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="L39" s="128"/>
-      <c r="M39" s="131">
+      <c r="L39" s="95"/>
+      <c r="M39" s="106">
         <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
-        <v>3.9999999999999982</v>
-      </c>
-      <c r="N39" s="132"/>
-      <c r="O39" s="132"/>
-      <c r="P39" s="132"/>
-      <c r="Q39" s="132"/>
-      <c r="R39" s="133"/>
-      <c r="S39" s="137" t="s">
+        <v>5.0000000000000009</v>
+      </c>
+      <c r="N39" s="107"/>
+      <c r="O39" s="107"/>
+      <c r="P39" s="107"/>
+      <c r="Q39" s="107"/>
+      <c r="R39" s="108"/>
+      <c r="S39" s="100" t="s">
         <v>25</v>
       </c>
-      <c r="T39" s="138"/>
-      <c r="U39" s="138"/>
-      <c r="V39" s="138"/>
-      <c r="W39" s="138"/>
-      <c r="X39" s="139"/>
+      <c r="T39" s="101"/>
+      <c r="U39" s="101"/>
+      <c r="V39" s="101"/>
+      <c r="W39" s="101"/>
+      <c r="X39" s="102"/>
     </row>
     <row r="40" spans="1:32" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="118"/>
-      <c r="E40" s="119"/>
-      <c r="F40" s="120"/>
-      <c r="G40" s="123"/>
-      <c r="H40" s="124"/>
-      <c r="I40" s="118"/>
-      <c r="J40" s="126"/>
-      <c r="K40" s="129"/>
-      <c r="L40" s="130"/>
-      <c r="M40" s="134"/>
-      <c r="N40" s="135"/>
-      <c r="O40" s="135"/>
-      <c r="P40" s="135"/>
-      <c r="Q40" s="135"/>
-      <c r="R40" s="136"/>
-      <c r="S40" s="140"/>
-      <c r="T40" s="141"/>
-      <c r="U40" s="141"/>
-      <c r="V40" s="141"/>
-      <c r="W40" s="141"/>
-      <c r="X40" s="142"/>
+      <c r="D40" s="87"/>
+      <c r="E40" s="88"/>
+      <c r="F40" s="89"/>
+      <c r="G40" s="92"/>
+      <c r="H40" s="93"/>
+      <c r="I40" s="87"/>
+      <c r="J40" s="99"/>
+      <c r="K40" s="96"/>
+      <c r="L40" s="97"/>
+      <c r="M40" s="109"/>
+      <c r="N40" s="110"/>
+      <c r="O40" s="110"/>
+      <c r="P40" s="110"/>
+      <c r="Q40" s="110"/>
+      <c r="R40" s="111"/>
+      <c r="S40" s="103"/>
+      <c r="T40" s="104"/>
+      <c r="U40" s="104"/>
+      <c r="V40" s="104"/>
+      <c r="W40" s="104"/>
+      <c r="X40" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="110">
-    <mergeCell ref="D39:F40"/>
-    <mergeCell ref="G39:H40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="K39:L40"/>
-    <mergeCell ref="M39:R40"/>
-    <mergeCell ref="S39:X40"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="O21:V21"/>
-    <mergeCell ref="W21:AD21"/>
-    <mergeCell ref="C30:K31"/>
-    <mergeCell ref="C2:AD2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="W5:AD5"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:V6"/>
-    <mergeCell ref="W6:AD6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="O5:V5"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="W7:AD7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="O8:V8"/>
-    <mergeCell ref="W8:AD8"/>
-    <mergeCell ref="O7:V7"/>
-    <mergeCell ref="W9:AD9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="O11:V11"/>
-    <mergeCell ref="W11:AD11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:V9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="W12:AD12"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="O14:V14"/>
-    <mergeCell ref="W14:AD14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="O12:V12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="W15:AD15"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="O17:V17"/>
-    <mergeCell ref="W17:AD17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="O15:V15"/>
-    <mergeCell ref="K15:N15"/>
     <mergeCell ref="W18:AD18"/>
     <mergeCell ref="C25:K26"/>
     <mergeCell ref="O25:U25"/>
@@ -5543,6 +5492,93 @@
     <mergeCell ref="E21:F21"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="I21:J21"/>
+    <mergeCell ref="W15:AD15"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="O17:V17"/>
+    <mergeCell ref="W17:AD17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="O15:V15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="W12:AD12"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O14:V14"/>
+    <mergeCell ref="W14:AD14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="O12:V12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="W9:AD9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="O11:V11"/>
+    <mergeCell ref="W11:AD11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:V9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="W7:AD7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="O8:V8"/>
+    <mergeCell ref="W8:AD8"/>
+    <mergeCell ref="O7:V7"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:V6"/>
+    <mergeCell ref="W6:AD6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="O5:V5"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="C2:AD2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="W5:AD5"/>
+    <mergeCell ref="D39:F40"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="K39:L40"/>
+    <mergeCell ref="M39:R40"/>
+    <mergeCell ref="S39:X40"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="O21:V21"/>
+    <mergeCell ref="W21:AD21"/>
+    <mergeCell ref="C30:K31"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 E5 G5 I5 K5:L5 O5 W5 C7 E8 G8 I8 K8:L8 O8 W8 C10 E11 G11 I11 K11:L11 O11 W11 C13 E14 G14 I14 K14:L14 O14 W14 C16 E17 G17 I17 K17:L17 O17 W17">
     <cfRule type="expression" dxfId="7" priority="3">
@@ -5633,42 +5669,42 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.9">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A2" s="29"/>
-      <c r="C2" s="113">
+      <c r="C2" s="117">
         <f ca="1">DATE(About!P8,11,1)</f>
         <v>46327</v>
       </c>
-      <c r="D2" s="113"/>
-      <c r="E2" s="113"/>
-      <c r="F2" s="113"/>
-      <c r="G2" s="113"/>
-      <c r="H2" s="113"/>
-      <c r="I2" s="113"/>
-      <c r="J2" s="113"/>
-      <c r="K2" s="113"/>
-      <c r="L2" s="113"/>
-      <c r="M2" s="113"/>
-      <c r="N2" s="113"/>
-      <c r="O2" s="113"/>
-      <c r="P2" s="113"/>
-      <c r="Q2" s="113"/>
-      <c r="R2" s="113"/>
-      <c r="S2" s="113"/>
-      <c r="T2" s="113"/>
-      <c r="U2" s="113"/>
-      <c r="V2" s="113"/>
-      <c r="W2" s="113"/>
-      <c r="X2" s="113"/>
-      <c r="Y2" s="113"/>
-      <c r="Z2" s="113"/>
-      <c r="AA2" s="113"/>
-      <c r="AB2" s="113"/>
-      <c r="AC2" s="113"/>
-      <c r="AD2" s="113"/>
+      <c r="D2" s="117"/>
+      <c r="E2" s="117"/>
+      <c r="F2" s="117"/>
+      <c r="G2" s="117"/>
+      <c r="H2" s="117"/>
+      <c r="I2" s="117"/>
+      <c r="J2" s="117"/>
+      <c r="K2" s="117"/>
+      <c r="L2" s="117"/>
+      <c r="M2" s="117"/>
+      <c r="N2" s="117"/>
+      <c r="O2" s="117"/>
+      <c r="P2" s="117"/>
+      <c r="Q2" s="117"/>
+      <c r="R2" s="117"/>
+      <c r="S2" s="117"/>
+      <c r="T2" s="117"/>
+      <c r="U2" s="117"/>
+      <c r="V2" s="117"/>
+      <c r="W2" s="117"/>
+      <c r="X2" s="117"/>
+      <c r="Y2" s="117"/>
+      <c r="Z2" s="117"/>
+      <c r="AA2" s="117"/>
+      <c r="AB2" s="117"/>
+      <c r="AC2" s="117"/>
+      <c r="AD2" s="117"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.9">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.8">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -5688,114 +5724,114 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="35"/>
-      <c r="C4" s="114">
+      <c r="C4" s="118">
         <f ca="1">C5</f>
         <v>46327</v>
       </c>
-      <c r="D4" s="114"/>
-      <c r="E4" s="114">
+      <c r="D4" s="118"/>
+      <c r="E4" s="118">
         <f ca="1">E5</f>
         <v>46328</v>
       </c>
-      <c r="F4" s="114"/>
-      <c r="G4" s="114">
+      <c r="F4" s="118"/>
+      <c r="G4" s="118">
         <f ca="1">G5</f>
         <v>46329</v>
       </c>
-      <c r="H4" s="114"/>
-      <c r="I4" s="114">
+      <c r="H4" s="118"/>
+      <c r="I4" s="118">
         <f ca="1">I5</f>
         <v>46330</v>
       </c>
-      <c r="J4" s="114"/>
-      <c r="K4" s="114">
+      <c r="J4" s="118"/>
+      <c r="K4" s="118">
         <f ca="1">K5</f>
         <v>46331</v>
       </c>
-      <c r="L4" s="114"/>
-      <c r="M4" s="114"/>
+      <c r="L4" s="118"/>
+      <c r="M4" s="118"/>
       <c r="N4" s="37"/>
-      <c r="O4" s="114">
+      <c r="O4" s="118">
         <f ca="1">O5</f>
         <v>46332</v>
       </c>
-      <c r="P4" s="114"/>
-      <c r="Q4" s="114"/>
-      <c r="R4" s="114"/>
-      <c r="S4" s="114"/>
-      <c r="T4" s="114"/>
-      <c r="U4" s="114"/>
-      <c r="V4" s="114"/>
-      <c r="W4" s="114">
+      <c r="P4" s="118"/>
+      <c r="Q4" s="118"/>
+      <c r="R4" s="118"/>
+      <c r="S4" s="118"/>
+      <c r="T4" s="118"/>
+      <c r="U4" s="118"/>
+      <c r="V4" s="118"/>
+      <c r="W4" s="118">
         <f ca="1">W5</f>
         <v>46333</v>
       </c>
-      <c r="X4" s="114"/>
-      <c r="Y4" s="114"/>
-      <c r="Z4" s="114"/>
-      <c r="AA4" s="114"/>
-      <c r="AB4" s="114"/>
-      <c r="AC4" s="114"/>
-      <c r="AD4" s="114"/>
+      <c r="X4" s="118"/>
+      <c r="Y4" s="118"/>
+      <c r="Z4" s="118"/>
+      <c r="AA4" s="118"/>
+      <c r="AB4" s="118"/>
+      <c r="AC4" s="118"/>
+      <c r="AD4" s="118"/>
       <c r="AF4" s="38"/>
       <c r="AG4" s="39"/>
       <c r="AH4" s="39"/>
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
-      <c r="C5" s="92">
+      <c r="C5" s="119">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46327</v>
       </c>
-      <c r="D5" s="93"/>
-      <c r="E5" s="92">
+      <c r="D5" s="121"/>
+      <c r="E5" s="119">
         <f ca="1">C5+1</f>
         <v>46328</v>
       </c>
-      <c r="F5" s="93"/>
-      <c r="G5" s="92">
+      <c r="F5" s="121"/>
+      <c r="G5" s="119">
         <f ca="1">E5+1</f>
         <v>46329</v>
       </c>
-      <c r="H5" s="93"/>
-      <c r="I5" s="92">
+      <c r="H5" s="121"/>
+      <c r="I5" s="119">
         <f ca="1">G5+1</f>
         <v>46330</v>
       </c>
-      <c r="J5" s="93"/>
-      <c r="K5" s="92">
+      <c r="J5" s="121"/>
+      <c r="K5" s="119">
         <f ca="1">I5+1</f>
         <v>46331</v>
       </c>
-      <c r="L5" s="112"/>
-      <c r="M5" s="112"/>
+      <c r="L5" s="120"/>
+      <c r="M5" s="120"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="92">
+      <c r="O5" s="119">
         <f ca="1">K5+1</f>
         <v>46332</v>
       </c>
-      <c r="P5" s="112"/>
-      <c r="Q5" s="112"/>
-      <c r="R5" s="112"/>
-      <c r="S5" s="112"/>
-      <c r="T5" s="112"/>
-      <c r="U5" s="112"/>
-      <c r="V5" s="93"/>
-      <c r="W5" s="92">
+      <c r="P5" s="120"/>
+      <c r="Q5" s="120"/>
+      <c r="R5" s="120"/>
+      <c r="S5" s="120"/>
+      <c r="T5" s="120"/>
+      <c r="U5" s="120"/>
+      <c r="V5" s="121"/>
+      <c r="W5" s="119">
         <f ca="1">O5+1</f>
         <v>46333</v>
       </c>
-      <c r="X5" s="112"/>
-      <c r="Y5" s="112"/>
-      <c r="Z5" s="112"/>
-      <c r="AA5" s="112"/>
-      <c r="AB5" s="112"/>
-      <c r="AC5" s="112"/>
-      <c r="AD5" s="93"/>
+      <c r="X5" s="120"/>
+      <c r="Y5" s="120"/>
+      <c r="Z5" s="120"/>
+      <c r="AA5" s="120"/>
+      <c r="AB5" s="120"/>
+      <c r="AC5" s="120"/>
+      <c r="AD5" s="121"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
@@ -5804,180 +5840,180 @@
     </row>
     <row r="6" spans="1:36" s="43" customFormat="1" ht="133.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="42"/>
-      <c r="C6" s="83"/>
-      <c r="D6" s="85"/>
-      <c r="E6" s="91" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="85"/>
-      <c r="G6" s="83"/>
-      <c r="H6" s="85"/>
-      <c r="I6" s="90" t="s">
+      <c r="C6" s="147"/>
+      <c r="D6" s="149"/>
+      <c r="E6" s="155" t="s">
+        <v>35</v>
+      </c>
+      <c r="F6" s="149"/>
+      <c r="G6" s="147"/>
+      <c r="H6" s="149"/>
+      <c r="I6" s="156" t="s">
+        <v>53</v>
+      </c>
+      <c r="J6" s="149"/>
+      <c r="K6" s="156" t="s">
         <v>54</v>
       </c>
-      <c r="J6" s="85"/>
-      <c r="K6" s="90" t="s">
-        <v>55</v>
-      </c>
-      <c r="L6" s="84"/>
-      <c r="M6" s="84"/>
-      <c r="N6" s="85"/>
-      <c r="O6" s="91" t="s">
-        <v>57</v>
-      </c>
-      <c r="P6" s="84"/>
-      <c r="Q6" s="84"/>
-      <c r="R6" s="84"/>
-      <c r="S6" s="84"/>
-      <c r="T6" s="84"/>
-      <c r="U6" s="84"/>
-      <c r="V6" s="85"/>
-      <c r="W6" s="83"/>
-      <c r="X6" s="84"/>
-      <c r="Y6" s="84"/>
-      <c r="Z6" s="84"/>
-      <c r="AA6" s="84"/>
-      <c r="AB6" s="84"/>
-      <c r="AC6" s="84"/>
-      <c r="AD6" s="85"/>
+      <c r="L6" s="148"/>
+      <c r="M6" s="148"/>
+      <c r="N6" s="149"/>
+      <c r="O6" s="155" t="s">
+        <v>56</v>
+      </c>
+      <c r="P6" s="148"/>
+      <c r="Q6" s="148"/>
+      <c r="R6" s="148"/>
+      <c r="S6" s="148"/>
+      <c r="T6" s="148"/>
+      <c r="U6" s="148"/>
+      <c r="V6" s="149"/>
+      <c r="W6" s="147"/>
+      <c r="X6" s="148"/>
+      <c r="Y6" s="148"/>
+      <c r="Z6" s="148"/>
+      <c r="AA6" s="148"/>
+      <c r="AB6" s="148"/>
+      <c r="AC6" s="148"/>
+      <c r="AD6" s="149"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
     <row r="7" spans="1:36" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="C7" s="155">
+      <c r="C7" s="157">
         <f ca="1">W5+1</f>
         <v>46334</v>
       </c>
-      <c r="D7" s="156"/>
-      <c r="E7" s="160"/>
-      <c r="F7" s="161"/>
-      <c r="G7" s="160"/>
-      <c r="H7" s="161"/>
-      <c r="I7" s="160"/>
-      <c r="J7" s="161"/>
-      <c r="K7" s="160"/>
-      <c r="L7" s="162"/>
-      <c r="M7" s="162"/>
+      <c r="D7" s="158"/>
+      <c r="E7" s="159"/>
+      <c r="F7" s="160"/>
+      <c r="G7" s="159"/>
+      <c r="H7" s="160"/>
+      <c r="I7" s="159"/>
+      <c r="J7" s="160"/>
+      <c r="K7" s="159"/>
+      <c r="L7" s="161"/>
+      <c r="M7" s="161"/>
       <c r="N7" s="80"/>
-      <c r="O7" s="160"/>
-      <c r="P7" s="162"/>
-      <c r="Q7" s="162"/>
-      <c r="R7" s="162"/>
-      <c r="S7" s="162"/>
-      <c r="T7" s="162"/>
-      <c r="U7" s="162"/>
-      <c r="V7" s="161"/>
-      <c r="W7" s="160"/>
-      <c r="X7" s="162"/>
-      <c r="Y7" s="162"/>
-      <c r="Z7" s="162"/>
-      <c r="AA7" s="162"/>
-      <c r="AB7" s="162"/>
-      <c r="AC7" s="162"/>
-      <c r="AD7" s="161"/>
+      <c r="O7" s="159"/>
+      <c r="P7" s="161"/>
+      <c r="Q7" s="161"/>
+      <c r="R7" s="161"/>
+      <c r="S7" s="161"/>
+      <c r="T7" s="161"/>
+      <c r="U7" s="161"/>
+      <c r="V7" s="160"/>
+      <c r="W7" s="159"/>
+      <c r="X7" s="161"/>
+      <c r="Y7" s="161"/>
+      <c r="Z7" s="161"/>
+      <c r="AA7" s="161"/>
+      <c r="AB7" s="161"/>
+      <c r="AC7" s="161"/>
+      <c r="AD7" s="160"/>
       <c r="AF7" s="1"/>
     </row>
     <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
-      <c r="C8" s="155"/>
-      <c r="D8" s="156"/>
-      <c r="E8" s="155">
+      <c r="C8" s="157"/>
+      <c r="D8" s="158"/>
+      <c r="E8" s="157">
         <f ca="1">C7+1</f>
         <v>46335</v>
       </c>
-      <c r="F8" s="156"/>
-      <c r="G8" s="155">
+      <c r="F8" s="158"/>
+      <c r="G8" s="157">
         <f ca="1">E8+1</f>
         <v>46336</v>
       </c>
-      <c r="H8" s="156"/>
-      <c r="I8" s="155">
+      <c r="H8" s="158"/>
+      <c r="I8" s="157">
         <f ca="1">G8+1</f>
         <v>46337</v>
       </c>
-      <c r="J8" s="156"/>
-      <c r="K8" s="155">
+      <c r="J8" s="158"/>
+      <c r="K8" s="157">
         <f ca="1">I8+1</f>
         <v>46338</v>
       </c>
-      <c r="L8" s="157"/>
-      <c r="M8" s="157"/>
+      <c r="L8" s="162"/>
+      <c r="M8" s="162"/>
       <c r="N8" s="78"/>
-      <c r="O8" s="155">
+      <c r="O8" s="157">
         <f ca="1">K8+1</f>
         <v>46339</v>
       </c>
-      <c r="P8" s="157"/>
-      <c r="Q8" s="157"/>
-      <c r="R8" s="157"/>
-      <c r="S8" s="157"/>
-      <c r="T8" s="157"/>
-      <c r="U8" s="157"/>
-      <c r="V8" s="156"/>
-      <c r="W8" s="155">
+      <c r="P8" s="162"/>
+      <c r="Q8" s="162"/>
+      <c r="R8" s="162"/>
+      <c r="S8" s="162"/>
+      <c r="T8" s="162"/>
+      <c r="U8" s="162"/>
+      <c r="V8" s="158"/>
+      <c r="W8" s="157">
         <f ca="1">O8+1</f>
         <v>46340</v>
       </c>
-      <c r="X8" s="157"/>
-      <c r="Y8" s="157"/>
-      <c r="Z8" s="157"/>
-      <c r="AA8" s="157"/>
-      <c r="AB8" s="157"/>
-      <c r="AC8" s="157"/>
-      <c r="AD8" s="156"/>
+      <c r="X8" s="162"/>
+      <c r="Y8" s="162"/>
+      <c r="Z8" s="162"/>
+      <c r="AA8" s="162"/>
+      <c r="AB8" s="162"/>
+      <c r="AC8" s="162"/>
+      <c r="AD8" s="158"/>
       <c r="AF8" s="4"/>
     </row>
     <row r="9" spans="1:36" s="43" customFormat="1" ht="146.44999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="42"/>
-      <c r="C9" s="83"/>
-      <c r="D9" s="85"/>
-      <c r="E9" s="91" t="s">
+      <c r="C9" s="147"/>
+      <c r="D9" s="149"/>
+      <c r="E9" s="155" t="s">
+        <v>42</v>
+      </c>
+      <c r="F9" s="149"/>
+      <c r="G9" s="156" t="s">
+        <v>55</v>
+      </c>
+      <c r="H9" s="149"/>
+      <c r="I9" s="147" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="85"/>
-      <c r="G9" s="90" t="s">
-        <v>56</v>
-      </c>
-      <c r="H9" s="85"/>
-      <c r="I9" s="83" t="s">
-        <v>44</v>
-      </c>
-      <c r="J9" s="85"/>
-      <c r="K9" s="83" t="s">
-        <v>49</v>
-      </c>
-      <c r="L9" s="84"/>
-      <c r="M9" s="84"/>
-      <c r="N9" s="85"/>
-      <c r="O9" s="158" t="s">
+      <c r="J9" s="149"/>
+      <c r="K9" s="147" t="s">
+        <v>48</v>
+      </c>
+      <c r="L9" s="148"/>
+      <c r="M9" s="148"/>
+      <c r="N9" s="149"/>
+      <c r="O9" s="164" t="s">
         <v>15</v>
       </c>
-      <c r="P9" s="154"/>
-      <c r="Q9" s="154"/>
-      <c r="R9" s="154"/>
-      <c r="S9" s="154"/>
-      <c r="T9" s="154"/>
-      <c r="U9" s="154"/>
-      <c r="V9" s="105"/>
-      <c r="W9" s="104"/>
-      <c r="X9" s="154"/>
-      <c r="Y9" s="154"/>
-      <c r="Z9" s="154"/>
-      <c r="AA9" s="154"/>
-      <c r="AB9" s="154"/>
-      <c r="AC9" s="154"/>
-      <c r="AD9" s="105"/>
+      <c r="P9" s="163"/>
+      <c r="Q9" s="163"/>
+      <c r="R9" s="163"/>
+      <c r="S9" s="163"/>
+      <c r="T9" s="163"/>
+      <c r="U9" s="163"/>
+      <c r="V9" s="145"/>
+      <c r="W9" s="144"/>
+      <c r="X9" s="163"/>
+      <c r="Y9" s="163"/>
+      <c r="Z9" s="163"/>
+      <c r="AA9" s="163"/>
+      <c r="AB9" s="163"/>
+      <c r="AC9" s="163"/>
+      <c r="AD9" s="145"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
     <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="42"/>
-      <c r="C10" s="155">
+      <c r="C10" s="157">
         <f ca="1">W8+1</f>
         <v>46341</v>
       </c>
-      <c r="D10" s="156"/>
+      <c r="D10" s="158"/>
       <c r="E10" s="79"/>
       <c r="F10" s="80"/>
       <c r="G10" s="79"/>
@@ -6009,97 +6045,97 @@
     </row>
     <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
-      <c r="C11" s="155"/>
-      <c r="D11" s="156"/>
-      <c r="E11" s="155">
+      <c r="C11" s="157"/>
+      <c r="D11" s="158"/>
+      <c r="E11" s="157">
         <f ca="1">C10+1</f>
         <v>46342</v>
       </c>
-      <c r="F11" s="156"/>
-      <c r="G11" s="155">
+      <c r="F11" s="158"/>
+      <c r="G11" s="157">
         <f ca="1">E11+1</f>
         <v>46343</v>
       </c>
-      <c r="H11" s="156"/>
-      <c r="I11" s="155">
+      <c r="H11" s="158"/>
+      <c r="I11" s="157">
         <f ca="1">G11+1</f>
         <v>46344</v>
       </c>
-      <c r="J11" s="156"/>
-      <c r="K11" s="155">
+      <c r="J11" s="158"/>
+      <c r="K11" s="157">
         <f ca="1">I11+1</f>
         <v>46345</v>
       </c>
-      <c r="L11" s="157"/>
-      <c r="M11" s="157"/>
+      <c r="L11" s="162"/>
+      <c r="M11" s="162"/>
       <c r="N11" s="78"/>
-      <c r="O11" s="155">
+      <c r="O11" s="157">
         <f ca="1">K11+1</f>
         <v>46346</v>
       </c>
-      <c r="P11" s="157"/>
-      <c r="Q11" s="157"/>
-      <c r="R11" s="157"/>
-      <c r="S11" s="157"/>
-      <c r="T11" s="157"/>
-      <c r="U11" s="157"/>
-      <c r="V11" s="156"/>
-      <c r="W11" s="155">
+      <c r="P11" s="162"/>
+      <c r="Q11" s="162"/>
+      <c r="R11" s="162"/>
+      <c r="S11" s="162"/>
+      <c r="T11" s="162"/>
+      <c r="U11" s="162"/>
+      <c r="V11" s="158"/>
+      <c r="W11" s="157">
         <f ca="1">O11+1</f>
         <v>46347</v>
       </c>
-      <c r="X11" s="157"/>
-      <c r="Y11" s="157"/>
-      <c r="Z11" s="157"/>
-      <c r="AA11" s="157"/>
-      <c r="AB11" s="157"/>
-      <c r="AC11" s="157"/>
-      <c r="AD11" s="156"/>
+      <c r="X11" s="162"/>
+      <c r="Y11" s="162"/>
+      <c r="Z11" s="162"/>
+      <c r="AA11" s="162"/>
+      <c r="AB11" s="162"/>
+      <c r="AC11" s="162"/>
+      <c r="AD11" s="158"/>
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
     <row r="12" spans="1:36" s="43" customFormat="1" ht="134.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="42"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="105"/>
-      <c r="E12" s="158" t="s">
+      <c r="C12" s="144"/>
+      <c r="D12" s="145"/>
+      <c r="E12" s="164" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="159"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="105"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="105"/>
-      <c r="K12" s="104"/>
-      <c r="L12" s="154"/>
-      <c r="M12" s="154"/>
-      <c r="N12" s="105"/>
-      <c r="O12" s="104"/>
-      <c r="P12" s="154"/>
-      <c r="Q12" s="154"/>
-      <c r="R12" s="154"/>
-      <c r="S12" s="154"/>
-      <c r="T12" s="154"/>
-      <c r="U12" s="154"/>
-      <c r="V12" s="105"/>
-      <c r="W12" s="104"/>
-      <c r="X12" s="154"/>
-      <c r="Y12" s="154"/>
-      <c r="Z12" s="154"/>
-      <c r="AA12" s="154"/>
-      <c r="AB12" s="154"/>
-      <c r="AC12" s="154"/>
-      <c r="AD12" s="105"/>
+      <c r="F12" s="165"/>
+      <c r="G12" s="144"/>
+      <c r="H12" s="145"/>
+      <c r="I12" s="144"/>
+      <c r="J12" s="145"/>
+      <c r="K12" s="144"/>
+      <c r="L12" s="163"/>
+      <c r="M12" s="163"/>
+      <c r="N12" s="145"/>
+      <c r="O12" s="144"/>
+      <c r="P12" s="163"/>
+      <c r="Q12" s="163"/>
+      <c r="R12" s="163"/>
+      <c r="S12" s="163"/>
+      <c r="T12" s="163"/>
+      <c r="U12" s="163"/>
+      <c r="V12" s="145"/>
+      <c r="W12" s="144"/>
+      <c r="X12" s="163"/>
+      <c r="Y12" s="163"/>
+      <c r="Z12" s="163"/>
+      <c r="AA12" s="163"/>
+      <c r="AB12" s="163"/>
+      <c r="AC12" s="163"/>
+      <c r="AD12" s="145"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
     <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="42"/>
-      <c r="C13" s="155">
+      <c r="C13" s="157">
         <f ca="1">W11+1</f>
         <v>46348</v>
       </c>
-      <c r="D13" s="156"/>
+      <c r="D13" s="158"/>
       <c r="E13" s="79"/>
       <c r="F13" s="80"/>
       <c r="G13" s="79"/>
@@ -6131,100 +6167,100 @@
     </row>
     <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4"/>
-      <c r="C14" s="155"/>
-      <c r="D14" s="156"/>
-      <c r="E14" s="155">
+      <c r="C14" s="157"/>
+      <c r="D14" s="158"/>
+      <c r="E14" s="157">
         <f ca="1">C13+1</f>
         <v>46349</v>
       </c>
-      <c r="F14" s="156"/>
-      <c r="G14" s="155">
+      <c r="F14" s="158"/>
+      <c r="G14" s="157">
         <f ca="1">E14+1</f>
         <v>46350</v>
       </c>
-      <c r="H14" s="156"/>
-      <c r="I14" s="155">
+      <c r="H14" s="158"/>
+      <c r="I14" s="157">
         <f ca="1">G14+1</f>
         <v>46351</v>
       </c>
-      <c r="J14" s="156"/>
-      <c r="K14" s="155">
+      <c r="J14" s="158"/>
+      <c r="K14" s="157">
         <f ca="1">I14+1</f>
         <v>46352</v>
       </c>
-      <c r="L14" s="157"/>
-      <c r="M14" s="157"/>
+      <c r="L14" s="162"/>
+      <c r="M14" s="162"/>
       <c r="N14" s="78"/>
-      <c r="O14" s="155">
+      <c r="O14" s="157">
         <f ca="1">K14+1</f>
         <v>46353</v>
       </c>
-      <c r="P14" s="157"/>
-      <c r="Q14" s="157"/>
-      <c r="R14" s="157"/>
-      <c r="S14" s="157"/>
-      <c r="T14" s="157"/>
-      <c r="U14" s="157"/>
-      <c r="V14" s="156"/>
-      <c r="W14" s="155">
+      <c r="P14" s="162"/>
+      <c r="Q14" s="162"/>
+      <c r="R14" s="162"/>
+      <c r="S14" s="162"/>
+      <c r="T14" s="162"/>
+      <c r="U14" s="162"/>
+      <c r="V14" s="158"/>
+      <c r="W14" s="157">
         <f ca="1">O14+1</f>
         <v>46354</v>
       </c>
-      <c r="X14" s="157"/>
-      <c r="Y14" s="157"/>
-      <c r="Z14" s="157"/>
-      <c r="AA14" s="157"/>
-      <c r="AB14" s="157"/>
-      <c r="AC14" s="157"/>
-      <c r="AD14" s="156"/>
+      <c r="X14" s="162"/>
+      <c r="Y14" s="162"/>
+      <c r="Z14" s="162"/>
+      <c r="AA14" s="162"/>
+      <c r="AB14" s="162"/>
+      <c r="AC14" s="162"/>
+      <c r="AD14" s="158"/>
       <c r="AF14" s="4"/>
     </row>
     <row r="15" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="42"/>
-      <c r="C15" s="104"/>
-      <c r="D15" s="105"/>
-      <c r="E15" s="104"/>
-      <c r="F15" s="105"/>
-      <c r="G15" s="104"/>
-      <c r="H15" s="105"/>
-      <c r="I15" s="104"/>
-      <c r="J15" s="105"/>
-      <c r="K15" s="104"/>
-      <c r="L15" s="154"/>
-      <c r="M15" s="154"/>
-      <c r="N15" s="105"/>
-      <c r="O15" s="104"/>
-      <c r="P15" s="154"/>
-      <c r="Q15" s="154"/>
-      <c r="R15" s="154"/>
-      <c r="S15" s="154"/>
-      <c r="T15" s="154"/>
-      <c r="U15" s="154"/>
-      <c r="V15" s="105"/>
-      <c r="W15" s="104"/>
-      <c r="X15" s="154"/>
-      <c r="Y15" s="154"/>
-      <c r="Z15" s="154"/>
-      <c r="AA15" s="154"/>
-      <c r="AB15" s="154"/>
-      <c r="AC15" s="154"/>
-      <c r="AD15" s="105"/>
+      <c r="C15" s="144"/>
+      <c r="D15" s="145"/>
+      <c r="E15" s="144"/>
+      <c r="F15" s="145"/>
+      <c r="G15" s="144"/>
+      <c r="H15" s="145"/>
+      <c r="I15" s="144"/>
+      <c r="J15" s="145"/>
+      <c r="K15" s="144"/>
+      <c r="L15" s="163"/>
+      <c r="M15" s="163"/>
+      <c r="N15" s="145"/>
+      <c r="O15" s="144"/>
+      <c r="P15" s="163"/>
+      <c r="Q15" s="163"/>
+      <c r="R15" s="163"/>
+      <c r="S15" s="163"/>
+      <c r="T15" s="163"/>
+      <c r="U15" s="163"/>
+      <c r="V15" s="145"/>
+      <c r="W15" s="144"/>
+      <c r="X15" s="163"/>
+      <c r="Y15" s="163"/>
+      <c r="Z15" s="163"/>
+      <c r="AA15" s="163"/>
+      <c r="AB15" s="163"/>
+      <c r="AC15" s="163"/>
+      <c r="AD15" s="145"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
     <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="42"/>
-      <c r="C16" s="92">
+      <c r="C16" s="119">
         <f ca="1">W14+1</f>
         <v>46355</v>
       </c>
-      <c r="D16" s="93"/>
+      <c r="D16" s="121"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
       <c r="H16" s="75"/>
-      <c r="I16" s="145"/>
-      <c r="J16" s="146"/>
+      <c r="I16" s="136"/>
+      <c r="J16" s="137"/>
       <c r="K16" s="66"/>
       <c r="L16" s="68"/>
       <c r="M16" s="68"/>
@@ -6250,101 +6286,101 @@
     </row>
     <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
-      <c r="C17" s="92"/>
-      <c r="D17" s="93"/>
-      <c r="E17" s="94">
+      <c r="C17" s="119"/>
+      <c r="D17" s="121"/>
+      <c r="E17" s="112">
         <f ca="1">C16+1</f>
         <v>46356</v>
       </c>
-      <c r="F17" s="95"/>
-      <c r="G17" s="94">
+      <c r="F17" s="113"/>
+      <c r="G17" s="112">
         <f ca="1">E17+1</f>
         <v>46357</v>
       </c>
-      <c r="H17" s="95"/>
-      <c r="I17" s="94">
+      <c r="H17" s="113"/>
+      <c r="I17" s="112">
         <f ca="1">G17+1</f>
         <v>46358</v>
       </c>
-      <c r="J17" s="95"/>
-      <c r="K17" s="94">
+      <c r="J17" s="113"/>
+      <c r="K17" s="112">
         <f ca="1">I17+1</f>
         <v>46359</v>
       </c>
-      <c r="L17" s="96"/>
-      <c r="M17" s="96"/>
-      <c r="N17" s="95"/>
-      <c r="O17" s="94">
+      <c r="L17" s="114"/>
+      <c r="M17" s="114"/>
+      <c r="N17" s="113"/>
+      <c r="O17" s="112">
         <f ca="1">K17+1</f>
         <v>46360</v>
       </c>
-      <c r="P17" s="96"/>
-      <c r="Q17" s="96"/>
-      <c r="R17" s="96"/>
-      <c r="S17" s="96"/>
-      <c r="T17" s="96"/>
-      <c r="U17" s="96"/>
-      <c r="V17" s="95"/>
-      <c r="W17" s="94">
+      <c r="P17" s="114"/>
+      <c r="Q17" s="114"/>
+      <c r="R17" s="114"/>
+      <c r="S17" s="114"/>
+      <c r="T17" s="114"/>
+      <c r="U17" s="114"/>
+      <c r="V17" s="113"/>
+      <c r="W17" s="112">
         <f ca="1">O17+1</f>
         <v>46361</v>
       </c>
-      <c r="X17" s="96"/>
-      <c r="Y17" s="96"/>
-      <c r="Z17" s="96"/>
-      <c r="AA17" s="96"/>
-      <c r="AB17" s="96"/>
-      <c r="AC17" s="96"/>
-      <c r="AD17" s="95"/>
+      <c r="X17" s="114"/>
+      <c r="Y17" s="114"/>
+      <c r="Z17" s="114"/>
+      <c r="AA17" s="114"/>
+      <c r="AB17" s="114"/>
+      <c r="AC17" s="114"/>
+      <c r="AD17" s="113"/>
       <c r="AF17" s="4"/>
     </row>
     <row r="18" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="42"/>
-      <c r="C18" s="97"/>
-      <c r="D18" s="98"/>
-      <c r="E18" s="97"/>
-      <c r="F18" s="98"/>
-      <c r="G18" s="97"/>
-      <c r="H18" s="98"/>
-      <c r="I18" s="97"/>
-      <c r="J18" s="98"/>
-      <c r="K18" s="97"/>
-      <c r="L18" s="143"/>
-      <c r="M18" s="143"/>
-      <c r="N18" s="98"/>
-      <c r="O18" s="97"/>
-      <c r="P18" s="143"/>
-      <c r="Q18" s="143"/>
-      <c r="R18" s="143"/>
-      <c r="S18" s="143"/>
-      <c r="T18" s="143"/>
-      <c r="U18" s="143"/>
-      <c r="V18" s="98"/>
-      <c r="W18" s="97"/>
-      <c r="X18" s="143"/>
-      <c r="Y18" s="143"/>
-      <c r="Z18" s="143"/>
-      <c r="AA18" s="143"/>
-      <c r="AB18" s="143"/>
-      <c r="AC18" s="143"/>
-      <c r="AD18" s="98"/>
+      <c r="C18" s="122"/>
+      <c r="D18" s="123"/>
+      <c r="E18" s="122"/>
+      <c r="F18" s="123"/>
+      <c r="G18" s="122"/>
+      <c r="H18" s="123"/>
+      <c r="I18" s="122"/>
+      <c r="J18" s="123"/>
+      <c r="K18" s="122"/>
+      <c r="L18" s="139"/>
+      <c r="M18" s="139"/>
+      <c r="N18" s="123"/>
+      <c r="O18" s="122"/>
+      <c r="P18" s="139"/>
+      <c r="Q18" s="139"/>
+      <c r="R18" s="139"/>
+      <c r="S18" s="139"/>
+      <c r="T18" s="139"/>
+      <c r="U18" s="139"/>
+      <c r="V18" s="123"/>
+      <c r="W18" s="122"/>
+      <c r="X18" s="139"/>
+      <c r="Y18" s="139"/>
+      <c r="Z18" s="139"/>
+      <c r="AA18" s="139"/>
+      <c r="AB18" s="139"/>
+      <c r="AC18" s="139"/>
+      <c r="AD18" s="123"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
     <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="42"/>
-      <c r="C19" s="92">
+      <c r="C19" s="119">
         <f ca="1">W17+1</f>
         <v>46362</v>
       </c>
-      <c r="D19" s="93"/>
+      <c r="D19" s="121"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
       <c r="H19" s="75"/>
-      <c r="I19" s="145"/>
-      <c r="J19" s="146"/>
+      <c r="I19" s="136"/>
+      <c r="J19" s="137"/>
       <c r="K19" s="66"/>
       <c r="L19" s="68"/>
       <c r="M19" s="68"/>
@@ -6370,84 +6406,84 @@
     </row>
     <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
-      <c r="C20" s="92"/>
-      <c r="D20" s="93"/>
-      <c r="E20" s="94">
+      <c r="C20" s="119"/>
+      <c r="D20" s="121"/>
+      <c r="E20" s="112">
         <f ca="1">C19+1</f>
         <v>46363</v>
       </c>
-      <c r="F20" s="95"/>
-      <c r="G20" s="94">
+      <c r="F20" s="113"/>
+      <c r="G20" s="112">
         <f ca="1">E20+1</f>
         <v>46364</v>
       </c>
-      <c r="H20" s="95"/>
-      <c r="I20" s="94">
+      <c r="H20" s="113"/>
+      <c r="I20" s="112">
         <f ca="1">G20+1</f>
         <v>46365</v>
       </c>
-      <c r="J20" s="95"/>
-      <c r="K20" s="94">
+      <c r="J20" s="113"/>
+      <c r="K20" s="112">
         <f ca="1">I20+1</f>
         <v>46366</v>
       </c>
-      <c r="L20" s="96"/>
-      <c r="M20" s="96"/>
-      <c r="N20" s="95"/>
-      <c r="O20" s="94">
+      <c r="L20" s="114"/>
+      <c r="M20" s="114"/>
+      <c r="N20" s="113"/>
+      <c r="O20" s="112">
         <f ca="1">K20+1</f>
         <v>46367</v>
       </c>
-      <c r="P20" s="96"/>
-      <c r="Q20" s="96"/>
-      <c r="R20" s="96"/>
-      <c r="S20" s="96"/>
-      <c r="T20" s="96"/>
-      <c r="U20" s="96"/>
-      <c r="V20" s="95"/>
-      <c r="W20" s="94">
+      <c r="P20" s="114"/>
+      <c r="Q20" s="114"/>
+      <c r="R20" s="114"/>
+      <c r="S20" s="114"/>
+      <c r="T20" s="114"/>
+      <c r="U20" s="114"/>
+      <c r="V20" s="113"/>
+      <c r="W20" s="112">
         <f ca="1">O20+1</f>
         <v>46368</v>
       </c>
-      <c r="X20" s="96"/>
-      <c r="Y20" s="96"/>
-      <c r="Z20" s="96"/>
-      <c r="AA20" s="96"/>
-      <c r="AB20" s="96"/>
-      <c r="AC20" s="96"/>
-      <c r="AD20" s="95"/>
+      <c r="X20" s="114"/>
+      <c r="Y20" s="114"/>
+      <c r="Z20" s="114"/>
+      <c r="AA20" s="114"/>
+      <c r="AB20" s="114"/>
+      <c r="AC20" s="114"/>
+      <c r="AD20" s="113"/>
       <c r="AF20" s="4"/>
     </row>
     <row r="21" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="42"/>
-      <c r="C21" s="97"/>
-      <c r="D21" s="98"/>
-      <c r="E21" s="97"/>
-      <c r="F21" s="98"/>
-      <c r="G21" s="97"/>
-      <c r="H21" s="98"/>
-      <c r="I21" s="97"/>
-      <c r="J21" s="98"/>
-      <c r="K21" s="97"/>
-      <c r="L21" s="143"/>
-      <c r="M21" s="143"/>
-      <c r="N21" s="98"/>
-      <c r="O21" s="97"/>
-      <c r="P21" s="143"/>
-      <c r="Q21" s="143"/>
-      <c r="R21" s="143"/>
-      <c r="S21" s="143"/>
-      <c r="T21" s="143"/>
-      <c r="U21" s="143"/>
-      <c r="V21" s="98"/>
-      <c r="W21" s="97"/>
-      <c r="X21" s="143"/>
-      <c r="Y21" s="143"/>
-      <c r="Z21" s="143"/>
-      <c r="AA21" s="143"/>
-      <c r="AB21" s="143"/>
-      <c r="AC21" s="143"/>
-      <c r="AD21" s="98"/>
+      <c r="C21" s="122"/>
+      <c r="D21" s="123"/>
+      <c r="E21" s="122"/>
+      <c r="F21" s="123"/>
+      <c r="G21" s="122"/>
+      <c r="H21" s="123"/>
+      <c r="I21" s="122"/>
+      <c r="J21" s="123"/>
+      <c r="K21" s="122"/>
+      <c r="L21" s="139"/>
+      <c r="M21" s="139"/>
+      <c r="N21" s="123"/>
+      <c r="O21" s="122"/>
+      <c r="P21" s="139"/>
+      <c r="Q21" s="139"/>
+      <c r="R21" s="139"/>
+      <c r="S21" s="139"/>
+      <c r="T21" s="139"/>
+      <c r="U21" s="139"/>
+      <c r="V21" s="123"/>
+      <c r="W21" s="122"/>
+      <c r="X21" s="139"/>
+      <c r="Y21" s="139"/>
+      <c r="Z21" s="139"/>
+      <c r="AA21" s="139"/>
+      <c r="AB21" s="139"/>
+      <c r="AC21" s="139"/>
+      <c r="AD21" s="123"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
@@ -6525,54 +6561,54 @@
     </row>
     <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
-      <c r="C25" s="86" t="s">
+      <c r="C25" s="140" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="86"/>
-      <c r="E25" s="86"/>
-      <c r="F25" s="86"/>
-      <c r="G25" s="86"/>
-      <c r="H25" s="86"/>
-      <c r="I25" s="86"/>
-      <c r="J25" s="86"/>
-      <c r="K25" s="86"/>
+      <c r="D25" s="140"/>
+      <c r="E25" s="140"/>
+      <c r="F25" s="140"/>
+      <c r="G25" s="140"/>
+      <c r="H25" s="140"/>
+      <c r="I25" s="140"/>
+      <c r="J25" s="140"/>
+      <c r="K25" s="140"/>
       <c r="L25" s="60"/>
       <c r="M25" s="1"/>
-      <c r="O25" s="87">
+      <c r="O25" s="141">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)-1,1)</f>
         <v>46296</v>
       </c>
-      <c r="P25" s="87"/>
-      <c r="Q25" s="87"/>
-      <c r="R25" s="87"/>
-      <c r="S25" s="87"/>
-      <c r="T25" s="87"/>
-      <c r="U25" s="87"/>
+      <c r="P25" s="141"/>
+      <c r="Q25" s="141"/>
+      <c r="R25" s="141"/>
+      <c r="S25" s="141"/>
+      <c r="T25" s="141"/>
+      <c r="U25" s="141"/>
       <c r="V25" s="61"/>
       <c r="W25" s="61"/>
-      <c r="X25" s="87">
+      <c r="X25" s="141">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)+1,1)</f>
         <v>46357</v>
       </c>
-      <c r="Y25" s="87"/>
-      <c r="Z25" s="87"/>
-      <c r="AA25" s="87"/>
-      <c r="AB25" s="87"/>
-      <c r="AC25" s="87"/>
-      <c r="AD25" s="87"/>
+      <c r="Y25" s="141"/>
+      <c r="Z25" s="141"/>
+      <c r="AA25" s="141"/>
+      <c r="AB25" s="141"/>
+      <c r="AC25" s="141"/>
+      <c r="AD25" s="141"/>
       <c r="AF25" s="1"/>
     </row>
     <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
-      <c r="C26" s="86"/>
-      <c r="D26" s="86"/>
-      <c r="E26" s="86"/>
-      <c r="F26" s="86"/>
-      <c r="G26" s="86"/>
-      <c r="H26" s="86"/>
-      <c r="I26" s="86"/>
-      <c r="J26" s="86"/>
-      <c r="K26" s="86"/>
+      <c r="C26" s="140"/>
+      <c r="D26" s="140"/>
+      <c r="E26" s="140"/>
+      <c r="F26" s="140"/>
+      <c r="G26" s="140"/>
+      <c r="H26" s="140"/>
+      <c r="I26" s="140"/>
+      <c r="J26" s="140"/>
+      <c r="K26" s="140"/>
       <c r="L26" s="60"/>
       <c r="M26" s="1"/>
       <c r="O26" s="62" t="str">
@@ -6637,15 +6673,15 @@
     </row>
     <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
-      <c r="C27" s="88"/>
-      <c r="D27" s="88"/>
-      <c r="E27" s="88"/>
-      <c r="F27" s="88"/>
-      <c r="G27" s="88"/>
-      <c r="H27" s="88"/>
-      <c r="I27" s="88"/>
-      <c r="J27" s="88"/>
-      <c r="K27" s="88"/>
+      <c r="C27" s="116"/>
+      <c r="D27" s="116"/>
+      <c r="E27" s="116"/>
+      <c r="F27" s="116"/>
+      <c r="G27" s="116"/>
+      <c r="H27" s="116"/>
+      <c r="I27" s="116"/>
+      <c r="J27" s="116"/>
+      <c r="K27" s="116"/>
       <c r="M27" s="1"/>
       <c r="O27" s="64" t="str">
         <f t="shared" ref="O27:U32" ca="1" si="0">IF(MONTH($O$25)&lt;&gt;MONTH($O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1)),"",$O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1))</f>
@@ -6709,15 +6745,15 @@
     </row>
     <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
-      <c r="C28" s="89"/>
-      <c r="D28" s="89"/>
-      <c r="E28" s="89"/>
-      <c r="F28" s="89"/>
-      <c r="G28" s="89"/>
-      <c r="H28" s="89"/>
-      <c r="I28" s="89"/>
-      <c r="J28" s="89"/>
-      <c r="K28" s="89"/>
+      <c r="C28" s="115"/>
+      <c r="D28" s="115"/>
+      <c r="E28" s="115"/>
+      <c r="F28" s="115"/>
+      <c r="G28" s="115"/>
+      <c r="H28" s="115"/>
+      <c r="I28" s="115"/>
+      <c r="J28" s="115"/>
+      <c r="K28" s="115"/>
       <c r="M28" s="1"/>
       <c r="O28" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6781,15 +6817,15 @@
     </row>
     <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
-      <c r="C29" s="88"/>
-      <c r="D29" s="88"/>
-      <c r="E29" s="88"/>
-      <c r="F29" s="88"/>
-      <c r="G29" s="88"/>
-      <c r="H29" s="88"/>
-      <c r="I29" s="88"/>
-      <c r="J29" s="88"/>
-      <c r="K29" s="88"/>
+      <c r="C29" s="116"/>
+      <c r="D29" s="116"/>
+      <c r="E29" s="116"/>
+      <c r="F29" s="116"/>
+      <c r="G29" s="116"/>
+      <c r="H29" s="116"/>
+      <c r="I29" s="116"/>
+      <c r="J29" s="116"/>
+      <c r="K29" s="116"/>
       <c r="M29" s="1"/>
       <c r="O29" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6853,15 +6889,15 @@
     </row>
     <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
-      <c r="C30" s="89"/>
-      <c r="D30" s="89"/>
-      <c r="E30" s="89"/>
-      <c r="F30" s="89"/>
-      <c r="G30" s="89"/>
-      <c r="H30" s="89"/>
-      <c r="I30" s="89"/>
-      <c r="J30" s="89"/>
-      <c r="K30" s="89"/>
+      <c r="C30" s="115"/>
+      <c r="D30" s="115"/>
+      <c r="E30" s="115"/>
+      <c r="F30" s="115"/>
+      <c r="G30" s="115"/>
+      <c r="H30" s="115"/>
+      <c r="I30" s="115"/>
+      <c r="J30" s="115"/>
+      <c r="K30" s="115"/>
       <c r="M30" s="1"/>
       <c r="O30" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6925,15 +6961,15 @@
     </row>
     <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
-      <c r="C31" s="88"/>
-      <c r="D31" s="88"/>
-      <c r="E31" s="88"/>
-      <c r="F31" s="88"/>
-      <c r="G31" s="88"/>
-      <c r="H31" s="88"/>
-      <c r="I31" s="88"/>
-      <c r="J31" s="88"/>
-      <c r="K31" s="88"/>
+      <c r="C31" s="116"/>
+      <c r="D31" s="116"/>
+      <c r="E31" s="116"/>
+      <c r="F31" s="116"/>
+      <c r="G31" s="116"/>
+      <c r="H31" s="116"/>
+      <c r="I31" s="116"/>
+      <c r="J31" s="116"/>
+      <c r="K31" s="116"/>
       <c r="M31" s="1"/>
       <c r="O31" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -7108,98 +7144,128 @@
     </row>
     <row r="37" spans="1:32" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D38" s="115" t="s">
+      <c r="D38" s="84" t="s">
         <v>23</v>
       </c>
-      <c r="E38" s="116"/>
-      <c r="F38" s="117"/>
-      <c r="G38" s="121">
+      <c r="E38" s="85"/>
+      <c r="F38" s="86"/>
+      <c r="G38" s="90">
         <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
-        <v>5</v>
-      </c>
-      <c r="H38" s="122"/>
-      <c r="I38" s="115" t="s">
+        <v>4</v>
+      </c>
+      <c r="H38" s="91"/>
+      <c r="I38" s="84" t="s">
         <v>26</v>
       </c>
-      <c r="J38" s="125"/>
-      <c r="K38" s="127" t="s">
+      <c r="J38" s="98"/>
+      <c r="K38" s="94" t="s">
         <v>24</v>
       </c>
-      <c r="L38" s="128"/>
-      <c r="M38" s="131">
+      <c r="L38" s="95"/>
+      <c r="M38" s="106">
         <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
-        <v>3.9999999999999982</v>
-      </c>
-      <c r="N38" s="132"/>
-      <c r="O38" s="132"/>
-      <c r="P38" s="132"/>
-      <c r="Q38" s="132"/>
-      <c r="R38" s="133"/>
-      <c r="S38" s="137" t="s">
+        <v>5.0000000000000009</v>
+      </c>
+      <c r="N38" s="107"/>
+      <c r="O38" s="107"/>
+      <c r="P38" s="107"/>
+      <c r="Q38" s="107"/>
+      <c r="R38" s="108"/>
+      <c r="S38" s="100" t="s">
         <v>25</v>
       </c>
-      <c r="T38" s="138"/>
-      <c r="U38" s="138"/>
-      <c r="V38" s="138"/>
-      <c r="W38" s="138"/>
-      <c r="X38" s="139"/>
+      <c r="T38" s="101"/>
+      <c r="U38" s="101"/>
+      <c r="V38" s="101"/>
+      <c r="W38" s="101"/>
+      <c r="X38" s="102"/>
     </row>
     <row r="39" spans="1:32" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="118"/>
-      <c r="E39" s="119"/>
-      <c r="F39" s="120"/>
-      <c r="G39" s="123"/>
-      <c r="H39" s="124"/>
-      <c r="I39" s="118"/>
-      <c r="J39" s="126"/>
-      <c r="K39" s="129"/>
-      <c r="L39" s="130"/>
-      <c r="M39" s="134"/>
-      <c r="N39" s="135"/>
-      <c r="O39" s="135"/>
-      <c r="P39" s="135"/>
-      <c r="Q39" s="135"/>
-      <c r="R39" s="136"/>
-      <c r="S39" s="140"/>
-      <c r="T39" s="141"/>
-      <c r="U39" s="141"/>
-      <c r="V39" s="141"/>
-      <c r="W39" s="141"/>
-      <c r="X39" s="142"/>
+      <c r="D39" s="87"/>
+      <c r="E39" s="88"/>
+      <c r="F39" s="89"/>
+      <c r="G39" s="92"/>
+      <c r="H39" s="93"/>
+      <c r="I39" s="87"/>
+      <c r="J39" s="99"/>
+      <c r="K39" s="96"/>
+      <c r="L39" s="97"/>
+      <c r="M39" s="109"/>
+      <c r="N39" s="110"/>
+      <c r="O39" s="110"/>
+      <c r="P39" s="110"/>
+      <c r="Q39" s="110"/>
+      <c r="R39" s="111"/>
+      <c r="S39" s="103"/>
+      <c r="T39" s="104"/>
+      <c r="U39" s="104"/>
+      <c r="V39" s="104"/>
+      <c r="W39" s="104"/>
+      <c r="X39" s="105"/>
     </row>
   </sheetData>
   <mergeCells count="112">
-    <mergeCell ref="D38:F39"/>
-    <mergeCell ref="G38:H39"/>
-    <mergeCell ref="I38:J39"/>
-    <mergeCell ref="K38:L39"/>
-    <mergeCell ref="M38:R39"/>
-    <mergeCell ref="S38:X39"/>
-    <mergeCell ref="C30:K31"/>
-    <mergeCell ref="O20:V20"/>
-    <mergeCell ref="W20:AD20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:N21"/>
-    <mergeCell ref="O21:V21"/>
-    <mergeCell ref="W21:AD21"/>
-    <mergeCell ref="C2:AD2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="W5:AD5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="O5:V5"/>
+    <mergeCell ref="K18:N18"/>
+    <mergeCell ref="W18:AD18"/>
+    <mergeCell ref="C25:K26"/>
+    <mergeCell ref="O25:U25"/>
+    <mergeCell ref="X25:AD25"/>
+    <mergeCell ref="C27:K27"/>
+    <mergeCell ref="C28:K29"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="O18:V18"/>
+    <mergeCell ref="C19:D20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:N20"/>
+    <mergeCell ref="W15:AD15"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="O17:V17"/>
+    <mergeCell ref="W17:AD17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="O15:V15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="W12:AD12"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O14:V14"/>
+    <mergeCell ref="W14:AD14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="O12:V12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="W9:AD9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="O11:V11"/>
+    <mergeCell ref="W11:AD11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:V9"/>
+    <mergeCell ref="K9:N9"/>
     <mergeCell ref="K6:N6"/>
     <mergeCell ref="C7:D8"/>
     <mergeCell ref="E7:F7"/>
@@ -7220,67 +7286,37 @@
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="O6:V6"/>
     <mergeCell ref="W6:AD6"/>
-    <mergeCell ref="W9:AD9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="O11:V11"/>
-    <mergeCell ref="W11:AD11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:V9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="W12:AD12"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="O14:V14"/>
-    <mergeCell ref="W14:AD14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="O12:V12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="W15:AD15"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="O17:V17"/>
-    <mergeCell ref="W17:AD17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="O15:V15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="K18:N18"/>
-    <mergeCell ref="W18:AD18"/>
-    <mergeCell ref="C25:K26"/>
-    <mergeCell ref="O25:U25"/>
-    <mergeCell ref="X25:AD25"/>
-    <mergeCell ref="C27:K27"/>
-    <mergeCell ref="C28:K29"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="O18:V18"/>
-    <mergeCell ref="C19:D20"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:N20"/>
+    <mergeCell ref="C2:AD2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="W5:AD5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="O5:V5"/>
+    <mergeCell ref="D38:F39"/>
+    <mergeCell ref="G38:H39"/>
+    <mergeCell ref="I38:J39"/>
+    <mergeCell ref="K38:L39"/>
+    <mergeCell ref="M38:R39"/>
+    <mergeCell ref="S38:X39"/>
+    <mergeCell ref="C30:K31"/>
+    <mergeCell ref="O20:V20"/>
+    <mergeCell ref="W20:AD20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:N21"/>
+    <mergeCell ref="O21:V21"/>
+    <mergeCell ref="W21:AD21"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 E5 G5 I5 K5:L5 O5 W5 C7 E8 G8 I8 K8:L8 O8 W8 C10 E11 G11 I11 K11:L11 O11 W11 C13 E14 G14 I14 K14:L14 O14 W14 C16 E17 G17 I17 K17 O17 W17">
     <cfRule type="expression" dxfId="3" priority="3">
@@ -7632,15 +7668,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -7658,6 +7685,15 @@
     <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7682,14 +7718,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F0D3479-5903-425F-9669-62B4E7216DE9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B201CC6-7A0A-429C-B445-7EDA1CF4A1D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -7701,6 +7729,14 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F0D3479-5903-425F-9669-62B4E7216DE9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata"/>
 </file>
--- a/Group_milestones.xlsx
+++ b/Group_milestones.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="24334"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F39CAEE9-AD7F-4550-8EC3-283B9F427DAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56C9CD3F-2DF0-4D62-AFD8-9604F9331952}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="824" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -228,9 +228,6 @@
     <t>MCTR2: Motor characterise in heavy current lab with avalable VFD's</t>
   </si>
   <si>
-    <t>MCTR2: Start with gearbox casing build</t>
-  </si>
-  <si>
     <t>EERI321: PRACTICAL 2 submission</t>
   </si>
   <si>
@@ -374,6 +371,20 @@
         <scheme val="minor"/>
       </rPr>
       <t>Obtain winding wire</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">MCTR2: Start with gearbox casing build       </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFFC000"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>EEII2: Required voltage calculations, Switching circuit prelim</t>
     </r>
   </si>
 </sst>
@@ -1129,6 +1140,102 @@
     <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1213,100 +1320,31 @@
     <xf numFmtId="0" fontId="35" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="41" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1318,42 +1356,27 @@
     <xf numFmtId="0" fontId="37" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -1361,18 +1384,6 @@
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -1746,7 +1757,7 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R15"/>
-  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="4" width="5.5703125" style="3" customWidth="1"/>
     <col min="5" max="9" width="10.5703125" style="3" customWidth="1"/>
@@ -1758,7 +1769,7 @@
     <col min="19" max="16384" width="8.7109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1800,7 +1811,7 @@
       <c r="Q2" s="6"/>
       <c r="R2" s="4"/>
     </row>
-    <row r="3" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="3" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="8"/>
@@ -1820,7 +1831,7 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -2070,7 +2081,7 @@
       <c r="Q14" s="18"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -2157,42 +2168,42 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A2" s="29"/>
-      <c r="C2" s="117">
+      <c r="C2" s="114">
         <f ca="1">DATE(About!P8,9,1)</f>
         <v>46266</v>
       </c>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="117"/>
-      <c r="H2" s="117"/>
-      <c r="I2" s="117"/>
-      <c r="J2" s="117"/>
-      <c r="K2" s="117"/>
-      <c r="L2" s="117"/>
-      <c r="M2" s="117"/>
-      <c r="N2" s="117"/>
-      <c r="O2" s="117"/>
-      <c r="P2" s="117"/>
-      <c r="Q2" s="117"/>
-      <c r="R2" s="117"/>
-      <c r="S2" s="117"/>
-      <c r="T2" s="117"/>
-      <c r="U2" s="117"/>
-      <c r="V2" s="117"/>
-      <c r="W2" s="117"/>
-      <c r="X2" s="117"/>
-      <c r="Y2" s="117"/>
-      <c r="Z2" s="117"/>
-      <c r="AA2" s="117"/>
-      <c r="AB2" s="117"/>
-      <c r="AC2" s="117"/>
-      <c r="AD2" s="117"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="114"/>
+      <c r="O2" s="114"/>
+      <c r="P2" s="114"/>
+      <c r="Q2" s="114"/>
+      <c r="R2" s="114"/>
+      <c r="S2" s="114"/>
+      <c r="T2" s="114"/>
+      <c r="U2" s="114"/>
+      <c r="V2" s="114"/>
+      <c r="W2" s="114"/>
+      <c r="X2" s="114"/>
+      <c r="Y2" s="114"/>
+      <c r="Z2" s="114"/>
+      <c r="AA2" s="114"/>
+      <c r="AB2" s="114"/>
+      <c r="AC2" s="114"/>
+      <c r="AD2" s="114"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -2212,114 +2223,114 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="35"/>
-      <c r="C4" s="118">
+      <c r="C4" s="115">
         <f ca="1">C5</f>
         <v>46264</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118">
+      <c r="D4" s="115"/>
+      <c r="E4" s="115">
         <f ca="1">E5</f>
         <v>46265</v>
       </c>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118">
+      <c r="F4" s="115"/>
+      <c r="G4" s="115">
         <f ca="1">G5</f>
         <v>46266</v>
       </c>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118">
+      <c r="H4" s="115"/>
+      <c r="I4" s="115">
         <f ca="1">I5</f>
         <v>46267</v>
       </c>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118">
+      <c r="J4" s="115"/>
+      <c r="K4" s="115">
         <f ca="1">K5</f>
         <v>46268</v>
       </c>
-      <c r="L4" s="118"/>
-      <c r="M4" s="118"/>
+      <c r="L4" s="115"/>
+      <c r="M4" s="115"/>
       <c r="N4" s="37"/>
-      <c r="O4" s="118">
+      <c r="O4" s="115">
         <f ca="1">O5</f>
         <v>46269</v>
       </c>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="118"/>
-      <c r="S4" s="118"/>
-      <c r="T4" s="118"/>
-      <c r="U4" s="118"/>
-      <c r="V4" s="118"/>
-      <c r="W4" s="118">
+      <c r="P4" s="115"/>
+      <c r="Q4" s="115"/>
+      <c r="R4" s="115"/>
+      <c r="S4" s="115"/>
+      <c r="T4" s="115"/>
+      <c r="U4" s="115"/>
+      <c r="V4" s="115"/>
+      <c r="W4" s="115">
         <f ca="1">W5</f>
         <v>46270</v>
       </c>
-      <c r="X4" s="118"/>
-      <c r="Y4" s="118"/>
-      <c r="Z4" s="118"/>
-      <c r="AA4" s="118"/>
-      <c r="AB4" s="118"/>
-      <c r="AC4" s="118"/>
-      <c r="AD4" s="118"/>
+      <c r="X4" s="115"/>
+      <c r="Y4" s="115"/>
+      <c r="Z4" s="115"/>
+      <c r="AA4" s="115"/>
+      <c r="AB4" s="115"/>
+      <c r="AC4" s="115"/>
+      <c r="AD4" s="115"/>
       <c r="AF4" s="38"/>
       <c r="AG4" s="39"/>
       <c r="AH4" s="39"/>
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="C5" s="119">
+      <c r="C5" s="95">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46264</v>
       </c>
-      <c r="D5" s="121"/>
-      <c r="E5" s="119">
+      <c r="D5" s="96"/>
+      <c r="E5" s="95">
         <f ca="1">C5+1</f>
         <v>46265</v>
       </c>
-      <c r="F5" s="121"/>
-      <c r="G5" s="119">
+      <c r="F5" s="96"/>
+      <c r="G5" s="95">
         <f ca="1">E5+1</f>
         <v>46266</v>
       </c>
-      <c r="H5" s="121"/>
-      <c r="I5" s="119">
+      <c r="H5" s="96"/>
+      <c r="I5" s="95">
         <f ca="1">G5+1</f>
         <v>46267</v>
       </c>
-      <c r="J5" s="121"/>
-      <c r="K5" s="119">
+      <c r="J5" s="96"/>
+      <c r="K5" s="95">
         <f ca="1">I5+1</f>
         <v>46268</v>
       </c>
-      <c r="L5" s="120"/>
-      <c r="M5" s="120"/>
+      <c r="L5" s="113"/>
+      <c r="M5" s="113"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="119">
+      <c r="O5" s="95">
         <f ca="1">K5+1</f>
         <v>46269</v>
       </c>
-      <c r="P5" s="120"/>
-      <c r="Q5" s="120"/>
-      <c r="R5" s="120"/>
-      <c r="S5" s="120"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="121"/>
-      <c r="W5" s="119">
+      <c r="P5" s="113"/>
+      <c r="Q5" s="113"/>
+      <c r="R5" s="113"/>
+      <c r="S5" s="113"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="113"/>
+      <c r="V5" s="96"/>
+      <c r="W5" s="95">
         <f ca="1">O5+1</f>
         <v>46270</v>
       </c>
-      <c r="X5" s="120"/>
-      <c r="Y5" s="120"/>
-      <c r="Z5" s="120"/>
-      <c r="AA5" s="120"/>
-      <c r="AB5" s="120"/>
-      <c r="AC5" s="120"/>
-      <c r="AD5" s="121"/>
+      <c r="X5" s="113"/>
+      <c r="Y5" s="113"/>
+      <c r="Z5" s="113"/>
+      <c r="AA5" s="113"/>
+      <c r="AB5" s="113"/>
+      <c r="AC5" s="113"/>
+      <c r="AD5" s="96"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
@@ -2328,164 +2339,164 @@
     </row>
     <row r="6" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="42"/>
-      <c r="C6" s="122"/>
-      <c r="D6" s="123"/>
-      <c r="E6" s="122"/>
-      <c r="F6" s="123"/>
-      <c r="G6" s="124"/>
-      <c r="H6" s="125"/>
-      <c r="I6" s="124"/>
-      <c r="J6" s="125"/>
-      <c r="K6" s="124"/>
-      <c r="L6" s="126"/>
-      <c r="M6" s="126"/>
-      <c r="N6" s="125"/>
-      <c r="O6" s="124"/>
-      <c r="P6" s="126"/>
-      <c r="Q6" s="126"/>
-      <c r="R6" s="126"/>
-      <c r="S6" s="126"/>
-      <c r="T6" s="126"/>
-      <c r="U6" s="126"/>
-      <c r="V6" s="125"/>
-      <c r="W6" s="124"/>
-      <c r="X6" s="126"/>
-      <c r="Y6" s="126"/>
-      <c r="Z6" s="126"/>
-      <c r="AA6" s="126"/>
-      <c r="AB6" s="126"/>
-      <c r="AC6" s="126"/>
-      <c r="AD6" s="125"/>
+      <c r="C6" s="84"/>
+      <c r="D6" s="86"/>
+      <c r="E6" s="84"/>
+      <c r="F6" s="86"/>
+      <c r="G6" s="104"/>
+      <c r="H6" s="105"/>
+      <c r="I6" s="104"/>
+      <c r="J6" s="105"/>
+      <c r="K6" s="104"/>
+      <c r="L6" s="106"/>
+      <c r="M6" s="106"/>
+      <c r="N6" s="105"/>
+      <c r="O6" s="104"/>
+      <c r="P6" s="106"/>
+      <c r="Q6" s="106"/>
+      <c r="R6" s="106"/>
+      <c r="S6" s="106"/>
+      <c r="T6" s="106"/>
+      <c r="U6" s="106"/>
+      <c r="V6" s="105"/>
+      <c r="W6" s="104"/>
+      <c r="X6" s="106"/>
+      <c r="Y6" s="106"/>
+      <c r="Z6" s="106"/>
+      <c r="AA6" s="106"/>
+      <c r="AB6" s="106"/>
+      <c r="AC6" s="106"/>
+      <c r="AD6" s="105"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
     <row r="7" spans="1:36" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="C7" s="119">
+      <c r="C7" s="95">
         <f ca="1">W5+1</f>
         <v>46271</v>
       </c>
-      <c r="D7" s="121"/>
-      <c r="E7" s="127"/>
-      <c r="F7" s="128"/>
-      <c r="G7" s="127"/>
-      <c r="H7" s="128"/>
-      <c r="I7" s="127"/>
-      <c r="J7" s="128"/>
-      <c r="K7" s="127"/>
-      <c r="L7" s="129"/>
-      <c r="M7" s="129"/>
+      <c r="D7" s="96"/>
+      <c r="E7" s="110"/>
+      <c r="F7" s="111"/>
+      <c r="G7" s="110"/>
+      <c r="H7" s="111"/>
+      <c r="I7" s="110"/>
+      <c r="J7" s="111"/>
+      <c r="K7" s="110"/>
+      <c r="L7" s="112"/>
+      <c r="M7" s="112"/>
       <c r="N7" s="75"/>
-      <c r="O7" s="127"/>
-      <c r="P7" s="129"/>
-      <c r="Q7" s="129"/>
-      <c r="R7" s="129"/>
-      <c r="S7" s="129"/>
-      <c r="T7" s="129"/>
-      <c r="U7" s="129"/>
-      <c r="V7" s="128"/>
-      <c r="W7" s="127"/>
-      <c r="X7" s="129"/>
-      <c r="Y7" s="129"/>
-      <c r="Z7" s="129"/>
-      <c r="AA7" s="129"/>
-      <c r="AB7" s="129"/>
-      <c r="AC7" s="129"/>
-      <c r="AD7" s="128"/>
+      <c r="O7" s="110"/>
+      <c r="P7" s="112"/>
+      <c r="Q7" s="112"/>
+      <c r="R7" s="112"/>
+      <c r="S7" s="112"/>
+      <c r="T7" s="112"/>
+      <c r="U7" s="112"/>
+      <c r="V7" s="111"/>
+      <c r="W7" s="110"/>
+      <c r="X7" s="112"/>
+      <c r="Y7" s="112"/>
+      <c r="Z7" s="112"/>
+      <c r="AA7" s="112"/>
+      <c r="AB7" s="112"/>
+      <c r="AC7" s="112"/>
+      <c r="AD7" s="111"/>
       <c r="AF7" s="1"/>
     </row>
     <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="121"/>
-      <c r="E8" s="112">
+      <c r="C8" s="95"/>
+      <c r="D8" s="96"/>
+      <c r="E8" s="99">
         <f ca="1">C7+1</f>
         <v>46272</v>
       </c>
-      <c r="F8" s="113"/>
-      <c r="G8" s="112">
+      <c r="F8" s="101"/>
+      <c r="G8" s="99">
         <f ca="1">E8+1</f>
         <v>46273</v>
       </c>
-      <c r="H8" s="113"/>
-      <c r="I8" s="112">
+      <c r="H8" s="101"/>
+      <c r="I8" s="99">
         <f ca="1">G8+1</f>
         <v>46274</v>
       </c>
-      <c r="J8" s="113"/>
-      <c r="K8" s="112">
+      <c r="J8" s="101"/>
+      <c r="K8" s="99">
         <f ca="1">I8+1</f>
         <v>46275</v>
       </c>
-      <c r="L8" s="114"/>
-      <c r="M8" s="114"/>
+      <c r="L8" s="100"/>
+      <c r="M8" s="100"/>
       <c r="N8" s="50"/>
-      <c r="O8" s="112">
+      <c r="O8" s="99">
         <f ca="1">K8+1</f>
         <v>46276</v>
       </c>
-      <c r="P8" s="114"/>
-      <c r="Q8" s="114"/>
-      <c r="R8" s="114"/>
-      <c r="S8" s="114"/>
-      <c r="T8" s="114"/>
-      <c r="U8" s="114"/>
-      <c r="V8" s="113"/>
-      <c r="W8" s="112">
+      <c r="P8" s="100"/>
+      <c r="Q8" s="100"/>
+      <c r="R8" s="100"/>
+      <c r="S8" s="100"/>
+      <c r="T8" s="100"/>
+      <c r="U8" s="100"/>
+      <c r="V8" s="101"/>
+      <c r="W8" s="99">
         <f ca="1">O8+1</f>
         <v>46277</v>
       </c>
-      <c r="X8" s="114"/>
-      <c r="Y8" s="114"/>
-      <c r="Z8" s="114"/>
-      <c r="AA8" s="114"/>
-      <c r="AB8" s="114"/>
-      <c r="AC8" s="114"/>
-      <c r="AD8" s="113"/>
+      <c r="X8" s="100"/>
+      <c r="Y8" s="100"/>
+      <c r="Z8" s="100"/>
+      <c r="AA8" s="100"/>
+      <c r="AB8" s="100"/>
+      <c r="AC8" s="100"/>
+      <c r="AD8" s="101"/>
       <c r="AF8" s="4"/>
     </row>
     <row r="9" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="42"/>
-      <c r="C9" s="124"/>
-      <c r="D9" s="125"/>
-      <c r="E9" s="124"/>
-      <c r="F9" s="125"/>
-      <c r="G9" s="124"/>
-      <c r="H9" s="125"/>
-      <c r="I9" s="124"/>
-      <c r="J9" s="125"/>
-      <c r="K9" s="124"/>
-      <c r="L9" s="126"/>
-      <c r="M9" s="126"/>
-      <c r="N9" s="125"/>
-      <c r="O9" s="130" t="s">
-        <v>40</v>
-      </c>
-      <c r="P9" s="131"/>
-      <c r="Q9" s="131"/>
-      <c r="R9" s="131"/>
-      <c r="S9" s="131"/>
-      <c r="T9" s="131"/>
-      <c r="U9" s="131"/>
-      <c r="V9" s="132"/>
-      <c r="W9" s="124"/>
-      <c r="X9" s="126"/>
-      <c r="Y9" s="126"/>
-      <c r="Z9" s="126"/>
-      <c r="AA9" s="126"/>
-      <c r="AB9" s="126"/>
-      <c r="AC9" s="126"/>
-      <c r="AD9" s="125"/>
+      <c r="C9" s="104"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="104"/>
+      <c r="F9" s="105"/>
+      <c r="G9" s="104"/>
+      <c r="H9" s="105"/>
+      <c r="I9" s="104"/>
+      <c r="J9" s="105"/>
+      <c r="K9" s="104"/>
+      <c r="L9" s="106"/>
+      <c r="M9" s="106"/>
+      <c r="N9" s="105"/>
+      <c r="O9" s="107" t="s">
+        <v>39</v>
+      </c>
+      <c r="P9" s="109"/>
+      <c r="Q9" s="109"/>
+      <c r="R9" s="109"/>
+      <c r="S9" s="109"/>
+      <c r="T9" s="109"/>
+      <c r="U9" s="109"/>
+      <c r="V9" s="108"/>
+      <c r="W9" s="104"/>
+      <c r="X9" s="106"/>
+      <c r="Y9" s="106"/>
+      <c r="Z9" s="106"/>
+      <c r="AA9" s="106"/>
+      <c r="AB9" s="106"/>
+      <c r="AC9" s="106"/>
+      <c r="AD9" s="105"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
     <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="42"/>
-      <c r="C10" s="119">
+      <c r="C10" s="95">
         <f ca="1">W8+1</f>
         <v>46278</v>
       </c>
-      <c r="D10" s="121"/>
+      <c r="D10" s="96"/>
       <c r="E10" s="45"/>
       <c r="F10" s="75"/>
       <c r="G10" s="45"/>
@@ -2517,97 +2528,97 @@
     </row>
     <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="112">
+      <c r="C11" s="95"/>
+      <c r="D11" s="96"/>
+      <c r="E11" s="99">
         <f ca="1">C10+1</f>
         <v>46279</v>
       </c>
-      <c r="F11" s="113"/>
-      <c r="G11" s="112">
+      <c r="F11" s="101"/>
+      <c r="G11" s="99">
         <f ca="1">E11+1</f>
         <v>46280</v>
       </c>
-      <c r="H11" s="113"/>
-      <c r="I11" s="112">
+      <c r="H11" s="101"/>
+      <c r="I11" s="99">
         <f ca="1">G11+1</f>
         <v>46281</v>
       </c>
-      <c r="J11" s="113"/>
-      <c r="K11" s="112">
+      <c r="J11" s="101"/>
+      <c r="K11" s="99">
         <f ca="1">I11+1</f>
         <v>46282</v>
       </c>
-      <c r="L11" s="114"/>
-      <c r="M11" s="114"/>
+      <c r="L11" s="100"/>
+      <c r="M11" s="100"/>
       <c r="N11" s="50"/>
-      <c r="O11" s="112">
+      <c r="O11" s="99">
         <f ca="1">K11+1</f>
         <v>46283</v>
       </c>
-      <c r="P11" s="114"/>
-      <c r="Q11" s="114"/>
-      <c r="R11" s="114"/>
-      <c r="S11" s="114"/>
-      <c r="T11" s="114"/>
-      <c r="U11" s="114"/>
-      <c r="V11" s="113"/>
-      <c r="W11" s="112">
+      <c r="P11" s="100"/>
+      <c r="Q11" s="100"/>
+      <c r="R11" s="100"/>
+      <c r="S11" s="100"/>
+      <c r="T11" s="100"/>
+      <c r="U11" s="100"/>
+      <c r="V11" s="101"/>
+      <c r="W11" s="99">
         <f ca="1">O11+1</f>
         <v>46284</v>
       </c>
-      <c r="X11" s="114"/>
-      <c r="Y11" s="114"/>
-      <c r="Z11" s="114"/>
-      <c r="AA11" s="114"/>
-      <c r="AB11" s="114"/>
-      <c r="AC11" s="114"/>
-      <c r="AD11" s="113"/>
+      <c r="X11" s="100"/>
+      <c r="Y11" s="100"/>
+      <c r="Z11" s="100"/>
+      <c r="AA11" s="100"/>
+      <c r="AB11" s="100"/>
+      <c r="AC11" s="100"/>
+      <c r="AD11" s="101"/>
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
     <row r="12" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="42"/>
-      <c r="C12" s="124"/>
-      <c r="D12" s="125"/>
-      <c r="E12" s="130" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" s="132"/>
-      <c r="G12" s="124"/>
-      <c r="H12" s="125"/>
-      <c r="I12" s="124"/>
-      <c r="J12" s="125"/>
-      <c r="K12" s="124"/>
-      <c r="L12" s="126"/>
-      <c r="M12" s="126"/>
-      <c r="N12" s="125"/>
-      <c r="O12" s="124"/>
-      <c r="P12" s="126"/>
-      <c r="Q12" s="126"/>
-      <c r="R12" s="126"/>
-      <c r="S12" s="126"/>
-      <c r="T12" s="126"/>
-      <c r="U12" s="126"/>
-      <c r="V12" s="125"/>
-      <c r="W12" s="124"/>
-      <c r="X12" s="126"/>
-      <c r="Y12" s="126"/>
-      <c r="Z12" s="126"/>
-      <c r="AA12" s="126"/>
-      <c r="AB12" s="126"/>
-      <c r="AC12" s="126"/>
-      <c r="AD12" s="125"/>
+      <c r="C12" s="104"/>
+      <c r="D12" s="105"/>
+      <c r="E12" s="107" t="s">
+        <v>40</v>
+      </c>
+      <c r="F12" s="108"/>
+      <c r="G12" s="104"/>
+      <c r="H12" s="105"/>
+      <c r="I12" s="104"/>
+      <c r="J12" s="105"/>
+      <c r="K12" s="104"/>
+      <c r="L12" s="106"/>
+      <c r="M12" s="106"/>
+      <c r="N12" s="105"/>
+      <c r="O12" s="104"/>
+      <c r="P12" s="106"/>
+      <c r="Q12" s="106"/>
+      <c r="R12" s="106"/>
+      <c r="S12" s="106"/>
+      <c r="T12" s="106"/>
+      <c r="U12" s="106"/>
+      <c r="V12" s="105"/>
+      <c r="W12" s="104"/>
+      <c r="X12" s="106"/>
+      <c r="Y12" s="106"/>
+      <c r="Z12" s="106"/>
+      <c r="AA12" s="106"/>
+      <c r="AB12" s="106"/>
+      <c r="AC12" s="106"/>
+      <c r="AD12" s="105"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
     <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="42"/>
-      <c r="C13" s="119">
+      <c r="C13" s="95">
         <f ca="1">W11+1</f>
         <v>46285</v>
       </c>
-      <c r="D13" s="121"/>
+      <c r="D13" s="96"/>
       <c r="E13" s="45"/>
       <c r="F13" s="75"/>
       <c r="G13" s="45"/>
@@ -2639,112 +2650,112 @@
     </row>
     <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4"/>
-      <c r="C14" s="119"/>
-      <c r="D14" s="121"/>
-      <c r="E14" s="112">
+      <c r="C14" s="95"/>
+      <c r="D14" s="96"/>
+      <c r="E14" s="99">
         <f ca="1">C13+1</f>
         <v>46286</v>
       </c>
-      <c r="F14" s="113"/>
-      <c r="G14" s="112">
+      <c r="F14" s="101"/>
+      <c r="G14" s="99">
         <f ca="1">E14+1</f>
         <v>46287</v>
       </c>
-      <c r="H14" s="113"/>
-      <c r="I14" s="112">
+      <c r="H14" s="101"/>
+      <c r="I14" s="99">
         <f ca="1">G14+1</f>
         <v>46288</v>
       </c>
-      <c r="J14" s="113"/>
-      <c r="K14" s="112">
+      <c r="J14" s="101"/>
+      <c r="K14" s="99">
         <f ca="1">I14+1</f>
         <v>46289</v>
       </c>
-      <c r="L14" s="114"/>
-      <c r="M14" s="114"/>
+      <c r="L14" s="100"/>
+      <c r="M14" s="100"/>
       <c r="N14" s="50"/>
-      <c r="O14" s="112">
+      <c r="O14" s="99">
         <f ca="1">K14+1</f>
         <v>46290</v>
       </c>
-      <c r="P14" s="114"/>
-      <c r="Q14" s="114"/>
-      <c r="R14" s="114"/>
-      <c r="S14" s="114"/>
-      <c r="T14" s="114"/>
-      <c r="U14" s="114"/>
-      <c r="V14" s="113"/>
-      <c r="W14" s="112">
+      <c r="P14" s="100"/>
+      <c r="Q14" s="100"/>
+      <c r="R14" s="100"/>
+      <c r="S14" s="100"/>
+      <c r="T14" s="100"/>
+      <c r="U14" s="100"/>
+      <c r="V14" s="101"/>
+      <c r="W14" s="99">
         <f ca="1">O14+1</f>
         <v>46291</v>
       </c>
-      <c r="X14" s="114"/>
-      <c r="Y14" s="114"/>
-      <c r="Z14" s="114"/>
-      <c r="AA14" s="114"/>
-      <c r="AB14" s="114"/>
-      <c r="AC14" s="114"/>
-      <c r="AD14" s="113"/>
+      <c r="X14" s="100"/>
+      <c r="Y14" s="100"/>
+      <c r="Z14" s="100"/>
+      <c r="AA14" s="100"/>
+      <c r="AB14" s="100"/>
+      <c r="AC14" s="100"/>
+      <c r="AD14" s="101"/>
       <c r="AF14" s="4"/>
     </row>
     <row r="15" spans="1:36" s="43" customFormat="1" ht="162.94999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="42"/>
-      <c r="C15" s="124"/>
-      <c r="D15" s="125"/>
-      <c r="E15" s="124"/>
-      <c r="F15" s="125"/>
-      <c r="G15" s="124"/>
-      <c r="H15" s="125"/>
-      <c r="I15" s="133"/>
-      <c r="J15" s="135"/>
-      <c r="K15" s="133"/>
-      <c r="L15" s="134"/>
-      <c r="M15" s="134"/>
-      <c r="N15" s="135"/>
-      <c r="O15" s="133"/>
-      <c r="P15" s="134"/>
-      <c r="Q15" s="134"/>
-      <c r="R15" s="134"/>
-      <c r="S15" s="134"/>
-      <c r="T15" s="134"/>
-      <c r="U15" s="134"/>
-      <c r="V15" s="135"/>
-      <c r="W15" s="133"/>
-      <c r="X15" s="134"/>
-      <c r="Y15" s="134"/>
-      <c r="Z15" s="134"/>
-      <c r="AA15" s="134"/>
-      <c r="AB15" s="134"/>
-      <c r="AC15" s="134"/>
-      <c r="AD15" s="135"/>
+      <c r="C15" s="104"/>
+      <c r="D15" s="105"/>
+      <c r="E15" s="104"/>
+      <c r="F15" s="105"/>
+      <c r="G15" s="104"/>
+      <c r="H15" s="105"/>
+      <c r="I15" s="93"/>
+      <c r="J15" s="94"/>
+      <c r="K15" s="93"/>
+      <c r="L15" s="103"/>
+      <c r="M15" s="103"/>
+      <c r="N15" s="94"/>
+      <c r="O15" s="93"/>
+      <c r="P15" s="103"/>
+      <c r="Q15" s="103"/>
+      <c r="R15" s="103"/>
+      <c r="S15" s="103"/>
+      <c r="T15" s="103"/>
+      <c r="U15" s="103"/>
+      <c r="V15" s="94"/>
+      <c r="W15" s="93"/>
+      <c r="X15" s="103"/>
+      <c r="Y15" s="103"/>
+      <c r="Z15" s="103"/>
+      <c r="AA15" s="103"/>
+      <c r="AB15" s="103"/>
+      <c r="AC15" s="103"/>
+      <c r="AD15" s="94"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
     <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="42"/>
-      <c r="C16" s="119">
+      <c r="C16" s="95">
         <f ca="1">W14+1</f>
         <v>46292</v>
       </c>
-      <c r="D16" s="121"/>
+      <c r="D16" s="96"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
       <c r="H16" s="75"/>
-      <c r="I16" s="136"/>
-      <c r="J16" s="137"/>
+      <c r="I16" s="97"/>
+      <c r="J16" s="98"/>
       <c r="K16" s="66"/>
       <c r="L16" s="68"/>
       <c r="M16" s="68"/>
       <c r="N16" s="67"/>
-      <c r="O16" s="136"/>
-      <c r="P16" s="138"/>
-      <c r="Q16" s="138"/>
-      <c r="R16" s="138"/>
-      <c r="S16" s="138"/>
-      <c r="T16" s="138"/>
-      <c r="U16" s="138"/>
-      <c r="V16" s="137"/>
+      <c r="O16" s="97"/>
+      <c r="P16" s="102"/>
+      <c r="Q16" s="102"/>
+      <c r="R16" s="102"/>
+      <c r="S16" s="102"/>
+      <c r="T16" s="102"/>
+      <c r="U16" s="102"/>
+      <c r="V16" s="98"/>
       <c r="W16" s="45"/>
       <c r="X16" s="76"/>
       <c r="Y16" s="76"/>
@@ -2758,23 +2769,23 @@
     </row>
     <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
-      <c r="C17" s="119"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="112">
+      <c r="C17" s="95"/>
+      <c r="D17" s="96"/>
+      <c r="E17" s="99">
         <f ca="1">C16+1</f>
         <v>46293</v>
       </c>
-      <c r="F17" s="113"/>
-      <c r="G17" s="112">
+      <c r="F17" s="101"/>
+      <c r="G17" s="99">
         <f ca="1">E17+1</f>
         <v>46294</v>
       </c>
-      <c r="H17" s="113"/>
-      <c r="I17" s="112">
+      <c r="H17" s="101"/>
+      <c r="I17" s="99">
         <f ca="1">G17+1</f>
         <v>46295</v>
       </c>
-      <c r="J17" s="113"/>
+      <c r="J17" s="101"/>
       <c r="K17" s="46">
         <f ca="1">I17+1</f>
         <v>46296</v>
@@ -2782,93 +2793,93 @@
       <c r="L17" s="51"/>
       <c r="M17" s="51"/>
       <c r="N17" s="69"/>
-      <c r="O17" s="112">
+      <c r="O17" s="99">
         <f ca="1">K17+1</f>
         <v>46297</v>
       </c>
-      <c r="P17" s="114"/>
-      <c r="Q17" s="114"/>
-      <c r="R17" s="114"/>
-      <c r="S17" s="114"/>
-      <c r="T17" s="114"/>
-      <c r="U17" s="114"/>
-      <c r="V17" s="113"/>
-      <c r="W17" s="112">
+      <c r="P17" s="100"/>
+      <c r="Q17" s="100"/>
+      <c r="R17" s="100"/>
+      <c r="S17" s="100"/>
+      <c r="T17" s="100"/>
+      <c r="U17" s="100"/>
+      <c r="V17" s="101"/>
+      <c r="W17" s="99">
         <f ca="1">O17+1</f>
         <v>46298</v>
       </c>
-      <c r="X17" s="114"/>
-      <c r="Y17" s="114"/>
-      <c r="Z17" s="114"/>
-      <c r="AA17" s="114"/>
-      <c r="AB17" s="114"/>
-      <c r="AC17" s="114"/>
-      <c r="AD17" s="113"/>
+      <c r="X17" s="100"/>
+      <c r="Y17" s="100"/>
+      <c r="Z17" s="100"/>
+      <c r="AA17" s="100"/>
+      <c r="AB17" s="100"/>
+      <c r="AC17" s="100"/>
+      <c r="AD17" s="101"/>
       <c r="AF17" s="4"/>
     </row>
     <row r="18" spans="1:42" s="43" customFormat="1" ht="147.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="42"/>
-      <c r="C18" s="142" t="s">
+      <c r="C18" s="91" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="143"/>
-      <c r="E18" s="133"/>
-      <c r="F18" s="135"/>
-      <c r="G18" s="133"/>
-      <c r="H18" s="135"/>
-      <c r="I18" s="142" t="s">
+      <c r="D18" s="92"/>
+      <c r="E18" s="93"/>
+      <c r="F18" s="94"/>
+      <c r="G18" s="93"/>
+      <c r="H18" s="94"/>
+      <c r="I18" s="91" t="s">
         <v>17</v>
       </c>
-      <c r="J18" s="143"/>
+      <c r="J18" s="92"/>
       <c r="K18" s="70"/>
       <c r="L18" s="71"/>
       <c r="M18" s="71"/>
       <c r="N18" s="72"/>
-      <c r="O18" s="122"/>
-      <c r="P18" s="139"/>
-      <c r="Q18" s="139"/>
-      <c r="R18" s="139"/>
-      <c r="S18" s="139"/>
-      <c r="T18" s="139"/>
-      <c r="U18" s="139"/>
-      <c r="V18" s="123"/>
-      <c r="W18" s="122"/>
-      <c r="X18" s="139"/>
-      <c r="Y18" s="139"/>
-      <c r="Z18" s="139"/>
-      <c r="AA18" s="139"/>
-      <c r="AB18" s="139"/>
-      <c r="AC18" s="139"/>
-      <c r="AD18" s="123"/>
+      <c r="O18" s="84"/>
+      <c r="P18" s="85"/>
+      <c r="Q18" s="85"/>
+      <c r="R18" s="85"/>
+      <c r="S18" s="85"/>
+      <c r="T18" s="85"/>
+      <c r="U18" s="85"/>
+      <c r="V18" s="86"/>
+      <c r="W18" s="84"/>
+      <c r="X18" s="85"/>
+      <c r="Y18" s="85"/>
+      <c r="Z18" s="85"/>
+      <c r="AA18" s="85"/>
+      <c r="AB18" s="85"/>
+      <c r="AC18" s="85"/>
+      <c r="AD18" s="86"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
     <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="42"/>
-      <c r="C19" s="119">
+      <c r="C19" s="95">
         <f ca="1">W17+1</f>
         <v>46299</v>
       </c>
-      <c r="D19" s="121"/>
+      <c r="D19" s="96"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
       <c r="H19" s="75"/>
-      <c r="I19" s="136"/>
-      <c r="J19" s="137"/>
+      <c r="I19" s="97"/>
+      <c r="J19" s="98"/>
       <c r="K19" s="66"/>
       <c r="L19" s="68"/>
       <c r="M19" s="68"/>
       <c r="N19" s="67"/>
-      <c r="O19" s="136"/>
-      <c r="P19" s="138"/>
-      <c r="Q19" s="138"/>
-      <c r="R19" s="138"/>
-      <c r="S19" s="138"/>
-      <c r="T19" s="138"/>
-      <c r="U19" s="138"/>
-      <c r="V19" s="137"/>
+      <c r="O19" s="97"/>
+      <c r="P19" s="102"/>
+      <c r="Q19" s="102"/>
+      <c r="R19" s="102"/>
+      <c r="S19" s="102"/>
+      <c r="T19" s="102"/>
+      <c r="U19" s="102"/>
+      <c r="V19" s="98"/>
       <c r="W19" s="45"/>
       <c r="X19" s="76"/>
       <c r="Y19" s="76"/>
@@ -2882,23 +2893,23 @@
     </row>
     <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
-      <c r="C20" s="119"/>
-      <c r="D20" s="121"/>
-      <c r="E20" s="112">
+      <c r="C20" s="95"/>
+      <c r="D20" s="96"/>
+      <c r="E20" s="99">
         <f ca="1">C19+1</f>
         <v>46300</v>
       </c>
-      <c r="F20" s="113"/>
-      <c r="G20" s="112">
+      <c r="F20" s="101"/>
+      <c r="G20" s="99">
         <f ca="1">E20+1</f>
         <v>46301</v>
       </c>
-      <c r="H20" s="113"/>
-      <c r="I20" s="112">
+      <c r="H20" s="101"/>
+      <c r="I20" s="99">
         <f ca="1">G20+1</f>
         <v>46302</v>
       </c>
-      <c r="J20" s="113"/>
+      <c r="J20" s="101"/>
       <c r="K20" s="46">
         <f ca="1">I20+1</f>
         <v>46303</v>
@@ -2906,60 +2917,60 @@
       <c r="L20" s="51"/>
       <c r="M20" s="51"/>
       <c r="N20" s="69"/>
-      <c r="O20" s="112">
+      <c r="O20" s="99">
         <f ca="1">K20+1</f>
         <v>46304</v>
       </c>
-      <c r="P20" s="114"/>
-      <c r="Q20" s="114"/>
-      <c r="R20" s="114"/>
-      <c r="S20" s="114"/>
-      <c r="T20" s="114"/>
-      <c r="U20" s="114"/>
-      <c r="V20" s="113"/>
-      <c r="W20" s="112">
+      <c r="P20" s="100"/>
+      <c r="Q20" s="100"/>
+      <c r="R20" s="100"/>
+      <c r="S20" s="100"/>
+      <c r="T20" s="100"/>
+      <c r="U20" s="100"/>
+      <c r="V20" s="101"/>
+      <c r="W20" s="99">
         <f ca="1">O20+1</f>
         <v>46305</v>
       </c>
-      <c r="X20" s="114"/>
-      <c r="Y20" s="114"/>
-      <c r="Z20" s="114"/>
-      <c r="AA20" s="114"/>
-      <c r="AB20" s="114"/>
-      <c r="AC20" s="114"/>
-      <c r="AD20" s="113"/>
+      <c r="X20" s="100"/>
+      <c r="Y20" s="100"/>
+      <c r="Z20" s="100"/>
+      <c r="AA20" s="100"/>
+      <c r="AB20" s="100"/>
+      <c r="AC20" s="100"/>
+      <c r="AD20" s="101"/>
       <c r="AF20" s="4"/>
     </row>
     <row r="21" spans="1:42" s="43" customFormat="1" ht="166.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="42"/>
-      <c r="C21" s="122"/>
-      <c r="D21" s="123"/>
-      <c r="E21" s="122"/>
-      <c r="F21" s="123"/>
-      <c r="G21" s="122"/>
-      <c r="H21" s="123"/>
-      <c r="I21" s="122"/>
-      <c r="J21" s="123"/>
+      <c r="C21" s="84"/>
+      <c r="D21" s="86"/>
+      <c r="E21" s="84"/>
+      <c r="F21" s="86"/>
+      <c r="G21" s="84"/>
+      <c r="H21" s="86"/>
+      <c r="I21" s="84"/>
+      <c r="J21" s="86"/>
       <c r="K21" s="70"/>
       <c r="L21" s="71"/>
       <c r="M21" s="71"/>
       <c r="N21" s="72"/>
-      <c r="O21" s="122"/>
-      <c r="P21" s="139"/>
-      <c r="Q21" s="139"/>
-      <c r="R21" s="139"/>
-      <c r="S21" s="139"/>
-      <c r="T21" s="139"/>
-      <c r="U21" s="139"/>
-      <c r="V21" s="123"/>
-      <c r="W21" s="122"/>
-      <c r="X21" s="139"/>
-      <c r="Y21" s="139"/>
-      <c r="Z21" s="139"/>
-      <c r="AA21" s="139"/>
-      <c r="AB21" s="139"/>
-      <c r="AC21" s="139"/>
-      <c r="AD21" s="123"/>
+      <c r="O21" s="84"/>
+      <c r="P21" s="85"/>
+      <c r="Q21" s="85"/>
+      <c r="R21" s="85"/>
+      <c r="S21" s="85"/>
+      <c r="T21" s="85"/>
+      <c r="U21" s="85"/>
+      <c r="V21" s="86"/>
+      <c r="W21" s="84"/>
+      <c r="X21" s="85"/>
+      <c r="Y21" s="85"/>
+      <c r="Z21" s="85"/>
+      <c r="AA21" s="85"/>
+      <c r="AB21" s="85"/>
+      <c r="AC21" s="85"/>
+      <c r="AD21" s="86"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
@@ -3037,54 +3048,54 @@
     </row>
     <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
-      <c r="C25" s="140" t="s">
+      <c r="C25" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="140"/>
-      <c r="E25" s="140"/>
-      <c r="F25" s="140"/>
-      <c r="G25" s="140"/>
-      <c r="H25" s="140"/>
-      <c r="I25" s="140"/>
-      <c r="J25" s="140"/>
-      <c r="K25" s="140"/>
+      <c r="D25" s="87"/>
+      <c r="E25" s="87"/>
+      <c r="F25" s="87"/>
+      <c r="G25" s="87"/>
+      <c r="H25" s="87"/>
+      <c r="I25" s="87"/>
+      <c r="J25" s="87"/>
+      <c r="K25" s="87"/>
       <c r="L25" s="60"/>
       <c r="M25" s="1"/>
-      <c r="O25" s="141">
+      <c r="O25" s="88">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)-1,1)</f>
         <v>46235</v>
       </c>
-      <c r="P25" s="141"/>
-      <c r="Q25" s="141"/>
-      <c r="R25" s="141"/>
-      <c r="S25" s="141"/>
-      <c r="T25" s="141"/>
-      <c r="U25" s="141"/>
+      <c r="P25" s="88"/>
+      <c r="Q25" s="88"/>
+      <c r="R25" s="88"/>
+      <c r="S25" s="88"/>
+      <c r="T25" s="88"/>
+      <c r="U25" s="88"/>
       <c r="V25" s="61"/>
       <c r="W25" s="61"/>
-      <c r="X25" s="141">
+      <c r="X25" s="88">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)+1,1)</f>
         <v>46296</v>
       </c>
-      <c r="Y25" s="141"/>
-      <c r="Z25" s="141"/>
-      <c r="AA25" s="141"/>
-      <c r="AB25" s="141"/>
-      <c r="AC25" s="141"/>
-      <c r="AD25" s="141"/>
+      <c r="Y25" s="88"/>
+      <c r="Z25" s="88"/>
+      <c r="AA25" s="88"/>
+      <c r="AB25" s="88"/>
+      <c r="AC25" s="88"/>
+      <c r="AD25" s="88"/>
       <c r="AF25" s="1"/>
     </row>
     <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
-      <c r="C26" s="140"/>
-      <c r="D26" s="140"/>
-      <c r="E26" s="140"/>
-      <c r="F26" s="140"/>
-      <c r="G26" s="140"/>
-      <c r="H26" s="140"/>
-      <c r="I26" s="140"/>
-      <c r="J26" s="140"/>
-      <c r="K26" s="140"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="87"/>
+      <c r="E26" s="87"/>
+      <c r="F26" s="87"/>
+      <c r="G26" s="87"/>
+      <c r="H26" s="87"/>
+      <c r="I26" s="87"/>
+      <c r="J26" s="87"/>
+      <c r="K26" s="87"/>
       <c r="L26" s="60"/>
       <c r="M26" s="1"/>
       <c r="O26" s="62" t="str">
@@ -3149,17 +3160,17 @@
     </row>
     <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
-      <c r="C27" s="116" t="s">
+      <c r="C27" s="89" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="116"/>
-      <c r="E27" s="116"/>
-      <c r="F27" s="116"/>
-      <c r="G27" s="116"/>
-      <c r="H27" s="116"/>
-      <c r="I27" s="116"/>
-      <c r="J27" s="116"/>
-      <c r="K27" s="116"/>
+      <c r="D27" s="89"/>
+      <c r="E27" s="89"/>
+      <c r="F27" s="89"/>
+      <c r="G27" s="89"/>
+      <c r="H27" s="89"/>
+      <c r="I27" s="89"/>
+      <c r="J27" s="89"/>
+      <c r="K27" s="89"/>
       <c r="M27" s="1"/>
       <c r="O27" s="64" t="str">
         <f t="shared" ref="O27:U32" ca="1" si="0">IF(MONTH($O$25)&lt;&gt;MONTH($O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1)),"",$O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1))</f>
@@ -3223,17 +3234,17 @@
     </row>
     <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
-      <c r="C28" s="115" t="s">
+      <c r="C28" s="90" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="115"/>
-      <c r="E28" s="115"/>
-      <c r="F28" s="115"/>
-      <c r="G28" s="115"/>
-      <c r="H28" s="115"/>
-      <c r="I28" s="115"/>
-      <c r="J28" s="115"/>
-      <c r="K28" s="115"/>
+      <c r="D28" s="90"/>
+      <c r="E28" s="90"/>
+      <c r="F28" s="90"/>
+      <c r="G28" s="90"/>
+      <c r="H28" s="90"/>
+      <c r="I28" s="90"/>
+      <c r="J28" s="90"/>
+      <c r="K28" s="90"/>
       <c r="M28" s="1"/>
       <c r="O28" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3297,15 +3308,15 @@
     </row>
     <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
-      <c r="C29" s="116"/>
-      <c r="D29" s="116"/>
-      <c r="E29" s="116"/>
-      <c r="F29" s="116"/>
-      <c r="G29" s="116"/>
-      <c r="H29" s="116"/>
-      <c r="I29" s="116"/>
-      <c r="J29" s="116"/>
-      <c r="K29" s="116"/>
+      <c r="C29" s="89"/>
+      <c r="D29" s="89"/>
+      <c r="E29" s="89"/>
+      <c r="F29" s="89"/>
+      <c r="G29" s="89"/>
+      <c r="H29" s="89"/>
+      <c r="I29" s="89"/>
+      <c r="J29" s="89"/>
+      <c r="K29" s="89"/>
       <c r="M29" s="1"/>
       <c r="O29" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3369,17 +3380,17 @@
     </row>
     <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
-      <c r="C30" s="115" t="s">
+      <c r="C30" s="90" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="115"/>
-      <c r="E30" s="115"/>
-      <c r="F30" s="115"/>
-      <c r="G30" s="115"/>
-      <c r="H30" s="115"/>
-      <c r="I30" s="115"/>
-      <c r="J30" s="115"/>
-      <c r="K30" s="115"/>
+      <c r="D30" s="90"/>
+      <c r="E30" s="90"/>
+      <c r="F30" s="90"/>
+      <c r="G30" s="90"/>
+      <c r="H30" s="90"/>
+      <c r="I30" s="90"/>
+      <c r="J30" s="90"/>
+      <c r="K30" s="90"/>
       <c r="M30" s="1"/>
       <c r="O30" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3443,15 +3454,15 @@
     </row>
     <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
-      <c r="C31" s="116"/>
-      <c r="D31" s="116"/>
-      <c r="E31" s="116"/>
-      <c r="F31" s="116"/>
-      <c r="G31" s="116"/>
-      <c r="H31" s="116"/>
-      <c r="I31" s="116"/>
-      <c r="J31" s="116"/>
-      <c r="K31" s="116"/>
+      <c r="C31" s="89"/>
+      <c r="D31" s="89"/>
+      <c r="E31" s="89"/>
+      <c r="F31" s="89"/>
+      <c r="G31" s="89"/>
+      <c r="H31" s="89"/>
+      <c r="I31" s="89"/>
+      <c r="J31" s="89"/>
+      <c r="K31" s="89"/>
       <c r="M31" s="1"/>
       <c r="O31" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3633,67 +3644,156 @@
     </row>
     <row r="38" spans="1:32" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D39" s="84" t="s">
+      <c r="D39" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="E39" s="85"/>
-      <c r="F39" s="86"/>
-      <c r="G39" s="90">
+      <c r="E39" s="117"/>
+      <c r="F39" s="118"/>
+      <c r="G39" s="122">
         <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
         <v>4</v>
       </c>
-      <c r="H39" s="91"/>
-      <c r="I39" s="84" t="s">
+      <c r="H39" s="123"/>
+      <c r="I39" s="116" t="s">
         <v>26</v>
       </c>
-      <c r="J39" s="98"/>
-      <c r="K39" s="94" t="s">
+      <c r="J39" s="130"/>
+      <c r="K39" s="126" t="s">
         <v>24</v>
       </c>
-      <c r="L39" s="95"/>
-      <c r="M39" s="106">
+      <c r="L39" s="127"/>
+      <c r="M39" s="138">
         <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
         <v>5.0000000000000009</v>
       </c>
-      <c r="N39" s="107"/>
-      <c r="O39" s="107"/>
-      <c r="P39" s="107"/>
-      <c r="Q39" s="107"/>
-      <c r="R39" s="108"/>
-      <c r="S39" s="100" t="s">
+      <c r="N39" s="139"/>
+      <c r="O39" s="139"/>
+      <c r="P39" s="139"/>
+      <c r="Q39" s="139"/>
+      <c r="R39" s="140"/>
+      <c r="S39" s="132" t="s">
         <v>25</v>
       </c>
-      <c r="T39" s="101"/>
-      <c r="U39" s="101"/>
-      <c r="V39" s="101"/>
-      <c r="W39" s="101"/>
-      <c r="X39" s="102"/>
+      <c r="T39" s="133"/>
+      <c r="U39" s="133"/>
+      <c r="V39" s="133"/>
+      <c r="W39" s="133"/>
+      <c r="X39" s="134"/>
     </row>
     <row r="40" spans="1:32" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="87"/>
-      <c r="E40" s="88"/>
-      <c r="F40" s="89"/>
-      <c r="G40" s="92"/>
-      <c r="H40" s="93"/>
-      <c r="I40" s="87"/>
-      <c r="J40" s="99"/>
-      <c r="K40" s="96"/>
-      <c r="L40" s="97"/>
-      <c r="M40" s="109"/>
-      <c r="N40" s="110"/>
-      <c r="O40" s="110"/>
-      <c r="P40" s="110"/>
-      <c r="Q40" s="110"/>
-      <c r="R40" s="111"/>
-      <c r="S40" s="103"/>
-      <c r="T40" s="104"/>
-      <c r="U40" s="104"/>
-      <c r="V40" s="104"/>
-      <c r="W40" s="104"/>
-      <c r="X40" s="105"/>
+      <c r="D40" s="119"/>
+      <c r="E40" s="120"/>
+      <c r="F40" s="121"/>
+      <c r="G40" s="124"/>
+      <c r="H40" s="125"/>
+      <c r="I40" s="119"/>
+      <c r="J40" s="131"/>
+      <c r="K40" s="128"/>
+      <c r="L40" s="129"/>
+      <c r="M40" s="141"/>
+      <c r="N40" s="142"/>
+      <c r="O40" s="142"/>
+      <c r="P40" s="142"/>
+      <c r="Q40" s="142"/>
+      <c r="R40" s="143"/>
+      <c r="S40" s="135"/>
+      <c r="T40" s="136"/>
+      <c r="U40" s="136"/>
+      <c r="V40" s="136"/>
+      <c r="W40" s="136"/>
+      <c r="X40" s="137"/>
     </row>
   </sheetData>
   <mergeCells count="110">
+    <mergeCell ref="D39:F40"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="K39:L40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="S39:X40"/>
+    <mergeCell ref="M39:R40"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="O20:V20"/>
+    <mergeCell ref="C30:K31"/>
+    <mergeCell ref="C2:AD2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="W5:AD5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:V6"/>
+    <mergeCell ref="W6:AD6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="O5:V5"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="W7:AD7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="O8:V8"/>
+    <mergeCell ref="W8:AD8"/>
+    <mergeCell ref="O7:V7"/>
+    <mergeCell ref="W9:AD9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="O11:V11"/>
+    <mergeCell ref="W11:AD11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:V9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="W12:AD12"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O14:V14"/>
+    <mergeCell ref="W14:AD14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="O12:V12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="W15:AD15"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="O17:V17"/>
+    <mergeCell ref="W17:AD17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="O15:V15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="O16:V16"/>
     <mergeCell ref="W18:AD18"/>
     <mergeCell ref="C25:K26"/>
     <mergeCell ref="O25:U25"/>
@@ -3715,95 +3815,6 @@
     <mergeCell ref="O21:V21"/>
     <mergeCell ref="W21:AD21"/>
     <mergeCell ref="O19:V19"/>
-    <mergeCell ref="W15:AD15"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="O17:V17"/>
-    <mergeCell ref="W17:AD17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="O15:V15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="O16:V16"/>
-    <mergeCell ref="W12:AD12"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="O14:V14"/>
-    <mergeCell ref="W14:AD14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="O12:V12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="W9:AD9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="O11:V11"/>
-    <mergeCell ref="W11:AD11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:V9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="W7:AD7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="O8:V8"/>
-    <mergeCell ref="W8:AD8"/>
-    <mergeCell ref="O7:V7"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:V6"/>
-    <mergeCell ref="W6:AD6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="O5:V5"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="C2:AD2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="W5:AD5"/>
-    <mergeCell ref="D39:F40"/>
-    <mergeCell ref="G39:H40"/>
-    <mergeCell ref="K39:L40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="S39:X40"/>
-    <mergeCell ref="M39:R40"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="O20:V20"/>
-    <mergeCell ref="C30:K31"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 E5 G5 I5 K5:L5 O5 W5 C7 E8 G8 I8 K8:L8 O8 W8 C10 E11 G11 I11 K11:L11 O11 W11 C13 E14 G14 I14 K14:L14 O14 W14 C16 E17 G17 I17 K17:L17 O17 W17">
     <cfRule type="expression" dxfId="11" priority="3">
@@ -3894,42 +3905,42 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A2" s="29"/>
-      <c r="C2" s="117">
+      <c r="C2" s="114">
         <f ca="1">DATE(About!P8,10,1)</f>
         <v>46296</v>
       </c>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="117"/>
-      <c r="H2" s="117"/>
-      <c r="I2" s="117"/>
-      <c r="J2" s="117"/>
-      <c r="K2" s="117"/>
-      <c r="L2" s="117"/>
-      <c r="M2" s="117"/>
-      <c r="N2" s="117"/>
-      <c r="O2" s="117"/>
-      <c r="P2" s="117"/>
-      <c r="Q2" s="117"/>
-      <c r="R2" s="117"/>
-      <c r="S2" s="117"/>
-      <c r="T2" s="117"/>
-      <c r="U2" s="117"/>
-      <c r="V2" s="117"/>
-      <c r="W2" s="117"/>
-      <c r="X2" s="117"/>
-      <c r="Y2" s="117"/>
-      <c r="Z2" s="117"/>
-      <c r="AA2" s="117"/>
-      <c r="AB2" s="117"/>
-      <c r="AC2" s="117"/>
-      <c r="AD2" s="117"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="114"/>
+      <c r="O2" s="114"/>
+      <c r="P2" s="114"/>
+      <c r="Q2" s="114"/>
+      <c r="R2" s="114"/>
+      <c r="S2" s="114"/>
+      <c r="T2" s="114"/>
+      <c r="U2" s="114"/>
+      <c r="V2" s="114"/>
+      <c r="W2" s="114"/>
+      <c r="X2" s="114"/>
+      <c r="Y2" s="114"/>
+      <c r="Z2" s="114"/>
+      <c r="AA2" s="114"/>
+      <c r="AB2" s="114"/>
+      <c r="AC2" s="114"/>
+      <c r="AD2" s="114"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -3949,114 +3960,114 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="35"/>
-      <c r="C4" s="118">
+      <c r="C4" s="115">
         <f ca="1">C5</f>
         <v>46292</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118">
+      <c r="D4" s="115"/>
+      <c r="E4" s="115">
         <f ca="1">E5</f>
         <v>46293</v>
       </c>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118">
+      <c r="F4" s="115"/>
+      <c r="G4" s="115">
         <f ca="1">G5</f>
         <v>46294</v>
       </c>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118">
+      <c r="H4" s="115"/>
+      <c r="I4" s="115">
         <f ca="1">I5</f>
         <v>46295</v>
       </c>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118">
+      <c r="J4" s="115"/>
+      <c r="K4" s="115">
         <f ca="1">K5</f>
         <v>46296</v>
       </c>
-      <c r="L4" s="118"/>
-      <c r="M4" s="118"/>
+      <c r="L4" s="115"/>
+      <c r="M4" s="115"/>
       <c r="N4" s="37"/>
-      <c r="O4" s="118">
+      <c r="O4" s="115">
         <f ca="1">O5</f>
         <v>46297</v>
       </c>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="118"/>
-      <c r="S4" s="118"/>
-      <c r="T4" s="118"/>
-      <c r="U4" s="118"/>
-      <c r="V4" s="118"/>
-      <c r="W4" s="118">
+      <c r="P4" s="115"/>
+      <c r="Q4" s="115"/>
+      <c r="R4" s="115"/>
+      <c r="S4" s="115"/>
+      <c r="T4" s="115"/>
+      <c r="U4" s="115"/>
+      <c r="V4" s="115"/>
+      <c r="W4" s="115">
         <f ca="1">W5</f>
         <v>46298</v>
       </c>
-      <c r="X4" s="118"/>
-      <c r="Y4" s="118"/>
-      <c r="Z4" s="118"/>
-      <c r="AA4" s="118"/>
-      <c r="AB4" s="118"/>
-      <c r="AC4" s="118"/>
-      <c r="AD4" s="118"/>
+      <c r="X4" s="115"/>
+      <c r="Y4" s="115"/>
+      <c r="Z4" s="115"/>
+      <c r="AA4" s="115"/>
+      <c r="AB4" s="115"/>
+      <c r="AC4" s="115"/>
+      <c r="AD4" s="115"/>
       <c r="AF4" s="38"/>
       <c r="AG4" s="39"/>
       <c r="AH4" s="39"/>
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="C5" s="119">
+      <c r="C5" s="95">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46292</v>
       </c>
-      <c r="D5" s="121"/>
-      <c r="E5" s="119">
+      <c r="D5" s="96"/>
+      <c r="E5" s="95">
         <f ca="1">C5+1</f>
         <v>46293</v>
       </c>
-      <c r="F5" s="121"/>
-      <c r="G5" s="119">
+      <c r="F5" s="96"/>
+      <c r="G5" s="95">
         <f ca="1">E5+1</f>
         <v>46294</v>
       </c>
-      <c r="H5" s="121"/>
-      <c r="I5" s="119">
+      <c r="H5" s="96"/>
+      <c r="I5" s="95">
         <f ca="1">G5+1</f>
         <v>46295</v>
       </c>
-      <c r="J5" s="121"/>
-      <c r="K5" s="119">
+      <c r="J5" s="96"/>
+      <c r="K5" s="95">
         <f ca="1">I5+1</f>
         <v>46296</v>
       </c>
-      <c r="L5" s="120"/>
-      <c r="M5" s="120"/>
+      <c r="L5" s="113"/>
+      <c r="M5" s="113"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="119">
+      <c r="O5" s="95">
         <f ca="1">K5+1</f>
         <v>46297</v>
       </c>
-      <c r="P5" s="120"/>
-      <c r="Q5" s="120"/>
-      <c r="R5" s="120"/>
-      <c r="S5" s="120"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="121"/>
-      <c r="W5" s="119">
+      <c r="P5" s="113"/>
+      <c r="Q5" s="113"/>
+      <c r="R5" s="113"/>
+      <c r="S5" s="113"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="113"/>
+      <c r="V5" s="96"/>
+      <c r="W5" s="95">
         <f ca="1">O5+1</f>
         <v>46298</v>
       </c>
-      <c r="X5" s="120"/>
-      <c r="Y5" s="120"/>
-      <c r="Z5" s="120"/>
-      <c r="AA5" s="120"/>
-      <c r="AB5" s="120"/>
-      <c r="AC5" s="120"/>
-      <c r="AD5" s="121"/>
+      <c r="X5" s="113"/>
+      <c r="Y5" s="113"/>
+      <c r="Z5" s="113"/>
+      <c r="AA5" s="113"/>
+      <c r="AB5" s="113"/>
+      <c r="AC5" s="113"/>
+      <c r="AD5" s="96"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
@@ -4065,174 +4076,174 @@
     </row>
     <row r="6" spans="1:36" s="43" customFormat="1" ht="131.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="42"/>
-      <c r="C6" s="144"/>
-      <c r="D6" s="145"/>
-      <c r="E6" s="144"/>
-      <c r="F6" s="145"/>
-      <c r="G6" s="144"/>
-      <c r="H6" s="145"/>
-      <c r="I6" s="144"/>
-      <c r="J6" s="145"/>
-      <c r="K6" s="133"/>
-      <c r="L6" s="134"/>
-      <c r="M6" s="134"/>
-      <c r="N6" s="135"/>
-      <c r="O6" s="133"/>
-      <c r="P6" s="134"/>
-      <c r="Q6" s="134"/>
-      <c r="R6" s="134"/>
-      <c r="S6" s="134"/>
-      <c r="T6" s="134"/>
-      <c r="U6" s="134"/>
-      <c r="V6" s="135"/>
-      <c r="W6" s="142" t="s">
+      <c r="C6" s="153"/>
+      <c r="D6" s="154"/>
+      <c r="E6" s="153"/>
+      <c r="F6" s="154"/>
+      <c r="G6" s="153"/>
+      <c r="H6" s="154"/>
+      <c r="I6" s="153"/>
+      <c r="J6" s="154"/>
+      <c r="K6" s="93"/>
+      <c r="L6" s="103"/>
+      <c r="M6" s="103"/>
+      <c r="N6" s="94"/>
+      <c r="O6" s="93"/>
+      <c r="P6" s="103"/>
+      <c r="Q6" s="103"/>
+      <c r="R6" s="103"/>
+      <c r="S6" s="103"/>
+      <c r="T6" s="103"/>
+      <c r="U6" s="103"/>
+      <c r="V6" s="94"/>
+      <c r="W6" s="91" t="s">
         <v>19</v>
       </c>
-      <c r="X6" s="146"/>
-      <c r="Y6" s="146"/>
-      <c r="Z6" s="146"/>
-      <c r="AA6" s="146"/>
-      <c r="AB6" s="146"/>
-      <c r="AC6" s="146"/>
-      <c r="AD6" s="143"/>
+      <c r="X6" s="155"/>
+      <c r="Y6" s="155"/>
+      <c r="Z6" s="155"/>
+      <c r="AA6" s="155"/>
+      <c r="AB6" s="155"/>
+      <c r="AC6" s="155"/>
+      <c r="AD6" s="92"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
     <row r="7" spans="1:36" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="C7" s="119">
+      <c r="C7" s="95">
         <f ca="1">W5+1</f>
         <v>46299</v>
       </c>
-      <c r="D7" s="121"/>
-      <c r="E7" s="127"/>
-      <c r="F7" s="128"/>
-      <c r="G7" s="127"/>
-      <c r="H7" s="128"/>
-      <c r="I7" s="127"/>
-      <c r="J7" s="128"/>
-      <c r="K7" s="127"/>
-      <c r="L7" s="129"/>
-      <c r="M7" s="129"/>
+      <c r="D7" s="96"/>
+      <c r="E7" s="110"/>
+      <c r="F7" s="111"/>
+      <c r="G7" s="110"/>
+      <c r="H7" s="111"/>
+      <c r="I7" s="110"/>
+      <c r="J7" s="111"/>
+      <c r="K7" s="110"/>
+      <c r="L7" s="112"/>
+      <c r="M7" s="112"/>
       <c r="N7" s="75"/>
-      <c r="O7" s="127"/>
-      <c r="P7" s="129"/>
-      <c r="Q7" s="129"/>
-      <c r="R7" s="129"/>
-      <c r="S7" s="129"/>
-      <c r="T7" s="129"/>
-      <c r="U7" s="129"/>
-      <c r="V7" s="128"/>
-      <c r="W7" s="127"/>
-      <c r="X7" s="129"/>
-      <c r="Y7" s="129"/>
-      <c r="Z7" s="129"/>
-      <c r="AA7" s="129"/>
-      <c r="AB7" s="129"/>
-      <c r="AC7" s="129"/>
-      <c r="AD7" s="128"/>
+      <c r="O7" s="110"/>
+      <c r="P7" s="112"/>
+      <c r="Q7" s="112"/>
+      <c r="R7" s="112"/>
+      <c r="S7" s="112"/>
+      <c r="T7" s="112"/>
+      <c r="U7" s="112"/>
+      <c r="V7" s="111"/>
+      <c r="W7" s="110"/>
+      <c r="X7" s="112"/>
+      <c r="Y7" s="112"/>
+      <c r="Z7" s="112"/>
+      <c r="AA7" s="112"/>
+      <c r="AB7" s="112"/>
+      <c r="AC7" s="112"/>
+      <c r="AD7" s="111"/>
       <c r="AF7" s="1"/>
     </row>
     <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
-      <c r="C8" s="119"/>
-      <c r="D8" s="121"/>
-      <c r="E8" s="112">
+      <c r="C8" s="95"/>
+      <c r="D8" s="96"/>
+      <c r="E8" s="99">
         <f ca="1">C7+1</f>
         <v>46300</v>
       </c>
-      <c r="F8" s="113"/>
-      <c r="G8" s="112">
+      <c r="F8" s="101"/>
+      <c r="G8" s="99">
         <f ca="1">E8+1</f>
         <v>46301</v>
       </c>
-      <c r="H8" s="113"/>
-      <c r="I8" s="112">
+      <c r="H8" s="101"/>
+      <c r="I8" s="99">
         <f ca="1">G8+1</f>
         <v>46302</v>
       </c>
-      <c r="J8" s="113"/>
-      <c r="K8" s="112">
+      <c r="J8" s="101"/>
+      <c r="K8" s="99">
         <f ca="1">I8+1</f>
         <v>46303</v>
       </c>
-      <c r="L8" s="114"/>
-      <c r="M8" s="114"/>
+      <c r="L8" s="100"/>
+      <c r="M8" s="100"/>
       <c r="N8" s="50"/>
-      <c r="O8" s="112">
+      <c r="O8" s="99">
         <f ca="1">K8+1</f>
         <v>46304</v>
       </c>
-      <c r="P8" s="114"/>
-      <c r="Q8" s="114"/>
-      <c r="R8" s="114"/>
-      <c r="S8" s="114"/>
-      <c r="T8" s="114"/>
-      <c r="U8" s="114"/>
-      <c r="V8" s="113"/>
-      <c r="W8" s="112">
+      <c r="P8" s="100"/>
+      <c r="Q8" s="100"/>
+      <c r="R8" s="100"/>
+      <c r="S8" s="100"/>
+      <c r="T8" s="100"/>
+      <c r="U8" s="100"/>
+      <c r="V8" s="101"/>
+      <c r="W8" s="99">
         <f ca="1">O8+1</f>
         <v>46305</v>
       </c>
-      <c r="X8" s="114"/>
-      <c r="Y8" s="114"/>
-      <c r="Z8" s="114"/>
-      <c r="AA8" s="114"/>
-      <c r="AB8" s="114"/>
-      <c r="AC8" s="114"/>
-      <c r="AD8" s="113"/>
+      <c r="X8" s="100"/>
+      <c r="Y8" s="100"/>
+      <c r="Z8" s="100"/>
+      <c r="AA8" s="100"/>
+      <c r="AB8" s="100"/>
+      <c r="AC8" s="100"/>
+      <c r="AD8" s="101"/>
       <c r="AF8" s="4"/>
     </row>
     <row r="9" spans="1:36" s="43" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="42"/>
-      <c r="C9" s="147"/>
-      <c r="D9" s="149"/>
-      <c r="E9" s="147" t="s">
+      <c r="C9" s="144"/>
+      <c r="D9" s="146"/>
+      <c r="E9" s="144" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="149"/>
-      <c r="G9" s="147" t="s">
+      <c r="F9" s="146"/>
+      <c r="G9" s="144" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="149"/>
-      <c r="I9" s="147" t="s">
+      <c r="H9" s="146"/>
+      <c r="I9" s="144" t="s">
         <v>36</v>
       </c>
-      <c r="J9" s="149"/>
-      <c r="K9" s="147" t="s">
-        <v>61</v>
-      </c>
-      <c r="L9" s="148"/>
-      <c r="M9" s="148"/>
-      <c r="N9" s="149"/>
-      <c r="O9" s="147" t="s">
-        <v>47</v>
-      </c>
-      <c r="P9" s="148"/>
-      <c r="Q9" s="148"/>
-      <c r="R9" s="148"/>
-      <c r="S9" s="148"/>
-      <c r="T9" s="148"/>
-      <c r="U9" s="148"/>
-      <c r="V9" s="149"/>
-      <c r="W9" s="147"/>
-      <c r="X9" s="148"/>
-      <c r="Y9" s="148"/>
-      <c r="Z9" s="148"/>
-      <c r="AA9" s="148"/>
-      <c r="AB9" s="148"/>
-      <c r="AC9" s="148"/>
-      <c r="AD9" s="149"/>
+      <c r="J9" s="146"/>
+      <c r="K9" s="144" t="s">
+        <v>60</v>
+      </c>
+      <c r="L9" s="145"/>
+      <c r="M9" s="145"/>
+      <c r="N9" s="146"/>
+      <c r="O9" s="144" t="s">
+        <v>46</v>
+      </c>
+      <c r="P9" s="145"/>
+      <c r="Q9" s="145"/>
+      <c r="R9" s="145"/>
+      <c r="S9" s="145"/>
+      <c r="T9" s="145"/>
+      <c r="U9" s="145"/>
+      <c r="V9" s="146"/>
+      <c r="W9" s="144"/>
+      <c r="X9" s="145"/>
+      <c r="Y9" s="145"/>
+      <c r="Z9" s="145"/>
+      <c r="AA9" s="145"/>
+      <c r="AB9" s="145"/>
+      <c r="AC9" s="145"/>
+      <c r="AD9" s="146"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
     <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="42"/>
-      <c r="C10" s="119">
+      <c r="C10" s="95">
         <f ca="1">W8+1</f>
         <v>46306</v>
       </c>
-      <c r="D10" s="121"/>
+      <c r="D10" s="96"/>
       <c r="E10" s="45"/>
       <c r="F10" s="75"/>
       <c r="G10" s="45"/>
@@ -4264,109 +4275,109 @@
     </row>
     <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
-      <c r="C11" s="119"/>
-      <c r="D11" s="121"/>
-      <c r="E11" s="112">
+      <c r="C11" s="95"/>
+      <c r="D11" s="96"/>
+      <c r="E11" s="99">
         <f ca="1">C10+1</f>
         <v>46307</v>
       </c>
-      <c r="F11" s="113"/>
-      <c r="G11" s="112">
+      <c r="F11" s="101"/>
+      <c r="G11" s="99">
         <f ca="1">E11+1</f>
         <v>46308</v>
       </c>
-      <c r="H11" s="113"/>
-      <c r="I11" s="112">
+      <c r="H11" s="101"/>
+      <c r="I11" s="99">
         <f ca="1">G11+1</f>
         <v>46309</v>
       </c>
-      <c r="J11" s="113"/>
-      <c r="K11" s="112">
+      <c r="J11" s="101"/>
+      <c r="K11" s="99">
         <f ca="1">I11+1</f>
         <v>46310</v>
       </c>
-      <c r="L11" s="114"/>
-      <c r="M11" s="114"/>
+      <c r="L11" s="100"/>
+      <c r="M11" s="100"/>
       <c r="N11" s="50"/>
-      <c r="O11" s="112">
+      <c r="O11" s="99">
         <f ca="1">K11+1</f>
         <v>46311</v>
       </c>
-      <c r="P11" s="114"/>
-      <c r="Q11" s="114"/>
-      <c r="R11" s="114"/>
-      <c r="S11" s="114"/>
-      <c r="T11" s="114"/>
-      <c r="U11" s="114"/>
-      <c r="V11" s="113"/>
-      <c r="W11" s="112">
+      <c r="P11" s="100"/>
+      <c r="Q11" s="100"/>
+      <c r="R11" s="100"/>
+      <c r="S11" s="100"/>
+      <c r="T11" s="100"/>
+      <c r="U11" s="100"/>
+      <c r="V11" s="101"/>
+      <c r="W11" s="99">
         <f ca="1">O11+1</f>
         <v>46312</v>
       </c>
-      <c r="X11" s="114"/>
-      <c r="Y11" s="114"/>
-      <c r="Z11" s="114"/>
-      <c r="AA11" s="114"/>
-      <c r="AB11" s="114"/>
-      <c r="AC11" s="114"/>
-      <c r="AD11" s="113"/>
+      <c r="X11" s="100"/>
+      <c r="Y11" s="100"/>
+      <c r="Z11" s="100"/>
+      <c r="AA11" s="100"/>
+      <c r="AB11" s="100"/>
+      <c r="AC11" s="100"/>
+      <c r="AD11" s="101"/>
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
     <row r="12" spans="1:36" s="43" customFormat="1" ht="134.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="42"/>
-      <c r="C12" s="151" t="s">
-        <v>46</v>
-      </c>
-      <c r="D12" s="152"/>
-      <c r="E12" s="153" t="s">
+      <c r="C12" s="147" t="s">
+        <v>45</v>
+      </c>
+      <c r="D12" s="148"/>
+      <c r="E12" s="152" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="146"/>
+      <c r="G12" s="144" t="s">
+        <v>61</v>
+      </c>
+      <c r="H12" s="146"/>
+      <c r="I12" s="147" t="s">
+        <v>57</v>
+      </c>
+      <c r="J12" s="148"/>
+      <c r="K12" s="152" t="s">
         <v>38</v>
       </c>
-      <c r="F12" s="149"/>
-      <c r="G12" s="147" t="s">
-        <v>37</v>
-      </c>
-      <c r="H12" s="149"/>
-      <c r="I12" s="151" t="s">
-        <v>58</v>
-      </c>
-      <c r="J12" s="152"/>
-      <c r="K12" s="153" t="s">
-        <v>39</v>
-      </c>
-      <c r="L12" s="148"/>
-      <c r="M12" s="148"/>
-      <c r="N12" s="149"/>
-      <c r="O12" s="147" t="s">
-        <v>57</v>
-      </c>
-      <c r="P12" s="148"/>
-      <c r="Q12" s="148"/>
-      <c r="R12" s="148"/>
-      <c r="S12" s="148"/>
-      <c r="T12" s="148"/>
-      <c r="U12" s="148"/>
-      <c r="V12" s="149"/>
-      <c r="W12" s="150" t="s">
+      <c r="L12" s="145"/>
+      <c r="M12" s="145"/>
+      <c r="N12" s="146"/>
+      <c r="O12" s="144" t="s">
+        <v>56</v>
+      </c>
+      <c r="P12" s="145"/>
+      <c r="Q12" s="145"/>
+      <c r="R12" s="145"/>
+      <c r="S12" s="145"/>
+      <c r="T12" s="145"/>
+      <c r="U12" s="145"/>
+      <c r="V12" s="146"/>
+      <c r="W12" s="151" t="s">
         <v>29</v>
       </c>
-      <c r="X12" s="148"/>
-      <c r="Y12" s="148"/>
-      <c r="Z12" s="148"/>
-      <c r="AA12" s="148"/>
-      <c r="AB12" s="148"/>
-      <c r="AC12" s="148"/>
-      <c r="AD12" s="149"/>
+      <c r="X12" s="145"/>
+      <c r="Y12" s="145"/>
+      <c r="Z12" s="145"/>
+      <c r="AA12" s="145"/>
+      <c r="AB12" s="145"/>
+      <c r="AC12" s="145"/>
+      <c r="AD12" s="146"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
     <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="42"/>
-      <c r="C13" s="119">
+      <c r="C13" s="95">
         <f ca="1">W11+1</f>
         <v>46313</v>
       </c>
-      <c r="D13" s="121"/>
+      <c r="D13" s="96"/>
       <c r="E13" s="45"/>
       <c r="F13" s="75"/>
       <c r="G13" s="45"/>
@@ -4398,108 +4409,108 @@
     </row>
     <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4"/>
-      <c r="C14" s="119"/>
-      <c r="D14" s="121"/>
-      <c r="E14" s="112">
+      <c r="C14" s="95"/>
+      <c r="D14" s="96"/>
+      <c r="E14" s="99">
         <f ca="1">C13+1</f>
         <v>46314</v>
       </c>
-      <c r="F14" s="113"/>
-      <c r="G14" s="112">
+      <c r="F14" s="101"/>
+      <c r="G14" s="99">
         <f ca="1">E14+1</f>
         <v>46315</v>
       </c>
-      <c r="H14" s="113"/>
-      <c r="I14" s="112">
+      <c r="H14" s="101"/>
+      <c r="I14" s="99">
         <f ca="1">G14+1</f>
         <v>46316</v>
       </c>
-      <c r="J14" s="113"/>
-      <c r="K14" s="112">
+      <c r="J14" s="101"/>
+      <c r="K14" s="99">
         <f ca="1">I14+1</f>
         <v>46317</v>
       </c>
-      <c r="L14" s="114"/>
-      <c r="M14" s="114"/>
+      <c r="L14" s="100"/>
+      <c r="M14" s="100"/>
       <c r="N14" s="50"/>
-      <c r="O14" s="112">
+      <c r="O14" s="99">
         <f ca="1">K14+1</f>
         <v>46318</v>
       </c>
-      <c r="P14" s="114"/>
-      <c r="Q14" s="114"/>
-      <c r="R14" s="114"/>
-      <c r="S14" s="114"/>
-      <c r="T14" s="114"/>
-      <c r="U14" s="114"/>
-      <c r="V14" s="113"/>
-      <c r="W14" s="112">
+      <c r="P14" s="100"/>
+      <c r="Q14" s="100"/>
+      <c r="R14" s="100"/>
+      <c r="S14" s="100"/>
+      <c r="T14" s="100"/>
+      <c r="U14" s="100"/>
+      <c r="V14" s="101"/>
+      <c r="W14" s="99">
         <f ca="1">O14+1</f>
         <v>46319</v>
       </c>
-      <c r="X14" s="114"/>
-      <c r="Y14" s="114"/>
-      <c r="Z14" s="114"/>
-      <c r="AA14" s="114"/>
-      <c r="AB14" s="114"/>
-      <c r="AC14" s="114"/>
-      <c r="AD14" s="113"/>
+      <c r="X14" s="100"/>
+      <c r="Y14" s="100"/>
+      <c r="Z14" s="100"/>
+      <c r="AA14" s="100"/>
+      <c r="AB14" s="100"/>
+      <c r="AC14" s="100"/>
+      <c r="AD14" s="101"/>
       <c r="AF14" s="4"/>
     </row>
     <row r="15" spans="1:36" s="43" customFormat="1" ht="140.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="42"/>
-      <c r="C15" s="150" t="s">
+      <c r="C15" s="151" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="149"/>
-      <c r="E15" s="151" t="s">
+      <c r="D15" s="146"/>
+      <c r="E15" s="147" t="s">
+        <v>48</v>
+      </c>
+      <c r="F15" s="148"/>
+      <c r="G15" s="147" t="s">
         <v>49</v>
       </c>
-      <c r="F15" s="152"/>
-      <c r="G15" s="151" t="s">
-        <v>50</v>
-      </c>
-      <c r="H15" s="152"/>
-      <c r="I15" s="150" t="s">
+      <c r="H15" s="148"/>
+      <c r="I15" s="151" t="s">
         <v>33</v>
       </c>
-      <c r="J15" s="149"/>
-      <c r="K15" s="151" t="s">
-        <v>59</v>
-      </c>
-      <c r="L15" s="154"/>
-      <c r="M15" s="154"/>
-      <c r="N15" s="152"/>
-      <c r="O15" s="147" t="s">
+      <c r="J15" s="146"/>
+      <c r="K15" s="147" t="s">
+        <v>58</v>
+      </c>
+      <c r="L15" s="150"/>
+      <c r="M15" s="150"/>
+      <c r="N15" s="148"/>
+      <c r="O15" s="144" t="s">
         <v>31</v>
       </c>
-      <c r="P15" s="148"/>
-      <c r="Q15" s="148"/>
-      <c r="R15" s="148"/>
-      <c r="S15" s="148"/>
-      <c r="T15" s="148"/>
-      <c r="U15" s="148"/>
-      <c r="V15" s="149"/>
-      <c r="W15" s="150" t="s">
+      <c r="P15" s="145"/>
+      <c r="Q15" s="145"/>
+      <c r="R15" s="145"/>
+      <c r="S15" s="145"/>
+      <c r="T15" s="145"/>
+      <c r="U15" s="145"/>
+      <c r="V15" s="146"/>
+      <c r="W15" s="151" t="s">
         <v>32</v>
       </c>
-      <c r="X15" s="148"/>
-      <c r="Y15" s="148"/>
-      <c r="Z15" s="148"/>
-      <c r="AA15" s="148"/>
-      <c r="AB15" s="148"/>
-      <c r="AC15" s="148"/>
-      <c r="AD15" s="149"/>
+      <c r="X15" s="145"/>
+      <c r="Y15" s="145"/>
+      <c r="Z15" s="145"/>
+      <c r="AA15" s="145"/>
+      <c r="AB15" s="145"/>
+      <c r="AC15" s="145"/>
+      <c r="AD15" s="146"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
     <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="42"/>
-      <c r="C16" s="119">
+      <c r="C16" s="95">
         <f ca="1">W14+1</f>
         <v>46320</v>
       </c>
-      <c r="D16" s="121"/>
+      <c r="D16" s="96"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
@@ -4531,107 +4542,107 @@
     </row>
     <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
-      <c r="C17" s="119"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="112">
+      <c r="C17" s="95"/>
+      <c r="D17" s="96"/>
+      <c r="E17" s="99">
         <f ca="1">C16+1</f>
         <v>46321</v>
       </c>
-      <c r="F17" s="113"/>
-      <c r="G17" s="112">
+      <c r="F17" s="101"/>
+      <c r="G17" s="99">
         <f ca="1">E17+1</f>
         <v>46322</v>
       </c>
-      <c r="H17" s="113"/>
-      <c r="I17" s="112">
+      <c r="H17" s="101"/>
+      <c r="I17" s="99">
         <f ca="1">G17+1</f>
         <v>46323</v>
       </c>
-      <c r="J17" s="113"/>
-      <c r="K17" s="112">
+      <c r="J17" s="101"/>
+      <c r="K17" s="99">
         <f ca="1">I17+1</f>
         <v>46324</v>
       </c>
-      <c r="L17" s="114"/>
-      <c r="M17" s="114"/>
+      <c r="L17" s="100"/>
+      <c r="M17" s="100"/>
       <c r="N17" s="50"/>
-      <c r="O17" s="112">
+      <c r="O17" s="99">
         <f ca="1">K17+1</f>
         <v>46325</v>
       </c>
-      <c r="P17" s="114"/>
-      <c r="Q17" s="114"/>
-      <c r="R17" s="114"/>
-      <c r="S17" s="114"/>
-      <c r="T17" s="114"/>
-      <c r="U17" s="114"/>
-      <c r="V17" s="113"/>
-      <c r="W17" s="112">
+      <c r="P17" s="100"/>
+      <c r="Q17" s="100"/>
+      <c r="R17" s="100"/>
+      <c r="S17" s="100"/>
+      <c r="T17" s="100"/>
+      <c r="U17" s="100"/>
+      <c r="V17" s="101"/>
+      <c r="W17" s="99">
         <f ca="1">O17+1</f>
         <v>46326</v>
       </c>
-      <c r="X17" s="114"/>
-      <c r="Y17" s="114"/>
-      <c r="Z17" s="114"/>
-      <c r="AA17" s="114"/>
-      <c r="AB17" s="114"/>
-      <c r="AC17" s="114"/>
-      <c r="AD17" s="113"/>
+      <c r="X17" s="100"/>
+      <c r="Y17" s="100"/>
+      <c r="Z17" s="100"/>
+      <c r="AA17" s="100"/>
+      <c r="AB17" s="100"/>
+      <c r="AC17" s="100"/>
+      <c r="AD17" s="101"/>
       <c r="AF17" s="4"/>
     </row>
     <row r="18" spans="1:42" s="43" customFormat="1" ht="149.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="42"/>
-      <c r="C18" s="151" t="s">
-        <v>60</v>
-      </c>
-      <c r="D18" s="152"/>
-      <c r="E18" s="147" t="s">
+      <c r="C18" s="147" t="s">
+        <v>59</v>
+      </c>
+      <c r="D18" s="148"/>
+      <c r="E18" s="144" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="146"/>
+      <c r="G18" s="147" t="s">
         <v>44</v>
       </c>
-      <c r="F18" s="149"/>
-      <c r="G18" s="151" t="s">
-        <v>45</v>
-      </c>
-      <c r="H18" s="152"/>
-      <c r="I18" s="151" t="s">
+      <c r="H18" s="148"/>
+      <c r="I18" s="147" t="s">
+        <v>50</v>
+      </c>
+      <c r="J18" s="148"/>
+      <c r="K18" s="149" t="s">
+        <v>34</v>
+      </c>
+      <c r="L18" s="145"/>
+      <c r="M18" s="145"/>
+      <c r="N18" s="82"/>
+      <c r="O18" s="147" t="s">
         <v>51</v>
       </c>
-      <c r="J18" s="152"/>
-      <c r="K18" s="155" t="s">
-        <v>34</v>
-      </c>
-      <c r="L18" s="148"/>
-      <c r="M18" s="148"/>
-      <c r="N18" s="82"/>
-      <c r="O18" s="151" t="s">
-        <v>52</v>
-      </c>
-      <c r="P18" s="154"/>
-      <c r="Q18" s="154"/>
-      <c r="R18" s="154"/>
-      <c r="S18" s="154"/>
-      <c r="T18" s="154"/>
-      <c r="U18" s="154"/>
-      <c r="V18" s="152"/>
-      <c r="W18" s="147"/>
-      <c r="X18" s="148"/>
-      <c r="Y18" s="148"/>
-      <c r="Z18" s="148"/>
-      <c r="AA18" s="148"/>
-      <c r="AB18" s="148"/>
-      <c r="AC18" s="148"/>
-      <c r="AD18" s="149"/>
+      <c r="P18" s="150"/>
+      <c r="Q18" s="150"/>
+      <c r="R18" s="150"/>
+      <c r="S18" s="150"/>
+      <c r="T18" s="150"/>
+      <c r="U18" s="150"/>
+      <c r="V18" s="148"/>
+      <c r="W18" s="144"/>
+      <c r="X18" s="145"/>
+      <c r="Y18" s="145"/>
+      <c r="Z18" s="145"/>
+      <c r="AA18" s="145"/>
+      <c r="AB18" s="145"/>
+      <c r="AC18" s="145"/>
+      <c r="AD18" s="146"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
     <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="42"/>
-      <c r="C19" s="119">
+      <c r="C19" s="95">
         <f ca="1">W17+1</f>
         <v>46327</v>
       </c>
-      <c r="D19" s="121"/>
+      <c r="D19" s="96"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
@@ -4663,84 +4674,84 @@
     </row>
     <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
-      <c r="C20" s="119"/>
-      <c r="D20" s="121"/>
-      <c r="E20" s="112">
+      <c r="C20" s="95"/>
+      <c r="D20" s="96"/>
+      <c r="E20" s="99">
         <f ca="1">C19+1</f>
         <v>46328</v>
       </c>
-      <c r="F20" s="113"/>
-      <c r="G20" s="112">
+      <c r="F20" s="101"/>
+      <c r="G20" s="99">
         <f ca="1">E20+1</f>
         <v>46329</v>
       </c>
-      <c r="H20" s="113"/>
-      <c r="I20" s="112">
+      <c r="H20" s="101"/>
+      <c r="I20" s="99">
         <f ca="1">G20+1</f>
         <v>46330</v>
       </c>
-      <c r="J20" s="113"/>
-      <c r="K20" s="112">
+      <c r="J20" s="101"/>
+      <c r="K20" s="99">
         <f ca="1">I20+1</f>
         <v>46331</v>
       </c>
-      <c r="L20" s="114"/>
-      <c r="M20" s="114"/>
+      <c r="L20" s="100"/>
+      <c r="M20" s="100"/>
       <c r="N20" s="50"/>
-      <c r="O20" s="112">
+      <c r="O20" s="99">
         <f ca="1">K20+1</f>
         <v>46332</v>
       </c>
-      <c r="P20" s="114"/>
-      <c r="Q20" s="114"/>
-      <c r="R20" s="114"/>
-      <c r="S20" s="114"/>
-      <c r="T20" s="114"/>
-      <c r="U20" s="114"/>
-      <c r="V20" s="113"/>
-      <c r="W20" s="112">
+      <c r="P20" s="100"/>
+      <c r="Q20" s="100"/>
+      <c r="R20" s="100"/>
+      <c r="S20" s="100"/>
+      <c r="T20" s="100"/>
+      <c r="U20" s="100"/>
+      <c r="V20" s="101"/>
+      <c r="W20" s="99">
         <f ca="1">O20+1</f>
         <v>46333</v>
       </c>
-      <c r="X20" s="114"/>
-      <c r="Y20" s="114"/>
-      <c r="Z20" s="114"/>
-      <c r="AA20" s="114"/>
-      <c r="AB20" s="114"/>
-      <c r="AC20" s="114"/>
-      <c r="AD20" s="113"/>
+      <c r="X20" s="100"/>
+      <c r="Y20" s="100"/>
+      <c r="Z20" s="100"/>
+      <c r="AA20" s="100"/>
+      <c r="AB20" s="100"/>
+      <c r="AC20" s="100"/>
+      <c r="AD20" s="101"/>
       <c r="AF20" s="4"/>
     </row>
     <row r="21" spans="1:42" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="42"/>
-      <c r="C21" s="122"/>
-      <c r="D21" s="123"/>
-      <c r="E21" s="122"/>
-      <c r="F21" s="123"/>
-      <c r="G21" s="122"/>
-      <c r="H21" s="123"/>
-      <c r="I21" s="122"/>
-      <c r="J21" s="123"/>
-      <c r="K21" s="122"/>
-      <c r="L21" s="139"/>
-      <c r="M21" s="139"/>
+      <c r="C21" s="84"/>
+      <c r="D21" s="86"/>
+      <c r="E21" s="84"/>
+      <c r="F21" s="86"/>
+      <c r="G21" s="84"/>
+      <c r="H21" s="86"/>
+      <c r="I21" s="84"/>
+      <c r="J21" s="86"/>
+      <c r="K21" s="84"/>
+      <c r="L21" s="85"/>
+      <c r="M21" s="85"/>
       <c r="N21" s="44"/>
-      <c r="O21" s="122"/>
-      <c r="P21" s="139"/>
-      <c r="Q21" s="139"/>
-      <c r="R21" s="139"/>
-      <c r="S21" s="139"/>
-      <c r="T21" s="139"/>
-      <c r="U21" s="139"/>
-      <c r="V21" s="123"/>
-      <c r="W21" s="122"/>
-      <c r="X21" s="139"/>
-      <c r="Y21" s="139"/>
-      <c r="Z21" s="139"/>
-      <c r="AA21" s="139"/>
-      <c r="AB21" s="139"/>
-      <c r="AC21" s="139"/>
-      <c r="AD21" s="123"/>
+      <c r="O21" s="84"/>
+      <c r="P21" s="85"/>
+      <c r="Q21" s="85"/>
+      <c r="R21" s="85"/>
+      <c r="S21" s="85"/>
+      <c r="T21" s="85"/>
+      <c r="U21" s="85"/>
+      <c r="V21" s="86"/>
+      <c r="W21" s="84"/>
+      <c r="X21" s="85"/>
+      <c r="Y21" s="85"/>
+      <c r="Z21" s="85"/>
+      <c r="AA21" s="85"/>
+      <c r="AB21" s="85"/>
+      <c r="AC21" s="85"/>
+      <c r="AD21" s="86"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
@@ -4818,54 +4829,54 @@
     </row>
     <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
-      <c r="C25" s="140" t="s">
+      <c r="C25" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="140"/>
-      <c r="E25" s="140"/>
-      <c r="F25" s="140"/>
-      <c r="G25" s="140"/>
-      <c r="H25" s="140"/>
-      <c r="I25" s="140"/>
-      <c r="J25" s="140"/>
-      <c r="K25" s="140"/>
+      <c r="D25" s="87"/>
+      <c r="E25" s="87"/>
+      <c r="F25" s="87"/>
+      <c r="G25" s="87"/>
+      <c r="H25" s="87"/>
+      <c r="I25" s="87"/>
+      <c r="J25" s="87"/>
+      <c r="K25" s="87"/>
       <c r="L25" s="60"/>
       <c r="M25" s="1"/>
-      <c r="O25" s="141">
+      <c r="O25" s="88">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)-1,1)</f>
         <v>46266</v>
       </c>
-      <c r="P25" s="141"/>
-      <c r="Q25" s="141"/>
-      <c r="R25" s="141"/>
-      <c r="S25" s="141"/>
-      <c r="T25" s="141"/>
-      <c r="U25" s="141"/>
+      <c r="P25" s="88"/>
+      <c r="Q25" s="88"/>
+      <c r="R25" s="88"/>
+      <c r="S25" s="88"/>
+      <c r="T25" s="88"/>
+      <c r="U25" s="88"/>
       <c r="V25" s="61"/>
       <c r="W25" s="61"/>
-      <c r="X25" s="141">
+      <c r="X25" s="88">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)+1,1)</f>
         <v>46327</v>
       </c>
-      <c r="Y25" s="141"/>
-      <c r="Z25" s="141"/>
-      <c r="AA25" s="141"/>
-      <c r="AB25" s="141"/>
-      <c r="AC25" s="141"/>
-      <c r="AD25" s="141"/>
+      <c r="Y25" s="88"/>
+      <c r="Z25" s="88"/>
+      <c r="AA25" s="88"/>
+      <c r="AB25" s="88"/>
+      <c r="AC25" s="88"/>
+      <c r="AD25" s="88"/>
       <c r="AF25" s="1"/>
     </row>
     <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
-      <c r="C26" s="140"/>
-      <c r="D26" s="140"/>
-      <c r="E26" s="140"/>
-      <c r="F26" s="140"/>
-      <c r="G26" s="140"/>
-      <c r="H26" s="140"/>
-      <c r="I26" s="140"/>
-      <c r="J26" s="140"/>
-      <c r="K26" s="140"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="87"/>
+      <c r="E26" s="87"/>
+      <c r="F26" s="87"/>
+      <c r="G26" s="87"/>
+      <c r="H26" s="87"/>
+      <c r="I26" s="87"/>
+      <c r="J26" s="87"/>
+      <c r="K26" s="87"/>
       <c r="L26" s="60"/>
       <c r="M26" s="1"/>
       <c r="O26" s="62" t="str">
@@ -4930,15 +4941,15 @@
     </row>
     <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
-      <c r="C27" s="116"/>
-      <c r="D27" s="116"/>
-      <c r="E27" s="116"/>
-      <c r="F27" s="116"/>
-      <c r="G27" s="116"/>
-      <c r="H27" s="116"/>
-      <c r="I27" s="116"/>
-      <c r="J27" s="116"/>
-      <c r="K27" s="116"/>
+      <c r="C27" s="89"/>
+      <c r="D27" s="89"/>
+      <c r="E27" s="89"/>
+      <c r="F27" s="89"/>
+      <c r="G27" s="89"/>
+      <c r="H27" s="89"/>
+      <c r="I27" s="89"/>
+      <c r="J27" s="89"/>
+      <c r="K27" s="89"/>
       <c r="M27" s="1"/>
       <c r="O27" s="64" t="str">
         <f t="shared" ref="O27:U32" ca="1" si="0">IF(MONTH($O$25)&lt;&gt;MONTH($O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1)),"",$O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1))</f>
@@ -5002,15 +5013,15 @@
     </row>
     <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
-      <c r="C28" s="115"/>
-      <c r="D28" s="115"/>
-      <c r="E28" s="115"/>
-      <c r="F28" s="115"/>
-      <c r="G28" s="115"/>
-      <c r="H28" s="115"/>
-      <c r="I28" s="115"/>
-      <c r="J28" s="115"/>
-      <c r="K28" s="115"/>
+      <c r="C28" s="90"/>
+      <c r="D28" s="90"/>
+      <c r="E28" s="90"/>
+      <c r="F28" s="90"/>
+      <c r="G28" s="90"/>
+      <c r="H28" s="90"/>
+      <c r="I28" s="90"/>
+      <c r="J28" s="90"/>
+      <c r="K28" s="90"/>
       <c r="M28" s="1"/>
       <c r="O28" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -5074,15 +5085,15 @@
     </row>
     <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
-      <c r="C29" s="116"/>
-      <c r="D29" s="116"/>
-      <c r="E29" s="116"/>
-      <c r="F29" s="116"/>
-      <c r="G29" s="116"/>
-      <c r="H29" s="116"/>
-      <c r="I29" s="116"/>
-      <c r="J29" s="116"/>
-      <c r="K29" s="116"/>
+      <c r="C29" s="89"/>
+      <c r="D29" s="89"/>
+      <c r="E29" s="89"/>
+      <c r="F29" s="89"/>
+      <c r="G29" s="89"/>
+      <c r="H29" s="89"/>
+      <c r="I29" s="89"/>
+      <c r="J29" s="89"/>
+      <c r="K29" s="89"/>
       <c r="M29" s="1"/>
       <c r="O29" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -5146,15 +5157,15 @@
     </row>
     <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
-      <c r="C30" s="115"/>
-      <c r="D30" s="115"/>
-      <c r="E30" s="115"/>
-      <c r="F30" s="115"/>
-      <c r="G30" s="115"/>
-      <c r="H30" s="115"/>
-      <c r="I30" s="115"/>
-      <c r="J30" s="115"/>
-      <c r="K30" s="115"/>
+      <c r="C30" s="90"/>
+      <c r="D30" s="90"/>
+      <c r="E30" s="90"/>
+      <c r="F30" s="90"/>
+      <c r="G30" s="90"/>
+      <c r="H30" s="90"/>
+      <c r="I30" s="90"/>
+      <c r="J30" s="90"/>
+      <c r="K30" s="90"/>
       <c r="M30" s="1"/>
       <c r="O30" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -5218,15 +5229,15 @@
     </row>
     <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
-      <c r="C31" s="116"/>
-      <c r="D31" s="116"/>
-      <c r="E31" s="116"/>
-      <c r="F31" s="116"/>
-      <c r="G31" s="116"/>
-      <c r="H31" s="116"/>
-      <c r="I31" s="116"/>
-      <c r="J31" s="116"/>
-      <c r="K31" s="116"/>
+      <c r="C31" s="89"/>
+      <c r="D31" s="89"/>
+      <c r="E31" s="89"/>
+      <c r="F31" s="89"/>
+      <c r="G31" s="89"/>
+      <c r="H31" s="89"/>
+      <c r="I31" s="89"/>
+      <c r="J31" s="89"/>
+      <c r="K31" s="89"/>
       <c r="M31" s="1"/>
       <c r="O31" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -5408,67 +5419,154 @@
     </row>
     <row r="38" spans="1:32" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D39" s="84" t="s">
+      <c r="D39" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="E39" s="85"/>
-      <c r="F39" s="86"/>
-      <c r="G39" s="90">
+      <c r="E39" s="117"/>
+      <c r="F39" s="118"/>
+      <c r="G39" s="122">
         <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
         <v>4</v>
       </c>
-      <c r="H39" s="91"/>
-      <c r="I39" s="84" t="s">
+      <c r="H39" s="123"/>
+      <c r="I39" s="116" t="s">
         <v>26</v>
       </c>
-      <c r="J39" s="98"/>
-      <c r="K39" s="94" t="s">
+      <c r="J39" s="130"/>
+      <c r="K39" s="126" t="s">
         <v>24</v>
       </c>
-      <c r="L39" s="95"/>
-      <c r="M39" s="106">
+      <c r="L39" s="127"/>
+      <c r="M39" s="138">
         <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
         <v>5.0000000000000009</v>
       </c>
-      <c r="N39" s="107"/>
-      <c r="O39" s="107"/>
-      <c r="P39" s="107"/>
-      <c r="Q39" s="107"/>
-      <c r="R39" s="108"/>
-      <c r="S39" s="100" t="s">
+      <c r="N39" s="139"/>
+      <c r="O39" s="139"/>
+      <c r="P39" s="139"/>
+      <c r="Q39" s="139"/>
+      <c r="R39" s="140"/>
+      <c r="S39" s="132" t="s">
         <v>25</v>
       </c>
-      <c r="T39" s="101"/>
-      <c r="U39" s="101"/>
-      <c r="V39" s="101"/>
-      <c r="W39" s="101"/>
-      <c r="X39" s="102"/>
+      <c r="T39" s="133"/>
+      <c r="U39" s="133"/>
+      <c r="V39" s="133"/>
+      <c r="W39" s="133"/>
+      <c r="X39" s="134"/>
     </row>
     <row r="40" spans="1:32" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D40" s="87"/>
-      <c r="E40" s="88"/>
-      <c r="F40" s="89"/>
-      <c r="G40" s="92"/>
-      <c r="H40" s="93"/>
-      <c r="I40" s="87"/>
-      <c r="J40" s="99"/>
-      <c r="K40" s="96"/>
-      <c r="L40" s="97"/>
-      <c r="M40" s="109"/>
-      <c r="N40" s="110"/>
-      <c r="O40" s="110"/>
-      <c r="P40" s="110"/>
-      <c r="Q40" s="110"/>
-      <c r="R40" s="111"/>
-      <c r="S40" s="103"/>
-      <c r="T40" s="104"/>
-      <c r="U40" s="104"/>
-      <c r="V40" s="104"/>
-      <c r="W40" s="104"/>
-      <c r="X40" s="105"/>
+      <c r="D40" s="119"/>
+      <c r="E40" s="120"/>
+      <c r="F40" s="121"/>
+      <c r="G40" s="124"/>
+      <c r="H40" s="125"/>
+      <c r="I40" s="119"/>
+      <c r="J40" s="131"/>
+      <c r="K40" s="128"/>
+      <c r="L40" s="129"/>
+      <c r="M40" s="141"/>
+      <c r="N40" s="142"/>
+      <c r="O40" s="142"/>
+      <c r="P40" s="142"/>
+      <c r="Q40" s="142"/>
+      <c r="R40" s="143"/>
+      <c r="S40" s="135"/>
+      <c r="T40" s="136"/>
+      <c r="U40" s="136"/>
+      <c r="V40" s="136"/>
+      <c r="W40" s="136"/>
+      <c r="X40" s="137"/>
     </row>
   </sheetData>
   <mergeCells count="110">
+    <mergeCell ref="D39:F40"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="K39:L40"/>
+    <mergeCell ref="M39:R40"/>
+    <mergeCell ref="S39:X40"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="O21:V21"/>
+    <mergeCell ref="W21:AD21"/>
+    <mergeCell ref="C30:K31"/>
+    <mergeCell ref="C2:AD2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="W5:AD5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:V6"/>
+    <mergeCell ref="W6:AD6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="O5:V5"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="W7:AD7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="O8:V8"/>
+    <mergeCell ref="W8:AD8"/>
+    <mergeCell ref="O7:V7"/>
+    <mergeCell ref="W9:AD9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="O11:V11"/>
+    <mergeCell ref="W11:AD11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:V9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="W12:AD12"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O14:V14"/>
+    <mergeCell ref="W14:AD14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="O12:V12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="W15:AD15"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="O17:V17"/>
+    <mergeCell ref="W17:AD17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="O15:V15"/>
+    <mergeCell ref="K15:N15"/>
     <mergeCell ref="W18:AD18"/>
     <mergeCell ref="C25:K26"/>
     <mergeCell ref="O25:U25"/>
@@ -5492,93 +5590,6 @@
     <mergeCell ref="E21:F21"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="I21:J21"/>
-    <mergeCell ref="W15:AD15"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="O17:V17"/>
-    <mergeCell ref="W17:AD17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="O15:V15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="W12:AD12"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="O14:V14"/>
-    <mergeCell ref="W14:AD14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="O12:V12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="W9:AD9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="O11:V11"/>
-    <mergeCell ref="W11:AD11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:V9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="W7:AD7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="O8:V8"/>
-    <mergeCell ref="W8:AD8"/>
-    <mergeCell ref="O7:V7"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:V6"/>
-    <mergeCell ref="W6:AD6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="O5:V5"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="C2:AD2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="W5:AD5"/>
-    <mergeCell ref="D39:F40"/>
-    <mergeCell ref="G39:H40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="K39:L40"/>
-    <mergeCell ref="M39:R40"/>
-    <mergeCell ref="S39:X40"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="O21:V21"/>
-    <mergeCell ref="W21:AD21"/>
-    <mergeCell ref="C30:K31"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 E5 G5 I5 K5:L5 O5 W5 C7 E8 G8 I8 K8:L8 O8 W8 C10 E11 G11 I11 K11:L11 O11 W11 C13 E14 G14 I14 K14:L14 O14 W14 C16 E17 G17 I17 K17:L17 O17 W17">
     <cfRule type="expression" dxfId="7" priority="3">
@@ -5669,42 +5680,42 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A2" s="29"/>
-      <c r="C2" s="117">
+      <c r="C2" s="114">
         <f ca="1">DATE(About!P8,11,1)</f>
         <v>46327</v>
       </c>
-      <c r="D2" s="117"/>
-      <c r="E2" s="117"/>
-      <c r="F2" s="117"/>
-      <c r="G2" s="117"/>
-      <c r="H2" s="117"/>
-      <c r="I2" s="117"/>
-      <c r="J2" s="117"/>
-      <c r="K2" s="117"/>
-      <c r="L2" s="117"/>
-      <c r="M2" s="117"/>
-      <c r="N2" s="117"/>
-      <c r="O2" s="117"/>
-      <c r="P2" s="117"/>
-      <c r="Q2" s="117"/>
-      <c r="R2" s="117"/>
-      <c r="S2" s="117"/>
-      <c r="T2" s="117"/>
-      <c r="U2" s="117"/>
-      <c r="V2" s="117"/>
-      <c r="W2" s="117"/>
-      <c r="X2" s="117"/>
-      <c r="Y2" s="117"/>
-      <c r="Z2" s="117"/>
-      <c r="AA2" s="117"/>
-      <c r="AB2" s="117"/>
-      <c r="AC2" s="117"/>
-      <c r="AD2" s="117"/>
+      <c r="D2" s="114"/>
+      <c r="E2" s="114"/>
+      <c r="F2" s="114"/>
+      <c r="G2" s="114"/>
+      <c r="H2" s="114"/>
+      <c r="I2" s="114"/>
+      <c r="J2" s="114"/>
+      <c r="K2" s="114"/>
+      <c r="L2" s="114"/>
+      <c r="M2" s="114"/>
+      <c r="N2" s="114"/>
+      <c r="O2" s="114"/>
+      <c r="P2" s="114"/>
+      <c r="Q2" s="114"/>
+      <c r="R2" s="114"/>
+      <c r="S2" s="114"/>
+      <c r="T2" s="114"/>
+      <c r="U2" s="114"/>
+      <c r="V2" s="114"/>
+      <c r="W2" s="114"/>
+      <c r="X2" s="114"/>
+      <c r="Y2" s="114"/>
+      <c r="Z2" s="114"/>
+      <c r="AA2" s="114"/>
+      <c r="AB2" s="114"/>
+      <c r="AC2" s="114"/>
+      <c r="AD2" s="114"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.8">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -5724,114 +5735,114 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="35"/>
-      <c r="C4" s="118">
+      <c r="C4" s="115">
         <f ca="1">C5</f>
         <v>46327</v>
       </c>
-      <c r="D4" s="118"/>
-      <c r="E4" s="118">
+      <c r="D4" s="115"/>
+      <c r="E4" s="115">
         <f ca="1">E5</f>
         <v>46328</v>
       </c>
-      <c r="F4" s="118"/>
-      <c r="G4" s="118">
+      <c r="F4" s="115"/>
+      <c r="G4" s="115">
         <f ca="1">G5</f>
         <v>46329</v>
       </c>
-      <c r="H4" s="118"/>
-      <c r="I4" s="118">
+      <c r="H4" s="115"/>
+      <c r="I4" s="115">
         <f ca="1">I5</f>
         <v>46330</v>
       </c>
-      <c r="J4" s="118"/>
-      <c r="K4" s="118">
+      <c r="J4" s="115"/>
+      <c r="K4" s="115">
         <f ca="1">K5</f>
         <v>46331</v>
       </c>
-      <c r="L4" s="118"/>
-      <c r="M4" s="118"/>
+      <c r="L4" s="115"/>
+      <c r="M4" s="115"/>
       <c r="N4" s="37"/>
-      <c r="O4" s="118">
+      <c r="O4" s="115">
         <f ca="1">O5</f>
         <v>46332</v>
       </c>
-      <c r="P4" s="118"/>
-      <c r="Q4" s="118"/>
-      <c r="R4" s="118"/>
-      <c r="S4" s="118"/>
-      <c r="T4" s="118"/>
-      <c r="U4" s="118"/>
-      <c r="V4" s="118"/>
-      <c r="W4" s="118">
+      <c r="P4" s="115"/>
+      <c r="Q4" s="115"/>
+      <c r="R4" s="115"/>
+      <c r="S4" s="115"/>
+      <c r="T4" s="115"/>
+      <c r="U4" s="115"/>
+      <c r="V4" s="115"/>
+      <c r="W4" s="115">
         <f ca="1">W5</f>
         <v>46333</v>
       </c>
-      <c r="X4" s="118"/>
-      <c r="Y4" s="118"/>
-      <c r="Z4" s="118"/>
-      <c r="AA4" s="118"/>
-      <c r="AB4" s="118"/>
-      <c r="AC4" s="118"/>
-      <c r="AD4" s="118"/>
+      <c r="X4" s="115"/>
+      <c r="Y4" s="115"/>
+      <c r="Z4" s="115"/>
+      <c r="AA4" s="115"/>
+      <c r="AB4" s="115"/>
+      <c r="AC4" s="115"/>
+      <c r="AD4" s="115"/>
       <c r="AF4" s="38"/>
       <c r="AG4" s="39"/>
       <c r="AH4" s="39"/>
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="C5" s="119">
+      <c r="C5" s="95">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46327</v>
       </c>
-      <c r="D5" s="121"/>
-      <c r="E5" s="119">
+      <c r="D5" s="96"/>
+      <c r="E5" s="95">
         <f ca="1">C5+1</f>
         <v>46328</v>
       </c>
-      <c r="F5" s="121"/>
-      <c r="G5" s="119">
+      <c r="F5" s="96"/>
+      <c r="G5" s="95">
         <f ca="1">E5+1</f>
         <v>46329</v>
       </c>
-      <c r="H5" s="121"/>
-      <c r="I5" s="119">
+      <c r="H5" s="96"/>
+      <c r="I5" s="95">
         <f ca="1">G5+1</f>
         <v>46330</v>
       </c>
-      <c r="J5" s="121"/>
-      <c r="K5" s="119">
+      <c r="J5" s="96"/>
+      <c r="K5" s="95">
         <f ca="1">I5+1</f>
         <v>46331</v>
       </c>
-      <c r="L5" s="120"/>
-      <c r="M5" s="120"/>
+      <c r="L5" s="113"/>
+      <c r="M5" s="113"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="119">
+      <c r="O5" s="95">
         <f ca="1">K5+1</f>
         <v>46332</v>
       </c>
-      <c r="P5" s="120"/>
-      <c r="Q5" s="120"/>
-      <c r="R5" s="120"/>
-      <c r="S5" s="120"/>
-      <c r="T5" s="120"/>
-      <c r="U5" s="120"/>
-      <c r="V5" s="121"/>
-      <c r="W5" s="119">
+      <c r="P5" s="113"/>
+      <c r="Q5" s="113"/>
+      <c r="R5" s="113"/>
+      <c r="S5" s="113"/>
+      <c r="T5" s="113"/>
+      <c r="U5" s="113"/>
+      <c r="V5" s="96"/>
+      <c r="W5" s="95">
         <f ca="1">O5+1</f>
         <v>46333</v>
       </c>
-      <c r="X5" s="120"/>
-      <c r="Y5" s="120"/>
-      <c r="Z5" s="120"/>
-      <c r="AA5" s="120"/>
-      <c r="AB5" s="120"/>
-      <c r="AC5" s="120"/>
-      <c r="AD5" s="121"/>
+      <c r="X5" s="113"/>
+      <c r="Y5" s="113"/>
+      <c r="Z5" s="113"/>
+      <c r="AA5" s="113"/>
+      <c r="AB5" s="113"/>
+      <c r="AC5" s="113"/>
+      <c r="AD5" s="96"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
@@ -5840,42 +5851,42 @@
     </row>
     <row r="6" spans="1:36" s="43" customFormat="1" ht="133.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="42"/>
-      <c r="C6" s="147"/>
-      <c r="D6" s="149"/>
-      <c r="E6" s="155" t="s">
+      <c r="C6" s="144"/>
+      <c r="D6" s="146"/>
+      <c r="E6" s="149" t="s">
         <v>35</v>
       </c>
-      <c r="F6" s="149"/>
-      <c r="G6" s="147"/>
-      <c r="H6" s="149"/>
-      <c r="I6" s="156" t="s">
+      <c r="F6" s="146"/>
+      <c r="G6" s="144"/>
+      <c r="H6" s="146"/>
+      <c r="I6" s="162" t="s">
+        <v>52</v>
+      </c>
+      <c r="J6" s="146"/>
+      <c r="K6" s="162" t="s">
         <v>53</v>
       </c>
-      <c r="J6" s="149"/>
-      <c r="K6" s="156" t="s">
-        <v>54</v>
-      </c>
-      <c r="L6" s="148"/>
-      <c r="M6" s="148"/>
-      <c r="N6" s="149"/>
-      <c r="O6" s="155" t="s">
-        <v>56</v>
-      </c>
-      <c r="P6" s="148"/>
-      <c r="Q6" s="148"/>
-      <c r="R6" s="148"/>
-      <c r="S6" s="148"/>
-      <c r="T6" s="148"/>
-      <c r="U6" s="148"/>
-      <c r="V6" s="149"/>
-      <c r="W6" s="147"/>
-      <c r="X6" s="148"/>
-      <c r="Y6" s="148"/>
-      <c r="Z6" s="148"/>
-      <c r="AA6" s="148"/>
-      <c r="AB6" s="148"/>
-      <c r="AC6" s="148"/>
-      <c r="AD6" s="149"/>
+      <c r="L6" s="145"/>
+      <c r="M6" s="145"/>
+      <c r="N6" s="146"/>
+      <c r="O6" s="149" t="s">
+        <v>55</v>
+      </c>
+      <c r="P6" s="145"/>
+      <c r="Q6" s="145"/>
+      <c r="R6" s="145"/>
+      <c r="S6" s="145"/>
+      <c r="T6" s="145"/>
+      <c r="U6" s="145"/>
+      <c r="V6" s="146"/>
+      <c r="W6" s="144"/>
+      <c r="X6" s="145"/>
+      <c r="Y6" s="145"/>
+      <c r="Z6" s="145"/>
+      <c r="AA6" s="145"/>
+      <c r="AB6" s="145"/>
+      <c r="AC6" s="145"/>
+      <c r="AD6" s="146"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
@@ -5886,32 +5897,32 @@
         <v>46334</v>
       </c>
       <c r="D7" s="158"/>
-      <c r="E7" s="159"/>
-      <c r="F7" s="160"/>
-      <c r="G7" s="159"/>
-      <c r="H7" s="160"/>
-      <c r="I7" s="159"/>
-      <c r="J7" s="160"/>
-      <c r="K7" s="159"/>
-      <c r="L7" s="161"/>
-      <c r="M7" s="161"/>
+      <c r="E7" s="163"/>
+      <c r="F7" s="164"/>
+      <c r="G7" s="163"/>
+      <c r="H7" s="164"/>
+      <c r="I7" s="163"/>
+      <c r="J7" s="164"/>
+      <c r="K7" s="163"/>
+      <c r="L7" s="165"/>
+      <c r="M7" s="165"/>
       <c r="N7" s="80"/>
-      <c r="O7" s="159"/>
-      <c r="P7" s="161"/>
-      <c r="Q7" s="161"/>
-      <c r="R7" s="161"/>
-      <c r="S7" s="161"/>
-      <c r="T7" s="161"/>
-      <c r="U7" s="161"/>
-      <c r="V7" s="160"/>
-      <c r="W7" s="159"/>
-      <c r="X7" s="161"/>
-      <c r="Y7" s="161"/>
-      <c r="Z7" s="161"/>
-      <c r="AA7" s="161"/>
-      <c r="AB7" s="161"/>
-      <c r="AC7" s="161"/>
-      <c r="AD7" s="160"/>
+      <c r="O7" s="163"/>
+      <c r="P7" s="165"/>
+      <c r="Q7" s="165"/>
+      <c r="R7" s="165"/>
+      <c r="S7" s="165"/>
+      <c r="T7" s="165"/>
+      <c r="U7" s="165"/>
+      <c r="V7" s="164"/>
+      <c r="W7" s="163"/>
+      <c r="X7" s="165"/>
+      <c r="Y7" s="165"/>
+      <c r="Z7" s="165"/>
+      <c r="AA7" s="165"/>
+      <c r="AB7" s="165"/>
+      <c r="AC7" s="165"/>
+      <c r="AD7" s="164"/>
       <c r="AF7" s="1"/>
     </row>
     <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
@@ -5937,73 +5948,73 @@
         <f ca="1">I8+1</f>
         <v>46338</v>
       </c>
-      <c r="L8" s="162"/>
-      <c r="M8" s="162"/>
+      <c r="L8" s="159"/>
+      <c r="M8" s="159"/>
       <c r="N8" s="78"/>
       <c r="O8" s="157">
         <f ca="1">K8+1</f>
         <v>46339</v>
       </c>
-      <c r="P8" s="162"/>
-      <c r="Q8" s="162"/>
-      <c r="R8" s="162"/>
-      <c r="S8" s="162"/>
-      <c r="T8" s="162"/>
-      <c r="U8" s="162"/>
+      <c r="P8" s="159"/>
+      <c r="Q8" s="159"/>
+      <c r="R8" s="159"/>
+      <c r="S8" s="159"/>
+      <c r="T8" s="159"/>
+      <c r="U8" s="159"/>
       <c r="V8" s="158"/>
       <c r="W8" s="157">
         <f ca="1">O8+1</f>
         <v>46340</v>
       </c>
-      <c r="X8" s="162"/>
-      <c r="Y8" s="162"/>
-      <c r="Z8" s="162"/>
-      <c r="AA8" s="162"/>
-      <c r="AB8" s="162"/>
-      <c r="AC8" s="162"/>
+      <c r="X8" s="159"/>
+      <c r="Y8" s="159"/>
+      <c r="Z8" s="159"/>
+      <c r="AA8" s="159"/>
+      <c r="AB8" s="159"/>
+      <c r="AC8" s="159"/>
       <c r="AD8" s="158"/>
       <c r="AF8" s="4"/>
     </row>
     <row r="9" spans="1:36" s="43" customFormat="1" ht="146.44999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="42"/>
-      <c r="C9" s="147"/>
-      <c r="D9" s="149"/>
-      <c r="E9" s="155" t="s">
+      <c r="C9" s="144"/>
+      <c r="D9" s="146"/>
+      <c r="E9" s="149" t="s">
+        <v>41</v>
+      </c>
+      <c r="F9" s="146"/>
+      <c r="G9" s="162" t="s">
+        <v>54</v>
+      </c>
+      <c r="H9" s="146"/>
+      <c r="I9" s="144" t="s">
         <v>42</v>
       </c>
-      <c r="F9" s="149"/>
-      <c r="G9" s="156" t="s">
-        <v>55</v>
-      </c>
-      <c r="H9" s="149"/>
-      <c r="I9" s="147" t="s">
-        <v>43</v>
-      </c>
-      <c r="J9" s="149"/>
-      <c r="K9" s="147" t="s">
-        <v>48</v>
-      </c>
-      <c r="L9" s="148"/>
-      <c r="M9" s="148"/>
-      <c r="N9" s="149"/>
-      <c r="O9" s="164" t="s">
+      <c r="J9" s="146"/>
+      <c r="K9" s="144" t="s">
+        <v>47</v>
+      </c>
+      <c r="L9" s="145"/>
+      <c r="M9" s="145"/>
+      <c r="N9" s="146"/>
+      <c r="O9" s="160" t="s">
         <v>15</v>
       </c>
-      <c r="P9" s="163"/>
-      <c r="Q9" s="163"/>
-      <c r="R9" s="163"/>
-      <c r="S9" s="163"/>
-      <c r="T9" s="163"/>
-      <c r="U9" s="163"/>
-      <c r="V9" s="145"/>
-      <c r="W9" s="144"/>
-      <c r="X9" s="163"/>
-      <c r="Y9" s="163"/>
-      <c r="Z9" s="163"/>
-      <c r="AA9" s="163"/>
-      <c r="AB9" s="163"/>
-      <c r="AC9" s="163"/>
-      <c r="AD9" s="145"/>
+      <c r="P9" s="156"/>
+      <c r="Q9" s="156"/>
+      <c r="R9" s="156"/>
+      <c r="S9" s="156"/>
+      <c r="T9" s="156"/>
+      <c r="U9" s="156"/>
+      <c r="V9" s="154"/>
+      <c r="W9" s="153"/>
+      <c r="X9" s="156"/>
+      <c r="Y9" s="156"/>
+      <c r="Z9" s="156"/>
+      <c r="AA9" s="156"/>
+      <c r="AB9" s="156"/>
+      <c r="AC9" s="156"/>
+      <c r="AD9" s="154"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
@@ -6066,66 +6077,66 @@
         <f ca="1">I11+1</f>
         <v>46345</v>
       </c>
-      <c r="L11" s="162"/>
-      <c r="M11" s="162"/>
+      <c r="L11" s="159"/>
+      <c r="M11" s="159"/>
       <c r="N11" s="78"/>
       <c r="O11" s="157">
         <f ca="1">K11+1</f>
         <v>46346</v>
       </c>
-      <c r="P11" s="162"/>
-      <c r="Q11" s="162"/>
-      <c r="R11" s="162"/>
-      <c r="S11" s="162"/>
-      <c r="T11" s="162"/>
-      <c r="U11" s="162"/>
+      <c r="P11" s="159"/>
+      <c r="Q11" s="159"/>
+      <c r="R11" s="159"/>
+      <c r="S11" s="159"/>
+      <c r="T11" s="159"/>
+      <c r="U11" s="159"/>
       <c r="V11" s="158"/>
       <c r="W11" s="157">
         <f ca="1">O11+1</f>
         <v>46347</v>
       </c>
-      <c r="X11" s="162"/>
-      <c r="Y11" s="162"/>
-      <c r="Z11" s="162"/>
-      <c r="AA11" s="162"/>
-      <c r="AB11" s="162"/>
-      <c r="AC11" s="162"/>
+      <c r="X11" s="159"/>
+      <c r="Y11" s="159"/>
+      <c r="Z11" s="159"/>
+      <c r="AA11" s="159"/>
+      <c r="AB11" s="159"/>
+      <c r="AC11" s="159"/>
       <c r="AD11" s="158"/>
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
     <row r="12" spans="1:36" s="43" customFormat="1" ht="134.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="42"/>
-      <c r="C12" s="144"/>
-      <c r="D12" s="145"/>
-      <c r="E12" s="164" t="s">
+      <c r="C12" s="153"/>
+      <c r="D12" s="154"/>
+      <c r="E12" s="160" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="165"/>
-      <c r="G12" s="144"/>
-      <c r="H12" s="145"/>
-      <c r="I12" s="144"/>
-      <c r="J12" s="145"/>
-      <c r="K12" s="144"/>
-      <c r="L12" s="163"/>
-      <c r="M12" s="163"/>
-      <c r="N12" s="145"/>
-      <c r="O12" s="144"/>
-      <c r="P12" s="163"/>
-      <c r="Q12" s="163"/>
-      <c r="R12" s="163"/>
-      <c r="S12" s="163"/>
-      <c r="T12" s="163"/>
-      <c r="U12" s="163"/>
-      <c r="V12" s="145"/>
-      <c r="W12" s="144"/>
-      <c r="X12" s="163"/>
-      <c r="Y12" s="163"/>
-      <c r="Z12" s="163"/>
-      <c r="AA12" s="163"/>
-      <c r="AB12" s="163"/>
-      <c r="AC12" s="163"/>
-      <c r="AD12" s="145"/>
+      <c r="F12" s="161"/>
+      <c r="G12" s="153"/>
+      <c r="H12" s="154"/>
+      <c r="I12" s="153"/>
+      <c r="J12" s="154"/>
+      <c r="K12" s="153"/>
+      <c r="L12" s="156"/>
+      <c r="M12" s="156"/>
+      <c r="N12" s="154"/>
+      <c r="O12" s="153"/>
+      <c r="P12" s="156"/>
+      <c r="Q12" s="156"/>
+      <c r="R12" s="156"/>
+      <c r="S12" s="156"/>
+      <c r="T12" s="156"/>
+      <c r="U12" s="156"/>
+      <c r="V12" s="154"/>
+      <c r="W12" s="153"/>
+      <c r="X12" s="156"/>
+      <c r="Y12" s="156"/>
+      <c r="Z12" s="156"/>
+      <c r="AA12" s="156"/>
+      <c r="AB12" s="156"/>
+      <c r="AC12" s="156"/>
+      <c r="AD12" s="154"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
@@ -6188,79 +6199,79 @@
         <f ca="1">I14+1</f>
         <v>46352</v>
       </c>
-      <c r="L14" s="162"/>
-      <c r="M14" s="162"/>
+      <c r="L14" s="159"/>
+      <c r="M14" s="159"/>
       <c r="N14" s="78"/>
       <c r="O14" s="157">
         <f ca="1">K14+1</f>
         <v>46353</v>
       </c>
-      <c r="P14" s="162"/>
-      <c r="Q14" s="162"/>
-      <c r="R14" s="162"/>
-      <c r="S14" s="162"/>
-      <c r="T14" s="162"/>
-      <c r="U14" s="162"/>
+      <c r="P14" s="159"/>
+      <c r="Q14" s="159"/>
+      <c r="R14" s="159"/>
+      <c r="S14" s="159"/>
+      <c r="T14" s="159"/>
+      <c r="U14" s="159"/>
       <c r="V14" s="158"/>
       <c r="W14" s="157">
         <f ca="1">O14+1</f>
         <v>46354</v>
       </c>
-      <c r="X14" s="162"/>
-      <c r="Y14" s="162"/>
-      <c r="Z14" s="162"/>
-      <c r="AA14" s="162"/>
-      <c r="AB14" s="162"/>
-      <c r="AC14" s="162"/>
+      <c r="X14" s="159"/>
+      <c r="Y14" s="159"/>
+      <c r="Z14" s="159"/>
+      <c r="AA14" s="159"/>
+      <c r="AB14" s="159"/>
+      <c r="AC14" s="159"/>
       <c r="AD14" s="158"/>
       <c r="AF14" s="4"/>
     </row>
     <row r="15" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="42"/>
-      <c r="C15" s="144"/>
-      <c r="D15" s="145"/>
-      <c r="E15" s="144"/>
-      <c r="F15" s="145"/>
-      <c r="G15" s="144"/>
-      <c r="H15" s="145"/>
-      <c r="I15" s="144"/>
-      <c r="J15" s="145"/>
-      <c r="K15" s="144"/>
-      <c r="L15" s="163"/>
-      <c r="M15" s="163"/>
-      <c r="N15" s="145"/>
-      <c r="O15" s="144"/>
-      <c r="P15" s="163"/>
-      <c r="Q15" s="163"/>
-      <c r="R15" s="163"/>
-      <c r="S15" s="163"/>
-      <c r="T15" s="163"/>
-      <c r="U15" s="163"/>
-      <c r="V15" s="145"/>
-      <c r="W15" s="144"/>
-      <c r="X15" s="163"/>
-      <c r="Y15" s="163"/>
-      <c r="Z15" s="163"/>
-      <c r="AA15" s="163"/>
-      <c r="AB15" s="163"/>
-      <c r="AC15" s="163"/>
-      <c r="AD15" s="145"/>
+      <c r="C15" s="153"/>
+      <c r="D15" s="154"/>
+      <c r="E15" s="153"/>
+      <c r="F15" s="154"/>
+      <c r="G15" s="153"/>
+      <c r="H15" s="154"/>
+      <c r="I15" s="153"/>
+      <c r="J15" s="154"/>
+      <c r="K15" s="153"/>
+      <c r="L15" s="156"/>
+      <c r="M15" s="156"/>
+      <c r="N15" s="154"/>
+      <c r="O15" s="153"/>
+      <c r="P15" s="156"/>
+      <c r="Q15" s="156"/>
+      <c r="R15" s="156"/>
+      <c r="S15" s="156"/>
+      <c r="T15" s="156"/>
+      <c r="U15" s="156"/>
+      <c r="V15" s="154"/>
+      <c r="W15" s="153"/>
+      <c r="X15" s="156"/>
+      <c r="Y15" s="156"/>
+      <c r="Z15" s="156"/>
+      <c r="AA15" s="156"/>
+      <c r="AB15" s="156"/>
+      <c r="AC15" s="156"/>
+      <c r="AD15" s="154"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
     <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="42"/>
-      <c r="C16" s="119">
+      <c r="C16" s="95">
         <f ca="1">W14+1</f>
         <v>46355</v>
       </c>
-      <c r="D16" s="121"/>
+      <c r="D16" s="96"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
       <c r="H16" s="75"/>
-      <c r="I16" s="136"/>
-      <c r="J16" s="137"/>
+      <c r="I16" s="97"/>
+      <c r="J16" s="98"/>
       <c r="K16" s="66"/>
       <c r="L16" s="68"/>
       <c r="M16" s="68"/>
@@ -6286,101 +6297,101 @@
     </row>
     <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
-      <c r="C17" s="119"/>
-      <c r="D17" s="121"/>
-      <c r="E17" s="112">
+      <c r="C17" s="95"/>
+      <c r="D17" s="96"/>
+      <c r="E17" s="99">
         <f ca="1">C16+1</f>
         <v>46356</v>
       </c>
-      <c r="F17" s="113"/>
-      <c r="G17" s="112">
+      <c r="F17" s="101"/>
+      <c r="G17" s="99">
         <f ca="1">E17+1</f>
         <v>46357</v>
       </c>
-      <c r="H17" s="113"/>
-      <c r="I17" s="112">
+      <c r="H17" s="101"/>
+      <c r="I17" s="99">
         <f ca="1">G17+1</f>
         <v>46358</v>
       </c>
-      <c r="J17" s="113"/>
-      <c r="K17" s="112">
+      <c r="J17" s="101"/>
+      <c r="K17" s="99">
         <f ca="1">I17+1</f>
         <v>46359</v>
       </c>
-      <c r="L17" s="114"/>
-      <c r="M17" s="114"/>
-      <c r="N17" s="113"/>
-      <c r="O17" s="112">
+      <c r="L17" s="100"/>
+      <c r="M17" s="100"/>
+      <c r="N17" s="101"/>
+      <c r="O17" s="99">
         <f ca="1">K17+1</f>
         <v>46360</v>
       </c>
-      <c r="P17" s="114"/>
-      <c r="Q17" s="114"/>
-      <c r="R17" s="114"/>
-      <c r="S17" s="114"/>
-      <c r="T17" s="114"/>
-      <c r="U17" s="114"/>
-      <c r="V17" s="113"/>
-      <c r="W17" s="112">
+      <c r="P17" s="100"/>
+      <c r="Q17" s="100"/>
+      <c r="R17" s="100"/>
+      <c r="S17" s="100"/>
+      <c r="T17" s="100"/>
+      <c r="U17" s="100"/>
+      <c r="V17" s="101"/>
+      <c r="W17" s="99">
         <f ca="1">O17+1</f>
         <v>46361</v>
       </c>
-      <c r="X17" s="114"/>
-      <c r="Y17" s="114"/>
-      <c r="Z17" s="114"/>
-      <c r="AA17" s="114"/>
-      <c r="AB17" s="114"/>
-      <c r="AC17" s="114"/>
-      <c r="AD17" s="113"/>
+      <c r="X17" s="100"/>
+      <c r="Y17" s="100"/>
+      <c r="Z17" s="100"/>
+      <c r="AA17" s="100"/>
+      <c r="AB17" s="100"/>
+      <c r="AC17" s="100"/>
+      <c r="AD17" s="101"/>
       <c r="AF17" s="4"/>
     </row>
     <row r="18" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="42"/>
-      <c r="C18" s="122"/>
-      <c r="D18" s="123"/>
-      <c r="E18" s="122"/>
-      <c r="F18" s="123"/>
-      <c r="G18" s="122"/>
-      <c r="H18" s="123"/>
-      <c r="I18" s="122"/>
-      <c r="J18" s="123"/>
-      <c r="K18" s="122"/>
-      <c r="L18" s="139"/>
-      <c r="M18" s="139"/>
-      <c r="N18" s="123"/>
-      <c r="O18" s="122"/>
-      <c r="P18" s="139"/>
-      <c r="Q18" s="139"/>
-      <c r="R18" s="139"/>
-      <c r="S18" s="139"/>
-      <c r="T18" s="139"/>
-      <c r="U18" s="139"/>
-      <c r="V18" s="123"/>
-      <c r="W18" s="122"/>
-      <c r="X18" s="139"/>
-      <c r="Y18" s="139"/>
-      <c r="Z18" s="139"/>
-      <c r="AA18" s="139"/>
-      <c r="AB18" s="139"/>
-      <c r="AC18" s="139"/>
-      <c r="AD18" s="123"/>
+      <c r="C18" s="84"/>
+      <c r="D18" s="86"/>
+      <c r="E18" s="84"/>
+      <c r="F18" s="86"/>
+      <c r="G18" s="84"/>
+      <c r="H18" s="86"/>
+      <c r="I18" s="84"/>
+      <c r="J18" s="86"/>
+      <c r="K18" s="84"/>
+      <c r="L18" s="85"/>
+      <c r="M18" s="85"/>
+      <c r="N18" s="86"/>
+      <c r="O18" s="84"/>
+      <c r="P18" s="85"/>
+      <c r="Q18" s="85"/>
+      <c r="R18" s="85"/>
+      <c r="S18" s="85"/>
+      <c r="T18" s="85"/>
+      <c r="U18" s="85"/>
+      <c r="V18" s="86"/>
+      <c r="W18" s="84"/>
+      <c r="X18" s="85"/>
+      <c r="Y18" s="85"/>
+      <c r="Z18" s="85"/>
+      <c r="AA18" s="85"/>
+      <c r="AB18" s="85"/>
+      <c r="AC18" s="85"/>
+      <c r="AD18" s="86"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
     <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="42"/>
-      <c r="C19" s="119">
+      <c r="C19" s="95">
         <f ca="1">W17+1</f>
         <v>46362</v>
       </c>
-      <c r="D19" s="121"/>
+      <c r="D19" s="96"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
       <c r="H19" s="75"/>
-      <c r="I19" s="136"/>
-      <c r="J19" s="137"/>
+      <c r="I19" s="97"/>
+      <c r="J19" s="98"/>
       <c r="K19" s="66"/>
       <c r="L19" s="68"/>
       <c r="M19" s="68"/>
@@ -6406,84 +6417,84 @@
     </row>
     <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
-      <c r="C20" s="119"/>
-      <c r="D20" s="121"/>
-      <c r="E20" s="112">
+      <c r="C20" s="95"/>
+      <c r="D20" s="96"/>
+      <c r="E20" s="99">
         <f ca="1">C19+1</f>
         <v>46363</v>
       </c>
-      <c r="F20" s="113"/>
-      <c r="G20" s="112">
+      <c r="F20" s="101"/>
+      <c r="G20" s="99">
         <f ca="1">E20+1</f>
         <v>46364</v>
       </c>
-      <c r="H20" s="113"/>
-      <c r="I20" s="112">
+      <c r="H20" s="101"/>
+      <c r="I20" s="99">
         <f ca="1">G20+1</f>
         <v>46365</v>
       </c>
-      <c r="J20" s="113"/>
-      <c r="K20" s="112">
+      <c r="J20" s="101"/>
+      <c r="K20" s="99">
         <f ca="1">I20+1</f>
         <v>46366</v>
       </c>
-      <c r="L20" s="114"/>
-      <c r="M20" s="114"/>
-      <c r="N20" s="113"/>
-      <c r="O20" s="112">
+      <c r="L20" s="100"/>
+      <c r="M20" s="100"/>
+      <c r="N20" s="101"/>
+      <c r="O20" s="99">
         <f ca="1">K20+1</f>
         <v>46367</v>
       </c>
-      <c r="P20" s="114"/>
-      <c r="Q20" s="114"/>
-      <c r="R20" s="114"/>
-      <c r="S20" s="114"/>
-      <c r="T20" s="114"/>
-      <c r="U20" s="114"/>
-      <c r="V20" s="113"/>
-      <c r="W20" s="112">
+      <c r="P20" s="100"/>
+      <c r="Q20" s="100"/>
+      <c r="R20" s="100"/>
+      <c r="S20" s="100"/>
+      <c r="T20" s="100"/>
+      <c r="U20" s="100"/>
+      <c r="V20" s="101"/>
+      <c r="W20" s="99">
         <f ca="1">O20+1</f>
         <v>46368</v>
       </c>
-      <c r="X20" s="114"/>
-      <c r="Y20" s="114"/>
-      <c r="Z20" s="114"/>
-      <c r="AA20" s="114"/>
-      <c r="AB20" s="114"/>
-      <c r="AC20" s="114"/>
-      <c r="AD20" s="113"/>
+      <c r="X20" s="100"/>
+      <c r="Y20" s="100"/>
+      <c r="Z20" s="100"/>
+      <c r="AA20" s="100"/>
+      <c r="AB20" s="100"/>
+      <c r="AC20" s="100"/>
+      <c r="AD20" s="101"/>
       <c r="AF20" s="4"/>
     </row>
     <row r="21" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="42"/>
-      <c r="C21" s="122"/>
-      <c r="D21" s="123"/>
-      <c r="E21" s="122"/>
-      <c r="F21" s="123"/>
-      <c r="G21" s="122"/>
-      <c r="H21" s="123"/>
-      <c r="I21" s="122"/>
-      <c r="J21" s="123"/>
-      <c r="K21" s="122"/>
-      <c r="L21" s="139"/>
-      <c r="M21" s="139"/>
-      <c r="N21" s="123"/>
-      <c r="O21" s="122"/>
-      <c r="P21" s="139"/>
-      <c r="Q21" s="139"/>
-      <c r="R21" s="139"/>
-      <c r="S21" s="139"/>
-      <c r="T21" s="139"/>
-      <c r="U21" s="139"/>
-      <c r="V21" s="123"/>
-      <c r="W21" s="122"/>
-      <c r="X21" s="139"/>
-      <c r="Y21" s="139"/>
-      <c r="Z21" s="139"/>
-      <c r="AA21" s="139"/>
-      <c r="AB21" s="139"/>
-      <c r="AC21" s="139"/>
-      <c r="AD21" s="123"/>
+      <c r="C21" s="84"/>
+      <c r="D21" s="86"/>
+      <c r="E21" s="84"/>
+      <c r="F21" s="86"/>
+      <c r="G21" s="84"/>
+      <c r="H21" s="86"/>
+      <c r="I21" s="84"/>
+      <c r="J21" s="86"/>
+      <c r="K21" s="84"/>
+      <c r="L21" s="85"/>
+      <c r="M21" s="85"/>
+      <c r="N21" s="86"/>
+      <c r="O21" s="84"/>
+      <c r="P21" s="85"/>
+      <c r="Q21" s="85"/>
+      <c r="R21" s="85"/>
+      <c r="S21" s="85"/>
+      <c r="T21" s="85"/>
+      <c r="U21" s="85"/>
+      <c r="V21" s="86"/>
+      <c r="W21" s="84"/>
+      <c r="X21" s="85"/>
+      <c r="Y21" s="85"/>
+      <c r="Z21" s="85"/>
+      <c r="AA21" s="85"/>
+      <c r="AB21" s="85"/>
+      <c r="AC21" s="85"/>
+      <c r="AD21" s="86"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
@@ -6561,54 +6572,54 @@
     </row>
     <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
-      <c r="C25" s="140" t="s">
+      <c r="C25" s="87" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="140"/>
-      <c r="E25" s="140"/>
-      <c r="F25" s="140"/>
-      <c r="G25" s="140"/>
-      <c r="H25" s="140"/>
-      <c r="I25" s="140"/>
-      <c r="J25" s="140"/>
-      <c r="K25" s="140"/>
+      <c r="D25" s="87"/>
+      <c r="E25" s="87"/>
+      <c r="F25" s="87"/>
+      <c r="G25" s="87"/>
+      <c r="H25" s="87"/>
+      <c r="I25" s="87"/>
+      <c r="J25" s="87"/>
+      <c r="K25" s="87"/>
       <c r="L25" s="60"/>
       <c r="M25" s="1"/>
-      <c r="O25" s="141">
+      <c r="O25" s="88">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)-1,1)</f>
         <v>46296</v>
       </c>
-      <c r="P25" s="141"/>
-      <c r="Q25" s="141"/>
-      <c r="R25" s="141"/>
-      <c r="S25" s="141"/>
-      <c r="T25" s="141"/>
-      <c r="U25" s="141"/>
+      <c r="P25" s="88"/>
+      <c r="Q25" s="88"/>
+      <c r="R25" s="88"/>
+      <c r="S25" s="88"/>
+      <c r="T25" s="88"/>
+      <c r="U25" s="88"/>
       <c r="V25" s="61"/>
       <c r="W25" s="61"/>
-      <c r="X25" s="141">
+      <c r="X25" s="88">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)+1,1)</f>
         <v>46357</v>
       </c>
-      <c r="Y25" s="141"/>
-      <c r="Z25" s="141"/>
-      <c r="AA25" s="141"/>
-      <c r="AB25" s="141"/>
-      <c r="AC25" s="141"/>
-      <c r="AD25" s="141"/>
+      <c r="Y25" s="88"/>
+      <c r="Z25" s="88"/>
+      <c r="AA25" s="88"/>
+      <c r="AB25" s="88"/>
+      <c r="AC25" s="88"/>
+      <c r="AD25" s="88"/>
       <c r="AF25" s="1"/>
     </row>
     <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
-      <c r="C26" s="140"/>
-      <c r="D26" s="140"/>
-      <c r="E26" s="140"/>
-      <c r="F26" s="140"/>
-      <c r="G26" s="140"/>
-      <c r="H26" s="140"/>
-      <c r="I26" s="140"/>
-      <c r="J26" s="140"/>
-      <c r="K26" s="140"/>
+      <c r="C26" s="87"/>
+      <c r="D26" s="87"/>
+      <c r="E26" s="87"/>
+      <c r="F26" s="87"/>
+      <c r="G26" s="87"/>
+      <c r="H26" s="87"/>
+      <c r="I26" s="87"/>
+      <c r="J26" s="87"/>
+      <c r="K26" s="87"/>
       <c r="L26" s="60"/>
       <c r="M26" s="1"/>
       <c r="O26" s="62" t="str">
@@ -6673,15 +6684,15 @@
     </row>
     <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
-      <c r="C27" s="116"/>
-      <c r="D27" s="116"/>
-      <c r="E27" s="116"/>
-      <c r="F27" s="116"/>
-      <c r="G27" s="116"/>
-      <c r="H27" s="116"/>
-      <c r="I27" s="116"/>
-      <c r="J27" s="116"/>
-      <c r="K27" s="116"/>
+      <c r="C27" s="89"/>
+      <c r="D27" s="89"/>
+      <c r="E27" s="89"/>
+      <c r="F27" s="89"/>
+      <c r="G27" s="89"/>
+      <c r="H27" s="89"/>
+      <c r="I27" s="89"/>
+      <c r="J27" s="89"/>
+      <c r="K27" s="89"/>
       <c r="M27" s="1"/>
       <c r="O27" s="64" t="str">
         <f t="shared" ref="O27:U32" ca="1" si="0">IF(MONTH($O$25)&lt;&gt;MONTH($O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1)),"",$O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1))</f>
@@ -6745,15 +6756,15 @@
     </row>
     <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
-      <c r="C28" s="115"/>
-      <c r="D28" s="115"/>
-      <c r="E28" s="115"/>
-      <c r="F28" s="115"/>
-      <c r="G28" s="115"/>
-      <c r="H28" s="115"/>
-      <c r="I28" s="115"/>
-      <c r="J28" s="115"/>
-      <c r="K28" s="115"/>
+      <c r="C28" s="90"/>
+      <c r="D28" s="90"/>
+      <c r="E28" s="90"/>
+      <c r="F28" s="90"/>
+      <c r="G28" s="90"/>
+      <c r="H28" s="90"/>
+      <c r="I28" s="90"/>
+      <c r="J28" s="90"/>
+      <c r="K28" s="90"/>
       <c r="M28" s="1"/>
       <c r="O28" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6817,15 +6828,15 @@
     </row>
     <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
-      <c r="C29" s="116"/>
-      <c r="D29" s="116"/>
-      <c r="E29" s="116"/>
-      <c r="F29" s="116"/>
-      <c r="G29" s="116"/>
-      <c r="H29" s="116"/>
-      <c r="I29" s="116"/>
-      <c r="J29" s="116"/>
-      <c r="K29" s="116"/>
+      <c r="C29" s="89"/>
+      <c r="D29" s="89"/>
+      <c r="E29" s="89"/>
+      <c r="F29" s="89"/>
+      <c r="G29" s="89"/>
+      <c r="H29" s="89"/>
+      <c r="I29" s="89"/>
+      <c r="J29" s="89"/>
+      <c r="K29" s="89"/>
       <c r="M29" s="1"/>
       <c r="O29" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6889,15 +6900,15 @@
     </row>
     <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
-      <c r="C30" s="115"/>
-      <c r="D30" s="115"/>
-      <c r="E30" s="115"/>
-      <c r="F30" s="115"/>
-      <c r="G30" s="115"/>
-      <c r="H30" s="115"/>
-      <c r="I30" s="115"/>
-      <c r="J30" s="115"/>
-      <c r="K30" s="115"/>
+      <c r="C30" s="90"/>
+      <c r="D30" s="90"/>
+      <c r="E30" s="90"/>
+      <c r="F30" s="90"/>
+      <c r="G30" s="90"/>
+      <c r="H30" s="90"/>
+      <c r="I30" s="90"/>
+      <c r="J30" s="90"/>
+      <c r="K30" s="90"/>
       <c r="M30" s="1"/>
       <c r="O30" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6961,15 +6972,15 @@
     </row>
     <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
-      <c r="C31" s="116"/>
-      <c r="D31" s="116"/>
-      <c r="E31" s="116"/>
-      <c r="F31" s="116"/>
-      <c r="G31" s="116"/>
-      <c r="H31" s="116"/>
-      <c r="I31" s="116"/>
-      <c r="J31" s="116"/>
-      <c r="K31" s="116"/>
+      <c r="C31" s="89"/>
+      <c r="D31" s="89"/>
+      <c r="E31" s="89"/>
+      <c r="F31" s="89"/>
+      <c r="G31" s="89"/>
+      <c r="H31" s="89"/>
+      <c r="I31" s="89"/>
+      <c r="J31" s="89"/>
+      <c r="K31" s="89"/>
       <c r="M31" s="1"/>
       <c r="O31" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -7144,128 +7155,98 @@
     </row>
     <row r="37" spans="1:32" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
     <row r="38" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="D38" s="84" t="s">
+      <c r="D38" s="116" t="s">
         <v>23</v>
       </c>
-      <c r="E38" s="85"/>
-      <c r="F38" s="86"/>
-      <c r="G38" s="90">
+      <c r="E38" s="117"/>
+      <c r="F38" s="118"/>
+      <c r="G38" s="122">
         <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
         <v>4</v>
       </c>
-      <c r="H38" s="91"/>
-      <c r="I38" s="84" t="s">
+      <c r="H38" s="123"/>
+      <c r="I38" s="116" t="s">
         <v>26</v>
       </c>
-      <c r="J38" s="98"/>
-      <c r="K38" s="94" t="s">
+      <c r="J38" s="130"/>
+      <c r="K38" s="126" t="s">
         <v>24</v>
       </c>
-      <c r="L38" s="95"/>
-      <c r="M38" s="106">
+      <c r="L38" s="127"/>
+      <c r="M38" s="138">
         <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
         <v>5.0000000000000009</v>
       </c>
-      <c r="N38" s="107"/>
-      <c r="O38" s="107"/>
-      <c r="P38" s="107"/>
-      <c r="Q38" s="107"/>
-      <c r="R38" s="108"/>
-      <c r="S38" s="100" t="s">
+      <c r="N38" s="139"/>
+      <c r="O38" s="139"/>
+      <c r="P38" s="139"/>
+      <c r="Q38" s="139"/>
+      <c r="R38" s="140"/>
+      <c r="S38" s="132" t="s">
         <v>25</v>
       </c>
-      <c r="T38" s="101"/>
-      <c r="U38" s="101"/>
-      <c r="V38" s="101"/>
-      <c r="W38" s="101"/>
-      <c r="X38" s="102"/>
+      <c r="T38" s="133"/>
+      <c r="U38" s="133"/>
+      <c r="V38" s="133"/>
+      <c r="W38" s="133"/>
+      <c r="X38" s="134"/>
     </row>
     <row r="39" spans="1:32" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="D39" s="87"/>
-      <c r="E39" s="88"/>
-      <c r="F39" s="89"/>
-      <c r="G39" s="92"/>
-      <c r="H39" s="93"/>
-      <c r="I39" s="87"/>
-      <c r="J39" s="99"/>
-      <c r="K39" s="96"/>
-      <c r="L39" s="97"/>
-      <c r="M39" s="109"/>
-      <c r="N39" s="110"/>
-      <c r="O39" s="110"/>
-      <c r="P39" s="110"/>
-      <c r="Q39" s="110"/>
-      <c r="R39" s="111"/>
-      <c r="S39" s="103"/>
-      <c r="T39" s="104"/>
-      <c r="U39" s="104"/>
-      <c r="V39" s="104"/>
-      <c r="W39" s="104"/>
-      <c r="X39" s="105"/>
+      <c r="D39" s="119"/>
+      <c r="E39" s="120"/>
+      <c r="F39" s="121"/>
+      <c r="G39" s="124"/>
+      <c r="H39" s="125"/>
+      <c r="I39" s="119"/>
+      <c r="J39" s="131"/>
+      <c r="K39" s="128"/>
+      <c r="L39" s="129"/>
+      <c r="M39" s="141"/>
+      <c r="N39" s="142"/>
+      <c r="O39" s="142"/>
+      <c r="P39" s="142"/>
+      <c r="Q39" s="142"/>
+      <c r="R39" s="143"/>
+      <c r="S39" s="135"/>
+      <c r="T39" s="136"/>
+      <c r="U39" s="136"/>
+      <c r="V39" s="136"/>
+      <c r="W39" s="136"/>
+      <c r="X39" s="137"/>
     </row>
   </sheetData>
   <mergeCells count="112">
-    <mergeCell ref="K18:N18"/>
-    <mergeCell ref="W18:AD18"/>
-    <mergeCell ref="C25:K26"/>
-    <mergeCell ref="O25:U25"/>
-    <mergeCell ref="X25:AD25"/>
-    <mergeCell ref="C27:K27"/>
-    <mergeCell ref="C28:K29"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="O18:V18"/>
-    <mergeCell ref="C19:D20"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:N20"/>
-    <mergeCell ref="W15:AD15"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="O17:V17"/>
-    <mergeCell ref="W17:AD17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="O15:V15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="W12:AD12"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="O14:V14"/>
-    <mergeCell ref="W14:AD14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="O12:V12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="W9:AD9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="O11:V11"/>
-    <mergeCell ref="W11:AD11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:V9"/>
-    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="D38:F39"/>
+    <mergeCell ref="G38:H39"/>
+    <mergeCell ref="I38:J39"/>
+    <mergeCell ref="K38:L39"/>
+    <mergeCell ref="M38:R39"/>
+    <mergeCell ref="S38:X39"/>
+    <mergeCell ref="C30:K31"/>
+    <mergeCell ref="O20:V20"/>
+    <mergeCell ref="W20:AD20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:N21"/>
+    <mergeCell ref="O21:V21"/>
+    <mergeCell ref="W21:AD21"/>
+    <mergeCell ref="C2:AD2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="W5:AD5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="O5:V5"/>
     <mergeCell ref="K6:N6"/>
     <mergeCell ref="C7:D8"/>
     <mergeCell ref="E7:F7"/>
@@ -7286,37 +7267,67 @@
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="O6:V6"/>
     <mergeCell ref="W6:AD6"/>
-    <mergeCell ref="C2:AD2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="W5:AD5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="O5:V5"/>
-    <mergeCell ref="D38:F39"/>
-    <mergeCell ref="G38:H39"/>
-    <mergeCell ref="I38:J39"/>
-    <mergeCell ref="K38:L39"/>
-    <mergeCell ref="M38:R39"/>
-    <mergeCell ref="S38:X39"/>
-    <mergeCell ref="C30:K31"/>
-    <mergeCell ref="O20:V20"/>
-    <mergeCell ref="W20:AD20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:N21"/>
-    <mergeCell ref="O21:V21"/>
-    <mergeCell ref="W21:AD21"/>
+    <mergeCell ref="W9:AD9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="O11:V11"/>
+    <mergeCell ref="W11:AD11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:V9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="W12:AD12"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O14:V14"/>
+    <mergeCell ref="W14:AD14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="O12:V12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="W15:AD15"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="O17:V17"/>
+    <mergeCell ref="W17:AD17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="O15:V15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="K18:N18"/>
+    <mergeCell ref="W18:AD18"/>
+    <mergeCell ref="C25:K26"/>
+    <mergeCell ref="O25:U25"/>
+    <mergeCell ref="X25:AD25"/>
+    <mergeCell ref="C27:K27"/>
+    <mergeCell ref="C28:K29"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="O18:V18"/>
+    <mergeCell ref="C19:D20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:N20"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 E5 G5 I5 K5:L5 O5 W5 C7 E8 G8 I8 K8:L8 O8 W8 C10 E11 G11 I11 K11:L11 O11 W11 C13 E14 G14 I14 K14:L14 O14 W14 C16 E17 G17 I17 K17 O17 W17">
     <cfRule type="expression" dxfId="3" priority="3">
@@ -7350,6 +7361,35 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Url xsi:nil="true"/>
+      <Description xsi:nil="true"/>
+    </Image>
+    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
+    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
+    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
+    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </ImageTagsTaxHTField>
+    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
+    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x01010079F111ED35F8CC479449609E8A0923A6" ma:contentTypeVersion="30" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="cec0622158e8f13124e9e8fd4de31bd1">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns1="http://schemas.microsoft.com/sharepoint/v3" xmlns:ns2="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xmlns:ns3="16c05727-aa75-4e4a-9b5f-8a80a1165891" xmlns:ns4="230e9df3-be65-4c73-a93b-d1236ebd677e" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="3b52f30ab005d15df08657af532e6e38" ns1:_="" ns2:_="" ns3:_="" ns4:_="">
     <xsd:import namespace="http://schemas.microsoft.com/sharepoint/v3"/>
@@ -7667,36 +7707,27 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <Image xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Url xsi:nil="true"/>
-      <Description xsi:nil="true"/>
-    </Image>
-    <Status xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">Not started</Status>
-    <Background xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">false</Background>
-    <_ip_UnifiedCompliancePolicyProperties xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
-    <ImageTagsTaxHTField xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </ImageTagsTaxHTField>
-    <TaxCatchAll xmlns="230e9df3-be65-4c73-a93b-d1236ebd677e" xsi:nil="true"/>
-    <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F0D3479-5903-425F-9669-62B4E7216DE9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B201CC6-7A0A-429C-B445-7EDA1CF4A1D7}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
+    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
+    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{652EDDE9-C911-407A-9906-647D87C81E69}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -7717,26 +7748,6 @@
 </ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B201CC6-7A0A-429C-B445-7EDA1CF4A1D7}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
-    <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
-    <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F0D3479-5903-425F-9669-62B4E7216DE9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata"/>
 </file>
--- a/Group_milestones.xlsx
+++ b/Group_milestones.xlsx
@@ -3,9 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30430"/>
   <workbookPr filterPrivacy="1" codeName="ThisWorkbook"/>
-  <xr:revisionPtr revIDLastSave="44" documentId="13_ncr:1_{6D2F1A88-5E4C-4A1B-983F-CCDEB225E021}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0C8FCD8C-DF16-42FB-BEAE-93AA2A70C77E}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AB527A1-308C-4AE4-8A08-DFA53DC0BAC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13872" tabRatio="824" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="824" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="52" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="71" uniqueCount="61">
   <si>
     <t>Notes</t>
   </si>
@@ -210,9 +210,6 @@
     <t>MCTR2: Motor characterise in heavy current lab with avalable VFD's</t>
   </si>
   <si>
-    <t>MCTR2: Start with gearbox casing build</t>
-  </si>
-  <si>
     <t>EERI321: Semester T3</t>
   </si>
   <si>
@@ -223,9 +220,6 @@
   </si>
   <si>
     <t>REII: participation evidence captured - scope TBD, confirm w/ lecturer (F-08)</t>
-  </si>
-  <si>
-    <t>REII: gate - Controller Spec + ESP32 codebase obtained; board powered (planned, not agreed)</t>
   </si>
   <si>
     <t>REII: STM32F411 dongle bring-up (planned, not agreed)
@@ -276,10 +270,6 @@
     <t>REII: pre-integration (planned, not agreed)
 · isolation bench-verify + HW E-stop path (pre-live drivers)
 · MCTR-I profile format D-04 + encoder handoff</t>
-  </si>
-  <si>
-    <t>EEII1:Order heat sinks and power supply(at the latest) MCTR2: Starting with all final draft printing parts
-REII: controller board delivery (estimate, Checkpoint2) - input to ESP32 nRF stub + integration</t>
   </si>
   <si>
     <t>MCTR1: Carriage v2 build, Carriage motor drive test</t>
@@ -508,6 +498,44 @@
 REII: demo dry-run + evidence pack check (planned, not agreed)</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t xml:space="preserve">REII: gate - Controller Spec + ESP32 codebase obtained; board powered (planned, not agreed) </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFCC6600"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>MCTR2: Start with gearbox casing build</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>EEII1:Order heat sinks and power supply(at the latest)</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFCC6600"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> MCTR2: Starting with all final draft printing parts</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="2" tint="-0.89999084444715716"/>
+        <rFont val="Seaford"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">
+REII: controller board delivery (estimate, Checkpoint2) - input to ESP32 nRF stub + integration</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -520,7 +548,7 @@
     <numFmt numFmtId="167" formatCode="mmmm\ yyyy"/>
     <numFmt numFmtId="168" formatCode="dddd"/>
   </numFmts>
-  <fonts count="45" x14ac:knownFonts="1">
+  <fonts count="46" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -808,6 +836,12 @@
       <name val="Seaford"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFCC6600"/>
+      <name val="Seaford"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -1036,7 +1070,7 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="167">
+  <cellXfs count="168">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1264,6 +1298,111 @@
     <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="166" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="44" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="40" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="32" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1348,114 +1487,21 @@
     <xf numFmtId="0" fontId="34" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1"/>
-    </xf>
-    <xf numFmtId="167" fontId="31" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="168" fontId="14" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="40" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="166" fontId="25" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
     <xf numFmtId="0" fontId="30" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -1468,30 +1514,33 @@
     <xf numFmtId="0" fontId="41" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="36" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="41" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
@@ -1501,19 +1550,7 @@
     <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="36" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="44" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="45" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1" indent="1"/>
     </xf>
   </cellXfs>
@@ -1666,6 +1703,7 @@
       <rgbColor rgb="00333333"/>
     </indexedColors>
     <mruColors>
+      <color rgb="FFCC6600"/>
       <color rgb="FFFF0000"/>
     </mruColors>
   </colors>
@@ -1887,19 +1925,19 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:R15"/>
-  <sheetFormatPr defaultColWidth="8.71875" defaultRowHeight="15.3" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="4" width="5.5546875" style="3" customWidth="1"/>
-    <col min="5" max="9" width="10.5546875" style="3" customWidth="1"/>
-    <col min="10" max="11" width="10.5546875" style="28" customWidth="1"/>
-    <col min="12" max="14" width="5.5546875" style="3" customWidth="1"/>
-    <col min="15" max="15" width="25.5546875" style="3" customWidth="1"/>
-    <col min="16" max="16" width="10.5546875" style="3" customWidth="1"/>
-    <col min="17" max="18" width="5.5546875" style="3" customWidth="1"/>
-    <col min="19" max="16384" width="8.71875" style="3"/>
+    <col min="1" max="4" width="5.5703125" style="3" customWidth="1"/>
+    <col min="5" max="9" width="10.5703125" style="3" customWidth="1"/>
+    <col min="10" max="11" width="10.5703125" style="28" customWidth="1"/>
+    <col min="12" max="14" width="5.5703125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="25.5703125" style="3" customWidth="1"/>
+    <col min="16" max="16" width="10.5703125" style="3" customWidth="1"/>
+    <col min="17" max="18" width="5.5703125" style="3" customWidth="1"/>
+    <col min="19" max="16384" width="8.7109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -1919,7 +1957,7 @@
       <c r="Q1" s="1"/>
       <c r="R1" s="1"/>
     </row>
-    <row r="2" spans="1:18" s="7" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:18" s="7" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="4"/>
       <c r="B2" s="5"/>
       <c r="C2" s="73" t="s">
@@ -1941,7 +1979,7 @@
       <c r="Q2" s="6"/>
       <c r="R2" s="4"/>
     </row>
-    <row r="3" spans="1:18" ht="25" customHeight="1" x14ac:dyDescent="2.15">
+    <row r="3" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A3" s="1"/>
       <c r="B3" s="1"/>
       <c r="C3" s="8"/>
@@ -1961,7 +1999,7 @@
       <c r="Q3" s="1"/>
       <c r="R3" s="1"/>
     </row>
-    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="11"/>
       <c r="C4" s="11"/>
@@ -1975,15 +2013,15 @@
       <c r="K4" s="12"/>
       <c r="L4" s="11"/>
       <c r="M4" s="1"/>
-      <c r="N4" s="146" t="s">
+      <c r="N4" s="147" t="s">
         <v>10</v>
       </c>
-      <c r="O4" s="146"/>
-      <c r="P4" s="146"/>
-      <c r="Q4" s="146"/>
+      <c r="O4" s="147"/>
+      <c r="P4" s="147"/>
+      <c r="Q4" s="147"/>
       <c r="R4" s="1"/>
     </row>
-    <row r="5" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1"/>
       <c r="B5" s="11"/>
       <c r="C5" s="13" t="s">
@@ -2001,13 +2039,13 @@
       <c r="K5" s="15"/>
       <c r="L5" s="16"/>
       <c r="M5" s="4"/>
-      <c r="N5" s="146"/>
-      <c r="O5" s="146"/>
-      <c r="P5" s="146"/>
-      <c r="Q5" s="146"/>
+      <c r="N5" s="147"/>
+      <c r="O5" s="147"/>
+      <c r="P5" s="147"/>
+      <c r="Q5" s="147"/>
       <c r="R5" s="1"/>
     </row>
-    <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1"/>
       <c r="B6" s="11"/>
       <c r="C6" s="17"/>
@@ -2021,13 +2059,13 @@
       <c r="K6" s="20"/>
       <c r="L6" s="19"/>
       <c r="M6" s="4"/>
-      <c r="N6" s="146"/>
-      <c r="O6" s="146"/>
-      <c r="P6" s="146"/>
-      <c r="Q6" s="146"/>
+      <c r="N6" s="147"/>
+      <c r="O6" s="147"/>
+      <c r="P6" s="147"/>
+      <c r="Q6" s="147"/>
       <c r="R6" s="1"/>
     </row>
-    <row r="7" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
       <c r="B7" s="11"/>
       <c r="C7" s="13" t="s">
@@ -2051,7 +2089,7 @@
       <c r="Q7" s="11"/>
       <c r="R7" s="1"/>
     </row>
-    <row r="8" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1"/>
       <c r="B8" s="11"/>
       <c r="C8" s="17"/>
@@ -2075,7 +2113,7 @@
       </c>
       <c r="R8" s="1"/>
     </row>
-    <row r="9" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1"/>
       <c r="B9" s="11"/>
       <c r="C9" s="13" t="s">
@@ -2099,7 +2137,7 @@
       <c r="Q9" s="11"/>
       <c r="R9" s="1"/>
     </row>
-    <row r="10" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1"/>
       <c r="B10" s="11"/>
       <c r="C10" s="24"/>
@@ -2125,7 +2163,7 @@
       <c r="Q10" s="18"/>
       <c r="R10" s="1"/>
     </row>
-    <row r="11" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1"/>
       <c r="B11" s="11"/>
       <c r="C11" s="24"/>
@@ -2145,7 +2183,7 @@
       <c r="Q11" s="18"/>
       <c r="R11" s="1"/>
     </row>
-    <row r="12" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1"/>
       <c r="B12" s="11"/>
       <c r="C12" s="13" t="s">
@@ -2169,7 +2207,7 @@
       <c r="Q12" s="18"/>
       <c r="R12" s="1"/>
     </row>
-    <row r="13" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1"/>
       <c r="B13" s="11"/>
       <c r="C13" s="25"/>
@@ -2191,7 +2229,7 @@
       <c r="Q13" s="18"/>
       <c r="R13" s="1"/>
     </row>
-    <row r="14" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:18" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1"/>
       <c r="B14" s="11"/>
       <c r="C14" s="18"/>
@@ -2211,7 +2249,7 @@
       <c r="Q14" s="18"/>
       <c r="R14" s="1"/>
     </row>
-    <row r="15" spans="1:18" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="15" spans="1:18" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
@@ -2246,25 +2284,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AP40"/>
-  <sheetFormatPr defaultColWidth="8.71875" defaultRowHeight="12.6" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="5.5546875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="5.5546875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="5.5546875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.5546875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="5.5546875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="15.5546875" style="3" customWidth="1"/>
-    <col min="11" max="14" width="5.5546875" style="3" customWidth="1"/>
-    <col min="15" max="30" width="2.5546875" style="3" customWidth="1"/>
-    <col min="31" max="32" width="5.5546875" style="3" customWidth="1"/>
-    <col min="33" max="33" width="17.1640625" style="3" customWidth="1"/>
-    <col min="34" max="34" width="10.44140625" style="3" customWidth="1"/>
-    <col min="35" max="16384" width="8.71875" style="3"/>
+    <col min="1" max="3" width="5.5703125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="5.5703125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="5.5703125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="5.5703125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="3" customWidth="1"/>
+    <col min="11" max="14" width="5.5703125" style="3" customWidth="1"/>
+    <col min="15" max="30" width="2.5703125" style="3" customWidth="1"/>
+    <col min="31" max="32" width="5.5703125" style="3" customWidth="1"/>
+    <col min="33" max="33" width="17.140625" style="3" customWidth="1"/>
+    <col min="34" max="34" width="10.42578125" style="3" customWidth="1"/>
+    <col min="35" max="16384" width="8.7109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2298,7 +2336,7 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="2.15">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A2" s="29"/>
       <c r="C2" s="116">
         <f ca="1">DATE(About!P8,9,1)</f>
@@ -2333,7 +2371,7 @@
       <c r="AD2" s="116"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="2.15">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -2353,7 +2391,7 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="35"/>
       <c r="C4" s="117">
         <f ca="1">C5</f>
@@ -2410,223 +2448,223 @@
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="C5" s="118">
+      <c r="C5" s="94">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46264</v>
       </c>
-      <c r="D5" s="120"/>
-      <c r="E5" s="118">
+      <c r="D5" s="95"/>
+      <c r="E5" s="94">
         <f ca="1">C5+1</f>
         <v>46265</v>
       </c>
-      <c r="F5" s="120"/>
-      <c r="G5" s="118">
+      <c r="F5" s="95"/>
+      <c r="G5" s="94">
         <f ca="1">E5+1</f>
         <v>46266</v>
       </c>
-      <c r="H5" s="120"/>
-      <c r="I5" s="118">
+      <c r="H5" s="95"/>
+      <c r="I5" s="94">
         <f ca="1">G5+1</f>
         <v>46267</v>
       </c>
-      <c r="J5" s="120"/>
-      <c r="K5" s="118">
+      <c r="J5" s="95"/>
+      <c r="K5" s="94">
         <f ca="1">I5+1</f>
         <v>46268</v>
       </c>
-      <c r="L5" s="119"/>
-      <c r="M5" s="119"/>
+      <c r="L5" s="115"/>
+      <c r="M5" s="115"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="118">
+      <c r="O5" s="94">
         <f ca="1">K5+1</f>
         <v>46269</v>
       </c>
-      <c r="P5" s="119"/>
-      <c r="Q5" s="119"/>
-      <c r="R5" s="119"/>
-      <c r="S5" s="119"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="120"/>
-      <c r="W5" s="118">
+      <c r="P5" s="115"/>
+      <c r="Q5" s="115"/>
+      <c r="R5" s="115"/>
+      <c r="S5" s="115"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="115"/>
+      <c r="V5" s="95"/>
+      <c r="W5" s="94">
         <f ca="1">O5+1</f>
         <v>46270</v>
       </c>
-      <c r="X5" s="119"/>
-      <c r="Y5" s="119"/>
-      <c r="Z5" s="119"/>
-      <c r="AA5" s="119"/>
-      <c r="AB5" s="119"/>
-      <c r="AC5" s="119"/>
-      <c r="AD5" s="120"/>
+      <c r="X5" s="115"/>
+      <c r="Y5" s="115"/>
+      <c r="Z5" s="115"/>
+      <c r="AA5" s="115"/>
+      <c r="AB5" s="115"/>
+      <c r="AC5" s="115"/>
+      <c r="AD5" s="95"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
       <c r="AI5" s="41"/>
       <c r="AJ5" s="41"/>
     </row>
-    <row r="6" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="42"/>
-      <c r="C6" s="111"/>
-      <c r="D6" s="113"/>
-      <c r="E6" s="111"/>
-      <c r="F6" s="113"/>
-      <c r="G6" s="147"/>
-      <c r="H6" s="148"/>
-      <c r="I6" s="147"/>
-      <c r="J6" s="148"/>
-      <c r="K6" s="147"/>
-      <c r="L6" s="149"/>
-      <c r="M6" s="149"/>
-      <c r="N6" s="148"/>
-      <c r="O6" s="147"/>
-      <c r="P6" s="149"/>
-      <c r="Q6" s="149"/>
-      <c r="R6" s="149"/>
-      <c r="S6" s="149"/>
-      <c r="T6" s="149"/>
-      <c r="U6" s="149"/>
-      <c r="V6" s="148"/>
-      <c r="W6" s="147"/>
-      <c r="X6" s="149"/>
-      <c r="Y6" s="149"/>
-      <c r="Z6" s="149"/>
-      <c r="AA6" s="149"/>
-      <c r="AB6" s="149"/>
-      <c r="AC6" s="149"/>
-      <c r="AD6" s="148"/>
+      <c r="C6" s="99"/>
+      <c r="D6" s="100"/>
+      <c r="E6" s="99"/>
+      <c r="F6" s="100"/>
+      <c r="G6" s="151"/>
+      <c r="H6" s="152"/>
+      <c r="I6" s="151"/>
+      <c r="J6" s="152"/>
+      <c r="K6" s="151"/>
+      <c r="L6" s="153"/>
+      <c r="M6" s="153"/>
+      <c r="N6" s="152"/>
+      <c r="O6" s="151"/>
+      <c r="P6" s="153"/>
+      <c r="Q6" s="153"/>
+      <c r="R6" s="153"/>
+      <c r="S6" s="153"/>
+      <c r="T6" s="153"/>
+      <c r="U6" s="153"/>
+      <c r="V6" s="152"/>
+      <c r="W6" s="151"/>
+      <c r="X6" s="153"/>
+      <c r="Y6" s="153"/>
+      <c r="Z6" s="153"/>
+      <c r="AA6" s="153"/>
+      <c r="AB6" s="153"/>
+      <c r="AC6" s="153"/>
+      <c r="AD6" s="152"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
-    <row r="7" spans="1:36" ht="10" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:36" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="C7" s="118">
+      <c r="C7" s="94">
         <f ca="1">W5+1</f>
         <v>46271</v>
       </c>
-      <c r="D7" s="120"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="130"/>
-      <c r="G7" s="129"/>
-      <c r="H7" s="130"/>
-      <c r="I7" s="129"/>
-      <c r="J7" s="130"/>
-      <c r="K7" s="129"/>
-      <c r="L7" s="131"/>
-      <c r="M7" s="131"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="108"/>
+      <c r="H7" s="109"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="109"/>
+      <c r="K7" s="108"/>
+      <c r="L7" s="110"/>
+      <c r="M7" s="110"/>
       <c r="N7" s="75"/>
-      <c r="O7" s="129"/>
-      <c r="P7" s="131"/>
-      <c r="Q7" s="131"/>
-      <c r="R7" s="131"/>
-      <c r="S7" s="131"/>
-      <c r="T7" s="131"/>
-      <c r="U7" s="131"/>
-      <c r="V7" s="130"/>
-      <c r="W7" s="129"/>
-      <c r="X7" s="131"/>
-      <c r="Y7" s="131"/>
-      <c r="Z7" s="131"/>
-      <c r="AA7" s="131"/>
-      <c r="AB7" s="131"/>
-      <c r="AC7" s="131"/>
-      <c r="AD7" s="130"/>
+      <c r="O7" s="108"/>
+      <c r="P7" s="110"/>
+      <c r="Q7" s="110"/>
+      <c r="R7" s="110"/>
+      <c r="S7" s="110"/>
+      <c r="T7" s="110"/>
+      <c r="U7" s="110"/>
+      <c r="V7" s="109"/>
+      <c r="W7" s="108"/>
+      <c r="X7" s="110"/>
+      <c r="Y7" s="110"/>
+      <c r="Z7" s="110"/>
+      <c r="AA7" s="110"/>
+      <c r="AB7" s="110"/>
+      <c r="AC7" s="110"/>
+      <c r="AD7" s="109"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
-      <c r="C8" s="118"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="132">
+      <c r="C8" s="94"/>
+      <c r="D8" s="95"/>
+      <c r="E8" s="96">
         <f ca="1">C7+1</f>
         <v>46272</v>
       </c>
-      <c r="F8" s="133"/>
-      <c r="G8" s="132">
+      <c r="F8" s="97"/>
+      <c r="G8" s="96">
         <f ca="1">E8+1</f>
         <v>46273</v>
       </c>
-      <c r="H8" s="133"/>
-      <c r="I8" s="132">
+      <c r="H8" s="97"/>
+      <c r="I8" s="96">
         <f ca="1">G8+1</f>
         <v>46274</v>
       </c>
-      <c r="J8" s="133"/>
-      <c r="K8" s="132">
+      <c r="J8" s="97"/>
+      <c r="K8" s="96">
         <f ca="1">I8+1</f>
         <v>46275</v>
       </c>
-      <c r="L8" s="134"/>
-      <c r="M8" s="134"/>
+      <c r="L8" s="98"/>
+      <c r="M8" s="98"/>
       <c r="N8" s="50"/>
-      <c r="O8" s="132">
+      <c r="O8" s="96">
         <f ca="1">K8+1</f>
         <v>46276</v>
       </c>
-      <c r="P8" s="134"/>
-      <c r="Q8" s="134"/>
-      <c r="R8" s="134"/>
-      <c r="S8" s="134"/>
-      <c r="T8" s="134"/>
-      <c r="U8" s="134"/>
-      <c r="V8" s="133"/>
-      <c r="W8" s="132">
+      <c r="P8" s="98"/>
+      <c r="Q8" s="98"/>
+      <c r="R8" s="98"/>
+      <c r="S8" s="98"/>
+      <c r="T8" s="98"/>
+      <c r="U8" s="98"/>
+      <c r="V8" s="97"/>
+      <c r="W8" s="96">
         <f ca="1">O8+1</f>
         <v>46277</v>
       </c>
-      <c r="X8" s="134"/>
-      <c r="Y8" s="134"/>
-      <c r="Z8" s="134"/>
-      <c r="AA8" s="134"/>
-      <c r="AB8" s="134"/>
-      <c r="AC8" s="134"/>
-      <c r="AD8" s="133"/>
+      <c r="X8" s="98"/>
+      <c r="Y8" s="98"/>
+      <c r="Z8" s="98"/>
+      <c r="AA8" s="98"/>
+      <c r="AB8" s="98"/>
+      <c r="AC8" s="98"/>
+      <c r="AD8" s="97"/>
       <c r="AF8" s="4"/>
     </row>
-    <row r="9" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="42"/>
-      <c r="C9" s="147"/>
-      <c r="D9" s="148"/>
-      <c r="E9" s="147"/>
-      <c r="F9" s="148"/>
-      <c r="G9" s="147"/>
-      <c r="H9" s="148"/>
-      <c r="I9" s="147"/>
-      <c r="J9" s="148"/>
-      <c r="K9" s="147"/>
-      <c r="L9" s="149"/>
-      <c r="M9" s="149"/>
-      <c r="N9" s="148"/>
-      <c r="O9" s="150" t="s">
-        <v>37</v>
-      </c>
-      <c r="P9" s="151"/>
-      <c r="Q9" s="151"/>
-      <c r="R9" s="151"/>
-      <c r="S9" s="151"/>
-      <c r="T9" s="151"/>
-      <c r="U9" s="151"/>
-      <c r="V9" s="152"/>
-      <c r="W9" s="147"/>
-      <c r="X9" s="149"/>
-      <c r="Y9" s="149"/>
-      <c r="Z9" s="149"/>
-      <c r="AA9" s="149"/>
-      <c r="AB9" s="149"/>
-      <c r="AC9" s="149"/>
-      <c r="AD9" s="148"/>
+      <c r="C9" s="151"/>
+      <c r="D9" s="152"/>
+      <c r="E9" s="151"/>
+      <c r="F9" s="152"/>
+      <c r="G9" s="151"/>
+      <c r="H9" s="152"/>
+      <c r="I9" s="151"/>
+      <c r="J9" s="152"/>
+      <c r="K9" s="151"/>
+      <c r="L9" s="153"/>
+      <c r="M9" s="153"/>
+      <c r="N9" s="152"/>
+      <c r="O9" s="154" t="s">
+        <v>36</v>
+      </c>
+      <c r="P9" s="156"/>
+      <c r="Q9" s="156"/>
+      <c r="R9" s="156"/>
+      <c r="S9" s="156"/>
+      <c r="T9" s="156"/>
+      <c r="U9" s="156"/>
+      <c r="V9" s="155"/>
+      <c r="W9" s="151"/>
+      <c r="X9" s="153"/>
+      <c r="Y9" s="153"/>
+      <c r="Z9" s="153"/>
+      <c r="AA9" s="153"/>
+      <c r="AB9" s="153"/>
+      <c r="AC9" s="153"/>
+      <c r="AD9" s="152"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
-    <row r="10" spans="1:36" s="43" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="42"/>
-      <c r="C10" s="118">
+      <c r="C10" s="94">
         <f ca="1">W8+1</f>
         <v>46278</v>
       </c>
-      <c r="D10" s="120"/>
+      <c r="D10" s="95"/>
       <c r="E10" s="45"/>
       <c r="F10" s="75"/>
       <c r="G10" s="45"/>
@@ -2656,99 +2694,99 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="42"/>
     </row>
-    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
-      <c r="C11" s="118"/>
-      <c r="D11" s="120"/>
-      <c r="E11" s="132">
+      <c r="C11" s="94"/>
+      <c r="D11" s="95"/>
+      <c r="E11" s="96">
         <f ca="1">C10+1</f>
         <v>46279</v>
       </c>
-      <c r="F11" s="133"/>
-      <c r="G11" s="132">
+      <c r="F11" s="97"/>
+      <c r="G11" s="96">
         <f ca="1">E11+1</f>
         <v>46280</v>
       </c>
-      <c r="H11" s="133"/>
-      <c r="I11" s="132">
+      <c r="H11" s="97"/>
+      <c r="I11" s="96">
         <f ca="1">G11+1</f>
         <v>46281</v>
       </c>
-      <c r="J11" s="133"/>
-      <c r="K11" s="132">
+      <c r="J11" s="97"/>
+      <c r="K11" s="96">
         <f ca="1">I11+1</f>
         <v>46282</v>
       </c>
-      <c r="L11" s="134"/>
-      <c r="M11" s="134"/>
+      <c r="L11" s="98"/>
+      <c r="M11" s="98"/>
       <c r="N11" s="50"/>
-      <c r="O11" s="132">
+      <c r="O11" s="96">
         <f ca="1">K11+1</f>
         <v>46283</v>
       </c>
-      <c r="P11" s="134"/>
-      <c r="Q11" s="134"/>
-      <c r="R11" s="134"/>
-      <c r="S11" s="134"/>
-      <c r="T11" s="134"/>
-      <c r="U11" s="134"/>
-      <c r="V11" s="133"/>
-      <c r="W11" s="132">
+      <c r="P11" s="98"/>
+      <c r="Q11" s="98"/>
+      <c r="R11" s="98"/>
+      <c r="S11" s="98"/>
+      <c r="T11" s="98"/>
+      <c r="U11" s="98"/>
+      <c r="V11" s="97"/>
+      <c r="W11" s="96">
         <f ca="1">O11+1</f>
         <v>46284</v>
       </c>
-      <c r="X11" s="134"/>
-      <c r="Y11" s="134"/>
-      <c r="Z11" s="134"/>
-      <c r="AA11" s="134"/>
-      <c r="AB11" s="134"/>
-      <c r="AC11" s="134"/>
-      <c r="AD11" s="133"/>
+      <c r="X11" s="98"/>
+      <c r="Y11" s="98"/>
+      <c r="Z11" s="98"/>
+      <c r="AA11" s="98"/>
+      <c r="AB11" s="98"/>
+      <c r="AC11" s="98"/>
+      <c r="AD11" s="97"/>
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="42"/>
-      <c r="C12" s="147"/>
-      <c r="D12" s="148"/>
-      <c r="E12" s="150" t="s">
-        <v>38</v>
-      </c>
-      <c r="F12" s="152"/>
-      <c r="G12" s="147"/>
-      <c r="H12" s="148"/>
-      <c r="I12" s="147"/>
-      <c r="J12" s="148"/>
-      <c r="K12" s="147"/>
-      <c r="L12" s="149"/>
-      <c r="M12" s="149"/>
-      <c r="N12" s="148"/>
-      <c r="O12" s="147"/>
-      <c r="P12" s="149"/>
-      <c r="Q12" s="149"/>
-      <c r="R12" s="149"/>
-      <c r="S12" s="149"/>
-      <c r="T12" s="149"/>
-      <c r="U12" s="149"/>
-      <c r="V12" s="148"/>
-      <c r="W12" s="147"/>
-      <c r="X12" s="149"/>
-      <c r="Y12" s="149"/>
-      <c r="Z12" s="149"/>
-      <c r="AA12" s="149"/>
-      <c r="AB12" s="149"/>
-      <c r="AC12" s="149"/>
-      <c r="AD12" s="148"/>
+      <c r="C12" s="151"/>
+      <c r="D12" s="152"/>
+      <c r="E12" s="154" t="s">
+        <v>37</v>
+      </c>
+      <c r="F12" s="155"/>
+      <c r="G12" s="151"/>
+      <c r="H12" s="152"/>
+      <c r="I12" s="151"/>
+      <c r="J12" s="152"/>
+      <c r="K12" s="151"/>
+      <c r="L12" s="153"/>
+      <c r="M12" s="153"/>
+      <c r="N12" s="152"/>
+      <c r="O12" s="151"/>
+      <c r="P12" s="153"/>
+      <c r="Q12" s="153"/>
+      <c r="R12" s="153"/>
+      <c r="S12" s="153"/>
+      <c r="T12" s="153"/>
+      <c r="U12" s="153"/>
+      <c r="V12" s="152"/>
+      <c r="W12" s="151"/>
+      <c r="X12" s="153"/>
+      <c r="Y12" s="153"/>
+      <c r="Z12" s="153"/>
+      <c r="AA12" s="153"/>
+      <c r="AB12" s="153"/>
+      <c r="AC12" s="153"/>
+      <c r="AD12" s="152"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
-    <row r="13" spans="1:36" s="43" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="42"/>
-      <c r="C13" s="118">
+      <c r="C13" s="94">
         <f ca="1">W11+1</f>
         <v>46285</v>
       </c>
-      <c r="D13" s="120"/>
+      <c r="D13" s="95"/>
       <c r="E13" s="45"/>
       <c r="F13" s="75"/>
       <c r="G13" s="45"/>
@@ -2778,114 +2816,114 @@
       <c r="AE13" s="7"/>
       <c r="AF13" s="42"/>
     </row>
-    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4"/>
-      <c r="C14" s="118"/>
-      <c r="D14" s="120"/>
-      <c r="E14" s="132">
+      <c r="C14" s="94"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="96">
         <f ca="1">C13+1</f>
         <v>46286</v>
       </c>
-      <c r="F14" s="133"/>
-      <c r="G14" s="132">
+      <c r="F14" s="97"/>
+      <c r="G14" s="96">
         <f ca="1">E14+1</f>
         <v>46287</v>
       </c>
-      <c r="H14" s="133"/>
-      <c r="I14" s="132">
+      <c r="H14" s="97"/>
+      <c r="I14" s="96">
         <f ca="1">G14+1</f>
         <v>46288</v>
       </c>
-      <c r="J14" s="133"/>
-      <c r="K14" s="132">
+      <c r="J14" s="97"/>
+      <c r="K14" s="96">
         <f ca="1">I14+1</f>
         <v>46289</v>
       </c>
-      <c r="L14" s="134"/>
-      <c r="M14" s="134"/>
+      <c r="L14" s="98"/>
+      <c r="M14" s="98"/>
       <c r="N14" s="50"/>
-      <c r="O14" s="132">
+      <c r="O14" s="96">
         <f ca="1">K14+1</f>
         <v>46290</v>
       </c>
-      <c r="P14" s="134"/>
-      <c r="Q14" s="134"/>
-      <c r="R14" s="134"/>
-      <c r="S14" s="134"/>
-      <c r="T14" s="134"/>
-      <c r="U14" s="134"/>
-      <c r="V14" s="133"/>
-      <c r="W14" s="132">
+      <c r="P14" s="98"/>
+      <c r="Q14" s="98"/>
+      <c r="R14" s="98"/>
+      <c r="S14" s="98"/>
+      <c r="T14" s="98"/>
+      <c r="U14" s="98"/>
+      <c r="V14" s="97"/>
+      <c r="W14" s="96">
         <f ca="1">O14+1</f>
         <v>46291</v>
       </c>
-      <c r="X14" s="134"/>
-      <c r="Y14" s="134"/>
-      <c r="Z14" s="134"/>
-      <c r="AA14" s="134"/>
-      <c r="AB14" s="134"/>
-      <c r="AC14" s="134"/>
-      <c r="AD14" s="133"/>
+      <c r="X14" s="98"/>
+      <c r="Y14" s="98"/>
+      <c r="Z14" s="98"/>
+      <c r="AA14" s="98"/>
+      <c r="AB14" s="98"/>
+      <c r="AC14" s="98"/>
+      <c r="AD14" s="97"/>
       <c r="AF14" s="4"/>
     </row>
-    <row r="15" spans="1:36" s="43" customFormat="1" ht="163" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:36" s="43" customFormat="1" ht="162.94999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="42"/>
-      <c r="C15" s="147"/>
-      <c r="D15" s="148"/>
-      <c r="E15" s="147"/>
-      <c r="F15" s="148"/>
-      <c r="G15" s="147"/>
-      <c r="H15" s="148"/>
-      <c r="I15" s="123"/>
-      <c r="J15" s="125"/>
-      <c r="K15" s="123"/>
-      <c r="L15" s="124"/>
-      <c r="M15" s="124"/>
-      <c r="N15" s="125"/>
-      <c r="O15" s="123"/>
-      <c r="P15" s="124"/>
-      <c r="Q15" s="124"/>
-      <c r="R15" s="124"/>
-      <c r="S15" s="124"/>
-      <c r="T15" s="124"/>
-      <c r="U15" s="124"/>
-      <c r="V15" s="125"/>
-      <c r="W15" s="123"/>
-      <c r="X15" s="124"/>
-      <c r="Y15" s="124"/>
-      <c r="Z15" s="124"/>
-      <c r="AA15" s="124"/>
-      <c r="AB15" s="124"/>
-      <c r="AC15" s="124"/>
-      <c r="AD15" s="125"/>
+      <c r="C15" s="151"/>
+      <c r="D15" s="152"/>
+      <c r="E15" s="151"/>
+      <c r="F15" s="152"/>
+      <c r="G15" s="151"/>
+      <c r="H15" s="152"/>
+      <c r="I15" s="104"/>
+      <c r="J15" s="105"/>
+      <c r="K15" s="104"/>
+      <c r="L15" s="113"/>
+      <c r="M15" s="113"/>
+      <c r="N15" s="105"/>
+      <c r="O15" s="104"/>
+      <c r="P15" s="113"/>
+      <c r="Q15" s="113"/>
+      <c r="R15" s="113"/>
+      <c r="S15" s="113"/>
+      <c r="T15" s="113"/>
+      <c r="U15" s="113"/>
+      <c r="V15" s="105"/>
+      <c r="W15" s="104"/>
+      <c r="X15" s="113"/>
+      <c r="Y15" s="113"/>
+      <c r="Z15" s="113"/>
+      <c r="AA15" s="113"/>
+      <c r="AB15" s="113"/>
+      <c r="AC15" s="113"/>
+      <c r="AD15" s="105"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
-    <row r="16" spans="1:36" s="43" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="42"/>
-      <c r="C16" s="118">
+      <c r="C16" s="94">
         <f ca="1">W14+1</f>
         <v>46292</v>
       </c>
-      <c r="D16" s="120"/>
+      <c r="D16" s="95"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
       <c r="H16" s="75"/>
-      <c r="I16" s="153"/>
-      <c r="J16" s="154"/>
+      <c r="I16" s="148"/>
+      <c r="J16" s="149"/>
       <c r="K16" s="66"/>
       <c r="L16" s="68"/>
       <c r="M16" s="68"/>
       <c r="N16" s="67"/>
-      <c r="O16" s="153"/>
-      <c r="P16" s="155"/>
-      <c r="Q16" s="155"/>
-      <c r="R16" s="155"/>
-      <c r="S16" s="155"/>
-      <c r="T16" s="155"/>
-      <c r="U16" s="155"/>
-      <c r="V16" s="154"/>
+      <c r="O16" s="148"/>
+      <c r="P16" s="150"/>
+      <c r="Q16" s="150"/>
+      <c r="R16" s="150"/>
+      <c r="S16" s="150"/>
+      <c r="T16" s="150"/>
+      <c r="U16" s="150"/>
+      <c r="V16" s="149"/>
       <c r="W16" s="45"/>
       <c r="X16" s="76"/>
       <c r="Y16" s="76"/>
@@ -2897,25 +2935,25 @@
       <c r="AE16" s="7"/>
       <c r="AF16" s="42"/>
     </row>
-    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
-      <c r="C17" s="118"/>
-      <c r="D17" s="120"/>
-      <c r="E17" s="132">
+      <c r="C17" s="94"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="96">
         <f ca="1">C16+1</f>
         <v>46293</v>
       </c>
-      <c r="F17" s="133"/>
-      <c r="G17" s="132">
+      <c r="F17" s="97"/>
+      <c r="G17" s="96">
         <f ca="1">E17+1</f>
         <v>46294</v>
       </c>
-      <c r="H17" s="133"/>
-      <c r="I17" s="132">
+      <c r="H17" s="97"/>
+      <c r="I17" s="96">
         <f ca="1">G17+1</f>
         <v>46295</v>
       </c>
-      <c r="J17" s="133"/>
+      <c r="J17" s="97"/>
       <c r="K17" s="46">
         <f ca="1">I17+1</f>
         <v>46296</v>
@@ -2923,93 +2961,93 @@
       <c r="L17" s="51"/>
       <c r="M17" s="51"/>
       <c r="N17" s="69"/>
-      <c r="O17" s="132">
+      <c r="O17" s="96">
         <f ca="1">K17+1</f>
         <v>46297</v>
       </c>
-      <c r="P17" s="134"/>
-      <c r="Q17" s="134"/>
-      <c r="R17" s="134"/>
-      <c r="S17" s="134"/>
-      <c r="T17" s="134"/>
-      <c r="U17" s="134"/>
-      <c r="V17" s="133"/>
-      <c r="W17" s="132">
+      <c r="P17" s="98"/>
+      <c r="Q17" s="98"/>
+      <c r="R17" s="98"/>
+      <c r="S17" s="98"/>
+      <c r="T17" s="98"/>
+      <c r="U17" s="98"/>
+      <c r="V17" s="97"/>
+      <c r="W17" s="96">
         <f ca="1">O17+1</f>
         <v>46298</v>
       </c>
-      <c r="X17" s="134"/>
-      <c r="Y17" s="134"/>
-      <c r="Z17" s="134"/>
-      <c r="AA17" s="134"/>
-      <c r="AB17" s="134"/>
-      <c r="AC17" s="134"/>
-      <c r="AD17" s="133"/>
+      <c r="X17" s="98"/>
+      <c r="Y17" s="98"/>
+      <c r="Z17" s="98"/>
+      <c r="AA17" s="98"/>
+      <c r="AB17" s="98"/>
+      <c r="AC17" s="98"/>
+      <c r="AD17" s="97"/>
       <c r="AF17" s="4"/>
     </row>
-    <row r="18" spans="1:42" s="43" customFormat="1" ht="147.4" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:42" s="43" customFormat="1" ht="147.4" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="42"/>
-      <c r="C18" s="126" t="s">
+      <c r="C18" s="106" t="s">
         <v>18</v>
       </c>
-      <c r="D18" s="128"/>
-      <c r="E18" s="123"/>
-      <c r="F18" s="125"/>
-      <c r="G18" s="123"/>
-      <c r="H18" s="125"/>
-      <c r="I18" s="126" t="s">
+      <c r="D18" s="107"/>
+      <c r="E18" s="104"/>
+      <c r="F18" s="105"/>
+      <c r="G18" s="104"/>
+      <c r="H18" s="105"/>
+      <c r="I18" s="106" t="s">
         <v>17</v>
       </c>
-      <c r="J18" s="128"/>
+      <c r="J18" s="107"/>
       <c r="K18" s="70"/>
       <c r="L18" s="71"/>
       <c r="M18" s="71"/>
       <c r="N18" s="72"/>
-      <c r="O18" s="111"/>
-      <c r="P18" s="112"/>
-      <c r="Q18" s="112"/>
-      <c r="R18" s="112"/>
-      <c r="S18" s="112"/>
-      <c r="T18" s="112"/>
-      <c r="U18" s="112"/>
-      <c r="V18" s="113"/>
-      <c r="W18" s="111"/>
-      <c r="X18" s="112"/>
-      <c r="Y18" s="112"/>
-      <c r="Z18" s="112"/>
-      <c r="AA18" s="112"/>
-      <c r="AB18" s="112"/>
-      <c r="AC18" s="112"/>
-      <c r="AD18" s="113"/>
+      <c r="O18" s="99"/>
+      <c r="P18" s="146"/>
+      <c r="Q18" s="146"/>
+      <c r="R18" s="146"/>
+      <c r="S18" s="146"/>
+      <c r="T18" s="146"/>
+      <c r="U18" s="146"/>
+      <c r="V18" s="100"/>
+      <c r="W18" s="99"/>
+      <c r="X18" s="146"/>
+      <c r="Y18" s="146"/>
+      <c r="Z18" s="146"/>
+      <c r="AA18" s="146"/>
+      <c r="AB18" s="146"/>
+      <c r="AC18" s="146"/>
+      <c r="AD18" s="100"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
-    <row r="19" spans="1:42" s="43" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="42"/>
-      <c r="C19" s="118">
+      <c r="C19" s="94">
         <f ca="1">W17+1</f>
         <v>46299</v>
       </c>
-      <c r="D19" s="120"/>
+      <c r="D19" s="95"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
       <c r="H19" s="75"/>
-      <c r="I19" s="153"/>
-      <c r="J19" s="154"/>
+      <c r="I19" s="148"/>
+      <c r="J19" s="149"/>
       <c r="K19" s="66"/>
       <c r="L19" s="68"/>
       <c r="M19" s="68"/>
       <c r="N19" s="67"/>
-      <c r="O19" s="153"/>
-      <c r="P19" s="155"/>
-      <c r="Q19" s="155"/>
-      <c r="R19" s="155"/>
-      <c r="S19" s="155"/>
-      <c r="T19" s="155"/>
-      <c r="U19" s="155"/>
-      <c r="V19" s="154"/>
+      <c r="O19" s="148"/>
+      <c r="P19" s="150"/>
+      <c r="Q19" s="150"/>
+      <c r="R19" s="150"/>
+      <c r="S19" s="150"/>
+      <c r="T19" s="150"/>
+      <c r="U19" s="150"/>
+      <c r="V19" s="149"/>
       <c r="W19" s="45"/>
       <c r="X19" s="76"/>
       <c r="Y19" s="76"/>
@@ -3021,25 +3059,25 @@
       <c r="AE19" s="7"/>
       <c r="AF19" s="42"/>
     </row>
-    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
-      <c r="C20" s="118"/>
-      <c r="D20" s="120"/>
-      <c r="E20" s="132">
+      <c r="C20" s="94"/>
+      <c r="D20" s="95"/>
+      <c r="E20" s="96">
         <f ca="1">C19+1</f>
         <v>46300</v>
       </c>
-      <c r="F20" s="133"/>
-      <c r="G20" s="132">
+      <c r="F20" s="97"/>
+      <c r="G20" s="96">
         <f ca="1">E20+1</f>
         <v>46301</v>
       </c>
-      <c r="H20" s="133"/>
-      <c r="I20" s="132">
+      <c r="H20" s="97"/>
+      <c r="I20" s="96">
         <f ca="1">G20+1</f>
         <v>46302</v>
       </c>
-      <c r="J20" s="133"/>
+      <c r="J20" s="97"/>
       <c r="K20" s="46">
         <f ca="1">I20+1</f>
         <v>46303</v>
@@ -3047,65 +3085,65 @@
       <c r="L20" s="51"/>
       <c r="M20" s="51"/>
       <c r="N20" s="69"/>
-      <c r="O20" s="132">
+      <c r="O20" s="96">
         <f ca="1">K20+1</f>
         <v>46304</v>
       </c>
-      <c r="P20" s="134"/>
-      <c r="Q20" s="134"/>
-      <c r="R20" s="134"/>
-      <c r="S20" s="134"/>
-      <c r="T20" s="134"/>
-      <c r="U20" s="134"/>
-      <c r="V20" s="133"/>
-      <c r="W20" s="132">
+      <c r="P20" s="98"/>
+      <c r="Q20" s="98"/>
+      <c r="R20" s="98"/>
+      <c r="S20" s="98"/>
+      <c r="T20" s="98"/>
+      <c r="U20" s="98"/>
+      <c r="V20" s="97"/>
+      <c r="W20" s="96">
         <f ca="1">O20+1</f>
         <v>46305</v>
       </c>
-      <c r="X20" s="134"/>
-      <c r="Y20" s="134"/>
-      <c r="Z20" s="134"/>
-      <c r="AA20" s="134"/>
-      <c r="AB20" s="134"/>
-      <c r="AC20" s="134"/>
-      <c r="AD20" s="133"/>
+      <c r="X20" s="98"/>
+      <c r="Y20" s="98"/>
+      <c r="Z20" s="98"/>
+      <c r="AA20" s="98"/>
+      <c r="AB20" s="98"/>
+      <c r="AC20" s="98"/>
+      <c r="AD20" s="97"/>
       <c r="AF20" s="4"/>
     </row>
-    <row r="21" spans="1:42" s="43" customFormat="1" ht="166.9" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:42" s="43" customFormat="1" ht="166.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="42"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="111"/>
-      <c r="H21" s="113"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="113"/>
+      <c r="C21" s="99"/>
+      <c r="D21" s="100"/>
+      <c r="E21" s="99"/>
+      <c r="F21" s="100"/>
+      <c r="G21" s="99"/>
+      <c r="H21" s="100"/>
+      <c r="I21" s="99"/>
+      <c r="J21" s="100"/>
       <c r="K21" s="70"/>
       <c r="L21" s="71"/>
       <c r="M21" s="71"/>
       <c r="N21" s="72"/>
-      <c r="O21" s="111"/>
-      <c r="P21" s="112"/>
-      <c r="Q21" s="112"/>
-      <c r="R21" s="112"/>
-      <c r="S21" s="112"/>
-      <c r="T21" s="112"/>
-      <c r="U21" s="112"/>
-      <c r="V21" s="113"/>
-      <c r="W21" s="111"/>
-      <c r="X21" s="112"/>
-      <c r="Y21" s="112"/>
-      <c r="Z21" s="112"/>
-      <c r="AA21" s="112"/>
-      <c r="AB21" s="112"/>
-      <c r="AC21" s="112"/>
-      <c r="AD21" s="113"/>
+      <c r="O21" s="99"/>
+      <c r="P21" s="146"/>
+      <c r="Q21" s="146"/>
+      <c r="R21" s="146"/>
+      <c r="S21" s="146"/>
+      <c r="T21" s="146"/>
+      <c r="U21" s="146"/>
+      <c r="V21" s="100"/>
+      <c r="W21" s="99"/>
+      <c r="X21" s="146"/>
+      <c r="Y21" s="146"/>
+      <c r="Z21" s="146"/>
+      <c r="AA21" s="146"/>
+      <c r="AB21" s="146"/>
+      <c r="AC21" s="146"/>
+      <c r="AD21" s="100"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
     </row>
-    <row r="22" spans="1:42" s="7" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52"/>
@@ -3137,7 +3175,7 @@
       <c r="AD22" s="55"/>
       <c r="AF22" s="4"/>
     </row>
-    <row r="23" spans="1:42" s="7" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="56"/>
@@ -3171,61 +3209,61 @@
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
     </row>
-    <row r="24" spans="1:42" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:42" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="M24" s="1"/>
       <c r="AF24" s="1"/>
     </row>
-    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
-      <c r="C25" s="143" t="s">
+      <c r="C25" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="143"/>
-      <c r="E25" s="143"/>
-      <c r="F25" s="143"/>
-      <c r="G25" s="143"/>
-      <c r="H25" s="143"/>
-      <c r="I25" s="143"/>
-      <c r="J25" s="143"/>
-      <c r="K25" s="143"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="86"/>
+      <c r="H25" s="86"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="86"/>
+      <c r="K25" s="86"/>
       <c r="L25" s="60"/>
       <c r="M25" s="1"/>
-      <c r="O25" s="144">
+      <c r="O25" s="87">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)-1,1)</f>
         <v>46235</v>
       </c>
-      <c r="P25" s="144"/>
-      <c r="Q25" s="144"/>
-      <c r="R25" s="144"/>
-      <c r="S25" s="144"/>
-      <c r="T25" s="144"/>
-      <c r="U25" s="144"/>
+      <c r="P25" s="87"/>
+      <c r="Q25" s="87"/>
+      <c r="R25" s="87"/>
+      <c r="S25" s="87"/>
+      <c r="T25" s="87"/>
+      <c r="U25" s="87"/>
       <c r="V25" s="61"/>
       <c r="W25" s="61"/>
-      <c r="X25" s="144">
+      <c r="X25" s="87">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)+1,1)</f>
         <v>46296</v>
       </c>
-      <c r="Y25" s="144"/>
-      <c r="Z25" s="144"/>
-      <c r="AA25" s="144"/>
-      <c r="AB25" s="144"/>
-      <c r="AC25" s="144"/>
-      <c r="AD25" s="144"/>
+      <c r="Y25" s="87"/>
+      <c r="Z25" s="87"/>
+      <c r="AA25" s="87"/>
+      <c r="AB25" s="87"/>
+      <c r="AC25" s="87"/>
+      <c r="AD25" s="87"/>
       <c r="AF25" s="1"/>
     </row>
-    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
-      <c r="C26" s="143"/>
-      <c r="D26" s="143"/>
-      <c r="E26" s="143"/>
-      <c r="F26" s="143"/>
-      <c r="G26" s="143"/>
-      <c r="H26" s="143"/>
-      <c r="I26" s="143"/>
-      <c r="J26" s="143"/>
-      <c r="K26" s="143"/>
+      <c r="C26" s="86"/>
+      <c r="D26" s="86"/>
+      <c r="E26" s="86"/>
+      <c r="F26" s="86"/>
+      <c r="G26" s="86"/>
+      <c r="H26" s="86"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="K26" s="86"/>
       <c r="L26" s="60"/>
       <c r="M26" s="1"/>
       <c r="O26" s="62" t="str">
@@ -3288,19 +3326,19 @@
       </c>
       <c r="AF26" s="1"/>
     </row>
-    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
-      <c r="C27" s="115" t="s">
+      <c r="C27" s="88" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="115"/>
-      <c r="E27" s="115"/>
-      <c r="F27" s="115"/>
-      <c r="G27" s="115"/>
-      <c r="H27" s="115"/>
-      <c r="I27" s="115"/>
-      <c r="J27" s="115"/>
-      <c r="K27" s="115"/>
+      <c r="D27" s="88"/>
+      <c r="E27" s="88"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="88"/>
+      <c r="H27" s="88"/>
+      <c r="I27" s="88"/>
+      <c r="J27" s="88"/>
+      <c r="K27" s="88"/>
       <c r="M27" s="1"/>
       <c r="O27" s="64" t="str">
         <f t="shared" ref="O27:U32" ca="1" si="0">IF(MONTH($O$25)&lt;&gt;MONTH($O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1)),"",$O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1))</f>
@@ -3362,19 +3400,19 @@
       </c>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
-      <c r="C28" s="114" t="s">
+      <c r="C28" s="89" t="s">
         <v>21</v>
       </c>
-      <c r="D28" s="114"/>
-      <c r="E28" s="114"/>
-      <c r="F28" s="114"/>
-      <c r="G28" s="114"/>
-      <c r="H28" s="114"/>
-      <c r="I28" s="114"/>
-      <c r="J28" s="114"/>
-      <c r="K28" s="114"/>
+      <c r="D28" s="89"/>
+      <c r="E28" s="89"/>
+      <c r="F28" s="89"/>
+      <c r="G28" s="89"/>
+      <c r="H28" s="89"/>
+      <c r="I28" s="89"/>
+      <c r="J28" s="89"/>
+      <c r="K28" s="89"/>
       <c r="M28" s="1"/>
       <c r="O28" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3436,17 +3474,17 @@
       </c>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
-      <c r="C29" s="115"/>
-      <c r="D29" s="115"/>
-      <c r="E29" s="115"/>
-      <c r="F29" s="115"/>
-      <c r="G29" s="115"/>
-      <c r="H29" s="115"/>
-      <c r="I29" s="115"/>
-      <c r="J29" s="115"/>
-      <c r="K29" s="115"/>
+      <c r="C29" s="88"/>
+      <c r="D29" s="88"/>
+      <c r="E29" s="88"/>
+      <c r="F29" s="88"/>
+      <c r="G29" s="88"/>
+      <c r="H29" s="88"/>
+      <c r="I29" s="88"/>
+      <c r="J29" s="88"/>
+      <c r="K29" s="88"/>
       <c r="M29" s="1"/>
       <c r="O29" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3508,19 +3546,19 @@
       </c>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
-      <c r="C30" s="114" t="s">
+      <c r="C30" s="89" t="s">
         <v>22</v>
       </c>
-      <c r="D30" s="114"/>
-      <c r="E30" s="114"/>
-      <c r="F30" s="114"/>
-      <c r="G30" s="114"/>
-      <c r="H30" s="114"/>
-      <c r="I30" s="114"/>
-      <c r="J30" s="114"/>
-      <c r="K30" s="114"/>
+      <c r="D30" s="89"/>
+      <c r="E30" s="89"/>
+      <c r="F30" s="89"/>
+      <c r="G30" s="89"/>
+      <c r="H30" s="89"/>
+      <c r="I30" s="89"/>
+      <c r="J30" s="89"/>
+      <c r="K30" s="89"/>
       <c r="M30" s="1"/>
       <c r="O30" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3582,17 +3620,17 @@
       </c>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
-      <c r="C31" s="115"/>
-      <c r="D31" s="115"/>
-      <c r="E31" s="115"/>
-      <c r="F31" s="115"/>
-      <c r="G31" s="115"/>
-      <c r="H31" s="115"/>
-      <c r="I31" s="115"/>
-      <c r="J31" s="115"/>
-      <c r="K31" s="115"/>
+      <c r="C31" s="88"/>
+      <c r="D31" s="88"/>
+      <c r="E31" s="88"/>
+      <c r="F31" s="88"/>
+      <c r="G31" s="88"/>
+      <c r="H31" s="88"/>
+      <c r="I31" s="88"/>
+      <c r="J31" s="88"/>
+      <c r="K31" s="88"/>
       <c r="M31" s="1"/>
       <c r="O31" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -3654,7 +3692,7 @@
       </c>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="M32" s="1"/>
       <c r="O32" s="64">
@@ -3717,7 +3755,7 @@
       </c>
       <c r="AF32" s="1"/>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="M33" s="1"/>
       <c r="O33" s="64"/>
@@ -3738,7 +3776,7 @@
       <c r="AD33" s="65"/>
       <c r="AF33" s="1"/>
     </row>
-    <row r="34" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -3772,69 +3810,158 @@
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
     </row>
-    <row r="38" spans="1:32" ht="12.9" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D39" s="83" t="s">
+    <row r="38" spans="1:32" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D39" s="118" t="s">
         <v>23</v>
       </c>
-      <c r="E39" s="84"/>
-      <c r="F39" s="85"/>
-      <c r="G39" s="89">
+      <c r="E39" s="119"/>
+      <c r="F39" s="120"/>
+      <c r="G39" s="124">
         <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
         <v>5</v>
       </c>
-      <c r="H39" s="90"/>
-      <c r="I39" s="83" t="s">
+      <c r="H39" s="125"/>
+      <c r="I39" s="118" t="s">
         <v>26</v>
       </c>
-      <c r="J39" s="93"/>
-      <c r="K39" s="95" t="s">
+      <c r="J39" s="128"/>
+      <c r="K39" s="130" t="s">
         <v>24</v>
       </c>
-      <c r="L39" s="96"/>
-      <c r="M39" s="99">
+      <c r="L39" s="131"/>
+      <c r="M39" s="134">
         <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
         <v>1.0000000000000027</v>
       </c>
-      <c r="N39" s="100"/>
-      <c r="O39" s="100"/>
-      <c r="P39" s="100"/>
-      <c r="Q39" s="100"/>
-      <c r="R39" s="101"/>
-      <c r="S39" s="105" t="s">
+      <c r="N39" s="135"/>
+      <c r="O39" s="135"/>
+      <c r="P39" s="135"/>
+      <c r="Q39" s="135"/>
+      <c r="R39" s="136"/>
+      <c r="S39" s="140" t="s">
         <v>25</v>
       </c>
-      <c r="T39" s="106"/>
-      <c r="U39" s="106"/>
-      <c r="V39" s="106"/>
-      <c r="W39" s="106"/>
-      <c r="X39" s="107"/>
-    </row>
-    <row r="40" spans="1:32" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D40" s="86"/>
-      <c r="E40" s="87"/>
-      <c r="F40" s="88"/>
-      <c r="G40" s="91"/>
-      <c r="H40" s="92"/>
-      <c r="I40" s="86"/>
-      <c r="J40" s="94"/>
-      <c r="K40" s="97"/>
-      <c r="L40" s="98"/>
-      <c r="M40" s="102"/>
-      <c r="N40" s="103"/>
-      <c r="O40" s="103"/>
-      <c r="P40" s="103"/>
-      <c r="Q40" s="103"/>
-      <c r="R40" s="104"/>
-      <c r="S40" s="108"/>
-      <c r="T40" s="109"/>
-      <c r="U40" s="109"/>
-      <c r="V40" s="109"/>
-      <c r="W40" s="109"/>
-      <c r="X40" s="110"/>
+      <c r="T39" s="141"/>
+      <c r="U39" s="141"/>
+      <c r="V39" s="141"/>
+      <c r="W39" s="141"/>
+      <c r="X39" s="142"/>
+    </row>
+    <row r="40" spans="1:32" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D40" s="121"/>
+      <c r="E40" s="122"/>
+      <c r="F40" s="123"/>
+      <c r="G40" s="126"/>
+      <c r="H40" s="127"/>
+      <c r="I40" s="121"/>
+      <c r="J40" s="129"/>
+      <c r="K40" s="132"/>
+      <c r="L40" s="133"/>
+      <c r="M40" s="137"/>
+      <c r="N40" s="138"/>
+      <c r="O40" s="138"/>
+      <c r="P40" s="138"/>
+      <c r="Q40" s="138"/>
+      <c r="R40" s="139"/>
+      <c r="S40" s="143"/>
+      <c r="T40" s="144"/>
+      <c r="U40" s="144"/>
+      <c r="V40" s="144"/>
+      <c r="W40" s="144"/>
+      <c r="X40" s="145"/>
     </row>
   </sheetData>
   <mergeCells count="110">
+    <mergeCell ref="D39:F40"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="K39:L40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="S39:X40"/>
+    <mergeCell ref="M39:R40"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="O20:V20"/>
+    <mergeCell ref="C30:K31"/>
+    <mergeCell ref="C2:AD2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="W5:AD5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:V6"/>
+    <mergeCell ref="W6:AD6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="O5:V5"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="W7:AD7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="O8:V8"/>
+    <mergeCell ref="W8:AD8"/>
+    <mergeCell ref="O7:V7"/>
+    <mergeCell ref="W9:AD9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="O11:V11"/>
+    <mergeCell ref="W11:AD11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:V9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="W12:AD12"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O14:V14"/>
+    <mergeCell ref="W14:AD14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="O12:V12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="W15:AD15"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="O17:V17"/>
+    <mergeCell ref="W17:AD17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="O15:V15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="O16:V16"/>
     <mergeCell ref="W18:AD18"/>
     <mergeCell ref="C25:K26"/>
     <mergeCell ref="O25:U25"/>
@@ -3856,95 +3983,6 @@
     <mergeCell ref="O21:V21"/>
     <mergeCell ref="W21:AD21"/>
     <mergeCell ref="O19:V19"/>
-    <mergeCell ref="W15:AD15"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="O17:V17"/>
-    <mergeCell ref="W17:AD17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="O15:V15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="O16:V16"/>
-    <mergeCell ref="W12:AD12"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="O14:V14"/>
-    <mergeCell ref="W14:AD14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="O12:V12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="W9:AD9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="O11:V11"/>
-    <mergeCell ref="W11:AD11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:V9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="W7:AD7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="O8:V8"/>
-    <mergeCell ref="W8:AD8"/>
-    <mergeCell ref="O7:V7"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:V6"/>
-    <mergeCell ref="W6:AD6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="O5:V5"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="C2:AD2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="W5:AD5"/>
-    <mergeCell ref="D39:F40"/>
-    <mergeCell ref="G39:H40"/>
-    <mergeCell ref="K39:L40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="S39:X40"/>
-    <mergeCell ref="M39:R40"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="O20:V20"/>
-    <mergeCell ref="C30:K31"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 E5 G5 I5 K5:L5 O5 W5 C7 E8 G8 I8 K8:L8 O8 W8 C10 E11 G11 I11 K11:L11 O11 W11 C13 E14 G14 I14 K14:L14 O14 W14 C16 E17 G17 I17 K17:L17 O17 W17">
     <cfRule type="expression" dxfId="11" priority="3">
@@ -3983,25 +4021,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AP40"/>
-  <sheetFormatPr defaultColWidth="8.71875" defaultRowHeight="12.6" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="5.5546875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="5.5546875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="5.5546875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.5546875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="5.5546875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="15.5546875" style="3" customWidth="1"/>
-    <col min="11" max="14" width="5.5546875" style="3" customWidth="1"/>
-    <col min="15" max="30" width="2.5546875" style="3" customWidth="1"/>
-    <col min="31" max="32" width="5.5546875" style="3" customWidth="1"/>
-    <col min="33" max="33" width="17.1640625" style="3" customWidth="1"/>
-    <col min="34" max="34" width="10.44140625" style="3" customWidth="1"/>
-    <col min="35" max="16384" width="8.71875" style="3"/>
+    <col min="1" max="3" width="5.5703125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="5.5703125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="5.5703125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="5.5703125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="3" customWidth="1"/>
+    <col min="11" max="14" width="5.5703125" style="3" customWidth="1"/>
+    <col min="15" max="30" width="2.5703125" style="3" customWidth="1"/>
+    <col min="31" max="32" width="5.5703125" style="3" customWidth="1"/>
+    <col min="33" max="33" width="17.140625" style="3" customWidth="1"/>
+    <col min="34" max="34" width="10.42578125" style="3" customWidth="1"/>
+    <col min="35" max="16384" width="8.7109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4035,7 +4073,7 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="2.15">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A2" s="29"/>
       <c r="C2" s="116">
         <f ca="1">DATE(About!P8,10,1)</f>
@@ -4070,7 +4108,7 @@
       <c r="AD2" s="116"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="2.15">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -4090,7 +4128,7 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="35"/>
       <c r="C4" s="117">
         <f ca="1">C5</f>
@@ -4147,233 +4185,233 @@
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="C5" s="118">
+      <c r="C5" s="94">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46292</v>
       </c>
-      <c r="D5" s="120"/>
-      <c r="E5" s="118">
+      <c r="D5" s="95"/>
+      <c r="E5" s="94">
         <f ca="1">C5+1</f>
         <v>46293</v>
       </c>
-      <c r="F5" s="120"/>
-      <c r="G5" s="118">
+      <c r="F5" s="95"/>
+      <c r="G5" s="94">
         <f ca="1">E5+1</f>
         <v>46294</v>
       </c>
-      <c r="H5" s="120"/>
-      <c r="I5" s="118">
+      <c r="H5" s="95"/>
+      <c r="I5" s="94">
         <f ca="1">G5+1</f>
         <v>46295</v>
       </c>
-      <c r="J5" s="120"/>
-      <c r="K5" s="118">
+      <c r="J5" s="95"/>
+      <c r="K5" s="94">
         <f ca="1">I5+1</f>
         <v>46296</v>
       </c>
-      <c r="L5" s="119"/>
-      <c r="M5" s="119"/>
+      <c r="L5" s="115"/>
+      <c r="M5" s="115"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="118">
+      <c r="O5" s="94">
         <f ca="1">K5+1</f>
         <v>46297</v>
       </c>
-      <c r="P5" s="119"/>
-      <c r="Q5" s="119"/>
-      <c r="R5" s="119"/>
-      <c r="S5" s="119"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="120"/>
-      <c r="W5" s="118">
+      <c r="P5" s="115"/>
+      <c r="Q5" s="115"/>
+      <c r="R5" s="115"/>
+      <c r="S5" s="115"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="115"/>
+      <c r="V5" s="95"/>
+      <c r="W5" s="94">
         <f ca="1">O5+1</f>
         <v>46298</v>
       </c>
-      <c r="X5" s="119"/>
-      <c r="Y5" s="119"/>
-      <c r="Z5" s="119"/>
-      <c r="AA5" s="119"/>
-      <c r="AB5" s="119"/>
-      <c r="AC5" s="119"/>
-      <c r="AD5" s="120"/>
+      <c r="X5" s="115"/>
+      <c r="Y5" s="115"/>
+      <c r="Z5" s="115"/>
+      <c r="AA5" s="115"/>
+      <c r="AB5" s="115"/>
+      <c r="AC5" s="115"/>
+      <c r="AD5" s="95"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
       <c r="AI5" s="41"/>
       <c r="AJ5" s="41"/>
     </row>
-    <row r="6" spans="1:36" s="43" customFormat="1" ht="131.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:36" s="43" customFormat="1" ht="131.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="42"/>
-      <c r="C6" s="121"/>
-      <c r="D6" s="122"/>
-      <c r="E6" s="121"/>
-      <c r="F6" s="122"/>
-      <c r="G6" s="121"/>
-      <c r="H6" s="122"/>
-      <c r="I6" s="121"/>
-      <c r="J6" s="122"/>
-      <c r="K6" s="123"/>
-      <c r="L6" s="124"/>
-      <c r="M6" s="124"/>
-      <c r="N6" s="125"/>
-      <c r="O6" s="123"/>
-      <c r="P6" s="124"/>
-      <c r="Q6" s="124"/>
-      <c r="R6" s="124"/>
-      <c r="S6" s="124"/>
-      <c r="T6" s="124"/>
-      <c r="U6" s="124"/>
-      <c r="V6" s="125"/>
-      <c r="W6" s="126" t="s">
+      <c r="C6" s="111"/>
+      <c r="D6" s="112"/>
+      <c r="E6" s="111"/>
+      <c r="F6" s="112"/>
+      <c r="G6" s="111"/>
+      <c r="H6" s="112"/>
+      <c r="I6" s="111"/>
+      <c r="J6" s="112"/>
+      <c r="K6" s="104"/>
+      <c r="L6" s="113"/>
+      <c r="M6" s="113"/>
+      <c r="N6" s="105"/>
+      <c r="O6" s="104"/>
+      <c r="P6" s="113"/>
+      <c r="Q6" s="113"/>
+      <c r="R6" s="113"/>
+      <c r="S6" s="113"/>
+      <c r="T6" s="113"/>
+      <c r="U6" s="113"/>
+      <c r="V6" s="105"/>
+      <c r="W6" s="106" t="s">
         <v>19</v>
       </c>
-      <c r="X6" s="127"/>
-      <c r="Y6" s="127"/>
-      <c r="Z6" s="127"/>
-      <c r="AA6" s="127"/>
-      <c r="AB6" s="127"/>
-      <c r="AC6" s="127"/>
-      <c r="AD6" s="128"/>
+      <c r="X6" s="114"/>
+      <c r="Y6" s="114"/>
+      <c r="Z6" s="114"/>
+      <c r="AA6" s="114"/>
+      <c r="AB6" s="114"/>
+      <c r="AC6" s="114"/>
+      <c r="AD6" s="107"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
-    <row r="7" spans="1:36" ht="10" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:36" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="C7" s="118">
+      <c r="C7" s="94">
         <f ca="1">W5+1</f>
         <v>46299</v>
       </c>
-      <c r="D7" s="120"/>
-      <c r="E7" s="129"/>
-      <c r="F7" s="130"/>
-      <c r="G7" s="129"/>
-      <c r="H7" s="130"/>
-      <c r="I7" s="129"/>
-      <c r="J7" s="130"/>
-      <c r="K7" s="129"/>
-      <c r="L7" s="131"/>
-      <c r="M7" s="131"/>
+      <c r="D7" s="95"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="109"/>
+      <c r="G7" s="108"/>
+      <c r="H7" s="109"/>
+      <c r="I7" s="108"/>
+      <c r="J7" s="109"/>
+      <c r="K7" s="108"/>
+      <c r="L7" s="110"/>
+      <c r="M7" s="110"/>
       <c r="N7" s="75"/>
-      <c r="O7" s="129"/>
-      <c r="P7" s="131"/>
-      <c r="Q7" s="131"/>
-      <c r="R7" s="131"/>
-      <c r="S7" s="131"/>
-      <c r="T7" s="131"/>
-      <c r="U7" s="131"/>
-      <c r="V7" s="130"/>
-      <c r="W7" s="129"/>
-      <c r="X7" s="131"/>
-      <c r="Y7" s="131"/>
-      <c r="Z7" s="131"/>
-      <c r="AA7" s="131"/>
-      <c r="AB7" s="131"/>
-      <c r="AC7" s="131"/>
-      <c r="AD7" s="130"/>
+      <c r="O7" s="108"/>
+      <c r="P7" s="110"/>
+      <c r="Q7" s="110"/>
+      <c r="R7" s="110"/>
+      <c r="S7" s="110"/>
+      <c r="T7" s="110"/>
+      <c r="U7" s="110"/>
+      <c r="V7" s="109"/>
+      <c r="W7" s="108"/>
+      <c r="X7" s="110"/>
+      <c r="Y7" s="110"/>
+      <c r="Z7" s="110"/>
+      <c r="AA7" s="110"/>
+      <c r="AB7" s="110"/>
+      <c r="AC7" s="110"/>
+      <c r="AD7" s="109"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
-      <c r="C8" s="118"/>
-      <c r="D8" s="120"/>
-      <c r="E8" s="132">
+      <c r="C8" s="94"/>
+      <c r="D8" s="95"/>
+      <c r="E8" s="96">
         <f ca="1">C7+1</f>
         <v>46300</v>
       </c>
-      <c r="F8" s="133"/>
-      <c r="G8" s="132">
+      <c r="F8" s="97"/>
+      <c r="G8" s="96">
         <f ca="1">E8+1</f>
         <v>46301</v>
       </c>
-      <c r="H8" s="133"/>
-      <c r="I8" s="132">
+      <c r="H8" s="97"/>
+      <c r="I8" s="96">
         <f ca="1">G8+1</f>
         <v>46302</v>
       </c>
-      <c r="J8" s="133"/>
-      <c r="K8" s="132">
+      <c r="J8" s="97"/>
+      <c r="K8" s="96">
         <f ca="1">I8+1</f>
         <v>46303</v>
       </c>
-      <c r="L8" s="134"/>
-      <c r="M8" s="134"/>
+      <c r="L8" s="98"/>
+      <c r="M8" s="98"/>
       <c r="N8" s="50"/>
-      <c r="O8" s="132">
+      <c r="O8" s="96">
         <f ca="1">K8+1</f>
         <v>46304</v>
       </c>
-      <c r="P8" s="134"/>
-      <c r="Q8" s="134"/>
-      <c r="R8" s="134"/>
-      <c r="S8" s="134"/>
-      <c r="T8" s="134"/>
-      <c r="U8" s="134"/>
-      <c r="V8" s="133"/>
-      <c r="W8" s="132">
+      <c r="P8" s="98"/>
+      <c r="Q8" s="98"/>
+      <c r="R8" s="98"/>
+      <c r="S8" s="98"/>
+      <c r="T8" s="98"/>
+      <c r="U8" s="98"/>
+      <c r="V8" s="97"/>
+      <c r="W8" s="96">
         <f ca="1">O8+1</f>
         <v>46305</v>
       </c>
-      <c r="X8" s="134"/>
-      <c r="Y8" s="134"/>
-      <c r="Z8" s="134"/>
-      <c r="AA8" s="134"/>
-      <c r="AB8" s="134"/>
-      <c r="AC8" s="134"/>
-      <c r="AD8" s="133"/>
+      <c r="X8" s="98"/>
+      <c r="Y8" s="98"/>
+      <c r="Z8" s="98"/>
+      <c r="AA8" s="98"/>
+      <c r="AB8" s="98"/>
+      <c r="AC8" s="98"/>
+      <c r="AD8" s="97"/>
       <c r="AF8" s="4"/>
     </row>
-    <row r="9" spans="1:36" s="43" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:36" s="43" customFormat="1" ht="210.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="42"/>
-      <c r="C9" s="123"/>
-      <c r="D9" s="125"/>
-      <c r="E9" s="126" t="s">
+      <c r="C9" s="104"/>
+      <c r="D9" s="105"/>
+      <c r="E9" s="106" t="s">
         <v>28</v>
       </c>
-      <c r="F9" s="128"/>
-      <c r="G9" s="126" t="s">
+      <c r="F9" s="107"/>
+      <c r="G9" s="106" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="128"/>
-      <c r="I9" s="123" t="s">
+      <c r="H9" s="107"/>
+      <c r="I9" s="167" t="s">
         <v>34</v>
       </c>
-      <c r="J9" s="125"/>
-      <c r="K9" s="135"/>
-      <c r="L9" s="136"/>
-      <c r="M9" s="136"/>
-      <c r="N9" s="137"/>
-      <c r="O9" s="135" t="s">
-        <v>50</v>
-      </c>
-      <c r="P9" s="136"/>
-      <c r="Q9" s="136"/>
-      <c r="R9" s="136"/>
-      <c r="S9" s="136"/>
-      <c r="T9" s="136"/>
-      <c r="U9" s="136"/>
-      <c r="V9" s="137"/>
-      <c r="W9" s="135" t="s">
-        <v>51</v>
-      </c>
-      <c r="X9" s="136"/>
-      <c r="Y9" s="136"/>
-      <c r="Z9" s="136"/>
-      <c r="AA9" s="136"/>
-      <c r="AB9" s="136"/>
-      <c r="AC9" s="136"/>
-      <c r="AD9" s="137"/>
+      <c r="J9" s="105"/>
+      <c r="K9" s="83"/>
+      <c r="L9" s="84"/>
+      <c r="M9" s="84"/>
+      <c r="N9" s="85"/>
+      <c r="O9" s="83" t="s">
+        <v>60</v>
+      </c>
+      <c r="P9" s="84"/>
+      <c r="Q9" s="84"/>
+      <c r="R9" s="84"/>
+      <c r="S9" s="84"/>
+      <c r="T9" s="84"/>
+      <c r="U9" s="84"/>
+      <c r="V9" s="85"/>
+      <c r="W9" s="83" t="s">
+        <v>48</v>
+      </c>
+      <c r="X9" s="84"/>
+      <c r="Y9" s="84"/>
+      <c r="Z9" s="84"/>
+      <c r="AA9" s="84"/>
+      <c r="AB9" s="84"/>
+      <c r="AC9" s="84"/>
+      <c r="AD9" s="85"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
-    <row r="10" spans="1:36" s="43" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="42"/>
-      <c r="C10" s="118">
+      <c r="C10" s="94">
         <f ca="1">W8+1</f>
         <v>46306</v>
       </c>
-      <c r="D10" s="120"/>
+      <c r="D10" s="95"/>
       <c r="E10" s="45"/>
       <c r="F10" s="75"/>
       <c r="G10" s="45"/>
@@ -4403,111 +4441,109 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="42"/>
     </row>
-    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
-      <c r="C11" s="118"/>
-      <c r="D11" s="120"/>
-      <c r="E11" s="132">
+      <c r="C11" s="94"/>
+      <c r="D11" s="95"/>
+      <c r="E11" s="96">
         <f ca="1">C10+1</f>
         <v>46307</v>
       </c>
-      <c r="F11" s="133"/>
-      <c r="G11" s="132">
+      <c r="F11" s="97"/>
+      <c r="G11" s="96">
         <f ca="1">E11+1</f>
         <v>46308</v>
       </c>
-      <c r="H11" s="133"/>
-      <c r="I11" s="132">
+      <c r="H11" s="97"/>
+      <c r="I11" s="96">
         <f ca="1">G11+1</f>
         <v>46309</v>
       </c>
-      <c r="J11" s="133"/>
-      <c r="K11" s="132">
+      <c r="J11" s="97"/>
+      <c r="K11" s="96">
         <f ca="1">I11+1</f>
         <v>46310</v>
       </c>
-      <c r="L11" s="134"/>
-      <c r="M11" s="134"/>
+      <c r="L11" s="98"/>
+      <c r="M11" s="98"/>
       <c r="N11" s="50"/>
-      <c r="O11" s="132">
+      <c r="O11" s="96">
         <f ca="1">K11+1</f>
         <v>46311</v>
       </c>
-      <c r="P11" s="134"/>
-      <c r="Q11" s="134"/>
-      <c r="R11" s="134"/>
-      <c r="S11" s="134"/>
-      <c r="T11" s="134"/>
-      <c r="U11" s="134"/>
-      <c r="V11" s="133"/>
-      <c r="W11" s="132">
+      <c r="P11" s="98"/>
+      <c r="Q11" s="98"/>
+      <c r="R11" s="98"/>
+      <c r="S11" s="98"/>
+      <c r="T11" s="98"/>
+      <c r="U11" s="98"/>
+      <c r="V11" s="97"/>
+      <c r="W11" s="96">
         <f ca="1">O11+1</f>
         <v>46312</v>
       </c>
-      <c r="X11" s="134"/>
-      <c r="Y11" s="134"/>
-      <c r="Z11" s="134"/>
-      <c r="AA11" s="134"/>
-      <c r="AB11" s="134"/>
-      <c r="AC11" s="134"/>
-      <c r="AD11" s="133"/>
+      <c r="X11" s="98"/>
+      <c r="Y11" s="98"/>
+      <c r="Z11" s="98"/>
+      <c r="AA11" s="98"/>
+      <c r="AB11" s="98"/>
+      <c r="AC11" s="98"/>
+      <c r="AD11" s="97"/>
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:36" s="43" customFormat="1" ht="169.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:36" s="43" customFormat="1" ht="169.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="42"/>
-      <c r="C12" s="139" t="s">
-        <v>40</v>
-      </c>
-      <c r="D12" s="140"/>
-      <c r="E12" s="166" t="s">
-        <v>53</v>
-      </c>
-      <c r="F12" s="137"/>
-      <c r="G12" s="135" t="s">
+      <c r="C12" s="90" t="s">
+        <v>59</v>
+      </c>
+      <c r="D12" s="91"/>
+      <c r="E12" s="102" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="85"/>
+      <c r="G12" s="83"/>
+      <c r="H12" s="85"/>
+      <c r="I12" s="90" t="s">
+        <v>46</v>
+      </c>
+      <c r="J12" s="91"/>
+      <c r="K12" s="103" t="s">
         <v>35</v>
       </c>
-      <c r="H12" s="137"/>
-      <c r="I12" s="139" t="s">
-        <v>48</v>
-      </c>
-      <c r="J12" s="140"/>
-      <c r="K12" s="141" t="s">
-        <v>36</v>
-      </c>
-      <c r="L12" s="136"/>
-      <c r="M12" s="136"/>
-      <c r="N12" s="137"/>
-      <c r="O12" s="135" t="s">
-        <v>54</v>
-      </c>
-      <c r="P12" s="136"/>
-      <c r="Q12" s="136"/>
-      <c r="R12" s="136"/>
-      <c r="S12" s="136"/>
-      <c r="T12" s="136"/>
-      <c r="U12" s="136"/>
-      <c r="V12" s="137"/>
-      <c r="W12" s="138" t="s">
+      <c r="L12" s="84"/>
+      <c r="M12" s="84"/>
+      <c r="N12" s="85"/>
+      <c r="O12" s="83" t="s">
+        <v>51</v>
+      </c>
+      <c r="P12" s="84"/>
+      <c r="Q12" s="84"/>
+      <c r="R12" s="84"/>
+      <c r="S12" s="84"/>
+      <c r="T12" s="84"/>
+      <c r="U12" s="84"/>
+      <c r="V12" s="85"/>
+      <c r="W12" s="101" t="s">
         <v>29</v>
       </c>
-      <c r="X12" s="136"/>
-      <c r="Y12" s="136"/>
-      <c r="Z12" s="136"/>
-      <c r="AA12" s="136"/>
-      <c r="AB12" s="136"/>
-      <c r="AC12" s="136"/>
-      <c r="AD12" s="137"/>
+      <c r="X12" s="84"/>
+      <c r="Y12" s="84"/>
+      <c r="Z12" s="84"/>
+      <c r="AA12" s="84"/>
+      <c r="AB12" s="84"/>
+      <c r="AC12" s="84"/>
+      <c r="AD12" s="85"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
-    <row r="13" spans="1:36" s="43" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="42"/>
-      <c r="C13" s="118">
+      <c r="C13" s="94">
         <f ca="1">W11+1</f>
         <v>46313</v>
       </c>
-      <c r="D13" s="120"/>
+      <c r="D13" s="95"/>
       <c r="E13" s="45"/>
       <c r="F13" s="75"/>
       <c r="G13" s="45"/>
@@ -4537,110 +4573,110 @@
       <c r="AE13" s="7"/>
       <c r="AF13" s="42"/>
     </row>
-    <row r="14" spans="1:36" s="7" customFormat="1" ht="21.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:36" s="7" customFormat="1" ht="21.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4"/>
-      <c r="C14" s="118"/>
-      <c r="D14" s="120"/>
-      <c r="E14" s="132">
+      <c r="C14" s="94"/>
+      <c r="D14" s="95"/>
+      <c r="E14" s="96">
         <f ca="1">C13+1</f>
         <v>46314</v>
       </c>
-      <c r="F14" s="133"/>
-      <c r="G14" s="132">
+      <c r="F14" s="97"/>
+      <c r="G14" s="96">
         <f ca="1">E14+1</f>
         <v>46315</v>
       </c>
-      <c r="H14" s="133"/>
-      <c r="I14" s="132">
+      <c r="H14" s="97"/>
+      <c r="I14" s="96">
         <f ca="1">G14+1</f>
         <v>46316</v>
       </c>
-      <c r="J14" s="133"/>
-      <c r="K14" s="132">
+      <c r="J14" s="97"/>
+      <c r="K14" s="96">
         <f ca="1">I14+1</f>
         <v>46317</v>
       </c>
-      <c r="L14" s="134"/>
-      <c r="M14" s="134"/>
+      <c r="L14" s="98"/>
+      <c r="M14" s="98"/>
       <c r="N14" s="50"/>
-      <c r="O14" s="132">
+      <c r="O14" s="96">
         <f ca="1">K14+1</f>
         <v>46318</v>
       </c>
-      <c r="P14" s="134"/>
-      <c r="Q14" s="134"/>
-      <c r="R14" s="134"/>
-      <c r="S14" s="134"/>
-      <c r="T14" s="134"/>
-      <c r="U14" s="134"/>
-      <c r="V14" s="133"/>
-      <c r="W14" s="132">
+      <c r="P14" s="98"/>
+      <c r="Q14" s="98"/>
+      <c r="R14" s="98"/>
+      <c r="S14" s="98"/>
+      <c r="T14" s="98"/>
+      <c r="U14" s="98"/>
+      <c r="V14" s="97"/>
+      <c r="W14" s="96">
         <f ca="1">O14+1</f>
         <v>46319</v>
       </c>
-      <c r="X14" s="134"/>
-      <c r="Y14" s="134"/>
-      <c r="Z14" s="134"/>
-      <c r="AA14" s="134"/>
-      <c r="AB14" s="134"/>
-      <c r="AC14" s="134"/>
-      <c r="AD14" s="133"/>
+      <c r="X14" s="98"/>
+      <c r="Y14" s="98"/>
+      <c r="Z14" s="98"/>
+      <c r="AA14" s="98"/>
+      <c r="AB14" s="98"/>
+      <c r="AC14" s="98"/>
+      <c r="AD14" s="97"/>
       <c r="AF14" s="4"/>
     </row>
-    <row r="15" spans="1:36" s="43" customFormat="1" ht="171" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:36" s="43" customFormat="1" ht="171" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="42"/>
-      <c r="C15" s="138" t="s">
+      <c r="C15" s="101" t="s">
         <v>30</v>
       </c>
-      <c r="D15" s="137"/>
-      <c r="E15" s="139" t="s">
-        <v>41</v>
-      </c>
-      <c r="F15" s="140"/>
-      <c r="G15" s="139" t="s">
-        <v>42</v>
-      </c>
-      <c r="H15" s="140"/>
-      <c r="I15" s="138" t="s">
+      <c r="D15" s="85"/>
+      <c r="E15" s="90" t="s">
+        <v>39</v>
+      </c>
+      <c r="F15" s="91"/>
+      <c r="G15" s="90" t="s">
+        <v>40</v>
+      </c>
+      <c r="H15" s="91"/>
+      <c r="I15" s="101" t="s">
+        <v>49</v>
+      </c>
+      <c r="J15" s="85"/>
+      <c r="K15" s="90" t="s">
+        <v>53</v>
+      </c>
+      <c r="L15" s="93"/>
+      <c r="M15" s="93"/>
+      <c r="N15" s="91"/>
+      <c r="O15" s="83" t="s">
         <v>52</v>
       </c>
-      <c r="J15" s="137"/>
-      <c r="K15" s="139" t="s">
-        <v>56</v>
-      </c>
-      <c r="L15" s="142"/>
-      <c r="M15" s="142"/>
-      <c r="N15" s="140"/>
-      <c r="O15" s="135" t="s">
-        <v>55</v>
-      </c>
-      <c r="P15" s="136"/>
-      <c r="Q15" s="136"/>
-      <c r="R15" s="136"/>
-      <c r="S15" s="136"/>
-      <c r="T15" s="136"/>
-      <c r="U15" s="136"/>
-      <c r="V15" s="137"/>
-      <c r="W15" s="138" t="s">
+      <c r="P15" s="84"/>
+      <c r="Q15" s="84"/>
+      <c r="R15" s="84"/>
+      <c r="S15" s="84"/>
+      <c r="T15" s="84"/>
+      <c r="U15" s="84"/>
+      <c r="V15" s="85"/>
+      <c r="W15" s="101" t="s">
         <v>31</v>
       </c>
-      <c r="X15" s="136"/>
-      <c r="Y15" s="136"/>
-      <c r="Z15" s="136"/>
-      <c r="AA15" s="136"/>
-      <c r="AB15" s="136"/>
-      <c r="AC15" s="136"/>
-      <c r="AD15" s="137"/>
+      <c r="X15" s="84"/>
+      <c r="Y15" s="84"/>
+      <c r="Z15" s="84"/>
+      <c r="AA15" s="84"/>
+      <c r="AB15" s="84"/>
+      <c r="AC15" s="84"/>
+      <c r="AD15" s="85"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
-    <row r="16" spans="1:36" s="43" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="42"/>
-      <c r="C16" s="118">
+      <c r="C16" s="94">
         <f ca="1">W14+1</f>
         <v>46320</v>
       </c>
-      <c r="D16" s="120"/>
+      <c r="D16" s="95"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
@@ -4670,109 +4706,109 @@
       <c r="AE16" s="7"/>
       <c r="AF16" s="42"/>
     </row>
-    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
-      <c r="C17" s="118"/>
-      <c r="D17" s="120"/>
-      <c r="E17" s="132">
+      <c r="C17" s="94"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="96">
         <f ca="1">C16+1</f>
         <v>46321</v>
       </c>
-      <c r="F17" s="133"/>
-      <c r="G17" s="132">
+      <c r="F17" s="97"/>
+      <c r="G17" s="96">
         <f ca="1">E17+1</f>
         <v>46322</v>
       </c>
-      <c r="H17" s="133"/>
-      <c r="I17" s="132">
+      <c r="H17" s="97"/>
+      <c r="I17" s="96">
         <f ca="1">G17+1</f>
         <v>46323</v>
       </c>
-      <c r="J17" s="133"/>
-      <c r="K17" s="132">
+      <c r="J17" s="97"/>
+      <c r="K17" s="96">
         <f ca="1">I17+1</f>
         <v>46324</v>
       </c>
-      <c r="L17" s="134"/>
-      <c r="M17" s="134"/>
+      <c r="L17" s="98"/>
+      <c r="M17" s="98"/>
       <c r="N17" s="50"/>
-      <c r="O17" s="132">
+      <c r="O17" s="96">
         <f ca="1">K17+1</f>
         <v>46325</v>
       </c>
-      <c r="P17" s="134"/>
-      <c r="Q17" s="134"/>
-      <c r="R17" s="134"/>
-      <c r="S17" s="134"/>
-      <c r="T17" s="134"/>
-      <c r="U17" s="134"/>
-      <c r="V17" s="133"/>
-      <c r="W17" s="132">
+      <c r="P17" s="98"/>
+      <c r="Q17" s="98"/>
+      <c r="R17" s="98"/>
+      <c r="S17" s="98"/>
+      <c r="T17" s="98"/>
+      <c r="U17" s="98"/>
+      <c r="V17" s="97"/>
+      <c r="W17" s="96">
         <f ca="1">O17+1</f>
         <v>46326</v>
       </c>
-      <c r="X17" s="134"/>
-      <c r="Y17" s="134"/>
-      <c r="Z17" s="134"/>
-      <c r="AA17" s="134"/>
-      <c r="AB17" s="134"/>
-      <c r="AC17" s="134"/>
-      <c r="AD17" s="133"/>
+      <c r="X17" s="98"/>
+      <c r="Y17" s="98"/>
+      <c r="Z17" s="98"/>
+      <c r="AA17" s="98"/>
+      <c r="AB17" s="98"/>
+      <c r="AC17" s="98"/>
+      <c r="AD17" s="97"/>
       <c r="AF17" s="4"/>
     </row>
-    <row r="18" spans="1:42" s="43" customFormat="1" ht="171" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:42" s="43" customFormat="1" ht="171" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="42"/>
-      <c r="C18" s="139" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="140"/>
-      <c r="E18" s="135" t="s">
-        <v>57</v>
-      </c>
-      <c r="F18" s="137"/>
-      <c r="G18" s="139" t="s">
-        <v>39</v>
-      </c>
-      <c r="H18" s="140"/>
-      <c r="I18" s="139" t="s">
-        <v>43</v>
-      </c>
-      <c r="J18" s="140"/>
-      <c r="K18" s="145" t="s">
+      <c r="C18" s="90" t="s">
+        <v>47</v>
+      </c>
+      <c r="D18" s="91"/>
+      <c r="E18" s="83" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="85"/>
+      <c r="G18" s="90" t="s">
+        <v>38</v>
+      </c>
+      <c r="H18" s="91"/>
+      <c r="I18" s="90" t="s">
+        <v>41</v>
+      </c>
+      <c r="J18" s="91"/>
+      <c r="K18" s="92" t="s">
         <v>32</v>
       </c>
-      <c r="L18" s="136"/>
-      <c r="M18" s="136"/>
+      <c r="L18" s="84"/>
+      <c r="M18" s="84"/>
       <c r="N18" s="82"/>
-      <c r="O18" s="139" t="s">
-        <v>44</v>
-      </c>
-      <c r="P18" s="142"/>
-      <c r="Q18" s="142"/>
-      <c r="R18" s="142"/>
-      <c r="S18" s="142"/>
-      <c r="T18" s="142"/>
-      <c r="U18" s="142"/>
-      <c r="V18" s="140"/>
-      <c r="W18" s="135"/>
-      <c r="X18" s="136"/>
-      <c r="Y18" s="136"/>
-      <c r="Z18" s="136"/>
-      <c r="AA18" s="136"/>
-      <c r="AB18" s="136"/>
-      <c r="AC18" s="136"/>
-      <c r="AD18" s="137"/>
+      <c r="O18" s="90" t="s">
+        <v>42</v>
+      </c>
+      <c r="P18" s="93"/>
+      <c r="Q18" s="93"/>
+      <c r="R18" s="93"/>
+      <c r="S18" s="93"/>
+      <c r="T18" s="93"/>
+      <c r="U18" s="93"/>
+      <c r="V18" s="91"/>
+      <c r="W18" s="83"/>
+      <c r="X18" s="84"/>
+      <c r="Y18" s="84"/>
+      <c r="Z18" s="84"/>
+      <c r="AA18" s="84"/>
+      <c r="AB18" s="84"/>
+      <c r="AC18" s="84"/>
+      <c r="AD18" s="85"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
-    <row r="19" spans="1:42" s="43" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="42"/>
-      <c r="C19" s="118">
+      <c r="C19" s="94">
         <f ca="1">W17+1</f>
         <v>46327</v>
       </c>
-      <c r="D19" s="120"/>
+      <c r="D19" s="95"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
@@ -4802,91 +4838,91 @@
       <c r="AE19" s="7"/>
       <c r="AF19" s="42"/>
     </row>
-    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
-      <c r="C20" s="118"/>
-      <c r="D20" s="120"/>
-      <c r="E20" s="132">
+      <c r="C20" s="94"/>
+      <c r="D20" s="95"/>
+      <c r="E20" s="96">
         <f ca="1">C19+1</f>
         <v>46328</v>
       </c>
-      <c r="F20" s="133"/>
-      <c r="G20" s="132">
+      <c r="F20" s="97"/>
+      <c r="G20" s="96">
         <f ca="1">E20+1</f>
         <v>46329</v>
       </c>
-      <c r="H20" s="133"/>
-      <c r="I20" s="132">
+      <c r="H20" s="97"/>
+      <c r="I20" s="96">
         <f ca="1">G20+1</f>
         <v>46330</v>
       </c>
-      <c r="J20" s="133"/>
-      <c r="K20" s="132">
+      <c r="J20" s="97"/>
+      <c r="K20" s="96">
         <f ca="1">I20+1</f>
         <v>46331</v>
       </c>
-      <c r="L20" s="134"/>
-      <c r="M20" s="134"/>
+      <c r="L20" s="98"/>
+      <c r="M20" s="98"/>
       <c r="N20" s="50"/>
-      <c r="O20" s="132">
+      <c r="O20" s="96">
         <f ca="1">K20+1</f>
         <v>46332</v>
       </c>
-      <c r="P20" s="134"/>
-      <c r="Q20" s="134"/>
-      <c r="R20" s="134"/>
-      <c r="S20" s="134"/>
-      <c r="T20" s="134"/>
-      <c r="U20" s="134"/>
-      <c r="V20" s="133"/>
-      <c r="W20" s="132">
+      <c r="P20" s="98"/>
+      <c r="Q20" s="98"/>
+      <c r="R20" s="98"/>
+      <c r="S20" s="98"/>
+      <c r="T20" s="98"/>
+      <c r="U20" s="98"/>
+      <c r="V20" s="97"/>
+      <c r="W20" s="96">
         <f ca="1">O20+1</f>
         <v>46333</v>
       </c>
-      <c r="X20" s="134"/>
-      <c r="Y20" s="134"/>
-      <c r="Z20" s="134"/>
-      <c r="AA20" s="134"/>
-      <c r="AB20" s="134"/>
-      <c r="AC20" s="134"/>
-      <c r="AD20" s="133"/>
+      <c r="X20" s="98"/>
+      <c r="Y20" s="98"/>
+      <c r="Z20" s="98"/>
+      <c r="AA20" s="98"/>
+      <c r="AB20" s="98"/>
+      <c r="AC20" s="98"/>
+      <c r="AD20" s="97"/>
       <c r="AF20" s="4"/>
     </row>
-    <row r="21" spans="1:42" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:42" s="43" customFormat="1" ht="7.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="42"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="111"/>
-      <c r="H21" s="113"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="113"/>
-      <c r="K21" s="111"/>
-      <c r="L21" s="112"/>
-      <c r="M21" s="112"/>
+      <c r="C21" s="99"/>
+      <c r="D21" s="100"/>
+      <c r="E21" s="99"/>
+      <c r="F21" s="100"/>
+      <c r="G21" s="99"/>
+      <c r="H21" s="100"/>
+      <c r="I21" s="99"/>
+      <c r="J21" s="100"/>
+      <c r="K21" s="99"/>
+      <c r="L21" s="146"/>
+      <c r="M21" s="146"/>
       <c r="N21" s="44"/>
-      <c r="O21" s="111"/>
-      <c r="P21" s="112"/>
-      <c r="Q21" s="112"/>
-      <c r="R21" s="112"/>
-      <c r="S21" s="112"/>
-      <c r="T21" s="112"/>
-      <c r="U21" s="112"/>
-      <c r="V21" s="113"/>
-      <c r="W21" s="111"/>
-      <c r="X21" s="112"/>
-      <c r="Y21" s="112"/>
-      <c r="Z21" s="112"/>
-      <c r="AA21" s="112"/>
-      <c r="AB21" s="112"/>
-      <c r="AC21" s="112"/>
-      <c r="AD21" s="113"/>
+      <c r="O21" s="99"/>
+      <c r="P21" s="146"/>
+      <c r="Q21" s="146"/>
+      <c r="R21" s="146"/>
+      <c r="S21" s="146"/>
+      <c r="T21" s="146"/>
+      <c r="U21" s="146"/>
+      <c r="V21" s="100"/>
+      <c r="W21" s="99"/>
+      <c r="X21" s="146"/>
+      <c r="Y21" s="146"/>
+      <c r="Z21" s="146"/>
+      <c r="AA21" s="146"/>
+      <c r="AB21" s="146"/>
+      <c r="AC21" s="146"/>
+      <c r="AD21" s="100"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
     </row>
-    <row r="22" spans="1:42" s="7" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52"/>
@@ -4918,7 +4954,7 @@
       <c r="AD22" s="55"/>
       <c r="AF22" s="4"/>
     </row>
-    <row r="23" spans="1:42" s="7" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="56"/>
@@ -4952,61 +4988,61 @@
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
     </row>
-    <row r="24" spans="1:42" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:42" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="M24" s="1"/>
       <c r="AF24" s="1"/>
     </row>
-    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
-      <c r="C25" s="143" t="s">
+      <c r="C25" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="143"/>
-      <c r="E25" s="143"/>
-      <c r="F25" s="143"/>
-      <c r="G25" s="143"/>
-      <c r="H25" s="143"/>
-      <c r="I25" s="143"/>
-      <c r="J25" s="143"/>
-      <c r="K25" s="143"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="86"/>
+      <c r="H25" s="86"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="86"/>
+      <c r="K25" s="86"/>
       <c r="L25" s="60"/>
       <c r="M25" s="1"/>
-      <c r="O25" s="144">
+      <c r="O25" s="87">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)-1,1)</f>
         <v>46266</v>
       </c>
-      <c r="P25" s="144"/>
-      <c r="Q25" s="144"/>
-      <c r="R25" s="144"/>
-      <c r="S25" s="144"/>
-      <c r="T25" s="144"/>
-      <c r="U25" s="144"/>
+      <c r="P25" s="87"/>
+      <c r="Q25" s="87"/>
+      <c r="R25" s="87"/>
+      <c r="S25" s="87"/>
+      <c r="T25" s="87"/>
+      <c r="U25" s="87"/>
       <c r="V25" s="61"/>
       <c r="W25" s="61"/>
-      <c r="X25" s="144">
+      <c r="X25" s="87">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)+1,1)</f>
         <v>46327</v>
       </c>
-      <c r="Y25" s="144"/>
-      <c r="Z25" s="144"/>
-      <c r="AA25" s="144"/>
-      <c r="AB25" s="144"/>
-      <c r="AC25" s="144"/>
-      <c r="AD25" s="144"/>
+      <c r="Y25" s="87"/>
+      <c r="Z25" s="87"/>
+      <c r="AA25" s="87"/>
+      <c r="AB25" s="87"/>
+      <c r="AC25" s="87"/>
+      <c r="AD25" s="87"/>
       <c r="AF25" s="1"/>
     </row>
-    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
-      <c r="C26" s="143"/>
-      <c r="D26" s="143"/>
-      <c r="E26" s="143"/>
-      <c r="F26" s="143"/>
-      <c r="G26" s="143"/>
-      <c r="H26" s="143"/>
-      <c r="I26" s="143"/>
-      <c r="J26" s="143"/>
-      <c r="K26" s="143"/>
+      <c r="C26" s="86"/>
+      <c r="D26" s="86"/>
+      <c r="E26" s="86"/>
+      <c r="F26" s="86"/>
+      <c r="G26" s="86"/>
+      <c r="H26" s="86"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="K26" s="86"/>
       <c r="L26" s="60"/>
       <c r="M26" s="1"/>
       <c r="O26" s="62" t="str">
@@ -5069,17 +5105,17 @@
       </c>
       <c r="AF26" s="1"/>
     </row>
-    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
-      <c r="C27" s="115"/>
-      <c r="D27" s="115"/>
-      <c r="E27" s="115"/>
-      <c r="F27" s="115"/>
-      <c r="G27" s="115"/>
-      <c r="H27" s="115"/>
-      <c r="I27" s="115"/>
-      <c r="J27" s="115"/>
-      <c r="K27" s="115"/>
+      <c r="C27" s="88"/>
+      <c r="D27" s="88"/>
+      <c r="E27" s="88"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="88"/>
+      <c r="H27" s="88"/>
+      <c r="I27" s="88"/>
+      <c r="J27" s="88"/>
+      <c r="K27" s="88"/>
       <c r="M27" s="1"/>
       <c r="O27" s="64" t="str">
         <f t="shared" ref="O27:U32" ca="1" si="0">IF(MONTH($O$25)&lt;&gt;MONTH($O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1)),"",$O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1))</f>
@@ -5141,17 +5177,17 @@
       </c>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
-      <c r="C28" s="114"/>
-      <c r="D28" s="114"/>
-      <c r="E28" s="114"/>
-      <c r="F28" s="114"/>
-      <c r="G28" s="114"/>
-      <c r="H28" s="114"/>
-      <c r="I28" s="114"/>
-      <c r="J28" s="114"/>
-      <c r="K28" s="114"/>
+      <c r="C28" s="89"/>
+      <c r="D28" s="89"/>
+      <c r="E28" s="89"/>
+      <c r="F28" s="89"/>
+      <c r="G28" s="89"/>
+      <c r="H28" s="89"/>
+      <c r="I28" s="89"/>
+      <c r="J28" s="89"/>
+      <c r="K28" s="89"/>
       <c r="M28" s="1"/>
       <c r="O28" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -5213,17 +5249,17 @@
       </c>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
-      <c r="C29" s="115"/>
-      <c r="D29" s="115"/>
-      <c r="E29" s="115"/>
-      <c r="F29" s="115"/>
-      <c r="G29" s="115"/>
-      <c r="H29" s="115"/>
-      <c r="I29" s="115"/>
-      <c r="J29" s="115"/>
-      <c r="K29" s="115"/>
+      <c r="C29" s="88"/>
+      <c r="D29" s="88"/>
+      <c r="E29" s="88"/>
+      <c r="F29" s="88"/>
+      <c r="G29" s="88"/>
+      <c r="H29" s="88"/>
+      <c r="I29" s="88"/>
+      <c r="J29" s="88"/>
+      <c r="K29" s="88"/>
       <c r="M29" s="1"/>
       <c r="O29" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -5285,17 +5321,17 @@
       </c>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
-      <c r="C30" s="114"/>
-      <c r="D30" s="114"/>
-      <c r="E30" s="114"/>
-      <c r="F30" s="114"/>
-      <c r="G30" s="114"/>
-      <c r="H30" s="114"/>
-      <c r="I30" s="114"/>
-      <c r="J30" s="114"/>
-      <c r="K30" s="114"/>
+      <c r="C30" s="89"/>
+      <c r="D30" s="89"/>
+      <c r="E30" s="89"/>
+      <c r="F30" s="89"/>
+      <c r="G30" s="89"/>
+      <c r="H30" s="89"/>
+      <c r="I30" s="89"/>
+      <c r="J30" s="89"/>
+      <c r="K30" s="89"/>
       <c r="M30" s="1"/>
       <c r="O30" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -5357,17 +5393,17 @@
       </c>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
-      <c r="C31" s="115"/>
-      <c r="D31" s="115"/>
-      <c r="E31" s="115"/>
-      <c r="F31" s="115"/>
-      <c r="G31" s="115"/>
-      <c r="H31" s="115"/>
-      <c r="I31" s="115"/>
-      <c r="J31" s="115"/>
-      <c r="K31" s="115"/>
+      <c r="C31" s="88"/>
+      <c r="D31" s="88"/>
+      <c r="E31" s="88"/>
+      <c r="F31" s="88"/>
+      <c r="G31" s="88"/>
+      <c r="H31" s="88"/>
+      <c r="I31" s="88"/>
+      <c r="J31" s="88"/>
+      <c r="K31" s="88"/>
       <c r="M31" s="1"/>
       <c r="O31" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -5429,7 +5465,7 @@
       </c>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="M32" s="1"/>
       <c r="O32" s="64" t="str">
@@ -5492,7 +5528,7 @@
       </c>
       <c r="AF32" s="1"/>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="M33" s="1"/>
       <c r="O33" s="64"/>
@@ -5513,7 +5549,7 @@
       <c r="AD33" s="65"/>
       <c r="AF33" s="1"/>
     </row>
-    <row r="34" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -5547,69 +5583,156 @@
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
     </row>
-    <row r="38" spans="1:32" ht="12.9" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D39" s="83" t="s">
+    <row r="38" spans="1:32" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="39" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D39" s="118" t="s">
         <v>23</v>
       </c>
-      <c r="E39" s="84"/>
-      <c r="F39" s="85"/>
-      <c r="G39" s="89">
+      <c r="E39" s="119"/>
+      <c r="F39" s="120"/>
+      <c r="G39" s="124">
         <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
         <v>5</v>
       </c>
-      <c r="H39" s="90"/>
-      <c r="I39" s="83" t="s">
+      <c r="H39" s="125"/>
+      <c r="I39" s="118" t="s">
         <v>26</v>
       </c>
-      <c r="J39" s="93"/>
-      <c r="K39" s="95" t="s">
+      <c r="J39" s="128"/>
+      <c r="K39" s="130" t="s">
         <v>24</v>
       </c>
-      <c r="L39" s="96"/>
-      <c r="M39" s="99">
+      <c r="L39" s="131"/>
+      <c r="M39" s="134">
         <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
         <v>1.0000000000000027</v>
       </c>
-      <c r="N39" s="100"/>
-      <c r="O39" s="100"/>
-      <c r="P39" s="100"/>
-      <c r="Q39" s="100"/>
-      <c r="R39" s="101"/>
-      <c r="S39" s="105" t="s">
+      <c r="N39" s="135"/>
+      <c r="O39" s="135"/>
+      <c r="P39" s="135"/>
+      <c r="Q39" s="135"/>
+      <c r="R39" s="136"/>
+      <c r="S39" s="140" t="s">
         <v>25</v>
       </c>
-      <c r="T39" s="106"/>
-      <c r="U39" s="106"/>
-      <c r="V39" s="106"/>
-      <c r="W39" s="106"/>
-      <c r="X39" s="107"/>
-    </row>
-    <row r="40" spans="1:32" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D40" s="86"/>
-      <c r="E40" s="87"/>
-      <c r="F40" s="88"/>
-      <c r="G40" s="91"/>
-      <c r="H40" s="92"/>
-      <c r="I40" s="86"/>
-      <c r="J40" s="94"/>
-      <c r="K40" s="97"/>
-      <c r="L40" s="98"/>
-      <c r="M40" s="102"/>
-      <c r="N40" s="103"/>
-      <c r="O40" s="103"/>
-      <c r="P40" s="103"/>
-      <c r="Q40" s="103"/>
-      <c r="R40" s="104"/>
-      <c r="S40" s="108"/>
-      <c r="T40" s="109"/>
-      <c r="U40" s="109"/>
-      <c r="V40" s="109"/>
-      <c r="W40" s="109"/>
-      <c r="X40" s="110"/>
+      <c r="T39" s="141"/>
+      <c r="U39" s="141"/>
+      <c r="V39" s="141"/>
+      <c r="W39" s="141"/>
+      <c r="X39" s="142"/>
+    </row>
+    <row r="40" spans="1:32" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D40" s="121"/>
+      <c r="E40" s="122"/>
+      <c r="F40" s="123"/>
+      <c r="G40" s="126"/>
+      <c r="H40" s="127"/>
+      <c r="I40" s="121"/>
+      <c r="J40" s="129"/>
+      <c r="K40" s="132"/>
+      <c r="L40" s="133"/>
+      <c r="M40" s="137"/>
+      <c r="N40" s="138"/>
+      <c r="O40" s="138"/>
+      <c r="P40" s="138"/>
+      <c r="Q40" s="138"/>
+      <c r="R40" s="139"/>
+      <c r="S40" s="143"/>
+      <c r="T40" s="144"/>
+      <c r="U40" s="144"/>
+      <c r="V40" s="144"/>
+      <c r="W40" s="144"/>
+      <c r="X40" s="145"/>
     </row>
   </sheetData>
   <mergeCells count="110">
+    <mergeCell ref="D39:F40"/>
+    <mergeCell ref="G39:H40"/>
+    <mergeCell ref="I39:J40"/>
+    <mergeCell ref="K39:L40"/>
+    <mergeCell ref="M39:R40"/>
+    <mergeCell ref="S39:X40"/>
+    <mergeCell ref="K21:M21"/>
+    <mergeCell ref="O21:V21"/>
+    <mergeCell ref="W21:AD21"/>
+    <mergeCell ref="C30:K31"/>
+    <mergeCell ref="C2:AD2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="W5:AD5"/>
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="E6:F6"/>
+    <mergeCell ref="G6:H6"/>
+    <mergeCell ref="I6:J6"/>
+    <mergeCell ref="O6:V6"/>
+    <mergeCell ref="W6:AD6"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="O5:V5"/>
+    <mergeCell ref="K6:N6"/>
+    <mergeCell ref="C7:D8"/>
+    <mergeCell ref="E7:F7"/>
+    <mergeCell ref="G7:H7"/>
+    <mergeCell ref="I7:J7"/>
+    <mergeCell ref="K7:M7"/>
+    <mergeCell ref="W7:AD7"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="G8:H8"/>
+    <mergeCell ref="I8:J8"/>
+    <mergeCell ref="K8:M8"/>
+    <mergeCell ref="O8:V8"/>
+    <mergeCell ref="W8:AD8"/>
+    <mergeCell ref="O7:V7"/>
+    <mergeCell ref="W9:AD9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="O11:V11"/>
+    <mergeCell ref="W11:AD11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:V9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="W12:AD12"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O14:V14"/>
+    <mergeCell ref="W14:AD14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="O12:V12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="W15:AD15"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="O17:V17"/>
+    <mergeCell ref="W17:AD17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="O15:V15"/>
+    <mergeCell ref="K15:N15"/>
     <mergeCell ref="W18:AD18"/>
     <mergeCell ref="C25:K26"/>
     <mergeCell ref="O25:U25"/>
@@ -5633,93 +5756,6 @@
     <mergeCell ref="E21:F21"/>
     <mergeCell ref="G21:H21"/>
     <mergeCell ref="I21:J21"/>
-    <mergeCell ref="W15:AD15"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="O17:V17"/>
-    <mergeCell ref="W17:AD17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="O15:V15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="W12:AD12"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="O14:V14"/>
-    <mergeCell ref="W14:AD14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="O12:V12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="W9:AD9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="O11:V11"/>
-    <mergeCell ref="W11:AD11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:V9"/>
-    <mergeCell ref="K9:N9"/>
-    <mergeCell ref="C7:D8"/>
-    <mergeCell ref="E7:F7"/>
-    <mergeCell ref="G7:H7"/>
-    <mergeCell ref="I7:J7"/>
-    <mergeCell ref="K7:M7"/>
-    <mergeCell ref="W7:AD7"/>
-    <mergeCell ref="E8:F8"/>
-    <mergeCell ref="G8:H8"/>
-    <mergeCell ref="I8:J8"/>
-    <mergeCell ref="K8:M8"/>
-    <mergeCell ref="O8:V8"/>
-    <mergeCell ref="W8:AD8"/>
-    <mergeCell ref="O7:V7"/>
-    <mergeCell ref="C6:D6"/>
-    <mergeCell ref="E6:F6"/>
-    <mergeCell ref="G6:H6"/>
-    <mergeCell ref="I6:J6"/>
-    <mergeCell ref="O6:V6"/>
-    <mergeCell ref="W6:AD6"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="O5:V5"/>
-    <mergeCell ref="K6:N6"/>
-    <mergeCell ref="C2:AD2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="W5:AD5"/>
-    <mergeCell ref="D39:F40"/>
-    <mergeCell ref="G39:H40"/>
-    <mergeCell ref="I39:J40"/>
-    <mergeCell ref="K39:L40"/>
-    <mergeCell ref="M39:R40"/>
-    <mergeCell ref="S39:X40"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="O21:V21"/>
-    <mergeCell ref="W21:AD21"/>
-    <mergeCell ref="C30:K31"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 E5 G5 I5 K5:L5 O5 W5 C7 E8 G8 I8 K8:L8 O8 W8 C10 E11 G11 I11 K11:L11 O11 W11 C13 E14 G14 I14 K14:L14 O14 W14 C16 E17 G17 I17 K17:L17 O17 W17">
     <cfRule type="expression" dxfId="7" priority="3">
@@ -5758,25 +5794,25 @@
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:AP39"/>
-  <sheetFormatPr defaultColWidth="8.71875" defaultRowHeight="12.6" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="3" width="5.5546875" style="3" customWidth="1"/>
-    <col min="4" max="4" width="15.5546875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="5.5546875" style="3" customWidth="1"/>
-    <col min="6" max="6" width="15.5546875" style="3" customWidth="1"/>
-    <col min="7" max="7" width="5.5546875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="15.5546875" style="3" customWidth="1"/>
-    <col min="9" max="9" width="5.5546875" style="3" customWidth="1"/>
-    <col min="10" max="10" width="15.5546875" style="3" customWidth="1"/>
-    <col min="11" max="14" width="5.5546875" style="3" customWidth="1"/>
-    <col min="15" max="30" width="2.5546875" style="3" customWidth="1"/>
-    <col min="31" max="32" width="5.5546875" style="3" customWidth="1"/>
-    <col min="33" max="33" width="17.1640625" style="3" customWidth="1"/>
-    <col min="34" max="34" width="10.44140625" style="3" customWidth="1"/>
-    <col min="35" max="16384" width="8.71875" style="3"/>
+    <col min="1" max="3" width="5.5703125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="15.5703125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="5.5703125" style="3" customWidth="1"/>
+    <col min="6" max="6" width="15.5703125" style="3" customWidth="1"/>
+    <col min="7" max="7" width="5.5703125" style="3" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" style="3" customWidth="1"/>
+    <col min="9" max="9" width="5.5703125" style="3" customWidth="1"/>
+    <col min="10" max="10" width="15.5703125" style="3" customWidth="1"/>
+    <col min="11" max="14" width="5.5703125" style="3" customWidth="1"/>
+    <col min="15" max="30" width="2.5703125" style="3" customWidth="1"/>
+    <col min="31" max="32" width="5.5703125" style="3" customWidth="1"/>
+    <col min="33" max="33" width="17.140625" style="3" customWidth="1"/>
+    <col min="34" max="34" width="10.42578125" style="3" customWidth="1"/>
+    <col min="35" max="16384" width="8.7109375" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5810,7 +5846,7 @@
       <c r="AE1" s="1"/>
       <c r="AF1" s="1"/>
     </row>
-    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="2.15">
+    <row r="2" spans="1:36" s="30" customFormat="1" ht="90" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A2" s="29"/>
       <c r="C2" s="116">
         <f ca="1">DATE(About!P8,11,1)</f>
@@ -5845,7 +5881,7 @@
       <c r="AD2" s="116"/>
       <c r="AF2" s="29"/>
     </row>
-    <row r="3" spans="1:36" s="32" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="2.15">
+    <row r="3" spans="1:36" s="32" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.9">
       <c r="A3" s="31"/>
       <c r="C3" s="33"/>
       <c r="D3" s="33"/>
@@ -5865,7 +5901,7 @@
       <c r="AH3" s="30"/>
       <c r="AI3" s="30"/>
     </row>
-    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.65">
+    <row r="4" spans="1:36" s="36" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="35"/>
       <c r="C4" s="117">
         <f ca="1">C5</f>
@@ -5922,239 +5958,239 @@
       <c r="AI4" s="39"/>
       <c r="AJ4" s="39"/>
     </row>
-    <row r="5" spans="1:36" ht="25" customHeight="1" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:36" ht="24.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
-      <c r="C5" s="118">
+      <c r="C5" s="94">
         <f ca="1">$C$2-(WEEKDAY($C$2,1)-(start_day-1))-IF((WEEKDAY($C$2,1)-(start_day-1))&lt;=0,7,0)+1</f>
         <v>46327</v>
       </c>
-      <c r="D5" s="120"/>
-      <c r="E5" s="118">
+      <c r="D5" s="95"/>
+      <c r="E5" s="94">
         <f ca="1">C5+1</f>
         <v>46328</v>
       </c>
-      <c r="F5" s="120"/>
-      <c r="G5" s="118">
+      <c r="F5" s="95"/>
+      <c r="G5" s="94">
         <f ca="1">E5+1</f>
         <v>46329</v>
       </c>
-      <c r="H5" s="120"/>
-      <c r="I5" s="118">
+      <c r="H5" s="95"/>
+      <c r="I5" s="94">
         <f ca="1">G5+1</f>
         <v>46330</v>
       </c>
-      <c r="J5" s="120"/>
-      <c r="K5" s="118">
+      <c r="J5" s="95"/>
+      <c r="K5" s="94">
         <f ca="1">I5+1</f>
         <v>46331</v>
       </c>
-      <c r="L5" s="119"/>
-      <c r="M5" s="119"/>
+      <c r="L5" s="115"/>
+      <c r="M5" s="115"/>
       <c r="N5" s="74"/>
-      <c r="O5" s="118">
+      <c r="O5" s="94">
         <f ca="1">K5+1</f>
         <v>46332</v>
       </c>
-      <c r="P5" s="119"/>
-      <c r="Q5" s="119"/>
-      <c r="R5" s="119"/>
-      <c r="S5" s="119"/>
-      <c r="T5" s="119"/>
-      <c r="U5" s="119"/>
-      <c r="V5" s="120"/>
-      <c r="W5" s="118">
+      <c r="P5" s="115"/>
+      <c r="Q5" s="115"/>
+      <c r="R5" s="115"/>
+      <c r="S5" s="115"/>
+      <c r="T5" s="115"/>
+      <c r="U5" s="115"/>
+      <c r="V5" s="95"/>
+      <c r="W5" s="94">
         <f ca="1">O5+1</f>
         <v>46333</v>
       </c>
-      <c r="X5" s="119"/>
-      <c r="Y5" s="119"/>
-      <c r="Z5" s="119"/>
-      <c r="AA5" s="119"/>
-      <c r="AB5" s="119"/>
-      <c r="AC5" s="119"/>
-      <c r="AD5" s="120"/>
+      <c r="X5" s="115"/>
+      <c r="Y5" s="115"/>
+      <c r="Z5" s="115"/>
+      <c r="AA5" s="115"/>
+      <c r="AB5" s="115"/>
+      <c r="AC5" s="115"/>
+      <c r="AD5" s="95"/>
       <c r="AF5" s="40"/>
       <c r="AG5" s="41"/>
       <c r="AH5" s="41"/>
       <c r="AI5" s="41"/>
       <c r="AJ5" s="41"/>
     </row>
-    <row r="6" spans="1:36" s="43" customFormat="1" ht="133.9" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:36" s="43" customFormat="1" ht="133.9" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="42"/>
-      <c r="C6" s="135"/>
-      <c r="D6" s="137"/>
-      <c r="E6" s="141" t="s">
+      <c r="C6" s="83"/>
+      <c r="D6" s="85"/>
+      <c r="E6" s="103" t="s">
         <v>33</v>
       </c>
-      <c r="F6" s="137"/>
-      <c r="G6" s="135"/>
-      <c r="H6" s="137"/>
-      <c r="I6" s="156" t="s">
-        <v>45</v>
-      </c>
-      <c r="J6" s="137"/>
-      <c r="K6" s="156" t="s">
-        <v>46</v>
-      </c>
-      <c r="L6" s="136"/>
-      <c r="M6" s="136"/>
-      <c r="N6" s="137"/>
-      <c r="O6" s="145" t="s">
-        <v>59</v>
-      </c>
-      <c r="P6" s="136"/>
-      <c r="Q6" s="136"/>
-      <c r="R6" s="136"/>
-      <c r="S6" s="136"/>
-      <c r="T6" s="136"/>
-      <c r="U6" s="136"/>
-      <c r="V6" s="137"/>
-      <c r="W6" s="135"/>
-      <c r="X6" s="136"/>
-      <c r="Y6" s="136"/>
-      <c r="Z6" s="136"/>
-      <c r="AA6" s="136"/>
-      <c r="AB6" s="136"/>
-      <c r="AC6" s="136"/>
-      <c r="AD6" s="137"/>
+      <c r="F6" s="85"/>
+      <c r="G6" s="83"/>
+      <c r="H6" s="85"/>
+      <c r="I6" s="163" t="s">
+        <v>43</v>
+      </c>
+      <c r="J6" s="85"/>
+      <c r="K6" s="163" t="s">
+        <v>44</v>
+      </c>
+      <c r="L6" s="84"/>
+      <c r="M6" s="84"/>
+      <c r="N6" s="85"/>
+      <c r="O6" s="92" t="s">
+        <v>56</v>
+      </c>
+      <c r="P6" s="84"/>
+      <c r="Q6" s="84"/>
+      <c r="R6" s="84"/>
+      <c r="S6" s="84"/>
+      <c r="T6" s="84"/>
+      <c r="U6" s="84"/>
+      <c r="V6" s="85"/>
+      <c r="W6" s="83"/>
+      <c r="X6" s="84"/>
+      <c r="Y6" s="84"/>
+      <c r="Z6" s="84"/>
+      <c r="AA6" s="84"/>
+      <c r="AB6" s="84"/>
+      <c r="AC6" s="84"/>
+      <c r="AD6" s="85"/>
       <c r="AE6" s="7"/>
       <c r="AF6" s="42"/>
     </row>
-    <row r="7" spans="1:36" ht="10" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:36" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1"/>
-      <c r="C7" s="157">
+      <c r="C7" s="158">
         <f ca="1">W5+1</f>
         <v>46334</v>
       </c>
-      <c r="D7" s="158"/>
-      <c r="E7" s="159"/>
-      <c r="F7" s="160"/>
-      <c r="G7" s="159"/>
-      <c r="H7" s="160"/>
-      <c r="I7" s="159"/>
-      <c r="J7" s="160"/>
-      <c r="K7" s="159"/>
-      <c r="L7" s="161"/>
-      <c r="M7" s="161"/>
+      <c r="D7" s="159"/>
+      <c r="E7" s="164"/>
+      <c r="F7" s="165"/>
+      <c r="G7" s="164"/>
+      <c r="H7" s="165"/>
+      <c r="I7" s="164"/>
+      <c r="J7" s="165"/>
+      <c r="K7" s="164"/>
+      <c r="L7" s="166"/>
+      <c r="M7" s="166"/>
       <c r="N7" s="80"/>
-      <c r="O7" s="159"/>
-      <c r="P7" s="161"/>
-      <c r="Q7" s="161"/>
-      <c r="R7" s="161"/>
-      <c r="S7" s="161"/>
-      <c r="T7" s="161"/>
-      <c r="U7" s="161"/>
-      <c r="V7" s="160"/>
-      <c r="W7" s="159"/>
-      <c r="X7" s="161"/>
-      <c r="Y7" s="161"/>
-      <c r="Z7" s="161"/>
-      <c r="AA7" s="161"/>
-      <c r="AB7" s="161"/>
-      <c r="AC7" s="161"/>
-      <c r="AD7" s="160"/>
+      <c r="O7" s="164"/>
+      <c r="P7" s="166"/>
+      <c r="Q7" s="166"/>
+      <c r="R7" s="166"/>
+      <c r="S7" s="166"/>
+      <c r="T7" s="166"/>
+      <c r="U7" s="166"/>
+      <c r="V7" s="165"/>
+      <c r="W7" s="164"/>
+      <c r="X7" s="166"/>
+      <c r="Y7" s="166"/>
+      <c r="Z7" s="166"/>
+      <c r="AA7" s="166"/>
+      <c r="AB7" s="166"/>
+      <c r="AC7" s="166"/>
+      <c r="AD7" s="165"/>
       <c r="AF7" s="1"/>
     </row>
-    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="4"/>
-      <c r="C8" s="157"/>
-      <c r="D8" s="158"/>
-      <c r="E8" s="157">
+      <c r="C8" s="158"/>
+      <c r="D8" s="159"/>
+      <c r="E8" s="158">
         <f ca="1">C7+1</f>
         <v>46335</v>
       </c>
-      <c r="F8" s="158"/>
-      <c r="G8" s="157">
+      <c r="F8" s="159"/>
+      <c r="G8" s="158">
         <f ca="1">E8+1</f>
         <v>46336</v>
       </c>
-      <c r="H8" s="158"/>
-      <c r="I8" s="157">
+      <c r="H8" s="159"/>
+      <c r="I8" s="158">
         <f ca="1">G8+1</f>
         <v>46337</v>
       </c>
-      <c r="J8" s="158"/>
-      <c r="K8" s="157">
+      <c r="J8" s="159"/>
+      <c r="K8" s="158">
         <f ca="1">I8+1</f>
         <v>46338</v>
       </c>
-      <c r="L8" s="162"/>
-      <c r="M8" s="162"/>
+      <c r="L8" s="160"/>
+      <c r="M8" s="160"/>
       <c r="N8" s="78"/>
-      <c r="O8" s="157">
+      <c r="O8" s="158">
         <f ca="1">K8+1</f>
         <v>46339</v>
       </c>
-      <c r="P8" s="162"/>
-      <c r="Q8" s="162"/>
-      <c r="R8" s="162"/>
-      <c r="S8" s="162"/>
-      <c r="T8" s="162"/>
-      <c r="U8" s="162"/>
-      <c r="V8" s="158"/>
-      <c r="W8" s="157">
+      <c r="P8" s="160"/>
+      <c r="Q8" s="160"/>
+      <c r="R8" s="160"/>
+      <c r="S8" s="160"/>
+      <c r="T8" s="160"/>
+      <c r="U8" s="160"/>
+      <c r="V8" s="159"/>
+      <c r="W8" s="158">
         <f ca="1">O8+1</f>
         <v>46340</v>
       </c>
-      <c r="X8" s="162"/>
-      <c r="Y8" s="162"/>
-      <c r="Z8" s="162"/>
-      <c r="AA8" s="162"/>
-      <c r="AB8" s="162"/>
-      <c r="AC8" s="162"/>
-      <c r="AD8" s="158"/>
+      <c r="X8" s="160"/>
+      <c r="Y8" s="160"/>
+      <c r="Z8" s="160"/>
+      <c r="AA8" s="160"/>
+      <c r="AB8" s="160"/>
+      <c r="AC8" s="160"/>
+      <c r="AD8" s="159"/>
       <c r="AF8" s="4"/>
     </row>
-    <row r="9" spans="1:36" s="43" customFormat="1" ht="146.5" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:36" s="43" customFormat="1" ht="146.44999999999999" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="42"/>
-      <c r="C9" s="135"/>
-      <c r="D9" s="137"/>
-      <c r="E9" s="145" t="s">
+      <c r="C9" s="83"/>
+      <c r="D9" s="85"/>
+      <c r="E9" s="92" t="s">
+        <v>55</v>
+      </c>
+      <c r="F9" s="85"/>
+      <c r="G9" s="163" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" s="85"/>
+      <c r="I9" s="83" t="s">
+        <v>57</v>
+      </c>
+      <c r="J9" s="85"/>
+      <c r="K9" s="83" t="s">
         <v>58</v>
       </c>
-      <c r="F9" s="137"/>
-      <c r="G9" s="156" t="s">
-        <v>47</v>
-      </c>
-      <c r="H9" s="137"/>
-      <c r="I9" s="135" t="s">
-        <v>60</v>
-      </c>
-      <c r="J9" s="137"/>
-      <c r="K9" s="135" t="s">
-        <v>61</v>
-      </c>
-      <c r="L9" s="136"/>
-      <c r="M9" s="136"/>
-      <c r="N9" s="137"/>
-      <c r="O9" s="164" t="s">
+      <c r="L9" s="84"/>
+      <c r="M9" s="84"/>
+      <c r="N9" s="85"/>
+      <c r="O9" s="161" t="s">
         <v>15</v>
       </c>
-      <c r="P9" s="163"/>
-      <c r="Q9" s="163"/>
-      <c r="R9" s="163"/>
-      <c r="S9" s="163"/>
-      <c r="T9" s="163"/>
-      <c r="U9" s="163"/>
-      <c r="V9" s="122"/>
-      <c r="W9" s="121"/>
-      <c r="X9" s="163"/>
-      <c r="Y9" s="163"/>
-      <c r="Z9" s="163"/>
-      <c r="AA9" s="163"/>
-      <c r="AB9" s="163"/>
-      <c r="AC9" s="163"/>
-      <c r="AD9" s="122"/>
+      <c r="P9" s="157"/>
+      <c r="Q9" s="157"/>
+      <c r="R9" s="157"/>
+      <c r="S9" s="157"/>
+      <c r="T9" s="157"/>
+      <c r="U9" s="157"/>
+      <c r="V9" s="112"/>
+      <c r="W9" s="111"/>
+      <c r="X9" s="157"/>
+      <c r="Y9" s="157"/>
+      <c r="Z9" s="157"/>
+      <c r="AA9" s="157"/>
+      <c r="AB9" s="157"/>
+      <c r="AC9" s="157"/>
+      <c r="AD9" s="112"/>
       <c r="AE9" s="7"/>
       <c r="AF9" s="42"/>
     </row>
-    <row r="10" spans="1:36" s="43" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="42"/>
-      <c r="C10" s="157">
+      <c r="C10" s="158">
         <f ca="1">W8+1</f>
         <v>46341</v>
       </c>
-      <c r="D10" s="158"/>
+      <c r="D10" s="159"/>
       <c r="E10" s="79"/>
       <c r="F10" s="80"/>
       <c r="G10" s="79"/>
@@ -6184,99 +6220,99 @@
       <c r="AE10" s="7"/>
       <c r="AF10" s="42"/>
     </row>
-    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="4"/>
-      <c r="C11" s="157"/>
-      <c r="D11" s="158"/>
-      <c r="E11" s="157">
+      <c r="C11" s="158"/>
+      <c r="D11" s="159"/>
+      <c r="E11" s="158">
         <f ca="1">C10+1</f>
         <v>46342</v>
       </c>
-      <c r="F11" s="158"/>
-      <c r="G11" s="157">
+      <c r="F11" s="159"/>
+      <c r="G11" s="158">
         <f ca="1">E11+1</f>
         <v>46343</v>
       </c>
-      <c r="H11" s="158"/>
-      <c r="I11" s="157">
+      <c r="H11" s="159"/>
+      <c r="I11" s="158">
         <f ca="1">G11+1</f>
         <v>46344</v>
       </c>
-      <c r="J11" s="158"/>
-      <c r="K11" s="157">
+      <c r="J11" s="159"/>
+      <c r="K11" s="158">
         <f ca="1">I11+1</f>
         <v>46345</v>
       </c>
-      <c r="L11" s="162"/>
-      <c r="M11" s="162"/>
+      <c r="L11" s="160"/>
+      <c r="M11" s="160"/>
       <c r="N11" s="78"/>
-      <c r="O11" s="157">
+      <c r="O11" s="158">
         <f ca="1">K11+1</f>
         <v>46346</v>
       </c>
-      <c r="P11" s="162"/>
-      <c r="Q11" s="162"/>
-      <c r="R11" s="162"/>
-      <c r="S11" s="162"/>
-      <c r="T11" s="162"/>
-      <c r="U11" s="162"/>
-      <c r="V11" s="158"/>
-      <c r="W11" s="157">
+      <c r="P11" s="160"/>
+      <c r="Q11" s="160"/>
+      <c r="R11" s="160"/>
+      <c r="S11" s="160"/>
+      <c r="T11" s="160"/>
+      <c r="U11" s="160"/>
+      <c r="V11" s="159"/>
+      <c r="W11" s="158">
         <f ca="1">O11+1</f>
         <v>46347</v>
       </c>
-      <c r="X11" s="162"/>
-      <c r="Y11" s="162"/>
-      <c r="Z11" s="162"/>
-      <c r="AA11" s="162"/>
-      <c r="AB11" s="162"/>
-      <c r="AC11" s="162"/>
-      <c r="AD11" s="158"/>
+      <c r="X11" s="160"/>
+      <c r="Y11" s="160"/>
+      <c r="Z11" s="160"/>
+      <c r="AA11" s="160"/>
+      <c r="AB11" s="160"/>
+      <c r="AC11" s="160"/>
+      <c r="AD11" s="159"/>
       <c r="AF11" s="4"/>
       <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:36" s="43" customFormat="1" ht="134.65" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:36" s="43" customFormat="1" ht="134.65" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="42"/>
-      <c r="C12" s="121"/>
-      <c r="D12" s="122"/>
-      <c r="E12" s="164" t="s">
+      <c r="C12" s="111"/>
+      <c r="D12" s="112"/>
+      <c r="E12" s="161" t="s">
         <v>16</v>
       </c>
-      <c r="F12" s="165"/>
-      <c r="G12" s="121"/>
-      <c r="H12" s="122"/>
-      <c r="I12" s="121"/>
-      <c r="J12" s="122"/>
-      <c r="K12" s="121"/>
-      <c r="L12" s="163"/>
-      <c r="M12" s="163"/>
-      <c r="N12" s="122"/>
-      <c r="O12" s="121"/>
-      <c r="P12" s="163"/>
-      <c r="Q12" s="163"/>
-      <c r="R12" s="163"/>
-      <c r="S12" s="163"/>
-      <c r="T12" s="163"/>
-      <c r="U12" s="163"/>
-      <c r="V12" s="122"/>
-      <c r="W12" s="121"/>
-      <c r="X12" s="163"/>
-      <c r="Y12" s="163"/>
-      <c r="Z12" s="163"/>
-      <c r="AA12" s="163"/>
-      <c r="AB12" s="163"/>
-      <c r="AC12" s="163"/>
-      <c r="AD12" s="122"/>
+      <c r="F12" s="162"/>
+      <c r="G12" s="111"/>
+      <c r="H12" s="112"/>
+      <c r="I12" s="111"/>
+      <c r="J12" s="112"/>
+      <c r="K12" s="111"/>
+      <c r="L12" s="157"/>
+      <c r="M12" s="157"/>
+      <c r="N12" s="112"/>
+      <c r="O12" s="111"/>
+      <c r="P12" s="157"/>
+      <c r="Q12" s="157"/>
+      <c r="R12" s="157"/>
+      <c r="S12" s="157"/>
+      <c r="T12" s="157"/>
+      <c r="U12" s="157"/>
+      <c r="V12" s="112"/>
+      <c r="W12" s="111"/>
+      <c r="X12" s="157"/>
+      <c r="Y12" s="157"/>
+      <c r="Z12" s="157"/>
+      <c r="AA12" s="157"/>
+      <c r="AB12" s="157"/>
+      <c r="AC12" s="157"/>
+      <c r="AD12" s="112"/>
       <c r="AE12" s="7"/>
       <c r="AF12" s="42"/>
     </row>
-    <row r="13" spans="1:36" s="43" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="42"/>
-      <c r="C13" s="157">
+      <c r="C13" s="158">
         <f ca="1">W11+1</f>
         <v>46348</v>
       </c>
-      <c r="D13" s="158"/>
+      <c r="D13" s="159"/>
       <c r="E13" s="79"/>
       <c r="F13" s="80"/>
       <c r="G13" s="79"/>
@@ -6306,102 +6342,102 @@
       <c r="AE13" s="7"/>
       <c r="AF13" s="42"/>
     </row>
-    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:36" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="4"/>
-      <c r="C14" s="157"/>
-      <c r="D14" s="158"/>
-      <c r="E14" s="157">
+      <c r="C14" s="158"/>
+      <c r="D14" s="159"/>
+      <c r="E14" s="158">
         <f ca="1">C13+1</f>
         <v>46349</v>
       </c>
-      <c r="F14" s="158"/>
-      <c r="G14" s="157">
+      <c r="F14" s="159"/>
+      <c r="G14" s="158">
         <f ca="1">E14+1</f>
         <v>46350</v>
       </c>
-      <c r="H14" s="158"/>
-      <c r="I14" s="157">
+      <c r="H14" s="159"/>
+      <c r="I14" s="158">
         <f ca="1">G14+1</f>
         <v>46351</v>
       </c>
-      <c r="J14" s="158"/>
-      <c r="K14" s="157">
+      <c r="J14" s="159"/>
+      <c r="K14" s="158">
         <f ca="1">I14+1</f>
         <v>46352</v>
       </c>
-      <c r="L14" s="162"/>
-      <c r="M14" s="162"/>
+      <c r="L14" s="160"/>
+      <c r="M14" s="160"/>
       <c r="N14" s="78"/>
-      <c r="O14" s="157">
+      <c r="O14" s="158">
         <f ca="1">K14+1</f>
         <v>46353</v>
       </c>
-      <c r="P14" s="162"/>
-      <c r="Q14" s="162"/>
-      <c r="R14" s="162"/>
-      <c r="S14" s="162"/>
-      <c r="T14" s="162"/>
-      <c r="U14" s="162"/>
-      <c r="V14" s="158"/>
-      <c r="W14" s="157">
+      <c r="P14" s="160"/>
+      <c r="Q14" s="160"/>
+      <c r="R14" s="160"/>
+      <c r="S14" s="160"/>
+      <c r="T14" s="160"/>
+      <c r="U14" s="160"/>
+      <c r="V14" s="159"/>
+      <c r="W14" s="158">
         <f ca="1">O14+1</f>
         <v>46354</v>
       </c>
-      <c r="X14" s="162"/>
-      <c r="Y14" s="162"/>
-      <c r="Z14" s="162"/>
-      <c r="AA14" s="162"/>
-      <c r="AB14" s="162"/>
-      <c r="AC14" s="162"/>
-      <c r="AD14" s="158"/>
+      <c r="X14" s="160"/>
+      <c r="Y14" s="160"/>
+      <c r="Z14" s="160"/>
+      <c r="AA14" s="160"/>
+      <c r="AB14" s="160"/>
+      <c r="AC14" s="160"/>
+      <c r="AD14" s="159"/>
       <c r="AF14" s="4"/>
     </row>
-    <row r="15" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:36" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="42"/>
-      <c r="C15" s="121"/>
-      <c r="D15" s="122"/>
-      <c r="E15" s="121"/>
-      <c r="F15" s="122"/>
-      <c r="G15" s="121"/>
-      <c r="H15" s="122"/>
-      <c r="I15" s="121"/>
-      <c r="J15" s="122"/>
-      <c r="K15" s="121"/>
-      <c r="L15" s="163"/>
-      <c r="M15" s="163"/>
-      <c r="N15" s="122"/>
-      <c r="O15" s="121"/>
-      <c r="P15" s="163"/>
-      <c r="Q15" s="163"/>
-      <c r="R15" s="163"/>
-      <c r="S15" s="163"/>
-      <c r="T15" s="163"/>
-      <c r="U15" s="163"/>
-      <c r="V15" s="122"/>
-      <c r="W15" s="121"/>
-      <c r="X15" s="163"/>
-      <c r="Y15" s="163"/>
-      <c r="Z15" s="163"/>
-      <c r="AA15" s="163"/>
-      <c r="AB15" s="163"/>
-      <c r="AC15" s="163"/>
-      <c r="AD15" s="122"/>
+      <c r="C15" s="111"/>
+      <c r="D15" s="112"/>
+      <c r="E15" s="111"/>
+      <c r="F15" s="112"/>
+      <c r="G15" s="111"/>
+      <c r="H15" s="112"/>
+      <c r="I15" s="111"/>
+      <c r="J15" s="112"/>
+      <c r="K15" s="111"/>
+      <c r="L15" s="157"/>
+      <c r="M15" s="157"/>
+      <c r="N15" s="112"/>
+      <c r="O15" s="111"/>
+      <c r="P15" s="157"/>
+      <c r="Q15" s="157"/>
+      <c r="R15" s="157"/>
+      <c r="S15" s="157"/>
+      <c r="T15" s="157"/>
+      <c r="U15" s="157"/>
+      <c r="V15" s="112"/>
+      <c r="W15" s="111"/>
+      <c r="X15" s="157"/>
+      <c r="Y15" s="157"/>
+      <c r="Z15" s="157"/>
+      <c r="AA15" s="157"/>
+      <c r="AB15" s="157"/>
+      <c r="AC15" s="157"/>
+      <c r="AD15" s="112"/>
       <c r="AE15" s="7"/>
       <c r="AF15" s="42"/>
     </row>
-    <row r="16" spans="1:36" s="43" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:36" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="42"/>
-      <c r="C16" s="118">
+      <c r="C16" s="94">
         <f ca="1">W14+1</f>
         <v>46355</v>
       </c>
-      <c r="D16" s="120"/>
+      <c r="D16" s="95"/>
       <c r="E16" s="45"/>
       <c r="F16" s="75"/>
       <c r="G16" s="45"/>
       <c r="H16" s="75"/>
-      <c r="I16" s="153"/>
-      <c r="J16" s="154"/>
+      <c r="I16" s="148"/>
+      <c r="J16" s="149"/>
       <c r="K16" s="66"/>
       <c r="L16" s="68"/>
       <c r="M16" s="68"/>
@@ -6425,103 +6461,103 @@
       <c r="AE16" s="7"/>
       <c r="AF16" s="42"/>
     </row>
-    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="4"/>
-      <c r="C17" s="118"/>
-      <c r="D17" s="120"/>
-      <c r="E17" s="132">
+      <c r="C17" s="94"/>
+      <c r="D17" s="95"/>
+      <c r="E17" s="96">
         <f ca="1">C16+1</f>
         <v>46356</v>
       </c>
-      <c r="F17" s="133"/>
-      <c r="G17" s="132">
+      <c r="F17" s="97"/>
+      <c r="G17" s="96">
         <f ca="1">E17+1</f>
         <v>46357</v>
       </c>
-      <c r="H17" s="133"/>
-      <c r="I17" s="132">
+      <c r="H17" s="97"/>
+      <c r="I17" s="96">
         <f ca="1">G17+1</f>
         <v>46358</v>
       </c>
-      <c r="J17" s="133"/>
-      <c r="K17" s="132">
+      <c r="J17" s="97"/>
+      <c r="K17" s="96">
         <f ca="1">I17+1</f>
         <v>46359</v>
       </c>
-      <c r="L17" s="134"/>
-      <c r="M17" s="134"/>
-      <c r="N17" s="133"/>
-      <c r="O17" s="132">
+      <c r="L17" s="98"/>
+      <c r="M17" s="98"/>
+      <c r="N17" s="97"/>
+      <c r="O17" s="96">
         <f ca="1">K17+1</f>
         <v>46360</v>
       </c>
-      <c r="P17" s="134"/>
-      <c r="Q17" s="134"/>
-      <c r="R17" s="134"/>
-      <c r="S17" s="134"/>
-      <c r="T17" s="134"/>
-      <c r="U17" s="134"/>
-      <c r="V17" s="133"/>
-      <c r="W17" s="132">
+      <c r="P17" s="98"/>
+      <c r="Q17" s="98"/>
+      <c r="R17" s="98"/>
+      <c r="S17" s="98"/>
+      <c r="T17" s="98"/>
+      <c r="U17" s="98"/>
+      <c r="V17" s="97"/>
+      <c r="W17" s="96">
         <f ca="1">O17+1</f>
         <v>46361</v>
       </c>
-      <c r="X17" s="134"/>
-      <c r="Y17" s="134"/>
-      <c r="Z17" s="134"/>
-      <c r="AA17" s="134"/>
-      <c r="AB17" s="134"/>
-      <c r="AC17" s="134"/>
-      <c r="AD17" s="133"/>
+      <c r="X17" s="98"/>
+      <c r="Y17" s="98"/>
+      <c r="Z17" s="98"/>
+      <c r="AA17" s="98"/>
+      <c r="AB17" s="98"/>
+      <c r="AC17" s="98"/>
+      <c r="AD17" s="97"/>
       <c r="AF17" s="4"/>
     </row>
-    <row r="18" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="42"/>
-      <c r="C18" s="111"/>
-      <c r="D18" s="113"/>
-      <c r="E18" s="111"/>
-      <c r="F18" s="113"/>
-      <c r="G18" s="111"/>
-      <c r="H18" s="113"/>
-      <c r="I18" s="111"/>
-      <c r="J18" s="113"/>
-      <c r="K18" s="111"/>
-      <c r="L18" s="112"/>
-      <c r="M18" s="112"/>
-      <c r="N18" s="113"/>
-      <c r="O18" s="111"/>
-      <c r="P18" s="112"/>
-      <c r="Q18" s="112"/>
-      <c r="R18" s="112"/>
-      <c r="S18" s="112"/>
-      <c r="T18" s="112"/>
-      <c r="U18" s="112"/>
-      <c r="V18" s="113"/>
-      <c r="W18" s="111"/>
-      <c r="X18" s="112"/>
-      <c r="Y18" s="112"/>
-      <c r="Z18" s="112"/>
-      <c r="AA18" s="112"/>
-      <c r="AB18" s="112"/>
-      <c r="AC18" s="112"/>
-      <c r="AD18" s="113"/>
+      <c r="C18" s="99"/>
+      <c r="D18" s="100"/>
+      <c r="E18" s="99"/>
+      <c r="F18" s="100"/>
+      <c r="G18" s="99"/>
+      <c r="H18" s="100"/>
+      <c r="I18" s="99"/>
+      <c r="J18" s="100"/>
+      <c r="K18" s="99"/>
+      <c r="L18" s="146"/>
+      <c r="M18" s="146"/>
+      <c r="N18" s="100"/>
+      <c r="O18" s="99"/>
+      <c r="P18" s="146"/>
+      <c r="Q18" s="146"/>
+      <c r="R18" s="146"/>
+      <c r="S18" s="146"/>
+      <c r="T18" s="146"/>
+      <c r="U18" s="146"/>
+      <c r="V18" s="100"/>
+      <c r="W18" s="99"/>
+      <c r="X18" s="146"/>
+      <c r="Y18" s="146"/>
+      <c r="Z18" s="146"/>
+      <c r="AA18" s="146"/>
+      <c r="AB18" s="146"/>
+      <c r="AC18" s="146"/>
+      <c r="AD18" s="100"/>
       <c r="AE18" s="7"/>
       <c r="AF18" s="42"/>
       <c r="AP18" s="3"/>
     </row>
-    <row r="19" spans="1:42" s="43" customFormat="1" ht="10" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:42" s="43" customFormat="1" ht="9.9499999999999993" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="42"/>
-      <c r="C19" s="118">
+      <c r="C19" s="94">
         <f ca="1">W17+1</f>
         <v>46362</v>
       </c>
-      <c r="D19" s="120"/>
+      <c r="D19" s="95"/>
       <c r="E19" s="45"/>
       <c r="F19" s="75"/>
       <c r="G19" s="45"/>
       <c r="H19" s="75"/>
-      <c r="I19" s="153"/>
-      <c r="J19" s="154"/>
+      <c r="I19" s="148"/>
+      <c r="J19" s="149"/>
       <c r="K19" s="66"/>
       <c r="L19" s="68"/>
       <c r="M19" s="68"/>
@@ -6545,91 +6581,91 @@
       <c r="AE19" s="7"/>
       <c r="AF19" s="42"/>
     </row>
-    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:42" s="7" customFormat="1" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="4"/>
-      <c r="C20" s="118"/>
-      <c r="D20" s="120"/>
-      <c r="E20" s="132">
+      <c r="C20" s="94"/>
+      <c r="D20" s="95"/>
+      <c r="E20" s="96">
         <f ca="1">C19+1</f>
         <v>46363</v>
       </c>
-      <c r="F20" s="133"/>
-      <c r="G20" s="132">
+      <c r="F20" s="97"/>
+      <c r="G20" s="96">
         <f ca="1">E20+1</f>
         <v>46364</v>
       </c>
-      <c r="H20" s="133"/>
-      <c r="I20" s="132">
+      <c r="H20" s="97"/>
+      <c r="I20" s="96">
         <f ca="1">G20+1</f>
         <v>46365</v>
       </c>
-      <c r="J20" s="133"/>
-      <c r="K20" s="132">
+      <c r="J20" s="97"/>
+      <c r="K20" s="96">
         <f ca="1">I20+1</f>
         <v>46366</v>
       </c>
-      <c r="L20" s="134"/>
-      <c r="M20" s="134"/>
-      <c r="N20" s="133"/>
-      <c r="O20" s="132">
+      <c r="L20" s="98"/>
+      <c r="M20" s="98"/>
+      <c r="N20" s="97"/>
+      <c r="O20" s="96">
         <f ca="1">K20+1</f>
         <v>46367</v>
       </c>
-      <c r="P20" s="134"/>
-      <c r="Q20" s="134"/>
-      <c r="R20" s="134"/>
-      <c r="S20" s="134"/>
-      <c r="T20" s="134"/>
-      <c r="U20" s="134"/>
-      <c r="V20" s="133"/>
-      <c r="W20" s="132">
+      <c r="P20" s="98"/>
+      <c r="Q20" s="98"/>
+      <c r="R20" s="98"/>
+      <c r="S20" s="98"/>
+      <c r="T20" s="98"/>
+      <c r="U20" s="98"/>
+      <c r="V20" s="97"/>
+      <c r="W20" s="96">
         <f ca="1">O20+1</f>
         <v>46368</v>
       </c>
-      <c r="X20" s="134"/>
-      <c r="Y20" s="134"/>
-      <c r="Z20" s="134"/>
-      <c r="AA20" s="134"/>
-      <c r="AB20" s="134"/>
-      <c r="AC20" s="134"/>
-      <c r="AD20" s="133"/>
+      <c r="X20" s="98"/>
+      <c r="Y20" s="98"/>
+      <c r="Z20" s="98"/>
+      <c r="AA20" s="98"/>
+      <c r="AB20" s="98"/>
+      <c r="AC20" s="98"/>
+      <c r="AD20" s="97"/>
       <c r="AF20" s="4"/>
     </row>
-    <row r="21" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:42" s="43" customFormat="1" ht="75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="42"/>
-      <c r="C21" s="111"/>
-      <c r="D21" s="113"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="113"/>
-      <c r="G21" s="111"/>
-      <c r="H21" s="113"/>
-      <c r="I21" s="111"/>
-      <c r="J21" s="113"/>
-      <c r="K21" s="111"/>
-      <c r="L21" s="112"/>
-      <c r="M21" s="112"/>
-      <c r="N21" s="113"/>
-      <c r="O21" s="111"/>
-      <c r="P21" s="112"/>
-      <c r="Q21" s="112"/>
-      <c r="R21" s="112"/>
-      <c r="S21" s="112"/>
-      <c r="T21" s="112"/>
-      <c r="U21" s="112"/>
-      <c r="V21" s="113"/>
-      <c r="W21" s="111"/>
-      <c r="X21" s="112"/>
-      <c r="Y21" s="112"/>
-      <c r="Z21" s="112"/>
-      <c r="AA21" s="112"/>
-      <c r="AB21" s="112"/>
-      <c r="AC21" s="112"/>
-      <c r="AD21" s="113"/>
+      <c r="C21" s="99"/>
+      <c r="D21" s="100"/>
+      <c r="E21" s="99"/>
+      <c r="F21" s="100"/>
+      <c r="G21" s="99"/>
+      <c r="H21" s="100"/>
+      <c r="I21" s="99"/>
+      <c r="J21" s="100"/>
+      <c r="K21" s="99"/>
+      <c r="L21" s="146"/>
+      <c r="M21" s="146"/>
+      <c r="N21" s="100"/>
+      <c r="O21" s="99"/>
+      <c r="P21" s="146"/>
+      <c r="Q21" s="146"/>
+      <c r="R21" s="146"/>
+      <c r="S21" s="146"/>
+      <c r="T21" s="146"/>
+      <c r="U21" s="146"/>
+      <c r="V21" s="100"/>
+      <c r="W21" s="99"/>
+      <c r="X21" s="146"/>
+      <c r="Y21" s="146"/>
+      <c r="Z21" s="146"/>
+      <c r="AA21" s="146"/>
+      <c r="AB21" s="146"/>
+      <c r="AC21" s="146"/>
+      <c r="AD21" s="100"/>
       <c r="AE21" s="7"/>
       <c r="AF21" s="42"/>
       <c r="AP21" s="3"/>
     </row>
-    <row r="22" spans="1:42" s="7" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:42" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A22" s="4"/>
       <c r="C22" s="52"/>
       <c r="D22" s="52"/>
@@ -6661,7 +6697,7 @@
       <c r="AD22" s="55"/>
       <c r="AF22" s="4"/>
     </row>
-    <row r="23" spans="1:42" s="7" customFormat="1" ht="25" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:42" s="7" customFormat="1" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="4"/>
       <c r="B23" s="4"/>
       <c r="C23" s="56"/>
@@ -6695,61 +6731,61 @@
       <c r="AE23" s="4"/>
       <c r="AF23" s="4"/>
     </row>
-    <row r="24" spans="1:42" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:42" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A24" s="1"/>
       <c r="M24" s="1"/>
       <c r="AF24" s="1"/>
     </row>
-    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:42" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A25" s="1"/>
-      <c r="C25" s="143" t="s">
+      <c r="C25" s="86" t="s">
         <v>0</v>
       </c>
-      <c r="D25" s="143"/>
-      <c r="E25" s="143"/>
-      <c r="F25" s="143"/>
-      <c r="G25" s="143"/>
-      <c r="H25" s="143"/>
-      <c r="I25" s="143"/>
-      <c r="J25" s="143"/>
-      <c r="K25" s="143"/>
+      <c r="D25" s="86"/>
+      <c r="E25" s="86"/>
+      <c r="F25" s="86"/>
+      <c r="G25" s="86"/>
+      <c r="H25" s="86"/>
+      <c r="I25" s="86"/>
+      <c r="J25" s="86"/>
+      <c r="K25" s="86"/>
       <c r="L25" s="60"/>
       <c r="M25" s="1"/>
-      <c r="O25" s="144">
+      <c r="O25" s="87">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)-1,1)</f>
         <v>46296</v>
       </c>
-      <c r="P25" s="144"/>
-      <c r="Q25" s="144"/>
-      <c r="R25" s="144"/>
-      <c r="S25" s="144"/>
-      <c r="T25" s="144"/>
-      <c r="U25" s="144"/>
+      <c r="P25" s="87"/>
+      <c r="Q25" s="87"/>
+      <c r="R25" s="87"/>
+      <c r="S25" s="87"/>
+      <c r="T25" s="87"/>
+      <c r="U25" s="87"/>
       <c r="V25" s="61"/>
       <c r="W25" s="61"/>
-      <c r="X25" s="144">
+      <c r="X25" s="87">
         <f ca="1">DATE(YEAR(C2),MONTH(C2)+1,1)</f>
         <v>46357</v>
       </c>
-      <c r="Y25" s="144"/>
-      <c r="Z25" s="144"/>
-      <c r="AA25" s="144"/>
-      <c r="AB25" s="144"/>
-      <c r="AC25" s="144"/>
-      <c r="AD25" s="144"/>
+      <c r="Y25" s="87"/>
+      <c r="Z25" s="87"/>
+      <c r="AA25" s="87"/>
+      <c r="AB25" s="87"/>
+      <c r="AC25" s="87"/>
+      <c r="AD25" s="87"/>
       <c r="AF25" s="1"/>
     </row>
-    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="26" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A26" s="1"/>
-      <c r="C26" s="143"/>
-      <c r="D26" s="143"/>
-      <c r="E26" s="143"/>
-      <c r="F26" s="143"/>
-      <c r="G26" s="143"/>
-      <c r="H26" s="143"/>
-      <c r="I26" s="143"/>
-      <c r="J26" s="143"/>
-      <c r="K26" s="143"/>
+      <c r="C26" s="86"/>
+      <c r="D26" s="86"/>
+      <c r="E26" s="86"/>
+      <c r="F26" s="86"/>
+      <c r="G26" s="86"/>
+      <c r="H26" s="86"/>
+      <c r="I26" s="86"/>
+      <c r="J26" s="86"/>
+      <c r="K26" s="86"/>
       <c r="L26" s="60"/>
       <c r="M26" s="1"/>
       <c r="O26" s="62" t="str">
@@ -6812,17 +6848,17 @@
       </c>
       <c r="AF26" s="1"/>
     </row>
-    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="27" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A27" s="1"/>
-      <c r="C27" s="115"/>
-      <c r="D27" s="115"/>
-      <c r="E27" s="115"/>
-      <c r="F27" s="115"/>
-      <c r="G27" s="115"/>
-      <c r="H27" s="115"/>
-      <c r="I27" s="115"/>
-      <c r="J27" s="115"/>
-      <c r="K27" s="115"/>
+      <c r="C27" s="88"/>
+      <c r="D27" s="88"/>
+      <c r="E27" s="88"/>
+      <c r="F27" s="88"/>
+      <c r="G27" s="88"/>
+      <c r="H27" s="88"/>
+      <c r="I27" s="88"/>
+      <c r="J27" s="88"/>
+      <c r="K27" s="88"/>
       <c r="M27" s="1"/>
       <c r="O27" s="64" t="str">
         <f t="shared" ref="O27:U32" ca="1" si="0">IF(MONTH($O$25)&lt;&gt;MONTH($O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1)),"",$O$25-(WEEKDAY($O$25,1)-(start_day-1))-IF((WEEKDAY($O$25,1)-(start_day-1))&lt;=0,7,0)+(ROW(O27)-ROW($O$27))*7+(COLUMN(O27)-COLUMN($O$27)+1))</f>
@@ -6884,17 +6920,17 @@
       </c>
       <c r="AF27" s="1"/>
     </row>
-    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="28" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="1"/>
-      <c r="C28" s="114"/>
-      <c r="D28" s="114"/>
-      <c r="E28" s="114"/>
-      <c r="F28" s="114"/>
-      <c r="G28" s="114"/>
-      <c r="H28" s="114"/>
-      <c r="I28" s="114"/>
-      <c r="J28" s="114"/>
-      <c r="K28" s="114"/>
+      <c r="C28" s="89"/>
+      <c r="D28" s="89"/>
+      <c r="E28" s="89"/>
+      <c r="F28" s="89"/>
+      <c r="G28" s="89"/>
+      <c r="H28" s="89"/>
+      <c r="I28" s="89"/>
+      <c r="J28" s="89"/>
+      <c r="K28" s="89"/>
       <c r="M28" s="1"/>
       <c r="O28" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -6956,17 +6992,17 @@
       </c>
       <c r="AF28" s="1"/>
     </row>
-    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="29" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A29" s="1"/>
-      <c r="C29" s="115"/>
-      <c r="D29" s="115"/>
-      <c r="E29" s="115"/>
-      <c r="F29" s="115"/>
-      <c r="G29" s="115"/>
-      <c r="H29" s="115"/>
-      <c r="I29" s="115"/>
-      <c r="J29" s="115"/>
-      <c r="K29" s="115"/>
+      <c r="C29" s="88"/>
+      <c r="D29" s="88"/>
+      <c r="E29" s="88"/>
+      <c r="F29" s="88"/>
+      <c r="G29" s="88"/>
+      <c r="H29" s="88"/>
+      <c r="I29" s="88"/>
+      <c r="J29" s="88"/>
+      <c r="K29" s="88"/>
       <c r="M29" s="1"/>
       <c r="O29" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -7028,17 +7064,17 @@
       </c>
       <c r="AF29" s="1"/>
     </row>
-    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="30" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A30" s="1"/>
-      <c r="C30" s="114"/>
-      <c r="D30" s="114"/>
-      <c r="E30" s="114"/>
-      <c r="F30" s="114"/>
-      <c r="G30" s="114"/>
-      <c r="H30" s="114"/>
-      <c r="I30" s="114"/>
-      <c r="J30" s="114"/>
-      <c r="K30" s="114"/>
+      <c r="C30" s="89"/>
+      <c r="D30" s="89"/>
+      <c r="E30" s="89"/>
+      <c r="F30" s="89"/>
+      <c r="G30" s="89"/>
+      <c r="H30" s="89"/>
+      <c r="I30" s="89"/>
+      <c r="J30" s="89"/>
+      <c r="K30" s="89"/>
       <c r="M30" s="1"/>
       <c r="O30" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -7100,17 +7136,17 @@
       </c>
       <c r="AF30" s="1"/>
     </row>
-    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="31" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="1"/>
-      <c r="C31" s="115"/>
-      <c r="D31" s="115"/>
-      <c r="E31" s="115"/>
-      <c r="F31" s="115"/>
-      <c r="G31" s="115"/>
-      <c r="H31" s="115"/>
-      <c r="I31" s="115"/>
-      <c r="J31" s="115"/>
-      <c r="K31" s="115"/>
+      <c r="C31" s="88"/>
+      <c r="D31" s="88"/>
+      <c r="E31" s="88"/>
+      <c r="F31" s="88"/>
+      <c r="G31" s="88"/>
+      <c r="H31" s="88"/>
+      <c r="I31" s="88"/>
+      <c r="J31" s="88"/>
+      <c r="K31" s="88"/>
       <c r="M31" s="1"/>
       <c r="O31" s="64">
         <f t="shared" ca="1" si="0"/>
@@ -7172,7 +7208,7 @@
       </c>
       <c r="AF31" s="1"/>
     </row>
-    <row r="32" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="32" spans="1:42" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A32" s="1"/>
       <c r="C32" s="77"/>
       <c r="D32" s="77"/>
@@ -7244,12 +7280,12 @@
       </c>
       <c r="AF32" s="1"/>
     </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:32" x14ac:dyDescent="0.2">
       <c r="A33" s="1"/>
       <c r="M33" s="1"/>
       <c r="AF33" s="1"/>
     </row>
-    <row r="34" spans="1:32" ht="25" customHeight="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:32" ht="24.95" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A34" s="1"/>
       <c r="B34" s="1"/>
       <c r="C34" s="1"/>
@@ -7283,130 +7319,100 @@
       <c r="AE34" s="1"/>
       <c r="AF34" s="1"/>
     </row>
-    <row r="37" spans="1:32" ht="12.9" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="38" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D38" s="83" t="s">
+    <row r="37" spans="1:32" ht="13.5" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="38" spans="1:32" ht="12.6" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="D38" s="118" t="s">
         <v>23</v>
       </c>
-      <c r="E38" s="84"/>
-      <c r="F38" s="85"/>
-      <c r="G38" s="89">
+      <c r="E38" s="119"/>
+      <c r="F38" s="120"/>
+      <c r="G38" s="124">
         <f ca="1">ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0)</f>
         <v>5</v>
       </c>
-      <c r="H38" s="90"/>
-      <c r="I38" s="83" t="s">
+      <c r="H38" s="125"/>
+      <c r="I38" s="118" t="s">
         <v>26</v>
       </c>
-      <c r="J38" s="93"/>
-      <c r="K38" s="95" t="s">
+      <c r="J38" s="128"/>
+      <c r="K38" s="130" t="s">
         <v>24</v>
       </c>
-      <c r="L38" s="96"/>
-      <c r="M38" s="99">
+      <c r="L38" s="131"/>
+      <c r="M38" s="134">
         <f ca="1">7*(((DATE(2026,11,13)-TODAY())/7)-ROUNDDOWN((DATE(2026,11,13)-TODAY())/7,0))</f>
         <v>1.0000000000000027</v>
       </c>
-      <c r="N38" s="100"/>
-      <c r="O38" s="100"/>
-      <c r="P38" s="100"/>
-      <c r="Q38" s="100"/>
-      <c r="R38" s="101"/>
-      <c r="S38" s="105" t="s">
+      <c r="N38" s="135"/>
+      <c r="O38" s="135"/>
+      <c r="P38" s="135"/>
+      <c r="Q38" s="135"/>
+      <c r="R38" s="136"/>
+      <c r="S38" s="140" t="s">
         <v>25</v>
       </c>
-      <c r="T38" s="106"/>
-      <c r="U38" s="106"/>
-      <c r="V38" s="106"/>
-      <c r="W38" s="106"/>
-      <c r="X38" s="107"/>
-    </row>
-    <row r="39" spans="1:32" ht="13" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D39" s="86"/>
-      <c r="E39" s="87"/>
-      <c r="F39" s="88"/>
-      <c r="G39" s="91"/>
-      <c r="H39" s="92"/>
-      <c r="I39" s="86"/>
-      <c r="J39" s="94"/>
-      <c r="K39" s="97"/>
-      <c r="L39" s="98"/>
-      <c r="M39" s="102"/>
-      <c r="N39" s="103"/>
-      <c r="O39" s="103"/>
-      <c r="P39" s="103"/>
-      <c r="Q39" s="103"/>
-      <c r="R39" s="104"/>
-      <c r="S39" s="108"/>
-      <c r="T39" s="109"/>
-      <c r="U39" s="109"/>
-      <c r="V39" s="109"/>
-      <c r="W39" s="109"/>
-      <c r="X39" s="110"/>
+      <c r="T38" s="141"/>
+      <c r="U38" s="141"/>
+      <c r="V38" s="141"/>
+      <c r="W38" s="141"/>
+      <c r="X38" s="142"/>
+    </row>
+    <row r="39" spans="1:32" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="D39" s="121"/>
+      <c r="E39" s="122"/>
+      <c r="F39" s="123"/>
+      <c r="G39" s="126"/>
+      <c r="H39" s="127"/>
+      <c r="I39" s="121"/>
+      <c r="J39" s="129"/>
+      <c r="K39" s="132"/>
+      <c r="L39" s="133"/>
+      <c r="M39" s="137"/>
+      <c r="N39" s="138"/>
+      <c r="O39" s="138"/>
+      <c r="P39" s="138"/>
+      <c r="Q39" s="138"/>
+      <c r="R39" s="139"/>
+      <c r="S39" s="143"/>
+      <c r="T39" s="144"/>
+      <c r="U39" s="144"/>
+      <c r="V39" s="144"/>
+      <c r="W39" s="144"/>
+      <c r="X39" s="145"/>
     </row>
   </sheetData>
   <mergeCells count="112">
-    <mergeCell ref="K18:N18"/>
-    <mergeCell ref="W18:AD18"/>
-    <mergeCell ref="C25:K26"/>
-    <mergeCell ref="O25:U25"/>
-    <mergeCell ref="X25:AD25"/>
-    <mergeCell ref="C27:K27"/>
-    <mergeCell ref="C28:K29"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="E18:F18"/>
-    <mergeCell ref="G18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="O18:V18"/>
-    <mergeCell ref="C19:D20"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="E20:F20"/>
-    <mergeCell ref="G20:H20"/>
-    <mergeCell ref="I20:J20"/>
-    <mergeCell ref="K20:N20"/>
-    <mergeCell ref="W15:AD15"/>
-    <mergeCell ref="C16:D17"/>
-    <mergeCell ref="E17:F17"/>
-    <mergeCell ref="G17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="O17:V17"/>
-    <mergeCell ref="W17:AD17"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="E15:F15"/>
-    <mergeCell ref="G15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="O15:V15"/>
-    <mergeCell ref="K15:N15"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="K17:N17"/>
-    <mergeCell ref="W12:AD12"/>
-    <mergeCell ref="C13:D14"/>
-    <mergeCell ref="E14:F14"/>
-    <mergeCell ref="G14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="K14:M14"/>
-    <mergeCell ref="O14:V14"/>
-    <mergeCell ref="W14:AD14"/>
-    <mergeCell ref="C12:D12"/>
-    <mergeCell ref="E12:F12"/>
-    <mergeCell ref="G12:H12"/>
-    <mergeCell ref="I12:J12"/>
-    <mergeCell ref="O12:V12"/>
-    <mergeCell ref="K12:N12"/>
-    <mergeCell ref="W9:AD9"/>
-    <mergeCell ref="C10:D11"/>
-    <mergeCell ref="E11:F11"/>
-    <mergeCell ref="G11:H11"/>
-    <mergeCell ref="I11:J11"/>
-    <mergeCell ref="K11:M11"/>
-    <mergeCell ref="O11:V11"/>
-    <mergeCell ref="W11:AD11"/>
-    <mergeCell ref="C9:D9"/>
-    <mergeCell ref="E9:F9"/>
-    <mergeCell ref="G9:H9"/>
-    <mergeCell ref="I9:J9"/>
-    <mergeCell ref="O9:V9"/>
-    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="D38:F39"/>
+    <mergeCell ref="G38:H39"/>
+    <mergeCell ref="I38:J39"/>
+    <mergeCell ref="K38:L39"/>
+    <mergeCell ref="M38:R39"/>
+    <mergeCell ref="S38:X39"/>
+    <mergeCell ref="C30:K31"/>
+    <mergeCell ref="O20:V20"/>
+    <mergeCell ref="W20:AD20"/>
+    <mergeCell ref="C21:D21"/>
+    <mergeCell ref="E21:F21"/>
+    <mergeCell ref="G21:H21"/>
+    <mergeCell ref="I21:J21"/>
+    <mergeCell ref="K21:N21"/>
+    <mergeCell ref="O21:V21"/>
+    <mergeCell ref="W21:AD21"/>
+    <mergeCell ref="C2:AD2"/>
+    <mergeCell ref="C4:D4"/>
+    <mergeCell ref="E4:F4"/>
+    <mergeCell ref="G4:H4"/>
+    <mergeCell ref="I4:J4"/>
+    <mergeCell ref="K4:M4"/>
+    <mergeCell ref="O4:V4"/>
+    <mergeCell ref="W4:AD4"/>
+    <mergeCell ref="W5:AD5"/>
+    <mergeCell ref="C5:D5"/>
+    <mergeCell ref="E5:F5"/>
+    <mergeCell ref="G5:H5"/>
+    <mergeCell ref="I5:J5"/>
+    <mergeCell ref="K5:M5"/>
+    <mergeCell ref="O5:V5"/>
     <mergeCell ref="K6:N6"/>
     <mergeCell ref="C7:D8"/>
     <mergeCell ref="E7:F7"/>
@@ -7427,37 +7433,67 @@
     <mergeCell ref="I6:J6"/>
     <mergeCell ref="O6:V6"/>
     <mergeCell ref="W6:AD6"/>
-    <mergeCell ref="C2:AD2"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="E4:F4"/>
-    <mergeCell ref="G4:H4"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="K4:M4"/>
-    <mergeCell ref="O4:V4"/>
-    <mergeCell ref="W4:AD4"/>
-    <mergeCell ref="W5:AD5"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="E5:F5"/>
-    <mergeCell ref="G5:H5"/>
-    <mergeCell ref="I5:J5"/>
-    <mergeCell ref="K5:M5"/>
-    <mergeCell ref="O5:V5"/>
-    <mergeCell ref="D38:F39"/>
-    <mergeCell ref="G38:H39"/>
-    <mergeCell ref="I38:J39"/>
-    <mergeCell ref="K38:L39"/>
-    <mergeCell ref="M38:R39"/>
-    <mergeCell ref="S38:X39"/>
-    <mergeCell ref="C30:K31"/>
-    <mergeCell ref="O20:V20"/>
-    <mergeCell ref="W20:AD20"/>
-    <mergeCell ref="C21:D21"/>
-    <mergeCell ref="E21:F21"/>
-    <mergeCell ref="G21:H21"/>
-    <mergeCell ref="I21:J21"/>
-    <mergeCell ref="K21:N21"/>
-    <mergeCell ref="O21:V21"/>
-    <mergeCell ref="W21:AD21"/>
+    <mergeCell ref="W9:AD9"/>
+    <mergeCell ref="C10:D11"/>
+    <mergeCell ref="E11:F11"/>
+    <mergeCell ref="G11:H11"/>
+    <mergeCell ref="I11:J11"/>
+    <mergeCell ref="K11:M11"/>
+    <mergeCell ref="O11:V11"/>
+    <mergeCell ref="W11:AD11"/>
+    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="E9:F9"/>
+    <mergeCell ref="G9:H9"/>
+    <mergeCell ref="I9:J9"/>
+    <mergeCell ref="O9:V9"/>
+    <mergeCell ref="K9:N9"/>
+    <mergeCell ref="W12:AD12"/>
+    <mergeCell ref="C13:D14"/>
+    <mergeCell ref="E14:F14"/>
+    <mergeCell ref="G14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="K14:M14"/>
+    <mergeCell ref="O14:V14"/>
+    <mergeCell ref="W14:AD14"/>
+    <mergeCell ref="C12:D12"/>
+    <mergeCell ref="E12:F12"/>
+    <mergeCell ref="G12:H12"/>
+    <mergeCell ref="I12:J12"/>
+    <mergeCell ref="O12:V12"/>
+    <mergeCell ref="K12:N12"/>
+    <mergeCell ref="W15:AD15"/>
+    <mergeCell ref="C16:D17"/>
+    <mergeCell ref="E17:F17"/>
+    <mergeCell ref="G17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="O17:V17"/>
+    <mergeCell ref="W17:AD17"/>
+    <mergeCell ref="C15:D15"/>
+    <mergeCell ref="E15:F15"/>
+    <mergeCell ref="G15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="O15:V15"/>
+    <mergeCell ref="K15:N15"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="K17:N17"/>
+    <mergeCell ref="K18:N18"/>
+    <mergeCell ref="W18:AD18"/>
+    <mergeCell ref="C25:K26"/>
+    <mergeCell ref="O25:U25"/>
+    <mergeCell ref="X25:AD25"/>
+    <mergeCell ref="C27:K27"/>
+    <mergeCell ref="C28:K29"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="E18:F18"/>
+    <mergeCell ref="G18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="O18:V18"/>
+    <mergeCell ref="C19:D20"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="E20:F20"/>
+    <mergeCell ref="G20:H20"/>
+    <mergeCell ref="I20:J20"/>
+    <mergeCell ref="K20:N20"/>
   </mergeCells>
   <conditionalFormatting sqref="C5 E5 G5 I5 K5:L5 O5 W5 C7 E8 G8 I8 K8:L8 O8 W8 C10 E11 G11 I11 K11:L11 O11 W11 C13 E14 G14 I14 K14:L14 O14 W14 C16 E17 G17 I17 K17 O17 W17">
     <cfRule type="expression" dxfId="3" priority="3">
@@ -7491,6 +7527,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement>
     <_ip_UnifiedCompliancePolicyUIAction xmlns="http://schemas.microsoft.com/sharepoint/v3" xsi:nil="true"/>
@@ -7508,15 +7553,6 @@
     <MediaServiceKeyPoints xmlns="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5" xsi:nil="true"/>
   </documentManagement>
 </p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -7838,6 +7874,14 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F0D3479-5903-425F-9669-62B4E7216DE9}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{0B201CC6-7A0A-429C-B445-7EDA1CF4A1D7}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
@@ -7845,14 +7889,6 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3"/>
     <ds:schemaRef ds:uri="71af3243-3dd4-4a8d-8c0d-dd76da1f02a5"/>
     <ds:schemaRef ds:uri="230e9df3-be65-4c73-a93b-d1236ebd677e"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7F0D3479-5903-425F-9669-62B4E7216DE9}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
